--- a/public/REM/raw/REM.xlsx
+++ b/public/REM/raw/REM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcranet.sharepoint.com/sites/REM/Documentos compartidos/REM/Publicación/Pagina WEB/2026/25 01 Ene/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcranet.sharepoint.com/sites/REM/Documentos compartidos/REM/Publicación/Pagina WEB/2026/26 02 Feb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{563D5886-1088-4C76-92B3-92AAC244057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="8_{563D5886-1088-4C76-92B3-92AAC244057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6C4A1AC-8CCC-4547-99F3-2187D6A0D046}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A5F0209-F8EA-4E2B-A469-F799AD0A214D}"/>
   </bookViews>
@@ -19,11 +19,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Cuadros de resultados'!$B$2:$M$112</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Resultados TOP 10'!$B$2:$M$87</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Resultados TOP 10'!$B$2:$M$86</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Cuadros de resultados'!$2:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Resultados TOP 10'!$2:$4</definedName>
   </definedNames>
-  <calcPr calcId="191028" iterate="1"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -184,34 +184,36 @@
     <t>% de la PEA; Trim. IV-27</t>
   </si>
   <si>
-    <t>var. % i.a.; ene-27</t>
+    <t>Relevamiento de Expectativas de Mercado (REM)  Top 10 - BCRA - Febrero 2026</t>
   </si>
   <si>
-    <t>Relevamiento de Expectativas de Mercado (REM)  Top 10 - BCRA - Enero 2026</t>
+    <t>var. % i.a.; feb-27</t>
   </si>
   <si>
-    <t>var. % i.a.; ene-28</t>
+    <t>TNA; %; feb-27</t>
   </si>
   <si>
-    <t>TNA; %; ene-27</t>
+    <t>$/USD; feb-27</t>
   </si>
   <si>
-    <t>$/USD; ene-27</t>
+    <t>Fuente: REM - BCRA (feb-26)</t>
   </si>
   <si>
-    <t>Fuente: REM - BCRA (ene-26)</t>
+    <t>Relevamiento de Expectativas de Mercado (REM)  - BCRA - Febrero 2026</t>
   </si>
   <si>
-    <t>Relevamiento de Expectativas de Mercado (REM)  - BCRA - Enero 2026</t>
+    <t>var. % i.a.; feb-28</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -287,7 +289,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -390,29 +392,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -500,7 +488,15 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -509,37 +505,39 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
+    <cellStyle name="Millares" xfId="4" builtinId="3"/>
     <cellStyle name="Millares 2" xfId="1" xr:uid="{E1EAF663-1358-40F2-AE07-51712904DA28}"/>
     <cellStyle name="Millares 2 2" xfId="2" xr:uid="{E0690555-5B9A-4C29-B9FC-5B57FD1C99F4}"/>
     <cellStyle name="Millares 3" xfId="3" xr:uid="{F0619288-BA2C-4FE5-AAC5-C9B30D145308}"/>
@@ -1895,7 +1893,7 @@
   <sheetData>
     <row r="2" spans="2:14" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B2" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -1983,354 +1981,354 @@
     </row>
     <row r="7" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B7" s="17">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="19">
+        <v>2.690410151713714</v>
+      </c>
+      <c r="E7" s="19">
+        <v>2.640300109904544</v>
+      </c>
+      <c r="F7" s="19">
+        <v>0.21676238612146179</v>
+      </c>
+      <c r="G7" s="19">
+        <v>3</v>
+      </c>
+      <c r="H7" s="19">
+        <v>2.0127686378889749</v>
+      </c>
+      <c r="I7" s="19">
+        <v>2.9</v>
+      </c>
+      <c r="J7" s="19">
+        <v>2.7941561110827942</v>
+      </c>
+      <c r="K7" s="19">
+        <v>2.5815972069022579</v>
+      </c>
+      <c r="L7" s="19">
         <v>2.4</v>
       </c>
-      <c r="E7" s="19">
-        <v>2.3673706013096072</v>
-      </c>
-      <c r="F7" s="19">
-        <v>0.1615353897031177</v>
-      </c>
-      <c r="G7" s="19">
-        <v>2.6616613582840509</v>
-      </c>
-      <c r="H7" s="19">
-        <v>1.8472528945311399</v>
-      </c>
-      <c r="I7" s="19">
-        <v>2.5</v>
-      </c>
-      <c r="J7" s="19">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="K7" s="19">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="L7" s="19">
-        <v>2.2999999999999998</v>
-      </c>
       <c r="M7" s="20">
-        <v>45</v>
-      </c>
-      <c r="N7" s="43"/>
+        <v>46</v>
+      </c>
+      <c r="N7" s="31"/>
     </row>
     <row r="8" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="4">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="E8" s="4">
-        <v>2.088167674209394</v>
+        <v>2.518346184713339</v>
       </c>
       <c r="F8" s="4">
-        <v>0.2037025458123658</v>
+        <v>0.27741076718030161</v>
       </c>
       <c r="G8" s="4">
-        <v>2.5099999999999998</v>
+        <v>3.11</v>
       </c>
       <c r="H8" s="4">
-        <v>1.5</v>
+        <v>1.8857824562493299</v>
       </c>
       <c r="I8" s="4">
-        <v>2.2999999999999998</v>
+        <v>2.8</v>
       </c>
       <c r="J8" s="4">
+        <v>2.7</v>
+      </c>
+      <c r="K8" s="4">
+        <v>2.369945700547337</v>
+      </c>
+      <c r="L8" s="4">
         <v>2.2000000000000002</v>
       </c>
-      <c r="K8" s="4">
-        <v>2</v>
-      </c>
-      <c r="L8" s="4">
-        <v>1.860417494869717</v>
-      </c>
       <c r="M8" s="5">
-        <v>45</v>
-      </c>
-      <c r="N8" s="43"/>
+        <v>46</v>
+      </c>
+      <c r="N8" s="31"/>
     </row>
     <row r="9" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B9" s="17">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="19">
-        <v>2.2000000000000002</v>
+        <v>2.19</v>
       </c>
       <c r="E9" s="19">
-        <v>2.2025131542208669</v>
+        <v>2.1561493040907602</v>
       </c>
       <c r="F9" s="19">
-        <v>0.25764765103878212</v>
+        <v>0.29690903359079968</v>
       </c>
       <c r="G9" s="19">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="H9" s="19">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="I9" s="19">
-        <v>2.4878930612935211</v>
+        <v>2.5</v>
       </c>
       <c r="J9" s="19">
-        <v>2.3977820764239839</v>
+        <v>2.380207941650216</v>
       </c>
       <c r="K9" s="19">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="L9" s="19">
-        <v>1.9</v>
+        <v>1.792431477173027</v>
       </c>
       <c r="M9" s="20">
-        <v>45</v>
-      </c>
-      <c r="N9" s="43"/>
+        <v>46</v>
+      </c>
+      <c r="N9" s="31"/>
     </row>
     <row r="10" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="4">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="E10" s="4">
-        <v>1.925252921187653</v>
+        <v>1.9097236539325031</v>
       </c>
       <c r="F10" s="4">
-        <v>0.22945227009704211</v>
+        <v>0.34485990588086329</v>
       </c>
       <c r="G10" s="4">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="H10" s="4">
-        <v>1.3</v>
+        <v>0.90000000000000013</v>
       </c>
       <c r="I10" s="4">
-        <v>2.2004104731402179</v>
+        <v>2.35</v>
       </c>
       <c r="J10" s="4">
-        <v>2.1</v>
+        <v>2.1535159117098441</v>
       </c>
       <c r="K10" s="4">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="L10" s="4">
-        <v>1.6921853183387761</v>
+        <v>1.550738366435545</v>
       </c>
       <c r="M10" s="5">
-        <v>45</v>
-      </c>
-      <c r="N10" s="43"/>
+        <v>46</v>
+      </c>
+      <c r="N10" s="31"/>
     </row>
     <row r="11" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B11" s="17">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="19">
-        <v>1.7</v>
+        <v>1.7999283980248959</v>
       </c>
       <c r="E11" s="19">
-        <v>1.7301743448098139</v>
+        <v>1.7608541247164351</v>
       </c>
       <c r="F11" s="19">
-        <v>0.26821717496135983</v>
+        <v>0.30124665505394121</v>
       </c>
       <c r="G11" s="19">
-        <v>2.4</v>
+        <v>2.3949179711396869</v>
       </c>
       <c r="H11" s="19">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="I11" s="19">
-        <v>2.0183387347222861</v>
+        <v>2.15</v>
       </c>
       <c r="J11" s="19">
-        <v>1.9</v>
+        <v>1.9375</v>
       </c>
       <c r="K11" s="19">
-        <v>1.5379975534861849</v>
+        <v>1.57</v>
       </c>
       <c r="L11" s="19">
-        <v>1.4221440276132451</v>
+        <v>1.4</v>
       </c>
       <c r="M11" s="20">
-        <v>45</v>
-      </c>
-      <c r="N11" s="43"/>
+        <v>46</v>
+      </c>
+      <c r="N11" s="31"/>
     </row>
     <row r="12" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B12" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="4">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="E12" s="4">
-        <v>1.610035441622524</v>
+        <v>1.7003879842396841</v>
       </c>
       <c r="F12" s="4">
-        <v>0.26289227741035098</v>
+        <v>0.33031004230671968</v>
       </c>
       <c r="G12" s="4">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="H12" s="4">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I12" s="4">
-        <v>1.9286388076649339</v>
+        <v>2.100010731535241</v>
       </c>
       <c r="J12" s="4">
-        <v>1.8</v>
+        <v>1.8975</v>
       </c>
       <c r="K12" s="4">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="L12" s="4">
-        <v>1.252</v>
+        <v>1.355116176528409</v>
       </c>
       <c r="M12" s="5">
-        <v>45</v>
-      </c>
-      <c r="N12" s="43"/>
+        <v>46</v>
+      </c>
+      <c r="N12" s="31"/>
     </row>
     <row r="13" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B13" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="19">
-        <v>1.5</v>
+        <v>1.5249999999999999</v>
       </c>
       <c r="E13" s="19">
-        <v>1.5566795902389781</v>
+        <v>1.601042801541414</v>
       </c>
       <c r="F13" s="19">
-        <v>0.27229105970617468</v>
+        <v>0.31378567509516608</v>
       </c>
       <c r="G13" s="19">
-        <v>2.09</v>
+        <v>2.2808436605211702</v>
       </c>
       <c r="H13" s="19">
-        <v>0.8</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="I13" s="19">
-        <v>1.9915999104944331</v>
+        <v>2.0206458656108039</v>
       </c>
       <c r="J13" s="19">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="K13" s="19">
         <v>1.4</v>
       </c>
       <c r="L13" s="19">
-        <v>1.194</v>
+        <v>1.239823825275288</v>
       </c>
       <c r="M13" s="20">
-        <v>45</v>
-      </c>
-      <c r="N13" s="43"/>
+        <v>46</v>
+      </c>
+      <c r="N13" s="31"/>
     </row>
     <row r="14" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="4">
-        <v>20.972204042663261</v>
+        <v>22.3</v>
       </c>
       <c r="E14" s="4">
-        <v>20.983917175061439</v>
+        <v>22.317663291018839</v>
       </c>
       <c r="F14" s="4">
-        <v>3.361089873224318</v>
+        <v>4.1138787246723716</v>
       </c>
       <c r="G14" s="4">
-        <v>27.4</v>
+        <v>31.170894380583221</v>
       </c>
       <c r="H14" s="4">
-        <v>11.2</v>
+        <v>9.75</v>
       </c>
       <c r="I14" s="4">
-        <v>25.088532090094461</v>
+        <v>27.1</v>
       </c>
       <c r="J14" s="4">
-        <v>23.3</v>
+        <v>24.9</v>
       </c>
       <c r="K14" s="4">
-        <v>19.019283488763389</v>
+        <v>20.195</v>
       </c>
       <c r="L14" s="4">
-        <v>17.315414321377219</v>
+        <v>17.335276022895759</v>
       </c>
       <c r="M14" s="5">
-        <v>42</v>
-      </c>
-      <c r="N14" s="43"/>
+        <v>43</v>
+      </c>
+      <c r="N14" s="31"/>
     </row>
     <row r="15" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B15" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D15" s="19">
-        <v>14.6</v>
+        <v>15.4</v>
       </c>
       <c r="E15" s="19">
-        <v>13.86813921411767</v>
+        <v>14.967614366651491</v>
       </c>
       <c r="F15" s="19">
-        <v>3.6638429123387048</v>
+        <v>4.0487297666120048</v>
       </c>
       <c r="G15" s="19">
-        <v>20.08058906548802</v>
+        <v>22.31</v>
       </c>
       <c r="H15" s="19">
         <v>3.5</v>
       </c>
       <c r="I15" s="19">
-        <v>18.454000000000001</v>
+        <v>19.526</v>
       </c>
       <c r="J15" s="19">
-        <v>16.2</v>
+        <v>17.850000000000001</v>
       </c>
       <c r="K15" s="19">
-        <v>11.458261944809429</v>
+        <v>12.3</v>
       </c>
       <c r="L15" s="19">
-        <v>9.2291899165999993</v>
+        <v>9.6003218080532928</v>
       </c>
       <c r="M15" s="20">
         <v>37</v>
       </c>
-      <c r="N15" s="43"/>
+      <c r="N15" s="31"/>
     </row>
     <row r="16" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
@@ -2340,36 +2338,36 @@
         <v>16</v>
       </c>
       <c r="D16" s="4">
-        <v>22.417992281752142</v>
+        <v>26.05</v>
       </c>
       <c r="E16" s="4">
-        <v>22.3510334435028</v>
+        <v>25.70488805516392</v>
       </c>
       <c r="F16" s="4">
-        <v>3.1605224972766641</v>
+        <v>3.4794579506547532</v>
       </c>
       <c r="G16" s="4">
-        <v>28.6</v>
+        <v>32.986836814213859</v>
       </c>
       <c r="H16" s="4">
-        <v>12.9</v>
+        <v>14.7</v>
       </c>
       <c r="I16" s="4">
-        <v>26.015756744974588</v>
+        <v>29.6</v>
       </c>
       <c r="J16" s="4">
-        <v>24.365890203749132</v>
+        <v>27.225000000000001</v>
       </c>
       <c r="K16" s="4">
-        <v>20.399999999999999</v>
+        <v>23.532499999999999</v>
       </c>
       <c r="L16" s="4">
-        <v>18.622</v>
+        <v>21.85</v>
       </c>
       <c r="M16" s="5">
-        <v>45</v>
-      </c>
-      <c r="N16" s="43"/>
+        <v>46</v>
+      </c>
+      <c r="N16" s="31"/>
     </row>
     <row r="17" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B17" s="21" t="s">
@@ -2379,36 +2377,36 @@
         <v>17</v>
       </c>
       <c r="D17" s="19">
-        <v>15</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="E17" s="19">
-        <v>14.323387924215419</v>
+        <v>15.914471236690369</v>
       </c>
       <c r="F17" s="19">
-        <v>4.342314471482597</v>
+        <v>4.5382144965834073</v>
       </c>
       <c r="G17" s="19">
-        <v>23.00466751580046</v>
+        <v>24.750505320674971</v>
       </c>
       <c r="H17" s="19">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="I17" s="19">
-        <v>19.600000000000001</v>
+        <v>20.66</v>
       </c>
       <c r="J17" s="19">
-        <v>17</v>
+        <v>18.881564821910452</v>
       </c>
       <c r="K17" s="19">
-        <v>11.71</v>
+        <v>13.2</v>
       </c>
       <c r="L17" s="19">
-        <v>8.6126138378744841</v>
+        <v>10.5558739118802</v>
       </c>
       <c r="M17" s="20">
-        <v>41</v>
-      </c>
-      <c r="N17" s="43"/>
+        <v>43</v>
+      </c>
+      <c r="N17" s="31"/>
     </row>
     <row r="18" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
@@ -2418,36 +2416,36 @@
         <v>41</v>
       </c>
       <c r="D18" s="4">
-        <v>9.8699999999999992</v>
+        <v>11.175483747833381</v>
       </c>
       <c r="E18" s="4">
-        <v>10.429310889619</v>
+        <v>11.252417067295321</v>
       </c>
       <c r="F18" s="4">
-        <v>3.6730158833250282</v>
+        <v>3.610276168705477</v>
       </c>
       <c r="G18" s="4">
-        <v>20.70420076422041</v>
+        <v>18.7</v>
       </c>
       <c r="H18" s="4">
         <v>2.4</v>
       </c>
       <c r="I18" s="4">
-        <v>14.2</v>
+        <v>15.28</v>
       </c>
       <c r="J18" s="4">
-        <v>12.35</v>
+        <v>13.675000000000001</v>
       </c>
       <c r="K18" s="4">
-        <v>8.5407120100482263</v>
+        <v>8.8036425848144226</v>
       </c>
       <c r="L18" s="4">
-        <v>7</v>
+        <v>7.1353047112875094</v>
       </c>
       <c r="M18" s="5">
-        <v>31</v>
-      </c>
-      <c r="N18" s="43"/>
+        <v>34</v>
+      </c>
+      <c r="N18" s="31"/>
     </row>
     <row r="21" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B21" s="14" t="s">
@@ -2505,202 +2503,202 @@
     </row>
     <row r="23" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B23" s="17">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="19">
+        <v>2.477906852987577</v>
+      </c>
+      <c r="E23" s="19">
+        <v>2.4837276475093888</v>
+      </c>
+      <c r="F23" s="19">
+        <v>0.29138896983624851</v>
+      </c>
+      <c r="G23" s="19">
+        <v>3</v>
+      </c>
+      <c r="H23" s="19">
+        <v>1.794327385678506</v>
+      </c>
+      <c r="I23" s="19">
+        <v>2.8719999999999999</v>
+      </c>
+      <c r="J23" s="19">
+        <v>2.7</v>
+      </c>
+      <c r="K23" s="19">
         <v>2.4</v>
       </c>
-      <c r="E23" s="19">
-        <v>2.3242450999648598</v>
-      </c>
-      <c r="F23" s="19">
-        <v>0.29340262344619822</v>
-      </c>
-      <c r="G23" s="19">
-        <v>2.900879255163535</v>
-      </c>
-      <c r="H23" s="19">
-        <v>1.5</v>
-      </c>
-      <c r="I23" s="19">
-        <v>2.6160000000000001</v>
-      </c>
-      <c r="J23" s="19">
-        <v>2.5</v>
-      </c>
-      <c r="K23" s="19">
-        <v>2.2000000000000002</v>
-      </c>
       <c r="L23" s="19">
-        <v>2.024</v>
+        <v>2.1160000000000001</v>
       </c>
       <c r="M23" s="20">
-        <v>37</v>
-      </c>
-      <c r="N23" s="43"/>
+        <v>38</v>
+      </c>
+      <c r="N23" s="31"/>
     </row>
     <row r="24" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B24" s="2">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="4">
-        <v>2.1</v>
+        <v>2.3689708250394399</v>
       </c>
       <c r="E24" s="4">
-        <v>2.0522349273094238</v>
+        <v>2.35363873610802</v>
       </c>
       <c r="F24" s="4">
-        <v>0.29328466827431893</v>
+        <v>0.29285145517973882</v>
       </c>
       <c r="G24" s="4">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="H24" s="4">
-        <v>1.1000000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="I24" s="4">
-        <v>2.4075950593364048</v>
+        <v>2.7496</v>
       </c>
       <c r="J24" s="4">
-        <v>2.2488454153260169</v>
+        <v>2.5876797044388038</v>
       </c>
       <c r="K24" s="4">
-        <v>1.83</v>
+        <v>2.125</v>
       </c>
       <c r="L24" s="4">
-        <v>1.76</v>
+        <v>1.999223018513276</v>
       </c>
       <c r="M24" s="5">
-        <v>37</v>
-      </c>
-      <c r="N24" s="43"/>
+        <v>38</v>
+      </c>
+      <c r="N24" s="31"/>
     </row>
     <row r="25" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B25" s="17">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="19">
-        <v>2.1</v>
+        <v>2.1425000000000001</v>
       </c>
       <c r="E25" s="19">
-        <v>2.0744965498416921</v>
+        <v>2.104251523861274</v>
       </c>
       <c r="F25" s="19">
-        <v>0.3290390293586854</v>
+        <v>0.28871334798553261</v>
       </c>
       <c r="G25" s="19">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H25" s="19">
-        <v>1.4</v>
+        <v>1.3669819631023701</v>
       </c>
       <c r="I25" s="19">
-        <v>2.5116646558020341</v>
+        <v>2.4</v>
       </c>
       <c r="J25" s="19">
-        <v>2.2999999999999998</v>
+        <v>2.25860396909713</v>
       </c>
       <c r="K25" s="19">
-        <v>1.8</v>
+        <v>1.9892782112109599</v>
       </c>
       <c r="L25" s="19">
-        <v>1.6559999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="M25" s="20">
-        <v>37</v>
-      </c>
-      <c r="N25" s="43"/>
+        <v>38</v>
+      </c>
+      <c r="N25" s="31"/>
     </row>
     <row r="26" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B26" s="2">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="4">
-        <v>1.9</v>
+        <v>1.823510666242967</v>
       </c>
       <c r="E26" s="4">
-        <v>1.8727931294017099</v>
+        <v>1.8995197815586871</v>
       </c>
       <c r="F26" s="4">
-        <v>0.25714164970685432</v>
+        <v>0.31237314100071578</v>
       </c>
       <c r="G26" s="4">
-        <v>2.2759253594371338</v>
+        <v>2.5</v>
       </c>
       <c r="H26" s="4">
-        <v>1.3</v>
+        <v>1.1527769732256361</v>
       </c>
       <c r="I26" s="4">
-        <v>2.2000000000000002</v>
+        <v>2.3149999999999999</v>
       </c>
       <c r="J26" s="4">
-        <v>2.027508102002952</v>
+        <v>2.1522940066364931</v>
       </c>
       <c r="K26" s="4">
         <v>1.7</v>
       </c>
       <c r="L26" s="4">
-        <v>1.5</v>
+        <v>1.573</v>
       </c>
       <c r="M26" s="5">
-        <v>37</v>
-      </c>
-      <c r="N26" s="43"/>
+        <v>38</v>
+      </c>
+      <c r="N26" s="31"/>
     </row>
     <row r="27" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B27" s="17">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C27" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="19">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="E27" s="19">
-        <v>1.6994800709378519</v>
+        <v>1.741965425712545</v>
       </c>
       <c r="F27" s="19">
-        <v>0.29235176384864492</v>
+        <v>0.27090944028431713</v>
       </c>
       <c r="G27" s="19">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="H27" s="19">
-        <v>1</v>
+        <v>1.2117514759902039</v>
       </c>
       <c r="I27" s="19">
-        <v>2.0247827153093771</v>
+        <v>2.125986578598285</v>
       </c>
       <c r="J27" s="19">
-        <v>1.9</v>
+        <v>1.8885465722278461</v>
       </c>
       <c r="K27" s="19">
         <v>1.6</v>
       </c>
       <c r="L27" s="19">
-        <v>1.3</v>
+        <v>1.4175</v>
       </c>
       <c r="M27" s="20">
-        <v>37</v>
-      </c>
-      <c r="N27" s="43"/>
+        <v>38</v>
+      </c>
+      <c r="N27" s="31"/>
     </row>
     <row r="28" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B28" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>13</v>
@@ -2709,150 +2707,150 @@
         <v>1.6</v>
       </c>
       <c r="E28" s="4">
-        <v>1.602394346352831</v>
+        <v>1.646774311468802</v>
       </c>
       <c r="F28" s="4">
-        <v>0.26520352923393992</v>
+        <v>0.28686054028793029</v>
       </c>
       <c r="G28" s="4">
-        <v>2.16</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="H28" s="4">
-        <v>1.1000000000000001</v>
+        <v>0.92441227673873994</v>
       </c>
       <c r="I28" s="4">
-        <v>1.966608018749999</v>
+        <v>2.009037967917946</v>
       </c>
       <c r="J28" s="4">
-        <v>1.74186213811624</v>
+        <v>1.8</v>
       </c>
       <c r="K28" s="4">
-        <v>1.44</v>
+        <v>1.425</v>
       </c>
       <c r="L28" s="4">
-        <v>1.217706095066095</v>
+        <v>1.396662781930472</v>
       </c>
       <c r="M28" s="5">
-        <v>37</v>
-      </c>
-      <c r="N28" s="43"/>
+        <v>38</v>
+      </c>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B29" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D29" s="19">
-        <v>1.5</v>
+        <v>1.5874999999999999</v>
       </c>
       <c r="E29" s="19">
-        <v>1.534195860399338</v>
+        <v>1.576243981054871</v>
       </c>
       <c r="F29" s="19">
-        <v>0.30656576909767791</v>
+        <v>0.26790998299468138</v>
       </c>
       <c r="G29" s="19">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="H29" s="19">
-        <v>0.8</v>
+        <v>0.82445672886766097</v>
       </c>
       <c r="I29" s="19">
-        <v>1.920301783675473</v>
+        <v>1.9572491708293309</v>
       </c>
       <c r="J29" s="19">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="K29" s="19">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="L29" s="19">
-        <v>1.1759999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="M29" s="20">
-        <v>37</v>
-      </c>
-      <c r="N29" s="43"/>
+        <v>38</v>
+      </c>
+      <c r="N29" s="31"/>
     </row>
     <row r="30" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D30" s="4">
-        <v>19.899999999999999</v>
+        <v>21.85954688792685</v>
       </c>
       <c r="E30" s="4">
-        <v>20.745939748403739</v>
+        <v>21.762390424188389</v>
       </c>
       <c r="F30" s="4">
-        <v>3.630025376966461</v>
+        <v>3.485872450384754</v>
       </c>
       <c r="G30" s="4">
-        <v>28.45</v>
+        <v>29.75</v>
       </c>
       <c r="H30" s="4">
-        <v>12.7</v>
+        <v>15.3</v>
       </c>
       <c r="I30" s="4">
-        <v>25.42</v>
+        <v>26.39427710685078</v>
       </c>
       <c r="J30" s="4">
-        <v>23.159420810910142</v>
+        <v>23.765000000000001</v>
       </c>
       <c r="K30" s="4">
-        <v>18.653715813059321</v>
+        <v>18.839219290503241</v>
       </c>
       <c r="L30" s="4">
-        <v>16.88</v>
+        <v>18.024082764395441</v>
       </c>
       <c r="M30" s="5">
-        <v>35</v>
-      </c>
-      <c r="N30" s="43"/>
+        <v>36</v>
+      </c>
+      <c r="N30" s="31"/>
     </row>
     <row r="31" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B31" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D31" s="19">
-        <v>13.16229071474487</v>
+        <v>14.63954773085891</v>
       </c>
       <c r="E31" s="19">
-        <v>13.463569803548589</v>
+        <v>14.50346868835188</v>
       </c>
       <c r="F31" s="19">
-        <v>3.8201996055276348</v>
+        <v>4.1138390728911354</v>
       </c>
       <c r="G31" s="19">
-        <v>20.3</v>
+        <v>21.28</v>
       </c>
       <c r="H31" s="19">
         <v>2.2999999999999998</v>
       </c>
       <c r="I31" s="19">
-        <v>18.803000000000001</v>
+        <v>19.658000000000001</v>
       </c>
       <c r="J31" s="19">
-        <v>16.024999999999999</v>
+        <v>17.45</v>
       </c>
       <c r="K31" s="19">
-        <v>11.07834398075487</v>
+        <v>11.60303928564665</v>
       </c>
       <c r="L31" s="19">
-        <v>9.316542440000001</v>
+        <v>9.4614411027304222</v>
       </c>
       <c r="M31" s="20">
-        <v>32</v>
-      </c>
-      <c r="N31" s="43"/>
+        <v>34</v>
+      </c>
+      <c r="N31" s="31"/>
     </row>
     <row r="32" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
@@ -2862,36 +2860,36 @@
         <v>16</v>
       </c>
       <c r="D32" s="4">
-        <v>22.133345966031872</v>
+        <v>24.35</v>
       </c>
       <c r="E32" s="4">
-        <v>22.031492204554269</v>
+        <v>24.63846045001798</v>
       </c>
       <c r="F32" s="4">
-        <v>3.4775979409550679</v>
+        <v>3.187320720973843</v>
       </c>
       <c r="G32" s="4">
-        <v>28.84050718878024</v>
+        <v>32</v>
       </c>
       <c r="H32" s="4">
-        <v>15.1</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="I32" s="4">
-        <v>26.611548231419569</v>
+        <v>28.216112439309288</v>
       </c>
       <c r="J32" s="4">
-        <v>24.5</v>
+        <v>26.774407242118318</v>
       </c>
       <c r="K32" s="4">
-        <v>19.8</v>
+        <v>22.606830705893351</v>
       </c>
       <c r="L32" s="4">
-        <v>17.675999999999998</v>
+        <v>21.007000000000001</v>
       </c>
       <c r="M32" s="5">
-        <v>37</v>
-      </c>
-      <c r="N32" s="43"/>
+        <v>38</v>
+      </c>
+      <c r="N32" s="31"/>
     </row>
     <row r="33" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B33" s="21" t="s">
@@ -2901,36 +2899,36 @@
         <v>17</v>
       </c>
       <c r="D33" s="19">
-        <v>13.901730653577451</v>
+        <v>16</v>
       </c>
       <c r="E33" s="19">
-        <v>14.42801388932933</v>
+        <v>15.689848349933831</v>
       </c>
       <c r="F33" s="19">
-        <v>4.470364920332405</v>
+        <v>4.2414672153580861</v>
       </c>
       <c r="G33" s="19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H33" s="19">
-        <v>2.2999999999999998</v>
+        <v>3</v>
       </c>
       <c r="I33" s="19">
-        <v>21.310315475487641</v>
+        <v>20.85</v>
       </c>
       <c r="J33" s="19">
-        <v>17.106987633073381</v>
+        <v>18.15533681016991</v>
       </c>
       <c r="K33" s="19">
-        <v>11.831437436218399</v>
+        <v>12.166004798435949</v>
       </c>
       <c r="L33" s="19">
-        <v>9.855814155307689</v>
+        <v>10.93734315190429</v>
       </c>
       <c r="M33" s="20">
-        <v>34</v>
-      </c>
-      <c r="N33" s="43"/>
+        <v>36</v>
+      </c>
+      <c r="N33" s="31"/>
     </row>
     <row r="34" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="s">
@@ -2940,36 +2938,36 @@
         <v>41</v>
       </c>
       <c r="D34" s="4">
-        <v>9.1999999999999993</v>
+        <v>10.87824763106341</v>
       </c>
       <c r="E34" s="4">
-        <v>10.19749465880621</v>
+        <v>10.896167867398511</v>
       </c>
       <c r="F34" s="4">
-        <v>3.619519497366773</v>
+        <v>3.712339572720587</v>
       </c>
       <c r="G34" s="4">
-        <v>20.159723995059949</v>
+        <v>18.7</v>
       </c>
       <c r="H34" s="4">
         <v>1.8</v>
       </c>
       <c r="I34" s="4">
-        <v>13.24</v>
+        <v>14.891</v>
       </c>
       <c r="J34" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K34" s="4">
-        <v>8.3000000000000007</v>
+        <v>8.4558770254155053</v>
       </c>
       <c r="L34" s="4">
-        <v>6.8493518474913584</v>
+        <v>6.3499471558165421</v>
       </c>
       <c r="M34" s="5">
-        <v>29</v>
-      </c>
-      <c r="N34" s="43"/>
+        <v>32</v>
+      </c>
+      <c r="N34" s="31"/>
     </row>
     <row r="36" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B36" s="22"/>
@@ -3031,229 +3029,229 @@
     </row>
     <row r="39" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B39" s="7">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="26">
-        <v>31.8</v>
+        <v>31.31800839374284</v>
       </c>
       <c r="E39" s="26">
-        <v>31.058330006879711</v>
+        <v>31.67741847608756</v>
       </c>
       <c r="F39" s="26">
-        <v>2.629775230120591</v>
+        <v>1.8207707424563271</v>
       </c>
       <c r="G39" s="26">
-        <v>37.111632179499402</v>
+        <v>36</v>
       </c>
       <c r="H39" s="26">
-        <v>25</v>
+        <v>28.928750000000001</v>
       </c>
       <c r="I39" s="26">
-        <v>33.460205854011349</v>
+        <v>34.5</v>
       </c>
       <c r="J39" s="26">
-        <v>32.83</v>
+        <v>32.4</v>
       </c>
       <c r="K39" s="26">
-        <v>29.5</v>
+        <v>30.5</v>
       </c>
       <c r="L39" s="26">
-        <v>27.289797333826019</v>
+        <v>29.359294535703381</v>
       </c>
       <c r="M39" s="8">
         <v>41</v>
       </c>
-      <c r="N39" s="43"/>
+      <c r="N39" s="31"/>
     </row>
     <row r="40" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B40" s="17">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C40" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="27">
-        <v>30.141818181818191</v>
+        <v>30</v>
       </c>
       <c r="E40" s="27">
-        <v>30.171062360433151</v>
+        <v>29.975417095304621</v>
       </c>
       <c r="F40" s="27">
-        <v>2.9431380998926149</v>
+        <v>2.129459741861206</v>
       </c>
       <c r="G40" s="27">
-        <v>37.833570060401307</v>
+        <v>35</v>
       </c>
       <c r="H40" s="27">
-        <v>24</v>
+        <v>24.95511627906977</v>
       </c>
       <c r="I40" s="27">
-        <v>34.1</v>
+        <v>32.5</v>
       </c>
       <c r="J40" s="27">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K40" s="27">
-        <v>28.3</v>
+        <v>29</v>
       </c>
       <c r="L40" s="27">
-        <v>26.616379132368269</v>
+        <v>28</v>
       </c>
       <c r="M40" s="20">
         <v>41</v>
       </c>
-      <c r="N40" s="43"/>
+      <c r="N40" s="31"/>
     </row>
     <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B41" s="2">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D41" s="26">
-        <v>28.649519325082078</v>
+        <v>28.6</v>
       </c>
       <c r="E41" s="26">
-        <v>28.63736490674836</v>
+        <v>28.45942287945606</v>
       </c>
       <c r="F41" s="26">
-        <v>2.958028455972979</v>
+        <v>2.3285674686260038</v>
       </c>
       <c r="G41" s="26">
-        <v>35.516097501923142</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="H41" s="26">
-        <v>22</v>
+        <v>20.8</v>
       </c>
       <c r="I41" s="26">
-        <v>32.4</v>
+        <v>30.6</v>
       </c>
       <c r="J41" s="26">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K41" s="26">
-        <v>26.89</v>
+        <v>27</v>
       </c>
       <c r="L41" s="26">
-        <v>24.503195154890101</v>
+        <v>26</v>
       </c>
       <c r="M41" s="5">
         <v>41</v>
       </c>
-      <c r="N41" s="43"/>
+      <c r="N41" s="31"/>
     </row>
     <row r="42" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B42" s="17">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C42" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D42" s="27">
-        <v>27.6</v>
+        <v>27.413545454545449</v>
       </c>
       <c r="E42" s="27">
-        <v>27.203347329776829</v>
+        <v>27.311367789039839</v>
       </c>
       <c r="F42" s="27">
-        <v>3.151303936266292</v>
+        <v>2.4910758267036388</v>
       </c>
       <c r="G42" s="27">
-        <v>33.129764403111331</v>
+        <v>32.1</v>
       </c>
       <c r="H42" s="27">
-        <v>20.25</v>
+        <v>20.8</v>
       </c>
       <c r="I42" s="27">
-        <v>31.2</v>
+        <v>30</v>
       </c>
       <c r="J42" s="27">
-        <v>29.132602193419739</v>
+        <v>29.158145745898508</v>
       </c>
       <c r="K42" s="27">
-        <v>24.74</v>
+        <v>26</v>
       </c>
       <c r="L42" s="27">
-        <v>23</v>
+        <v>24.527616279069768</v>
       </c>
       <c r="M42" s="20">
         <v>41</v>
       </c>
-      <c r="N42" s="43"/>
+      <c r="N42" s="31"/>
     </row>
     <row r="43" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B43" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D43" s="26">
-        <v>26.15</v>
+        <v>26.187413311109701</v>
       </c>
       <c r="E43" s="26">
-        <v>26.198392237520132</v>
+        <v>26.248171382352378</v>
       </c>
       <c r="F43" s="26">
-        <v>3.269426005811336</v>
+        <v>2.4956186148875799</v>
       </c>
       <c r="G43" s="26">
-        <v>32.531639585965308</v>
+        <v>30.4</v>
       </c>
       <c r="H43" s="26">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="I43" s="26">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J43" s="26">
-        <v>28.053616926996789</v>
+        <v>28.25</v>
       </c>
       <c r="K43" s="26">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="L43" s="26">
-        <v>22.3</v>
+        <v>22.908901316935491</v>
       </c>
       <c r="M43" s="5">
         <v>41</v>
       </c>
-      <c r="N43" s="43"/>
+      <c r="N43" s="31"/>
     </row>
     <row r="44" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B44" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C44" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D44" s="27">
-        <v>25</v>
+        <v>25.48</v>
       </c>
       <c r="E44" s="27">
-        <v>25.13385234697127</v>
+        <v>25.401547494422811</v>
       </c>
       <c r="F44" s="27">
-        <v>3.170418268610574</v>
+        <v>2.8029097531801122</v>
       </c>
       <c r="G44" s="27">
-        <v>31.797076307168339</v>
+        <v>30.2</v>
       </c>
       <c r="H44" s="27">
-        <v>17.8</v>
+        <v>16.2</v>
       </c>
       <c r="I44" s="27">
-        <v>29</v>
+        <v>28.5</v>
       </c>
       <c r="J44" s="27">
-        <v>27.878281821203061</v>
+        <v>27.3</v>
       </c>
       <c r="K44" s="27">
-        <v>23.713043478260861</v>
+        <v>24.5</v>
       </c>
       <c r="L44" s="27">
         <v>21.5</v>
@@ -3261,46 +3259,46 @@
       <c r="M44" s="20">
         <v>41</v>
       </c>
-      <c r="N44" s="43"/>
+      <c r="N44" s="31"/>
     </row>
     <row r="45" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D45" s="26">
-        <v>21.774852664229531</v>
+        <v>22.145</v>
       </c>
       <c r="E45" s="26">
-        <v>21.46101584912725</v>
+        <v>21.588526460464209</v>
       </c>
       <c r="F45" s="26">
-        <v>4.9594155939325004</v>
+        <v>4.2567912757716861</v>
       </c>
       <c r="G45" s="26">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H45" s="26">
-        <v>8.8000000000000007</v>
+        <v>11.2</v>
       </c>
       <c r="I45" s="26">
-        <v>26.600000000000009</v>
+        <v>25.596</v>
       </c>
       <c r="J45" s="26">
-        <v>24</v>
+        <v>24.374613697062191</v>
       </c>
       <c r="K45" s="26">
-        <v>18.541227402472369</v>
+        <v>19</v>
       </c>
       <c r="L45" s="26">
-        <v>15.86999999999996</v>
+        <v>17</v>
       </c>
       <c r="M45" s="5">
         <v>38</v>
       </c>
-      <c r="N45" s="43"/>
+      <c r="N45" s="31"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B46" s="21" t="s">
@@ -3310,36 +3308,36 @@
         <v>20</v>
       </c>
       <c r="D46" s="27">
-        <v>22.41</v>
+        <v>24</v>
       </c>
       <c r="E46" s="27">
-        <v>22.364056767059139</v>
+        <v>23.22452523011172</v>
       </c>
       <c r="F46" s="27">
-        <v>4.4299855217777049</v>
+        <v>4.0315296677751276</v>
       </c>
       <c r="G46" s="27">
         <v>35</v>
       </c>
       <c r="H46" s="27">
-        <v>11.2</v>
+        <v>12.7</v>
       </c>
       <c r="I46" s="27">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J46" s="27">
-        <v>24.1</v>
+        <v>25.4</v>
       </c>
       <c r="K46" s="27">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="L46" s="27">
-        <v>17</v>
+        <v>18.588691860465119</v>
       </c>
       <c r="M46" s="20">
         <v>41</v>
       </c>
-      <c r="N46" s="43"/>
+      <c r="N46" s="31"/>
     </row>
     <row r="47" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B47" s="6" t="s">
@@ -3349,44 +3347,44 @@
         <v>42</v>
       </c>
       <c r="D47" s="26">
-        <v>16.079999999999998</v>
+        <v>17.25</v>
       </c>
       <c r="E47" s="26">
-        <v>17.122072759309859</v>
+        <v>17.629729189639029</v>
       </c>
       <c r="F47" s="26">
-        <v>4.3407053134023288</v>
+        <v>4.1532065265512097</v>
       </c>
       <c r="G47" s="26">
-        <v>28.388850680861879</v>
+        <v>27</v>
       </c>
       <c r="H47" s="26">
         <v>7</v>
       </c>
       <c r="I47" s="26">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="J47" s="26">
-        <v>19.5</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="K47" s="26">
         <v>15</v>
       </c>
       <c r="L47" s="26">
-        <v>12.279217982157819</v>
+        <v>12.662907967289099</v>
       </c>
       <c r="M47" s="5">
         <v>37</v>
       </c>
-      <c r="N47" s="43"/>
+      <c r="N47" s="31"/>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B48" s="22"/>
       <c r="C48" s="23"/>
-      <c r="N48" s="43"/>
+      <c r="N48" s="31"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="N49" s="43"/>
+      <c r="N49" s="31"/>
     </row>
     <row r="50" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B50" s="14" t="s">
@@ -3403,7 +3401,7 @@
       <c r="K50" s="14"/>
       <c r="L50" s="14"/>
       <c r="M50" s="15"/>
-      <c r="N50" s="43"/>
+      <c r="N50" s="31"/>
     </row>
     <row r="51" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B51" s="24" t="s">
@@ -3445,276 +3443,276 @@
     </row>
     <row r="52" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B52" s="7">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D52" s="28">
-        <v>1475</v>
+        <v>1428.7881960142861</v>
       </c>
       <c r="E52" s="28">
-        <v>1477.385211817071</v>
+        <v>1431.0525849532801</v>
       </c>
       <c r="F52" s="28">
-        <v>19.87634698229375</v>
+        <v>25.212150295418731</v>
       </c>
       <c r="G52" s="28">
-        <v>1563.333333333333</v>
+        <v>1502</v>
       </c>
       <c r="H52" s="28">
-        <v>1444.06</v>
+        <v>1392.4821565838929</v>
       </c>
       <c r="I52" s="28">
-        <v>1496.191409123388</v>
+        <v>1464.0095167857139</v>
       </c>
       <c r="J52" s="28">
-        <v>1486.763394246</v>
+        <v>1439.6125130827161</v>
       </c>
       <c r="K52" s="28">
-        <v>1464.2</v>
+        <v>1418.079955306722</v>
       </c>
       <c r="L52" s="28">
-        <v>1459.4228426754969</v>
+        <v>1401.44</v>
       </c>
       <c r="M52" s="5">
-        <v>45</v>
-      </c>
-      <c r="N52" s="43"/>
+        <v>46</v>
+      </c>
+      <c r="N52" s="31"/>
     </row>
     <row r="53" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B53" s="17">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C53" s="18" t="s">
         <v>22</v>
       </c>
       <c r="D53" s="29">
-        <v>1501.63102818846</v>
+        <v>1451.806710434533</v>
       </c>
       <c r="E53" s="29">
-        <v>1505.043021492053</v>
+        <v>1461.159229716837</v>
       </c>
       <c r="F53" s="29">
-        <v>25.73091061304244</v>
+        <v>34.028580268127477</v>
       </c>
       <c r="G53" s="29">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="H53" s="29">
-        <v>1451.5</v>
+        <v>1413</v>
       </c>
       <c r="I53" s="29">
-        <v>1545.8713945926479</v>
+        <v>1512.05</v>
       </c>
       <c r="J53" s="29">
-        <v>1519.25</v>
+        <v>1472.272351599951</v>
       </c>
       <c r="K53" s="29">
-        <v>1491</v>
+        <v>1438.9198710859371</v>
       </c>
       <c r="L53" s="29">
-        <v>1479.98</v>
+        <v>1427</v>
       </c>
       <c r="M53" s="20">
-        <v>45</v>
-      </c>
-      <c r="N53" s="43"/>
+        <v>46</v>
+      </c>
+      <c r="N53" s="31"/>
     </row>
     <row r="54" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B54" s="2">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D54" s="28">
-        <v>1525.661604667109</v>
+        <v>1474.5287610910509</v>
       </c>
       <c r="E54" s="28">
-        <v>1532.2602996487749</v>
+        <v>1488.6920936626209</v>
       </c>
       <c r="F54" s="28">
-        <v>31.96373537080596</v>
+        <v>43.23239806909455</v>
       </c>
       <c r="G54" s="28">
-        <v>1607.47</v>
+        <v>1627</v>
       </c>
       <c r="H54" s="28">
-        <v>1449.2</v>
+        <v>1420</v>
       </c>
       <c r="I54" s="28">
-        <v>1578.666666666667</v>
+        <v>1550.073796958151</v>
       </c>
       <c r="J54" s="28">
-        <v>1552.7313342237851</v>
+        <v>1510.3428880383501</v>
       </c>
       <c r="K54" s="28">
-        <v>1514.7000096184449</v>
+        <v>1459.1796634681789</v>
       </c>
       <c r="L54" s="28">
-        <v>1496.058</v>
+        <v>1442.682573050118</v>
       </c>
       <c r="M54" s="5">
-        <v>45</v>
-      </c>
-      <c r="N54" s="43"/>
+        <v>46</v>
+      </c>
+      <c r="N54" s="31"/>
     </row>
     <row r="55" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B55" s="17">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C55" s="18" t="s">
         <v>22</v>
       </c>
       <c r="D55" s="29">
-        <v>1548.5465287371151</v>
+        <v>1500.0038</v>
       </c>
       <c r="E55" s="29">
-        <v>1553.278059588584</v>
+        <v>1518.2785208098881</v>
       </c>
       <c r="F55" s="29">
-        <v>41.059652869329511</v>
+        <v>51.91490559526089</v>
       </c>
       <c r="G55" s="29">
-        <v>1663.21</v>
+        <v>1668</v>
       </c>
       <c r="H55" s="29">
-        <v>1447.1</v>
+        <v>1435</v>
       </c>
       <c r="I55" s="29">
-        <v>1609.76741729019</v>
+        <v>1598.326010866896</v>
       </c>
       <c r="J55" s="29">
-        <v>1583.333333333333</v>
+        <v>1544.83</v>
       </c>
       <c r="K55" s="29">
-        <v>1524</v>
+        <v>1487.375</v>
       </c>
       <c r="L55" s="29">
-        <v>1512.3015678202439</v>
+        <v>1460.822351273385</v>
       </c>
       <c r="M55" s="20">
-        <v>45</v>
-      </c>
-      <c r="N55" s="43"/>
+        <v>46</v>
+      </c>
+      <c r="N55" s="31"/>
     </row>
     <row r="56" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B56" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D56" s="28">
-        <v>1577.438884016841</v>
+        <v>1532</v>
       </c>
       <c r="E56" s="28">
-        <v>1577.261854621888</v>
+        <v>1550.0516089640751</v>
       </c>
       <c r="F56" s="28">
-        <v>50.375561831096768</v>
+        <v>61.661558533804858</v>
       </c>
       <c r="G56" s="28">
-        <v>1701.97</v>
+        <v>1692</v>
       </c>
       <c r="H56" s="28">
-        <v>1447.8</v>
+        <v>1443</v>
       </c>
       <c r="I56" s="28">
-        <v>1645.4932012016361</v>
+        <v>1636.412810342357</v>
       </c>
       <c r="J56" s="28">
-        <v>1615</v>
+        <v>1604.329511072192</v>
       </c>
       <c r="K56" s="28">
-        <v>1539.1</v>
+        <v>1507.067888160499</v>
       </c>
       <c r="L56" s="28">
-        <v>1526.612978111883</v>
+        <v>1480.149954454416</v>
       </c>
       <c r="M56" s="5">
-        <v>45</v>
-      </c>
-      <c r="N56" s="43"/>
+        <v>46</v>
+      </c>
+      <c r="N56" s="31"/>
     </row>
     <row r="57" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B57" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C57" s="18" t="s">
         <v>22</v>
       </c>
       <c r="D57" s="29">
-        <v>1604</v>
+        <v>1564.784724889086</v>
       </c>
       <c r="E57" s="29">
-        <v>1607.5089479448579</v>
+        <v>1580.5509639512759</v>
       </c>
       <c r="F57" s="29">
-        <v>60.654769777879117</v>
+        <v>68.129624705653711</v>
       </c>
       <c r="G57" s="29">
-        <v>1741.28</v>
+        <v>1745.000945757258</v>
       </c>
       <c r="H57" s="29">
-        <v>1454.3</v>
+        <v>1449</v>
       </c>
       <c r="I57" s="29">
-        <v>1689.7625537341339</v>
+        <v>1675.504775445942</v>
       </c>
       <c r="J57" s="29">
-        <v>1645</v>
+        <v>1640.9594187463131</v>
       </c>
       <c r="K57" s="29">
-        <v>1564.294625872443</v>
+        <v>1530.5844343821441</v>
       </c>
       <c r="L57" s="29">
-        <v>1542.24</v>
+        <v>1503.5562676339521</v>
       </c>
       <c r="M57" s="20">
-        <v>45</v>
-      </c>
-      <c r="N57" s="43"/>
+        <v>46</v>
+      </c>
+      <c r="N57" s="31"/>
     </row>
     <row r="58" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D58" s="28">
-        <v>1767.5650000000001</v>
+        <v>1747.5167264935501</v>
       </c>
       <c r="E58" s="28">
-        <v>1768.6156409996699</v>
+        <v>1744.7571746027611</v>
       </c>
       <c r="F58" s="28">
-        <v>119.3968945271486</v>
+        <v>113.5117086500322</v>
       </c>
       <c r="G58" s="28">
-        <v>2111</v>
+        <v>2041.8</v>
       </c>
       <c r="H58" s="28">
-        <v>1480</v>
+        <v>1470</v>
       </c>
       <c r="I58" s="28">
-        <v>1883.3239448597631</v>
+        <v>1874.596023077396</v>
       </c>
       <c r="J58" s="28">
-        <v>1832.2853195311559</v>
+        <v>1791.6875</v>
       </c>
       <c r="K58" s="28">
-        <v>1698.1223318132249</v>
+        <v>1660</v>
       </c>
       <c r="L58" s="28">
-        <v>1633.64</v>
+        <v>1624.3</v>
       </c>
       <c r="M58" s="5">
         <v>42</v>
       </c>
-      <c r="N58" s="43"/>
+      <c r="N58" s="31"/>
     </row>
     <row r="59" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B59" s="21" t="s">
@@ -3724,36 +3722,36 @@
         <v>23</v>
       </c>
       <c r="D59" s="29">
-        <v>1750</v>
+        <v>1706.787480237655</v>
       </c>
       <c r="E59" s="29">
-        <v>1746.5753341494731</v>
+        <v>1709.9712208124861</v>
       </c>
       <c r="F59" s="29">
-        <v>110.0402844962843</v>
+        <v>99.004336572651411</v>
       </c>
       <c r="G59" s="29">
-        <v>2082</v>
+        <v>2001.708139775357</v>
       </c>
       <c r="H59" s="29">
-        <v>1476.6</v>
+        <v>1465</v>
       </c>
       <c r="I59" s="29">
-        <v>1850.940644165192</v>
+        <v>1828.6723726032501</v>
       </c>
       <c r="J59" s="29">
-        <v>1803.1337347346389</v>
+        <v>1759.5225</v>
       </c>
       <c r="K59" s="29">
-        <v>1665.097178599613</v>
+        <v>1644.116372807176</v>
       </c>
       <c r="L59" s="29">
-        <v>1620.4</v>
+        <v>1607</v>
       </c>
       <c r="M59" s="20">
-        <v>45</v>
-      </c>
-      <c r="N59" s="43"/>
+        <v>46</v>
+      </c>
+      <c r="N59" s="31"/>
     </row>
     <row r="60" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B60" s="2" t="s">
@@ -3763,36 +3761,36 @@
         <v>43</v>
       </c>
       <c r="D60" s="28">
-        <v>1971</v>
+        <v>1955</v>
       </c>
       <c r="E60" s="28">
-        <v>1988.234975917565</v>
+        <v>1964.422332101954</v>
       </c>
       <c r="F60" s="28">
-        <v>173.42476109955669</v>
+        <v>171.0205500328978</v>
       </c>
       <c r="G60" s="28">
-        <v>2371</v>
+        <v>2410.04</v>
       </c>
       <c r="H60" s="28">
-        <v>1509.5</v>
+        <v>1498</v>
       </c>
       <c r="I60" s="28">
-        <v>2210.3065741893652</v>
+        <v>2151.192</v>
       </c>
       <c r="J60" s="28">
-        <v>2100</v>
+        <v>2083.2249999999999</v>
       </c>
       <c r="K60" s="28">
-        <v>1881</v>
+        <v>1848</v>
       </c>
       <c r="L60" s="28">
-        <v>1840</v>
+        <v>1769.198538792479</v>
       </c>
       <c r="M60" s="5">
-        <v>41</v>
-      </c>
-      <c r="N60" s="43"/>
+        <v>43</v>
+      </c>
+      <c r="N60" s="31"/>
     </row>
     <row r="61" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B61" s="22"/>
@@ -3858,276 +3856,276 @@
     </row>
     <row r="65" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B65" s="7">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D65" s="28">
-        <v>6621.4915106058806</v>
+        <v>6820</v>
       </c>
       <c r="E65" s="28">
-        <v>6666.8208205847077</v>
+        <v>6789.3088604406066</v>
       </c>
       <c r="F65" s="28">
-        <v>485.12053668863518</v>
+        <v>361.33986301635531</v>
       </c>
       <c r="G65" s="28">
-        <v>7756</v>
+        <v>7452.4541796272397</v>
       </c>
       <c r="H65" s="28">
-        <v>5487.4503752946794</v>
+        <v>6139.7040570999998</v>
       </c>
       <c r="I65" s="28">
-        <v>7307</v>
+        <v>7269.7545162649521</v>
       </c>
       <c r="J65" s="28">
-        <v>6943.2553011528598</v>
+        <v>7090.25</v>
       </c>
       <c r="K65" s="28">
-        <v>6401.2501905337986</v>
+        <v>6557.8975</v>
       </c>
       <c r="L65" s="28">
-        <v>6202</v>
+        <v>6305.84</v>
       </c>
       <c r="M65" s="8">
-        <v>39</v>
-      </c>
-      <c r="N65" s="44"/>
+        <v>38</v>
+      </c>
+      <c r="N65" s="32"/>
     </row>
     <row r="66" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B66" s="17">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="C66" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D66" s="29">
-        <v>6698</v>
+        <v>7358.8279266223217</v>
       </c>
       <c r="E66" s="29">
-        <v>6719.2046150809783</v>
+        <v>7463.2042349255398</v>
       </c>
       <c r="F66" s="29">
-        <v>314.27004131380551</v>
+        <v>443.89655703708422</v>
       </c>
       <c r="G66" s="29">
-        <v>7452.4541796272397</v>
+        <v>8549.019280067434</v>
       </c>
       <c r="H66" s="29">
-        <v>6148.959072604669</v>
+        <v>6642.3469731900004</v>
       </c>
       <c r="I66" s="29">
-        <v>7164.9600433400137</v>
+        <v>8115.3</v>
       </c>
       <c r="J66" s="29">
-        <v>6898.9014961420889</v>
+        <v>7718.3014166802577</v>
       </c>
       <c r="K66" s="29">
-        <v>6520.2800000000007</v>
+        <v>7238.1006594395267</v>
       </c>
       <c r="L66" s="29">
-        <v>6329.4</v>
+        <v>6835.990237548539</v>
       </c>
       <c r="M66" s="20">
-        <v>39</v>
-      </c>
-      <c r="N66" s="44"/>
+        <v>38</v>
+      </c>
+      <c r="N66" s="32"/>
     </row>
     <row r="67" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="2">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D67" s="28">
-        <v>7322.7304639530184</v>
+        <v>7841.3930457882552</v>
       </c>
       <c r="E67" s="28">
-        <v>7399.9363035115784</v>
+        <v>7839.1995177765448</v>
       </c>
       <c r="F67" s="28">
-        <v>421.47001234396998</v>
+        <v>627.61966653473314</v>
       </c>
       <c r="G67" s="28">
-        <v>8549.019280067434</v>
+        <v>9499.5813244242654</v>
       </c>
       <c r="H67" s="28">
-        <v>6702.9728989048444</v>
+        <v>6674.3306841699996</v>
       </c>
       <c r="I67" s="28">
-        <v>7879.0463346383121</v>
+        <v>8584.9</v>
       </c>
       <c r="J67" s="28">
-        <v>7649.8164006963543</v>
+        <v>8094.8401719028107</v>
       </c>
       <c r="K67" s="28">
-        <v>7125</v>
+        <v>7488</v>
       </c>
       <c r="L67" s="28">
-        <v>6937.2843625348878</v>
+        <v>7029.7009762563703</v>
       </c>
       <c r="M67" s="5">
-        <v>39</v>
-      </c>
-      <c r="N67" s="44"/>
+        <v>38</v>
+      </c>
+      <c r="N67" s="32"/>
     </row>
     <row r="68" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B68" s="17">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C68" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D68" s="29">
-        <v>7815.8607022848846</v>
+        <v>8275.5148378251761</v>
       </c>
       <c r="E68" s="29">
-        <v>7780.3919147865072</v>
+        <v>8350.1784366760821</v>
       </c>
       <c r="F68" s="29">
-        <v>531.84037159499917</v>
+        <v>619.73923295363068</v>
       </c>
       <c r="G68" s="29">
-        <v>9315.0163940606744</v>
+        <v>9612.7787517514171</v>
       </c>
       <c r="H68" s="29">
-        <v>6807</v>
+        <v>7095.18297927</v>
       </c>
       <c r="I68" s="29">
-        <v>8310.1658418713942</v>
+        <v>9133.4011750773298</v>
       </c>
       <c r="J68" s="29">
-        <v>8056.8810718559562</v>
+        <v>8868.4721695899534</v>
       </c>
       <c r="K68" s="29">
-        <v>7464.6079621217232</v>
+        <v>8000.5036198541202</v>
       </c>
       <c r="L68" s="29">
-        <v>7186.3658575498721</v>
+        <v>7597.3712259970462</v>
       </c>
       <c r="M68" s="20">
-        <v>39</v>
-      </c>
-      <c r="N68" s="44"/>
+        <v>38</v>
+      </c>
+      <c r="N68" s="32"/>
     </row>
     <row r="69" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B69" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D69" s="28">
-        <v>8249.1042863587263</v>
+        <v>8115.5</v>
       </c>
       <c r="E69" s="28">
-        <v>8263.5925458383408</v>
+        <v>8149.3262174944211</v>
       </c>
       <c r="F69" s="28">
-        <v>500.55832762240942</v>
+        <v>524.07919416495781</v>
       </c>
       <c r="G69" s="28">
-        <v>9414.9362944449749</v>
+        <v>9871.4532105056478</v>
       </c>
       <c r="H69" s="28">
-        <v>7216.22</v>
+        <v>7275.2606452399996</v>
       </c>
       <c r="I69" s="28">
-        <v>8877.9962070700458</v>
+        <v>8667.4964410407356</v>
       </c>
       <c r="J69" s="28">
-        <v>8604.5298225142542</v>
+        <v>8461.2102208935339</v>
       </c>
       <c r="K69" s="28">
-        <v>7937.5</v>
+        <v>7843.75</v>
       </c>
       <c r="L69" s="28">
-        <v>7674.1860055987099</v>
+        <v>7471.5749999999998</v>
       </c>
       <c r="M69" s="5">
-        <v>39</v>
-      </c>
-      <c r="N69" s="44"/>
+        <v>38</v>
+      </c>
+      <c r="N69" s="32"/>
     </row>
     <row r="70" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B70" s="17">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C70" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D70" s="29">
-        <v>7991.4618070202196</v>
+        <v>8225.653588923411</v>
       </c>
       <c r="E70" s="29">
-        <v>8064.9690677309018</v>
+        <v>8252.4367493986065</v>
       </c>
       <c r="F70" s="29">
-        <v>484.46366303435298</v>
+        <v>492.49753810195767</v>
       </c>
       <c r="G70" s="29">
-        <v>9871.4532105056478</v>
+        <v>9684.456232295679</v>
       </c>
       <c r="H70" s="29">
-        <v>7116.3068070104009</v>
+        <v>7000</v>
       </c>
       <c r="I70" s="29">
-        <v>8619.2356908562288</v>
+        <v>8730.8640396315241</v>
       </c>
       <c r="J70" s="29">
-        <v>8289.6690131268588</v>
+        <v>8504.9610768315997</v>
       </c>
       <c r="K70" s="29">
-        <v>7768.1860116369526</v>
+        <v>7894.25</v>
       </c>
       <c r="L70" s="29">
-        <v>7589.6979527971043</v>
+        <v>7820.5978766782528</v>
       </c>
       <c r="M70" s="20">
-        <v>39</v>
-      </c>
-      <c r="N70" s="44"/>
+        <v>38</v>
+      </c>
+      <c r="N70" s="32"/>
     </row>
     <row r="71" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B71" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D71" s="28">
-        <v>8199.73</v>
+        <v>8216.4970172361009</v>
       </c>
       <c r="E71" s="28">
-        <v>8190.919435823409</v>
+        <v>8222.5086615763303</v>
       </c>
       <c r="F71" s="28">
-        <v>629.38488489228814</v>
+        <v>561.04514551071225</v>
       </c>
       <c r="G71" s="28">
-        <v>9684.456232295679</v>
+        <v>10165.564280137931</v>
       </c>
       <c r="H71" s="28">
-        <v>6004.3387760152636</v>
+        <v>7000</v>
       </c>
       <c r="I71" s="28">
-        <v>8782.1557801563795</v>
+        <v>8766.8097509001364</v>
       </c>
       <c r="J71" s="28">
-        <v>8515.5819196930825</v>
+        <v>8578.75</v>
       </c>
       <c r="K71" s="28">
-        <v>7881</v>
+        <v>7941.7395862353778</v>
       </c>
       <c r="L71" s="28">
-        <v>7618.7039999999997</v>
+        <v>7751.3772575522626</v>
       </c>
       <c r="M71" s="5">
-        <v>39</v>
-      </c>
-      <c r="N71" s="44"/>
+        <v>38</v>
+      </c>
+      <c r="N71" s="32"/>
     </row>
     <row r="72" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B72" s="21" t="s">
@@ -4137,36 +4135,36 @@
         <v>25</v>
       </c>
       <c r="D72" s="29">
-        <v>91884.832304551266</v>
+        <v>92736.94012581819</v>
       </c>
       <c r="E72" s="29">
-        <v>92489.944247092266</v>
+        <v>93635.105560844619</v>
       </c>
       <c r="F72" s="29">
-        <v>4738.2166461834158</v>
+        <v>4321.4446605068442</v>
       </c>
       <c r="G72" s="29">
-        <v>113893.9543061141</v>
+        <v>114160.3104429737</v>
       </c>
       <c r="H72" s="29">
-        <v>85310</v>
+        <v>87803.121317923462</v>
       </c>
       <c r="I72" s="29">
-        <v>96862.225470702382</v>
+        <v>97220</v>
       </c>
       <c r="J72" s="29">
-        <v>93931.802737486956</v>
+        <v>94847</v>
       </c>
       <c r="K72" s="29">
-        <v>89495.683318160416</v>
+        <v>91467</v>
       </c>
       <c r="L72" s="29">
-        <v>88044.612994159601</v>
+        <v>89999.869982060001</v>
       </c>
       <c r="M72" s="20">
-        <v>42</v>
-      </c>
-      <c r="N72" s="44"/>
+        <v>41</v>
+      </c>
+      <c r="N72" s="32"/>
     </row>
     <row r="73" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B73" s="6" t="s">
@@ -4176,36 +4174,36 @@
         <v>25</v>
       </c>
       <c r="D73" s="28">
-        <v>98531.48000000001</v>
+        <v>98463</v>
       </c>
       <c r="E73" s="28">
-        <v>98686.633619362212</v>
+        <v>98806.987085864443</v>
       </c>
       <c r="F73" s="28">
-        <v>6941.3045829602715</v>
+        <v>5160.3993953349009</v>
       </c>
       <c r="G73" s="28">
-        <v>120000</v>
+        <v>119216.8941094664</v>
       </c>
       <c r="H73" s="28">
-        <v>85290</v>
+        <v>88920</v>
       </c>
       <c r="I73" s="28">
-        <v>103335.9348092874</v>
+        <v>102764.9258385946</v>
       </c>
       <c r="J73" s="28">
-        <v>101224.5</v>
+        <v>101196</v>
       </c>
       <c r="K73" s="28">
-        <v>95941.35417417706</v>
+        <v>96423</v>
       </c>
       <c r="L73" s="28">
-        <v>90758</v>
+        <v>92797.773981626757</v>
       </c>
       <c r="M73" s="5">
-        <v>36</v>
-      </c>
-      <c r="N73" s="44"/>
+        <v>37</v>
+      </c>
+      <c r="N73" s="32"/>
     </row>
     <row r="74" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B74" s="22"/>
@@ -4271,276 +4269,276 @@
     </row>
     <row r="78" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B78" s="7">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D78" s="28">
-        <v>6000</v>
+        <v>5826</v>
       </c>
       <c r="E78" s="28">
-        <v>5986.1410173779514</v>
+        <v>5768.8232323566017</v>
       </c>
       <c r="F78" s="28">
-        <v>376.22511362848348</v>
+        <v>446.77070528809548</v>
       </c>
       <c r="G78" s="28">
-        <v>6982.4925756844495</v>
+        <v>7135.8667290243693</v>
       </c>
       <c r="H78" s="28">
-        <v>5246.7851804536231</v>
+        <v>5002</v>
       </c>
       <c r="I78" s="28">
-        <v>6444</v>
+        <v>6123.5</v>
       </c>
       <c r="J78" s="28">
-        <v>6218.7456710962088</v>
+        <v>5996.0529999999999</v>
       </c>
       <c r="K78" s="28">
-        <v>5734.8442379854023</v>
+        <v>5566.0120435831614</v>
       </c>
       <c r="L78" s="28">
-        <v>5578.3264542169109</v>
+        <v>5115.7291749612341</v>
       </c>
       <c r="M78" s="8">
-        <v>39</v>
-      </c>
-      <c r="N78" s="44"/>
+        <v>38</v>
+      </c>
+      <c r="N78" s="32"/>
     </row>
     <row r="79" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B79" s="17">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="C79" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D79" s="29">
-        <v>6000</v>
+        <v>6311.5</v>
       </c>
       <c r="E79" s="29">
-        <v>5919.6601261581918</v>
+        <v>6339.5151910569248</v>
       </c>
       <c r="F79" s="29">
-        <v>407.80693295666441</v>
+        <v>454.56265913867628</v>
       </c>
       <c r="G79" s="29">
-        <v>7052.4356828003702</v>
+        <v>7640.1492081188362</v>
       </c>
       <c r="H79" s="29">
-        <v>4955.6656843901901</v>
+        <v>5440.2231602957572</v>
       </c>
       <c r="I79" s="29">
-        <v>6404.5392783269244</v>
+        <v>6801.353514840438</v>
       </c>
       <c r="J79" s="29">
-        <v>6102.3449999999993</v>
+        <v>6594.1525050983128</v>
       </c>
       <c r="K79" s="29">
-        <v>5611.4752901206266</v>
+        <v>6041.4762585572907</v>
       </c>
       <c r="L79" s="29">
-        <v>5435.5178243161236</v>
+        <v>5791.9214418741722</v>
       </c>
       <c r="M79" s="20">
-        <v>39</v>
-      </c>
-      <c r="N79" s="44"/>
+        <v>38</v>
+      </c>
+      <c r="N79" s="32"/>
     </row>
     <row r="80" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B80" s="2">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D80" s="28">
-        <v>6493.8846938678507</v>
+        <v>6500.7788746879123</v>
       </c>
       <c r="E80" s="28">
-        <v>6411.7863439883449</v>
+        <v>6530.5370175144744</v>
       </c>
       <c r="F80" s="28">
-        <v>393.00652711225513</v>
+        <v>348.30924752557388</v>
       </c>
       <c r="G80" s="28">
-        <v>7239</v>
+        <v>7576.2468761207383</v>
       </c>
       <c r="H80" s="28">
-        <v>5402.1652097985616</v>
+        <v>5972.2724099999996</v>
       </c>
       <c r="I80" s="28">
-        <v>6872.6457598629313</v>
+        <v>6951.6495759619856</v>
       </c>
       <c r="J80" s="28">
-        <v>6647.7108638598584</v>
+        <v>6655.1768844756334</v>
       </c>
       <c r="K80" s="28">
-        <v>6181.7881814954908</v>
+        <v>6332.9803378588922</v>
       </c>
       <c r="L80" s="28">
-        <v>5954.6866367993234</v>
+        <v>6118.3</v>
       </c>
       <c r="M80" s="5">
-        <v>39</v>
-      </c>
-      <c r="N80" s="44"/>
+        <v>38</v>
+      </c>
+      <c r="N80" s="32"/>
     </row>
     <row r="81" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B81" s="17">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C81" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D81" s="29">
-        <v>6604.2181182640797</v>
+        <v>6849.5532937952648</v>
       </c>
       <c r="E81" s="29">
-        <v>6620.0834178411806</v>
+        <v>6898.5799144514913</v>
       </c>
       <c r="F81" s="29">
-        <v>350.47106963122673</v>
+        <v>438.67106681398928</v>
       </c>
       <c r="G81" s="29">
-        <v>7531.129713440665</v>
+        <v>8301.2622668812437</v>
       </c>
       <c r="H81" s="29">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="I81" s="29">
-        <v>7052</v>
+        <v>7415.4225492795258</v>
       </c>
       <c r="J81" s="29">
-        <v>6762.6143995634166</v>
+        <v>7149.0334845001253</v>
       </c>
       <c r="K81" s="29">
-        <v>6392.5671323949864</v>
+        <v>6637.8879096173523</v>
       </c>
       <c r="L81" s="29">
-        <v>6204.9992185164037</v>
+        <v>6383.4888346566904</v>
       </c>
       <c r="M81" s="20">
-        <v>39</v>
-      </c>
-      <c r="N81" s="44"/>
+        <v>38</v>
+      </c>
+      <c r="N81" s="32"/>
     </row>
     <row r="82" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B82" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D82" s="28">
-        <v>6950.7882631303464</v>
+        <v>6891.7730416205286</v>
       </c>
       <c r="E82" s="28">
-        <v>6935.2542231142424</v>
+        <v>6923.3583767375567</v>
       </c>
       <c r="F82" s="28">
-        <v>420.26157190776871</v>
+        <v>400.31716871792162</v>
       </c>
       <c r="G82" s="28">
-        <v>7900</v>
+        <v>8136.8805849166347</v>
       </c>
       <c r="H82" s="28">
-        <v>6100</v>
+        <v>6200</v>
       </c>
       <c r="I82" s="28">
-        <v>7464.119232150153</v>
+        <v>7388.1363158569848</v>
       </c>
       <c r="J82" s="28">
-        <v>7252.5132221477143</v>
+        <v>7066.6966555493509</v>
       </c>
       <c r="K82" s="28">
-        <v>6646.361297186786</v>
+        <v>6708.2941218988844</v>
       </c>
       <c r="L82" s="28">
-        <v>6390.9508426552193</v>
+        <v>6472.3629428791546</v>
       </c>
       <c r="M82" s="5">
-        <v>39</v>
-      </c>
-      <c r="N82" s="44"/>
+        <v>38</v>
+      </c>
+      <c r="N82" s="32"/>
     </row>
     <row r="83" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B83" s="17">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C83" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D83" s="29">
-        <v>6942.2093282749383</v>
+        <v>7318.5</v>
       </c>
       <c r="E83" s="29">
-        <v>6912.3543162407896</v>
+        <v>7250.7752641430588</v>
       </c>
       <c r="F83" s="29">
-        <v>380.19078497235517</v>
+        <v>442.69381875811632</v>
       </c>
       <c r="G83" s="29">
-        <v>7564.3792143533456</v>
+        <v>8181.5925722602442</v>
       </c>
       <c r="H83" s="29">
-        <v>6145.3442796922227</v>
+        <v>5900</v>
       </c>
       <c r="I83" s="29">
-        <v>7310.9770931547228</v>
+        <v>7706.7801078670336</v>
       </c>
       <c r="J83" s="29">
-        <v>7200.2852701969387</v>
+        <v>7545.6336861224436</v>
       </c>
       <c r="K83" s="29">
-        <v>6681.8627479325896</v>
+        <v>7000</v>
       </c>
       <c r="L83" s="29">
-        <v>6319.1857259702338</v>
+        <v>6721.3119347614802</v>
       </c>
       <c r="M83" s="20">
-        <v>39</v>
-      </c>
-      <c r="N83" s="44"/>
+        <v>38</v>
+      </c>
+      <c r="N83" s="32"/>
     </row>
     <row r="84" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B84" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D84" s="28">
-        <v>7317</v>
+        <v>7152.796565866769</v>
       </c>
       <c r="E84" s="28">
-        <v>7227.3730656252174</v>
+        <v>7114.1741412359452</v>
       </c>
       <c r="F84" s="28">
-        <v>504.82802631420537</v>
+        <v>487.02598104844969</v>
       </c>
       <c r="G84" s="28">
-        <v>8342.9875834676568</v>
+        <v>7943.6201748847679</v>
       </c>
       <c r="H84" s="28">
-        <v>5900</v>
+        <v>5800</v>
       </c>
       <c r="I84" s="28">
-        <v>7694.0557822660539</v>
+        <v>7723.6639972649782</v>
       </c>
       <c r="J84" s="28">
-        <v>7523.1998728427861</v>
+        <v>7400.7250000000004</v>
       </c>
       <c r="K84" s="28">
-        <v>7005.8942020405248</v>
+        <v>6843.3927992909476</v>
       </c>
       <c r="L84" s="28">
-        <v>6563.587905213888</v>
+        <v>6456.1976321958491</v>
       </c>
       <c r="M84" s="5">
-        <v>39</v>
-      </c>
-      <c r="N84" s="44"/>
+        <v>38</v>
+      </c>
+      <c r="N84" s="32"/>
     </row>
     <row r="85" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B85" s="21" t="s">
@@ -4550,36 +4548,36 @@
         <v>25</v>
       </c>
       <c r="D85" s="29">
-        <v>80709.5</v>
+        <v>80203.858560367691</v>
       </c>
       <c r="E85" s="29">
-        <v>80580.615479673885</v>
+        <v>79972.09667408622</v>
       </c>
       <c r="F85" s="29">
-        <v>3150.2367418590688</v>
+        <v>3087.420661986449</v>
       </c>
       <c r="G85" s="29">
-        <v>88745.232790366397</v>
+        <v>87847.401871401438</v>
       </c>
       <c r="H85" s="29">
-        <v>73820</v>
+        <v>73488.254769533334</v>
       </c>
       <c r="I85" s="29">
-        <v>83657.249105527881</v>
+        <v>83199.899503048509</v>
       </c>
       <c r="J85" s="29">
-        <v>82132.887092730147</v>
+        <v>81700</v>
       </c>
       <c r="K85" s="29">
-        <v>78788.016510359419</v>
+        <v>77999</v>
       </c>
       <c r="L85" s="29">
-        <v>76550.3</v>
+        <v>75374</v>
       </c>
       <c r="M85" s="20">
-        <v>42</v>
-      </c>
-      <c r="N85" s="44"/>
+        <v>41</v>
+      </c>
+      <c r="N85" s="32"/>
     </row>
     <row r="86" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B86" s="6" t="s">
@@ -4589,36 +4587,36 @@
         <v>25</v>
       </c>
       <c r="D86" s="28">
-        <v>85156.231834348961</v>
+        <v>85199</v>
       </c>
       <c r="E86" s="28">
-        <v>85929.449544764881</v>
+        <v>85647.318123030709</v>
       </c>
       <c r="F86" s="28">
-        <v>5903.1613273874873</v>
+        <v>4983.2277380503247</v>
       </c>
       <c r="G86" s="28">
-        <v>98363.818730191764</v>
+        <v>97155.108229308855</v>
       </c>
       <c r="H86" s="28">
-        <v>74510</v>
+        <v>75328.427326754027</v>
       </c>
       <c r="I86" s="28">
-        <v>94313.520146828465</v>
+        <v>92668.804619915682</v>
       </c>
       <c r="J86" s="28">
-        <v>89597.781782848862</v>
+        <v>88092</v>
       </c>
       <c r="K86" s="28">
-        <v>82073.5</v>
+        <v>82679</v>
       </c>
       <c r="L86" s="28">
-        <v>78857</v>
+        <v>79772.399999999994</v>
       </c>
       <c r="M86" s="5">
-        <v>36</v>
-      </c>
-      <c r="N86" s="44"/>
+        <v>37</v>
+      </c>
+      <c r="N86" s="32"/>
     </row>
     <row r="87" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B87" s="9"/>
@@ -4696,36 +4694,36 @@
         <v>28</v>
       </c>
       <c r="D91" s="29">
-        <v>16000</v>
+        <v>16080</v>
       </c>
       <c r="E91" s="29">
-        <v>15468.17162809911</v>
+        <v>15598.66416189245</v>
       </c>
       <c r="F91" s="29">
-        <v>2207.0947726099771</v>
+        <v>2139.8807089270722</v>
       </c>
       <c r="G91" s="29">
-        <v>18224.369398282299</v>
+        <v>19000</v>
       </c>
       <c r="H91" s="29">
-        <v>9004</v>
+        <v>9000</v>
       </c>
       <c r="I91" s="29">
-        <v>17721</v>
+        <v>17729.77867516558</v>
       </c>
       <c r="J91" s="29">
-        <v>16838.53</v>
+        <v>16892.570425442162</v>
       </c>
       <c r="K91" s="29">
-        <v>15082</v>
+        <v>14905</v>
       </c>
       <c r="L91" s="29">
-        <v>12500</v>
+        <v>12564.04388456352</v>
       </c>
       <c r="M91" s="20">
-        <v>41</v>
-      </c>
-      <c r="N91" s="43"/>
+        <v>40</v>
+      </c>
+      <c r="N91" s="31"/>
     </row>
     <row r="92" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B92" s="6" t="s">
@@ -4735,36 +4733,36 @@
         <v>28</v>
       </c>
       <c r="D92" s="28">
-        <v>19200</v>
+        <v>19740.016994455451</v>
       </c>
       <c r="E92" s="28">
-        <v>18635.17828252081</v>
+        <v>18839.581270077269</v>
       </c>
       <c r="F92" s="28">
-        <v>4246.6697004547541</v>
+        <v>3444.6313240200229</v>
       </c>
       <c r="G92" s="28">
-        <v>26929.63</v>
+        <v>23566.04</v>
       </c>
       <c r="H92" s="28">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="I92" s="28">
-        <v>22079.909340166068</v>
+        <v>21755.682233610121</v>
       </c>
       <c r="J92" s="28">
-        <v>20834.25</v>
+        <v>21018.25</v>
       </c>
       <c r="K92" s="28">
-        <v>17527.5</v>
+        <v>17438.977079300072</v>
       </c>
       <c r="L92" s="28">
-        <v>14458.994575671801</v>
+        <v>15000</v>
       </c>
       <c r="M92" s="5">
-        <v>34</v>
-      </c>
-      <c r="N92" s="43"/>
+        <v>36</v>
+      </c>
+      <c r="N92" s="31"/>
     </row>
     <row r="93" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B93" s="9"/>
@@ -4842,36 +4840,36 @@
         <v>30</v>
       </c>
       <c r="D97" s="4">
-        <v>6.7222115435231782</v>
+        <v>6.7</v>
       </c>
       <c r="E97" s="4">
-        <v>6.7986147782534756</v>
+        <v>6.8023718522159502</v>
       </c>
       <c r="F97" s="4">
-        <v>0.44489756209527209</v>
+        <v>0.3891955647683662</v>
       </c>
       <c r="G97" s="4">
         <v>8.1</v>
       </c>
       <c r="H97" s="4">
-        <v>5.9882005014101942</v>
+        <v>6.14</v>
       </c>
       <c r="I97" s="4">
-        <v>7.4</v>
+        <v>7.26</v>
       </c>
       <c r="J97" s="4">
         <v>7</v>
       </c>
       <c r="K97" s="4">
-        <v>6.5</v>
+        <v>6.6300000000000008</v>
       </c>
       <c r="L97" s="4">
-        <v>6.3000000000000007</v>
+        <v>6.44</v>
       </c>
       <c r="M97" s="8">
-        <v>36</v>
-      </c>
-      <c r="N97" s="43"/>
+        <v>35</v>
+      </c>
+      <c r="N97" s="31"/>
     </row>
     <row r="98" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B98" s="17" t="s">
@@ -4884,33 +4882,33 @@
         <v>7.3</v>
       </c>
       <c r="E98" s="19">
-        <v>7.2905209725055578</v>
+        <v>7.2691858921509542</v>
       </c>
       <c r="F98" s="19">
-        <v>0.4744476558759711</v>
+        <v>0.43617611341474422</v>
       </c>
       <c r="G98" s="19">
-        <v>8.3000000000000007</v>
+        <v>8.4</v>
       </c>
       <c r="H98" s="19">
         <v>6.4</v>
       </c>
       <c r="I98" s="19">
-        <v>7.8840000000000003</v>
+        <v>7.77</v>
       </c>
       <c r="J98" s="19">
-        <v>7.6318379425839069</v>
+        <v>7.5</v>
       </c>
       <c r="K98" s="19">
-        <v>7</v>
+        <v>7.0250000000000004</v>
       </c>
       <c r="L98" s="19">
-        <v>6.6</v>
+        <v>6.6261113412660366</v>
       </c>
       <c r="M98" s="20">
-        <v>35</v>
-      </c>
-      <c r="N98" s="43"/>
+        <v>34</v>
+      </c>
+      <c r="N98" s="31"/>
     </row>
     <row r="99" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B99" s="6" t="s">
@@ -4920,36 +4918,36 @@
         <v>30</v>
       </c>
       <c r="D99" s="4">
-        <v>7.2</v>
+        <v>7.15</v>
       </c>
       <c r="E99" s="4">
-        <v>7.1208092617664516</v>
+        <v>7.1095290279087724</v>
       </c>
       <c r="F99" s="4">
-        <v>0.55977117273179067</v>
+        <v>0.5822696364922666</v>
       </c>
       <c r="G99" s="4">
-        <v>8.4</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="H99" s="4">
-        <v>6.2175137401140592</v>
+        <v>6.274548463389519</v>
       </c>
       <c r="I99" s="4">
-        <v>7.7020000000000008</v>
+        <v>7.8</v>
       </c>
       <c r="J99" s="4">
         <v>7.5</v>
       </c>
       <c r="K99" s="4">
-        <v>6.66</v>
+        <v>6.5475000000000003</v>
       </c>
       <c r="L99" s="4">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="M99" s="5">
-        <v>35</v>
-      </c>
-      <c r="N99" s="43"/>
+        <v>34</v>
+      </c>
+      <c r="N99" s="31"/>
     </row>
     <row r="100" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B100" s="21" t="s">
@@ -4959,36 +4957,36 @@
         <v>31</v>
       </c>
       <c r="D100" s="19">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="E100" s="19">
-        <v>6.7071012544176298</v>
+        <v>6.8580140960867624</v>
       </c>
       <c r="F100" s="19">
-        <v>0.61223685424154506</v>
+        <v>0.66410542229908653</v>
       </c>
       <c r="G100" s="19">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="H100" s="19">
-        <v>5.0785095504135827</v>
+        <v>5.7</v>
       </c>
       <c r="I100" s="19">
-        <v>7.4060000000000006</v>
+        <v>7.4823821846054202</v>
       </c>
       <c r="J100" s="19">
-        <v>6.9580045913649728</v>
+        <v>7.15</v>
       </c>
       <c r="K100" s="19">
-        <v>6.3500000000000014</v>
+        <v>6.5299999999999994</v>
       </c>
       <c r="L100" s="19">
-        <v>6.1974643458316523</v>
+        <v>6.2192846205023464</v>
       </c>
       <c r="M100" s="20">
         <v>35</v>
       </c>
-      <c r="N100" s="43"/>
+      <c r="N100" s="31"/>
     </row>
     <row r="101" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B101" s="6" t="s">
@@ -5001,33 +4999,33 @@
         <v>6.5</v>
       </c>
       <c r="E101" s="4">
-        <v>6.5816771714761861</v>
+        <v>6.6912426032503447</v>
       </c>
       <c r="F101" s="4">
-        <v>0.72650706279252575</v>
+        <v>0.87977999001093021</v>
       </c>
       <c r="G101" s="4">
-        <v>8.1999999999999993</v>
+        <v>10</v>
       </c>
       <c r="H101" s="4">
-        <v>4.7302581941679378</v>
+        <v>5.376023903541209</v>
       </c>
       <c r="I101" s="4">
-        <v>7.44</v>
+        <v>7.5</v>
       </c>
       <c r="J101" s="4">
-        <v>7.1</v>
+        <v>7.0749999999999993</v>
       </c>
       <c r="K101" s="4">
-        <v>6.0883255091442354</v>
+        <v>6.2200000000000006</v>
       </c>
       <c r="L101" s="4">
-        <v>5.84</v>
+        <v>5.8</v>
       </c>
       <c r="M101" s="5">
-        <v>33</v>
-      </c>
-      <c r="N101" s="43"/>
+        <v>34</v>
+      </c>
+      <c r="N101" s="31"/>
     </row>
     <row r="102" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B102" s="9"/>
@@ -5105,36 +5103,36 @@
         <v>33</v>
       </c>
       <c r="D106" s="19">
-        <v>0.13109489618399969</v>
+        <v>0.7567949337364599</v>
       </c>
       <c r="E106" s="19">
-        <v>0.24435923384415081</v>
+        <v>0.71596649246569799</v>
       </c>
       <c r="F106" s="19">
-        <v>0.31622400503116183</v>
+        <v>0.1866747725515136</v>
       </c>
       <c r="G106" s="19">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="H106" s="19">
-        <v>-0.19335920059689871</v>
+        <v>0.15</v>
       </c>
       <c r="I106" s="19">
-        <v>0.65089831927516317</v>
+        <v>0.83444912872401877</v>
       </c>
       <c r="J106" s="19">
-        <v>0.31151954382744029</v>
+        <v>0.8</v>
       </c>
       <c r="K106" s="19">
-        <v>8.2500000000000004E-2</v>
+        <v>0.7</v>
       </c>
       <c r="L106" s="19">
-        <v>-1.37732848547023E-2</v>
+        <v>0.47326044347827823</v>
       </c>
       <c r="M106" s="20">
         <v>38</v>
       </c>
-      <c r="N106" s="43"/>
+      <c r="N106" s="31"/>
     </row>
     <row r="107" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B107" s="6" t="s">
@@ -5144,36 +5142,36 @@
         <v>33</v>
       </c>
       <c r="D107" s="4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E107" s="4">
-        <v>0.87856983116249787</v>
+        <v>1.0202757783154679</v>
       </c>
       <c r="F107" s="4">
-        <v>0.55508168016261195</v>
+        <v>0.47510497134427909</v>
       </c>
       <c r="G107" s="4">
-        <v>3.46983603033526</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H107" s="4">
-        <v>0.1</v>
+        <v>8.5008923760465649E-2</v>
       </c>
       <c r="I107" s="4">
-        <v>1.3336467009544419</v>
+        <v>1.6105767590262581</v>
       </c>
       <c r="J107" s="4">
-        <v>1</v>
+        <v>1.2904911467065521</v>
       </c>
       <c r="K107" s="4">
-        <v>0.60293114881066434</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="L107" s="4">
-        <v>0.28499999999999998</v>
+        <v>0.37300000000000011</v>
       </c>
       <c r="M107" s="5">
         <v>38</v>
       </c>
-      <c r="N107" s="43"/>
+      <c r="N107" s="31"/>
     </row>
     <row r="108" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B108" s="17" t="s">
@@ -5183,36 +5181,36 @@
         <v>33</v>
       </c>
       <c r="D108" s="19">
-        <v>1.02</v>
+        <v>0.93336924515468733</v>
       </c>
       <c r="E108" s="19">
-        <v>1.075097269094591</v>
+        <v>0.9280191792022523</v>
       </c>
       <c r="F108" s="19">
-        <v>0.44961416831536749</v>
+        <v>0.41177916757644017</v>
       </c>
       <c r="G108" s="19">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H108" s="19">
-        <v>0.3</v>
+        <v>0.16659991102225821</v>
       </c>
       <c r="I108" s="19">
-        <v>1.5176631670819349</v>
+        <v>1.360000000000001</v>
       </c>
       <c r="J108" s="19">
-        <v>1.3</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K108" s="19">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="L108" s="19">
-        <v>0.49099999999999999</v>
+        <v>0.38800000000000001</v>
       </c>
       <c r="M108" s="20">
         <v>38</v>
       </c>
-      <c r="N108" s="43"/>
+      <c r="N108" s="31"/>
     </row>
     <row r="109" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B109" s="6" t="s">
@@ -5222,36 +5220,36 @@
         <v>34</v>
       </c>
       <c r="D109" s="4">
-        <v>3.235914853899136</v>
+        <v>3.4019209692617269</v>
       </c>
       <c r="E109" s="4">
-        <v>3.2658765876893008</v>
+        <v>3.3253341782855088</v>
       </c>
       <c r="F109" s="4">
-        <v>0.78933032519859991</v>
+        <v>0.67085302813125136</v>
       </c>
       <c r="G109" s="4">
-        <v>5.2</v>
+        <v>5.0178551707368069</v>
       </c>
       <c r="H109" s="4">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="I109" s="4">
-        <v>4.1800000000000006</v>
+        <v>4.1409119291826624</v>
       </c>
       <c r="J109" s="4">
-        <v>3.9129900559775872</v>
+        <v>3.7</v>
       </c>
       <c r="K109" s="4">
-        <v>2.7727388763773901</v>
+        <v>2.9</v>
       </c>
       <c r="L109" s="4">
-        <v>2.261112147985588</v>
+        <v>2.5254574418494911</v>
       </c>
       <c r="M109" s="5">
-        <v>43</v>
-      </c>
-      <c r="N109" s="43"/>
+        <v>44</v>
+      </c>
+      <c r="N109" s="31"/>
     </row>
     <row r="110" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B110" s="21" t="s">
@@ -5261,36 +5259,36 @@
         <v>34</v>
       </c>
       <c r="D110" s="19">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="E110" s="19">
-        <v>3.2660503054024348</v>
+        <v>3.1888268870110141</v>
       </c>
       <c r="F110" s="19">
-        <v>0.71361985951220486</v>
+        <v>0.681832643713844</v>
       </c>
       <c r="G110" s="19">
-        <v>5.3</v>
+        <v>5.1367219472784109</v>
       </c>
       <c r="H110" s="19">
         <v>2</v>
       </c>
       <c r="I110" s="19">
-        <v>4.4758878708254972</v>
+        <v>4</v>
       </c>
       <c r="J110" s="19">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K110" s="19">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="L110" s="19">
-        <v>2.5</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="M110" s="20">
-        <v>38</v>
-      </c>
-      <c r="N110" s="43"/>
+        <v>41</v>
+      </c>
+      <c r="N110" s="31"/>
     </row>
     <row r="111" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B111" s="6" t="s">
@@ -5300,13 +5298,13 @@
         <v>34</v>
       </c>
       <c r="D111" s="4">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="E111" s="4">
-        <v>3.1302730795620199</v>
+        <v>3.10594605483247</v>
       </c>
       <c r="F111" s="4">
-        <v>0.78152454985114184</v>
+        <v>0.78265271294294125</v>
       </c>
       <c r="G111" s="4">
         <v>5</v>
@@ -5315,25 +5313,25 @@
         <v>0.5</v>
       </c>
       <c r="I111" s="4">
-        <v>3.8561322606329038</v>
+        <v>3.99</v>
       </c>
       <c r="J111" s="4">
         <v>3.5</v>
       </c>
       <c r="K111" s="4">
-        <v>2.889066978886623</v>
+        <v>2.873823454092963</v>
       </c>
       <c r="L111" s="4">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="M111" s="5">
-        <v>29</v>
-      </c>
-      <c r="N111" s="43"/>
+        <v>32</v>
+      </c>
+      <c r="N111" s="31"/>
     </row>
     <row r="112" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B112" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C112" s="10"/>
       <c r="D112" s="10"/>
@@ -5378,21 +5376,21 @@
     <col min="13" max="13" width="18.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
+    <row r="2" spans="2:14" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B2" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
     </row>
     <row r="3" spans="2:14" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B3" s="30"/>
@@ -5413,323 +5411,323 @@
       <c r="M4" s="13"/>
     </row>
     <row r="5" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="15"/>
     </row>
     <row r="6" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="42" t="s">
+      <c r="F6" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="42" t="s">
+      <c r="G6" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="42" t="s">
+      <c r="H6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="42" t="s">
+      <c r="I6" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="42" t="s">
+      <c r="J6" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="42" t="s">
+      <c r="K6" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="42" t="s">
+      <c r="L6" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="M6" s="42" t="s">
+      <c r="M6" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B7" s="2">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="4">
-        <v>2.4070011506796121</v>
+        <v>2.6840820303427431</v>
       </c>
       <c r="E7" s="4">
+        <v>2.6404101517137142</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0.16105004162975839</v>
+      </c>
+      <c r="G7" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="H7" s="4">
         <v>2.4</v>
       </c>
-      <c r="F7" s="4">
-        <v>0.1060457028515715</v>
-      </c>
-      <c r="G7" s="4">
+      <c r="I7" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="J7" s="4">
+        <v>2.82</v>
+      </c>
+      <c r="K7" s="4">
         <v>2.6</v>
       </c>
-      <c r="H7" s="4">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="I7" s="4">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="J7" s="4">
-        <v>2.490002876699029</v>
-      </c>
-      <c r="K7" s="4">
-        <v>2.3025000000000002</v>
-      </c>
       <c r="L7" s="4">
-        <v>2.2999999999999998</v>
+        <v>2.58</v>
       </c>
       <c r="M7" s="5">
         <v>10</v>
       </c>
-      <c r="N7" s="43"/>
+      <c r="N7" s="31"/>
     </row>
     <row r="8" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="37">
-        <v>46081</v>
-      </c>
-      <c r="C8" s="32" t="s">
+      <c r="B8" s="35">
+        <v>46112</v>
+      </c>
+      <c r="C8" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="33">
-        <v>2.1634273059756608</v>
-      </c>
-      <c r="E8" s="33">
-        <v>2.1495398401550059</v>
-      </c>
-      <c r="F8" s="33">
-        <v>0.1995546735897524</v>
-      </c>
-      <c r="G8" s="33">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="H8" s="33">
-        <v>1.9</v>
-      </c>
-      <c r="I8" s="33">
-        <v>2.343674041501941</v>
-      </c>
-      <c r="J8" s="33">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="K8" s="33">
-        <v>2.0249999999999999</v>
-      </c>
-      <c r="L8" s="33">
-        <v>1.9</v>
-      </c>
-      <c r="M8" s="36">
+      <c r="D8" s="37">
+        <v>2.5604564311061</v>
+      </c>
+      <c r="E8" s="37">
+        <v>2.5522821555305009</v>
+      </c>
+      <c r="F8" s="37">
+        <v>0.23180065538369521</v>
+      </c>
+      <c r="G8" s="37">
+        <v>2.8</v>
+      </c>
+      <c r="H8" s="37">
+        <v>2.04</v>
+      </c>
+      <c r="I8" s="37">
+        <v>2.8</v>
+      </c>
+      <c r="J8" s="37">
+        <v>2.7450000000000001</v>
+      </c>
+      <c r="K8" s="37">
+        <v>2.5</v>
+      </c>
+      <c r="L8" s="37">
+        <v>2.3639999999999999</v>
+      </c>
+      <c r="M8" s="38">
         <v>10</v>
       </c>
-      <c r="N8" s="43"/>
+      <c r="N8" s="31"/>
     </row>
     <row r="9" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="4">
-        <v>2.2525708992391569</v>
+        <v>2.2450277255533631</v>
       </c>
       <c r="E9" s="4">
-        <v>2.2789634579837892</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="F9" s="4">
-        <v>0.18730138603033539</v>
+        <v>0.23634496287520021</v>
       </c>
       <c r="G9" s="4">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="H9" s="4">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="I9" s="4">
-        <v>2.4279999999999999</v>
+        <v>2.42</v>
       </c>
       <c r="J9" s="4">
-        <v>2.385836557317988</v>
+        <v>2.3975693138834049</v>
       </c>
       <c r="K9" s="4">
-        <v>2.2000000000000002</v>
+        <v>2.12</v>
       </c>
       <c r="L9" s="4">
-        <v>1.99</v>
+        <v>1.978</v>
       </c>
       <c r="M9" s="5">
         <v>10</v>
       </c>
-      <c r="N9" s="43"/>
+      <c r="N9" s="31"/>
     </row>
     <row r="10" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="37">
-        <v>46142</v>
-      </c>
-      <c r="C10" s="32" t="s">
+      <c r="B10" s="35">
+        <v>46173</v>
+      </c>
+      <c r="C10" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="33">
-        <v>2.0899707175934119</v>
-      </c>
-      <c r="E10" s="33">
-        <v>2.1</v>
-      </c>
-      <c r="F10" s="33">
-        <v>0.18372412849714889</v>
-      </c>
-      <c r="G10" s="33">
-        <v>2.33</v>
-      </c>
-      <c r="H10" s="33">
-        <v>1.72</v>
-      </c>
-      <c r="I10" s="33">
-        <v>2.3029999999999999</v>
-      </c>
-      <c r="J10" s="33">
-        <v>2.1955130914252732</v>
-      </c>
-      <c r="K10" s="33">
-        <v>2.01725576350844</v>
-      </c>
-      <c r="L10" s="33">
-        <v>1.8819999999999999</v>
-      </c>
-      <c r="M10" s="36">
+      <c r="D10" s="37">
+        <v>2.109896623906705</v>
+      </c>
+      <c r="E10" s="37">
+        <v>2.124483119533525</v>
+      </c>
+      <c r="F10" s="37">
+        <v>0.27908877218300759</v>
+      </c>
+      <c r="G10" s="37">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="H10" s="37">
+        <v>1.64</v>
+      </c>
+      <c r="I10" s="37">
+        <v>2.411</v>
+      </c>
+      <c r="J10" s="37">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K10" s="37">
+        <v>1.925</v>
+      </c>
+      <c r="L10" s="37">
+        <v>1.784</v>
+      </c>
+      <c r="M10" s="38">
         <v>10</v>
       </c>
-      <c r="N10" s="43"/>
+      <c r="N10" s="31"/>
     </row>
     <row r="11" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="4">
-        <v>1.923507072902815</v>
+        <v>1.92103443282414</v>
       </c>
       <c r="E11" s="4">
-        <v>1.847253085578838</v>
+        <v>1.9750000000000001</v>
       </c>
       <c r="F11" s="4">
-        <v>0.23726947041435401</v>
+        <v>0.23285820426730361</v>
       </c>
       <c r="G11" s="4">
         <v>2.31</v>
       </c>
       <c r="H11" s="4">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="I11" s="4">
-        <v>2.3010000000000002</v>
+        <v>2.121</v>
       </c>
       <c r="J11" s="4">
-        <v>2.0229234184028568</v>
+        <v>2.067758246181056</v>
       </c>
       <c r="K11" s="4">
         <v>1.8</v>
       </c>
       <c r="L11" s="4">
-        <v>1.69</v>
+        <v>1.5960000000000001</v>
       </c>
       <c r="M11" s="5">
         <v>10</v>
       </c>
-      <c r="N11" s="43"/>
+      <c r="N11" s="31"/>
     </row>
     <row r="12" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="37">
-        <v>46203</v>
-      </c>
-      <c r="C12" s="32" t="s">
+      <c r="B12" s="35">
+        <v>46234</v>
+      </c>
+      <c r="C12" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="33">
-        <v>1.830348264098312</v>
-      </c>
-      <c r="E12" s="33">
-        <v>1.8128756474374501</v>
-      </c>
-      <c r="F12" s="33">
-        <v>0.2070366334929569</v>
-      </c>
-      <c r="G12" s="33">
-        <v>2.11</v>
-      </c>
-      <c r="H12" s="33">
-        <v>1.5</v>
-      </c>
-      <c r="I12" s="33">
-        <v>2.101</v>
-      </c>
-      <c r="J12" s="33">
-        <v>1.986932836527056</v>
-      </c>
-      <c r="K12" s="33">
-        <v>1.7050000000000001</v>
-      </c>
-      <c r="L12" s="33">
-        <v>1.59</v>
-      </c>
-      <c r="M12" s="36">
+      <c r="D12" s="37">
+        <v>1.8930021463070481</v>
+      </c>
+      <c r="E12" s="37">
+        <v>1.9</v>
+      </c>
+      <c r="F12" s="37">
+        <v>0.21250330353661601</v>
+      </c>
+      <c r="G12" s="37">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="H12" s="37">
+        <v>1.52</v>
+      </c>
+      <c r="I12" s="37">
+        <v>2.1120193167634329</v>
+      </c>
+      <c r="J12" s="37">
+        <v>2</v>
+      </c>
+      <c r="K12" s="37">
+        <v>1.8225</v>
+      </c>
+      <c r="L12" s="37">
+        <v>1.5920000000000001</v>
+      </c>
+      <c r="M12" s="38">
         <v>10</v>
       </c>
-      <c r="N12" s="43"/>
+      <c r="N12" s="31"/>
     </row>
     <row r="13" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B13" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="4">
-        <v>1.777487470291329</v>
+        <v>1.752287834187068</v>
       </c>
       <c r="E13" s="4">
-        <v>1.782937463338607</v>
+        <v>1.8</v>
       </c>
       <c r="F13" s="4">
-        <v>0.2440030283471033</v>
+        <v>0.25797018499068952</v>
       </c>
       <c r="G13" s="4">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="H13" s="4">
         <v>1.4</v>
       </c>
       <c r="I13" s="4">
-        <v>2.0089999999999999</v>
+        <v>2.012</v>
       </c>
       <c r="J13" s="4">
-        <v>1.9947499440590211</v>
+        <v>1.972158756403009</v>
       </c>
       <c r="K13" s="4">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="L13" s="4">
         <v>1.49</v>
@@ -5737,46 +5735,46 @@
       <c r="M13" s="5">
         <v>10</v>
       </c>
-      <c r="N13" s="43"/>
+      <c r="N13" s="31"/>
     </row>
     <row r="14" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="33">
-        <v>23.275905283361741</v>
-      </c>
-      <c r="E14" s="33">
-        <v>23.65</v>
-      </c>
-      <c r="F14" s="33">
-        <v>3.1941797662219269</v>
-      </c>
-      <c r="G14" s="33">
-        <v>27.4</v>
-      </c>
-      <c r="H14" s="33">
-        <v>17.8</v>
-      </c>
-      <c r="I14" s="33">
-        <v>26.277863315313081</v>
-      </c>
-      <c r="J14" s="33">
-        <v>25.731330225236139</v>
-      </c>
-      <c r="K14" s="33">
-        <v>21.635412853410379</v>
-      </c>
-      <c r="L14" s="33">
-        <v>18.61</v>
-      </c>
-      <c r="M14" s="36">
+      <c r="C14" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="37">
+        <v>25.07119898103975</v>
+      </c>
+      <c r="E14" s="37">
+        <v>24.85</v>
+      </c>
+      <c r="F14" s="37">
+        <v>2.7514996674194792</v>
+      </c>
+      <c r="G14" s="37">
+        <v>30.42</v>
+      </c>
+      <c r="H14" s="37">
+        <v>20.6</v>
+      </c>
+      <c r="I14" s="37">
+        <v>27.431999999999999</v>
+      </c>
+      <c r="J14" s="37">
+        <v>26.392499999999998</v>
+      </c>
+      <c r="K14" s="37">
+        <v>24.05</v>
+      </c>
+      <c r="L14" s="37">
+        <v>21.789790829357791</v>
+      </c>
+      <c r="M14" s="38">
         <v>10</v>
       </c>
-      <c r="N14" s="43"/>
+      <c r="N14" s="31"/>
     </row>
     <row r="15" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
@@ -5786,402 +5784,402 @@
         <v>16</v>
       </c>
       <c r="D15" s="4">
-        <v>24.517452409140091</v>
+        <v>27.831465949491481</v>
       </c>
       <c r="E15" s="4">
-        <v>25</v>
+        <v>27.15</v>
       </c>
       <c r="F15" s="4">
-        <v>2.9754015962113538</v>
+        <v>2.5666655468704529</v>
       </c>
       <c r="G15" s="4">
-        <v>28.6</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="H15" s="4">
-        <v>19.899999999999999</v>
+        <v>23.6</v>
       </c>
       <c r="I15" s="4">
-        <v>27.34</v>
+        <v>29.92</v>
       </c>
       <c r="J15" s="4">
-        <v>26.781834008962459</v>
+        <v>29.5</v>
       </c>
       <c r="K15" s="4">
-        <v>22.756863128370011</v>
+        <v>26.85</v>
       </c>
       <c r="L15" s="4">
-        <v>19.989999999999998</v>
+        <v>25.233193545423291</v>
       </c>
       <c r="M15" s="5">
         <v>10</v>
       </c>
-      <c r="N15" s="43"/>
+      <c r="N15" s="31"/>
     </row>
     <row r="18" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="41"/>
-      <c r="L18" s="41"/>
-      <c r="M18" s="41"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="15"/>
     </row>
     <row r="19" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="42" t="s">
+      <c r="D19" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E19" s="42" t="s">
+      <c r="E19" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F19" s="42" t="s">
+      <c r="F19" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G19" s="42" t="s">
+      <c r="G19" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H19" s="42" t="s">
+      <c r="H19" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I19" s="42" t="s">
+      <c r="I19" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J19" s="42" t="s">
+      <c r="J19" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K19" s="42" t="s">
+      <c r="K19" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="L19" s="42" t="s">
+      <c r="L19" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="M19" s="42" t="s">
+      <c r="M19" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="20" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B20" s="2">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="4">
-        <v>2.3574999999999999</v>
+        <v>2.5115813705975158</v>
       </c>
       <c r="E20" s="4">
-        <v>2.3574999999999999</v>
+        <v>2.4929068529875771</v>
       </c>
       <c r="F20" s="4">
-        <v>0.28541636253025149</v>
+        <v>0.20373184158730409</v>
       </c>
       <c r="G20" s="4">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="H20" s="4">
-        <v>1.75</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="I20" s="4">
-        <v>2.62</v>
+        <v>2.806</v>
       </c>
       <c r="J20" s="4">
-        <v>2.5150000000000001</v>
+        <v>2.5775000000000001</v>
       </c>
       <c r="K20" s="4">
-        <v>2.2250000000000001</v>
+        <v>2.4175</v>
       </c>
       <c r="L20" s="4">
-        <v>2.1459999999999999</v>
+        <v>2.2810000000000001</v>
       </c>
       <c r="M20" s="5">
         <v>10</v>
       </c>
-      <c r="N20" s="43"/>
+      <c r="N20" s="31"/>
     </row>
     <row r="21" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B21" s="37">
-        <v>46081</v>
-      </c>
-      <c r="C21" s="32" t="s">
+      <c r="B21" s="35">
+        <v>46112</v>
+      </c>
+      <c r="C21" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="33">
-        <v>2.1309999999999998</v>
-      </c>
-      <c r="E21" s="33">
-        <v>2.2025000000000001</v>
-      </c>
-      <c r="F21" s="33">
-        <v>0.25281525973634489</v>
-      </c>
-      <c r="G21" s="33">
-        <v>2.48</v>
-      </c>
-      <c r="H21" s="33">
-        <v>1.7</v>
-      </c>
-      <c r="I21" s="33">
-        <v>2.4079999999999999</v>
-      </c>
-      <c r="J21" s="33">
-        <v>2.2762500000000001</v>
-      </c>
-      <c r="K21" s="33">
-        <v>1.95</v>
-      </c>
-      <c r="L21" s="33">
-        <v>1.8080000000000001</v>
-      </c>
-      <c r="M21" s="36">
+      <c r="D21" s="37">
+        <v>2.3277941650078882</v>
+      </c>
+      <c r="E21" s="37">
+        <v>2.3689708250394399</v>
+      </c>
+      <c r="F21" s="37">
+        <v>0.2359994103640928</v>
+      </c>
+      <c r="G21" s="37">
+        <v>2.6</v>
+      </c>
+      <c r="H21" s="37">
+        <v>1.89</v>
+      </c>
+      <c r="I21" s="37">
+        <v>2.573</v>
+      </c>
+      <c r="J21" s="37">
+        <v>2.5</v>
+      </c>
+      <c r="K21" s="37">
+        <v>2.15</v>
+      </c>
+      <c r="L21" s="37">
+        <v>2.0609999999999999</v>
+      </c>
+      <c r="M21" s="38">
         <v>10</v>
       </c>
-      <c r="N21" s="43"/>
+      <c r="N21" s="31"/>
     </row>
     <row r="22" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B22" s="2">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="4">
-        <v>2.0769250000000001</v>
+        <v>2.167350040256705</v>
       </c>
       <c r="E22" s="4">
-        <v>2.062125</v>
+        <v>2.2217502012835242</v>
       </c>
       <c r="F22" s="4">
-        <v>0.29255360501206551</v>
+        <v>0.27501254484277998</v>
       </c>
       <c r="G22" s="4">
-        <v>2.625</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="H22" s="4">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="I22" s="4">
-        <v>2.3325</v>
+        <v>2.4089999999999998</v>
       </c>
       <c r="J22" s="4">
-        <v>2.2149999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="K22" s="4">
-        <v>1.9624999999999999</v>
+        <v>2</v>
       </c>
       <c r="L22" s="4">
-        <v>1.7749999999999999</v>
+        <v>1.8740000000000001</v>
       </c>
       <c r="M22" s="5">
         <v>10</v>
       </c>
-      <c r="N22" s="43"/>
+      <c r="N22" s="31"/>
     </row>
     <row r="23" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B23" s="37">
-        <v>46142</v>
-      </c>
-      <c r="C23" s="32" t="s">
+      <c r="B23" s="35">
+        <v>46173</v>
+      </c>
+      <c r="C23" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="33">
-        <v>1.98306125</v>
-      </c>
-      <c r="E23" s="33">
-        <v>2</v>
-      </c>
-      <c r="F23" s="33">
-        <v>0.22923751332542641</v>
-      </c>
-      <c r="G23" s="33">
-        <v>2.23</v>
-      </c>
-      <c r="H23" s="33">
-        <v>1.47</v>
-      </c>
-      <c r="I23" s="33">
-        <v>2.2075</v>
-      </c>
-      <c r="J23" s="33">
-        <v>2.163903125</v>
-      </c>
-      <c r="K23" s="33">
-        <v>1.9025000000000001</v>
-      </c>
-      <c r="L23" s="33">
-        <v>1.7669999999999999</v>
-      </c>
-      <c r="M23" s="36">
+      <c r="D23" s="37">
+        <v>2.0504725342181991</v>
+      </c>
+      <c r="E23" s="37">
+        <v>2.1348626710909948</v>
+      </c>
+      <c r="F23" s="37">
+        <v>0.31793726227297692</v>
+      </c>
+      <c r="G23" s="37">
+        <v>2.46</v>
+      </c>
+      <c r="H23" s="37">
+        <v>1.51</v>
+      </c>
+      <c r="I23" s="37">
+        <v>2.4195000000000002</v>
+      </c>
+      <c r="J23" s="37">
+        <v>2.2749999999999999</v>
+      </c>
+      <c r="K23" s="37">
+        <v>1.8</v>
+      </c>
+      <c r="L23" s="37">
+        <v>1.726</v>
+      </c>
+      <c r="M23" s="38">
         <v>10</v>
       </c>
-      <c r="N23" s="43"/>
+      <c r="N23" s="31"/>
     </row>
     <row r="24" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B24" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="4">
-        <v>1.8172270625</v>
+        <v>1.878926654085469</v>
       </c>
       <c r="E24" s="4">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="F24" s="4">
-        <v>0.27878167137746201</v>
+        <v>0.28917961158639288</v>
       </c>
       <c r="G24" s="4">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="H24" s="4">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="I24" s="4">
-        <v>2.1934999999999998</v>
+        <v>2.2214999999999998</v>
       </c>
       <c r="J24" s="4">
-        <v>1.9993176562499999</v>
+        <v>2.0706999056410189</v>
       </c>
       <c r="K24" s="4">
-        <v>1.625</v>
+        <v>1.6775</v>
       </c>
       <c r="L24" s="4">
-        <v>1.5820000000000001</v>
+        <v>1.585</v>
       </c>
       <c r="M24" s="5">
         <v>10</v>
       </c>
-      <c r="N24" s="43"/>
+      <c r="N24" s="31"/>
     </row>
     <row r="25" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="37">
-        <v>46203</v>
-      </c>
-      <c r="C25" s="32" t="s">
+      <c r="B25" s="35">
+        <v>46234</v>
+      </c>
+      <c r="C25" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="33">
-        <v>1.7432680031250001</v>
-      </c>
-      <c r="E25" s="33">
-        <v>1.615</v>
-      </c>
-      <c r="F25" s="33">
-        <v>0.25736899514030009</v>
-      </c>
-      <c r="G25" s="33">
-        <v>2.16</v>
-      </c>
-      <c r="H25" s="33">
-        <v>1.4</v>
-      </c>
-      <c r="I25" s="33">
-        <v>2.016</v>
-      </c>
-      <c r="J25" s="33">
-        <v>1.9831700078125001</v>
-      </c>
-      <c r="K25" s="33">
-        <v>1.6</v>
-      </c>
-      <c r="L25" s="33">
-        <v>1.49</v>
-      </c>
-      <c r="M25" s="36">
+      <c r="D25" s="37">
+        <v>1.826512655972649</v>
+      </c>
+      <c r="E25" s="37">
+        <v>1.8975</v>
+      </c>
+      <c r="F25" s="37">
+        <v>0.26347127699751438</v>
+      </c>
+      <c r="G25" s="37">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="H25" s="37">
+        <v>1.42</v>
+      </c>
+      <c r="I25" s="37">
+        <v>2.0491139037538399</v>
+      </c>
+      <c r="J25" s="37">
+        <v>2</v>
+      </c>
+      <c r="K25" s="37">
+        <v>1.625</v>
+      </c>
+      <c r="L25" s="37">
+        <v>1.492</v>
+      </c>
+      <c r="M25" s="38">
         <v>10</v>
       </c>
-      <c r="N25" s="43"/>
+      <c r="N25" s="31"/>
     </row>
     <row r="26" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B26" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="4">
-        <v>1.6730528026562499</v>
+        <v>1.697060757576752</v>
       </c>
       <c r="E26" s="4">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="F26" s="4">
-        <v>0.30353569353644311</v>
+        <v>0.25989274376605193</v>
       </c>
       <c r="G26" s="4">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="H26" s="4">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="I26" s="4">
-        <v>2.0089999999999999</v>
+        <v>2.012</v>
       </c>
       <c r="J26" s="4">
-        <v>1.976382006640625</v>
+        <v>1.931705681825636</v>
       </c>
       <c r="K26" s="4">
-        <v>1.40625</v>
+        <v>1.51875</v>
       </c>
       <c r="L26" s="4">
-        <v>1.381</v>
+        <v>1.4</v>
       </c>
       <c r="M26" s="5">
         <v>10</v>
       </c>
-      <c r="N26" s="43"/>
+      <c r="N26" s="31"/>
     </row>
     <row r="27" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="37" t="s">
+      <c r="B27" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="33">
-        <v>22.222691282812779</v>
-      </c>
-      <c r="E27" s="33">
-        <v>21.278580998224651</v>
-      </c>
-      <c r="F27" s="33">
-        <v>3.759210434725623</v>
-      </c>
-      <c r="G27" s="33">
-        <v>28.45</v>
-      </c>
-      <c r="H27" s="33">
-        <v>16.8</v>
-      </c>
-      <c r="I27" s="33">
-        <v>27.055</v>
-      </c>
-      <c r="J27" s="33">
-        <v>25.024999999999999</v>
-      </c>
-      <c r="K27" s="33">
-        <v>19.639813123758859</v>
-      </c>
-      <c r="L27" s="33">
-        <v>18.690000000000001</v>
-      </c>
-      <c r="M27" s="36">
+      <c r="C27" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" s="37">
+        <v>23.622953297262391</v>
+      </c>
+      <c r="E27" s="37">
+        <v>22.85</v>
+      </c>
+      <c r="F27" s="37">
+        <v>3.9245340281639232</v>
+      </c>
+      <c r="G27" s="37">
+        <v>29.75</v>
+      </c>
+      <c r="H27" s="37">
+        <v>18.8</v>
+      </c>
+      <c r="I27" s="37">
+        <v>29.074999999999999</v>
+      </c>
+      <c r="J27" s="37">
+        <v>26.375</v>
+      </c>
+      <c r="K27" s="37">
+        <v>20.625102841541079</v>
+      </c>
+      <c r="L27" s="37">
+        <v>19.07</v>
+      </c>
+      <c r="M27" s="38">
         <v>10</v>
       </c>
-      <c r="N27" s="43"/>
+      <c r="N27" s="31"/>
     </row>
     <row r="28" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
@@ -6191,777 +6189,777 @@
         <v>16</v>
       </c>
       <c r="D28" s="4">
-        <v>23.548356218668381</v>
+        <v>26.713803189632799</v>
       </c>
       <c r="E28" s="4">
-        <v>23.15</v>
+        <v>26.3</v>
       </c>
       <c r="F28" s="4">
-        <v>3.312531181340181</v>
+        <v>3.204250994792381</v>
       </c>
       <c r="G28" s="4">
-        <v>28.8</v>
+        <v>32</v>
       </c>
       <c r="H28" s="4">
-        <v>19.399999999999999</v>
+        <v>21.7</v>
       </c>
       <c r="I28" s="4">
-        <v>28.17</v>
+        <v>30.65</v>
       </c>
       <c r="J28" s="4">
-        <v>25.764435289274459</v>
+        <v>28.524999999999999</v>
       </c>
       <c r="K28" s="4">
-        <v>20.906563367722491</v>
+        <v>25.103523922245969</v>
       </c>
       <c r="L28" s="4">
-        <v>19.850000000000001</v>
+        <v>22.78</v>
       </c>
       <c r="M28" s="5">
         <v>10</v>
       </c>
-      <c r="N28" s="43"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="30" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B30" s="22"/>
       <c r="C30" s="23"/>
     </row>
     <row r="31" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="41" t="s">
+      <c r="B31" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="41"/>
-      <c r="K31" s="41"/>
-      <c r="L31" s="41"/>
-      <c r="M31" s="41"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="15"/>
     </row>
     <row r="32" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B32" s="42" t="s">
+      <c r="B32" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C32" s="42" t="s">
+      <c r="C32" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="42" t="s">
+      <c r="D32" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="42" t="s">
+      <c r="E32" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F32" s="42" t="s">
+      <c r="F32" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G32" s="42" t="s">
+      <c r="G32" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H32" s="42" t="s">
+      <c r="H32" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I32" s="42" t="s">
+      <c r="I32" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="42" t="s">
+      <c r="J32" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K32" s="42" t="s">
+      <c r="K32" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="L32" s="42" t="s">
+      <c r="L32" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="M32" s="42" t="s">
+      <c r="M32" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="33" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B33" s="31">
-        <v>46081</v>
-      </c>
-      <c r="C33" s="32" t="s">
+      <c r="B33" s="35">
+        <v>46112</v>
+      </c>
+      <c r="C33" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="38">
-        <v>31.39616321794994</v>
-      </c>
-      <c r="E33" s="38">
-        <v>31.9</v>
-      </c>
-      <c r="F33" s="38">
-        <v>3.0602304732546619</v>
-      </c>
-      <c r="G33" s="33">
-        <v>37.111632179499402</v>
-      </c>
-      <c r="H33" s="33">
-        <v>25</v>
-      </c>
-      <c r="I33" s="33">
-        <v>33.411163217949941</v>
-      </c>
-      <c r="J33" s="33">
-        <v>32.4</v>
-      </c>
-      <c r="K33" s="33">
-        <v>30.25</v>
-      </c>
-      <c r="L33" s="33">
-        <v>29.004999999999999</v>
-      </c>
-      <c r="M33" s="34">
+      <c r="D33" s="37">
+        <v>30.867000000000001</v>
+      </c>
+      <c r="E33" s="37">
+        <v>30.75</v>
+      </c>
+      <c r="F33" s="37">
+        <v>1.105602399900917</v>
+      </c>
+      <c r="G33" s="37">
+        <v>33.1</v>
+      </c>
+      <c r="H33" s="37">
+        <v>29.36</v>
+      </c>
+      <c r="I33" s="37">
+        <v>31.93</v>
+      </c>
+      <c r="J33" s="37">
+        <v>31.465</v>
+      </c>
+      <c r="K33" s="37">
+        <v>30.022500000000001</v>
+      </c>
+      <c r="L33" s="37">
+        <v>29.936</v>
+      </c>
+      <c r="M33" s="38">
         <v>10</v>
       </c>
-      <c r="N33" s="43"/>
+      <c r="N33" s="31"/>
     </row>
     <row r="34" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B34" s="2">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D34" s="26">
-        <v>31.104357006040129</v>
-      </c>
-      <c r="E34" s="26">
-        <v>30.5</v>
-      </c>
-      <c r="F34" s="26">
-        <v>3.420345595327996</v>
+      <c r="D34" s="4">
+        <v>29.099</v>
+      </c>
+      <c r="E34" s="4">
+        <v>29.2</v>
+      </c>
+      <c r="F34" s="4">
+        <v>0.9829146001108694</v>
       </c>
       <c r="G34" s="4">
-        <v>37.833570060401307</v>
+        <v>30.65</v>
       </c>
       <c r="H34" s="4">
-        <v>25</v>
+        <v>27.25</v>
       </c>
       <c r="I34" s="4">
-        <v>34.563357006040142</v>
+        <v>30.146000000000001</v>
       </c>
       <c r="J34" s="4">
-        <v>32.625</v>
+        <v>29.5</v>
       </c>
       <c r="K34" s="4">
-        <v>29.625</v>
+        <v>28.7</v>
       </c>
       <c r="L34" s="4">
-        <v>28.609000000000002</v>
+        <v>27.925000000000001</v>
       </c>
       <c r="M34" s="5">
         <v>10</v>
       </c>
-      <c r="N34" s="43"/>
+      <c r="N34" s="31"/>
     </row>
     <row r="35" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B35" s="37">
-        <v>46142</v>
-      </c>
-      <c r="C35" s="32" t="s">
+      <c r="B35" s="35">
+        <v>46173</v>
+      </c>
+      <c r="C35" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="D35" s="38">
-        <v>28.750609750192311</v>
-      </c>
-      <c r="E35" s="38">
-        <v>28.2</v>
-      </c>
-      <c r="F35" s="38">
-        <v>3.2117781798246141</v>
-      </c>
-      <c r="G35" s="33">
-        <v>35.516097501923142</v>
-      </c>
-      <c r="H35" s="33">
-        <v>25</v>
-      </c>
-      <c r="I35" s="33">
-        <v>32.801609750192313</v>
-      </c>
-      <c r="J35" s="33">
-        <v>29.375</v>
-      </c>
-      <c r="K35" s="33">
-        <v>27.0425</v>
-      </c>
-      <c r="L35" s="33">
-        <v>25.18</v>
-      </c>
-      <c r="M35" s="36">
+      <c r="D35" s="37">
+        <v>27.573</v>
+      </c>
+      <c r="E35" s="37">
+        <v>27.5</v>
+      </c>
+      <c r="F35" s="37">
+        <v>1.789668187743813</v>
+      </c>
+      <c r="G35" s="37">
+        <v>30.07</v>
+      </c>
+      <c r="H35" s="37">
+        <v>25.11</v>
+      </c>
+      <c r="I35" s="37">
+        <v>29.872</v>
+      </c>
+      <c r="J35" s="37">
+        <v>28.875</v>
+      </c>
+      <c r="K35" s="37">
+        <v>26.5</v>
+      </c>
+      <c r="L35" s="37">
+        <v>25.190999999999999</v>
+      </c>
+      <c r="M35" s="38">
         <v>10</v>
       </c>
-      <c r="N35" s="43"/>
+      <c r="N35" s="31"/>
     </row>
     <row r="36" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B36" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D36" s="26">
-        <v>26.626976440311129</v>
-      </c>
-      <c r="E36" s="26">
-        <v>25.87</v>
-      </c>
-      <c r="F36" s="26">
-        <v>3.761650729205956</v>
+      <c r="D36" s="4">
+        <v>26.218</v>
+      </c>
+      <c r="E36" s="4">
+        <v>26.5</v>
+      </c>
+      <c r="F36" s="4">
+        <v>2.5949044084298918</v>
       </c>
       <c r="G36" s="4">
-        <v>33.129764403111331</v>
+        <v>30.06</v>
       </c>
       <c r="H36" s="4">
-        <v>22.9</v>
+        <v>21.6</v>
       </c>
       <c r="I36" s="4">
-        <v>32.11297644031113</v>
+        <v>29.151</v>
       </c>
       <c r="J36" s="4">
-        <v>28.375</v>
+        <v>27.75</v>
       </c>
       <c r="K36" s="4">
-        <v>23.25</v>
+        <v>25.125</v>
       </c>
       <c r="L36" s="4">
-        <v>22.99</v>
+        <v>22.832999999999998</v>
       </c>
       <c r="M36" s="5">
         <v>10</v>
       </c>
-      <c r="N36" s="43"/>
+      <c r="N36" s="31"/>
     </row>
     <row r="37" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B37" s="37">
-        <v>46203</v>
-      </c>
-      <c r="C37" s="32" t="s">
+      <c r="B37" s="35">
+        <v>46234</v>
+      </c>
+      <c r="C37" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="D37" s="38">
-        <v>25.657163958596531</v>
-      </c>
-      <c r="E37" s="38">
-        <v>24.5</v>
-      </c>
-      <c r="F37" s="38">
-        <v>3.8300645507774269</v>
-      </c>
-      <c r="G37" s="33">
-        <v>32.531639585965308</v>
-      </c>
-      <c r="H37" s="33">
-        <v>22</v>
-      </c>
-      <c r="I37" s="33">
-        <v>31.603163958596529</v>
-      </c>
-      <c r="J37" s="33">
-        <v>26.9</v>
-      </c>
-      <c r="K37" s="33">
-        <v>22.78</v>
-      </c>
-      <c r="L37" s="33">
-        <v>22.27</v>
-      </c>
-      <c r="M37" s="36">
+      <c r="D37" s="37">
+        <v>25.603999999999999</v>
+      </c>
+      <c r="E37" s="37">
+        <v>25.25</v>
+      </c>
+      <c r="F37" s="37">
+        <v>2.4604525329025688</v>
+      </c>
+      <c r="G37" s="37">
+        <v>30.05</v>
+      </c>
+      <c r="H37" s="37">
+        <v>21.5</v>
+      </c>
+      <c r="I37" s="37">
+        <v>28.43</v>
+      </c>
+      <c r="J37" s="37">
+        <v>26.875</v>
+      </c>
+      <c r="K37" s="37">
+        <v>24.184999999999999</v>
+      </c>
+      <c r="L37" s="37">
+        <v>23.3</v>
+      </c>
+      <c r="M37" s="38">
         <v>10</v>
       </c>
-      <c r="N37" s="43"/>
+      <c r="N37" s="31"/>
     </row>
     <row r="38" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B38" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D38" s="26">
-        <v>24.86870763071683</v>
-      </c>
-      <c r="E38" s="26">
-        <v>23.695</v>
-      </c>
-      <c r="F38" s="26">
-        <v>3.70075021618214</v>
+      <c r="D38" s="4">
+        <v>25.49</v>
+      </c>
+      <c r="E38" s="4">
+        <v>25.305</v>
+      </c>
+      <c r="F38" s="4">
+        <v>2.2485847400828218</v>
       </c>
       <c r="G38" s="4">
-        <v>31.797076307168339</v>
+        <v>30.04</v>
       </c>
       <c r="H38" s="4">
         <v>21.5</v>
       </c>
       <c r="I38" s="4">
-        <v>31.079707630716829</v>
+        <v>27.709</v>
       </c>
       <c r="J38" s="4">
-        <v>25.375</v>
+        <v>26.25</v>
       </c>
       <c r="K38" s="4">
-        <v>22.25</v>
+        <v>24.475000000000001</v>
       </c>
       <c r="L38" s="4">
-        <v>21.5</v>
+        <v>23.75</v>
       </c>
       <c r="M38" s="5">
         <v>10</v>
       </c>
-      <c r="N38" s="43"/>
+      <c r="N38" s="31"/>
     </row>
     <row r="39" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="37" t="s">
+      <c r="B39" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="D39" s="38">
-        <v>22.86169648846834</v>
-      </c>
-      <c r="E39" s="38">
-        <v>22.204999999999998</v>
-      </c>
-      <c r="F39" s="38">
-        <v>5.081647896013572</v>
-      </c>
-      <c r="G39" s="33">
-        <v>31.006964884683359</v>
-      </c>
-      <c r="H39" s="33">
-        <v>12.5</v>
-      </c>
-      <c r="I39" s="33">
-        <v>29.200696488468331</v>
-      </c>
-      <c r="J39" s="33">
-        <v>24.75</v>
-      </c>
-      <c r="K39" s="33">
-        <v>21.25</v>
-      </c>
-      <c r="L39" s="33">
-        <v>18.98</v>
-      </c>
-      <c r="M39" s="36">
+      <c r="C39" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39" s="37">
+        <v>22.91</v>
+      </c>
+      <c r="E39" s="37">
+        <v>23.15</v>
+      </c>
+      <c r="F39" s="37">
+        <v>2.222081106630549</v>
+      </c>
+      <c r="G39" s="37">
+        <v>25.82</v>
+      </c>
+      <c r="H39" s="37">
+        <v>19</v>
+      </c>
+      <c r="I39" s="37">
+        <v>25.082000000000001</v>
+      </c>
+      <c r="J39" s="37">
+        <v>24.337499999999999</v>
+      </c>
+      <c r="K39" s="37">
+        <v>22.497499999999999</v>
+      </c>
+      <c r="L39" s="37">
+        <v>19.36</v>
+      </c>
+      <c r="M39" s="38">
         <v>10</v>
       </c>
-      <c r="N39" s="43"/>
+      <c r="N39" s="31"/>
     </row>
     <row r="40" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D40" s="26">
-        <v>23.254832022961399</v>
-      </c>
-      <c r="E40" s="26">
-        <v>22.204999999999998</v>
-      </c>
-      <c r="F40" s="26">
-        <v>4.3528189909855026</v>
+      <c r="D40" s="4">
+        <v>24.184000000000001</v>
+      </c>
+      <c r="E40" s="4">
+        <v>24.17</v>
+      </c>
+      <c r="F40" s="4">
+        <v>2.1444823255145851</v>
       </c>
       <c r="G40" s="4">
-        <v>31.038320229614051</v>
+        <v>27</v>
       </c>
       <c r="H40" s="4">
-        <v>16.600000000000001</v>
+        <v>20</v>
       </c>
       <c r="I40" s="4">
-        <v>30.103832022961409</v>
+        <v>26.631</v>
       </c>
       <c r="J40" s="4">
-        <v>23.875</v>
+        <v>25.327500000000001</v>
       </c>
       <c r="K40" s="4">
-        <v>21.25</v>
+        <v>24</v>
       </c>
       <c r="L40" s="4">
-        <v>19.66</v>
+        <v>21.26</v>
       </c>
       <c r="M40" s="5">
         <v>10</v>
       </c>
-      <c r="N40" s="43"/>
+      <c r="N40" s="31"/>
     </row>
     <row r="41" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B41" s="22"/>
       <c r="C41" s="23"/>
-      <c r="N41" s="43"/>
+      <c r="N41" s="31"/>
     </row>
     <row r="43" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="41" t="s">
+      <c r="B43" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C43" s="41"/>
-      <c r="D43" s="41"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="41"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="41"/>
-      <c r="I43" s="41"/>
-      <c r="J43" s="41"/>
-      <c r="K43" s="41"/>
-      <c r="L43" s="41"/>
-      <c r="M43" s="41"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="14"/>
+      <c r="L43" s="14"/>
+      <c r="M43" s="15"/>
     </row>
     <row r="44" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B44" s="42" t="s">
+      <c r="B44" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C44" s="42" t="s">
+      <c r="C44" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D44" s="42" t="s">
+      <c r="D44" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E44" s="42" t="s">
+      <c r="E44" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F44" s="42" t="s">
+      <c r="F44" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G44" s="42" t="s">
+      <c r="G44" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H44" s="42" t="s">
+      <c r="H44" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I44" s="42" t="s">
+      <c r="I44" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J44" s="42" t="s">
+      <c r="J44" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K44" s="42" t="s">
+      <c r="K44" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="L44" s="42" t="s">
+      <c r="L44" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="M44" s="42" t="s">
+      <c r="M44" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="45" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B45" s="31">
-        <v>46081</v>
-      </c>
-      <c r="C45" s="32" t="s">
+      <c r="B45" s="35">
+        <v>46112</v>
+      </c>
+      <c r="C45" s="36" t="s">
         <v>22</v>
       </c>
       <c r="D45" s="39">
-        <v>1469.937731857427</v>
+        <v>1434.8956699701721</v>
       </c>
       <c r="E45" s="39">
-        <v>1469.4438730944901</v>
+        <v>1428.7881960142861</v>
       </c>
       <c r="F45" s="39">
-        <v>11.25545978615213</v>
+        <v>32.743237626160983</v>
       </c>
       <c r="G45" s="39">
-        <v>1487.54</v>
+        <v>1502</v>
       </c>
       <c r="H45" s="39">
-        <v>1450.9468656965421</v>
+        <v>1392.4821565838929</v>
       </c>
       <c r="I45" s="39">
-        <v>1480.7539999999999</v>
+        <v>1478.6179999999999</v>
       </c>
       <c r="J45" s="39">
-        <v>1478.3892000000001</v>
+        <v>1443.5157070300099</v>
       </c>
       <c r="K45" s="39">
-        <v>1463.19</v>
+        <v>1418.125</v>
       </c>
       <c r="L45" s="39">
-        <v>1459.1460825895231</v>
-      </c>
-      <c r="M45" s="34">
+        <v>1404.429703202703</v>
+      </c>
+      <c r="M45" s="38">
         <v>10</v>
       </c>
-      <c r="N45" s="43"/>
+      <c r="N45" s="31"/>
     </row>
     <row r="46" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B46" s="2">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D46" s="40">
-        <v>1501.428403369742</v>
+        <v>1467.7022569028379</v>
       </c>
       <c r="E46" s="40">
-        <v>1499.5927999999999</v>
+        <v>1449.0069732142861</v>
       </c>
       <c r="F46" s="40">
-        <v>23.9122127713336</v>
+        <v>49.644500540926529</v>
       </c>
       <c r="G46" s="40">
-        <v>1561.4</v>
+        <v>1572</v>
       </c>
       <c r="H46" s="40">
-        <v>1473.007033018207</v>
+        <v>1421.7242818721541</v>
       </c>
       <c r="I46" s="40">
-        <v>1515.14</v>
+        <v>1530.357</v>
       </c>
       <c r="J46" s="40">
-        <v>1504.205405196009</v>
+        <v>1491.4267532945651</v>
       </c>
       <c r="K46" s="40">
-        <v>1488.7192151044669</v>
+        <v>1433.5727183317249</v>
       </c>
       <c r="L46" s="40">
-        <v>1480.8217033018209</v>
+        <v>1424.672428187215</v>
       </c>
       <c r="M46" s="5">
         <v>10</v>
       </c>
-      <c r="N46" s="43"/>
+      <c r="N46" s="31"/>
     </row>
     <row r="47" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B47" s="37">
-        <v>46142</v>
-      </c>
-      <c r="C47" s="32" t="s">
+      <c r="B47" s="35">
+        <v>46173</v>
+      </c>
+      <c r="C47" s="36" t="s">
         <v>22</v>
       </c>
       <c r="D47" s="39">
-        <v>1533.728577908583</v>
+        <v>1489.518772309611</v>
       </c>
       <c r="E47" s="39">
-        <v>1525.156461020016</v>
+        <v>1463.67330414455</v>
       </c>
       <c r="F47" s="39">
-        <v>34.281836779334363</v>
+        <v>62.296157167927781</v>
       </c>
       <c r="G47" s="39">
-        <v>1607.47</v>
+        <v>1627</v>
       </c>
       <c r="H47" s="39">
-        <v>1495.402602685585</v>
+        <v>1435</v>
       </c>
       <c r="I47" s="39">
-        <v>1573.7470000000001</v>
+        <v>1570.471</v>
       </c>
       <c r="J47" s="39">
-        <v>1545.6871235900539</v>
+        <v>1508.107892135798</v>
       </c>
       <c r="K47" s="39">
-        <v>1516.89852</v>
+        <v>1451.99761146476</v>
       </c>
       <c r="L47" s="39">
-        <v>1495.967260268558</v>
-      </c>
-      <c r="M47" s="36">
+        <v>1442.245131490213</v>
+      </c>
+      <c r="M47" s="38">
         <v>10</v>
       </c>
-      <c r="N47" s="43"/>
+      <c r="N47" s="31"/>
     </row>
     <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B48" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D48" s="40">
-        <v>1554.562428752123</v>
+        <v>1521.5904213722049</v>
       </c>
       <c r="E48" s="40">
-        <v>1541.2181749112081</v>
+        <v>1494.4569732142861</v>
       </c>
       <c r="F48" s="40">
-        <v>45.48107668468586</v>
+        <v>75.50213699858179</v>
       </c>
       <c r="G48" s="40">
-        <v>1639.91</v>
+        <v>1668</v>
       </c>
       <c r="H48" s="40">
-        <v>1510.8</v>
+        <v>1450</v>
       </c>
       <c r="I48" s="40">
-        <v>1621.991</v>
+        <v>1613.037071716336</v>
       </c>
       <c r="J48" s="40">
-        <v>1576.25</v>
+        <v>1576.0125</v>
       </c>
       <c r="K48" s="40">
-        <v>1519.9128416116889</v>
+        <v>1471.1892871307989</v>
       </c>
       <c r="L48" s="40">
-        <v>1513.7735275955481</v>
+        <v>1456.2003131539741</v>
       </c>
       <c r="M48" s="5">
         <v>10</v>
       </c>
-      <c r="N48" s="43"/>
+      <c r="N48" s="31"/>
     </row>
     <row r="49" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="37">
-        <v>46203</v>
-      </c>
-      <c r="C49" s="32" t="s">
+      <c r="B49" s="35">
+        <v>46234</v>
+      </c>
+      <c r="C49" s="36" t="s">
         <v>22</v>
       </c>
       <c r="D49" s="39">
-        <v>1584.743072580259</v>
+        <v>1552.729999913583</v>
       </c>
       <c r="E49" s="39">
-        <v>1569.5927999999999</v>
+        <v>1518.4241402933551</v>
       </c>
       <c r="F49" s="39">
-        <v>58.053852315851039</v>
+        <v>86.562386562109467</v>
       </c>
       <c r="G49" s="39">
-        <v>1672.25</v>
+        <v>1692</v>
       </c>
       <c r="H49" s="39">
-        <v>1510.846830004285</v>
+        <v>1455.926853650147</v>
       </c>
       <c r="I49" s="39">
-        <v>1668.425</v>
+        <v>1682.0356563028561</v>
       </c>
       <c r="J49" s="39">
-        <v>1626.464359247487</v>
+        <v>1617.9725000000001</v>
       </c>
       <c r="K49" s="39">
-        <v>1540.69665040533</v>
+        <v>1497.0360379950159</v>
       </c>
       <c r="L49" s="39">
-        <v>1528.1926830004279</v>
-      </c>
-      <c r="M49" s="36">
+        <v>1473.0926853650151</v>
+      </c>
+      <c r="M49" s="38">
         <v>10</v>
       </c>
-      <c r="N49" s="43"/>
+      <c r="N49" s="31"/>
     </row>
     <row r="50" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B50" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D50" s="40">
-        <v>1619.339712397019</v>
+        <v>1585.2480228136201</v>
       </c>
       <c r="E50" s="40">
-        <v>1622.5</v>
+        <v>1553.072908353613</v>
       </c>
       <c r="F50" s="40">
-        <v>71.34744349565301</v>
+        <v>90.792494618342374</v>
       </c>
       <c r="G50" s="40">
-        <v>1706.18</v>
+        <v>1745.000945757258</v>
       </c>
       <c r="H50" s="40">
-        <v>1508.0591426108861</v>
+        <v>1481.5884556009771</v>
       </c>
       <c r="I50" s="40">
-        <v>1702.158157394826</v>
+        <v>1711.7000945757261</v>
       </c>
       <c r="J50" s="40">
-        <v>1684.5822400965201</v>
+        <v>1648.4275</v>
       </c>
       <c r="K50" s="40">
-        <v>1564.3842466809649</v>
+        <v>1530.481257553053</v>
       </c>
       <c r="L50" s="40">
-        <v>1545.0589142610891</v>
+        <v>1502.6588455600979</v>
       </c>
       <c r="M50" s="5">
         <v>10</v>
       </c>
-      <c r="N50" s="43"/>
+      <c r="N50" s="31"/>
     </row>
     <row r="51" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B51" s="37" t="s">
+      <c r="B51" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="32" t="s">
-        <v>50</v>
+      <c r="C51" s="36" t="s">
+        <v>49</v>
       </c>
       <c r="D51" s="39">
-        <v>1777.5998746086821</v>
+        <v>1749.857471464298</v>
       </c>
       <c r="E51" s="39">
-        <v>1785.2</v>
+        <v>1739.711476797919</v>
       </c>
       <c r="F51" s="39">
-        <v>92.479388997154871</v>
+        <v>87.759038646756593</v>
       </c>
       <c r="G51" s="39">
-        <v>1884.49</v>
+        <v>1903.2718822934121</v>
       </c>
       <c r="H51" s="39">
-        <v>1624</v>
+        <v>1627</v>
       </c>
       <c r="I51" s="39">
-        <v>1873.995503737862</v>
+        <v>1877.467188229341</v>
       </c>
       <c r="J51" s="39">
-        <v>1860.4403195311561</v>
+        <v>1780.5</v>
       </c>
       <c r="K51" s="39">
-        <v>1722.0835145234259</v>
+        <v>1694.659442651458</v>
       </c>
       <c r="L51" s="39">
-        <v>1647.4</v>
-      </c>
-      <c r="M51" s="36">
+        <v>1657.6</v>
+      </c>
+      <c r="M51" s="38">
         <v>10</v>
       </c>
-      <c r="N51" s="43"/>
+      <c r="N51" s="31"/>
     </row>
     <row r="52" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D52" s="40">
-        <v>1751.573351155291</v>
+        <v>1715.892120112077</v>
       </c>
       <c r="E52" s="40">
-        <v>1752.5</v>
+        <v>1721.6274802376549</v>
       </c>
       <c r="F52" s="40">
-        <v>77.041909296332761</v>
+        <v>88.580891303294834</v>
       </c>
       <c r="G52" s="40">
-        <v>1868.91</v>
+        <v>1858.0907494167579</v>
       </c>
       <c r="H52" s="40">
-        <v>1642.44</v>
+        <v>1580</v>
       </c>
       <c r="I52" s="40">
-        <v>1852.885651927731</v>
+        <v>1833.9880749416759</v>
       </c>
       <c r="J52" s="40">
-        <v>1796.2961362304529</v>
+        <v>1753.75</v>
       </c>
       <c r="K52" s="40">
-        <v>1700.4526208277871</v>
+        <v>1653.449118421526</v>
       </c>
       <c r="L52" s="40">
-        <v>1649.2439999999999</v>
+        <v>1616</v>
       </c>
       <c r="M52" s="5">
         <v>10</v>
       </c>
-      <c r="N52" s="43"/>
+      <c r="N52" s="31"/>
     </row>
     <row r="53" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B53" s="22"/>
@@ -6972,370 +6970,370 @@
       <c r="C54" s="23"/>
     </row>
     <row r="55" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B55" s="41" t="s">
+      <c r="B55" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C55" s="41"/>
-      <c r="D55" s="41"/>
-      <c r="E55" s="41"/>
-      <c r="F55" s="41"/>
-      <c r="G55" s="41"/>
-      <c r="H55" s="41"/>
-      <c r="I55" s="41"/>
-      <c r="J55" s="41"/>
-      <c r="K55" s="41"/>
-      <c r="L55" s="41"/>
-      <c r="M55" s="41"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="14"/>
+      <c r="L55" s="14"/>
+      <c r="M55" s="15"/>
     </row>
     <row r="56" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B56" s="42" t="s">
+      <c r="B56" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C56" s="42" t="s">
+      <c r="C56" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D56" s="42" t="s">
+      <c r="D56" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E56" s="42" t="s">
+      <c r="E56" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F56" s="42" t="s">
+      <c r="F56" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G56" s="42" t="s">
+      <c r="G56" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H56" s="42" t="s">
+      <c r="H56" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I56" s="42" t="s">
+      <c r="I56" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J56" s="42" t="s">
+      <c r="J56" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K56" s="42" t="s">
+      <c r="K56" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="L56" s="42" t="s">
+      <c r="L56" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="M56" s="42" t="s">
+      <c r="M56" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B57" s="31">
-        <v>46053</v>
-      </c>
-      <c r="C57" s="32" t="s">
+      <c r="B57" s="44">
+        <v>46081</v>
+      </c>
+      <c r="C57" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D57" s="39">
-        <v>6811.0724232653711</v>
-      </c>
-      <c r="E57" s="39">
-        <v>6612.5704243620085</v>
-      </c>
-      <c r="F57" s="39">
-        <v>496.67966630613472</v>
-      </c>
-      <c r="G57" s="39">
-        <v>7756</v>
-      </c>
-      <c r="H57" s="39">
-        <v>6388.2000000000007</v>
-      </c>
-      <c r="I57" s="39">
-        <v>7615.6</v>
-      </c>
-      <c r="J57" s="39">
-        <v>6967.2648168151609</v>
-      </c>
-      <c r="K57" s="39">
-        <v>6460.934964170362</v>
-      </c>
-      <c r="L57" s="39">
-        <v>6434.82</v>
-      </c>
-      <c r="M57" s="34">
+      <c r="D57" s="45">
+        <v>6914.7496649221694</v>
+      </c>
+      <c r="E57" s="45">
+        <v>6883.3100190260384</v>
+      </c>
+      <c r="F57" s="45">
+        <v>278.88715565709441</v>
+      </c>
+      <c r="G57" s="45">
+        <v>7300</v>
+      </c>
+      <c r="H57" s="45">
+        <v>6324.2</v>
+      </c>
+      <c r="I57" s="45">
+        <v>7170.5800487575152</v>
+      </c>
+      <c r="J57" s="45">
+        <v>7122.6774999999998</v>
+      </c>
+      <c r="K57" s="45">
+        <v>6819.9766392486499</v>
+      </c>
+      <c r="L57" s="45">
+        <v>6666.92</v>
+      </c>
+      <c r="M57" s="46">
         <v>10</v>
       </c>
-      <c r="N57" s="44"/>
+      <c r="N57" s="32"/>
     </row>
     <row r="58" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B58" s="2">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D58" s="40">
-        <v>6777.1542798722194</v>
-      </c>
-      <c r="E58" s="40">
-        <v>6743.9081136965651</v>
-      </c>
-      <c r="F58" s="40">
-        <v>301.33261514239132</v>
-      </c>
-      <c r="G58" s="40">
-        <v>7200</v>
-      </c>
-      <c r="H58" s="40">
-        <v>6148.959072604669</v>
-      </c>
-      <c r="I58" s="40">
-        <v>7160.5800487575152</v>
-      </c>
-      <c r="J58" s="40">
-        <v>6930.4140546667677</v>
-      </c>
-      <c r="K58" s="40">
-        <v>6645.9000000000005</v>
-      </c>
-      <c r="L58" s="40">
-        <v>6572.8959072604666</v>
+      <c r="D58" s="42">
+        <v>7533.1591285400154</v>
+      </c>
+      <c r="E58" s="42">
+        <v>7491.9742500000002</v>
+      </c>
+      <c r="F58" s="42">
+        <v>361.1811250862001</v>
+      </c>
+      <c r="G58" s="42">
+        <v>8123</v>
+      </c>
+      <c r="H58" s="42">
+        <v>6841.26</v>
+      </c>
+      <c r="I58" s="42">
+        <v>7895.9495665155127</v>
+      </c>
+      <c r="J58" s="42">
+        <v>7777.3978424724673</v>
+      </c>
+      <c r="K58" s="42">
+        <v>7372.5</v>
+      </c>
+      <c r="L58" s="42">
+        <v>7190.2027913274324</v>
       </c>
       <c r="M58" s="5">
         <v>10</v>
       </c>
-      <c r="N58" s="44"/>
+      <c r="N58" s="32"/>
     </row>
     <row r="59" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B59" s="37">
-        <v>46112</v>
-      </c>
-      <c r="C59" s="32" t="s">
+      <c r="B59" s="35">
+        <v>46142</v>
+      </c>
+      <c r="C59" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D59" s="39">
-        <v>7356.8871962315779</v>
-      </c>
-      <c r="E59" s="39">
-        <v>7379.9725864600177</v>
-      </c>
-      <c r="F59" s="39">
-        <v>338.89410940244318</v>
-      </c>
-      <c r="G59" s="39">
-        <v>7817.9522688242714</v>
-      </c>
-      <c r="H59" s="39">
-        <v>6702.9728989048444</v>
-      </c>
-      <c r="I59" s="39">
-        <v>7721.8824105971189</v>
-      </c>
-      <c r="J59" s="39">
-        <v>7592.1786634887321</v>
-      </c>
-      <c r="K59" s="39">
-        <v>7197.52</v>
-      </c>
-      <c r="L59" s="39">
-        <v>6970.2972898904854</v>
-      </c>
-      <c r="M59" s="36">
+      <c r="D59" s="45">
+        <v>8043.15592922408</v>
+      </c>
+      <c r="E59" s="45">
+        <v>7932.5</v>
+      </c>
+      <c r="F59" s="45">
+        <v>741.57980852618039</v>
+      </c>
+      <c r="G59" s="45">
+        <v>9499.5813244242654</v>
+      </c>
+      <c r="H59" s="45">
+        <v>6874.22</v>
+      </c>
+      <c r="I59" s="45">
+        <v>8763.2696472439584</v>
+      </c>
+      <c r="J59" s="45">
+        <v>8472.7935030451426</v>
+      </c>
+      <c r="K59" s="45">
+        <v>7639.2439538012914</v>
+      </c>
+      <c r="L59" s="45">
+        <v>7322.6433007092764</v>
+      </c>
+      <c r="M59" s="38">
         <v>10</v>
       </c>
-      <c r="N59" s="44"/>
+      <c r="N59" s="32"/>
     </row>
     <row r="60" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B60" s="2">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D60" s="40">
-        <v>7851.8677580958201</v>
-      </c>
-      <c r="E60" s="40">
-        <v>7621.3979315556471</v>
-      </c>
-      <c r="F60" s="40">
-        <v>550.93342975609335</v>
-      </c>
-      <c r="G60" s="40">
-        <v>8999.5813244242654</v>
-      </c>
-      <c r="H60" s="40">
-        <v>7207.92</v>
-      </c>
-      <c r="I60" s="40">
-        <v>8527.1850092437908</v>
-      </c>
-      <c r="J60" s="40">
-        <v>8105.8509545499264</v>
-      </c>
-      <c r="K60" s="40">
-        <v>7485</v>
-      </c>
-      <c r="L60" s="40">
-        <v>7452.0863318191014</v>
+      <c r="D60" s="42">
+        <v>8436.6422329980614</v>
+      </c>
+      <c r="E60" s="42">
+        <v>8310</v>
+      </c>
+      <c r="F60" s="42">
+        <v>736.17606975416027</v>
+      </c>
+      <c r="G60" s="42">
+        <v>9612.7787517514171</v>
+      </c>
+      <c r="H60" s="42">
+        <v>7307.85</v>
+      </c>
+      <c r="I60" s="42">
+        <v>9187.2778751751412</v>
+      </c>
+      <c r="J60" s="42">
+        <v>9027.6017249094657</v>
+      </c>
+      <c r="K60" s="42">
+        <v>8009.4352234535781</v>
+      </c>
+      <c r="L60" s="42">
+        <v>7570.7849999999999</v>
       </c>
       <c r="M60" s="5">
         <v>10</v>
       </c>
-      <c r="N60" s="44"/>
+      <c r="N60" s="32"/>
     </row>
     <row r="61" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B61" s="37">
-        <v>46173</v>
-      </c>
-      <c r="C61" s="32" t="s">
+      <c r="B61" s="35">
+        <v>46203</v>
+      </c>
+      <c r="C61" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D61" s="39">
-        <v>8253.3144046607576</v>
-      </c>
-      <c r="E61" s="39">
-        <v>8321.2542884945578</v>
-      </c>
-      <c r="F61" s="39">
-        <v>381.38199709671301</v>
-      </c>
-      <c r="G61" s="39">
-        <v>8932.3429195982608</v>
-      </c>
-      <c r="H61" s="39">
-        <v>7662.6</v>
-      </c>
-      <c r="I61" s="39">
-        <v>8583.589344985221</v>
-      </c>
-      <c r="J61" s="39">
-        <v>8463.1251601531385</v>
-      </c>
-      <c r="K61" s="39">
-        <v>7986.911809817786</v>
-      </c>
-      <c r="L61" s="39">
-        <v>7786.26</v>
-      </c>
-      <c r="M61" s="36">
+      <c r="D61" s="45">
+        <v>8084.6708531869153</v>
+      </c>
+      <c r="E61" s="45">
+        <v>8037.5</v>
+      </c>
+      <c r="F61" s="45">
+        <v>507.9199459325643</v>
+      </c>
+      <c r="G61" s="45">
+        <v>9093.2076922841152</v>
+      </c>
+      <c r="H61" s="45">
+        <v>7300</v>
+      </c>
+      <c r="I61" s="45">
+        <v>8527.4730343006522</v>
+      </c>
+      <c r="J61" s="45">
+        <v>8338.9305547759577</v>
+      </c>
+      <c r="K61" s="45">
+        <v>7856.3968826763921</v>
+      </c>
+      <c r="L61" s="45">
+        <v>7473.9250000000002</v>
+      </c>
+      <c r="M61" s="38">
         <v>10</v>
       </c>
-      <c r="N61" s="44"/>
+      <c r="N61" s="32"/>
     </row>
     <row r="62" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B62" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D62" s="40">
-        <v>7935.1740975963839</v>
-      </c>
-      <c r="E62" s="40">
-        <v>7978.0377174391324</v>
-      </c>
-      <c r="F62" s="40">
-        <v>377.2322376499838</v>
-      </c>
-      <c r="G62" s="40">
-        <v>8487.9462056439534</v>
-      </c>
-      <c r="H62" s="40">
-        <v>7116.3068070104009</v>
-      </c>
-      <c r="I62" s="40">
-        <v>8346.8662548871616</v>
-      </c>
-      <c r="J62" s="40">
-        <v>8060</v>
-      </c>
-      <c r="K62" s="40">
-        <v>7873.5554559070397</v>
-      </c>
-      <c r="L62" s="40">
-        <v>7551.6306807010405</v>
+      <c r="D62" s="42">
+        <v>8143.1209254741043</v>
+      </c>
+      <c r="E62" s="42">
+        <v>8342.5</v>
+      </c>
+      <c r="F62" s="42">
+        <v>634.2264127830814</v>
+      </c>
+      <c r="G62" s="42">
+        <v>8968.5027880154757</v>
+      </c>
+      <c r="H62" s="42">
+        <v>7000</v>
+      </c>
+      <c r="I62" s="42">
+        <v>8683.9346696396187</v>
+      </c>
+      <c r="J62" s="42">
+        <v>8543.2792996648041</v>
+      </c>
+      <c r="K62" s="42">
+        <v>7897.9575000000004</v>
+      </c>
+      <c r="L62" s="42">
+        <v>7180</v>
       </c>
       <c r="M62" s="5">
         <v>10</v>
       </c>
-      <c r="N62" s="44"/>
+      <c r="N62" s="32"/>
     </row>
     <row r="63" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B63" s="37">
-        <v>46234</v>
-      </c>
-      <c r="C63" s="32" t="s">
+      <c r="B63" s="35">
+        <v>46265</v>
+      </c>
+      <c r="C63" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D63" s="39">
-        <v>8236.8622979027277</v>
-      </c>
-      <c r="E63" s="39">
-        <v>8466.3802702405301</v>
-      </c>
-      <c r="F63" s="39">
-        <v>893.38666511514373</v>
-      </c>
-      <c r="G63" s="39">
-        <v>9174.8727227236868</v>
-      </c>
-      <c r="H63" s="39">
-        <v>6004.3387760152636</v>
-      </c>
-      <c r="I63" s="39">
-        <v>8938.5964366059052</v>
-      </c>
-      <c r="J63" s="39">
-        <v>8666.4430679108355</v>
-      </c>
-      <c r="K63" s="39">
-        <v>8186.7875000000004</v>
-      </c>
-      <c r="L63" s="39">
-        <v>7440.4338776015265</v>
-      </c>
-      <c r="M63" s="36">
+      <c r="D63" s="45">
+        <v>8075.9873056495426</v>
+      </c>
+      <c r="E63" s="45">
+        <v>8176.4325437691123</v>
+      </c>
+      <c r="F63" s="45">
+        <v>662.57951349695509</v>
+      </c>
+      <c r="G63" s="45">
+        <v>8939.6518060804337</v>
+      </c>
+      <c r="H63" s="45">
+        <v>7000</v>
+      </c>
+      <c r="I63" s="45">
+        <v>8780.9857271971396</v>
+      </c>
+      <c r="J63" s="45">
+        <v>8523.75</v>
+      </c>
+      <c r="K63" s="45">
+        <v>7864.25</v>
+      </c>
+      <c r="L63" s="45">
+        <v>7000</v>
+      </c>
+      <c r="M63" s="38">
         <v>10</v>
       </c>
-      <c r="N63" s="44"/>
+      <c r="N63" s="32"/>
     </row>
     <row r="64" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="D64" s="40">
-        <v>92672.708496741048</v>
-      </c>
-      <c r="E64" s="40">
-        <v>93341</v>
-      </c>
-      <c r="F64" s="40">
-        <v>3321.282627690025</v>
-      </c>
-      <c r="G64" s="40">
-        <v>97749.93501511385</v>
-      </c>
-      <c r="H64" s="40">
-        <v>86448.63791588493</v>
-      </c>
-      <c r="I64" s="40">
-        <v>95468.521638987004</v>
-      </c>
-      <c r="J64" s="40">
-        <v>94603.97935707029</v>
-      </c>
-      <c r="K64" s="40">
-        <v>91530.363740780696</v>
-      </c>
-      <c r="L64" s="40">
-        <v>88115.763791588499</v>
-      </c>
-      <c r="M64" s="5">
+      <c r="D64" s="42">
+        <v>93863.871636781172</v>
+      </c>
+      <c r="E64" s="42">
+        <v>94382.771543886629</v>
+      </c>
+      <c r="F64" s="42">
+        <v>3426.018917890915</v>
+      </c>
+      <c r="G64" s="42">
+        <v>99806.587740335817</v>
+      </c>
+      <c r="H64" s="42">
+        <v>88301</v>
+      </c>
+      <c r="I64" s="42">
+        <v>97333.74275288888</v>
+      </c>
+      <c r="J64" s="42">
+        <v>95572.243600967573</v>
+      </c>
+      <c r="K64" s="42">
+        <v>91807.806418218213</v>
+      </c>
+      <c r="L64" s="42">
+        <v>89829.982983854003</v>
+      </c>
+      <c r="M64" s="43">
         <v>10</v>
       </c>
-      <c r="N64" s="44"/>
+      <c r="N64" s="32"/>
     </row>
     <row r="65" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B65" s="22"/>
@@ -7346,370 +7344,370 @@
       <c r="C66" s="23"/>
     </row>
     <row r="67" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B67" s="41" t="s">
+      <c r="B67" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C67" s="41"/>
-      <c r="D67" s="41"/>
-      <c r="E67" s="41"/>
-      <c r="F67" s="41"/>
-      <c r="G67" s="41"/>
-      <c r="H67" s="41"/>
-      <c r="I67" s="41"/>
-      <c r="J67" s="41"/>
-      <c r="K67" s="41"/>
-      <c r="L67" s="41"/>
-      <c r="M67" s="41"/>
+      <c r="C67" s="14"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
+      <c r="H67" s="14"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="14"/>
+      <c r="K67" s="14"/>
+      <c r="L67" s="14"/>
+      <c r="M67" s="15"/>
     </row>
     <row r="68" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B68" s="42" t="s">
+      <c r="B68" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C68" s="42" t="s">
+      <c r="C68" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D68" s="42" t="s">
+      <c r="D68" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E68" s="42" t="s">
+      <c r="E68" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F68" s="42" t="s">
+      <c r="F68" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G68" s="42" t="s">
+      <c r="G68" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H68" s="42" t="s">
+      <c r="H68" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I68" s="42" t="s">
+      <c r="I68" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J68" s="42" t="s">
+      <c r="J68" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K68" s="42" t="s">
+      <c r="K68" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="L68" s="42" t="s">
+      <c r="L68" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="M68" s="42" t="s">
+      <c r="M68" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="69" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="31">
-        <v>46053</v>
-      </c>
-      <c r="C69" s="32" t="s">
+      <c r="B69" s="44">
+        <v>46081</v>
+      </c>
+      <c r="C69" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D69" s="39">
-        <v>5982.6908653457494</v>
-      </c>
-      <c r="E69" s="39">
-        <v>6029.9084311130609</v>
-      </c>
-      <c r="F69" s="39">
-        <v>302.90637568773838</v>
-      </c>
-      <c r="G69" s="39">
-        <v>6430</v>
-      </c>
-      <c r="H69" s="39">
-        <v>5319.4634418897685</v>
-      </c>
-      <c r="I69" s="39">
-        <v>6268.9</v>
-      </c>
-      <c r="J69" s="39">
-        <v>6149.6332029231917</v>
-      </c>
-      <c r="K69" s="39">
-        <v>5849.6714661441902</v>
-      </c>
-      <c r="L69" s="39">
-        <v>5770.7462557155604</v>
-      </c>
-      <c r="M69" s="34">
+      <c r="D69" s="45">
+        <v>5806.565678253477</v>
+      </c>
+      <c r="E69" s="45">
+        <v>5853.6437803200006</v>
+      </c>
+      <c r="F69" s="45">
+        <v>241.1420198775526</v>
+      </c>
+      <c r="G69" s="45">
+        <v>6169</v>
+      </c>
+      <c r="H69" s="45">
+        <v>5305.7373551553956</v>
+      </c>
+      <c r="I69" s="45">
+        <v>6036.190108662483</v>
+      </c>
+      <c r="J69" s="45">
+        <v>5911.8915694394873</v>
+      </c>
+      <c r="K69" s="45">
+        <v>5711.7716827912654</v>
+      </c>
+      <c r="L69" s="45">
+        <v>5544.8163374575124</v>
+      </c>
+      <c r="M69" s="46">
         <v>10</v>
       </c>
-      <c r="N69" s="44"/>
+      <c r="N69" s="32"/>
     </row>
     <row r="70" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B70" s="2">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D70" s="40">
-        <v>5798.2480377051997</v>
-      </c>
-      <c r="E70" s="40">
-        <v>5941.415890888371</v>
-      </c>
-      <c r="F70" s="40">
-        <v>390.10296901195738</v>
-      </c>
-      <c r="G70" s="40">
-        <v>6160</v>
-      </c>
-      <c r="H70" s="40">
-        <v>4955.6656843901901</v>
-      </c>
-      <c r="I70" s="40">
-        <v>6139.3</v>
-      </c>
-      <c r="J70" s="40">
-        <v>6063.0432483003624</v>
-      </c>
-      <c r="K70" s="40">
-        <v>5661.2329038085454</v>
-      </c>
-      <c r="L70" s="40">
-        <v>5306.8278116617139</v>
+      <c r="D70" s="42">
+        <v>6492.6827852246961</v>
+      </c>
+      <c r="E70" s="42">
+        <v>6535.555191207528</v>
+      </c>
+      <c r="F70" s="42">
+        <v>502.99773985247208</v>
+      </c>
+      <c r="G70" s="42">
+        <v>7640.1492081188362</v>
+      </c>
+      <c r="H70" s="42">
+        <v>5985.0668372843356</v>
+      </c>
+      <c r="I70" s="42">
+        <v>6815.6149208118832</v>
+      </c>
+      <c r="J70" s="42">
+        <v>6683.3173999604815</v>
+      </c>
+      <c r="K70" s="42">
+        <v>6056.6825664500884</v>
+      </c>
+      <c r="L70" s="42">
+        <v>6015.4698617594331</v>
       </c>
       <c r="M70" s="5">
         <v>10</v>
       </c>
-      <c r="N70" s="44"/>
+      <c r="N70" s="32"/>
     </row>
     <row r="71" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B71" s="37">
-        <v>46112</v>
-      </c>
-      <c r="C71" s="32" t="s">
+      <c r="B71" s="35">
+        <v>46142</v>
+      </c>
+      <c r="C71" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D71" s="39">
-        <v>6481.2058532939136</v>
-      </c>
-      <c r="E71" s="39">
-        <v>6609.8108428513588</v>
-      </c>
-      <c r="F71" s="39">
-        <v>464.14727295210821</v>
-      </c>
-      <c r="G71" s="39">
-        <v>6901.3929451472677</v>
-      </c>
-      <c r="H71" s="39">
-        <v>5402.1652097985616</v>
-      </c>
-      <c r="I71" s="39">
-        <v>6894.0030358126696</v>
-      </c>
-      <c r="J71" s="39">
-        <v>6780.048085298291</v>
-      </c>
-      <c r="K71" s="39">
-        <v>6410.75</v>
-      </c>
-      <c r="L71" s="39">
-        <v>5942.4704956695914</v>
-      </c>
-      <c r="M71" s="36">
+      <c r="D71" s="45">
+        <v>6544.4766656650336</v>
+      </c>
+      <c r="E71" s="45">
+        <v>6511.4795945699998</v>
+      </c>
+      <c r="F71" s="45">
+        <v>394.64894283890521</v>
+      </c>
+      <c r="G71" s="45">
+        <v>7339.9100809943011</v>
+      </c>
+      <c r="H71" s="45">
+        <v>5974.5089368252238</v>
+      </c>
+      <c r="I71" s="45">
+        <v>7031.2910080994297</v>
+      </c>
+      <c r="J71" s="45">
+        <v>6630.7208925849882</v>
+      </c>
+      <c r="K71" s="45">
+        <v>6327.4937703307241</v>
+      </c>
+      <c r="L71" s="45">
+        <v>6167.4599498400939</v>
+      </c>
+      <c r="M71" s="38">
         <v>10</v>
       </c>
-      <c r="N71" s="44"/>
+      <c r="N71" s="32"/>
     </row>
     <row r="72" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B72" s="2">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D72" s="40">
-        <v>6743.5935373103712</v>
-      </c>
-      <c r="E72" s="40">
-        <v>6680.7289583038491</v>
-      </c>
-      <c r="F72" s="40">
-        <v>343.25662100949842</v>
-      </c>
-      <c r="G72" s="40">
-        <v>7531.129713440665</v>
-      </c>
-      <c r="H72" s="40">
-        <v>6366.4991686741851</v>
-      </c>
-      <c r="I72" s="40">
-        <v>7089.112971344066</v>
-      </c>
-      <c r="J72" s="40">
-        <v>6807.25</v>
-      </c>
-      <c r="K72" s="40">
-        <v>6532.8699520857108</v>
-      </c>
-      <c r="L72" s="40">
-        <v>6396.1857551783933</v>
+      <c r="D72" s="42">
+        <v>6968.5313294346633</v>
+      </c>
+      <c r="E72" s="42">
+        <v>6940.7288275244819</v>
+      </c>
+      <c r="F72" s="42">
+        <v>594.16821680799217</v>
+      </c>
+      <c r="G72" s="42">
+        <v>8301.2622668812437</v>
+      </c>
+      <c r="H72" s="42">
+        <v>6234.9522612827004</v>
+      </c>
+      <c r="I72" s="42">
+        <v>7431.6700477862432</v>
+      </c>
+      <c r="J72" s="42">
+        <v>7177.75</v>
+      </c>
+      <c r="K72" s="42">
+        <v>6565.6424141689322</v>
+      </c>
+      <c r="L72" s="42">
+        <v>6333.9617300983382</v>
       </c>
       <c r="M72" s="5">
         <v>10</v>
       </c>
-      <c r="N72" s="44"/>
+      <c r="N72" s="32"/>
     </row>
     <row r="73" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B73" s="37">
-        <v>46173</v>
-      </c>
-      <c r="C73" s="32" t="s">
+      <c r="B73" s="35">
+        <v>46203</v>
+      </c>
+      <c r="C73" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D73" s="39">
-        <v>7149.1414689466637</v>
-      </c>
-      <c r="E73" s="39">
-        <v>7266.5858079433256</v>
-      </c>
-      <c r="F73" s="39">
-        <v>350.12822190868877</v>
-      </c>
-      <c r="G73" s="39">
-        <v>7531.0858216495244</v>
-      </c>
-      <c r="H73" s="39">
-        <v>6362.7542132760973</v>
-      </c>
-      <c r="I73" s="39">
-        <v>7511.0802304927429</v>
-      </c>
-      <c r="J73" s="39">
-        <v>7321.472587869469</v>
-      </c>
-      <c r="K73" s="39">
-        <v>6998.2896818478857</v>
-      </c>
-      <c r="L73" s="39">
-        <v>6799.4754213276101</v>
-      </c>
-      <c r="M73" s="36">
+      <c r="D73" s="45">
+        <v>6998.1147913059094</v>
+      </c>
+      <c r="E73" s="45">
+        <v>6937.2730416205286</v>
+      </c>
+      <c r="F73" s="45">
+        <v>548.65141981773706</v>
+      </c>
+      <c r="G73" s="45">
+        <v>8136.8805849166347</v>
+      </c>
+      <c r="H73" s="45">
+        <v>6213.7266457764244</v>
+      </c>
+      <c r="I73" s="45">
+        <v>7482.9213586815267</v>
+      </c>
+      <c r="J73" s="45">
+        <v>7288.75</v>
+      </c>
+      <c r="K73" s="45">
+        <v>6757.5278859980745</v>
+      </c>
+      <c r="L73" s="45">
+        <v>6377.6917724066416</v>
+      </c>
+      <c r="M73" s="38">
         <v>10</v>
       </c>
-      <c r="N73" s="44"/>
+      <c r="N73" s="32"/>
     </row>
     <row r="74" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B74" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D74" s="40">
-        <v>6954.5511495336923</v>
-      </c>
-      <c r="E74" s="40">
-        <v>7028.2822656868912</v>
-      </c>
-      <c r="F74" s="40">
-        <v>429.00600449921183</v>
-      </c>
-      <c r="G74" s="40">
-        <v>7483.8731524841869</v>
-      </c>
-      <c r="H74" s="40">
-        <v>6213.7266457764263</v>
-      </c>
-      <c r="I74" s="40">
-        <v>7417.5431131731739</v>
-      </c>
-      <c r="J74" s="40">
-        <v>7241.75</v>
-      </c>
-      <c r="K74" s="40">
-        <v>6778.0479748586131</v>
-      </c>
-      <c r="L74" s="40">
-        <v>6312.9566062941558</v>
+      <c r="D74" s="42">
+        <v>7269.6716630964902</v>
+      </c>
+      <c r="E74" s="42">
+        <v>7317.3501964617963</v>
+      </c>
+      <c r="F74" s="42">
+        <v>400.1176503932283</v>
+      </c>
+      <c r="G74" s="42">
+        <v>7750.3689773279848</v>
+      </c>
+      <c r="H74" s="42">
+        <v>6537.9395260694328</v>
+      </c>
+      <c r="I74" s="42">
+        <v>7698.7368977327988</v>
+      </c>
+      <c r="J74" s="42">
+        <v>7546.5145086835983</v>
+      </c>
+      <c r="K74" s="42">
+        <v>7056.9905475302603</v>
+      </c>
+      <c r="L74" s="42">
+        <v>6822.0984377059431</v>
       </c>
       <c r="M74" s="5">
         <v>10</v>
       </c>
-      <c r="N74" s="44"/>
+      <c r="N74" s="32"/>
     </row>
     <row r="75" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B75" s="37">
-        <v>46234</v>
-      </c>
-      <c r="C75" s="32" t="s">
+      <c r="B75" s="35">
+        <v>46265</v>
+      </c>
+      <c r="C75" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D75" s="39">
-        <v>7399.2252721945433</v>
-      </c>
-      <c r="E75" s="39">
-        <v>7395.9148400180256</v>
-      </c>
-      <c r="F75" s="39">
-        <v>494.58717972010868</v>
-      </c>
-      <c r="G75" s="39">
-        <v>8342.9875834676568</v>
-      </c>
-      <c r="H75" s="39">
-        <v>6537.9395260694382</v>
-      </c>
-      <c r="I75" s="39">
-        <v>7809.5497785440093</v>
-      </c>
-      <c r="J75" s="39">
-        <v>7661.5</v>
-      </c>
-      <c r="K75" s="39">
-        <v>7139.9837018966373</v>
-      </c>
-      <c r="L75" s="39">
-        <v>6902.7088292687977</v>
-      </c>
-      <c r="M75" s="36">
+      <c r="D75" s="45">
+        <v>7096.1429521679911</v>
+      </c>
+      <c r="E75" s="45">
+        <v>7040.5</v>
+      </c>
+      <c r="F75" s="45">
+        <v>541.5578881030101</v>
+      </c>
+      <c r="G75" s="45">
+        <v>7802.1267630134289</v>
+      </c>
+      <c r="H75" s="45">
+        <v>6395.9237498412849</v>
+      </c>
+      <c r="I75" s="45">
+        <v>7715.2558575953926</v>
+      </c>
+      <c r="J75" s="45">
+        <v>7616.5617092178982</v>
+      </c>
+      <c r="K75" s="45">
+        <v>6600.7482257465672</v>
+      </c>
+      <c r="L75" s="45">
+        <v>6436.4717984426761</v>
+      </c>
+      <c r="M75" s="38">
         <v>10</v>
       </c>
-      <c r="N75" s="44"/>
+      <c r="N75" s="32"/>
     </row>
     <row r="76" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B76" s="6" t="s">
+      <c r="B76" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="D76" s="40">
-        <v>81761.092321851887</v>
-      </c>
-      <c r="E76" s="40">
-        <v>81693.761218181346</v>
-      </c>
-      <c r="F76" s="40">
-        <v>3553.540104948283</v>
-      </c>
-      <c r="G76" s="40">
-        <v>86207.316470277612</v>
-      </c>
-      <c r="H76" s="40">
-        <v>75338</v>
-      </c>
-      <c r="I76" s="40">
-        <v>86119.731647027758</v>
-      </c>
-      <c r="J76" s="40">
-        <v>84668.348907849839</v>
-      </c>
-      <c r="K76" s="40">
-        <v>79449.5</v>
-      </c>
-      <c r="L76" s="40">
-        <v>78299.619812431294</v>
-      </c>
-      <c r="M76" s="5">
+      <c r="D76" s="42">
+        <v>80358.315782740858</v>
+      </c>
+      <c r="E76" s="42">
+        <v>80340.109432809521</v>
+      </c>
+      <c r="F76" s="42">
+        <v>3855.9619956781062</v>
+      </c>
+      <c r="G76" s="42">
+        <v>86267.646593271842</v>
+      </c>
+      <c r="H76" s="42">
+        <v>74493.452105731427</v>
+      </c>
+      <c r="I76" s="42">
+        <v>83933.695859327185</v>
+      </c>
+      <c r="J76" s="42">
+        <v>83266.228826094899</v>
+      </c>
+      <c r="K76" s="42">
+        <v>77733.925619470479</v>
+      </c>
+      <c r="L76" s="42">
+        <v>75285.945210573147</v>
+      </c>
+      <c r="M76" s="43">
         <v>10</v>
       </c>
-      <c r="N76" s="44"/>
+      <c r="N76" s="32"/>
     </row>
     <row r="77" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B77" s="9"/>
@@ -7726,56 +7724,56 @@
       <c r="M77" s="10"/>
     </row>
     <row r="79" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="41" t="s">
+      <c r="B79" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C79" s="41"/>
-      <c r="D79" s="41"/>
-      <c r="E79" s="41"/>
-      <c r="F79" s="41"/>
-      <c r="G79" s="41"/>
-      <c r="H79" s="41"/>
-      <c r="I79" s="41"/>
-      <c r="J79" s="41"/>
-      <c r="K79" s="41"/>
-      <c r="L79" s="41"/>
-      <c r="M79" s="41"/>
+      <c r="C79" s="14"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="14"/>
+      <c r="F79" s="14"/>
+      <c r="G79" s="14"/>
+      <c r="H79" s="14"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="14"/>
+      <c r="K79" s="14"/>
+      <c r="L79" s="14"/>
+      <c r="M79" s="15"/>
     </row>
     <row r="80" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B80" s="42" t="s">
+      <c r="B80" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C80" s="42" t="s">
+      <c r="C80" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D80" s="42" t="s">
+      <c r="D80" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E80" s="42" t="s">
+      <c r="E80" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F80" s="42" t="s">
+      <c r="F80" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G80" s="42" t="s">
+      <c r="G80" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H80" s="42" t="s">
+      <c r="H80" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I80" s="42" t="s">
+      <c r="I80" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J80" s="42" t="s">
+      <c r="J80" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K80" s="42" t="s">
+      <c r="K80" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="L80" s="42" t="s">
+      <c r="L80" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="M80" s="42" t="s">
+      <c r="M80" s="25" t="s">
         <v>12</v>
       </c>
     </row>
@@ -7786,37 +7784,37 @@
       <c r="C81" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="40">
-        <v>15466.36568859111</v>
-      </c>
-      <c r="E81" s="40">
-        <v>15650</v>
-      </c>
-      <c r="F81" s="40">
-        <v>1717.572730397166</v>
-      </c>
-      <c r="G81" s="40">
-        <v>17828.38290353704</v>
-      </c>
-      <c r="H81" s="40">
-        <v>11769</v>
-      </c>
-      <c r="I81" s="40">
-        <v>16957.279290353701</v>
-      </c>
-      <c r="J81" s="40">
-        <v>16451.7</v>
-      </c>
-      <c r="K81" s="40">
-        <v>15293.656302469661</v>
-      </c>
-      <c r="L81" s="40">
-        <v>13408.47802117305</v>
+      <c r="D81" s="33">
+        <v>15913.736253091431</v>
+      </c>
+      <c r="E81" s="33">
+        <v>16270.5</v>
+      </c>
+      <c r="F81" s="33">
+        <v>1623.8605847333381</v>
+      </c>
+      <c r="G81" s="33">
+        <v>18273.092980624231</v>
+      </c>
+      <c r="H81" s="33">
+        <v>12626.7154272928</v>
+      </c>
+      <c r="I81" s="33">
+        <v>17647.518298062419</v>
+      </c>
+      <c r="J81" s="33">
+        <v>16673.075000000001</v>
+      </c>
+      <c r="K81" s="33">
+        <v>15150</v>
+      </c>
+      <c r="L81" s="33">
+        <v>14250.07125342677</v>
       </c>
       <c r="M81" s="5">
         <v>10</v>
       </c>
-      <c r="N81" s="43"/>
+      <c r="N81" s="31"/>
     </row>
     <row r="82" spans="2:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B82" s="9"/>
@@ -7832,215 +7830,216 @@
       <c r="L82" s="10"/>
       <c r="M82" s="10"/>
     </row>
-    <row r="84" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="41" t="s">
+    <row r="83" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B84" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C84" s="41"/>
-      <c r="D84" s="41"/>
-      <c r="E84" s="41"/>
-      <c r="F84" s="41"/>
-      <c r="G84" s="41"/>
-      <c r="H84" s="41"/>
-      <c r="I84" s="41"/>
-      <c r="J84" s="41"/>
-      <c r="K84" s="41"/>
-      <c r="L84" s="41"/>
-      <c r="M84" s="41"/>
+      <c r="C84" s="14"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="14"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="14"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="14"/>
+      <c r="K84" s="14"/>
+      <c r="L84" s="14"/>
+      <c r="M84" s="15"/>
     </row>
     <row r="85" spans="2:16" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B85" s="42" t="s">
+      <c r="B85" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C85" s="42" t="s">
+      <c r="C85" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D85" s="42" t="s">
+      <c r="D85" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E85" s="42" t="s">
+      <c r="E85" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F85" s="42" t="s">
+      <c r="F85" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G85" s="42" t="s">
+      <c r="G85" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H85" s="42" t="s">
+      <c r="H85" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I85" s="42" t="s">
+      <c r="I85" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J85" s="42" t="s">
+      <c r="J85" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K85" s="42" t="s">
+      <c r="K85" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="L85" s="42" t="s">
+      <c r="L85" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="M85" s="42" t="s">
+      <c r="M85" s="25" t="s">
         <v>12</v>
       </c>
+      <c r="N85" s="31"/>
     </row>
     <row r="86" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B86" s="31" t="s">
+      <c r="B86" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="C86" s="32" t="s">
+      <c r="C86" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="D86" s="33">
-        <v>6.7198099088172913</v>
-      </c>
-      <c r="E86" s="33">
-        <v>6.6781123630373376</v>
-      </c>
-      <c r="F86" s="33">
-        <v>0.37496752367985042</v>
-      </c>
-      <c r="G86" s="33">
+      <c r="D86" s="37">
+        <v>6.6913845681962414</v>
+      </c>
+      <c r="E86" s="37">
+        <v>6.6831123630373384</v>
+      </c>
+      <c r="F86" s="37">
+        <v>0.32184339150869912</v>
+      </c>
+      <c r="G86" s="37">
         <v>7.3</v>
       </c>
-      <c r="H86" s="33">
-        <v>6.1542534062105032</v>
-      </c>
-      <c r="I86" s="33">
-        <v>7.21</v>
-      </c>
-      <c r="J86" s="33">
-        <v>6.9907157169157976</v>
-      </c>
-      <c r="K86" s="33">
-        <v>6.5250000000000004</v>
-      </c>
-      <c r="L86" s="33">
-        <v>6.2854253406210514</v>
-      </c>
-      <c r="M86" s="34">
+      <c r="H86" s="37">
+        <v>6.2</v>
+      </c>
+      <c r="I86" s="37">
+        <v>7.1088588602989571</v>
+      </c>
+      <c r="J86" s="37">
+        <v>6.7</v>
+      </c>
+      <c r="K86" s="37">
+        <v>6.6150000000000002</v>
+      </c>
+      <c r="L86" s="37">
+        <v>6.29</v>
+      </c>
+      <c r="M86" s="46">
         <v>10</v>
       </c>
-      <c r="N86" s="43"/>
+      <c r="N86" s="31"/>
     </row>
     <row r="87" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="2" t="s">
+      <c r="B87" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D87" s="4">
-        <v>7.2729057628387164</v>
+        <v>7.2202895076872293</v>
       </c>
       <c r="E87" s="4">
         <v>7.3</v>
       </c>
       <c r="F87" s="4">
-        <v>0.50723307968402942</v>
+        <v>0.32194623085600887</v>
       </c>
       <c r="G87" s="4">
-        <v>8.0416788902996341</v>
+        <v>7.5886822345868117</v>
       </c>
       <c r="H87" s="4">
         <v>6.4</v>
       </c>
       <c r="I87" s="4">
-        <v>7.8241678890299644</v>
+        <v>7.431659781515604</v>
       </c>
       <c r="J87" s="4">
-        <v>7.5786826271057901</v>
+        <v>7.3</v>
       </c>
       <c r="K87" s="4">
-        <v>7.0750000000000002</v>
+        <v>7.3</v>
       </c>
       <c r="L87" s="4">
-        <v>6.58</v>
+        <v>6.94</v>
       </c>
       <c r="M87" s="5">
         <v>10</v>
       </c>
-      <c r="N87" s="43"/>
+      <c r="N87" s="31"/>
     </row>
     <row r="88" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B88" s="35" t="s">
+      <c r="B88" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="C88" s="32" t="s">
+      <c r="C88" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="D88" s="33">
-        <v>7.0130089686393209</v>
-      </c>
-      <c r="E88" s="33">
-        <v>6.9811001909775197</v>
-      </c>
-      <c r="F88" s="33">
-        <v>0.65040632219387817</v>
-      </c>
-      <c r="G88" s="33">
-        <v>8.3744438601916027</v>
-      </c>
-      <c r="H88" s="33">
-        <v>6.2175137401140592</v>
-      </c>
-      <c r="I88" s="33">
-        <v>7.677444386019161</v>
-      </c>
-      <c r="J88" s="33">
-        <v>7.2569487780993693</v>
-      </c>
-      <c r="K88" s="33">
+      <c r="D88" s="37">
+        <v>6.9540845192427954</v>
+      </c>
+      <c r="E88" s="37">
+        <v>7.13110019097752</v>
+      </c>
+      <c r="F88" s="37">
+        <v>0.49393260274473361</v>
+      </c>
+      <c r="G88" s="37">
+        <v>7.8301336256976999</v>
+      </c>
+      <c r="H88" s="37">
+        <v>6.2885111847752126</v>
+      </c>
+      <c r="I88" s="37">
+        <v>7.31701336256977</v>
+      </c>
+      <c r="J88" s="37">
+        <v>7.2</v>
+      </c>
+      <c r="K88" s="37">
         <v>6.55</v>
       </c>
-      <c r="L88" s="33">
-        <v>6.2917513740114046</v>
-      </c>
-      <c r="M88" s="36">
+      <c r="L88" s="37">
+        <v>6.2988511184775211</v>
+      </c>
+      <c r="M88" s="38">
         <v>10</v>
       </c>
-      <c r="N88" s="43"/>
+      <c r="N88" s="31"/>
     </row>
     <row r="89" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B89" s="6" t="s">
+      <c r="B89" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>31</v>
       </c>
       <c r="D89" s="4">
-        <v>6.7176339393137736</v>
+        <v>6.7511356001973848</v>
       </c>
       <c r="E89" s="4">
-        <v>6.7322781503441833</v>
+        <v>6.65</v>
       </c>
       <c r="F89" s="4">
-        <v>0.52861171793905581</v>
+        <v>0.45032804827589978</v>
       </c>
       <c r="G89" s="4">
-        <v>7.5</v>
+        <v>7.4559554615135513</v>
       </c>
       <c r="H89" s="4">
         <v>5.9</v>
       </c>
       <c r="I89" s="4">
-        <v>7.3199999999999994</v>
+        <v>7.3155955461513553</v>
       </c>
       <c r="J89" s="4">
-        <v>7.1290022956824863</v>
+        <v>7.0342722550010333</v>
       </c>
       <c r="K89" s="4">
-        <v>6.2750000000000004</v>
+        <v>6.5250000000000004</v>
       </c>
       <c r="L89" s="4">
-        <v>6.166196518747479</v>
+        <v>6.44</v>
       </c>
       <c r="M89" s="5">
         <v>10</v>
       </c>
-      <c r="N89" s="43"/>
     </row>
     <row r="90" spans="2:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B90" s="9"/>
@@ -8056,223 +8055,224 @@
       <c r="L90" s="9"/>
       <c r="M90" s="9"/>
     </row>
-    <row r="92" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="41" t="s">
+    <row r="91" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B92" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C92" s="41"/>
-      <c r="D92" s="41"/>
-      <c r="E92" s="41"/>
-      <c r="F92" s="41"/>
-      <c r="G92" s="41"/>
-      <c r="H92" s="41"/>
-      <c r="I92" s="41"/>
-      <c r="J92" s="41"/>
-      <c r="K92" s="41"/>
-      <c r="L92" s="41"/>
-      <c r="M92" s="41"/>
+      <c r="C92" s="14"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="14"/>
+      <c r="G92" s="14"/>
+      <c r="H92" s="14"/>
+      <c r="I92" s="14"/>
+      <c r="J92" s="14"/>
+      <c r="K92" s="14"/>
+      <c r="L92" s="14"/>
+      <c r="M92" s="15"/>
     </row>
     <row r="93" spans="2:16" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B93" s="42" t="s">
+      <c r="B93" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C93" s="42" t="s">
+      <c r="C93" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D93" s="42" t="s">
+      <c r="D93" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E93" s="42" t="s">
+      <c r="E93" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F93" s="42" t="s">
+      <c r="F93" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G93" s="42" t="s">
+      <c r="G93" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H93" s="42" t="s">
+      <c r="H93" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I93" s="42" t="s">
+      <c r="I93" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J93" s="42" t="s">
+      <c r="J93" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K93" s="42" t="s">
+      <c r="K93" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="L93" s="42" t="s">
+      <c r="L93" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="M93" s="42" t="s">
+      <c r="M93" s="25" t="s">
         <v>12</v>
       </c>
+      <c r="N93" s="31"/>
+      <c r="P93" s="31"/>
     </row>
     <row r="94" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B94" s="37" t="s">
+      <c r="B94" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="C94" s="32" t="s">
+      <c r="C94" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="D94" s="33">
-        <v>9.2919308142511189E-2</v>
-      </c>
-      <c r="E94" s="33">
-        <v>0.09</v>
-      </c>
-      <c r="F94" s="33">
-        <v>0.16242024832841251</v>
-      </c>
-      <c r="G94" s="33">
-        <v>0.4</v>
-      </c>
-      <c r="H94" s="33">
-        <v>-0.19335920059689871</v>
-      </c>
-      <c r="I94" s="33">
-        <v>0.28309983975755448</v>
-      </c>
-      <c r="J94" s="33">
-        <v>0.13554744809199981</v>
-      </c>
-      <c r="K94" s="33">
-        <v>0.01</v>
-      </c>
-      <c r="L94" s="33">
-        <v>-4.6109519128634258E-2</v>
-      </c>
-      <c r="M94" s="36">
+      <c r="D94" s="37">
+        <v>0.69919370341620002</v>
+      </c>
+      <c r="E94" s="37">
+        <v>0.75046167979364586</v>
+      </c>
+      <c r="F94" s="37">
+        <v>0.2137589216062131</v>
+      </c>
+      <c r="G94" s="37">
+        <v>0.9</v>
+      </c>
+      <c r="H94" s="37">
+        <v>0.15</v>
+      </c>
+      <c r="I94" s="37">
+        <v>0.81572030835945208</v>
+      </c>
+      <c r="J94" s="37">
+        <v>0.8</v>
+      </c>
+      <c r="K94" s="37">
+        <v>0.75</v>
+      </c>
+      <c r="L94" s="37">
+        <v>0.49619199875778619</v>
+      </c>
+      <c r="M94" s="46">
         <v>10</v>
       </c>
-      <c r="N94" s="43"/>
-      <c r="P94" s="43"/>
+      <c r="N94" s="31"/>
+      <c r="P94" s="31"/>
     </row>
     <row r="95" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B95" s="2" t="s">
+      <c r="B95" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D95" s="4">
-        <v>1.144898181066776</v>
+        <v>1.169491955674659</v>
       </c>
       <c r="E95" s="4">
-        <v>0.95906651890847971</v>
+        <v>1.0449999999999999</v>
       </c>
       <c r="F95" s="4">
-        <v>0.87256353441298051</v>
+        <v>0.43766092544896312</v>
       </c>
       <c r="G95" s="4">
-        <v>3.46983603033526</v>
+        <v>1.970642791097021</v>
       </c>
       <c r="H95" s="4">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I95" s="4">
-        <v>1.59692370589685</v>
+        <v>1.817064279109702</v>
       </c>
       <c r="J95" s="4">
-        <v>1.2324999999999999</v>
+        <v>1.2904911467065521</v>
       </c>
       <c r="K95" s="4">
-        <v>0.65664280450054913</v>
+        <v>0.96497090477202763</v>
       </c>
       <c r="L95" s="4">
-        <v>0.5</v>
+        <v>0.69</v>
       </c>
       <c r="M95" s="5">
         <v>10</v>
       </c>
-      <c r="N95" s="43"/>
-      <c r="P95" s="43"/>
+      <c r="N95" s="31"/>
+      <c r="P95" s="31"/>
     </row>
     <row r="96" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B96" s="35" t="s">
+      <c r="B96" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="C96" s="32" t="s">
+      <c r="C96" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="D96" s="33">
-        <v>0.89046049542566941</v>
-      </c>
-      <c r="E96" s="33">
-        <v>0.91135134999998435</v>
-      </c>
-      <c r="F96" s="33">
-        <v>0.30264257448882997</v>
-      </c>
-      <c r="G96" s="33">
-        <v>1.541348056939817</v>
-      </c>
-      <c r="H96" s="33">
-        <v>0.47</v>
-      </c>
-      <c r="I96" s="33">
-        <v>1.0541348056939821</v>
-      </c>
-      <c r="J96" s="33">
+      <c r="D96" s="37">
+        <v>0.70612465640842925</v>
+      </c>
+      <c r="E96" s="37">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="F96" s="37">
+        <v>0.33372712626231021</v>
+      </c>
+      <c r="G96" s="37">
         <v>1</v>
       </c>
-      <c r="K96" s="33">
-        <v>0.67590060000000929</v>
-      </c>
-      <c r="L96" s="33">
-        <v>0.55941805758520669</v>
-      </c>
-      <c r="M96" s="36">
+      <c r="H96" s="37">
+        <v>0.16659991102225821</v>
+      </c>
+      <c r="I96" s="37">
+        <v>1</v>
+      </c>
+      <c r="J96" s="37">
+        <v>0.9748907197586365</v>
+      </c>
+      <c r="K96" s="37">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="L96" s="37">
+        <v>0.28693002096206838</v>
+      </c>
+      <c r="M96" s="38">
         <v>10</v>
       </c>
-      <c r="N96" s="43"/>
-      <c r="P96" s="43"/>
-    </row>
-    <row r="97" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B97" s="6" t="s">
+      <c r="N96" s="31"/>
+      <c r="P96" s="31"/>
+    </row>
+    <row r="97" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B97" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D97" s="4">
-        <v>2.6821341358304829</v>
+        <v>2.962285633998416</v>
       </c>
       <c r="E97" s="4">
-        <v>2.69</v>
+        <v>2.7426755893834631</v>
       </c>
       <c r="F97" s="4">
-        <v>0.90251538788567576</v>
+        <v>0.77890860287159136</v>
       </c>
       <c r="G97" s="4">
-        <v>4.2134933086128923</v>
+        <v>4.1584456131180891</v>
       </c>
       <c r="H97" s="4">
-        <v>1</v>
+        <v>1.94</v>
       </c>
       <c r="I97" s="4">
-        <v>3.9547314316209459</v>
+        <v>4.0698445613118084</v>
       </c>
       <c r="J97" s="4">
-        <v>2.776623848687676</v>
+        <v>3.4287300871889079</v>
       </c>
       <c r="K97" s="4">
-        <v>2.2697926387364888</v>
+        <v>2.514547868207909</v>
       </c>
       <c r="L97" s="4">
-        <v>2.0169999999999999</v>
+        <v>1.994</v>
       </c>
       <c r="M97" s="5">
         <v>10</v>
       </c>
-      <c r="N97" s="43"/>
-      <c r="P97" s="43"/>
-    </row>
-    <row r="98" spans="2:16" ht="18.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B98" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="10"/>
@@ -8287,6 +8287,9 @@
       <c r="M98" s="10"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:M2"/>
+  </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="41" fitToHeight="2" orientation="landscape" r:id="rId1"/>
@@ -8318,6 +8321,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b80df5a0-8011-40eb-be96-4c6a59f56b6e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6b042263-e944-4dfe-97a8-6e4c84e0ae4b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004E1357DA6D65CA49A875959554824B49" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="e8f8602aebf7bbdcbcb5348c529dc11a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b80df5a0-8011-40eb-be96-4c6a59f56b6e" xmlns:ns3="6b042263-e944-4dfe-97a8-6e4c84e0ae4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a39dbf9ae3c20398b89cd584be7bda98" ns2:_="" ns3:_="">
     <xsd:import namespace="b80df5a0-8011-40eb-be96-4c6a59f56b6e"/>
@@ -8566,27 +8589,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E4A204-179E-478B-A62E-54900BF00ECD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b80df5a0-8011-40eb-be96-4c6a59f56b6e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6b042263-e944-4dfe-97a8-6e4c84e0ae4b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB7C2FA5-1A6F-45A0-B729-06C123F95F83}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="6b042263-e944-4dfe-97a8-6e4c84e0ae4b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="b80df5a0-8011-40eb-be96-4c6a59f56b6e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89E97169-F966-43F7-97A7-EB3192694F7A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8603,29 +8631,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E4A204-179E-478B-A62E-54900BF00ECD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB7C2FA5-1A6F-45A0-B729-06C123F95F83}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="6b042263-e944-4dfe-97a8-6e4c84e0ae4b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="b80df5a0-8011-40eb-be96-4c6a59f56b6e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/public/REM/raw/REM.xlsx
+++ b/public/REM/raw/REM.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcranet.sharepoint.com/sites/REM/Documentos compartidos/REM/Publicación/Pagina WEB/2026/26 02 Feb/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcranet.sharepoint.com/sites/REM/Documentos compartidos/REM/Publicación/Pagina WEB/2026/26 03 Mar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{563D5886-1088-4C76-92B3-92AAC244057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6C4A1AC-8CCC-4547-99F3-2187D6A0D046}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="8_{563D5886-1088-4C76-92B3-92AAC244057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F895A9E-B8AD-42E1-B37C-C782B04A5BC2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A5F0209-F8EA-4E2B-A469-F799AD0A214D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Cuadros de resultados" sheetId="14" r:id="rId1"/>
-    <sheet name="Resultados TOP 10" sheetId="13" r:id="rId2"/>
+    <sheet name="Cuadros de resultados" sheetId="16" r:id="rId1"/>
+    <sheet name="Resultados TOP 10" sheetId="15" r:id="rId2"/>
     <sheet name="Notas Metodólogicas" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Cuadros de resultados'!$B$2:$M$112</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Resultados TOP 10'!$B$2:$M$86</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Resultados TOP 10'!$B$2:$M$98</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Cuadros de resultados'!$2:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Resultados TOP 10'!$2:$4</definedName>
   </definedNames>
@@ -160,9 +160,6 @@
     <t>2027</t>
   </si>
   <si>
-    <t>Trim. IV-25</t>
-  </si>
-  <si>
     <t>Trim. I-26</t>
   </si>
   <si>
@@ -184,36 +181,38 @@
     <t>% de la PEA; Trim. IV-27</t>
   </si>
   <si>
-    <t>Relevamiento de Expectativas de Mercado (REM)  Top 10 - BCRA - Febrero 2026</t>
+    <t>Relevamiento de Expectativas de Mercado (REM)  Top 10 - BCRA - Marzo 2026</t>
   </si>
   <si>
-    <t>var. % i.a.; feb-27</t>
+    <t>var. % i.a.; mar-27</t>
   </si>
   <si>
-    <t>TNA; %; feb-27</t>
+    <t>var. % i.a.; mar-28</t>
   </si>
   <si>
-    <t>$/USD; feb-27</t>
+    <t>TNA; %; mar-27</t>
   </si>
   <si>
-    <t>Fuente: REM - BCRA (feb-26)</t>
+    <t>$/USD; mar-27</t>
   </si>
   <si>
-    <t>Relevamiento de Expectativas de Mercado (REM)  - BCRA - Febrero 2026</t>
+    <t>Trim. III-26</t>
   </si>
   <si>
-    <t>var. % i.a.; feb-28</t>
+    <t>Fuente: REM - BCRA (mar-26)</t>
+  </si>
+  <si>
+    <t>Relevamiento de Expectativas de Mercado (REM)  - BCRA - Marzo 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -400,7 +399,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -488,14 +487,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="17" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -506,12 +497,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -535,6 +520,12 @@
     <xf numFmtId="14" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Millares" xfId="4" builtinId="3"/>
@@ -544,7 +535,9 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{1C591AF6-600F-4556-A61E-DD4A85B64263}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1873,12 +1866,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{556BA34D-D1CA-4035-A3E8-638451BB2414}">
-  <sheetPr codeName="Hoja1">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19E327E7-B164-47AD-AD5E-FA66C450386C}">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:N112"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:M112"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.5703125" style="1" customWidth="1"/>
     <col min="3" max="3" width="30.85546875" style="1" customWidth="1"/>
@@ -1891,9 +1884,9 @@
     <col min="13" max="13" width="18.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B2" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -1907,7 +1900,7 @@
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
     </row>
-    <row r="3" spans="2:14" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
@@ -1921,11 +1914,11 @@
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="L4" s="12"/>
       <c r="M4" s="13"/>
     </row>
-    <row r="5" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
         <v>0</v>
       </c>
@@ -1941,7 +1934,7 @@
       <c r="L5" s="14"/>
       <c r="M5" s="15"/>
     </row>
-    <row r="6" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B6" s="16" t="s">
         <v>1</v>
       </c>
@@ -1979,358 +1972,349 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B7" s="17">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="19">
-        <v>2.690410151713714</v>
+        <v>3</v>
       </c>
       <c r="E7" s="19">
-        <v>2.640300109904544</v>
+        <v>3.0243883054932441</v>
       </c>
       <c r="F7" s="19">
-        <v>0.21676238612146179</v>
+        <v>0.1849467560456424</v>
       </c>
       <c r="G7" s="19">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="H7" s="19">
-        <v>2.0127686378889749</v>
+        <v>2.5</v>
       </c>
       <c r="I7" s="19">
-        <v>2.9</v>
+        <v>3.2127094616641449</v>
       </c>
       <c r="J7" s="19">
-        <v>2.7941561110827942</v>
+        <v>3.1205227197818841</v>
       </c>
       <c r="K7" s="19">
-        <v>2.5815972069022579</v>
+        <v>2.9047014999999998</v>
       </c>
       <c r="L7" s="19">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="M7" s="20">
         <v>46</v>
       </c>
-      <c r="N7" s="31"/>
-    </row>
-    <row r="8" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="4">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="E8" s="4">
-        <v>2.518346184713339</v>
+        <v>2.5705335165110199</v>
       </c>
       <c r="F8" s="4">
-        <v>0.27741076718030161</v>
+        <v>0.28318350828592759</v>
       </c>
       <c r="G8" s="4">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="H8" s="4">
-        <v>1.8857824562493299</v>
+        <v>1.3</v>
       </c>
       <c r="I8" s="4">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="J8" s="4">
-        <v>2.7</v>
+        <v>2.7123327793798881</v>
       </c>
       <c r="K8" s="4">
-        <v>2.369945700547337</v>
+        <v>2.4390036830923232</v>
       </c>
       <c r="L8" s="4">
-        <v>2.2000000000000002</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="M8" s="5">
         <v>46</v>
       </c>
-      <c r="N8" s="31"/>
-    </row>
-    <row r="9" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B9" s="17">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="19">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="E9" s="19">
-        <v>2.1561493040907602</v>
+        <v>2.2317104245191031</v>
       </c>
       <c r="F9" s="19">
-        <v>0.29690903359079968</v>
+        <v>0.32546577421435791</v>
       </c>
       <c r="G9" s="19">
-        <v>2.7</v>
+        <v>2.7108206923785132</v>
       </c>
       <c r="H9" s="19">
-        <v>1.3</v>
+        <v>0.90000000000000013</v>
       </c>
       <c r="I9" s="19">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="J9" s="19">
-        <v>2.380207941650216</v>
+        <v>2.4750000000000001</v>
       </c>
       <c r="K9" s="19">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="L9" s="19">
-        <v>1.792431477173027</v>
+        <v>1.91</v>
       </c>
       <c r="M9" s="20">
         <v>46</v>
       </c>
-      <c r="N9" s="31"/>
-    </row>
-    <row r="10" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="4">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="E10" s="4">
-        <v>1.9097236539325031</v>
+        <v>2.038777101239948</v>
       </c>
       <c r="F10" s="4">
-        <v>0.34485990588086329</v>
+        <v>0.31296766245883179</v>
       </c>
       <c r="G10" s="4">
-        <v>2.7</v>
+        <v>2.7199970764476471</v>
       </c>
       <c r="H10" s="4">
-        <v>0.90000000000000013</v>
+        <v>1</v>
       </c>
       <c r="I10" s="4">
-        <v>2.35</v>
+        <v>2.4750000000000001</v>
       </c>
       <c r="J10" s="4">
-        <v>2.1535159117098441</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K10" s="4">
-        <v>1.7</v>
+        <v>1.8075000000000001</v>
       </c>
       <c r="L10" s="4">
-        <v>1.550738366435545</v>
+        <v>1.741522692820193</v>
       </c>
       <c r="M10" s="5">
         <v>46</v>
       </c>
-      <c r="N10" s="31"/>
-    </row>
-    <row r="11" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B11" s="17">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="19">
-        <v>1.7999283980248959</v>
+        <v>1.9750000000000001</v>
       </c>
       <c r="E11" s="19">
-        <v>1.7608541247164351</v>
+        <v>1.9688550797838209</v>
       </c>
       <c r="F11" s="19">
-        <v>0.30124665505394121</v>
+        <v>0.33896380127268821</v>
       </c>
       <c r="G11" s="19">
-        <v>2.3949179711396869</v>
+        <v>2.658120071355865</v>
       </c>
       <c r="H11" s="19">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I11" s="19">
-        <v>2.15</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="J11" s="19">
-        <v>1.9375</v>
+        <v>2.216236748553202</v>
       </c>
       <c r="K11" s="19">
-        <v>1.57</v>
+        <v>1.720509429572683</v>
       </c>
       <c r="L11" s="19">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="M11" s="20">
         <v>46</v>
       </c>
-      <c r="N11" s="31"/>
-    </row>
-    <row r="12" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B12" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="4">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="E12" s="4">
-        <v>1.7003879842396841</v>
+        <v>1.8004639144284269</v>
       </c>
       <c r="F12" s="4">
-        <v>0.33031004230671968</v>
+        <v>0.33382281173407302</v>
       </c>
       <c r="G12" s="4">
-        <v>2.5</v>
+        <v>2.5307687309620248</v>
       </c>
       <c r="H12" s="4">
-        <v>0.8</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="I12" s="4">
-        <v>2.100010731535241</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J12" s="4">
-        <v>1.8975</v>
+        <v>2</v>
       </c>
       <c r="K12" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="L12" s="4">
         <v>1.5</v>
-      </c>
-      <c r="L12" s="4">
-        <v>1.355116176528409</v>
       </c>
       <c r="M12" s="5">
         <v>46</v>
       </c>
-      <c r="N12" s="31"/>
-    </row>
-    <row r="13" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B13" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="19">
-        <v>1.5249999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="E13" s="19">
-        <v>1.601042801541414</v>
+        <v>1.7589175909647601</v>
       </c>
       <c r="F13" s="19">
-        <v>0.31378567509516608</v>
+        <v>0.39012938906764127</v>
       </c>
       <c r="G13" s="19">
-        <v>2.2808436605211702</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="H13" s="19">
-        <v>0.70000000000000007</v>
+        <v>0.49999999999999961</v>
       </c>
       <c r="I13" s="19">
-        <v>2.0206458656108039</v>
+        <v>2.19</v>
       </c>
       <c r="J13" s="19">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="K13" s="19">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="L13" s="19">
-        <v>1.239823825275288</v>
+        <v>1.307766533333333</v>
       </c>
       <c r="M13" s="20">
-        <v>46</v>
-      </c>
-      <c r="N13" s="31"/>
-    </row>
-    <row r="14" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" s="4">
-        <v>22.3</v>
+        <v>23.8</v>
       </c>
       <c r="E14" s="4">
-        <v>22.317663291018839</v>
+        <v>24.20470515697836</v>
       </c>
       <c r="F14" s="4">
-        <v>4.1138787246723716</v>
+        <v>4.7176107589933221</v>
       </c>
       <c r="G14" s="4">
-        <v>31.170894380583221</v>
+        <v>34.308126543182198</v>
       </c>
       <c r="H14" s="4">
-        <v>9.75</v>
+        <v>8</v>
       </c>
       <c r="I14" s="4">
-        <v>27.1</v>
+        <v>29.72</v>
       </c>
       <c r="J14" s="4">
-        <v>24.9</v>
+        <v>26.35</v>
       </c>
       <c r="K14" s="4">
-        <v>20.195</v>
+        <v>21.717590944072722</v>
       </c>
       <c r="L14" s="4">
-        <v>17.335276022895759</v>
+        <v>20.052833678439871</v>
       </c>
       <c r="M14" s="5">
         <v>43</v>
       </c>
-      <c r="N14" s="31"/>
-    </row>
-    <row r="15" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B15" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D15" s="19">
-        <v>15.4</v>
+        <v>16.991709420688782</v>
       </c>
       <c r="E15" s="19">
-        <v>14.967614366651491</v>
+        <v>16.805497071043721</v>
       </c>
       <c r="F15" s="19">
-        <v>4.0487297666120048</v>
+        <v>5.1232034741216923</v>
       </c>
       <c r="G15" s="19">
-        <v>22.31</v>
+        <v>31.535102105975671</v>
       </c>
       <c r="H15" s="19">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="I15" s="19">
-        <v>19.526</v>
+        <v>22.12</v>
       </c>
       <c r="J15" s="19">
-        <v>17.850000000000001</v>
+        <v>20</v>
       </c>
       <c r="K15" s="19">
-        <v>12.3</v>
+        <v>13.362500000000001</v>
       </c>
       <c r="L15" s="19">
-        <v>9.6003218080532928</v>
+        <v>10.81441352833294</v>
       </c>
       <c r="M15" s="20">
-        <v>37</v>
-      </c>
-      <c r="N15" s="31"/>
-    </row>
-    <row r="16" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>36</v>
       </c>
@@ -2338,38 +2322,37 @@
         <v>16</v>
       </c>
       <c r="D16" s="4">
-        <v>26.05</v>
+        <v>29.12968726072387</v>
       </c>
       <c r="E16" s="4">
-        <v>25.70488805516392</v>
+        <v>29.364780840856799</v>
       </c>
       <c r="F16" s="4">
-        <v>3.4794579506547532</v>
+        <v>3.6426105368490691</v>
       </c>
       <c r="G16" s="4">
-        <v>32.986836814213859</v>
+        <v>37.052619716606607</v>
       </c>
       <c r="H16" s="4">
-        <v>14.7</v>
+        <v>15.8</v>
       </c>
       <c r="I16" s="4">
-        <v>29.6</v>
+        <v>33.650000000000013</v>
       </c>
       <c r="J16" s="4">
-        <v>27.225000000000001</v>
+        <v>31.880119821641511</v>
       </c>
       <c r="K16" s="4">
-        <v>23.532499999999999</v>
+        <v>27.131255506987049</v>
       </c>
       <c r="L16" s="4">
-        <v>21.85</v>
+        <v>26.31189266958857</v>
       </c>
       <c r="M16" s="5">
         <v>46</v>
       </c>
-      <c r="N16" s="31"/>
-    </row>
-    <row r="17" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B17" s="21" t="s">
         <v>37</v>
       </c>
@@ -2377,77 +2360,75 @@
         <v>17</v>
       </c>
       <c r="D17" s="19">
-        <v>16.399999999999999</v>
+        <v>19.325995936541691</v>
       </c>
       <c r="E17" s="19">
-        <v>15.914471236690369</v>
+        <v>18.277515791214679</v>
       </c>
       <c r="F17" s="19">
-        <v>4.5382144965834073</v>
+        <v>5.3529968106177064</v>
       </c>
       <c r="G17" s="19">
-        <v>24.750505320674971</v>
+        <v>27.271455363129409</v>
       </c>
       <c r="H17" s="19">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I17" s="19">
-        <v>20.66</v>
+        <v>24.66</v>
       </c>
       <c r="J17" s="19">
-        <v>18.881564821910452</v>
+        <v>21.57732040147167</v>
       </c>
       <c r="K17" s="19">
-        <v>13.2</v>
+        <v>14.695068221793109</v>
       </c>
       <c r="L17" s="19">
-        <v>10.5558739118802</v>
+        <v>12.10568965372936</v>
       </c>
       <c r="M17" s="20">
         <v>43</v>
       </c>
-      <c r="N17" s="31"/>
-    </row>
-    <row r="18" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="D18" s="4">
-        <v>11.175483747833381</v>
+        <v>12.7</v>
       </c>
       <c r="E18" s="4">
-        <v>11.252417067295321</v>
+        <v>12.51903116629969</v>
       </c>
       <c r="F18" s="4">
-        <v>3.610276168705477</v>
+        <v>4.6491516261838406</v>
       </c>
       <c r="G18" s="4">
-        <v>18.7</v>
+        <v>24.34266665422302</v>
       </c>
       <c r="H18" s="4">
         <v>2.4</v>
       </c>
       <c r="I18" s="4">
-        <v>15.28</v>
+        <v>17.8</v>
       </c>
       <c r="J18" s="4">
-        <v>13.675000000000001</v>
+        <v>15</v>
       </c>
       <c r="K18" s="4">
-        <v>8.8036425848144226</v>
+        <v>9.4</v>
       </c>
       <c r="L18" s="4">
-        <v>7.1353047112875094</v>
+        <v>6.7232687565027014</v>
       </c>
       <c r="M18" s="5">
-        <v>34</v>
-      </c>
-      <c r="N18" s="31"/>
-    </row>
-    <row r="21" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B21" s="14" t="s">
         <v>18</v>
       </c>
@@ -2463,7 +2444,7 @@
       <c r="L21" s="14"/>
       <c r="M21" s="15"/>
     </row>
-    <row r="22" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B22" s="16" t="s">
         <v>1</v>
       </c>
@@ -2501,358 +2482,349 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B23" s="17">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="19">
-        <v>2.477906852987577</v>
+        <v>2.872034455593615</v>
       </c>
       <c r="E23" s="19">
-        <v>2.4837276475093888</v>
+        <v>2.8507090935547921</v>
       </c>
       <c r="F23" s="19">
-        <v>0.29138896983624851</v>
+        <v>0.35875504816816228</v>
       </c>
       <c r="G23" s="19">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="H23" s="19">
-        <v>1.794327385678506</v>
+        <v>1.74</v>
       </c>
       <c r="I23" s="19">
-        <v>2.8719999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="J23" s="19">
+        <v>3.0975000000000001</v>
+      </c>
+      <c r="K23" s="19">
         <v>2.7</v>
       </c>
-      <c r="K23" s="19">
-        <v>2.4</v>
-      </c>
       <c r="L23" s="19">
-        <v>2.1160000000000001</v>
+        <v>2.4270320962481091</v>
       </c>
       <c r="M23" s="20">
         <v>38</v>
       </c>
-      <c r="N23" s="31"/>
-    </row>
-    <row r="24" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B24" s="2">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="4">
-        <v>2.3689708250394399</v>
+        <v>2.423835035366698</v>
       </c>
       <c r="E24" s="4">
-        <v>2.35363873610802</v>
+        <v>2.4731122288819232</v>
       </c>
       <c r="F24" s="4">
-        <v>0.29285145517973882</v>
+        <v>0.32744965717700708</v>
       </c>
       <c r="G24" s="4">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="H24" s="4">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="I24" s="4">
-        <v>2.7496</v>
+        <v>2.8210407240276578</v>
       </c>
       <c r="J24" s="4">
-        <v>2.5876797044388038</v>
+        <v>2.6949999999999998</v>
       </c>
       <c r="K24" s="4">
-        <v>2.125</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="L24" s="4">
-        <v>1.999223018513276</v>
+        <v>2.0880000000000001</v>
       </c>
       <c r="M24" s="5">
         <v>38</v>
       </c>
-      <c r="N24" s="31"/>
-    </row>
-    <row r="25" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B25" s="17">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="19">
-        <v>2.1425000000000001</v>
+        <v>2.2144258723347319</v>
       </c>
       <c r="E25" s="19">
-        <v>2.104251523861274</v>
+        <v>2.2257270296275031</v>
       </c>
       <c r="F25" s="19">
-        <v>0.28871334798553261</v>
+        <v>0.36215394711807902</v>
       </c>
       <c r="G25" s="19">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="H25" s="19">
-        <v>1.3669819631023701</v>
+        <v>1.3969062933345391</v>
       </c>
       <c r="I25" s="19">
-        <v>2.4</v>
+        <v>2.6355</v>
       </c>
       <c r="J25" s="19">
-        <v>2.25860396909713</v>
+        <v>2.5</v>
       </c>
       <c r="K25" s="19">
-        <v>1.9892782112109599</v>
+        <v>1.9624999999999999</v>
       </c>
       <c r="L25" s="19">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="M25" s="20">
         <v>38</v>
       </c>
-      <c r="N25" s="31"/>
-    </row>
-    <row r="26" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B26" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="4">
-        <v>1.823510666242967</v>
+        <v>2.0303797468354432</v>
       </c>
       <c r="E26" s="4">
-        <v>1.8995197815586871</v>
+        <v>2.038900710476351</v>
       </c>
       <c r="F26" s="4">
-        <v>0.31237314100071578</v>
+        <v>0.34740297760476058</v>
       </c>
       <c r="G26" s="4">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="H26" s="4">
-        <v>1.1527769732256361</v>
+        <v>1.18451780858147</v>
       </c>
       <c r="I26" s="4">
-        <v>2.3149999999999999</v>
+        <v>2.5030000000000001</v>
       </c>
       <c r="J26" s="4">
-        <v>2.1522940066364931</v>
+        <v>2.2528125000000001</v>
       </c>
       <c r="K26" s="4">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="L26" s="4">
-        <v>1.573</v>
+        <v>1.6850000000000001</v>
       </c>
       <c r="M26" s="5">
         <v>38</v>
       </c>
-      <c r="N26" s="31"/>
-    </row>
-    <row r="27" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B27" s="17">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C27" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="19">
-        <v>1.75</v>
+        <v>1.9799325218053561</v>
       </c>
       <c r="E27" s="19">
-        <v>1.741965425712545</v>
+        <v>1.958729365302746</v>
       </c>
       <c r="F27" s="19">
-        <v>0.27090944028431713</v>
+        <v>0.35642225562030672</v>
       </c>
       <c r="G27" s="19">
-        <v>2.37</v>
+        <v>2.8</v>
       </c>
       <c r="H27" s="19">
-        <v>1.2117514759902039</v>
+        <v>1.2373331071824469</v>
       </c>
       <c r="I27" s="19">
-        <v>2.125986578598285</v>
+        <v>2.4</v>
       </c>
       <c r="J27" s="19">
-        <v>1.8885465722278461</v>
+        <v>2.1946093750000002</v>
       </c>
       <c r="K27" s="19">
-        <v>1.6</v>
+        <v>1.640737315274253</v>
       </c>
       <c r="L27" s="19">
-        <v>1.4175</v>
+        <v>1.593462425550719</v>
       </c>
       <c r="M27" s="20">
         <v>38</v>
       </c>
-      <c r="N27" s="31"/>
-    </row>
-    <row r="28" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B28" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D28" s="4">
-        <v>1.6</v>
+        <v>1.8287186804502349</v>
       </c>
       <c r="E28" s="4">
-        <v>1.646774311468802</v>
+        <v>1.8296357958686249</v>
       </c>
       <c r="F28" s="4">
-        <v>0.28686054028793029</v>
+        <v>0.31659281765883979</v>
       </c>
       <c r="G28" s="4">
-        <v>2.2200000000000002</v>
+        <v>2.3799756884428742</v>
       </c>
       <c r="H28" s="4">
-        <v>0.92441227673873994</v>
+        <v>1.1676914887176051</v>
       </c>
       <c r="I28" s="4">
-        <v>2.009037967917946</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J28" s="4">
-        <v>1.8</v>
+        <v>2.0465742838551768</v>
       </c>
       <c r="K28" s="4">
-        <v>1.425</v>
+        <v>1.5844742143586441</v>
       </c>
       <c r="L28" s="4">
-        <v>1.396662781930472</v>
+        <v>1.4350000000000001</v>
       </c>
       <c r="M28" s="5">
         <v>38</v>
       </c>
-      <c r="N28" s="31"/>
-    </row>
-    <row r="29" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B29" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D29" s="19">
-        <v>1.5874999999999999</v>
+        <v>1.7692280427854341</v>
       </c>
       <c r="E29" s="19">
-        <v>1.576243981054871</v>
+        <v>1.75289730910135</v>
       </c>
       <c r="F29" s="19">
-        <v>0.26790998299468138</v>
+        <v>0.34088929644651128</v>
       </c>
       <c r="G29" s="19">
-        <v>2.12</v>
+        <v>2.54</v>
       </c>
       <c r="H29" s="19">
-        <v>0.82445672886766097</v>
+        <v>1.0221038174869419</v>
       </c>
       <c r="I29" s="19">
-        <v>1.9572491708293309</v>
+        <v>2.1244958324462062</v>
       </c>
       <c r="J29" s="19">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="K29" s="19">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="L29" s="19">
         <v>1.3</v>
       </c>
       <c r="M29" s="20">
-        <v>38</v>
-      </c>
-      <c r="N29" s="31"/>
-    </row>
-    <row r="30" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D30" s="4">
-        <v>21.85954688792685</v>
+        <v>23.6</v>
       </c>
       <c r="E30" s="4">
-        <v>21.762390424188389</v>
+        <v>23.88263961109234</v>
       </c>
       <c r="F30" s="4">
-        <v>3.485872450384754</v>
+        <v>4.0612835450691458</v>
       </c>
       <c r="G30" s="4">
-        <v>29.75</v>
+        <v>32.380058403899213</v>
       </c>
       <c r="H30" s="4">
-        <v>15.3</v>
+        <v>17.5</v>
       </c>
       <c r="I30" s="4">
-        <v>26.39427710685078</v>
+        <v>29.281373385152929</v>
       </c>
       <c r="J30" s="4">
-        <v>23.765000000000001</v>
+        <v>26.375</v>
       </c>
       <c r="K30" s="4">
-        <v>18.839219290503241</v>
+        <v>20.808301933471871</v>
       </c>
       <c r="L30" s="4">
-        <v>18.024082764395441</v>
+        <v>18.829889747662669</v>
       </c>
       <c r="M30" s="5">
-        <v>36</v>
-      </c>
-      <c r="N30" s="31"/>
-    </row>
-    <row r="31" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B31" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D31" s="19">
-        <v>14.63954773085891</v>
+        <v>17.220292073826851</v>
       </c>
       <c r="E31" s="19">
-        <v>14.50346868835188</v>
+        <v>16.41716855058867</v>
       </c>
       <c r="F31" s="19">
-        <v>4.1138390728911354</v>
+        <v>5.2807967693305189</v>
       </c>
       <c r="G31" s="19">
-        <v>21.28</v>
+        <v>30.843477381352709</v>
       </c>
       <c r="H31" s="19">
-        <v>2.2999999999999998</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="I31" s="19">
-        <v>19.658000000000001</v>
+        <v>21.96</v>
       </c>
       <c r="J31" s="19">
-        <v>17.45</v>
+        <v>19</v>
       </c>
       <c r="K31" s="19">
-        <v>11.60303928564665</v>
+        <v>13.84614584526742</v>
       </c>
       <c r="L31" s="19">
-        <v>9.4614411027304222</v>
+        <v>9.9590577130974793</v>
       </c>
       <c r="M31" s="20">
-        <v>34</v>
-      </c>
-      <c r="N31" s="31"/>
-    </row>
-    <row r="32" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
         <v>36</v>
       </c>
@@ -2860,38 +2832,37 @@
         <v>16</v>
       </c>
       <c r="D32" s="4">
-        <v>24.35</v>
+        <v>29.81683067285206</v>
       </c>
       <c r="E32" s="4">
-        <v>24.63846045001798</v>
+        <v>28.957544802450379</v>
       </c>
       <c r="F32" s="4">
-        <v>3.187320720973843</v>
+        <v>3.2531307834270189</v>
       </c>
       <c r="G32" s="4">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H32" s="4">
-        <v>16.899999999999999</v>
+        <v>23.7</v>
       </c>
       <c r="I32" s="4">
-        <v>28.216112439309288</v>
+        <v>33.06</v>
       </c>
       <c r="J32" s="4">
-        <v>26.774407242118318</v>
+        <v>31.126465259270621</v>
       </c>
       <c r="K32" s="4">
-        <v>22.606830705893351</v>
+        <v>26.188176926638029</v>
       </c>
       <c r="L32" s="4">
-        <v>21.007000000000001</v>
+        <v>24.925000000000001</v>
       </c>
       <c r="M32" s="5">
         <v>38</v>
       </c>
-      <c r="N32" s="31"/>
-    </row>
-    <row r="33" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B33" s="21" t="s">
         <v>37</v>
       </c>
@@ -2899,81 +2870,79 @@
         <v>17</v>
       </c>
       <c r="D33" s="19">
-        <v>16</v>
+        <v>19.149999999999999</v>
       </c>
       <c r="E33" s="19">
-        <v>15.689848349933831</v>
+        <v>17.954019455492759</v>
       </c>
       <c r="F33" s="19">
-        <v>4.2414672153580861</v>
+        <v>4.9783208027350296</v>
       </c>
       <c r="G33" s="19">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H33" s="19">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="I33" s="19">
-        <v>20.85</v>
+        <v>23.2</v>
       </c>
       <c r="J33" s="19">
-        <v>18.15533681016991</v>
+        <v>21.024999999999999</v>
       </c>
       <c r="K33" s="19">
-        <v>12.166004798435949</v>
+        <v>14.6675</v>
       </c>
       <c r="L33" s="19">
-        <v>10.93734315190429</v>
+        <v>12.306078571293289</v>
       </c>
       <c r="M33" s="20">
         <v>36</v>
       </c>
-      <c r="N33" s="31"/>
-    </row>
-    <row r="34" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="D34" s="4">
-        <v>10.87824763106341</v>
+        <v>12.2</v>
       </c>
       <c r="E34" s="4">
-        <v>10.896167867398511</v>
+        <v>12.13332791235187</v>
       </c>
       <c r="F34" s="4">
-        <v>3.712339572720587</v>
+        <v>4.6155513647839106</v>
       </c>
       <c r="G34" s="4">
-        <v>18.7</v>
+        <v>24.227691346531159</v>
       </c>
       <c r="H34" s="4">
         <v>1.8</v>
       </c>
       <c r="I34" s="4">
-        <v>14.891</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="J34" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K34" s="4">
-        <v>8.4558770254155053</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="L34" s="4">
-        <v>6.3499471558165421</v>
+        <v>7.3643137767450986</v>
       </c>
       <c r="M34" s="5">
-        <v>32</v>
-      </c>
-      <c r="N34" s="31"/>
-    </row>
-    <row r="36" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B36" s="22"/>
       <c r="C36" s="23"/>
     </row>
-    <row r="37" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B37" s="14" t="s">
         <v>35</v>
       </c>
@@ -2989,7 +2958,7 @@
       <c r="L37" s="14"/>
       <c r="M37" s="15"/>
     </row>
-    <row r="38" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B38" s="24" t="s">
         <v>1</v>
       </c>
@@ -3027,241 +2996,235 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B39" s="7">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="26">
-        <v>31.31800839374284</v>
+        <v>26.8</v>
       </c>
       <c r="E39" s="26">
-        <v>31.67741847608756</v>
+        <v>27.34941001296308</v>
       </c>
       <c r="F39" s="26">
-        <v>1.8207707424563271</v>
-      </c>
-      <c r="G39" s="26">
-        <v>36</v>
-      </c>
-      <c r="H39" s="26">
-        <v>28.928750000000001</v>
-      </c>
-      <c r="I39" s="26">
-        <v>34.5</v>
-      </c>
-      <c r="J39" s="26">
-        <v>32.4</v>
-      </c>
-      <c r="K39" s="26">
-        <v>30.5</v>
-      </c>
-      <c r="L39" s="26">
-        <v>29.359294535703381</v>
+        <v>2.138073578521924</v>
+      </c>
+      <c r="G39" s="4">
+        <v>35</v>
+      </c>
+      <c r="H39" s="4">
+        <v>24.09</v>
+      </c>
+      <c r="I39" s="4">
+        <v>29.99144243493604</v>
+      </c>
+      <c r="J39" s="4">
+        <v>28.390299323313801</v>
+      </c>
+      <c r="K39" s="4">
+        <v>26</v>
+      </c>
+      <c r="L39" s="4">
+        <v>25.80007638888889</v>
       </c>
       <c r="M39" s="8">
-        <v>41</v>
-      </c>
-      <c r="N39" s="31"/>
-    </row>
-    <row r="40" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B40" s="17">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C40" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="27">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E40" s="27">
-        <v>29.975417095304621</v>
+        <v>26.552797460107641</v>
       </c>
       <c r="F40" s="27">
-        <v>2.129459741861206</v>
-      </c>
-      <c r="G40" s="27">
-        <v>35</v>
-      </c>
-      <c r="H40" s="27">
-        <v>24.95511627906977</v>
-      </c>
-      <c r="I40" s="27">
-        <v>32.5</v>
-      </c>
-      <c r="J40" s="27">
-        <v>31</v>
-      </c>
-      <c r="K40" s="27">
-        <v>29</v>
-      </c>
-      <c r="L40" s="27">
+        <v>2.2458940662448539</v>
+      </c>
+      <c r="G40" s="19">
+        <v>32</v>
+      </c>
+      <c r="H40" s="19">
+        <v>20.8</v>
+      </c>
+      <c r="I40" s="19">
+        <v>29.857944504474901</v>
+      </c>
+      <c r="J40" s="19">
         <v>28</v>
       </c>
+      <c r="K40" s="19">
+        <v>25.1175</v>
+      </c>
+      <c r="L40" s="19">
+        <v>24.04</v>
+      </c>
       <c r="M40" s="20">
-        <v>41</v>
-      </c>
-      <c r="N40" s="31"/>
-    </row>
-    <row r="41" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B41" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D41" s="26">
-        <v>28.6</v>
+        <v>25.75</v>
       </c>
       <c r="E41" s="26">
-        <v>28.45942287945606</v>
+        <v>25.89934695158999</v>
       </c>
       <c r="F41" s="26">
-        <v>2.3285674686260038</v>
-      </c>
-      <c r="G41" s="26">
-        <v>33.299999999999997</v>
-      </c>
-      <c r="H41" s="26">
+        <v>2.1909120697033719</v>
+      </c>
+      <c r="G41" s="4">
+        <v>30</v>
+      </c>
+      <c r="H41" s="4">
         <v>20.8</v>
       </c>
-      <c r="I41" s="26">
-        <v>30.6</v>
-      </c>
-      <c r="J41" s="26">
-        <v>30</v>
-      </c>
-      <c r="K41" s="26">
-        <v>27</v>
-      </c>
-      <c r="L41" s="26">
-        <v>26</v>
+      <c r="I41" s="4">
+        <v>28.841446846052051</v>
+      </c>
+      <c r="J41" s="4">
+        <v>27.375</v>
+      </c>
+      <c r="K41" s="4">
+        <v>24.327500000000001</v>
+      </c>
+      <c r="L41" s="4">
+        <v>23.02</v>
       </c>
       <c r="M41" s="5">
-        <v>41</v>
-      </c>
-      <c r="N41" s="31"/>
-    </row>
-    <row r="42" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B42" s="17">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C42" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D42" s="27">
-        <v>27.413545454545449</v>
+        <v>25.9</v>
       </c>
       <c r="E42" s="27">
-        <v>27.311367789039839</v>
+        <v>25.61408595492194</v>
       </c>
       <c r="F42" s="27">
-        <v>2.4910758267036388</v>
-      </c>
-      <c r="G42" s="27">
-        <v>32.1</v>
-      </c>
-      <c r="H42" s="27">
-        <v>20.8</v>
-      </c>
-      <c r="I42" s="27">
-        <v>30</v>
-      </c>
-      <c r="J42" s="27">
-        <v>29.158145745898508</v>
-      </c>
-      <c r="K42" s="27">
-        <v>26</v>
-      </c>
-      <c r="L42" s="27">
-        <v>24.527616279069768</v>
+        <v>2.4044811325923181</v>
+      </c>
+      <c r="G42" s="19">
+        <v>31.246333525991151</v>
+      </c>
+      <c r="H42" s="19">
+        <v>19.5</v>
+      </c>
+      <c r="I42" s="19">
+        <v>28.832446846052051</v>
+      </c>
+      <c r="J42" s="19">
+        <v>27</v>
+      </c>
+      <c r="K42" s="19">
+        <v>24.012499999999999</v>
+      </c>
+      <c r="L42" s="19">
+        <v>22.933072916666671</v>
       </c>
       <c r="M42" s="20">
-        <v>41</v>
-      </c>
-      <c r="N42" s="31"/>
-    </row>
-    <row r="43" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B43" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D43" s="26">
-        <v>26.187413311109701</v>
+        <v>25.055</v>
       </c>
       <c r="E43" s="26">
-        <v>26.248171382352378</v>
+        <v>25.062790122557089</v>
       </c>
       <c r="F43" s="26">
-        <v>2.4956186148875799</v>
-      </c>
-      <c r="G43" s="26">
-        <v>30.4</v>
-      </c>
-      <c r="H43" s="26">
-        <v>19.5</v>
-      </c>
-      <c r="I43" s="26">
-        <v>29</v>
-      </c>
-      <c r="J43" s="26">
-        <v>28.25</v>
-      </c>
-      <c r="K43" s="26">
-        <v>25</v>
-      </c>
-      <c r="L43" s="26">
-        <v>22.908901316935491</v>
+        <v>3.1872245393245739</v>
+      </c>
+      <c r="G43" s="4">
+        <v>32.022042313752323</v>
+      </c>
+      <c r="H43" s="4">
+        <v>16.2</v>
+      </c>
+      <c r="I43" s="4">
+        <v>28.6</v>
+      </c>
+      <c r="J43" s="4">
+        <v>27.130923635711099</v>
+      </c>
+      <c r="K43" s="4">
+        <v>23.15</v>
+      </c>
+      <c r="L43" s="4">
+        <v>21.064313657407411</v>
       </c>
       <c r="M43" s="5">
-        <v>41</v>
-      </c>
-      <c r="N43" s="31"/>
-    </row>
-    <row r="44" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B44" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C44" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D44" s="27">
-        <v>25.48</v>
+        <v>24.94</v>
       </c>
       <c r="E44" s="27">
-        <v>25.401547494422811</v>
+        <v>24.705590121412161</v>
       </c>
       <c r="F44" s="27">
-        <v>2.8029097531801122</v>
-      </c>
-      <c r="G44" s="27">
-        <v>30.2</v>
-      </c>
-      <c r="H44" s="27">
+        <v>3.1596727784866578</v>
+      </c>
+      <c r="G44" s="19">
+        <v>29.769850060587899</v>
+      </c>
+      <c r="H44" s="19">
         <v>16.2</v>
       </c>
-      <c r="I44" s="27">
-        <v>28.5</v>
-      </c>
-      <c r="J44" s="27">
-        <v>27.3</v>
-      </c>
-      <c r="K44" s="27">
-        <v>24.5</v>
-      </c>
-      <c r="L44" s="27">
-        <v>21.5</v>
+      <c r="I44" s="19">
+        <v>28.536000000000001</v>
+      </c>
+      <c r="J44" s="19">
+        <v>27.326168889597771</v>
+      </c>
+      <c r="K44" s="19">
+        <v>22.925000000000001</v>
+      </c>
+      <c r="L44" s="19">
+        <v>20.841563657407409</v>
       </c>
       <c r="M44" s="20">
-        <v>41</v>
-      </c>
-      <c r="N44" s="31"/>
-    </row>
-    <row r="45" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
         <v>14</v>
       </c>
@@ -3269,38 +3232,37 @@
         <v>48</v>
       </c>
       <c r="D45" s="26">
-        <v>22.145</v>
+        <v>22</v>
       </c>
       <c r="E45" s="26">
-        <v>21.588526460464209</v>
+        <v>21.307507522920599</v>
       </c>
       <c r="F45" s="26">
-        <v>4.2567912757716861</v>
-      </c>
-      <c r="G45" s="26">
-        <v>33</v>
-      </c>
-      <c r="H45" s="26">
-        <v>11.2</v>
-      </c>
-      <c r="I45" s="26">
-        <v>25.596</v>
-      </c>
-      <c r="J45" s="26">
-        <v>24.374613697062191</v>
-      </c>
-      <c r="K45" s="26">
+        <v>4.2579501937468907</v>
+      </c>
+      <c r="G45" s="4">
+        <v>29</v>
+      </c>
+      <c r="H45" s="4">
+        <v>10.7</v>
+      </c>
+      <c r="I45" s="4">
+        <v>26.76</v>
+      </c>
+      <c r="J45" s="4">
+        <v>24</v>
+      </c>
+      <c r="K45" s="4">
         <v>19</v>
       </c>
-      <c r="L45" s="26">
-        <v>17</v>
+      <c r="L45" s="4">
+        <v>16.48</v>
       </c>
       <c r="M45" s="5">
-        <v>38</v>
-      </c>
-      <c r="N45" s="31"/>
-    </row>
-    <row r="46" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B46" s="21" t="s">
         <v>36</v>
       </c>
@@ -3308,85 +3270,79 @@
         <v>20</v>
       </c>
       <c r="D46" s="27">
-        <v>24</v>
+        <v>23.4</v>
       </c>
       <c r="E46" s="27">
-        <v>23.22452523011172</v>
+        <v>23.072866933403422</v>
       </c>
       <c r="F46" s="27">
-        <v>4.0315296677751276</v>
-      </c>
-      <c r="G46" s="27">
-        <v>35</v>
-      </c>
-      <c r="H46" s="27">
+        <v>4.0688357887523576</v>
+      </c>
+      <c r="G46" s="19">
+        <v>30</v>
+      </c>
+      <c r="H46" s="19">
         <v>12.7</v>
       </c>
-      <c r="I46" s="27">
-        <v>27</v>
-      </c>
-      <c r="J46" s="27">
-        <v>25.4</v>
-      </c>
-      <c r="K46" s="27">
-        <v>21.4</v>
-      </c>
-      <c r="L46" s="27">
-        <v>18.588691860465119</v>
+      <c r="I46" s="19">
+        <v>27.95</v>
+      </c>
+      <c r="J46" s="19">
+        <v>25.712723911237791</v>
+      </c>
+      <c r="K46" s="19">
+        <v>21.074999999999999</v>
+      </c>
+      <c r="L46" s="19">
+        <v>17.05</v>
       </c>
       <c r="M46" s="20">
-        <v>41</v>
-      </c>
-      <c r="N46" s="31"/>
-    </row>
-    <row r="47" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B47" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D47" s="26">
-        <v>17.25</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="E47" s="26">
-        <v>17.629729189639029</v>
+        <v>18.36167243959375</v>
       </c>
       <c r="F47" s="26">
-        <v>4.1532065265512097</v>
-      </c>
-      <c r="G47" s="26">
-        <v>27</v>
-      </c>
-      <c r="H47" s="26">
-        <v>7</v>
-      </c>
-      <c r="I47" s="26">
+        <v>5.0458306567456814</v>
+      </c>
+      <c r="G47" s="4">
+        <v>29.6</v>
+      </c>
+      <c r="H47" s="4">
+        <v>6.2</v>
+      </c>
+      <c r="I47" s="4">
+        <v>25</v>
+      </c>
+      <c r="J47" s="4">
         <v>22</v>
       </c>
-      <c r="J47" s="26">
-        <v>20.399999999999999</v>
-      </c>
-      <c r="K47" s="26">
+      <c r="K47" s="4">
         <v>15</v>
       </c>
-      <c r="L47" s="26">
-        <v>12.662907967289099</v>
+      <c r="L47" s="4">
+        <v>11.902774908227769</v>
       </c>
       <c r="M47" s="5">
-        <v>37</v>
-      </c>
-      <c r="N47" s="31"/>
-    </row>
-    <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B48" s="22"/>
       <c r="C48" s="23"/>
-      <c r="N48" s="31"/>
-    </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="N49" s="31"/>
-    </row>
-    <row r="50" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B50" s="14" t="s">
         <v>21</v>
       </c>
@@ -3401,9 +3357,8 @@
       <c r="K50" s="14"/>
       <c r="L50" s="14"/>
       <c r="M50" s="15"/>
-      <c r="N50" s="31"/>
-    </row>
-    <row r="51" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B51" s="24" t="s">
         <v>1</v>
       </c>
@@ -3441,241 +3396,235 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B52" s="7">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D52" s="28">
-        <v>1428.7881960142861</v>
+        <v>1420</v>
       </c>
       <c r="E52" s="28">
-        <v>1431.0525849532801</v>
+        <v>1424.951780693922</v>
       </c>
       <c r="F52" s="28">
-        <v>25.212150295418731</v>
+        <v>24.870945476118951</v>
       </c>
       <c r="G52" s="28">
-        <v>1502</v>
+        <v>1514.1</v>
       </c>
       <c r="H52" s="28">
-        <v>1392.4821565838929</v>
+        <v>1389.17</v>
       </c>
       <c r="I52" s="28">
-        <v>1464.0095167857139</v>
+        <v>1454.6346372753601</v>
       </c>
       <c r="J52" s="28">
-        <v>1439.6125130827161</v>
+        <v>1431.402504110066</v>
       </c>
       <c r="K52" s="28">
-        <v>1418.079955306722</v>
+        <v>1410</v>
       </c>
       <c r="L52" s="28">
-        <v>1401.44</v>
+        <v>1402.5074999999999</v>
       </c>
       <c r="M52" s="5">
-        <v>46</v>
-      </c>
-      <c r="N52" s="31"/>
-    </row>
-    <row r="53" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B53" s="17">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C53" s="18" t="s">
         <v>22</v>
       </c>
       <c r="D53" s="29">
-        <v>1451.806710434533</v>
+        <v>1449.176973632419</v>
       </c>
       <c r="E53" s="29">
-        <v>1461.159229716837</v>
+        <v>1452.5170442135641</v>
       </c>
       <c r="F53" s="29">
-        <v>34.028580268127477</v>
+        <v>34.312222118742461</v>
       </c>
       <c r="G53" s="29">
-        <v>1572</v>
+        <v>1551.1141640000001</v>
       </c>
       <c r="H53" s="29">
-        <v>1413</v>
+        <v>1390.83</v>
       </c>
       <c r="I53" s="29">
-        <v>1512.05</v>
+        <v>1493.78</v>
       </c>
       <c r="J53" s="29">
-        <v>1472.272351599951</v>
+        <v>1463.3891522466031</v>
       </c>
       <c r="K53" s="29">
-        <v>1438.9198710859371</v>
+        <v>1430.168677345599</v>
       </c>
       <c r="L53" s="29">
-        <v>1427</v>
+        <v>1417.96</v>
       </c>
       <c r="M53" s="20">
-        <v>46</v>
-      </c>
-      <c r="N53" s="31"/>
-    </row>
-    <row r="54" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B54" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D54" s="28">
-        <v>1474.5287610910509</v>
+        <v>1481</v>
       </c>
       <c r="E54" s="28">
-        <v>1488.6920936626209</v>
+        <v>1480.075003237431</v>
       </c>
       <c r="F54" s="28">
-        <v>43.23239806909455</v>
+        <v>41.329590707650979</v>
       </c>
       <c r="G54" s="28">
-        <v>1627</v>
+        <v>1580</v>
       </c>
       <c r="H54" s="28">
-        <v>1420</v>
+        <v>1395.15</v>
       </c>
       <c r="I54" s="28">
-        <v>1550.073796958151</v>
+        <v>1537.3015733181239</v>
       </c>
       <c r="J54" s="28">
-        <v>1510.3428880383501</v>
+        <v>1500</v>
       </c>
       <c r="K54" s="28">
-        <v>1459.1796634681789</v>
+        <v>1447</v>
       </c>
       <c r="L54" s="28">
-        <v>1442.682573050118</v>
+        <v>1438.0055325799999</v>
       </c>
       <c r="M54" s="5">
-        <v>46</v>
-      </c>
-      <c r="N54" s="31"/>
-    </row>
-    <row r="55" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B55" s="17">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C55" s="18" t="s">
         <v>22</v>
       </c>
       <c r="D55" s="29">
-        <v>1500.0038</v>
+        <v>1503.5116157717389</v>
       </c>
       <c r="E55" s="29">
-        <v>1518.2785208098881</v>
+        <v>1510.592415862031</v>
       </c>
       <c r="F55" s="29">
-        <v>51.91490559526089</v>
+        <v>51.801656882493901</v>
       </c>
       <c r="G55" s="29">
-        <v>1668</v>
+        <v>1664.8959923126081</v>
       </c>
       <c r="H55" s="29">
-        <v>1435</v>
+        <v>1418</v>
       </c>
       <c r="I55" s="29">
-        <v>1598.326010866896</v>
+        <v>1571.0579759845621</v>
       </c>
       <c r="J55" s="29">
-        <v>1544.83</v>
+        <v>1534.52</v>
       </c>
       <c r="K55" s="29">
-        <v>1487.375</v>
+        <v>1476</v>
       </c>
       <c r="L55" s="29">
-        <v>1460.822351273385</v>
+        <v>1453.402671572514</v>
       </c>
       <c r="M55" s="20">
-        <v>46</v>
-      </c>
-      <c r="N55" s="31"/>
-    </row>
-    <row r="56" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B56" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D56" s="28">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="E56" s="28">
-        <v>1550.0516089640751</v>
+        <v>1547.559273125637</v>
       </c>
       <c r="F56" s="28">
-        <v>61.661558533804858</v>
+        <v>62.923625462616549</v>
       </c>
       <c r="G56" s="28">
-        <v>1692</v>
+        <v>1764.090152332587</v>
       </c>
       <c r="H56" s="28">
-        <v>1443</v>
+        <v>1424</v>
       </c>
       <c r="I56" s="28">
-        <v>1636.412810342357</v>
+        <v>1631.8678692166729</v>
       </c>
       <c r="J56" s="28">
-        <v>1604.329511072192</v>
+        <v>1575</v>
       </c>
       <c r="K56" s="28">
-        <v>1507.067888160499</v>
+        <v>1511.2775285550799</v>
       </c>
       <c r="L56" s="28">
-        <v>1480.149954454416</v>
+        <v>1483.1620150373251</v>
       </c>
       <c r="M56" s="5">
-        <v>46</v>
-      </c>
-      <c r="N56" s="31"/>
-    </row>
-    <row r="57" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B57" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C57" s="18" t="s">
         <v>22</v>
       </c>
       <c r="D57" s="29">
-        <v>1564.784724889086</v>
+        <v>1571.7286296972841</v>
       </c>
       <c r="E57" s="29">
-        <v>1580.5509639512759</v>
+        <v>1584.2685703643331</v>
       </c>
       <c r="F57" s="29">
-        <v>68.129624705653711</v>
+        <v>69.586976351397283</v>
       </c>
       <c r="G57" s="29">
-        <v>1745.000945757258</v>
+        <v>1805.4423321935151</v>
       </c>
       <c r="H57" s="29">
-        <v>1449</v>
+        <v>1428</v>
       </c>
       <c r="I57" s="29">
-        <v>1675.504775445942</v>
+        <v>1669.449226601007</v>
       </c>
       <c r="J57" s="29">
-        <v>1640.9594187463131</v>
+        <v>1615.93</v>
       </c>
       <c r="K57" s="29">
-        <v>1530.5844343821441</v>
+        <v>1542.19</v>
       </c>
       <c r="L57" s="29">
-        <v>1503.5562676339521</v>
+        <v>1517.92</v>
       </c>
       <c r="M57" s="20">
-        <v>46</v>
-      </c>
-      <c r="N57" s="31"/>
-    </row>
-    <row r="58" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
         <v>14</v>
       </c>
@@ -3683,38 +3632,37 @@
         <v>49</v>
       </c>
       <c r="D58" s="28">
-        <v>1747.5167264935501</v>
+        <v>1780</v>
       </c>
       <c r="E58" s="28">
-        <v>1744.7571746027611</v>
+        <v>1775.0088003771559</v>
       </c>
       <c r="F58" s="28">
-        <v>113.5117086500322</v>
+        <v>122.2262237331099</v>
       </c>
       <c r="G58" s="28">
-        <v>2041.8</v>
+        <v>2111.6412191657769</v>
       </c>
       <c r="H58" s="28">
-        <v>1470</v>
+        <v>1449</v>
       </c>
       <c r="I58" s="28">
-        <v>1874.596023077396</v>
+        <v>1921.38</v>
       </c>
       <c r="J58" s="28">
-        <v>1791.6875</v>
+        <v>1818.7071308558891</v>
       </c>
       <c r="K58" s="28">
-        <v>1660</v>
+        <v>1692</v>
       </c>
       <c r="L58" s="28">
-        <v>1624.3</v>
+        <v>1646.5439054595431</v>
       </c>
       <c r="M58" s="5">
-        <v>42</v>
-      </c>
-      <c r="N58" s="31"/>
-    </row>
-    <row r="59" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B59" s="21" t="s">
         <v>36</v>
       </c>
@@ -3722,85 +3670,83 @@
         <v>23</v>
       </c>
       <c r="D59" s="29">
-        <v>1706.787480237655</v>
+        <v>1700</v>
       </c>
       <c r="E59" s="29">
-        <v>1709.9712208124861</v>
+        <v>1700.094864090074</v>
       </c>
       <c r="F59" s="29">
-        <v>99.004336572651411</v>
+        <v>103.3069995854829</v>
       </c>
       <c r="G59" s="29">
-        <v>2001.708139775357</v>
+        <v>2052.6534105129131</v>
       </c>
       <c r="H59" s="29">
-        <v>1465</v>
+        <v>1440</v>
       </c>
       <c r="I59" s="29">
-        <v>1828.6723726032501</v>
+        <v>1811.597767438697</v>
       </c>
       <c r="J59" s="29">
-        <v>1759.5225</v>
+        <v>1750</v>
       </c>
       <c r="K59" s="29">
-        <v>1644.116372807176</v>
+        <v>1633.9</v>
       </c>
       <c r="L59" s="29">
-        <v>1607</v>
+        <v>1598.2</v>
       </c>
       <c r="M59" s="20">
-        <v>46</v>
-      </c>
-      <c r="N59" s="31"/>
-    </row>
-    <row r="60" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B60" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B60" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D60" s="28">
-        <v>1955</v>
+        <v>1997</v>
       </c>
       <c r="E60" s="28">
-        <v>1964.422332101954</v>
+        <v>1997.234967786693</v>
       </c>
       <c r="F60" s="28">
-        <v>171.0205500328978</v>
+        <v>188.272263162987</v>
       </c>
       <c r="G60" s="28">
-        <v>2410.04</v>
+        <v>2446.98</v>
       </c>
       <c r="H60" s="28">
-        <v>1498</v>
+        <v>1472</v>
       </c>
       <c r="I60" s="28">
-        <v>2151.192</v>
+        <v>2194.439236821996</v>
       </c>
       <c r="J60" s="28">
-        <v>2083.2249999999999</v>
+        <v>2132.5333686433892</v>
       </c>
       <c r="K60" s="28">
-        <v>1848</v>
+        <v>1889.3904505</v>
       </c>
       <c r="L60" s="28">
-        <v>1769.198538792479</v>
+        <v>1785.476444043964</v>
       </c>
       <c r="M60" s="5">
-        <v>43</v>
-      </c>
-      <c r="N60" s="31"/>
-    </row>
-    <row r="61" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B61" s="22"/>
       <c r="C61" s="23"/>
     </row>
-    <row r="62" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B62" s="22"/>
       <c r="C62" s="23"/>
     </row>
-    <row r="63" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B63" s="14" t="s">
         <v>24</v>
       </c>
@@ -3816,7 +3762,7 @@
       <c r="L63" s="14"/>
       <c r="M63" s="15"/>
     </row>
-    <row r="64" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B64" s="24" t="s">
         <v>1</v>
       </c>
@@ -3854,280 +3800,273 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B65" s="7">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D65" s="28">
-        <v>6820</v>
+        <v>7373.4294707837016</v>
       </c>
       <c r="E65" s="28">
-        <v>6789.3088604406066</v>
+        <v>7389.9565611686467</v>
       </c>
       <c r="F65" s="28">
-        <v>361.33986301635531</v>
+        <v>492.3675050999841</v>
       </c>
       <c r="G65" s="28">
-        <v>7452.4541796272397</v>
+        <v>8549.019280067434</v>
       </c>
       <c r="H65" s="28">
-        <v>6139.7040570999998</v>
+        <v>6592.0293329552451</v>
       </c>
       <c r="I65" s="28">
-        <v>7269.7545162649521</v>
+        <v>7930.9204458632112</v>
       </c>
       <c r="J65" s="28">
-        <v>7090.25</v>
+        <v>7748.0106391172403</v>
       </c>
       <c r="K65" s="28">
-        <v>6557.8975</v>
+        <v>6946.6011050450506</v>
       </c>
       <c r="L65" s="28">
-        <v>6305.84</v>
+        <v>6794.1344082853229</v>
       </c>
       <c r="M65" s="8">
         <v>38</v>
       </c>
-      <c r="N65" s="32"/>
-    </row>
-    <row r="66" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B66" s="17">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C66" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D66" s="29">
-        <v>7358.8279266223217</v>
+        <v>7824.6438280531056</v>
       </c>
       <c r="E66" s="29">
-        <v>7463.2042349255398</v>
+        <v>7887.3326905079639</v>
       </c>
       <c r="F66" s="29">
-        <v>443.89655703708422</v>
+        <v>709.80505217489417</v>
       </c>
       <c r="G66" s="29">
-        <v>8549.019280067434</v>
+        <v>9841</v>
       </c>
       <c r="H66" s="29">
-        <v>6642.3469731900004</v>
+        <v>6599.8592771050289</v>
       </c>
       <c r="I66" s="29">
-        <v>8115.3</v>
+        <v>8558.7083720474293</v>
       </c>
       <c r="J66" s="29">
-        <v>7718.3014166802577</v>
+        <v>8201.75</v>
       </c>
       <c r="K66" s="29">
-        <v>7238.1006594395267</v>
+        <v>7396.8453004800031</v>
       </c>
       <c r="L66" s="29">
-        <v>6835.990237548539</v>
+        <v>7111.7417471532008</v>
       </c>
       <c r="M66" s="20">
         <v>38</v>
       </c>
-      <c r="N66" s="32"/>
-    </row>
-    <row r="67" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="2">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D67" s="28">
-        <v>7841.3930457882552</v>
+        <v>8305</v>
       </c>
       <c r="E67" s="28">
-        <v>7839.1995177765448</v>
+        <v>8394.0163177023005</v>
       </c>
       <c r="F67" s="28">
-        <v>627.61966653473314</v>
+        <v>620.66420750826592</v>
       </c>
       <c r="G67" s="28">
-        <v>9499.5813244242654</v>
+        <v>10280</v>
       </c>
       <c r="H67" s="28">
-        <v>6674.3306841699996</v>
+        <v>7237</v>
       </c>
       <c r="I67" s="28">
-        <v>8584.9</v>
+        <v>9128.7719321759996</v>
       </c>
       <c r="J67" s="28">
-        <v>8094.8401719028107</v>
+        <v>8676.2256909907246</v>
       </c>
       <c r="K67" s="28">
-        <v>7488</v>
+        <v>7993.1065178101699</v>
       </c>
       <c r="L67" s="28">
-        <v>7029.7009762563703</v>
+        <v>7690.0663853193164</v>
       </c>
       <c r="M67" s="5">
         <v>38</v>
       </c>
-      <c r="N67" s="32"/>
-    </row>
-    <row r="68" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B68" s="17">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C68" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D68" s="29">
-        <v>8275.5148378251761</v>
+        <v>8144.3140728156104</v>
       </c>
       <c r="E68" s="29">
-        <v>8350.1784366760821</v>
+        <v>8244.7540727112864</v>
       </c>
       <c r="F68" s="29">
-        <v>619.73923295363068</v>
+        <v>590.79353947816662</v>
       </c>
       <c r="G68" s="29">
-        <v>9612.7787517514171</v>
+        <v>9871.4532105056478</v>
       </c>
       <c r="H68" s="29">
-        <v>7095.18297927</v>
+        <v>7145.3659300725603</v>
       </c>
       <c r="I68" s="29">
-        <v>9133.4011750773298</v>
+        <v>8934.4709904721512</v>
       </c>
       <c r="J68" s="29">
-        <v>8868.4721695899534</v>
+        <v>8566.1534069645113</v>
       </c>
       <c r="K68" s="29">
-        <v>8000.5036198541202</v>
+        <v>7914.5745302974537</v>
       </c>
       <c r="L68" s="29">
-        <v>7597.3712259970462</v>
+        <v>7572.1023245412043</v>
       </c>
       <c r="M68" s="20">
         <v>38</v>
       </c>
-      <c r="N68" s="32"/>
-    </row>
-    <row r="69" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B69" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D69" s="28">
-        <v>8115.5</v>
+        <v>8301.1697387125241</v>
       </c>
       <c r="E69" s="28">
-        <v>8149.3262174944211</v>
+        <v>8330.3277629346649</v>
       </c>
       <c r="F69" s="28">
-        <v>524.07919416495781</v>
+        <v>533.84514146992046</v>
       </c>
       <c r="G69" s="28">
-        <v>9871.4532105056478</v>
+        <v>9684.456232295679</v>
       </c>
       <c r="H69" s="28">
-        <v>7275.2606452399996</v>
+        <v>7025.7927983071213</v>
       </c>
       <c r="I69" s="28">
-        <v>8667.4964410407356</v>
+        <v>8967.2487321168664</v>
       </c>
       <c r="J69" s="28">
-        <v>8461.2102208935339</v>
+        <v>8651.5712068978555</v>
       </c>
       <c r="K69" s="28">
-        <v>7843.75</v>
+        <v>7993.2</v>
       </c>
       <c r="L69" s="28">
-        <v>7471.5749999999998</v>
+        <v>7845.2157480786364</v>
       </c>
       <c r="M69" s="5">
         <v>38</v>
       </c>
-      <c r="N69" s="32"/>
-    </row>
-    <row r="70" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B70" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C70" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D70" s="29">
-        <v>8225.653588923411</v>
+        <v>8309.4549927397456</v>
       </c>
       <c r="E70" s="29">
-        <v>8252.4367493986065</v>
+        <v>8302.7115078881561</v>
       </c>
       <c r="F70" s="29">
-        <v>492.49753810195767</v>
+        <v>607.09679252927469</v>
       </c>
       <c r="G70" s="29">
-        <v>9684.456232295679</v>
+        <v>10165.564280137931</v>
       </c>
       <c r="H70" s="29">
-        <v>7000</v>
+        <v>6983.9134992607533</v>
       </c>
       <c r="I70" s="29">
-        <v>8730.8640396315241</v>
+        <v>8941.677119459393</v>
       </c>
       <c r="J70" s="29">
-        <v>8504.9610768315997</v>
+        <v>8594.3392062753373</v>
       </c>
       <c r="K70" s="29">
-        <v>7894.25</v>
+        <v>7912.2497265119382</v>
       </c>
       <c r="L70" s="29">
-        <v>7820.5978766782528</v>
+        <v>7607.8</v>
       </c>
       <c r="M70" s="20">
         <v>38</v>
       </c>
-      <c r="N70" s="32"/>
-    </row>
-    <row r="71" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B71" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D71" s="28">
-        <v>8216.4970172361009</v>
+        <v>8148.5</v>
       </c>
       <c r="E71" s="28">
-        <v>8222.5086615763303</v>
+        <v>8195.434140493162</v>
       </c>
       <c r="F71" s="28">
-        <v>561.04514551071225</v>
+        <v>702.5586086430676</v>
       </c>
       <c r="G71" s="28">
-        <v>10165.564280137931</v>
+        <v>10615.8881347724</v>
       </c>
       <c r="H71" s="28">
-        <v>7000</v>
+        <v>6617.5984820154054</v>
       </c>
       <c r="I71" s="28">
-        <v>8766.8097509001364</v>
+        <v>8855.2451685553078</v>
       </c>
       <c r="J71" s="28">
-        <v>8578.75</v>
+        <v>8506.1150366270376</v>
       </c>
       <c r="K71" s="28">
-        <v>7941.7395862353778</v>
+        <v>7685.6333709856972</v>
       </c>
       <c r="L71" s="28">
-        <v>7751.3772575522626</v>
+        <v>7518.9</v>
       </c>
       <c r="M71" s="5">
         <v>38</v>
       </c>
-      <c r="N71" s="32"/>
-    </row>
-    <row r="72" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B72" s="21" t="s">
         <v>36</v>
       </c>
@@ -4135,38 +4074,37 @@
         <v>25</v>
       </c>
       <c r="D72" s="29">
-        <v>92736.94012581819</v>
+        <v>93235</v>
       </c>
       <c r="E72" s="29">
-        <v>93635.105560844619</v>
+        <v>94019.797084966543</v>
       </c>
       <c r="F72" s="29">
-        <v>4321.4446605068442</v>
+        <v>4550.7093864988319</v>
       </c>
       <c r="G72" s="29">
-        <v>114160.3104429737</v>
+        <v>112857.8562633464</v>
       </c>
       <c r="H72" s="29">
-        <v>87803.121317923462</v>
+        <v>88000</v>
       </c>
       <c r="I72" s="29">
-        <v>97220</v>
+        <v>98963.97207742231</v>
       </c>
       <c r="J72" s="29">
-        <v>94847</v>
+        <v>95410</v>
       </c>
       <c r="K72" s="29">
-        <v>91467</v>
+        <v>91362.223222749861</v>
       </c>
       <c r="L72" s="29">
-        <v>89999.869982060001</v>
+        <v>89741.82486386408</v>
       </c>
       <c r="M72" s="20">
         <v>41</v>
       </c>
-      <c r="N72" s="32"/>
-    </row>
-    <row r="73" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B73" s="6" t="s">
         <v>37</v>
       </c>
@@ -4174,46 +4112,45 @@
         <v>25</v>
       </c>
       <c r="D73" s="28">
-        <v>98463</v>
+        <v>98825</v>
       </c>
       <c r="E73" s="28">
-        <v>98806.987085864443</v>
+        <v>98894.658179882928</v>
       </c>
       <c r="F73" s="28">
-        <v>5160.3993953349009</v>
+        <v>5112.7278890122861</v>
       </c>
       <c r="G73" s="28">
-        <v>119216.8941094664</v>
+        <v>117406.1449877891</v>
       </c>
       <c r="H73" s="28">
-        <v>88920</v>
+        <v>88710</v>
       </c>
       <c r="I73" s="28">
-        <v>102764.9258385946</v>
+        <v>103596.0307354659</v>
       </c>
       <c r="J73" s="28">
-        <v>101196</v>
+        <v>101329</v>
       </c>
       <c r="K73" s="28">
-        <v>96423</v>
+        <v>95610</v>
       </c>
       <c r="L73" s="28">
-        <v>92797.773981626757</v>
+        <v>92627.774220621723</v>
       </c>
       <c r="M73" s="5">
         <v>37</v>
       </c>
-      <c r="N73" s="32"/>
-    </row>
-    <row r="74" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B74" s="22"/>
       <c r="C74" s="23"/>
     </row>
-    <row r="75" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B75" s="22"/>
       <c r="C75" s="23"/>
     </row>
-    <row r="76" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B76" s="14" t="s">
         <v>26</v>
       </c>
@@ -4229,7 +4166,7 @@
       <c r="L76" s="14"/>
       <c r="M76" s="15"/>
     </row>
-    <row r="77" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B77" s="24" t="s">
         <v>1</v>
       </c>
@@ -4267,280 +4204,273 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B78" s="7">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D78" s="28">
-        <v>5826</v>
+        <v>6141.2</v>
       </c>
       <c r="E78" s="28">
-        <v>5768.8232323566017</v>
+        <v>6213.9292690527727</v>
       </c>
       <c r="F78" s="28">
-        <v>446.77070528809548</v>
+        <v>430.60825719241848</v>
       </c>
       <c r="G78" s="28">
-        <v>7135.8667290243693</v>
+        <v>7273.3638476630513</v>
       </c>
       <c r="H78" s="28">
-        <v>5002</v>
+        <v>5440.22</v>
       </c>
       <c r="I78" s="28">
-        <v>6123.5</v>
+        <v>6794.4194139688589</v>
       </c>
       <c r="J78" s="28">
-        <v>5996.0529999999999</v>
+        <v>6462.0857411160596</v>
       </c>
       <c r="K78" s="28">
-        <v>5566.0120435831614</v>
+        <v>5999.9701185081503</v>
       </c>
       <c r="L78" s="28">
-        <v>5115.7291749612341</v>
+        <v>5623.9708713128339</v>
       </c>
       <c r="M78" s="8">
         <v>38</v>
       </c>
-      <c r="N78" s="32"/>
-    </row>
-    <row r="79" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B79" s="17">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C79" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D79" s="29">
-        <v>6311.5</v>
+        <v>6505.7397972849994</v>
       </c>
       <c r="E79" s="29">
-        <v>6339.5151910569248</v>
+        <v>6514.0814980949372</v>
       </c>
       <c r="F79" s="29">
-        <v>454.56265913867628</v>
+        <v>402.88014275233758</v>
       </c>
       <c r="G79" s="29">
-        <v>7640.1492081188362</v>
+        <v>7563</v>
       </c>
       <c r="H79" s="29">
-        <v>5440.2231602957572</v>
+        <v>5700</v>
       </c>
       <c r="I79" s="29">
-        <v>6801.353514840438</v>
+        <v>7009.8198549066065</v>
       </c>
       <c r="J79" s="29">
-        <v>6594.1525050983128</v>
+        <v>6715</v>
       </c>
       <c r="K79" s="29">
-        <v>6041.4762585572907</v>
+        <v>6234.9718282521089</v>
       </c>
       <c r="L79" s="29">
-        <v>5791.9214418741722</v>
+        <v>6019.8148883049871</v>
       </c>
       <c r="M79" s="20">
         <v>38</v>
       </c>
-      <c r="N79" s="32"/>
-    </row>
-    <row r="80" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B80" s="2">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D80" s="28">
-        <v>6500.7788746879123</v>
+        <v>6834.9847165348201</v>
       </c>
       <c r="E80" s="28">
-        <v>6530.5370175144744</v>
+        <v>6877.2217111845557</v>
       </c>
       <c r="F80" s="28">
-        <v>348.30924752557388</v>
+        <v>462.40830679746801</v>
       </c>
       <c r="G80" s="28">
-        <v>7576.2468761207383</v>
+        <v>8003</v>
       </c>
       <c r="H80" s="28">
-        <v>5972.2724099999996</v>
+        <v>6000</v>
       </c>
       <c r="I80" s="28">
-        <v>6951.6495759619856</v>
+        <v>7441.4559701277258</v>
       </c>
       <c r="J80" s="28">
-        <v>6655.1768844756334</v>
+        <v>7105.5433820499211</v>
       </c>
       <c r="K80" s="28">
-        <v>6332.9803378588922</v>
+        <v>6602.1900000000014</v>
       </c>
       <c r="L80" s="28">
-        <v>6118.3</v>
+        <v>6340.8404688355886</v>
       </c>
       <c r="M80" s="5">
         <v>38</v>
       </c>
-      <c r="N80" s="32"/>
-    </row>
-    <row r="81" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B81" s="17">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C81" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D81" s="29">
-        <v>6849.5532937952648</v>
+        <v>6926.0979228841652</v>
       </c>
       <c r="E81" s="29">
-        <v>6898.5799144514913</v>
+        <v>6915.8250956628881</v>
       </c>
       <c r="F81" s="29">
-        <v>438.67106681398928</v>
+        <v>382.68119336842312</v>
       </c>
       <c r="G81" s="29">
-        <v>8301.2622668812437</v>
+        <v>7957</v>
       </c>
       <c r="H81" s="29">
-        <v>6100</v>
+        <v>6200</v>
       </c>
       <c r="I81" s="29">
-        <v>7415.4225492795258</v>
+        <v>7372.8376717201263</v>
       </c>
       <c r="J81" s="29">
-        <v>7149.0334845001253</v>
+        <v>7046</v>
       </c>
       <c r="K81" s="29">
-        <v>6637.8879096173523</v>
+        <v>6668.4313739662948</v>
       </c>
       <c r="L81" s="29">
-        <v>6383.4888346566904</v>
+        <v>6519.6660000000002</v>
       </c>
       <c r="M81" s="20">
         <v>38</v>
       </c>
-      <c r="N81" s="32"/>
-    </row>
-    <row r="82" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B82" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D82" s="28">
-        <v>6891.7730416205286</v>
+        <v>7329.413828288717</v>
       </c>
       <c r="E82" s="28">
-        <v>6923.3583767375567</v>
+        <v>7241.3391405827178</v>
       </c>
       <c r="F82" s="28">
-        <v>400.31716871792162</v>
+        <v>409.80063376535122</v>
       </c>
       <c r="G82" s="28">
-        <v>8136.8805849166347</v>
+        <v>8046</v>
       </c>
       <c r="H82" s="28">
-        <v>6200</v>
+        <v>6300</v>
       </c>
       <c r="I82" s="28">
-        <v>7388.1363158569848</v>
+        <v>7659.6978495190424</v>
       </c>
       <c r="J82" s="28">
-        <v>7066.6966555493509</v>
+        <v>7528.1504019402337</v>
       </c>
       <c r="K82" s="28">
-        <v>6708.2941218988844</v>
+        <v>7002.9471010202624</v>
       </c>
       <c r="L82" s="28">
-        <v>6472.3629428791546</v>
+        <v>6770.0451976759432</v>
       </c>
       <c r="M82" s="5">
         <v>38</v>
       </c>
-      <c r="N82" s="32"/>
-    </row>
-    <row r="83" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B83" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C83" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D83" s="29">
-        <v>7318.5</v>
+        <v>7105.0647535137005</v>
       </c>
       <c r="E83" s="29">
-        <v>7250.7752641430588</v>
+        <v>7104.9214365139351</v>
       </c>
       <c r="F83" s="29">
-        <v>442.69381875811632</v>
+        <v>445.02443761885968</v>
       </c>
       <c r="G83" s="29">
-        <v>8181.5925722602442</v>
+        <v>8065.9103591017974</v>
       </c>
       <c r="H83" s="29">
-        <v>5900</v>
+        <v>6100</v>
       </c>
       <c r="I83" s="29">
-        <v>7706.7801078670336</v>
+        <v>7667.1684182542194</v>
       </c>
       <c r="J83" s="29">
-        <v>7545.6336861224436</v>
+        <v>7315.5371245779679</v>
       </c>
       <c r="K83" s="29">
-        <v>7000</v>
+        <v>6922.25</v>
       </c>
       <c r="L83" s="29">
-        <v>6721.3119347614802</v>
+        <v>6555.6662104469997</v>
       </c>
       <c r="M83" s="20">
         <v>38</v>
       </c>
-      <c r="N83" s="32"/>
-    </row>
-    <row r="84" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B84" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D84" s="28">
-        <v>7152.796565866769</v>
+        <v>7322.5173998828859</v>
       </c>
       <c r="E84" s="28">
-        <v>7114.1741412359452</v>
+        <v>7235.8252554080036</v>
       </c>
       <c r="F84" s="28">
-        <v>487.02598104844969</v>
+        <v>540.37431961517586</v>
       </c>
       <c r="G84" s="28">
-        <v>7943.6201748847679</v>
+        <v>8204.8018404735867</v>
       </c>
       <c r="H84" s="28">
-        <v>5800</v>
+        <v>5900</v>
       </c>
       <c r="I84" s="28">
-        <v>7723.6639972649782</v>
+        <v>7873.9820601273077</v>
       </c>
       <c r="J84" s="28">
-        <v>7400.7250000000004</v>
+        <v>7569.7687328486873</v>
       </c>
       <c r="K84" s="28">
-        <v>6843.3927992909476</v>
+        <v>6856.6356100896955</v>
       </c>
       <c r="L84" s="28">
-        <v>6456.1976321958491</v>
+        <v>6584.1617612913651</v>
       </c>
       <c r="M84" s="5">
         <v>38</v>
       </c>
-      <c r="N84" s="32"/>
-    </row>
-    <row r="85" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B85" s="21" t="s">
         <v>36</v>
       </c>
@@ -4548,38 +4478,37 @@
         <v>25</v>
       </c>
       <c r="D85" s="29">
-        <v>80203.858560367691</v>
+        <v>79120.991314693369</v>
       </c>
       <c r="E85" s="29">
-        <v>79972.09667408622</v>
+        <v>79224.573811124952</v>
       </c>
       <c r="F85" s="29">
-        <v>3087.420661986449</v>
+        <v>3488.4377876049448</v>
       </c>
       <c r="G85" s="29">
-        <v>87847.401871401438</v>
+        <v>86280</v>
       </c>
       <c r="H85" s="29">
-        <v>73488.254769533334</v>
+        <v>70844</v>
       </c>
       <c r="I85" s="29">
-        <v>83199.899503048509</v>
+        <v>83288.338600443691</v>
       </c>
       <c r="J85" s="29">
-        <v>81700</v>
+        <v>81000</v>
       </c>
       <c r="K85" s="29">
-        <v>77999</v>
+        <v>77443.599366499984</v>
       </c>
       <c r="L85" s="29">
-        <v>75374</v>
+        <v>75000</v>
       </c>
       <c r="M85" s="20">
         <v>41</v>
       </c>
-      <c r="N85" s="32"/>
-    </row>
-    <row r="86" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B86" s="6" t="s">
         <v>37</v>
       </c>
@@ -4587,38 +4516,37 @@
         <v>25</v>
       </c>
       <c r="D86" s="28">
-        <v>85199</v>
+        <v>85000</v>
       </c>
       <c r="E86" s="28">
-        <v>85647.318123030709</v>
+        <v>84573.421361730521</v>
       </c>
       <c r="F86" s="28">
-        <v>4983.2277380503247</v>
+        <v>5260.5251158121418</v>
       </c>
       <c r="G86" s="28">
-        <v>97155.108229308855</v>
+        <v>94510</v>
       </c>
       <c r="H86" s="28">
-        <v>75328.427326754027</v>
+        <v>69250</v>
       </c>
       <c r="I86" s="28">
-        <v>92668.804619915682</v>
+        <v>91395.187858085279</v>
       </c>
       <c r="J86" s="28">
-        <v>88092</v>
+        <v>87000</v>
       </c>
       <c r="K86" s="28">
-        <v>82679</v>
+        <v>82695</v>
       </c>
       <c r="L86" s="28">
-        <v>79772.399999999994</v>
+        <v>78582</v>
       </c>
       <c r="M86" s="5">
         <v>37</v>
       </c>
-      <c r="N86" s="32"/>
-    </row>
-    <row r="87" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B87" s="9"/>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
@@ -4632,7 +4560,7 @@
       <c r="L87" s="10"/>
       <c r="M87" s="10"/>
     </row>
-    <row r="89" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B89" s="14" t="s">
         <v>27</v>
       </c>
@@ -4648,7 +4576,7 @@
       <c r="L89" s="14"/>
       <c r="M89" s="15"/>
     </row>
-    <row r="90" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B90" s="24" t="s">
         <v>1</v>
       </c>
@@ -4686,7 +4614,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B91" s="21" t="s">
         <v>36</v>
       </c>
@@ -4694,38 +4622,37 @@
         <v>28</v>
       </c>
       <c r="D91" s="29">
-        <v>16080</v>
+        <v>16000</v>
       </c>
       <c r="E91" s="29">
-        <v>15598.66416189245</v>
+        <v>15661.112283935619</v>
       </c>
       <c r="F91" s="29">
-        <v>2139.8807089270722</v>
+        <v>2337.594735785749</v>
       </c>
       <c r="G91" s="29">
-        <v>19000</v>
+        <v>21056</v>
       </c>
       <c r="H91" s="29">
         <v>9000</v>
       </c>
       <c r="I91" s="29">
-        <v>17729.77867516558</v>
+        <v>17968.029600000002</v>
       </c>
       <c r="J91" s="29">
-        <v>16892.570425442162</v>
+        <v>16861.58611150815</v>
       </c>
       <c r="K91" s="29">
-        <v>14905</v>
+        <v>14874</v>
       </c>
       <c r="L91" s="29">
-        <v>12564.04388456352</v>
+        <v>11927</v>
       </c>
       <c r="M91" s="20">
-        <v>40</v>
-      </c>
-      <c r="N91" s="31"/>
-    </row>
-    <row r="92" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="92" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B92" s="6" t="s">
         <v>37</v>
       </c>
@@ -4733,38 +4660,37 @@
         <v>28</v>
       </c>
       <c r="D92" s="28">
-        <v>19740.016994455451</v>
+        <v>19950</v>
       </c>
       <c r="E92" s="28">
-        <v>18839.581270077269</v>
+        <v>18779.39801059278</v>
       </c>
       <c r="F92" s="28">
-        <v>3444.6313240200229</v>
+        <v>3617.8658809494559</v>
       </c>
       <c r="G92" s="28">
-        <v>23566.04</v>
+        <v>23064</v>
       </c>
       <c r="H92" s="28">
         <v>5000</v>
       </c>
       <c r="I92" s="28">
-        <v>21755.682233610121</v>
+        <v>22291.824228030058</v>
       </c>
       <c r="J92" s="28">
-        <v>21018.25</v>
+        <v>20718.75</v>
       </c>
       <c r="K92" s="28">
-        <v>17438.977079300072</v>
+        <v>17583</v>
       </c>
       <c r="L92" s="28">
-        <v>15000</v>
+        <v>14746.6</v>
       </c>
       <c r="M92" s="5">
-        <v>36</v>
-      </c>
-      <c r="N92" s="31"/>
-    </row>
-    <row r="93" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="93" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B93" s="9"/>
       <c r="C93" s="10"/>
       <c r="D93" s="10"/>
@@ -4778,7 +4704,7 @@
       <c r="L93" s="10"/>
       <c r="M93" s="10"/>
     </row>
-    <row r="95" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B95" s="14" t="s">
         <v>29</v>
       </c>
@@ -4794,7 +4720,7 @@
       <c r="L95" s="14"/>
       <c r="M95" s="15"/>
     </row>
-    <row r="96" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B96" s="24" t="s">
         <v>1</v>
       </c>
@@ -4832,7 +4758,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="97" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B97" s="7" t="s">
         <v>38</v>
       </c>
@@ -4840,79 +4766,77 @@
         <v>30</v>
       </c>
       <c r="D97" s="4">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="E97" s="4">
-        <v>6.8023718522159502</v>
+        <v>7.6175248557677797</v>
       </c>
       <c r="F97" s="4">
-        <v>0.3891955647683662</v>
+        <v>0.44041119118483057</v>
       </c>
       <c r="G97" s="4">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="H97" s="4">
-        <v>6.14</v>
+        <v>6.5</v>
       </c>
       <c r="I97" s="4">
-        <v>7.26</v>
+        <v>8.1580000000000013</v>
       </c>
       <c r="J97" s="4">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="K97" s="4">
-        <v>6.6300000000000008</v>
+        <v>7.3989200616030359</v>
       </c>
       <c r="L97" s="4">
-        <v>6.44</v>
+        <v>7.1567793070557864</v>
       </c>
       <c r="M97" s="8">
         <v>35</v>
       </c>
-      <c r="N97" s="31"/>
-    </row>
-    <row r="98" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B98" s="17" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C98" s="18" t="s">
         <v>30</v>
       </c>
       <c r="D98" s="19">
-        <v>7.3</v>
+        <v>7.4597714540951543</v>
       </c>
       <c r="E98" s="19">
-        <v>7.2691858921509542</v>
+        <v>7.454581643810859</v>
       </c>
       <c r="F98" s="19">
-        <v>0.43617611341474422</v>
+        <v>0.53653238622025157</v>
       </c>
       <c r="G98" s="19">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="H98" s="19">
-        <v>6.4</v>
+        <v>6.274548463389519</v>
       </c>
       <c r="I98" s="19">
-        <v>7.77</v>
+        <v>8.1700171544649756</v>
       </c>
       <c r="J98" s="19">
-        <v>7.5</v>
+        <v>7.7925000000000004</v>
       </c>
       <c r="K98" s="19">
-        <v>7.0250000000000004</v>
+        <v>7.1051548217512774</v>
       </c>
       <c r="L98" s="19">
-        <v>6.6261113412660366</v>
+        <v>6.86</v>
       </c>
       <c r="M98" s="20">
         <v>34</v>
       </c>
-      <c r="N98" s="31"/>
-    </row>
-    <row r="99" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B99" s="6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>30</v>
@@ -4921,35 +4845,34 @@
         <v>7.15</v>
       </c>
       <c r="E99" s="4">
-        <v>7.1095290279087724</v>
+        <v>7.159166124393801</v>
       </c>
       <c r="F99" s="4">
-        <v>0.5822696364922666</v>
+        <v>0.6024273319589829</v>
       </c>
       <c r="G99" s="4">
-        <v>8.6999999999999993</v>
+        <v>8.6</v>
       </c>
       <c r="H99" s="4">
-        <v>6.274548463389519</v>
+        <v>5.9985369511645477</v>
       </c>
       <c r="I99" s="4">
-        <v>7.8</v>
+        <v>7.7223176028971006</v>
       </c>
       <c r="J99" s="4">
-        <v>7.5</v>
+        <v>7.5075000000000003</v>
       </c>
       <c r="K99" s="4">
-        <v>6.5475000000000003</v>
+        <v>6.8250000000000002</v>
       </c>
       <c r="L99" s="4">
-        <v>6.4</v>
+        <v>6.46311604048433</v>
       </c>
       <c r="M99" s="5">
         <v>34</v>
       </c>
-      <c r="N99" s="31"/>
-    </row>
-    <row r="100" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B100" s="21" t="s">
         <v>36</v>
       </c>
@@ -4957,77 +4880,75 @@
         <v>31</v>
       </c>
       <c r="D100" s="19">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="E100" s="19">
-        <v>6.8580140960867624</v>
+        <v>7.2605381405330647</v>
       </c>
       <c r="F100" s="19">
-        <v>0.66410542229908653</v>
+        <v>0.74189228030908738</v>
       </c>
       <c r="G100" s="19">
         <v>9</v>
       </c>
       <c r="H100" s="19">
-        <v>5.7</v>
+        <v>5.7167676533114582</v>
       </c>
       <c r="I100" s="19">
-        <v>7.4823821846054202</v>
+        <v>7.9565296545939894</v>
       </c>
       <c r="J100" s="19">
-        <v>7.15</v>
+        <v>7.7</v>
       </c>
       <c r="K100" s="19">
-        <v>6.5299999999999994</v>
+        <v>6.9</v>
       </c>
       <c r="L100" s="19">
-        <v>6.2192846205023464</v>
+        <v>6.330000000000001</v>
       </c>
       <c r="M100" s="20">
-        <v>35</v>
-      </c>
-      <c r="N100" s="31"/>
-    </row>
-    <row r="101" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="101" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B101" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D101" s="4">
-        <v>6.5</v>
+        <v>7.0230618385449306</v>
       </c>
       <c r="E101" s="4">
-        <v>6.6912426032503447</v>
+        <v>7.1267666280723017</v>
       </c>
       <c r="F101" s="4">
-        <v>0.87977999001093021</v>
+        <v>1.087072076713115</v>
       </c>
       <c r="G101" s="4">
         <v>10</v>
       </c>
       <c r="H101" s="4">
-        <v>5.376023903541209</v>
+        <v>5.0678975151484691</v>
       </c>
       <c r="I101" s="4">
-        <v>7.5</v>
+        <v>8.08</v>
       </c>
       <c r="J101" s="4">
-        <v>7.0749999999999993</v>
+        <v>7.64</v>
       </c>
       <c r="K101" s="4">
-        <v>6.2200000000000006</v>
+        <v>6.5</v>
       </c>
       <c r="L101" s="4">
-        <v>5.8</v>
+        <v>5.74</v>
       </c>
       <c r="M101" s="5">
-        <v>34</v>
-      </c>
-      <c r="N101" s="31"/>
-    </row>
-    <row r="102" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="102" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B102" s="9"/>
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
@@ -5041,7 +4962,7 @@
       <c r="L102" s="9"/>
       <c r="M102" s="9"/>
     </row>
-    <row r="104" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B104" s="14" t="s">
         <v>32</v>
       </c>
@@ -5057,7 +4978,7 @@
       <c r="L104" s="14"/>
       <c r="M104" s="15"/>
     </row>
-    <row r="105" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B105" s="24" t="s">
         <v>1</v>
       </c>
@@ -5095,124 +5016,121 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B106" s="17" t="s">
+    <row r="106" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B106" s="21" t="s">
         <v>38</v>
       </c>
       <c r="C106" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D106" s="19">
-        <v>0.7567949337364599</v>
+        <v>1.290491180436337</v>
       </c>
       <c r="E106" s="19">
-        <v>0.71596649246569799</v>
+        <v>1.2235234860201549</v>
       </c>
       <c r="F106" s="19">
-        <v>0.1866747725515136</v>
+        <v>0.46739766137869038</v>
       </c>
       <c r="G106" s="19">
-        <v>1</v>
+        <v>2.271484024092052</v>
       </c>
       <c r="H106" s="19">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="I106" s="19">
-        <v>0.83444912872401877</v>
+        <v>1.784309194955721</v>
       </c>
       <c r="J106" s="19">
+        <v>1.585387299076801</v>
+      </c>
+      <c r="K106" s="19">
         <v>0.8</v>
       </c>
-      <c r="K106" s="19">
-        <v>0.7</v>
-      </c>
       <c r="L106" s="19">
-        <v>0.47326044347827823</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="M106" s="20">
-        <v>38</v>
-      </c>
-      <c r="N106" s="31"/>
-    </row>
-    <row r="107" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="107" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B107" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D107" s="4">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E107" s="4">
-        <v>1.0202757783154679</v>
+        <v>0.77863357224919305</v>
       </c>
       <c r="F107" s="4">
-        <v>0.47510497134427909</v>
+        <v>0.47362986739561952</v>
       </c>
       <c r="G107" s="4">
         <v>2.2000000000000002</v>
       </c>
       <c r="H107" s="4">
-        <v>8.5008923760465649E-2</v>
+        <v>-0.28000000000000003</v>
       </c>
       <c r="I107" s="4">
-        <v>1.6105767590262581</v>
+        <v>1.3</v>
       </c>
       <c r="J107" s="4">
-        <v>1.2904911467065521</v>
+        <v>1.002797734563043</v>
       </c>
       <c r="K107" s="4">
-        <v>0.72499999999999998</v>
+        <v>0.5</v>
       </c>
       <c r="L107" s="4">
-        <v>0.37300000000000011</v>
+        <v>0.27339109477527251</v>
       </c>
       <c r="M107" s="5">
-        <v>38</v>
-      </c>
-      <c r="N107" s="31"/>
-    </row>
-    <row r="108" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B108" s="17" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="108" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B108" s="21" t="s">
+        <v>50</v>
       </c>
       <c r="C108" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D108" s="19">
-        <v>0.93336924515468733</v>
+        <v>0.70176856717751868</v>
       </c>
       <c r="E108" s="19">
-        <v>0.9280191792022523</v>
+        <v>0.67022639902541703</v>
       </c>
       <c r="F108" s="19">
-        <v>0.41177916757644017</v>
+        <v>0.398438606054551</v>
       </c>
       <c r="G108" s="19">
-        <v>2.2000000000000002</v>
+        <v>1.305306133169726</v>
       </c>
       <c r="H108" s="19">
-        <v>0.16659991102225821</v>
+        <v>-0.50915971381411129</v>
       </c>
       <c r="I108" s="19">
-        <v>1.360000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="J108" s="19">
-        <v>1.1000000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="K108" s="19">
-        <v>0.7</v>
+        <v>0.40643674044333888</v>
       </c>
       <c r="L108" s="19">
-        <v>0.38800000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="M108" s="20">
-        <v>38</v>
-      </c>
-      <c r="N108" s="31"/>
-    </row>
-    <row r="109" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="109" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B109" s="6" t="s">
         <v>36</v>
       </c>
@@ -5220,22 +5138,22 @@
         <v>34</v>
       </c>
       <c r="D109" s="4">
-        <v>3.4019209692617269</v>
+        <v>3.3</v>
       </c>
       <c r="E109" s="4">
-        <v>3.3253341782855088</v>
+        <v>3.2372963012560612</v>
       </c>
       <c r="F109" s="4">
-        <v>0.67085302813125136</v>
+        <v>0.66293886197448693</v>
       </c>
       <c r="G109" s="4">
-        <v>5.0178551707368069</v>
+        <v>4.3</v>
       </c>
       <c r="H109" s="4">
-        <v>1.8</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="I109" s="4">
-        <v>4.1409119291826624</v>
+        <v>4.0640000000000001</v>
       </c>
       <c r="J109" s="4">
         <v>3.7</v>
@@ -5244,14 +5162,13 @@
         <v>2.9</v>
       </c>
       <c r="L109" s="4">
-        <v>2.5254574418494911</v>
+        <v>2.706560739196727</v>
       </c>
       <c r="M109" s="5">
-        <v>44</v>
-      </c>
-      <c r="N109" s="31"/>
-    </row>
-    <row r="110" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="110" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B110" s="21" t="s">
         <v>37</v>
       </c>
@@ -5259,40 +5176,39 @@
         <v>34</v>
       </c>
       <c r="D110" s="19">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="E110" s="19">
-        <v>3.1888268870110141</v>
+        <v>3.1211426659240069</v>
       </c>
       <c r="F110" s="19">
-        <v>0.681832643713844</v>
+        <v>0.68057136754235914</v>
       </c>
       <c r="G110" s="19">
-        <v>5.1367219472784109</v>
+        <v>4.5</v>
       </c>
       <c r="H110" s="19">
+        <v>1.6985474026730121</v>
+      </c>
+      <c r="I110" s="19">
+        <v>3.8382977658669928</v>
+      </c>
+      <c r="J110" s="19">
+        <v>3.7</v>
+      </c>
+      <c r="K110" s="19">
+        <v>2.6856562299519511</v>
+      </c>
+      <c r="L110" s="19">
         <v>2</v>
       </c>
-      <c r="I110" s="19">
-        <v>4</v>
-      </c>
-      <c r="J110" s="19">
-        <v>3.5</v>
-      </c>
-      <c r="K110" s="19">
-        <v>2.9</v>
-      </c>
-      <c r="L110" s="19">
-        <v>2.2999999999999998</v>
-      </c>
       <c r="M110" s="20">
-        <v>41</v>
-      </c>
-      <c r="N110" s="31"/>
-    </row>
-    <row r="111" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="111" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B111" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>34</v>
@@ -5301,10 +5217,10 @@
         <v>3.05</v>
       </c>
       <c r="E111" s="4">
-        <v>3.10594605483247</v>
+        <v>3.1257917222901268</v>
       </c>
       <c r="F111" s="4">
-        <v>0.78265271294294125</v>
+        <v>0.7743526756534751</v>
       </c>
       <c r="G111" s="4">
         <v>5</v>
@@ -5313,25 +5229,24 @@
         <v>0.5</v>
       </c>
       <c r="I111" s="4">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="J111" s="4">
-        <v>3.5</v>
+        <v>3.5127268385737831</v>
       </c>
       <c r="K111" s="4">
-        <v>2.873823454092963</v>
+        <v>2.7988234540929628</v>
       </c>
       <c r="L111" s="4">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="M111" s="5">
         <v>32</v>
       </c>
-      <c r="N111" s="31"/>
-    </row>
-    <row r="112" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="112" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B112" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C112" s="10"/>
       <c r="D112" s="10"/>
@@ -5359,11 +5274,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E9156F-0B7F-473C-A470-6ABA7EE18CEE}">
-  <sheetPr codeName="Hoja3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57923761-BB78-4562-94B9-0D392E6CF52E}">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:P98"/>
+  <dimension ref="B2:M98"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.5703125" style="1" customWidth="1"/>
@@ -5376,23 +5291,23 @@
     <col min="13" max="13" width="18.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B2" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-    </row>
-    <row r="3" spans="2:14" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+    </row>
+    <row r="3" spans="2:13" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B3" s="30"/>
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
@@ -5406,11 +5321,11 @@
       <c r="L3" s="30"/>
       <c r="M3" s="30"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="L4" s="12"/>
       <c r="M4" s="13"/>
     </row>
-    <row r="5" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
         <v>0</v>
       </c>
@@ -5426,7 +5341,7 @@
       <c r="L5" s="14"/>
       <c r="M5" s="15"/>
     </row>
-    <row r="6" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B6" s="16" t="s">
         <v>1</v>
       </c>
@@ -5464,319 +5379,311 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B7" s="2">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="4">
-        <v>2.6840820303427431</v>
+        <v>3.0701158267483639</v>
       </c>
       <c r="E7" s="4">
-        <v>2.6404101517137142</v>
+        <v>3.0249999999999999</v>
       </c>
       <c r="F7" s="4">
-        <v>0.16105004162975839</v>
+        <v>0.2123213558184163</v>
       </c>
       <c r="G7" s="4">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="H7" s="4">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="I7" s="4">
-        <v>2.9</v>
+        <v>3.32</v>
       </c>
       <c r="J7" s="4">
-        <v>2.82</v>
+        <v>3.1749999999999998</v>
       </c>
       <c r="K7" s="4">
-        <v>2.6</v>
+        <v>2.912789566870909</v>
       </c>
       <c r="L7" s="4">
-        <v>2.58</v>
+        <v>2.89</v>
       </c>
       <c r="M7" s="5">
         <v>10</v>
       </c>
-      <c r="N7" s="31"/>
-    </row>
-    <row r="8" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="35">
-        <v>46112</v>
-      </c>
-      <c r="C8" s="36" t="s">
+    </row>
+    <row r="8" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="31">
+        <v>46142</v>
+      </c>
+      <c r="C8" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="37">
-        <v>2.5604564311061</v>
-      </c>
-      <c r="E8" s="37">
-        <v>2.5522821555305009</v>
-      </c>
-      <c r="F8" s="37">
-        <v>0.23180065538369521</v>
-      </c>
-      <c r="G8" s="37">
+      <c r="D8" s="33">
+        <v>2.6747149849625291</v>
+      </c>
+      <c r="E8" s="33">
+        <v>2.6749999999999998</v>
+      </c>
+      <c r="F8" s="33">
+        <v>0.19341516474431919</v>
+      </c>
+      <c r="G8" s="33">
+        <v>3</v>
+      </c>
+      <c r="H8" s="33">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I8" s="33">
+        <v>2.82</v>
+      </c>
+      <c r="J8" s="33">
         <v>2.8</v>
       </c>
-      <c r="H8" s="37">
-        <v>2.04</v>
-      </c>
-      <c r="I8" s="37">
-        <v>2.8</v>
-      </c>
-      <c r="J8" s="37">
-        <v>2.7450000000000001</v>
-      </c>
-      <c r="K8" s="37">
-        <v>2.5</v>
-      </c>
-      <c r="L8" s="37">
-        <v>2.3639999999999999</v>
-      </c>
-      <c r="M8" s="38">
+      <c r="K8" s="33">
+        <v>2.5978623872189681</v>
+      </c>
+      <c r="L8" s="33">
+        <v>2.48</v>
+      </c>
+      <c r="M8" s="34">
         <v>10</v>
       </c>
-      <c r="N8" s="31"/>
-    </row>
-    <row r="9" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="4">
-        <v>2.2450277255533631</v>
+        <v>2.5122548589946279</v>
       </c>
       <c r="E9" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.1222674617534809</v>
+      </c>
+      <c r="G9" s="4">
+        <v>2.71</v>
+      </c>
+      <c r="H9" s="4">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F9" s="4">
-        <v>0.23634496287520021</v>
-      </c>
-      <c r="G9" s="4">
-        <v>2.6</v>
-      </c>
-      <c r="H9" s="4">
-        <v>1.78</v>
-      </c>
       <c r="I9" s="4">
-        <v>2.42</v>
+        <v>2.7010000000000001</v>
       </c>
       <c r="J9" s="4">
-        <v>2.3975693138834049</v>
+        <v>2.5150000000000001</v>
       </c>
       <c r="K9" s="4">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="L9" s="4">
-        <v>1.978</v>
+        <v>2.383293730951654</v>
       </c>
       <c r="M9" s="5">
         <v>10</v>
       </c>
-      <c r="N9" s="31"/>
-    </row>
-    <row r="10" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="35">
-        <v>46173</v>
-      </c>
-      <c r="C10" s="36" t="s">
+    </row>
+    <row r="10" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="31">
+        <v>46203</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="37">
-        <v>2.109896623906705</v>
-      </c>
-      <c r="E10" s="37">
-        <v>2.124483119533525</v>
-      </c>
-      <c r="F10" s="37">
-        <v>0.27908877218300759</v>
-      </c>
-      <c r="G10" s="37">
+      <c r="D10" s="33">
+        <v>2.261807248882937</v>
+      </c>
+      <c r="E10" s="33">
+        <v>2.2290362444146892</v>
+      </c>
+      <c r="F10" s="33">
+        <v>0.19543997481865941</v>
+      </c>
+      <c r="G10" s="33">
         <v>2.5099999999999998</v>
       </c>
-      <c r="H10" s="37">
-        <v>1.64</v>
-      </c>
-      <c r="I10" s="37">
-        <v>2.411</v>
-      </c>
-      <c r="J10" s="37">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="K10" s="37">
-        <v>1.925</v>
-      </c>
-      <c r="L10" s="37">
-        <v>1.784</v>
-      </c>
-      <c r="M10" s="38">
+      <c r="H10" s="33">
+        <v>2</v>
+      </c>
+      <c r="I10" s="33">
+        <v>2.5009999999999999</v>
+      </c>
+      <c r="J10" s="33">
+        <v>2.4375</v>
+      </c>
+      <c r="K10" s="33">
+        <v>2.125</v>
+      </c>
+      <c r="L10" s="33">
+        <v>2</v>
+      </c>
+      <c r="M10" s="34">
         <v>10</v>
       </c>
-      <c r="N10" s="31"/>
-    </row>
-    <row r="11" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="4">
-        <v>1.92103443282414</v>
+        <v>2.2503550373156398</v>
       </c>
       <c r="E11" s="4">
-        <v>1.9750000000000001</v>
+        <v>2.3317751865781999</v>
       </c>
       <c r="F11" s="4">
-        <v>0.23285820426730361</v>
+        <v>0.25000896365518732</v>
       </c>
       <c r="G11" s="4">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="H11" s="4">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="I11" s="4">
-        <v>2.121</v>
+        <v>2.5</v>
       </c>
       <c r="J11" s="4">
-        <v>2.067758246181056</v>
+        <v>2.4849999999999999</v>
       </c>
       <c r="K11" s="4">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="L11" s="4">
-        <v>1.5960000000000001</v>
+        <v>1.99</v>
       </c>
       <c r="M11" s="5">
         <v>10</v>
       </c>
-      <c r="N11" s="31"/>
-    </row>
-    <row r="12" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="35">
-        <v>46234</v>
-      </c>
-      <c r="C12" s="36" t="s">
+    </row>
+    <row r="12" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="31">
+        <v>46265</v>
+      </c>
+      <c r="C12" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="37">
-        <v>1.8930021463070481</v>
-      </c>
-      <c r="E12" s="37">
-        <v>1.9</v>
-      </c>
-      <c r="F12" s="37">
-        <v>0.21250330353661601</v>
-      </c>
-      <c r="G12" s="37">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="H12" s="37">
-        <v>1.52</v>
-      </c>
-      <c r="I12" s="37">
-        <v>2.1120193167634329</v>
-      </c>
-      <c r="J12" s="37">
-        <v>2</v>
-      </c>
-      <c r="K12" s="37">
-        <v>1.8225</v>
-      </c>
-      <c r="L12" s="37">
-        <v>1.5920000000000001</v>
-      </c>
-      <c r="M12" s="38">
+      <c r="D12" s="33">
+        <v>1.981237393480539</v>
+      </c>
+      <c r="E12" s="33">
+        <v>2.04</v>
+      </c>
+      <c r="F12" s="33">
+        <v>0.25558376474033889</v>
+      </c>
+      <c r="G12" s="33">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="H12" s="33">
+        <v>1.5</v>
+      </c>
+      <c r="I12" s="33">
+        <v>2.2120000000000002</v>
+      </c>
+      <c r="J12" s="33">
+        <v>2.178093483701347</v>
+      </c>
+      <c r="K12" s="33">
+        <v>1.825</v>
+      </c>
+      <c r="L12" s="33">
+        <v>1.68</v>
+      </c>
+      <c r="M12" s="34">
         <v>10</v>
       </c>
-      <c r="N12" s="31"/>
-    </row>
-    <row r="13" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B13" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="4">
-        <v>1.752287834187068</v>
+        <v>1.9609879349276049</v>
       </c>
       <c r="E13" s="4">
+        <v>2</v>
+      </c>
+      <c r="F13" s="4">
+        <v>0.26982935971678962</v>
+      </c>
+      <c r="G13" s="4">
+        <v>2.42</v>
+      </c>
+      <c r="H13" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="I13" s="4">
+        <v>2.2669999999999999</v>
+      </c>
+      <c r="J13" s="4">
+        <v>2.0849698373190129</v>
+      </c>
+      <c r="K13" s="4">
         <v>1.8</v>
       </c>
-      <c r="F13" s="4">
-        <v>0.25797018499068952</v>
-      </c>
-      <c r="G13" s="4">
-        <v>2.12</v>
-      </c>
-      <c r="H13" s="4">
-        <v>1.4</v>
-      </c>
-      <c r="I13" s="4">
-        <v>2.012</v>
-      </c>
-      <c r="J13" s="4">
-        <v>1.972158756403009</v>
-      </c>
-      <c r="K13" s="4">
-        <v>1.5</v>
-      </c>
       <c r="L13" s="4">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="M13" s="5">
         <v>10</v>
       </c>
-      <c r="N13" s="31"/>
-    </row>
-    <row r="14" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="35" t="s">
+    </row>
+    <row r="14" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="37">
-        <v>25.07119898103975</v>
-      </c>
-      <c r="E14" s="37">
-        <v>24.85</v>
-      </c>
-      <c r="F14" s="37">
-        <v>2.7514996674194792</v>
-      </c>
-      <c r="G14" s="37">
-        <v>30.42</v>
-      </c>
-      <c r="H14" s="37">
-        <v>20.6</v>
-      </c>
-      <c r="I14" s="37">
-        <v>27.431999999999999</v>
-      </c>
-      <c r="J14" s="37">
-        <v>26.392499999999998</v>
-      </c>
-      <c r="K14" s="37">
-        <v>24.05</v>
-      </c>
-      <c r="L14" s="37">
-        <v>21.789790829357791</v>
-      </c>
-      <c r="M14" s="38">
+      <c r="C14" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="33">
+        <v>26.761746881794341</v>
+      </c>
+      <c r="E14" s="33">
+        <v>26.1</v>
+      </c>
+      <c r="F14" s="33">
+        <v>3.4383631252434701</v>
+      </c>
+      <c r="G14" s="33">
+        <v>32.35</v>
+      </c>
+      <c r="H14" s="33">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="I14" s="33">
+        <v>30.055</v>
+      </c>
+      <c r="J14" s="33">
+        <v>29.081066238502551</v>
+      </c>
+      <c r="K14" s="33">
+        <v>25.175000000000001</v>
+      </c>
+      <c r="L14" s="33">
+        <v>23.91888347753985</v>
+      </c>
+      <c r="M14" s="34">
         <v>10</v>
       </c>
-      <c r="N14" s="31"/>
-    </row>
-    <row r="15" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>36</v>
       </c>
@@ -5784,38 +5691,37 @@
         <v>16</v>
       </c>
       <c r="D15" s="4">
-        <v>27.831465949491481</v>
+        <v>31.794117135222351</v>
       </c>
       <c r="E15" s="4">
-        <v>27.15</v>
+        <v>31.91023964328302</v>
       </c>
       <c r="F15" s="4">
-        <v>2.5666655468704529</v>
+        <v>2.589989223533586</v>
       </c>
       <c r="G15" s="4">
-        <v>32.799999999999997</v>
+        <v>35.6</v>
       </c>
       <c r="H15" s="4">
-        <v>23.6</v>
+        <v>27.5</v>
       </c>
       <c r="I15" s="4">
-        <v>29.92</v>
+        <v>34.159999999999997</v>
       </c>
       <c r="J15" s="4">
-        <v>29.5</v>
+        <v>33.555</v>
       </c>
       <c r="K15" s="4">
-        <v>26.85</v>
+        <v>30.650519049243069</v>
       </c>
       <c r="L15" s="4">
-        <v>25.233193545423291</v>
+        <v>27.95</v>
       </c>
       <c r="M15" s="5">
         <v>10</v>
       </c>
-      <c r="N15" s="31"/>
-    </row>
-    <row r="18" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="14" t="s">
         <v>18</v>
       </c>
@@ -5831,7 +5737,7 @@
       <c r="L18" s="14"/>
       <c r="M18" s="15"/>
     </row>
-    <row r="19" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B19" s="16" t="s">
         <v>1</v>
       </c>
@@ -5869,319 +5775,311 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B20" s="2">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="4">
-        <v>2.5115813705975158</v>
+        <v>2.959906891118723</v>
       </c>
       <c r="E20" s="4">
-        <v>2.4929068529875771</v>
+        <v>2.872034455593615</v>
       </c>
       <c r="F20" s="4">
-        <v>0.20373184158730409</v>
+        <v>0.25206429671551078</v>
       </c>
       <c r="G20" s="4">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="H20" s="4">
-        <v>2.2000000000000002</v>
+        <v>2.65</v>
       </c>
       <c r="I20" s="4">
-        <v>2.806</v>
+        <v>3.3</v>
       </c>
       <c r="J20" s="4">
-        <v>2.5775000000000001</v>
+        <v>3.2250000000000001</v>
       </c>
       <c r="K20" s="4">
-        <v>2.4175</v>
+        <v>2.7662499999999999</v>
       </c>
       <c r="L20" s="4">
-        <v>2.2810000000000001</v>
+        <v>2.74</v>
       </c>
       <c r="M20" s="5">
         <v>10</v>
       </c>
-      <c r="N20" s="31"/>
-    </row>
-    <row r="21" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B21" s="35">
-        <v>46112</v>
-      </c>
-      <c r="C21" s="36" t="s">
+    </row>
+    <row r="21" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="31">
+        <v>46142</v>
+      </c>
+      <c r="C21" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="37">
-        <v>2.3277941650078882</v>
-      </c>
-      <c r="E21" s="37">
-        <v>2.3689708250394399</v>
-      </c>
-      <c r="F21" s="37">
-        <v>0.2359994103640928</v>
-      </c>
-      <c r="G21" s="37">
-        <v>2.6</v>
-      </c>
-      <c r="H21" s="37">
-        <v>1.89</v>
-      </c>
-      <c r="I21" s="37">
-        <v>2.573</v>
-      </c>
-      <c r="J21" s="37">
-        <v>2.5</v>
-      </c>
-      <c r="K21" s="37">
-        <v>2.15</v>
-      </c>
-      <c r="L21" s="37">
-        <v>2.0609999999999999</v>
-      </c>
-      <c r="M21" s="38">
+      <c r="D21" s="33">
+        <v>2.6575000000000002</v>
+      </c>
+      <c r="E21" s="33">
+        <v>2.69</v>
+      </c>
+      <c r="F21" s="33">
+        <v>0.34399006768606938</v>
+      </c>
+      <c r="G21" s="33">
+        <v>3.3</v>
+      </c>
+      <c r="H21" s="33">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="I21" s="33">
+        <v>3.0209999999999999</v>
+      </c>
+      <c r="J21" s="33">
+        <v>2.8</v>
+      </c>
+      <c r="K21" s="33">
+        <v>2.40625</v>
+      </c>
+      <c r="L21" s="33">
+        <v>2.2429999999999999</v>
+      </c>
+      <c r="M21" s="34">
         <v>10</v>
       </c>
-      <c r="N21" s="31"/>
-    </row>
-    <row r="22" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B22" s="2">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="4">
-        <v>2.167350040256705</v>
+        <v>2.4849999999999999</v>
       </c>
       <c r="E22" s="4">
-        <v>2.2217502012835242</v>
+        <v>2.5</v>
       </c>
       <c r="F22" s="4">
-        <v>0.27501254484277998</v>
+        <v>0.34304194754836881</v>
       </c>
       <c r="G22" s="4">
-        <v>2.4900000000000002</v>
+        <v>3.1</v>
       </c>
       <c r="H22" s="4">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="I22" s="4">
-        <v>2.4089999999999998</v>
+        <v>2.722</v>
       </c>
       <c r="J22" s="4">
-        <v>2.4</v>
+        <v>2.6512500000000001</v>
       </c>
       <c r="K22" s="4">
-        <v>2</v>
+        <v>2.40625</v>
       </c>
       <c r="L22" s="4">
-        <v>1.8740000000000001</v>
+        <v>2.0310000000000001</v>
       </c>
       <c r="M22" s="5">
         <v>10</v>
       </c>
-      <c r="N22" s="31"/>
-    </row>
-    <row r="23" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B23" s="35">
-        <v>46173</v>
-      </c>
-      <c r="C23" s="36" t="s">
+    </row>
+    <row r="23" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="31">
+        <v>46203</v>
+      </c>
+      <c r="C23" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="37">
-        <v>2.0504725342181991</v>
-      </c>
-      <c r="E23" s="37">
-        <v>2.1348626710909948</v>
-      </c>
-      <c r="F23" s="37">
-        <v>0.31793726227297692</v>
-      </c>
-      <c r="G23" s="37">
-        <v>2.46</v>
-      </c>
-      <c r="H23" s="37">
-        <v>1.51</v>
-      </c>
-      <c r="I23" s="37">
-        <v>2.4195000000000002</v>
-      </c>
-      <c r="J23" s="37">
-        <v>2.2749999999999999</v>
-      </c>
-      <c r="K23" s="37">
-        <v>1.8</v>
-      </c>
-      <c r="L23" s="37">
-        <v>1.726</v>
-      </c>
-      <c r="M23" s="38">
+      <c r="D23" s="33">
+        <v>2.2523749999999998</v>
+      </c>
+      <c r="E23" s="33">
+        <v>2.202500000000001</v>
+      </c>
+      <c r="F23" s="33">
+        <v>0.35176067562572522</v>
+      </c>
+      <c r="G23" s="33">
+        <v>2.9</v>
+      </c>
+      <c r="H23" s="33">
+        <v>1.75</v>
+      </c>
+      <c r="I23" s="33">
+        <v>2.6120000000000001</v>
+      </c>
+      <c r="J23" s="33">
+        <v>2.4946874999999999</v>
+      </c>
+      <c r="K23" s="33">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="L23" s="33">
+        <v>1.84</v>
+      </c>
+      <c r="M23" s="34">
         <v>10</v>
       </c>
-      <c r="N23" s="31"/>
-    </row>
-    <row r="24" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B24" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="4">
-        <v>1.878926654085469</v>
+        <v>2.24134375</v>
       </c>
       <c r="E24" s="4">
-        <v>1.85</v>
+        <v>2.2492187499999998</v>
       </c>
       <c r="F24" s="4">
-        <v>0.28917961158639288</v>
+        <v>0.33494558177670608</v>
       </c>
       <c r="G24" s="4">
-        <v>2.37</v>
+        <v>2.8</v>
       </c>
       <c r="H24" s="4">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
       <c r="I24" s="4">
-        <v>2.2214999999999998</v>
+        <v>2.642500000000001</v>
       </c>
       <c r="J24" s="4">
-        <v>2.0706999056410189</v>
+        <v>2.415</v>
       </c>
       <c r="K24" s="4">
-        <v>1.6775</v>
+        <v>2.0125000000000002</v>
       </c>
       <c r="L24" s="4">
-        <v>1.585</v>
+        <v>1.8819999999999999</v>
       </c>
       <c r="M24" s="5">
         <v>10</v>
       </c>
-      <c r="N24" s="31"/>
-    </row>
-    <row r="25" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="35">
-        <v>46234</v>
-      </c>
-      <c r="C25" s="36" t="s">
+    </row>
+    <row r="25" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B25" s="31">
+        <v>46265</v>
+      </c>
+      <c r="C25" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="37">
-        <v>1.826512655972649</v>
-      </c>
-      <c r="E25" s="37">
-        <v>1.8975</v>
-      </c>
-      <c r="F25" s="37">
-        <v>0.26347127699751438</v>
-      </c>
-      <c r="G25" s="37">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="H25" s="37">
-        <v>1.42</v>
-      </c>
-      <c r="I25" s="37">
-        <v>2.0491139037538399</v>
-      </c>
-      <c r="J25" s="37">
-        <v>2</v>
-      </c>
-      <c r="K25" s="37">
-        <v>1.625</v>
-      </c>
-      <c r="L25" s="37">
-        <v>1.492</v>
-      </c>
-      <c r="M25" s="38">
+      <c r="D25" s="33">
+        <v>2.0261671875</v>
+      </c>
+      <c r="E25" s="33">
+        <v>2.0508359375</v>
+      </c>
+      <c r="F25" s="33">
+        <v>0.2242245781823349</v>
+      </c>
+      <c r="G25" s="33">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="H25" s="33">
+        <v>1.7</v>
+      </c>
+      <c r="I25" s="33">
+        <v>2.3109999999999999</v>
+      </c>
+      <c r="J25" s="33">
+        <v>2.19</v>
+      </c>
+      <c r="K25" s="33">
+        <v>1.8274999999999999</v>
+      </c>
+      <c r="L25" s="33">
+        <v>1.79</v>
+      </c>
+      <c r="M25" s="34">
         <v>10</v>
       </c>
-      <c r="N25" s="31"/>
-    </row>
-    <row r="26" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B26" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="4">
-        <v>1.697060757576752</v>
+        <v>1.9326421093749999</v>
       </c>
       <c r="E26" s="4">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="F26" s="4">
-        <v>0.25989274376605193</v>
+        <v>0.22436469364146391</v>
       </c>
       <c r="G26" s="4">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="H26" s="4">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="I26" s="4">
-        <v>2.012</v>
+        <v>2.074778984375</v>
       </c>
       <c r="J26" s="4">
-        <v>1.931705681825636</v>
+        <v>2</v>
       </c>
       <c r="K26" s="4">
-        <v>1.51875</v>
+        <v>1.7450000000000001</v>
       </c>
       <c r="L26" s="4">
-        <v>1.4</v>
+        <v>1.6950000000000001</v>
       </c>
       <c r="M26" s="5">
         <v>10</v>
       </c>
-      <c r="N26" s="31"/>
-    </row>
-    <row r="27" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="35" t="s">
+    </row>
+    <row r="27" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B27" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" s="37">
-        <v>23.622953297262391</v>
-      </c>
-      <c r="E27" s="37">
-        <v>22.85</v>
-      </c>
-      <c r="F27" s="37">
-        <v>3.9245340281639232</v>
-      </c>
-      <c r="G27" s="37">
-        <v>29.75</v>
-      </c>
-      <c r="H27" s="37">
-        <v>18.8</v>
-      </c>
-      <c r="I27" s="37">
-        <v>29.074999999999999</v>
-      </c>
-      <c r="J27" s="37">
-        <v>26.375</v>
-      </c>
-      <c r="K27" s="37">
-        <v>20.625102841541079</v>
-      </c>
-      <c r="L27" s="37">
-        <v>19.07</v>
-      </c>
-      <c r="M27" s="38">
+      <c r="C27" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="33">
+        <v>27.16702741534662</v>
+      </c>
+      <c r="E27" s="33">
+        <v>27.87</v>
+      </c>
+      <c r="F27" s="33">
+        <v>2.8872798292857071</v>
+      </c>
+      <c r="G27" s="33">
+        <v>31.8</v>
+      </c>
+      <c r="H27" s="33">
+        <v>22.4</v>
+      </c>
+      <c r="I27" s="33">
+        <v>29.82</v>
+      </c>
+      <c r="J27" s="33">
+        <v>29.002575097161749</v>
+      </c>
+      <c r="K27" s="33">
+        <v>25.024999999999999</v>
+      </c>
+      <c r="L27" s="33">
+        <v>24.04415662152546</v>
+      </c>
+      <c r="M27" s="34">
         <v>10</v>
       </c>
-      <c r="N27" s="31"/>
-    </row>
-    <row r="28" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
         <v>36</v>
       </c>
@@ -6189,42 +6087,41 @@
         <v>16</v>
       </c>
       <c r="D28" s="4">
-        <v>26.713803189632799</v>
+        <v>31.86138461124116</v>
       </c>
       <c r="E28" s="4">
-        <v>26.3</v>
+        <v>31.435092383353702</v>
       </c>
       <c r="F28" s="4">
-        <v>3.204250994792381</v>
+        <v>2.188885307012844</v>
       </c>
       <c r="G28" s="4">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H28" s="4">
-        <v>21.7</v>
+        <v>27.8</v>
       </c>
       <c r="I28" s="4">
-        <v>30.65</v>
+        <v>34.909999999999997</v>
       </c>
       <c r="J28" s="4">
-        <v>28.524999999999999</v>
+        <v>33.072500000000012</v>
       </c>
       <c r="K28" s="4">
-        <v>25.103523922245969</v>
+        <v>31.024999999999999</v>
       </c>
       <c r="L28" s="4">
-        <v>22.78</v>
+        <v>29.828295211133721</v>
       </c>
       <c r="M28" s="5">
         <v>10</v>
       </c>
-      <c r="N28" s="31"/>
-    </row>
-    <row r="30" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B30" s="22"/>
       <c r="C30" s="23"/>
     </row>
-    <row r="31" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="14" t="s">
         <v>35</v>
       </c>
@@ -6240,7 +6137,7 @@
       <c r="L31" s="14"/>
       <c r="M31" s="15"/>
     </row>
-    <row r="32" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B32" s="24" t="s">
         <v>1</v>
       </c>
@@ -6278,280 +6175,273 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B33" s="35">
-        <v>46112</v>
-      </c>
-      <c r="C33" s="36" t="s">
+    <row r="33" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B33" s="31">
+        <v>46142</v>
+      </c>
+      <c r="C33" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="37">
-        <v>30.867000000000001</v>
-      </c>
-      <c r="E33" s="37">
-        <v>30.75</v>
-      </c>
-      <c r="F33" s="37">
-        <v>1.105602399900917</v>
-      </c>
-      <c r="G33" s="37">
-        <v>33.1</v>
-      </c>
-      <c r="H33" s="37">
-        <v>29.36</v>
-      </c>
-      <c r="I33" s="37">
-        <v>31.93</v>
-      </c>
-      <c r="J33" s="37">
-        <v>31.465</v>
-      </c>
-      <c r="K33" s="37">
-        <v>30.022500000000001</v>
-      </c>
-      <c r="L33" s="37">
-        <v>29.936</v>
-      </c>
-      <c r="M33" s="38">
+      <c r="D33" s="33">
+        <v>26.780999999999999</v>
+      </c>
+      <c r="E33" s="33">
+        <v>26.75</v>
+      </c>
+      <c r="F33" s="33">
+        <v>0.91192653212854835</v>
+      </c>
+      <c r="G33" s="33">
+        <v>28.96</v>
+      </c>
+      <c r="H33" s="33">
+        <v>26</v>
+      </c>
+      <c r="I33" s="33">
+        <v>27.420999999999999</v>
+      </c>
+      <c r="J33" s="33">
+        <v>27</v>
+      </c>
+      <c r="K33" s="33">
+        <v>26.024999999999999</v>
+      </c>
+      <c r="L33" s="33">
+        <v>26</v>
+      </c>
+      <c r="M33" s="34">
         <v>10</v>
       </c>
-      <c r="N33" s="31"/>
-    </row>
-    <row r="34" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B34" s="2">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="4">
-        <v>29.099</v>
+        <v>26.309000000000001</v>
       </c>
       <c r="E34" s="4">
-        <v>29.2</v>
+        <v>26</v>
       </c>
       <c r="F34" s="4">
-        <v>0.9829146001108694</v>
+        <v>1.194510127393001</v>
       </c>
       <c r="G34" s="4">
-        <v>30.65</v>
+        <v>28.88</v>
       </c>
       <c r="H34" s="4">
-        <v>27.25</v>
+        <v>25</v>
       </c>
       <c r="I34" s="4">
-        <v>30.146000000000001</v>
+        <v>27.277999999999999</v>
       </c>
       <c r="J34" s="4">
-        <v>29.5</v>
+        <v>27</v>
       </c>
       <c r="K34" s="4">
-        <v>28.7</v>
+        <v>25.5</v>
       </c>
       <c r="L34" s="4">
-        <v>27.925000000000001</v>
+        <v>25.099</v>
       </c>
       <c r="M34" s="5">
         <v>10</v>
       </c>
-      <c r="N34" s="31"/>
-    </row>
-    <row r="35" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B35" s="35">
-        <v>46173</v>
-      </c>
-      <c r="C35" s="36" t="s">
+    </row>
+    <row r="35" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B35" s="31">
+        <v>46203</v>
+      </c>
+      <c r="C35" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="D35" s="37">
-        <v>27.573</v>
-      </c>
-      <c r="E35" s="37">
-        <v>27.5</v>
-      </c>
-      <c r="F35" s="37">
-        <v>1.789668187743813</v>
-      </c>
-      <c r="G35" s="37">
-        <v>30.07</v>
-      </c>
-      <c r="H35" s="37">
-        <v>25.11</v>
-      </c>
-      <c r="I35" s="37">
-        <v>29.872</v>
-      </c>
-      <c r="J35" s="37">
-        <v>28.875</v>
-      </c>
-      <c r="K35" s="37">
-        <v>26.5</v>
-      </c>
-      <c r="L35" s="37">
-        <v>25.190999999999999</v>
-      </c>
-      <c r="M35" s="38">
+      <c r="D35" s="33">
+        <v>25.806999999999999</v>
+      </c>
+      <c r="E35" s="33">
+        <v>26</v>
+      </c>
+      <c r="F35" s="33">
+        <v>1.733282371045693</v>
+      </c>
+      <c r="G35" s="33">
+        <v>28.8</v>
+      </c>
+      <c r="H35" s="33">
+        <v>22.97</v>
+      </c>
+      <c r="I35" s="33">
+        <v>27.18</v>
+      </c>
+      <c r="J35" s="33">
+        <v>26.95</v>
+      </c>
+      <c r="K35" s="33">
+        <v>24.625</v>
+      </c>
+      <c r="L35" s="33">
+        <v>23.896999999999998</v>
+      </c>
+      <c r="M35" s="34">
         <v>10</v>
       </c>
-      <c r="N35" s="31"/>
-    </row>
-    <row r="36" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B36" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D36" s="4">
-        <v>26.218</v>
+        <v>25.574999999999999</v>
       </c>
       <c r="E36" s="4">
-        <v>26.5</v>
+        <v>25.25</v>
       </c>
       <c r="F36" s="4">
-        <v>2.5949044084298918</v>
+        <v>1.7099528908390691</v>
       </c>
       <c r="G36" s="4">
-        <v>30.06</v>
+        <v>28.71</v>
       </c>
       <c r="H36" s="4">
-        <v>21.6</v>
+        <v>23</v>
       </c>
       <c r="I36" s="4">
-        <v>29.151</v>
+        <v>27.440999999999999</v>
       </c>
       <c r="J36" s="4">
-        <v>27.75</v>
+        <v>26.75</v>
       </c>
       <c r="K36" s="4">
-        <v>25.125</v>
+        <v>24.56</v>
       </c>
       <c r="L36" s="4">
-        <v>22.832999999999998</v>
+        <v>23.9</v>
       </c>
       <c r="M36" s="5">
         <v>10</v>
       </c>
-      <c r="N36" s="31"/>
-    </row>
-    <row r="37" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B37" s="35">
-        <v>46234</v>
-      </c>
-      <c r="C37" s="36" t="s">
+    </row>
+    <row r="37" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B37" s="31">
+        <v>46265</v>
+      </c>
+      <c r="C37" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="D37" s="37">
-        <v>25.603999999999999</v>
-      </c>
-      <c r="E37" s="37">
-        <v>25.25</v>
-      </c>
-      <c r="F37" s="37">
-        <v>2.4604525329025688</v>
-      </c>
-      <c r="G37" s="37">
-        <v>30.05</v>
-      </c>
-      <c r="H37" s="37">
-        <v>21.5</v>
-      </c>
-      <c r="I37" s="37">
-        <v>28.43</v>
-      </c>
-      <c r="J37" s="37">
-        <v>26.875</v>
-      </c>
-      <c r="K37" s="37">
-        <v>24.184999999999999</v>
-      </c>
-      <c r="L37" s="37">
-        <v>23.3</v>
-      </c>
-      <c r="M37" s="38">
+      <c r="D37" s="33">
+        <v>25.574000000000002</v>
+      </c>
+      <c r="E37" s="33">
+        <v>25.055</v>
+      </c>
+      <c r="F37" s="33">
+        <v>1.822520842740138</v>
+      </c>
+      <c r="G37" s="33">
+        <v>28.63</v>
+      </c>
+      <c r="H37" s="33">
+        <v>23</v>
+      </c>
+      <c r="I37" s="33">
+        <v>28.062999999999999</v>
+      </c>
+      <c r="J37" s="33">
+        <v>26.75</v>
+      </c>
+      <c r="K37" s="33">
+        <v>24.25</v>
+      </c>
+      <c r="L37" s="33">
+        <v>23.9</v>
+      </c>
+      <c r="M37" s="34">
         <v>10</v>
       </c>
-      <c r="N37" s="31"/>
-    </row>
-    <row r="38" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B38" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D38" s="4">
-        <v>25.49</v>
+        <v>25.466999999999999</v>
       </c>
       <c r="E38" s="4">
-        <v>25.305</v>
+        <v>24.94</v>
       </c>
       <c r="F38" s="4">
-        <v>2.2485847400828218</v>
+        <v>2.3670800108525651</v>
       </c>
       <c r="G38" s="4">
-        <v>30.04</v>
+        <v>29</v>
       </c>
       <c r="H38" s="4">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="I38" s="4">
-        <v>27.709</v>
+        <v>28.585999999999999</v>
       </c>
       <c r="J38" s="4">
-        <v>26.25</v>
+        <v>27.1875</v>
       </c>
       <c r="K38" s="4">
-        <v>24.475000000000001</v>
+        <v>24</v>
       </c>
       <c r="L38" s="4">
-        <v>23.75</v>
+        <v>22.9</v>
       </c>
       <c r="M38" s="5">
         <v>10</v>
       </c>
-      <c r="N38" s="31"/>
-    </row>
-    <row r="39" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="35" t="s">
+    </row>
+    <row r="39" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B39" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="36" t="s">
+      <c r="C39" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="D39" s="37">
-        <v>22.91</v>
-      </c>
-      <c r="E39" s="37">
-        <v>23.15</v>
-      </c>
-      <c r="F39" s="37">
-        <v>2.222081106630549</v>
-      </c>
-      <c r="G39" s="37">
-        <v>25.82</v>
-      </c>
-      <c r="H39" s="37">
-        <v>19</v>
-      </c>
-      <c r="I39" s="37">
-        <v>25.082000000000001</v>
-      </c>
-      <c r="J39" s="37">
-        <v>24.337499999999999</v>
-      </c>
-      <c r="K39" s="37">
-        <v>22.497499999999999</v>
-      </c>
-      <c r="L39" s="37">
-        <v>19.36</v>
-      </c>
-      <c r="M39" s="38">
+      <c r="D39" s="33">
+        <v>21.708999999999971</v>
+      </c>
+      <c r="E39" s="33">
+        <v>21.90499999999987</v>
+      </c>
+      <c r="F39" s="33">
+        <v>2.2773203063639889</v>
+      </c>
+      <c r="G39" s="33">
+        <v>25</v>
+      </c>
+      <c r="H39" s="33">
+        <v>18.5</v>
+      </c>
+      <c r="I39" s="33">
+        <v>24.1</v>
+      </c>
+      <c r="J39" s="33">
+        <v>23.45</v>
+      </c>
+      <c r="K39" s="33">
+        <v>19.545000000000002</v>
+      </c>
+      <c r="L39" s="33">
+        <v>18.95</v>
+      </c>
+      <c r="M39" s="34">
         <v>10</v>
       </c>
-      <c r="N39" s="31"/>
-    </row>
-    <row r="40" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
         <v>36</v>
       </c>
@@ -6559,43 +6449,41 @@
         <v>20</v>
       </c>
       <c r="D40" s="4">
-        <v>24.184000000000001</v>
+        <v>24.34008956449512</v>
       </c>
       <c r="E40" s="4">
-        <v>24.17</v>
+        <v>24.5</v>
       </c>
       <c r="F40" s="4">
-        <v>2.1444823255145851</v>
+        <v>2.105210178310351</v>
       </c>
       <c r="G40" s="4">
-        <v>27</v>
+        <v>28.29</v>
       </c>
       <c r="H40" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I40" s="4">
-        <v>26.631</v>
+        <v>26.048999999999999</v>
       </c>
       <c r="J40" s="4">
-        <v>25.327500000000001</v>
+        <v>25.365671733713381</v>
       </c>
       <c r="K40" s="4">
-        <v>24</v>
+        <v>23.25</v>
       </c>
       <c r="L40" s="4">
-        <v>21.26</v>
+        <v>21.675000000000001</v>
       </c>
       <c r="M40" s="5">
         <v>10</v>
       </c>
-      <c r="N40" s="31"/>
-    </row>
-    <row r="41" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B41" s="22"/>
       <c r="C41" s="23"/>
-      <c r="N41" s="31"/>
-    </row>
-    <row r="43" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="14" t="s">
         <v>21</v>
       </c>
@@ -6611,7 +6499,7 @@
       <c r="L43" s="14"/>
       <c r="M43" s="15"/>
     </row>
-    <row r="44" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B44" s="24" t="s">
         <v>1</v>
       </c>
@@ -6649,327 +6537,319 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B45" s="35">
-        <v>46112</v>
-      </c>
-      <c r="C45" s="36" t="s">
+    <row r="45" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B45" s="31">
+        <v>46142</v>
+      </c>
+      <c r="C45" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="D45" s="39">
-        <v>1434.8956699701721</v>
-      </c>
-      <c r="E45" s="39">
-        <v>1428.7881960142861</v>
-      </c>
-      <c r="F45" s="39">
-        <v>32.743237626160983</v>
-      </c>
-      <c r="G45" s="39">
-        <v>1502</v>
-      </c>
-      <c r="H45" s="39">
-        <v>1392.4821565838929</v>
-      </c>
-      <c r="I45" s="39">
-        <v>1478.6179999999999</v>
-      </c>
-      <c r="J45" s="39">
-        <v>1443.5157070300099</v>
-      </c>
-      <c r="K45" s="39">
-        <v>1418.125</v>
-      </c>
-      <c r="L45" s="39">
-        <v>1404.429703202703</v>
-      </c>
-      <c r="M45" s="38">
+      <c r="D45" s="42">
+        <v>1416.8869404913139</v>
+      </c>
+      <c r="E45" s="42">
+        <v>1417.8849951612899</v>
+      </c>
+      <c r="F45" s="42">
+        <v>7.648048134882405</v>
+      </c>
+      <c r="G45" s="42">
+        <v>1430</v>
+      </c>
+      <c r="H45" s="42">
+        <v>1405</v>
+      </c>
+      <c r="I45" s="42">
+        <v>1424.8676511161291</v>
+      </c>
+      <c r="J45" s="42">
+        <v>1420.5025000000001</v>
+      </c>
+      <c r="K45" s="42">
+        <v>1411.9200236153811</v>
+      </c>
+      <c r="L45" s="42">
+        <v>1407.25</v>
+      </c>
+      <c r="M45" s="34">
         <v>10</v>
       </c>
-      <c r="N45" s="31"/>
-    </row>
-    <row r="46" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B46" s="2">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D46" s="40">
-        <v>1467.7022569028379</v>
-      </c>
-      <c r="E46" s="40">
-        <v>1449.0069732142861</v>
-      </c>
-      <c r="F46" s="40">
-        <v>49.644500540926529</v>
-      </c>
-      <c r="G46" s="40">
-        <v>1572</v>
-      </c>
-      <c r="H46" s="40">
-        <v>1421.7242818721541</v>
-      </c>
-      <c r="I46" s="40">
-        <v>1530.357</v>
-      </c>
-      <c r="J46" s="40">
-        <v>1491.4267532945651</v>
-      </c>
-      <c r="K46" s="40">
-        <v>1433.5727183317249</v>
-      </c>
-      <c r="L46" s="40">
-        <v>1424.672428187215</v>
+      <c r="D46" s="36">
+        <v>1437.6218679037549</v>
+      </c>
+      <c r="E46" s="36">
+        <v>1438.1849951612901</v>
+      </c>
+      <c r="F46" s="36">
+        <v>16.235611191639769</v>
+      </c>
+      <c r="G46" s="36">
+        <v>1465</v>
+      </c>
+      <c r="H46" s="36">
+        <v>1411</v>
+      </c>
+      <c r="I46" s="36">
+        <v>1457.0260000000001</v>
+      </c>
+      <c r="J46" s="36">
+        <v>1446.379302014527</v>
+      </c>
+      <c r="K46" s="36">
+        <v>1426.3928758489001</v>
+      </c>
+      <c r="L46" s="36">
+        <v>1421.35</v>
       </c>
       <c r="M46" s="5">
         <v>10</v>
       </c>
-      <c r="N46" s="31"/>
-    </row>
-    <row r="47" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B47" s="35">
-        <v>46173</v>
-      </c>
-      <c r="C47" s="36" t="s">
+    </row>
+    <row r="47" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B47" s="31">
+        <v>46203</v>
+      </c>
+      <c r="C47" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="D47" s="39">
-        <v>1489.518772309611</v>
-      </c>
-      <c r="E47" s="39">
-        <v>1463.67330414455</v>
-      </c>
-      <c r="F47" s="39">
-        <v>62.296157167927781</v>
-      </c>
-      <c r="G47" s="39">
-        <v>1627</v>
-      </c>
-      <c r="H47" s="39">
-        <v>1435</v>
-      </c>
-      <c r="I47" s="39">
-        <v>1570.471</v>
-      </c>
-      <c r="J47" s="39">
-        <v>1508.107892135798</v>
-      </c>
-      <c r="K47" s="39">
-        <v>1451.99761146476</v>
-      </c>
-      <c r="L47" s="39">
-        <v>1442.245131490213</v>
-      </c>
-      <c r="M47" s="38">
+      <c r="D47" s="42">
+        <v>1459.2876847605289</v>
+      </c>
+      <c r="E47" s="42">
+        <v>1465.78499516129</v>
+      </c>
+      <c r="F47" s="42">
+        <v>24.537374099442651</v>
+      </c>
+      <c r="G47" s="42">
+        <v>1495</v>
+      </c>
+      <c r="H47" s="42">
+        <v>1412</v>
+      </c>
+      <c r="I47" s="42">
+        <v>1486.297</v>
+      </c>
+      <c r="J47" s="42">
+        <v>1469.942312255381</v>
+      </c>
+      <c r="K47" s="42">
+        <v>1442.6197111170461</v>
+      </c>
+      <c r="L47" s="42">
+        <v>1434.95</v>
+      </c>
+      <c r="M47" s="34">
         <v>10</v>
       </c>
-      <c r="N47" s="31"/>
-    </row>
-    <row r="48" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B48" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D48" s="40">
-        <v>1521.5904213722049</v>
-      </c>
-      <c r="E48" s="40">
-        <v>1494.4569732142861</v>
-      </c>
-      <c r="F48" s="40">
-        <v>75.50213699858179</v>
-      </c>
-      <c r="G48" s="40">
-        <v>1668</v>
-      </c>
-      <c r="H48" s="40">
-        <v>1450</v>
-      </c>
-      <c r="I48" s="40">
-        <v>1613.037071716336</v>
-      </c>
-      <c r="J48" s="40">
-        <v>1576.0125</v>
-      </c>
-      <c r="K48" s="40">
-        <v>1471.1892871307989</v>
-      </c>
-      <c r="L48" s="40">
-        <v>1456.2003131539741</v>
+      <c r="D48" s="36">
+        <v>1481.3160522422891</v>
+      </c>
+      <c r="E48" s="36">
+        <v>1484.9842149804181</v>
+      </c>
+      <c r="F48" s="36">
+        <v>32.752475142984288</v>
+      </c>
+      <c r="G48" s="36">
+        <v>1530</v>
+      </c>
+      <c r="H48" s="36">
+        <v>1418</v>
+      </c>
+      <c r="I48" s="36">
+        <v>1517.1120000000001</v>
+      </c>
+      <c r="J48" s="36">
+        <v>1499.3423678221429</v>
+      </c>
+      <c r="K48" s="36">
+        <v>1460.840786722237</v>
+      </c>
+      <c r="L48" s="36">
+        <v>1450.201526856082</v>
       </c>
       <c r="M48" s="5">
         <v>10</v>
       </c>
-      <c r="N48" s="31"/>
-    </row>
-    <row r="49" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="35">
-        <v>46234</v>
-      </c>
-      <c r="C49" s="36" t="s">
+    </row>
+    <row r="49" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B49" s="31">
+        <v>46265</v>
+      </c>
+      <c r="C49" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="D49" s="39">
-        <v>1552.729999913583</v>
-      </c>
-      <c r="E49" s="39">
-        <v>1518.4241402933551</v>
-      </c>
-      <c r="F49" s="39">
-        <v>86.562386562109467</v>
-      </c>
-      <c r="G49" s="39">
-        <v>1692</v>
-      </c>
-      <c r="H49" s="39">
-        <v>1455.926853650147</v>
-      </c>
-      <c r="I49" s="39">
-        <v>1682.0356563028561</v>
-      </c>
-      <c r="J49" s="39">
-        <v>1617.9725000000001</v>
-      </c>
-      <c r="K49" s="39">
-        <v>1497.0360379950159</v>
-      </c>
-      <c r="L49" s="39">
-        <v>1473.0926853650151</v>
-      </c>
-      <c r="M49" s="38">
+      <c r="D49" s="42">
+        <v>1509.6966297615049</v>
+      </c>
+      <c r="E49" s="42">
+        <v>1511.7478992800261</v>
+      </c>
+      <c r="F49" s="42">
+        <v>41.569195400872132</v>
+      </c>
+      <c r="G49" s="42">
+        <v>1561.76</v>
+      </c>
+      <c r="H49" s="42">
+        <v>1424</v>
+      </c>
+      <c r="I49" s="42">
+        <v>1555.6759999999999</v>
+      </c>
+      <c r="J49" s="42">
+        <v>1538.13867917517</v>
+      </c>
+      <c r="K49" s="42">
+        <v>1495.885414448514</v>
+      </c>
+      <c r="L49" s="42">
+        <v>1463.8855421246431</v>
+      </c>
+      <c r="M49" s="34">
         <v>10</v>
       </c>
-      <c r="N49" s="31"/>
-    </row>
-    <row r="50" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B50" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D50" s="40">
-        <v>1585.2480228136201</v>
-      </c>
-      <c r="E50" s="40">
-        <v>1553.072908353613</v>
-      </c>
-      <c r="F50" s="40">
-        <v>90.792494618342374</v>
-      </c>
-      <c r="G50" s="40">
-        <v>1745.000945757258</v>
-      </c>
-      <c r="H50" s="40">
-        <v>1481.5884556009771</v>
-      </c>
-      <c r="I50" s="40">
-        <v>1711.7000945757261</v>
-      </c>
-      <c r="J50" s="40">
-        <v>1648.4275</v>
-      </c>
-      <c r="K50" s="40">
-        <v>1530.481257553053</v>
-      </c>
-      <c r="L50" s="40">
-        <v>1502.6588455600979</v>
+      <c r="D50" s="36">
+        <v>1540.600328297686</v>
+      </c>
+      <c r="E50" s="36">
+        <v>1539.8810209167129</v>
+      </c>
+      <c r="F50" s="36">
+        <v>53.40078837656894</v>
+      </c>
+      <c r="G50" s="36">
+        <v>1615.93</v>
+      </c>
+      <c r="H50" s="36">
+        <v>1428</v>
+      </c>
+      <c r="I50" s="36">
+        <v>1595.208472623779</v>
+      </c>
+      <c r="J50" s="36">
+        <v>1567.5</v>
+      </c>
+      <c r="K50" s="36">
+        <v>1537.451179683173</v>
+      </c>
+      <c r="L50" s="36">
+        <v>1477.500397545889</v>
       </c>
       <c r="M50" s="5">
         <v>10</v>
       </c>
-      <c r="N50" s="31"/>
-    </row>
-    <row r="51" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B51" s="35" t="s">
+    </row>
+    <row r="51" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B51" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="36" t="s">
+      <c r="C51" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="D51" s="39">
-        <v>1749.857471464298</v>
-      </c>
-      <c r="E51" s="39">
-        <v>1739.711476797919</v>
-      </c>
-      <c r="F51" s="39">
-        <v>87.759038646756593</v>
-      </c>
-      <c r="G51" s="39">
-        <v>1903.2718822934121</v>
-      </c>
-      <c r="H51" s="39">
-        <v>1627</v>
-      </c>
-      <c r="I51" s="39">
-        <v>1877.467188229341</v>
-      </c>
-      <c r="J51" s="39">
-        <v>1780.5</v>
-      </c>
-      <c r="K51" s="39">
-        <v>1694.659442651458</v>
-      </c>
-      <c r="L51" s="39">
-        <v>1657.6</v>
-      </c>
-      <c r="M51" s="38">
+      <c r="D51" s="42">
+        <v>1688.3743184397929</v>
+      </c>
+      <c r="E51" s="42">
+        <v>1692.5</v>
+      </c>
+      <c r="F51" s="42">
+        <v>111.84654751848851</v>
+      </c>
+      <c r="G51" s="42">
+        <v>1804.82</v>
+      </c>
+      <c r="H51" s="42">
+        <v>1449</v>
+      </c>
+      <c r="I51" s="42">
+        <v>1789.682</v>
+      </c>
+      <c r="J51" s="42">
+        <v>1782.906473232131</v>
+      </c>
+      <c r="K51" s="42">
+        <v>1654.538014932532</v>
+      </c>
+      <c r="L51" s="42">
+        <v>1561.5</v>
+      </c>
+      <c r="M51" s="34">
         <v>10</v>
       </c>
-      <c r="N51" s="31"/>
-    </row>
-    <row r="52" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D52" s="40">
-        <v>1715.892120112077</v>
-      </c>
-      <c r="E52" s="40">
-        <v>1721.6274802376549</v>
-      </c>
-      <c r="F52" s="40">
-        <v>88.580891303294834</v>
-      </c>
-      <c r="G52" s="40">
-        <v>1858.0907494167579</v>
-      </c>
-      <c r="H52" s="40">
-        <v>1580</v>
-      </c>
-      <c r="I52" s="40">
-        <v>1833.9880749416759</v>
-      </c>
-      <c r="J52" s="40">
-        <v>1753.75</v>
-      </c>
-      <c r="K52" s="40">
-        <v>1653.449118421526</v>
-      </c>
-      <c r="L52" s="40">
-        <v>1616</v>
+      <c r="D52" s="36">
+        <v>1632.572228390168</v>
+      </c>
+      <c r="E52" s="36">
+        <v>1660</v>
+      </c>
+      <c r="F52" s="36">
+        <v>89.966592818116752</v>
+      </c>
+      <c r="G52" s="36">
+        <v>1752.55</v>
+      </c>
+      <c r="H52" s="36">
+        <v>1440</v>
+      </c>
+      <c r="I52" s="36">
+        <v>1711.845074373965</v>
+      </c>
+      <c r="J52" s="36">
+        <v>1672.5</v>
+      </c>
+      <c r="K52" s="36">
+        <v>1615.487494760431</v>
+      </c>
+      <c r="L52" s="36">
+        <v>1519.11</v>
       </c>
       <c r="M52" s="5">
         <v>10</v>
       </c>
-      <c r="N52" s="31"/>
-    </row>
-    <row r="53" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B53" s="22"/>
       <c r="C53" s="23"/>
     </row>
-    <row r="54" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B54" s="22"/>
       <c r="C54" s="23"/>
     </row>
-    <row r="55" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B55" s="14" t="s">
         <v>24</v>
       </c>
@@ -6985,7 +6865,7 @@
       <c r="L55" s="14"/>
       <c r="M55" s="15"/>
     </row>
-    <row r="56" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B56" s="24" t="s">
         <v>1</v>
       </c>
@@ -7023,327 +6903,319 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B57" s="44">
-        <v>46081</v>
-      </c>
-      <c r="C57" s="36" t="s">
+    <row r="57" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B57" s="38">
+        <v>46112</v>
+      </c>
+      <c r="C57" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="D57" s="45">
-        <v>6914.7496649221694</v>
-      </c>
-      <c r="E57" s="45">
-        <v>6883.3100190260384</v>
-      </c>
-      <c r="F57" s="45">
-        <v>278.88715565709441</v>
-      </c>
-      <c r="G57" s="45">
-        <v>7300</v>
-      </c>
-      <c r="H57" s="45">
-        <v>6324.2</v>
-      </c>
-      <c r="I57" s="45">
-        <v>7170.5800487575152</v>
-      </c>
-      <c r="J57" s="45">
-        <v>7122.6774999999998</v>
-      </c>
-      <c r="K57" s="45">
-        <v>6819.9766392486499</v>
-      </c>
-      <c r="L57" s="45">
-        <v>6666.92</v>
-      </c>
-      <c r="M57" s="46">
+      <c r="D57" s="39">
+        <v>7362.3736544049507</v>
+      </c>
+      <c r="E57" s="39">
+        <v>7459.1917805892572</v>
+      </c>
+      <c r="F57" s="39">
+        <v>324.14311372368951</v>
+      </c>
+      <c r="G57" s="39">
+        <v>7845</v>
+      </c>
+      <c r="H57" s="39">
+        <v>6780.2629675981862</v>
+      </c>
+      <c r="I57" s="39">
+        <v>7570.5</v>
+      </c>
+      <c r="J57" s="39">
+        <v>7521.5925114546062</v>
+      </c>
+      <c r="K57" s="39">
+        <v>7317.5</v>
+      </c>
+      <c r="L57" s="39">
+        <v>6835.1962967598192</v>
+      </c>
+      <c r="M57" s="40">
         <v>10</v>
       </c>
-      <c r="N57" s="32"/>
-    </row>
-    <row r="58" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B58" s="2">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D58" s="42">
-        <v>7533.1591285400154</v>
-      </c>
-      <c r="E58" s="42">
-        <v>7491.9742500000002</v>
-      </c>
-      <c r="F58" s="42">
-        <v>361.1811250862001</v>
-      </c>
-      <c r="G58" s="42">
-        <v>8123</v>
-      </c>
-      <c r="H58" s="42">
-        <v>6841.26</v>
-      </c>
-      <c r="I58" s="42">
-        <v>7895.9495665155127</v>
-      </c>
-      <c r="J58" s="42">
-        <v>7777.3978424724673</v>
-      </c>
-      <c r="K58" s="42">
-        <v>7372.5</v>
-      </c>
-      <c r="L58" s="42">
-        <v>7190.2027913274324</v>
+      <c r="D58" s="36">
+        <v>7743.7392986506329</v>
+      </c>
+      <c r="E58" s="36">
+        <v>7699.5112431869402</v>
+      </c>
+      <c r="F58" s="36">
+        <v>434.91508077415591</v>
+      </c>
+      <c r="G58" s="36">
+        <v>8500</v>
+      </c>
+      <c r="H58" s="36">
+        <v>6874.2</v>
+      </c>
+      <c r="I58" s="36">
+        <v>8212</v>
+      </c>
+      <c r="J58" s="36">
+        <v>7956.25</v>
+      </c>
+      <c r="K58" s="36">
+        <v>7566.9423162384828</v>
+      </c>
+      <c r="L58" s="36">
+        <v>7461.942670633025</v>
       </c>
       <c r="M58" s="5">
         <v>10</v>
       </c>
-      <c r="N58" s="32"/>
-    </row>
-    <row r="59" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B59" s="35">
-        <v>46142</v>
-      </c>
-      <c r="C59" s="36" t="s">
+    </row>
+    <row r="59" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B59" s="31">
+        <v>46173</v>
+      </c>
+      <c r="C59" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="D59" s="45">
-        <v>8043.15592922408</v>
-      </c>
-      <c r="E59" s="45">
-        <v>7932.5</v>
-      </c>
-      <c r="F59" s="45">
-        <v>741.57980852618039</v>
-      </c>
-      <c r="G59" s="45">
-        <v>9499.5813244242654</v>
-      </c>
-      <c r="H59" s="45">
-        <v>6874.22</v>
-      </c>
-      <c r="I59" s="45">
-        <v>8763.2696472439584</v>
-      </c>
-      <c r="J59" s="45">
-        <v>8472.7935030451426</v>
-      </c>
-      <c r="K59" s="45">
-        <v>7639.2439538012914</v>
-      </c>
-      <c r="L59" s="45">
-        <v>7322.6433007092764</v>
-      </c>
-      <c r="M59" s="38">
+      <c r="D59" s="39">
+        <v>8201.9335995119945</v>
+      </c>
+      <c r="E59" s="39">
+        <v>8244.0987190766355</v>
+      </c>
+      <c r="F59" s="39">
+        <v>414.11883977650461</v>
+      </c>
+      <c r="G59" s="39">
+        <v>8814.8740509557356</v>
+      </c>
+      <c r="H59" s="39">
+        <v>7307.9</v>
+      </c>
+      <c r="I59" s="39">
+        <v>8693.4874050955732</v>
+      </c>
+      <c r="J59" s="39">
+        <v>8295.25</v>
+      </c>
+      <c r="K59" s="39">
+        <v>8078.0233795082167</v>
+      </c>
+      <c r="L59" s="39">
+        <v>7840.79</v>
+      </c>
+      <c r="M59" s="34">
         <v>10</v>
       </c>
-      <c r="N59" s="32"/>
-    </row>
-    <row r="60" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B60" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D60" s="42">
-        <v>8436.6422329980614</v>
-      </c>
-      <c r="E60" s="42">
-        <v>8310</v>
-      </c>
-      <c r="F60" s="42">
-        <v>736.17606975416027</v>
-      </c>
-      <c r="G60" s="42">
-        <v>9612.7787517514171</v>
-      </c>
-      <c r="H60" s="42">
-        <v>7307.85</v>
-      </c>
-      <c r="I60" s="42">
-        <v>9187.2778751751412</v>
-      </c>
-      <c r="J60" s="42">
-        <v>9027.6017249094657</v>
-      </c>
-      <c r="K60" s="42">
-        <v>8009.4352234535781</v>
-      </c>
-      <c r="L60" s="42">
-        <v>7570.7849999999999</v>
+      <c r="D60" s="36">
+        <v>8104.1926700078066</v>
+      </c>
+      <c r="E60" s="36">
+        <v>8105.8140728156104</v>
+      </c>
+      <c r="F60" s="36">
+        <v>241.85364912898251</v>
+      </c>
+      <c r="G60" s="36">
+        <v>8370</v>
+      </c>
+      <c r="H60" s="36">
+        <v>7493.3</v>
+      </c>
+      <c r="I60" s="36">
+        <v>8330.1934153065831</v>
+      </c>
+      <c r="J60" s="36">
+        <v>8227.1710697463132</v>
+      </c>
+      <c r="K60" s="36">
+        <v>8085</v>
+      </c>
+      <c r="L60" s="36">
+        <v>7971.83</v>
       </c>
       <c r="M60" s="5">
         <v>10</v>
       </c>
-      <c r="N60" s="32"/>
-    </row>
-    <row r="61" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B61" s="35">
-        <v>46203</v>
-      </c>
-      <c r="C61" s="36" t="s">
+    </row>
+    <row r="61" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B61" s="31">
+        <v>46234</v>
+      </c>
+      <c r="C61" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="D61" s="45">
-        <v>8084.6708531869153</v>
-      </c>
-      <c r="E61" s="45">
-        <v>8037.5</v>
-      </c>
-      <c r="F61" s="45">
-        <v>507.9199459325643</v>
-      </c>
-      <c r="G61" s="45">
-        <v>9093.2076922841152</v>
-      </c>
-      <c r="H61" s="45">
-        <v>7300</v>
-      </c>
-      <c r="I61" s="45">
-        <v>8527.4730343006522</v>
-      </c>
-      <c r="J61" s="45">
-        <v>8338.9305547759577</v>
-      </c>
-      <c r="K61" s="45">
-        <v>7856.3968826763921</v>
-      </c>
-      <c r="L61" s="45">
-        <v>7473.9250000000002</v>
-      </c>
-      <c r="M61" s="38">
+      <c r="D61" s="39">
+        <v>8350.7695703034005</v>
+      </c>
+      <c r="E61" s="39">
+        <v>8448.1466680609919</v>
+      </c>
+      <c r="F61" s="39">
+        <v>359.37206454919959</v>
+      </c>
+      <c r="G61" s="39">
+        <v>8821.1574269908306</v>
+      </c>
+      <c r="H61" s="39">
+        <v>7865</v>
+      </c>
+      <c r="I61" s="39">
+        <v>8685.1157426990831</v>
+      </c>
+      <c r="J61" s="39">
+        <v>8646.3337049408965</v>
+      </c>
+      <c r="K61" s="39">
+        <v>7995.35</v>
+      </c>
+      <c r="L61" s="39">
+        <v>7980.2</v>
+      </c>
+      <c r="M61" s="34">
         <v>10</v>
       </c>
-      <c r="N61" s="32"/>
-    </row>
-    <row r="62" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B62" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D62" s="42">
-        <v>8143.1209254741043</v>
-      </c>
-      <c r="E62" s="42">
-        <v>8342.5</v>
-      </c>
-      <c r="F62" s="42">
-        <v>634.2264127830814</v>
-      </c>
-      <c r="G62" s="42">
-        <v>8968.5027880154757</v>
-      </c>
-      <c r="H62" s="42">
-        <v>7000</v>
-      </c>
-      <c r="I62" s="42">
-        <v>8683.9346696396187</v>
-      </c>
-      <c r="J62" s="42">
-        <v>8543.2792996648041</v>
-      </c>
-      <c r="K62" s="42">
-        <v>7897.9575000000004</v>
-      </c>
-      <c r="L62" s="42">
-        <v>7180</v>
+      <c r="D62" s="36">
+        <v>8233.9606009179442</v>
+      </c>
+      <c r="E62" s="36">
+        <v>8143.485699152774</v>
+      </c>
+      <c r="F62" s="36">
+        <v>512.64802799747679</v>
+      </c>
+      <c r="G62" s="36">
+        <v>9137.543488644842</v>
+      </c>
+      <c r="H62" s="36">
+        <v>7500</v>
+      </c>
+      <c r="I62" s="36">
+        <v>8792.436358870631</v>
+      </c>
+      <c r="J62" s="36">
+        <v>8582.5</v>
+      </c>
+      <c r="K62" s="36">
+        <v>7922.75</v>
+      </c>
+      <c r="L62" s="36">
+        <v>7638.6</v>
       </c>
       <c r="M62" s="5">
         <v>10</v>
       </c>
-      <c r="N62" s="32"/>
-    </row>
-    <row r="63" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B63" s="35">
-        <v>46265</v>
-      </c>
-      <c r="C63" s="36" t="s">
+    </row>
+    <row r="63" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B63" s="31">
+        <v>46295</v>
+      </c>
+      <c r="C63" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="D63" s="45">
-        <v>8075.9873056495426</v>
-      </c>
-      <c r="E63" s="45">
-        <v>8176.4325437691123</v>
-      </c>
-      <c r="F63" s="45">
-        <v>662.57951349695509</v>
-      </c>
-      <c r="G63" s="45">
-        <v>8939.6518060804337</v>
-      </c>
-      <c r="H63" s="45">
-        <v>7000</v>
-      </c>
-      <c r="I63" s="45">
-        <v>8780.9857271971396</v>
-      </c>
-      <c r="J63" s="45">
-        <v>8523.75</v>
-      </c>
-      <c r="K63" s="45">
-        <v>7864.25</v>
-      </c>
-      <c r="L63" s="45">
-        <v>7000</v>
-      </c>
-      <c r="M63" s="38">
+      <c r="D63" s="39">
+        <v>8274.9456676732825</v>
+      </c>
+      <c r="E63" s="39">
+        <v>8120.3427817949969</v>
+      </c>
+      <c r="F63" s="39">
+        <v>684.42668375152141</v>
+      </c>
+      <c r="G63" s="39">
+        <v>9456.2614126757271</v>
+      </c>
+      <c r="H63" s="39">
+        <v>7300</v>
+      </c>
+      <c r="I63" s="39">
+        <v>9048.7848716879671</v>
+      </c>
+      <c r="J63" s="39">
+        <v>8747.5</v>
+      </c>
+      <c r="K63" s="39">
+        <v>7809</v>
+      </c>
+      <c r="L63" s="39">
+        <v>7504.3</v>
+      </c>
+      <c r="M63" s="34">
         <v>10</v>
       </c>
-      <c r="N63" s="32"/>
-    </row>
-    <row r="64" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B64" s="41" t="s">
+    </row>
+    <row r="64" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B64" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="C64" s="42" t="s">
+      <c r="C64" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D64" s="42">
-        <v>93863.871636781172</v>
-      </c>
-      <c r="E64" s="42">
-        <v>94382.771543886629</v>
-      </c>
-      <c r="F64" s="42">
-        <v>3426.018917890915</v>
-      </c>
-      <c r="G64" s="42">
-        <v>99806.587740335817</v>
-      </c>
-      <c r="H64" s="42">
-        <v>88301</v>
-      </c>
-      <c r="I64" s="42">
-        <v>97333.74275288888</v>
-      </c>
-      <c r="J64" s="42">
-        <v>95572.243600967573</v>
-      </c>
-      <c r="K64" s="42">
-        <v>91807.806418218213</v>
-      </c>
-      <c r="L64" s="42">
-        <v>89829.982983854003</v>
-      </c>
-      <c r="M64" s="43">
+      <c r="D64" s="36">
+        <v>93611.246992911707</v>
+      </c>
+      <c r="E64" s="36">
+        <v>92700.959808448999</v>
+      </c>
+      <c r="F64" s="36">
+        <v>3180.6167099813279</v>
+      </c>
+      <c r="G64" s="36">
+        <v>100200.0097815488</v>
+      </c>
+      <c r="H64" s="36">
+        <v>89999.9</v>
+      </c>
+      <c r="I64" s="36">
+        <v>98400.000978154887</v>
+      </c>
+      <c r="J64" s="36">
+        <v>93719.730398002735</v>
+      </c>
+      <c r="K64" s="36">
+        <v>91844.5</v>
+      </c>
+      <c r="L64" s="36">
+        <v>91156.49</v>
+      </c>
+      <c r="M64" s="37">
         <v>10</v>
       </c>
-      <c r="N64" s="32"/>
-    </row>
-    <row r="65" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B65" s="22"/>
       <c r="C65" s="23"/>
     </row>
-    <row r="66" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B66" s="22"/>
       <c r="C66" s="23"/>
     </row>
-    <row r="67" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="14" t="s">
         <v>26</v>
       </c>
@@ -7359,7 +7231,7 @@
       <c r="L67" s="14"/>
       <c r="M67" s="15"/>
     </row>
-    <row r="68" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B68" s="24" t="s">
         <v>1</v>
       </c>
@@ -7397,319 +7269,311 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="44">
-        <v>46081</v>
-      </c>
-      <c r="C69" s="36" t="s">
+    <row r="69" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B69" s="38">
+        <v>46112</v>
+      </c>
+      <c r="C69" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="D69" s="45">
-        <v>5806.565678253477</v>
-      </c>
-      <c r="E69" s="45">
-        <v>5853.6437803200006</v>
-      </c>
-      <c r="F69" s="45">
-        <v>241.1420198775526</v>
-      </c>
-      <c r="G69" s="45">
-        <v>6169</v>
-      </c>
-      <c r="H69" s="45">
-        <v>5305.7373551553956</v>
-      </c>
-      <c r="I69" s="45">
-        <v>6036.190108662483</v>
-      </c>
-      <c r="J69" s="45">
-        <v>5911.8915694394873</v>
-      </c>
-      <c r="K69" s="45">
-        <v>5711.7716827912654</v>
-      </c>
-      <c r="L69" s="45">
-        <v>5544.8163374575124</v>
-      </c>
-      <c r="M69" s="46">
+      <c r="D69" s="39">
+        <v>6484.0958437584486</v>
+      </c>
+      <c r="E69" s="39">
+        <v>6481.1976108129784</v>
+      </c>
+      <c r="F69" s="39">
+        <v>548.53116962807849</v>
+      </c>
+      <c r="G69" s="39">
+        <v>7273.3638476630513</v>
+      </c>
+      <c r="H69" s="39">
+        <v>5440.22</v>
+      </c>
+      <c r="I69" s="39">
+        <v>7201.9363847663053</v>
+      </c>
+      <c r="J69" s="39">
+        <v>6791.0330341435729</v>
+      </c>
+      <c r="K69" s="39">
+        <v>6154.491544932429</v>
+      </c>
+      <c r="L69" s="39">
+        <v>6018.9940998634011</v>
+      </c>
+      <c r="M69" s="40">
         <v>10</v>
       </c>
-      <c r="N69" s="32"/>
-    </row>
-    <row r="70" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B70" s="2">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D70" s="42">
-        <v>6492.6827852246961</v>
-      </c>
-      <c r="E70" s="42">
-        <v>6535.555191207528</v>
-      </c>
-      <c r="F70" s="42">
-        <v>502.99773985247208</v>
-      </c>
-      <c r="G70" s="42">
-        <v>7640.1492081188362</v>
-      </c>
-      <c r="H70" s="42">
-        <v>5985.0668372843356</v>
-      </c>
-      <c r="I70" s="42">
-        <v>6815.6149208118832</v>
-      </c>
-      <c r="J70" s="42">
-        <v>6683.3173999604815</v>
-      </c>
-      <c r="K70" s="42">
-        <v>6056.6825664500884</v>
-      </c>
-      <c r="L70" s="42">
-        <v>6015.4698617594331</v>
+      <c r="D70" s="36">
+        <v>6804.4500923462501</v>
+      </c>
+      <c r="E70" s="36">
+        <v>6739.6207656258848</v>
+      </c>
+      <c r="F70" s="36">
+        <v>446.56437606819031</v>
+      </c>
+      <c r="G70" s="36">
+        <v>7563</v>
+      </c>
+      <c r="H70" s="36">
+        <v>6188.8989512861908</v>
+      </c>
+      <c r="I70" s="36">
+        <v>7366.8</v>
+      </c>
+      <c r="J70" s="36">
+        <v>7066.5733832217593</v>
+      </c>
+      <c r="K70" s="36">
+        <v>6457.0845312751617</v>
+      </c>
+      <c r="L70" s="36">
+        <v>6345.381676020208</v>
       </c>
       <c r="M70" s="5">
         <v>10</v>
       </c>
-      <c r="N70" s="32"/>
-    </row>
-    <row r="71" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B71" s="35">
-        <v>46142</v>
-      </c>
-      <c r="C71" s="36" t="s">
+    </row>
+    <row r="71" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B71" s="31">
+        <v>46173</v>
+      </c>
+      <c r="C71" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="D71" s="45">
-        <v>6544.4766656650336</v>
-      </c>
-      <c r="E71" s="45">
-        <v>6511.4795945699998</v>
-      </c>
-      <c r="F71" s="45">
-        <v>394.64894283890521</v>
-      </c>
-      <c r="G71" s="45">
-        <v>7339.9100809943011</v>
-      </c>
-      <c r="H71" s="45">
-        <v>5974.5089368252238</v>
-      </c>
-      <c r="I71" s="45">
-        <v>7031.2910080994297</v>
-      </c>
-      <c r="J71" s="45">
-        <v>6630.7208925849882</v>
-      </c>
-      <c r="K71" s="45">
-        <v>6327.4937703307241</v>
-      </c>
-      <c r="L71" s="45">
-        <v>6167.4599498400939</v>
-      </c>
-      <c r="M71" s="38">
+      <c r="D71" s="39">
+        <v>7014.6057695504496</v>
+      </c>
+      <c r="E71" s="39">
+        <v>6970.8244849605871</v>
+      </c>
+      <c r="F71" s="39">
+        <v>598.30018642670257</v>
+      </c>
+      <c r="G71" s="39">
+        <v>8003</v>
+      </c>
+      <c r="H71" s="39">
+        <v>6234.9522612827004</v>
+      </c>
+      <c r="I71" s="39">
+        <v>7900.3857086605713</v>
+      </c>
+      <c r="J71" s="39">
+        <v>7301.2933820499211</v>
+      </c>
+      <c r="K71" s="39">
+        <v>6618.8572555818764</v>
+      </c>
+      <c r="L71" s="39">
+        <v>6331.9340398637833</v>
+      </c>
+      <c r="M71" s="34">
         <v>10</v>
       </c>
-      <c r="N71" s="32"/>
-    </row>
-    <row r="72" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B72" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D72" s="42">
-        <v>6968.5313294346633</v>
-      </c>
-      <c r="E72" s="42">
-        <v>6940.7288275244819</v>
-      </c>
-      <c r="F72" s="42">
-        <v>594.16821680799217</v>
-      </c>
-      <c r="G72" s="42">
-        <v>8301.2622668812437</v>
-      </c>
-      <c r="H72" s="42">
-        <v>6234.9522612827004</v>
-      </c>
-      <c r="I72" s="42">
-        <v>7431.6700477862432</v>
-      </c>
-      <c r="J72" s="42">
-        <v>7177.75</v>
-      </c>
-      <c r="K72" s="42">
-        <v>6565.6424141689322</v>
-      </c>
-      <c r="L72" s="42">
-        <v>6333.9617300983382</v>
+      <c r="D72" s="36">
+        <v>7059.9890981519884</v>
+      </c>
+      <c r="E72" s="36">
+        <v>6930.9614020739009</v>
+      </c>
+      <c r="F72" s="36">
+        <v>473.14816969676309</v>
+      </c>
+      <c r="G72" s="36">
+        <v>7957</v>
+      </c>
+      <c r="H72" s="36">
+        <v>6502.32</v>
+      </c>
+      <c r="I72" s="36">
+        <v>7771.1467902553386</v>
+      </c>
+      <c r="J72" s="36">
+        <v>7197.4489522954837</v>
+      </c>
+      <c r="K72" s="36">
+        <v>6857.9855222600636</v>
+      </c>
+      <c r="L72" s="36">
+        <v>6544.6420644590862</v>
       </c>
       <c r="M72" s="5">
         <v>10</v>
       </c>
-      <c r="N72" s="32"/>
-    </row>
-    <row r="73" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B73" s="35">
-        <v>46203</v>
-      </c>
-      <c r="C73" s="36" t="s">
+    </row>
+    <row r="73" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B73" s="31">
+        <v>46234</v>
+      </c>
+      <c r="C73" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="D73" s="45">
-        <v>6998.1147913059094</v>
-      </c>
-      <c r="E73" s="45">
-        <v>6937.2730416205286</v>
-      </c>
-      <c r="F73" s="45">
-        <v>548.65141981773706</v>
-      </c>
-      <c r="G73" s="45">
-        <v>8136.8805849166347</v>
-      </c>
-      <c r="H73" s="45">
-        <v>6213.7266457764244</v>
-      </c>
-      <c r="I73" s="45">
-        <v>7482.9213586815267</v>
-      </c>
-      <c r="J73" s="45">
-        <v>7288.75</v>
-      </c>
-      <c r="K73" s="45">
-        <v>6757.5278859980745</v>
-      </c>
-      <c r="L73" s="45">
-        <v>6377.6917724066416</v>
-      </c>
-      <c r="M73" s="38">
+      <c r="D73" s="39">
+        <v>7460.9073869963568</v>
+      </c>
+      <c r="E73" s="39">
+        <v>7456.6044427470006</v>
+      </c>
+      <c r="F73" s="39">
+        <v>360.08721871178159</v>
+      </c>
+      <c r="G73" s="39">
+        <v>8046</v>
+      </c>
+      <c r="H73" s="39">
+        <v>6891.068890282877</v>
+      </c>
+      <c r="I73" s="39">
+        <v>7827.0339626292252</v>
+      </c>
+      <c r="J73" s="39">
+        <v>7741.7924999999996</v>
+      </c>
+      <c r="K73" s="39">
+        <v>7184.2945276113414</v>
+      </c>
+      <c r="L73" s="39">
+        <v>7080.4965019640822</v>
+      </c>
+      <c r="M73" s="34">
         <v>10</v>
       </c>
-      <c r="N73" s="32"/>
-    </row>
-    <row r="74" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B74" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D74" s="42">
-        <v>7269.6716630964902</v>
-      </c>
-      <c r="E74" s="42">
-        <v>7317.3501964617963</v>
-      </c>
-      <c r="F74" s="42">
-        <v>400.1176503932283</v>
-      </c>
-      <c r="G74" s="42">
-        <v>7750.3689773279848</v>
-      </c>
-      <c r="H74" s="42">
-        <v>6537.9395260694328</v>
-      </c>
-      <c r="I74" s="42">
-        <v>7698.7368977327988</v>
-      </c>
-      <c r="J74" s="42">
-        <v>7546.5145086835983</v>
-      </c>
-      <c r="K74" s="42">
-        <v>7056.9905475302603</v>
-      </c>
-      <c r="L74" s="42">
-        <v>6822.0984377059431</v>
+      <c r="D74" s="36">
+        <v>7231.8536454316436</v>
+      </c>
+      <c r="E74" s="36">
+        <v>7173.2462177510106</v>
+      </c>
+      <c r="F74" s="36">
+        <v>496.15996146420309</v>
+      </c>
+      <c r="G74" s="36">
+        <v>8065.9103591017974</v>
+      </c>
+      <c r="H74" s="36">
+        <v>6440.9771371761644</v>
+      </c>
+      <c r="I74" s="36">
+        <v>7945.3910359101792</v>
+      </c>
+      <c r="J74" s="36">
+        <v>7396.9411447196344</v>
+      </c>
+      <c r="K74" s="36">
+        <v>6970.6297880489728</v>
+      </c>
+      <c r="L74" s="36">
+        <v>6711.3419733605533</v>
       </c>
       <c r="M74" s="5">
         <v>10</v>
       </c>
-      <c r="N74" s="32"/>
-    </row>
-    <row r="75" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B75" s="35">
-        <v>46265</v>
-      </c>
-      <c r="C75" s="36" t="s">
+    </row>
+    <row r="75" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B75" s="31">
+        <v>46295</v>
+      </c>
+      <c r="C75" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="D75" s="45">
-        <v>7096.1429521679911</v>
-      </c>
-      <c r="E75" s="45">
-        <v>7040.5</v>
-      </c>
-      <c r="F75" s="45">
-        <v>541.5578881030101</v>
-      </c>
-      <c r="G75" s="45">
-        <v>7802.1267630134289</v>
-      </c>
-      <c r="H75" s="45">
-        <v>6395.9237498412849</v>
-      </c>
-      <c r="I75" s="45">
-        <v>7715.2558575953926</v>
-      </c>
-      <c r="J75" s="45">
-        <v>7616.5617092178982</v>
-      </c>
-      <c r="K75" s="45">
-        <v>6600.7482257465672</v>
-      </c>
-      <c r="L75" s="45">
-        <v>6436.4717984426761</v>
-      </c>
-      <c r="M75" s="38">
+      <c r="D75" s="39">
+        <v>7597.8931451005392</v>
+      </c>
+      <c r="E75" s="39">
+        <v>7611.1391308748862</v>
+      </c>
+      <c r="F75" s="39">
+        <v>442.40197516235679</v>
+      </c>
+      <c r="G75" s="39">
+        <v>8198.7451022090518</v>
+      </c>
+      <c r="H75" s="39">
+        <v>6941.9598298557821</v>
+      </c>
+      <c r="I75" s="39">
+        <v>8179.1745102209052</v>
+      </c>
+      <c r="J75" s="39">
+        <v>7897.1</v>
+      </c>
+      <c r="K75" s="39">
+        <v>7234.7512820716274</v>
+      </c>
+      <c r="L75" s="39">
+        <v>7070.6959829855787</v>
+      </c>
+      <c r="M75" s="34">
         <v>10</v>
       </c>
-      <c r="N75" s="32"/>
-    </row>
-    <row r="76" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B76" s="41" t="s">
+    </row>
+    <row r="76" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B76" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="C76" s="42" t="s">
+      <c r="C76" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D76" s="42">
-        <v>80358.315782740858</v>
-      </c>
-      <c r="E76" s="42">
-        <v>80340.109432809521</v>
-      </c>
-      <c r="F76" s="42">
-        <v>3855.9619956781062</v>
-      </c>
-      <c r="G76" s="42">
-        <v>86267.646593271842</v>
-      </c>
-      <c r="H76" s="42">
-        <v>74493.452105731427</v>
-      </c>
-      <c r="I76" s="42">
-        <v>83933.695859327185</v>
-      </c>
-      <c r="J76" s="42">
-        <v>83266.228826094899</v>
-      </c>
-      <c r="K76" s="42">
-        <v>77733.925619470479</v>
-      </c>
-      <c r="L76" s="42">
-        <v>75285.945210573147</v>
-      </c>
-      <c r="M76" s="43">
+      <c r="D76" s="36">
+        <v>80302.785725372509</v>
+      </c>
+      <c r="E76" s="36">
+        <v>79556.760000000009</v>
+      </c>
+      <c r="F76" s="36">
+        <v>3664.2349507222998</v>
+      </c>
+      <c r="G76" s="36">
+        <v>86280</v>
+      </c>
+      <c r="H76" s="36">
+        <v>74348.355211546033</v>
+      </c>
+      <c r="I76" s="36">
+        <v>83712.722676453632</v>
+      </c>
+      <c r="J76" s="36">
+        <v>83266.253950332772</v>
+      </c>
+      <c r="K76" s="36">
+        <v>77881.880350923457</v>
+      </c>
+      <c r="L76" s="36">
+        <v>76807.735521154609</v>
+      </c>
+      <c r="M76" s="37">
         <v>10</v>
       </c>
-      <c r="N76" s="32"/>
-    </row>
-    <row r="77" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B77" s="9"/>
       <c r="C77" s="10"/>
       <c r="D77" s="10"/>
@@ -7723,7 +7587,7 @@
       <c r="L77" s="10"/>
       <c r="M77" s="10"/>
     </row>
-    <row r="79" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="14" t="s">
         <v>27</v>
       </c>
@@ -7739,7 +7603,7 @@
       <c r="L79" s="14"/>
       <c r="M79" s="15"/>
     </row>
-    <row r="80" spans="2:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B80" s="24" t="s">
         <v>1</v>
       </c>
@@ -7777,46 +7641,45 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B81" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="33">
-        <v>15913.736253091431</v>
-      </c>
-      <c r="E81" s="33">
-        <v>16270.5</v>
-      </c>
-      <c r="F81" s="33">
-        <v>1623.8605847333381</v>
-      </c>
-      <c r="G81" s="33">
-        <v>18273.092980624231</v>
-      </c>
-      <c r="H81" s="33">
-        <v>12626.7154272928</v>
-      </c>
-      <c r="I81" s="33">
-        <v>17647.518298062419</v>
-      </c>
-      <c r="J81" s="33">
-        <v>16673.075000000001</v>
-      </c>
-      <c r="K81" s="33">
-        <v>15150</v>
-      </c>
-      <c r="L81" s="33">
-        <v>14250.07125342677</v>
+      <c r="D81" s="43">
+        <v>16135.826871685729</v>
+      </c>
+      <c r="E81" s="43">
+        <v>16374.5</v>
+      </c>
+      <c r="F81" s="43">
+        <v>2427.7183821665189</v>
+      </c>
+      <c r="G81" s="43">
+        <v>21056</v>
+      </c>
+      <c r="H81" s="43">
+        <v>11634.15244290778</v>
+      </c>
+      <c r="I81" s="43">
+        <v>17861.28206832776</v>
+      </c>
+      <c r="J81" s="43">
+        <v>17043.75</v>
+      </c>
+      <c r="K81" s="43">
+        <v>14827</v>
+      </c>
+      <c r="L81" s="43">
+        <v>14441.83782251762</v>
       </c>
       <c r="M81" s="5">
         <v>10</v>
       </c>
-      <c r="N81" s="31"/>
-    </row>
-    <row r="82" spans="2:16" ht="18.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B82" s="9"/>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
@@ -7830,8 +7693,7 @@
       <c r="L82" s="10"/>
       <c r="M82" s="10"/>
     </row>
-    <row r="83" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="14" t="s">
         <v>29</v>
       </c>
@@ -7847,7 +7709,7 @@
       <c r="L84" s="14"/>
       <c r="M84" s="15"/>
     </row>
-    <row r="85" spans="2:16" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B85" s="24" t="s">
         <v>1</v>
       </c>
@@ -7884,126 +7746,122 @@
       <c r="M85" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="N85" s="31"/>
-    </row>
-    <row r="86" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B86" s="44" t="s">
+    </row>
+    <row r="86" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B86" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="C86" s="36" t="s">
+      <c r="C86" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="D86" s="37">
-        <v>6.6913845681962414</v>
-      </c>
-      <c r="E86" s="37">
-        <v>6.6831123630373384</v>
-      </c>
-      <c r="F86" s="37">
-        <v>0.32184339150869912</v>
-      </c>
-      <c r="G86" s="37">
-        <v>7.3</v>
-      </c>
-      <c r="H86" s="37">
-        <v>6.2</v>
-      </c>
-      <c r="I86" s="37">
-        <v>7.1088588602989571</v>
-      </c>
-      <c r="J86" s="37">
-        <v>6.7</v>
-      </c>
-      <c r="K86" s="37">
-        <v>6.6150000000000002</v>
-      </c>
-      <c r="L86" s="37">
-        <v>6.29</v>
-      </c>
-      <c r="M86" s="46">
+      <c r="D86" s="33">
+        <v>7.5638078870624481</v>
+      </c>
+      <c r="E86" s="33">
+        <v>7.6</v>
+      </c>
+      <c r="F86" s="33">
+        <v>0.33040648036709708</v>
+      </c>
+      <c r="G86" s="33">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="H86" s="33">
+        <v>7.0240623644232167</v>
+      </c>
+      <c r="I86" s="33">
+        <v>7.8789999999999996</v>
+      </c>
+      <c r="J86" s="33">
+        <v>7.7940127486104087</v>
+      </c>
+      <c r="K86" s="33">
+        <v>7.35</v>
+      </c>
+      <c r="L86" s="33">
+        <v>7.1175751970260004</v>
+      </c>
+      <c r="M86" s="40">
         <v>10</v>
       </c>
-      <c r="N86" s="31"/>
-    </row>
-    <row r="87" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B87" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D87" s="4">
-        <v>7.2202895076872293</v>
+        <v>7.3136219982696771</v>
       </c>
       <c r="E87" s="4">
-        <v>7.3</v>
+        <v>7.3597714540951547</v>
       </c>
       <c r="F87" s="4">
-        <v>0.32194623085600887</v>
+        <v>0.55236279879588568</v>
       </c>
       <c r="G87" s="4">
-        <v>7.5886822345868117</v>
+        <v>8.08</v>
       </c>
       <c r="H87" s="4">
-        <v>6.4</v>
+        <v>6.274548463389519</v>
       </c>
       <c r="I87" s="4">
-        <v>7.431659781515604</v>
+        <v>7.8009999999999993</v>
       </c>
       <c r="J87" s="4">
-        <v>7.3</v>
+        <v>7.65</v>
       </c>
       <c r="K87" s="4">
         <v>7.3</v>
       </c>
       <c r="L87" s="4">
-        <v>6.94</v>
+        <v>6.470370596344214</v>
       </c>
       <c r="M87" s="5">
         <v>10</v>
       </c>
-      <c r="N87" s="31"/>
-    </row>
-    <row r="88" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B88" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="C88" s="36" t="s">
+    </row>
+    <row r="88" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B88" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C88" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="D88" s="37">
-        <v>6.9540845192427954</v>
-      </c>
-      <c r="E88" s="37">
-        <v>7.13110019097752</v>
-      </c>
-      <c r="F88" s="37">
-        <v>0.49393260274473361</v>
-      </c>
-      <c r="G88" s="37">
-        <v>7.8301336256976999</v>
-      </c>
-      <c r="H88" s="37">
-        <v>6.2885111847752126</v>
-      </c>
-      <c r="I88" s="37">
-        <v>7.31701336256977</v>
-      </c>
-      <c r="J88" s="37">
-        <v>7.2</v>
-      </c>
-      <c r="K88" s="37">
-        <v>6.55</v>
-      </c>
-      <c r="L88" s="37">
-        <v>6.2988511184775211</v>
-      </c>
-      <c r="M88" s="38">
+      <c r="D88" s="33">
+        <v>6.8647307974561427</v>
+      </c>
+      <c r="E88" s="33">
+        <v>7</v>
+      </c>
+      <c r="F88" s="33">
+        <v>0.58157836038465016</v>
+      </c>
+      <c r="G88" s="33">
+        <v>7.51</v>
+      </c>
+      <c r="H88" s="33">
+        <v>5.9985369511645477</v>
+      </c>
+      <c r="I88" s="33">
+        <v>7.5010000000000003</v>
+      </c>
+      <c r="J88" s="33">
+        <v>7.3650000000000002</v>
+      </c>
+      <c r="K88" s="33">
+        <v>6.4604814719474959</v>
+      </c>
+      <c r="L88" s="33">
+        <v>6.0641698498366416</v>
+      </c>
+      <c r="M88" s="34">
         <v>10</v>
       </c>
-      <c r="N88" s="31"/>
-    </row>
-    <row r="89" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B89" s="2" t="s">
         <v>36</v>
       </c>
@@ -8011,37 +7869,37 @@
         <v>31</v>
       </c>
       <c r="D89" s="4">
-        <v>6.7511356001973848</v>
+        <v>7.0989442415886774</v>
       </c>
       <c r="E89" s="4">
-        <v>6.65</v>
+        <v>7.3</v>
       </c>
       <c r="F89" s="4">
-        <v>0.45032804827589978</v>
+        <v>0.67558021122334144</v>
       </c>
       <c r="G89" s="4">
-        <v>7.4559554615135513</v>
+        <v>7.7077230281297604</v>
       </c>
       <c r="H89" s="4">
-        <v>5.9</v>
+        <v>5.7167676533114582</v>
       </c>
       <c r="I89" s="4">
-        <v>7.3155955461513553</v>
+        <v>7.6467723028129759</v>
       </c>
       <c r="J89" s="4">
-        <v>7.0342722550010333</v>
+        <v>7.4775</v>
       </c>
       <c r="K89" s="4">
-        <v>6.5250000000000004</v>
+        <v>7.2</v>
       </c>
       <c r="L89" s="4">
-        <v>6.44</v>
+        <v>5.9851333263321456</v>
       </c>
       <c r="M89" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="2:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B90" s="9"/>
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
@@ -8055,8 +7913,7 @@
       <c r="L90" s="9"/>
       <c r="M90" s="9"/>
     </row>
-    <row r="91" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="14" t="s">
         <v>32</v>
       </c>
@@ -8072,7 +7929,7 @@
       <c r="L92" s="14"/>
       <c r="M92" s="15"/>
     </row>
-    <row r="93" spans="2:16" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B93" s="24" t="s">
         <v>1</v>
       </c>
@@ -8109,128 +7966,120 @@
       <c r="M93" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="N93" s="31"/>
-      <c r="P93" s="31"/>
-    </row>
-    <row r="94" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B94" s="44" t="s">
+    </row>
+    <row r="94" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B94" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="C94" s="36" t="s">
+      <c r="C94" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D94" s="37">
-        <v>0.69919370341620002</v>
-      </c>
-      <c r="E94" s="37">
-        <v>0.75046167979364586</v>
-      </c>
-      <c r="F94" s="37">
-        <v>0.2137589216062131</v>
-      </c>
-      <c r="G94" s="37">
-        <v>0.9</v>
-      </c>
-      <c r="H94" s="37">
-        <v>0.15</v>
-      </c>
-      <c r="I94" s="37">
-        <v>0.81572030835945208</v>
-      </c>
-      <c r="J94" s="37">
+      <c r="D94" s="33">
+        <v>1.2550491180436341</v>
+      </c>
+      <c r="E94" s="33">
+        <v>1.23</v>
+      </c>
+      <c r="F94" s="33">
+        <v>0.33709289846551571</v>
+      </c>
+      <c r="G94" s="33">
+        <v>1.91</v>
+      </c>
+      <c r="H94" s="33">
         <v>0.8</v>
       </c>
-      <c r="K94" s="37">
-        <v>0.75</v>
-      </c>
-      <c r="L94" s="37">
-        <v>0.49619199875778619</v>
-      </c>
-      <c r="M94" s="46">
+      <c r="I94" s="33">
+        <v>1.631</v>
+      </c>
+      <c r="J94" s="33">
+        <v>1.4476227951090841</v>
+      </c>
+      <c r="K94" s="33">
+        <v>1.01</v>
+      </c>
+      <c r="L94" s="33">
+        <v>0.93499999999999994</v>
+      </c>
+      <c r="M94" s="40">
         <v>10</v>
       </c>
-      <c r="N94" s="31"/>
-      <c r="P94" s="31"/>
-    </row>
-    <row r="95" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B95" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D95" s="4">
-        <v>1.169491955674659</v>
+        <v>0.87065999110222592</v>
       </c>
       <c r="E95" s="4">
-        <v>1.0449999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="F95" s="4">
-        <v>0.43766092544896312</v>
+        <v>0.53936869777869278</v>
       </c>
       <c r="G95" s="4">
-        <v>1.970642791097021</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H95" s="4">
-        <v>0.6</v>
+        <v>0.16659991102225821</v>
       </c>
       <c r="I95" s="4">
-        <v>1.817064279109702</v>
+        <v>1.21</v>
       </c>
       <c r="J95" s="4">
-        <v>1.2904911467065521</v>
+        <v>0.96250000000000002</v>
       </c>
       <c r="K95" s="4">
-        <v>0.96497090477202763</v>
+        <v>0.61250000000000004</v>
       </c>
       <c r="L95" s="4">
-        <v>0.69</v>
+        <v>0.46665999110222578</v>
       </c>
       <c r="M95" s="5">
         <v>10</v>
       </c>
-      <c r="N95" s="31"/>
-      <c r="P95" s="31"/>
-    </row>
-    <row r="96" spans="2:16" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B96" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="C96" s="36" t="s">
+    </row>
+    <row r="96" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B96" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C96" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D96" s="37">
-        <v>0.70612465640842925</v>
-      </c>
-      <c r="E96" s="37">
-        <v>0.90500000000000003</v>
-      </c>
-      <c r="F96" s="37">
-        <v>0.33372712626231021</v>
-      </c>
-      <c r="G96" s="37">
-        <v>1</v>
-      </c>
-      <c r="H96" s="37">
-        <v>0.16659991102225821</v>
-      </c>
-      <c r="I96" s="37">
-        <v>1</v>
-      </c>
-      <c r="J96" s="37">
-        <v>0.9748907197586365</v>
-      </c>
-      <c r="K96" s="37">
-        <v>0.39500000000000002</v>
-      </c>
-      <c r="L96" s="37">
-        <v>0.28693002096206838</v>
-      </c>
-      <c r="M96" s="38">
+      <c r="D96" s="33">
+        <v>0.6581134077881361</v>
+      </c>
+      <c r="E96" s="33">
+        <v>0.7</v>
+      </c>
+      <c r="F96" s="33">
+        <v>0.20710426909198801</v>
+      </c>
+      <c r="G96" s="33">
+        <v>0.91</v>
+      </c>
+      <c r="H96" s="33">
+        <v>0.32</v>
+      </c>
+      <c r="I96" s="33">
+        <v>0.90100000000000002</v>
+      </c>
+      <c r="J96" s="33">
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="K96" s="33">
+        <v>0.52528351947034002</v>
+      </c>
+      <c r="L96" s="33">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="M96" s="34">
         <v>10</v>
       </c>
-      <c r="N96" s="31"/>
-      <c r="P96" s="31"/>
     </row>
     <row r="97" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B97" s="2" t="s">
@@ -8240,31 +8089,31 @@
         <v>34</v>
       </c>
       <c r="D97" s="4">
-        <v>2.962285633998416</v>
+        <v>3.1902560699018379</v>
       </c>
       <c r="E97" s="4">
-        <v>2.7426755893834631</v>
+        <v>3</v>
       </c>
       <c r="F97" s="4">
-        <v>0.77890860287159136</v>
+        <v>0.50447297484337539</v>
       </c>
       <c r="G97" s="4">
-        <v>4.1584456131180891</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="H97" s="4">
-        <v>1.94</v>
+        <v>2.7328036959836322</v>
       </c>
       <c r="I97" s="4">
-        <v>4.0698445613118084</v>
+        <v>4.0819999999999999</v>
       </c>
       <c r="J97" s="4">
-        <v>3.4287300871889079</v>
+        <v>3.2574999999999998</v>
       </c>
       <c r="K97" s="4">
-        <v>2.514547868207909</v>
+        <v>2.9</v>
       </c>
       <c r="L97" s="4">
-        <v>1.994</v>
+        <v>2.7570616723296348</v>
       </c>
       <c r="M97" s="5">
         <v>10</v>
@@ -8272,7 +8121,7 @@
     </row>
     <row r="98" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B98" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="10"/>
@@ -8287,9 +8136,6 @@
       <c r="M98" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:M2"/>
-  </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="41" fitToHeight="2" orientation="landscape" r:id="rId1"/>
@@ -8297,7 +8143,7 @@
     <oddFooter>&amp;C&amp;"Roboto,Normal"Página &amp;P</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="36" min="1" max="12" man="1"/>
+    <brk id="42" min="1" max="12" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -8330,17 +8176,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b80df5a0-8011-40eb-be96-4c6a59f56b6e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6b042263-e944-4dfe-97a8-6e4c84e0ae4b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004E1357DA6D65CA49A875959554824B49" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="e8f8602aebf7bbdcbcb5348c529dc11a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b80df5a0-8011-40eb-be96-4c6a59f56b6e" xmlns:ns3="6b042263-e944-4dfe-97a8-6e4c84e0ae4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a39dbf9ae3c20398b89cd584be7bda98" ns2:_="" ns3:_="">
     <xsd:import namespace="b80df5a0-8011-40eb-be96-4c6a59f56b6e"/>
@@ -8589,6 +8424,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b80df5a0-8011-40eb-be96-4c6a59f56b6e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6b042263-e944-4dfe-97a8-6e4c84e0ae4b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E4A204-179E-478B-A62E-54900BF00ECD}">
   <ds:schemaRefs>
@@ -8598,23 +8444,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB7C2FA5-1A6F-45A0-B729-06C123F95F83}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="6b042263-e944-4dfe-97a8-6e4c84e0ae4b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="b80df5a0-8011-40eb-be96-4c6a59f56b6e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89E97169-F966-43F7-97A7-EB3192694F7A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8631,4 +8460,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB7C2FA5-1A6F-45A0-B729-06C123F95F83}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="6b042263-e944-4dfe-97a8-6e4c84e0ae4b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="b80df5a0-8011-40eb-be96-4c6a59f56b6e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/public/REM/raw/REM.xlsx
+++ b/public/REM/raw/REM.xlsx
@@ -5,16 +5,16 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcranet.sharepoint.com/sites/REM/Documentos compartidos/REM/Publicación/Pagina WEB/2026/26 03 Mar/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcranet.sharepoint.com/sites/REM/Documentos compartidos/REM/Publicación/Pagina WEB/2026/26 04 Abr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="8_{563D5886-1088-4C76-92B3-92AAC244057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F895A9E-B8AD-42E1-B37C-C782B04A5BC2}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="8_{563D5886-1088-4C76-92B3-92AAC244057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6B43FD0-6DAF-4689-A6AB-67C9C96316FF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A5F0209-F8EA-4E2B-A469-F799AD0A214D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8A5F0209-F8EA-4E2B-A469-F799AD0A214D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Cuadros de resultados" sheetId="16" r:id="rId1"/>
-    <sheet name="Resultados TOP 10" sheetId="15" r:id="rId2"/>
+    <sheet name="Cuadros de resultados" sheetId="18" r:id="rId1"/>
+    <sheet name="Resultados TOP 10" sheetId="17" r:id="rId2"/>
     <sheet name="Notas Metodólogicas" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
@@ -181,38 +181,39 @@
     <t>% de la PEA; Trim. IV-27</t>
   </si>
   <si>
-    <t>Relevamiento de Expectativas de Mercado (REM)  Top 10 - BCRA - Marzo 2026</t>
-  </si>
-  <si>
-    <t>var. % i.a.; mar-27</t>
-  </si>
-  <si>
-    <t>var. % i.a.; mar-28</t>
-  </si>
-  <si>
-    <t>TNA; %; mar-27</t>
-  </si>
-  <si>
-    <t>$/USD; mar-27</t>
-  </si>
-  <si>
     <t>Trim. III-26</t>
   </si>
   <si>
-    <t>Fuente: REM - BCRA (mar-26)</t>
+    <t>Relevamiento de Expectativas de Mercado (REM)  Top 10 - BCRA - Abril 2026</t>
   </si>
   <si>
-    <t>Relevamiento de Expectativas de Mercado (REM)  - BCRA - Marzo 2026</t>
+    <t>var. % i.a.; abr-27</t>
+  </si>
+  <si>
+    <t>var. % i.a.; abr-28</t>
+  </si>
+  <si>
+    <t>TNA; %; abr-27</t>
+  </si>
+  <si>
+    <t>$/USD; abr-27</t>
+  </si>
+  <si>
+    <t>Fuente: REM - BCRA (abr-26)</t>
+  </si>
+  <si>
+    <t>Relevamiento de Expectativas de Mercado (REM)  - BCRA - Abril 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -399,7 +400,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -524,6 +525,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="2" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1866,25 +1873,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19E327E7-B164-47AD-AD5E-FA66C450386C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{355761B5-36B1-4B45-8098-A926C2568F38}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:M112"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" style="1" customWidth="1"/>
-    <col min="9" max="12" width="14.42578125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="18.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.81640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.453125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.453125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="14.453125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="18.453125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="20.5" x14ac:dyDescent="0.35">
       <c r="B2" s="11" t="s">
         <v>52</v>
       </c>
@@ -1900,7 +1907,7 @@
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
     </row>
-    <row r="3" spans="2:13" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" ht="20.5" x14ac:dyDescent="0.35">
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
@@ -1914,11 +1921,11 @@
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
       <c r="L4" s="12"/>
       <c r="M4" s="13"/>
     </row>
-    <row r="5" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B5" s="14" t="s">
         <v>0</v>
       </c>
@@ -1934,7 +1941,7 @@
       <c r="L5" s="14"/>
       <c r="M5" s="15"/>
     </row>
-    <row r="6" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B6" s="16" t="s">
         <v>1</v>
       </c>
@@ -1972,123 +1979,123 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B7" s="17">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="19">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="E7" s="19">
-        <v>3.0243883054932441</v>
+        <v>2.635915686224175</v>
       </c>
       <c r="F7" s="19">
-        <v>0.1849467560456424</v>
+        <v>0.1933541276142057</v>
       </c>
       <c r="G7" s="19">
-        <v>3.5</v>
+        <v>3.2203570721405672</v>
       </c>
       <c r="H7" s="19">
+        <v>2</v>
+      </c>
+      <c r="I7" s="19">
+        <v>2.86</v>
+      </c>
+      <c r="J7" s="19">
+        <v>2.7</v>
+      </c>
+      <c r="K7" s="19">
         <v>2.5</v>
       </c>
-      <c r="I7" s="19">
-        <v>3.2127094616641449</v>
-      </c>
-      <c r="J7" s="19">
-        <v>3.1205227197818841</v>
-      </c>
-      <c r="K7" s="19">
-        <v>2.9047014999999998</v>
-      </c>
       <c r="L7" s="19">
-        <v>2.8</v>
+        <v>2.452</v>
       </c>
       <c r="M7" s="20">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B8" s="2">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="4">
-        <v>2.6</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="E8" s="4">
-        <v>2.5705335165110199</v>
+        <v>2.2867443141716119</v>
       </c>
       <c r="F8" s="4">
-        <v>0.28318350828592759</v>
+        <v>0.39450844352126557</v>
       </c>
       <c r="G8" s="4">
-        <v>3</v>
+        <v>4.2614964887320861</v>
       </c>
       <c r="H8" s="4">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="I8" s="4">
-        <v>2.85</v>
+        <v>2.532641738593866</v>
       </c>
       <c r="J8" s="4">
-        <v>2.7123327793798881</v>
+        <v>2.4</v>
       </c>
       <c r="K8" s="4">
-        <v>2.4390036830923232</v>
+        <v>2.1</v>
       </c>
       <c r="L8" s="4">
-        <v>2.2999999999999998</v>
+        <v>1.932945170799983</v>
       </c>
       <c r="M8" s="5">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B9" s="17">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="19">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="E9" s="19">
-        <v>2.2317104245191031</v>
+        <v>2.0732407212048471</v>
       </c>
       <c r="F9" s="19">
-        <v>0.32546577421435791</v>
+        <v>0.31165656475764331</v>
       </c>
       <c r="G9" s="19">
-        <v>2.7108206923785132</v>
+        <v>2.8558870343111442</v>
       </c>
       <c r="H9" s="19">
-        <v>0.90000000000000013</v>
+        <v>1</v>
       </c>
       <c r="I9" s="19">
-        <v>2.56</v>
+        <v>2.3719999999999999</v>
       </c>
       <c r="J9" s="19">
-        <v>2.4750000000000001</v>
+        <v>2.220660403931451</v>
       </c>
       <c r="K9" s="19">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="L9" s="19">
-        <v>1.91</v>
+        <v>1.732</v>
       </c>
       <c r="M9" s="20">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>13</v>
@@ -2097,112 +2104,112 @@
         <v>2</v>
       </c>
       <c r="E10" s="4">
-        <v>2.038777101239948</v>
+        <v>2.054743329977732</v>
       </c>
       <c r="F10" s="4">
-        <v>0.31296766245883179</v>
+        <v>0.3996493780329925</v>
       </c>
       <c r="G10" s="4">
-        <v>2.7199970764476471</v>
+        <v>3.5</v>
       </c>
       <c r="H10" s="4">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I10" s="4">
-        <v>2.4750000000000001</v>
+        <v>2.452</v>
       </c>
       <c r="J10" s="4">
-        <v>2.2000000000000002</v>
+        <v>2.23</v>
       </c>
       <c r="K10" s="4">
-        <v>1.8075000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="L10" s="4">
-        <v>1.741522692820193</v>
+        <v>1.7</v>
       </c>
       <c r="M10" s="5">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B11" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="19">
-        <v>1.9750000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="E11" s="19">
-        <v>1.9688550797838209</v>
+        <v>1.8950276844426019</v>
       </c>
       <c r="F11" s="19">
-        <v>0.33896380127268821</v>
+        <v>0.35886032468214718</v>
       </c>
       <c r="G11" s="19">
-        <v>2.658120071355865</v>
+        <v>2.8</v>
       </c>
       <c r="H11" s="19">
-        <v>0.8</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="I11" s="19">
-        <v>2.4300000000000002</v>
+        <v>2.36</v>
       </c>
       <c r="J11" s="19">
-        <v>2.216236748553202</v>
+        <v>2.1</v>
       </c>
       <c r="K11" s="19">
-        <v>1.720509429572683</v>
+        <v>1.7</v>
       </c>
       <c r="L11" s="19">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="M11" s="20">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="4">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="E12" s="4">
-        <v>1.8004639144284269</v>
+        <v>1.881652139799723</v>
       </c>
       <c r="F12" s="4">
-        <v>0.33382281173407302</v>
+        <v>0.36698905341149829</v>
       </c>
       <c r="G12" s="4">
-        <v>2.5307687309620248</v>
+        <v>2.6</v>
       </c>
       <c r="H12" s="4">
-        <v>0.70000000000000007</v>
+        <v>0.6</v>
       </c>
       <c r="I12" s="4">
-        <v>2.2000000000000002</v>
+        <v>2.3220000000000001</v>
       </c>
       <c r="J12" s="4">
-        <v>2</v>
+        <v>2.0381302513900401</v>
       </c>
       <c r="K12" s="4">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="L12" s="4">
         <v>1.5</v>
       </c>
       <c r="M12" s="5">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B13" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>13</v>
@@ -2211,110 +2218,110 @@
         <v>1.8</v>
       </c>
       <c r="E13" s="19">
-        <v>1.7589175909647601</v>
+        <v>1.7747136838776449</v>
       </c>
       <c r="F13" s="19">
-        <v>0.39012938906764127</v>
+        <v>0.34574101990640049</v>
       </c>
       <c r="G13" s="19">
-        <v>2.5499999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="H13" s="19">
-        <v>0.49999999999999961</v>
+        <v>0.6</v>
       </c>
       <c r="I13" s="19">
-        <v>2.19</v>
+        <v>2.206</v>
       </c>
       <c r="J13" s="19">
-        <v>2</v>
+        <v>1.989568231212052</v>
       </c>
       <c r="K13" s="19">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="L13" s="19">
-        <v>1.307766533333333</v>
+        <v>1.44</v>
       </c>
       <c r="M13" s="20">
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="4">
-        <v>23.8</v>
+        <v>24.15</v>
       </c>
       <c r="E14" s="4">
-        <v>24.20470515697836</v>
+        <v>24.11784834817918</v>
       </c>
       <c r="F14" s="4">
-        <v>4.7176107589933221</v>
+        <v>4.1853015587247828</v>
       </c>
       <c r="G14" s="4">
-        <v>34.308126543182198</v>
+        <v>34.556839957471212</v>
       </c>
       <c r="H14" s="4">
-        <v>8</v>
+        <v>9.15</v>
       </c>
       <c r="I14" s="4">
-        <v>29.72</v>
+        <v>28.213999999999999</v>
       </c>
       <c r="J14" s="4">
-        <v>26.35</v>
+        <v>26.524999999999999</v>
       </c>
       <c r="K14" s="4">
-        <v>21.717590944072722</v>
+        <v>22.454999999999998</v>
       </c>
       <c r="L14" s="4">
-        <v>20.052833678439871</v>
+        <v>21.11</v>
       </c>
       <c r="M14" s="5">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B15" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" s="19">
-        <v>16.991709420688782</v>
+        <v>17.41</v>
       </c>
       <c r="E15" s="19">
-        <v>16.805497071043721</v>
+        <v>17.119769979325341</v>
       </c>
       <c r="F15" s="19">
-        <v>5.1232034741216923</v>
+        <v>4.1458638126479199</v>
       </c>
       <c r="G15" s="19">
-        <v>31.535102105975671</v>
+        <v>24</v>
       </c>
       <c r="H15" s="19">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I15" s="19">
-        <v>22.12</v>
+        <v>21.04</v>
       </c>
       <c r="J15" s="19">
         <v>20</v>
       </c>
       <c r="K15" s="19">
-        <v>13.362500000000001</v>
+        <v>15.23</v>
       </c>
       <c r="L15" s="19">
-        <v>10.81441352833294</v>
+        <v>12.407999999999999</v>
       </c>
       <c r="M15" s="20">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B16" s="2" t="s">
         <v>36</v>
       </c>
@@ -2322,37 +2329,37 @@
         <v>16</v>
       </c>
       <c r="D16" s="4">
-        <v>29.12968726072387</v>
+        <v>30.5</v>
       </c>
       <c r="E16" s="4">
-        <v>29.364780840856799</v>
+        <v>30.873891340780052</v>
       </c>
       <c r="F16" s="4">
-        <v>3.6426105368490691</v>
+        <v>3.258278527528184</v>
       </c>
       <c r="G16" s="4">
-        <v>37.052619716606607</v>
+        <v>40.776691402728588</v>
       </c>
       <c r="H16" s="4">
-        <v>15.8</v>
+        <v>19</v>
       </c>
       <c r="I16" s="4">
-        <v>33.650000000000013</v>
+        <v>34.883323368401292</v>
       </c>
       <c r="J16" s="4">
-        <v>31.880119821641511</v>
+        <v>32.493578750716757</v>
       </c>
       <c r="K16" s="4">
-        <v>27.131255506987049</v>
+        <v>29.364008464559021</v>
       </c>
       <c r="L16" s="4">
-        <v>26.31189266958857</v>
+        <v>28.167999999999999</v>
       </c>
       <c r="M16" s="5">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B17" s="21" t="s">
         <v>37</v>
       </c>
@@ -2360,37 +2367,37 @@
         <v>17</v>
       </c>
       <c r="D17" s="19">
-        <v>19.325995936541691</v>
+        <v>19.915550103960111</v>
       </c>
       <c r="E17" s="19">
-        <v>18.277515791214679</v>
+        <v>19.793336033059081</v>
       </c>
       <c r="F17" s="19">
-        <v>5.3529968106177064</v>
+        <v>4.4722081043372981</v>
       </c>
       <c r="G17" s="19">
-        <v>27.271455363129409</v>
+        <v>26.9</v>
       </c>
       <c r="H17" s="19">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I17" s="19">
-        <v>24.66</v>
+        <v>24.84</v>
       </c>
       <c r="J17" s="19">
-        <v>21.57732040147167</v>
+        <v>22.35</v>
       </c>
       <c r="K17" s="19">
-        <v>14.695068221793109</v>
+        <v>18.05</v>
       </c>
       <c r="L17" s="19">
-        <v>12.10568965372936</v>
+        <v>15.718</v>
       </c>
       <c r="M17" s="20">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B18" s="6" t="s">
         <v>39</v>
       </c>
@@ -2398,37 +2405,37 @@
         <v>40</v>
       </c>
       <c r="D18" s="4">
-        <v>12.7</v>
+        <v>13.340712010048231</v>
       </c>
       <c r="E18" s="4">
-        <v>12.51903116629969</v>
+        <v>12.7948750098069</v>
       </c>
       <c r="F18" s="4">
-        <v>4.6491516261838406</v>
+        <v>4.0827398420033214</v>
       </c>
       <c r="G18" s="4">
-        <v>24.34266665422302</v>
+        <v>20</v>
       </c>
       <c r="H18" s="4">
         <v>2.4</v>
       </c>
       <c r="I18" s="4">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="J18" s="4">
-        <v>15</v>
+        <v>15.035044420583271</v>
       </c>
       <c r="K18" s="4">
-        <v>9.4</v>
+        <v>10.57365283835305</v>
       </c>
       <c r="L18" s="4">
-        <v>6.7232687565027014</v>
+        <v>7.751672731833902</v>
       </c>
       <c r="M18" s="5">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B21" s="14" t="s">
         <v>18</v>
       </c>
@@ -2444,7 +2451,7 @@
       <c r="L21" s="14"/>
       <c r="M21" s="15"/>
     </row>
-    <row r="22" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B22" s="16" t="s">
         <v>1</v>
       </c>
@@ -2482,349 +2489,349 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B23" s="17">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="19">
-        <v>2.872034455593615</v>
+        <v>2.5721153846153841</v>
       </c>
       <c r="E23" s="19">
-        <v>2.8507090935547921</v>
+        <v>2.5560386731405531</v>
       </c>
       <c r="F23" s="19">
-        <v>0.35875504816816228</v>
+        <v>0.30638569540681349</v>
       </c>
       <c r="G23" s="19">
-        <v>3.5</v>
+        <v>3.4716475453420599</v>
       </c>
       <c r="H23" s="19">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="I23" s="19">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="J23" s="19">
-        <v>3.0975000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="K23" s="19">
-        <v>2.7</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="L23" s="19">
-        <v>2.4270320962481091</v>
+        <v>2.1840000000000002</v>
       </c>
       <c r="M23" s="20">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B24" s="2">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="4">
-        <v>2.423835035366698</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="E24" s="4">
-        <v>2.4731122288819232</v>
+        <v>2.3243118147546502</v>
       </c>
       <c r="F24" s="4">
-        <v>0.32744965717700708</v>
+        <v>0.32088497231341062</v>
       </c>
       <c r="G24" s="4">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="H24" s="4">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="I24" s="4">
-        <v>2.8210407240276578</v>
+        <v>2.7240000000000002</v>
       </c>
       <c r="J24" s="4">
-        <v>2.6949999999999998</v>
+        <v>2.5189618916171308</v>
       </c>
       <c r="K24" s="4">
-        <v>2.2000000000000002</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="L24" s="4">
-        <v>2.0880000000000001</v>
+        <v>1.896237932828313</v>
       </c>
       <c r="M24" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B25" s="17">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="19">
-        <v>2.2144258723347319</v>
+        <v>2.15</v>
       </c>
       <c r="E25" s="19">
-        <v>2.2257270296275031</v>
+        <v>2.1327271299301791</v>
       </c>
       <c r="F25" s="19">
-        <v>0.36215394711807902</v>
+        <v>0.32395183978377479</v>
       </c>
       <c r="G25" s="19">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="H25" s="19">
-        <v>1.3969062933345391</v>
+        <v>1.51</v>
       </c>
       <c r="I25" s="19">
-        <v>2.6355</v>
+        <v>2.6</v>
       </c>
       <c r="J25" s="19">
-        <v>2.5</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="K25" s="19">
-        <v>1.9624999999999999</v>
+        <v>1.987760003120312</v>
       </c>
       <c r="L25" s="19">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="M25" s="20">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B26" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="4">
-        <v>2.0303797468354432</v>
+        <v>2</v>
       </c>
       <c r="E26" s="4">
-        <v>2.038900710476351</v>
+        <v>2.0768936912734759</v>
       </c>
       <c r="F26" s="4">
-        <v>0.34740297760476058</v>
+        <v>0.42272587283286489</v>
       </c>
       <c r="G26" s="4">
-        <v>2.9</v>
+        <v>3.6750000000000012</v>
       </c>
       <c r="H26" s="4">
-        <v>1.18451780858147</v>
+        <v>1.28</v>
       </c>
       <c r="I26" s="4">
-        <v>2.5030000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="J26" s="4">
-        <v>2.2528125000000001</v>
+        <v>2.2793558945894778</v>
       </c>
       <c r="K26" s="4">
-        <v>1.8</v>
+        <v>1.8825022900359301</v>
       </c>
       <c r="L26" s="4">
-        <v>1.6850000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="M26" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B27" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C27" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="19">
-        <v>1.9799325218053561</v>
+        <v>1.9</v>
       </c>
       <c r="E27" s="19">
-        <v>1.958729365302746</v>
+        <v>1.9564956241261711</v>
       </c>
       <c r="F27" s="19">
-        <v>0.35642225562030672</v>
+        <v>0.34389397363868818</v>
       </c>
       <c r="G27" s="19">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="H27" s="19">
-        <v>1.2373331071824469</v>
+        <v>1.4</v>
       </c>
       <c r="I27" s="19">
-        <v>2.4</v>
+        <v>2.3997573654000761</v>
       </c>
       <c r="J27" s="19">
-        <v>2.1946093750000002</v>
+        <v>2.1016718750000001</v>
       </c>
       <c r="K27" s="19">
-        <v>1.640737315274253</v>
+        <v>1.7</v>
       </c>
       <c r="L27" s="19">
-        <v>1.593462425550719</v>
+        <v>1.6</v>
       </c>
       <c r="M27" s="20">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B28" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D28" s="4">
-        <v>1.8287186804502349</v>
+        <v>1.85</v>
       </c>
       <c r="E28" s="4">
-        <v>1.8296357958686249</v>
+        <v>1.866648694429669</v>
       </c>
       <c r="F28" s="4">
-        <v>0.31659281765883979</v>
+        <v>0.29675319451424642</v>
       </c>
       <c r="G28" s="4">
-        <v>2.3799756884428742</v>
+        <v>2.7</v>
       </c>
       <c r="H28" s="4">
-        <v>1.1676914887176051</v>
+        <v>1.2</v>
       </c>
       <c r="I28" s="4">
-        <v>2.2999999999999998</v>
+        <v>2.2440000000000002</v>
       </c>
       <c r="J28" s="4">
-        <v>2.0465742838551768</v>
+        <v>2</v>
       </c>
       <c r="K28" s="4">
-        <v>1.5844742143586441</v>
+        <v>1.632420782765087</v>
       </c>
       <c r="L28" s="4">
-        <v>1.4350000000000001</v>
+        <v>1.56</v>
       </c>
       <c r="M28" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B29" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D29" s="19">
-        <v>1.7692280427854341</v>
+        <v>1.71</v>
       </c>
       <c r="E29" s="19">
-        <v>1.75289730910135</v>
+        <v>1.7825296567894311</v>
       </c>
       <c r="F29" s="19">
-        <v>0.34088929644651128</v>
+        <v>0.28457977612416618</v>
       </c>
       <c r="G29" s="19">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="H29" s="19">
-        <v>1.0221038174869419</v>
+        <v>1</v>
       </c>
       <c r="I29" s="19">
-        <v>2.1244958324462062</v>
+        <v>2.1440000000000001</v>
       </c>
       <c r="J29" s="19">
-        <v>2</v>
+        <v>1.9161827716113551</v>
       </c>
       <c r="K29" s="19">
-        <v>1.55</v>
+        <v>1.606797367064128</v>
       </c>
       <c r="L29" s="19">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="M29" s="20">
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B30" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D30" s="4">
-        <v>23.6</v>
+        <v>24.262037811214771</v>
       </c>
       <c r="E30" s="4">
-        <v>23.88263961109234</v>
+        <v>24.29873134822914</v>
       </c>
       <c r="F30" s="4">
-        <v>4.0612835450691458</v>
+        <v>3.544919403683334</v>
       </c>
       <c r="G30" s="4">
-        <v>32.380058403899213</v>
+        <v>33.1</v>
       </c>
       <c r="H30" s="4">
-        <v>17.5</v>
+        <v>14.7</v>
       </c>
       <c r="I30" s="4">
-        <v>29.281373385152929</v>
+        <v>28.471684183960569</v>
       </c>
       <c r="J30" s="4">
-        <v>26.375</v>
+        <v>25.635000000000002</v>
       </c>
       <c r="K30" s="4">
-        <v>20.808301933471871</v>
+        <v>22.727401914941009</v>
       </c>
       <c r="L30" s="4">
-        <v>18.829889747662669</v>
+        <v>20.425000000000001</v>
       </c>
       <c r="M30" s="5">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B31" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D31" s="19">
-        <v>17.220292073826851</v>
+        <v>17.089141716136961</v>
       </c>
       <c r="E31" s="19">
-        <v>16.41716855058867</v>
+        <v>16.829381000364261</v>
       </c>
       <c r="F31" s="19">
-        <v>5.2807967693305189</v>
+        <v>4.6611306387057798</v>
       </c>
       <c r="G31" s="19">
-        <v>30.843477381352709</v>
+        <v>24</v>
       </c>
       <c r="H31" s="19">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
       <c r="I31" s="19">
-        <v>21.96</v>
+        <v>20.97</v>
       </c>
       <c r="J31" s="19">
-        <v>19</v>
+        <v>19.934455264428021</v>
       </c>
       <c r="K31" s="19">
-        <v>13.84614584526742</v>
+        <v>15.0025</v>
       </c>
       <c r="L31" s="19">
-        <v>9.9590577130974793</v>
+        <v>9.7459586381162531</v>
       </c>
       <c r="M31" s="20">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="32" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B32" s="2" t="s">
         <v>36</v>
       </c>
@@ -2832,37 +2839,37 @@
         <v>16</v>
       </c>
       <c r="D32" s="4">
-        <v>29.81683067285206</v>
+        <v>30.274718214025651</v>
       </c>
       <c r="E32" s="4">
-        <v>28.957544802450379</v>
+        <v>30.745577763395492</v>
       </c>
       <c r="F32" s="4">
-        <v>3.2531307834270189</v>
+        <v>2.8444369519580608</v>
       </c>
       <c r="G32" s="4">
-        <v>35</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="H32" s="4">
-        <v>23.7</v>
+        <v>26</v>
       </c>
       <c r="I32" s="4">
-        <v>33.06</v>
+        <v>34.429864380011168</v>
       </c>
       <c r="J32" s="4">
-        <v>31.126465259270621</v>
+        <v>32.1</v>
       </c>
       <c r="K32" s="4">
-        <v>26.188176926638029</v>
+        <v>29.05</v>
       </c>
       <c r="L32" s="4">
-        <v>24.925000000000001</v>
+        <v>27.370535381404899</v>
       </c>
       <c r="M32" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B33" s="21" t="s">
         <v>37</v>
       </c>
@@ -2870,37 +2877,37 @@
         <v>17</v>
       </c>
       <c r="D33" s="19">
-        <v>19.149999999999999</v>
+        <v>19.33084243639756</v>
       </c>
       <c r="E33" s="19">
-        <v>17.954019455492759</v>
+        <v>19.05945285543137</v>
       </c>
       <c r="F33" s="19">
-        <v>4.9783208027350296</v>
+        <v>4.5845098097321113</v>
       </c>
       <c r="G33" s="19">
-        <v>27</v>
+        <v>27.4</v>
       </c>
       <c r="H33" s="19">
         <v>3.6</v>
       </c>
       <c r="I33" s="19">
-        <v>23.2</v>
+        <v>23.88468738898807</v>
       </c>
       <c r="J33" s="19">
-        <v>21.024999999999999</v>
+        <v>22.55</v>
       </c>
       <c r="K33" s="19">
-        <v>14.6675</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="L33" s="19">
-        <v>12.306078571293289</v>
+        <v>12.96662072254998</v>
       </c>
       <c r="M33" s="20">
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B34" s="6" t="s">
         <v>39</v>
       </c>
@@ -2908,41 +2915,41 @@
         <v>40</v>
       </c>
       <c r="D34" s="4">
-        <v>12.2</v>
+        <v>12.864489487</v>
       </c>
       <c r="E34" s="4">
-        <v>12.13332791235187</v>
+        <v>12.64748023646783</v>
       </c>
       <c r="F34" s="4">
-        <v>4.6155513647839106</v>
+        <v>4.2732020259204706</v>
       </c>
       <c r="G34" s="4">
-        <v>24.227691346531159</v>
+        <v>21.9</v>
       </c>
       <c r="H34" s="4">
         <v>1.8</v>
       </c>
       <c r="I34" s="4">
-        <v>16.399999999999999</v>
+        <v>18</v>
       </c>
       <c r="J34" s="4">
-        <v>14</v>
+        <v>14.28693255274775</v>
       </c>
       <c r="K34" s="4">
-        <v>9.8000000000000007</v>
+        <v>10.896984498277339</v>
       </c>
       <c r="L34" s="4">
-        <v>7.3643137767450986</v>
+        <v>7.5049582472899523</v>
       </c>
       <c r="M34" s="5">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="36" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B36" s="22"/>
       <c r="C36" s="23"/>
     </row>
-    <row r="37" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B37" s="14" t="s">
         <v>35</v>
       </c>
@@ -2958,7 +2965,7 @@
       <c r="L37" s="14"/>
       <c r="M37" s="15"/>
     </row>
-    <row r="38" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B38" s="24" t="s">
         <v>1</v>
       </c>
@@ -2996,273 +3003,273 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B39" s="7">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="26">
-        <v>26.8</v>
+        <v>23.1</v>
       </c>
       <c r="E39" s="26">
-        <v>27.34941001296308</v>
+        <v>23.0812035107664</v>
       </c>
       <c r="F39" s="26">
-        <v>2.138073578521924</v>
+        <v>1.0704068273868279</v>
       </c>
       <c r="G39" s="4">
-        <v>35</v>
+        <v>26.4</v>
       </c>
       <c r="H39" s="4">
-        <v>24.09</v>
+        <v>21</v>
       </c>
       <c r="I39" s="4">
-        <v>29.99144243493604</v>
+        <v>24</v>
       </c>
       <c r="J39" s="4">
-        <v>28.390299323313801</v>
+        <v>23.63</v>
       </c>
       <c r="K39" s="4">
-        <v>26</v>
+        <v>22.359375</v>
       </c>
       <c r="L39" s="4">
-        <v>25.80007638888889</v>
+        <v>21.797771628441751</v>
       </c>
       <c r="M39" s="8">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="40" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B40" s="17">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C40" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="27">
-        <v>26</v>
+        <v>22.949459806961709</v>
       </c>
       <c r="E40" s="27">
-        <v>26.552797460107641</v>
+        <v>22.8105751652487</v>
       </c>
       <c r="F40" s="27">
-        <v>2.2458940662448539</v>
+        <v>1.390274547889816</v>
       </c>
       <c r="G40" s="19">
-        <v>32</v>
+        <v>25.9</v>
       </c>
       <c r="H40" s="19">
+        <v>20</v>
+      </c>
+      <c r="I40" s="19">
+        <v>25</v>
+      </c>
+      <c r="J40" s="19">
+        <v>23.34833320879472</v>
+      </c>
+      <c r="K40" s="19">
+        <v>22</v>
+      </c>
+      <c r="L40" s="19">
         <v>20.8</v>
       </c>
-      <c r="I40" s="19">
-        <v>29.857944504474901</v>
-      </c>
-      <c r="J40" s="19">
-        <v>28</v>
-      </c>
-      <c r="K40" s="19">
-        <v>25.1175</v>
-      </c>
-      <c r="L40" s="19">
-        <v>24.04</v>
-      </c>
       <c r="M40" s="20">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="41" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D41" s="26">
-        <v>25.75</v>
+        <v>22.795572916666671</v>
       </c>
       <c r="E41" s="26">
-        <v>25.89934695158999</v>
+        <v>22.88682351686229</v>
       </c>
       <c r="F41" s="26">
-        <v>2.1909120697033719</v>
+        <v>2.0106638467265219</v>
       </c>
       <c r="G41" s="4">
-        <v>30</v>
+        <v>28.515862006449311</v>
       </c>
       <c r="H41" s="4">
-        <v>20.8</v>
+        <v>19.28</v>
       </c>
       <c r="I41" s="4">
-        <v>28.841446846052051</v>
+        <v>25.4</v>
       </c>
       <c r="J41" s="4">
-        <v>27.375</v>
+        <v>24.1</v>
       </c>
       <c r="K41" s="4">
-        <v>24.327500000000001</v>
+        <v>21.8</v>
       </c>
       <c r="L41" s="4">
-        <v>23.02</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M41" s="5">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="42" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B42" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C42" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D42" s="27">
-        <v>25.9</v>
+        <v>22.550833084256119</v>
       </c>
       <c r="E42" s="27">
-        <v>25.61408595492194</v>
+        <v>22.89291460207615</v>
       </c>
       <c r="F42" s="27">
-        <v>2.4044811325923181</v>
+        <v>2.6464120904879511</v>
       </c>
       <c r="G42" s="19">
-        <v>31.246333525991151</v>
+        <v>28.72311223847257</v>
       </c>
       <c r="H42" s="19">
-        <v>19.5</v>
+        <v>17.5625353699767</v>
       </c>
       <c r="I42" s="19">
-        <v>28.832446846052051</v>
+        <v>26.2</v>
       </c>
       <c r="J42" s="19">
-        <v>27</v>
+        <v>24.7</v>
       </c>
       <c r="K42" s="19">
-        <v>24.012499999999999</v>
+        <v>21</v>
       </c>
       <c r="L42" s="19">
-        <v>22.933072916666671</v>
+        <v>19.804124938433201</v>
       </c>
       <c r="M42" s="20">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B43" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D43" s="26">
-        <v>25.055</v>
+        <v>22.3</v>
       </c>
       <c r="E43" s="26">
-        <v>25.062790122557089</v>
+        <v>22.860155519261131</v>
       </c>
       <c r="F43" s="26">
-        <v>3.1872245393245739</v>
+        <v>2.7003013418734358</v>
       </c>
       <c r="G43" s="4">
-        <v>32.022042313752323</v>
+        <v>28.6</v>
       </c>
       <c r="H43" s="4">
-        <v>16.2</v>
+        <v>16.50372630536042</v>
       </c>
       <c r="I43" s="4">
-        <v>28.6</v>
+        <v>26.5</v>
       </c>
       <c r="J43" s="4">
-        <v>27.130923635711099</v>
+        <v>24.5</v>
       </c>
       <c r="K43" s="4">
-        <v>23.15</v>
+        <v>21</v>
       </c>
       <c r="L43" s="4">
-        <v>21.064313657407411</v>
+        <v>19.8</v>
       </c>
       <c r="M43" s="5">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B44" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C44" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D44" s="27">
-        <v>24.94</v>
+        <v>22.3</v>
       </c>
       <c r="E44" s="27">
-        <v>24.705590121412161</v>
+        <v>22.593670711401959</v>
       </c>
       <c r="F44" s="27">
-        <v>3.1596727784866578</v>
+        <v>3.0597223559784812</v>
       </c>
       <c r="G44" s="19">
-        <v>29.769850060587899</v>
+        <v>29.12</v>
       </c>
       <c r="H44" s="19">
-        <v>16.2</v>
+        <v>15.444917240744131</v>
       </c>
       <c r="I44" s="19">
-        <v>28.536000000000001</v>
+        <v>26.612359975325329</v>
       </c>
       <c r="J44" s="19">
-        <v>27.326168889597771</v>
+        <v>24.1</v>
       </c>
       <c r="K44" s="19">
-        <v>22.925000000000001</v>
+        <v>20.967461005451391</v>
       </c>
       <c r="L44" s="19">
-        <v>20.841563657407409</v>
+        <v>19.067560763888888</v>
       </c>
       <c r="M44" s="20">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="45" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B45" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D45" s="26">
-        <v>22</v>
+        <v>20.7</v>
       </c>
       <c r="E45" s="26">
-        <v>21.307507522920599</v>
+        <v>20.171513953840279</v>
       </c>
       <c r="F45" s="26">
-        <v>4.2579501937468907</v>
+        <v>3.7540939031233762</v>
       </c>
       <c r="G45" s="4">
-        <v>29</v>
+        <v>27.85</v>
       </c>
       <c r="H45" s="4">
-        <v>10.7</v>
+        <v>7.8</v>
       </c>
       <c r="I45" s="4">
-        <v>26.76</v>
+        <v>24</v>
       </c>
       <c r="J45" s="4">
-        <v>24</v>
+        <v>22.074999999999999</v>
       </c>
       <c r="K45" s="4">
-        <v>19</v>
+        <v>18.0275</v>
       </c>
       <c r="L45" s="4">
-        <v>16.48</v>
+        <v>16.35178663625793</v>
       </c>
       <c r="M45" s="5">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="46" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B46" s="21" t="s">
         <v>36</v>
       </c>
@@ -3270,37 +3277,37 @@
         <v>20</v>
       </c>
       <c r="D46" s="27">
-        <v>23.4</v>
+        <v>22</v>
       </c>
       <c r="E46" s="27">
-        <v>23.072866933403422</v>
+        <v>22.12359937628058</v>
       </c>
       <c r="F46" s="27">
-        <v>4.0688357887523576</v>
+        <v>3.4620746879673479</v>
       </c>
       <c r="G46" s="19">
-        <v>30</v>
+        <v>31.09</v>
       </c>
       <c r="H46" s="19">
-        <v>12.7</v>
+        <v>14.38610817612787</v>
       </c>
       <c r="I46" s="19">
-        <v>27.95</v>
+        <v>26.627157980800192</v>
       </c>
       <c r="J46" s="19">
-        <v>25.712723911237791</v>
+        <v>24</v>
       </c>
       <c r="K46" s="19">
-        <v>21.074999999999999</v>
+        <v>20</v>
       </c>
       <c r="L46" s="19">
-        <v>17.05</v>
+        <v>19.067560763888888</v>
       </c>
       <c r="M46" s="20">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="47" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B47" s="6" t="s">
         <v>37</v>
       </c>
@@ -3311,38 +3318,38 @@
         <v>17.899999999999999</v>
       </c>
       <c r="E47" s="26">
-        <v>18.36167243959375</v>
+        <v>17.864777524989648</v>
       </c>
       <c r="F47" s="26">
-        <v>5.0458306567456814</v>
+        <v>4.7206460376698187</v>
       </c>
       <c r="G47" s="4">
-        <v>29.6</v>
+        <v>27.5</v>
       </c>
       <c r="H47" s="4">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I47" s="4">
-        <v>25</v>
+        <v>23.82330333109774</v>
       </c>
       <c r="J47" s="4">
         <v>22</v>
       </c>
       <c r="K47" s="4">
-        <v>15</v>
+        <v>14.47</v>
       </c>
       <c r="L47" s="4">
-        <v>11.902774908227769</v>
+        <v>12.46</v>
       </c>
       <c r="M47" s="5">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="48" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B48" s="22"/>
       <c r="C48" s="23"/>
     </row>
-    <row r="50" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B50" s="14" t="s">
         <v>21</v>
       </c>
@@ -3358,7 +3365,7 @@
       <c r="L50" s="14"/>
       <c r="M50" s="15"/>
     </row>
-    <row r="51" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B51" s="24" t="s">
         <v>1</v>
       </c>
@@ -3396,161 +3403,161 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B52" s="7">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D52" s="28">
-        <v>1420</v>
+        <v>1410</v>
       </c>
       <c r="E52" s="28">
-        <v>1424.951780693922</v>
+        <v>1416.863500134916</v>
       </c>
       <c r="F52" s="28">
-        <v>24.870945476118951</v>
+        <v>29.519830644725712</v>
       </c>
       <c r="G52" s="28">
-        <v>1514.1</v>
+        <v>1551.1141640000001</v>
       </c>
       <c r="H52" s="28">
-        <v>1389.17</v>
+        <v>1373</v>
       </c>
       <c r="I52" s="28">
-        <v>1454.6346372753601</v>
+        <v>1437.9442986481049</v>
       </c>
       <c r="J52" s="28">
-        <v>1431.402504110066</v>
+        <v>1425</v>
       </c>
       <c r="K52" s="28">
-        <v>1410</v>
+        <v>1401.72</v>
       </c>
       <c r="L52" s="28">
-        <v>1402.5074999999999</v>
+        <v>1389.4</v>
       </c>
       <c r="M52" s="5">
         <v>45</v>
       </c>
     </row>
-    <row r="53" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B53" s="17">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C53" s="18" t="s">
         <v>22</v>
       </c>
       <c r="D53" s="29">
-        <v>1449.176973632419</v>
+        <v>1437</v>
       </c>
       <c r="E53" s="29">
-        <v>1452.5170442135641</v>
+        <v>1441.295650977456</v>
       </c>
       <c r="F53" s="29">
-        <v>34.312222118742461</v>
+        <v>34.3013807971994</v>
       </c>
       <c r="G53" s="29">
-        <v>1551.1141640000001</v>
+        <v>1542.582429</v>
       </c>
       <c r="H53" s="29">
-        <v>1390.83</v>
+        <v>1379.33</v>
       </c>
       <c r="I53" s="29">
-        <v>1493.78</v>
+        <v>1483.342420640874</v>
       </c>
       <c r="J53" s="29">
-        <v>1463.3891522466031</v>
+        <v>1459</v>
       </c>
       <c r="K53" s="29">
-        <v>1430.168677345599</v>
+        <v>1422.5338834416859</v>
       </c>
       <c r="L53" s="29">
-        <v>1417.96</v>
+        <v>1400.8</v>
       </c>
       <c r="M53" s="20">
         <v>45</v>
       </c>
     </row>
-    <row r="54" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B54" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D54" s="28">
-        <v>1481</v>
+        <v>1460</v>
       </c>
       <c r="E54" s="28">
-        <v>1480.075003237431</v>
+        <v>1468.518375575328</v>
       </c>
       <c r="F54" s="28">
-        <v>41.329590707650979</v>
+        <v>43.259148331608593</v>
       </c>
       <c r="G54" s="28">
-        <v>1580</v>
+        <v>1572.5137340000001</v>
       </c>
       <c r="H54" s="28">
-        <v>1395.15</v>
+        <v>1386</v>
       </c>
       <c r="I54" s="28">
-        <v>1537.3015733181239</v>
+        <v>1528.637283489229</v>
       </c>
       <c r="J54" s="28">
-        <v>1500</v>
+        <v>1493.546379994777</v>
       </c>
       <c r="K54" s="28">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="L54" s="28">
-        <v>1438.0055325799999</v>
+        <v>1418.32</v>
       </c>
       <c r="M54" s="5">
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B55" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C55" s="18" t="s">
         <v>22</v>
       </c>
       <c r="D55" s="29">
-        <v>1503.5116157717389</v>
+        <v>1500</v>
       </c>
       <c r="E55" s="29">
-        <v>1510.592415862031</v>
+        <v>1507.7131637901621</v>
       </c>
       <c r="F55" s="29">
-        <v>51.801656882493901</v>
+        <v>53.894629966054502</v>
       </c>
       <c r="G55" s="29">
-        <v>1664.8959923126081</v>
+        <v>1627.375896782112</v>
       </c>
       <c r="H55" s="29">
-        <v>1418</v>
+        <v>1392</v>
       </c>
       <c r="I55" s="29">
-        <v>1571.0579759845621</v>
+        <v>1593.6</v>
       </c>
       <c r="J55" s="29">
-        <v>1534.52</v>
+        <v>1534.43</v>
       </c>
       <c r="K55" s="29">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="L55" s="29">
-        <v>1453.402671572514</v>
+        <v>1454.6953454503539</v>
       </c>
       <c r="M55" s="20">
         <v>45</v>
       </c>
     </row>
-    <row r="56" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B56" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>22</v>
@@ -3559,110 +3566,110 @@
         <v>1533</v>
       </c>
       <c r="E56" s="28">
-        <v>1547.559273125637</v>
+        <v>1546.886483291177</v>
       </c>
       <c r="F56" s="28">
-        <v>62.923625462616549</v>
+        <v>60.698836203126447</v>
       </c>
       <c r="G56" s="28">
-        <v>1764.090152332587</v>
+        <v>1708.30283798855</v>
       </c>
       <c r="H56" s="28">
-        <v>1424</v>
+        <v>1397</v>
       </c>
       <c r="I56" s="28">
-        <v>1631.8678692166729</v>
+        <v>1616.18712460698</v>
       </c>
       <c r="J56" s="28">
-        <v>1575</v>
+        <v>1585</v>
       </c>
       <c r="K56" s="28">
-        <v>1511.2775285550799</v>
+        <v>1510.41</v>
       </c>
       <c r="L56" s="28">
-        <v>1483.1620150373251</v>
+        <v>1492.1137082654991</v>
       </c>
       <c r="M56" s="5">
         <v>45</v>
       </c>
     </row>
-    <row r="57" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B57" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C57" s="18" t="s">
         <v>22</v>
       </c>
       <c r="D57" s="29">
-        <v>1571.7286296972841</v>
+        <v>1578.825</v>
       </c>
       <c r="E57" s="29">
-        <v>1584.2685703643331</v>
+        <v>1588.762421590513</v>
       </c>
       <c r="F57" s="29">
-        <v>69.586976351397283</v>
+        <v>70.469362916634893</v>
       </c>
       <c r="G57" s="29">
-        <v>1805.4423321935151</v>
+        <v>1796.143955541193</v>
       </c>
       <c r="H57" s="29">
-        <v>1428</v>
+        <v>1404</v>
       </c>
       <c r="I57" s="29">
-        <v>1669.449226601007</v>
+        <v>1683.0440270978149</v>
       </c>
       <c r="J57" s="29">
-        <v>1615.93</v>
+        <v>1621.23338496</v>
       </c>
       <c r="K57" s="29">
-        <v>1542.19</v>
+        <v>1542</v>
       </c>
       <c r="L57" s="29">
-        <v>1517.92</v>
+        <v>1518.5015806722779</v>
       </c>
       <c r="M57" s="20">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="58" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D58" s="28">
-        <v>1780</v>
+        <v>1789</v>
       </c>
       <c r="E58" s="28">
-        <v>1775.0088003771559</v>
+        <v>1785.924216785096</v>
       </c>
       <c r="F58" s="28">
-        <v>122.2262237331099</v>
+        <v>124.3433240998848</v>
       </c>
       <c r="G58" s="28">
-        <v>2111.6412191657769</v>
+        <v>2044.705388943687</v>
       </c>
       <c r="H58" s="28">
-        <v>1449</v>
+        <v>1436</v>
       </c>
       <c r="I58" s="28">
-        <v>1921.38</v>
+        <v>1959.11</v>
       </c>
       <c r="J58" s="28">
-        <v>1818.7071308558891</v>
+        <v>1866</v>
       </c>
       <c r="K58" s="28">
-        <v>1692</v>
+        <v>1702.2</v>
       </c>
       <c r="L58" s="28">
-        <v>1646.5439054595431</v>
+        <v>1657.361924210194</v>
       </c>
       <c r="M58" s="5">
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B59" s="21" t="s">
         <v>36</v>
       </c>
@@ -3670,37 +3677,37 @@
         <v>23</v>
       </c>
       <c r="D59" s="29">
-        <v>1700</v>
+        <v>1676</v>
       </c>
       <c r="E59" s="29">
-        <v>1700.094864090074</v>
+        <v>1683.691910504996</v>
       </c>
       <c r="F59" s="29">
-        <v>103.3069995854829</v>
+        <v>95.269128238098276</v>
       </c>
       <c r="G59" s="29">
-        <v>2052.6534105129131</v>
+        <v>1951.6328885343901</v>
       </c>
       <c r="H59" s="29">
-        <v>1440</v>
+        <v>1416</v>
       </c>
       <c r="I59" s="29">
-        <v>1811.597767438697</v>
+        <v>1809.7254901625181</v>
       </c>
       <c r="J59" s="29">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="K59" s="29">
-        <v>1633.9</v>
+        <v>1615</v>
       </c>
       <c r="L59" s="29">
-        <v>1598.2</v>
+        <v>1582.3224112747721</v>
       </c>
       <c r="M59" s="20">
         <v>45</v>
       </c>
     </row>
-    <row r="60" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B60" s="6" t="s">
         <v>37</v>
       </c>
@@ -3708,45 +3715,45 @@
         <v>42</v>
       </c>
       <c r="D60" s="28">
-        <v>1997</v>
+        <v>2008.89</v>
       </c>
       <c r="E60" s="28">
-        <v>1997.234967786693</v>
+        <v>2016.822883486371</v>
       </c>
       <c r="F60" s="28">
-        <v>188.272263162987</v>
+        <v>192.70956690366509</v>
       </c>
       <c r="G60" s="28">
-        <v>2446.98</v>
+        <v>2500</v>
       </c>
       <c r="H60" s="28">
-        <v>1472</v>
+        <v>1516</v>
       </c>
       <c r="I60" s="28">
-        <v>2194.439236821996</v>
+        <v>2240.4578652887872</v>
       </c>
       <c r="J60" s="28">
-        <v>2132.5333686433892</v>
+        <v>2136.0524999999998</v>
       </c>
       <c r="K60" s="28">
-        <v>1889.3904505</v>
+        <v>1886.2904504999999</v>
       </c>
       <c r="L60" s="28">
-        <v>1785.476444043964</v>
+        <v>1803.2289644252969</v>
       </c>
       <c r="M60" s="5">
         <v>42</v>
       </c>
     </row>
-    <row r="61" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B61" s="22"/>
       <c r="C61" s="23"/>
     </row>
-    <row r="62" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B62" s="22"/>
       <c r="C62" s="23"/>
     </row>
-    <row r="63" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B63" s="14" t="s">
         <v>24</v>
       </c>
@@ -3762,7 +3769,7 @@
       <c r="L63" s="14"/>
       <c r="M63" s="15"/>
     </row>
-    <row r="64" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B64" s="24" t="s">
         <v>1</v>
       </c>
@@ -3800,273 +3807,273 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B65" s="7">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D65" s="28">
-        <v>7373.4294707837016</v>
+        <v>8343</v>
       </c>
       <c r="E65" s="28">
-        <v>7389.9565611686467</v>
+        <v>8338.5850355264829</v>
       </c>
       <c r="F65" s="28">
-        <v>492.3675050999841</v>
+        <v>682.58923843594448</v>
       </c>
       <c r="G65" s="28">
-        <v>8549.019280067434</v>
+        <v>10243</v>
       </c>
       <c r="H65" s="28">
-        <v>6592.0293329552451</v>
+        <v>6874.2</v>
       </c>
       <c r="I65" s="28">
-        <v>7930.9204458632112</v>
+        <v>9184.6777501129382</v>
       </c>
       <c r="J65" s="28">
-        <v>7748.0106391172403</v>
+        <v>8750</v>
       </c>
       <c r="K65" s="28">
-        <v>6946.6011050450506</v>
+        <v>8007.5569652688546</v>
       </c>
       <c r="L65" s="28">
-        <v>6794.1344082853229</v>
+        <v>7520</v>
       </c>
       <c r="M65" s="8">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="66" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B66" s="17">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C66" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D66" s="29">
-        <v>7824.6438280531056</v>
+        <v>8705</v>
       </c>
       <c r="E66" s="29">
-        <v>7887.3326905079639</v>
+        <v>8763.0558303530743</v>
       </c>
       <c r="F66" s="29">
-        <v>709.80505217489417</v>
+        <v>717.64957571261675</v>
       </c>
       <c r="G66" s="29">
-        <v>9841</v>
+        <v>11209</v>
       </c>
       <c r="H66" s="29">
-        <v>6599.8592771050289</v>
+        <v>7307.9</v>
       </c>
       <c r="I66" s="29">
-        <v>8558.7083720474293</v>
+        <v>9467.7067489396613</v>
       </c>
       <c r="J66" s="29">
-        <v>8201.75</v>
+        <v>9130.573107253329</v>
       </c>
       <c r="K66" s="29">
-        <v>7396.8453004800031</v>
+        <v>8346.6770418812448</v>
       </c>
       <c r="L66" s="29">
-        <v>7111.7417471532008</v>
+        <v>7886.013676859091</v>
       </c>
       <c r="M66" s="20">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="67" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B67" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D67" s="28">
-        <v>8305</v>
+        <v>8500</v>
       </c>
       <c r="E67" s="28">
-        <v>8394.0163177023005</v>
+        <v>8551.0219045028589</v>
       </c>
       <c r="F67" s="28">
-        <v>620.66420750826592</v>
+        <v>634.78317758971355</v>
       </c>
       <c r="G67" s="28">
-        <v>10280</v>
+        <v>10532</v>
       </c>
       <c r="H67" s="28">
-        <v>7237</v>
+        <v>7493.3</v>
       </c>
       <c r="I67" s="28">
-        <v>9128.7719321759996</v>
+        <v>9162.3272839501278</v>
       </c>
       <c r="J67" s="28">
-        <v>8676.2256909907246</v>
+        <v>8807.9238644313737</v>
       </c>
       <c r="K67" s="28">
-        <v>7993.1065178101699</v>
+        <v>8100</v>
       </c>
       <c r="L67" s="28">
-        <v>7690.0663853193164</v>
+        <v>7825.5881359890309</v>
       </c>
       <c r="M67" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="68" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B68" s="17">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C68" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D68" s="29">
-        <v>8144.3140728156104</v>
+        <v>8501.6007590370264</v>
       </c>
       <c r="E68" s="29">
-        <v>8244.7540727112864</v>
+        <v>8599.9308402448733</v>
       </c>
       <c r="F68" s="29">
-        <v>590.79353947816662</v>
+        <v>588.75632908820535</v>
       </c>
       <c r="G68" s="29">
-        <v>9871.4532105056478</v>
+        <v>10351</v>
       </c>
       <c r="H68" s="29">
-        <v>7145.3659300725603</v>
+        <v>7617.1167626854776</v>
       </c>
       <c r="I68" s="29">
-        <v>8934.4709904721512</v>
+        <v>9205.3745688902127</v>
       </c>
       <c r="J68" s="29">
-        <v>8566.1534069645113</v>
+        <v>8912.499716370834</v>
       </c>
       <c r="K68" s="29">
-        <v>7914.5745302974537</v>
+        <v>8203.6421176626482</v>
       </c>
       <c r="L68" s="29">
-        <v>7572.1023245412043</v>
+        <v>7930</v>
       </c>
       <c r="M68" s="20">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="69" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B69" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D69" s="28">
-        <v>8301.1697387125241</v>
+        <v>8480.8604630527734</v>
       </c>
       <c r="E69" s="28">
-        <v>8330.3277629346649</v>
+        <v>8536.4806165711288</v>
       </c>
       <c r="F69" s="28">
-        <v>533.84514146992046</v>
+        <v>633.90942043470295</v>
       </c>
       <c r="G69" s="28">
-        <v>9684.456232295679</v>
+        <v>10266</v>
       </c>
       <c r="H69" s="28">
-        <v>7025.7927983071213</v>
+        <v>7500</v>
       </c>
       <c r="I69" s="28">
-        <v>8967.2487321168664</v>
+        <v>9140.0616483893264</v>
       </c>
       <c r="J69" s="28">
-        <v>8651.5712068978555</v>
+        <v>8903.3942653305494</v>
       </c>
       <c r="K69" s="28">
-        <v>7993.2</v>
+        <v>8121.76130865505</v>
       </c>
       <c r="L69" s="28">
-        <v>7845.2157480786364</v>
+        <v>7769.54</v>
       </c>
       <c r="M69" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="70" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B70" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C70" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D70" s="29">
-        <v>8309.4549927397456</v>
+        <v>8184.83</v>
       </c>
       <c r="E70" s="29">
-        <v>8302.7115078881561</v>
+        <v>8369.5679037879563</v>
       </c>
       <c r="F70" s="29">
-        <v>607.09679252927469</v>
+        <v>701.68082239020259</v>
       </c>
       <c r="G70" s="29">
-        <v>10165.564280137931</v>
+        <v>10615.8881347724</v>
       </c>
       <c r="H70" s="29">
-        <v>6983.9134992607533</v>
+        <v>7200</v>
       </c>
       <c r="I70" s="29">
-        <v>8941.677119459393</v>
+        <v>9238.4213306380207</v>
       </c>
       <c r="J70" s="29">
-        <v>8594.3392062753373</v>
+        <v>8645</v>
       </c>
       <c r="K70" s="29">
-        <v>7912.2497265119382</v>
+        <v>7889.4213540513992</v>
       </c>
       <c r="L70" s="29">
-        <v>7607.8</v>
+        <v>7629.2</v>
       </c>
       <c r="M70" s="20">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="71" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B71" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D71" s="28">
-        <v>8148.5</v>
+        <v>8200</v>
       </c>
       <c r="E71" s="28">
-        <v>8195.434140493162</v>
+        <v>8312.2424006677411</v>
       </c>
       <c r="F71" s="28">
-        <v>702.5586086430676</v>
+        <v>663.12458464705003</v>
       </c>
       <c r="G71" s="28">
-        <v>10615.8881347724</v>
+        <v>10840.359725935061</v>
       </c>
       <c r="H71" s="28">
-        <v>6617.5984820154054</v>
+        <v>7200</v>
       </c>
       <c r="I71" s="28">
-        <v>8855.2451685553078</v>
+        <v>8987.4655455267311</v>
       </c>
       <c r="J71" s="28">
-        <v>8506.1150366270376</v>
+        <v>8488</v>
       </c>
       <c r="K71" s="28">
-        <v>7685.6333709856972</v>
+        <v>7984</v>
       </c>
       <c r="L71" s="28">
-        <v>7518.9</v>
+        <v>7649.3756914236601</v>
       </c>
       <c r="M71" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="72" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B72" s="21" t="s">
         <v>36</v>
       </c>
@@ -4074,37 +4081,37 @@
         <v>25</v>
       </c>
       <c r="D72" s="29">
-        <v>93235</v>
+        <v>96056</v>
       </c>
       <c r="E72" s="29">
-        <v>94019.797084966543</v>
+        <v>97413.901386463316</v>
       </c>
       <c r="F72" s="29">
-        <v>4550.7093864988319</v>
+        <v>4670.3925697109789</v>
       </c>
       <c r="G72" s="29">
         <v>112857.8562633464</v>
       </c>
       <c r="H72" s="29">
-        <v>88000</v>
+        <v>91630.2</v>
       </c>
       <c r="I72" s="29">
-        <v>98963.97207742231</v>
+        <v>101292.7264604292</v>
       </c>
       <c r="J72" s="29">
-        <v>95410</v>
+        <v>99808.78653023293</v>
       </c>
       <c r="K72" s="29">
-        <v>91362.223222749861</v>
+        <v>94491.5</v>
       </c>
       <c r="L72" s="29">
-        <v>89741.82486386408</v>
+        <v>93252.499530829649</v>
       </c>
       <c r="M72" s="20">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="73" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B73" s="6" t="s">
         <v>37</v>
       </c>
@@ -4112,45 +4119,45 @@
         <v>25</v>
       </c>
       <c r="D73" s="28">
-        <v>98825</v>
+        <v>100808.64</v>
       </c>
       <c r="E73" s="28">
-        <v>98894.658179882928</v>
+        <v>101806.2762360107</v>
       </c>
       <c r="F73" s="28">
-        <v>5112.7278890122861</v>
+        <v>5901.0000454287347</v>
       </c>
       <c r="G73" s="28">
         <v>117406.1449877891</v>
       </c>
       <c r="H73" s="28">
-        <v>88710</v>
+        <v>89510</v>
       </c>
       <c r="I73" s="28">
-        <v>103596.0307354659</v>
+        <v>110314.7542154702</v>
       </c>
       <c r="J73" s="28">
-        <v>101329</v>
+        <v>104808.764839055</v>
       </c>
       <c r="K73" s="28">
-        <v>95610</v>
+        <v>98164.315669467993</v>
       </c>
       <c r="L73" s="28">
-        <v>92627.774220621723</v>
+        <v>95816.603995944315</v>
       </c>
       <c r="M73" s="5">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="74" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B74" s="22"/>
       <c r="C74" s="23"/>
     </row>
-    <row r="75" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B75" s="22"/>
       <c r="C75" s="23"/>
     </row>
-    <row r="76" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B76" s="14" t="s">
         <v>26</v>
       </c>
@@ -4166,7 +4173,7 @@
       <c r="L76" s="14"/>
       <c r="M76" s="15"/>
     </row>
-    <row r="77" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B77" s="24" t="s">
         <v>1</v>
       </c>
@@ -4204,273 +4211,273 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B78" s="7">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D78" s="28">
-        <v>6141.2</v>
+        <v>6515.3747431719066</v>
       </c>
       <c r="E78" s="28">
-        <v>6213.9292690527727</v>
+        <v>6567.4636451322367</v>
       </c>
       <c r="F78" s="28">
-        <v>430.60825719241848</v>
+        <v>376.06779437197292</v>
       </c>
       <c r="G78" s="28">
-        <v>7273.3638476630513</v>
+        <v>8219</v>
       </c>
       <c r="H78" s="28">
-        <v>5440.22</v>
+        <v>6000</v>
       </c>
       <c r="I78" s="28">
-        <v>6794.4194139688589</v>
+        <v>6918.6957986093184</v>
       </c>
       <c r="J78" s="28">
-        <v>6462.0857411160596</v>
+        <v>6661.95</v>
       </c>
       <c r="K78" s="28">
-        <v>5999.9701185081503</v>
+        <v>6385.02</v>
       </c>
       <c r="L78" s="28">
-        <v>5623.9708713128339</v>
+        <v>6222.1376142820764</v>
       </c>
       <c r="M78" s="8">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="79" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B79" s="17">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C79" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D79" s="29">
-        <v>6505.7397972849994</v>
+        <v>6895.5233206873454</v>
       </c>
       <c r="E79" s="29">
-        <v>6514.0814980949372</v>
+        <v>6933.6505985854692</v>
       </c>
       <c r="F79" s="29">
-        <v>402.88014275233758</v>
+        <v>482.10605929090599</v>
       </c>
       <c r="G79" s="29">
-        <v>7563</v>
+        <v>8928</v>
       </c>
       <c r="H79" s="29">
-        <v>5700</v>
+        <v>6234.9522612827004</v>
       </c>
       <c r="I79" s="29">
-        <v>7009.8198549066065</v>
+        <v>7353.9137682925057</v>
       </c>
       <c r="J79" s="29">
-        <v>6715</v>
+        <v>7080.2084767259284</v>
       </c>
       <c r="K79" s="29">
-        <v>6234.9718282521089</v>
+        <v>6621</v>
       </c>
       <c r="L79" s="29">
-        <v>6019.8148883049871</v>
+        <v>6507.8254047674427</v>
       </c>
       <c r="M79" s="20">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="80" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="80" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B80" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D80" s="28">
-        <v>6834.9847165348201</v>
+        <v>6883.5460832410581</v>
       </c>
       <c r="E80" s="28">
-        <v>6877.2217111845557</v>
+        <v>6972.7729387405216</v>
       </c>
       <c r="F80" s="28">
-        <v>462.40830679746801</v>
+        <v>458.98571613302312</v>
       </c>
       <c r="G80" s="28">
-        <v>8003</v>
+        <v>8844</v>
       </c>
       <c r="H80" s="28">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="I80" s="28">
-        <v>7441.4559701277258</v>
+        <v>7429.5693268482764</v>
       </c>
       <c r="J80" s="28">
-        <v>7105.5433820499211</v>
+        <v>7160</v>
       </c>
       <c r="K80" s="28">
-        <v>6602.1900000000014</v>
+        <v>6701</v>
       </c>
       <c r="L80" s="28">
-        <v>6340.8404688355886</v>
+        <v>6518.66</v>
       </c>
       <c r="M80" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="81" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="81" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B81" s="17">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C81" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D81" s="29">
-        <v>6926.0979228841652</v>
+        <v>7191.4350563902026</v>
       </c>
       <c r="E81" s="29">
-        <v>6915.8250956628881</v>
+        <v>7301.9476384200707</v>
       </c>
       <c r="F81" s="29">
-        <v>382.68119336842312</v>
+        <v>434.35135418764293</v>
       </c>
       <c r="G81" s="29">
-        <v>7957</v>
+        <v>8917</v>
       </c>
       <c r="H81" s="29">
-        <v>6200</v>
+        <v>6491.1334618600004</v>
       </c>
       <c r="I81" s="29">
-        <v>7372.8376717201263</v>
+        <v>7704.2986082304196</v>
       </c>
       <c r="J81" s="29">
-        <v>7046</v>
+        <v>7539</v>
       </c>
       <c r="K81" s="29">
-        <v>6668.4313739662948</v>
+        <v>7000</v>
       </c>
       <c r="L81" s="29">
-        <v>6519.6660000000002</v>
+        <v>6912.6</v>
       </c>
       <c r="M81" s="20">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="82" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="82" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B82" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D82" s="28">
-        <v>7329.413828288717</v>
+        <v>7117.6396046259979</v>
       </c>
       <c r="E82" s="28">
-        <v>7241.3391405827178</v>
+        <v>7174.8733253751698</v>
       </c>
       <c r="F82" s="28">
-        <v>409.80063376535122</v>
+        <v>482.03768348448642</v>
       </c>
       <c r="G82" s="28">
-        <v>8046</v>
+        <v>8770</v>
       </c>
       <c r="H82" s="28">
-        <v>6300</v>
+        <v>6341.1334618600004</v>
       </c>
       <c r="I82" s="28">
-        <v>7659.6978495190424</v>
+        <v>7619.9537452552449</v>
       </c>
       <c r="J82" s="28">
-        <v>7528.1504019402337</v>
+        <v>7310.4659893623957</v>
       </c>
       <c r="K82" s="28">
-        <v>7002.9471010202624</v>
+        <v>7000</v>
       </c>
       <c r="L82" s="28">
-        <v>6770.0451976759432</v>
+        <v>6598.2</v>
       </c>
       <c r="M82" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="83" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="83" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B83" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C83" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D83" s="29">
-        <v>7105.0647535137005</v>
+        <v>7214.7286574187656</v>
       </c>
       <c r="E83" s="29">
-        <v>7104.9214365139351</v>
+        <v>7318.05960639558</v>
       </c>
       <c r="F83" s="29">
-        <v>445.02443761885968</v>
+        <v>498.07675865054398</v>
       </c>
       <c r="G83" s="29">
-        <v>8065.9103591017974</v>
+        <v>8553.938094788864</v>
       </c>
       <c r="H83" s="29">
-        <v>6100</v>
+        <v>6241.1334618600004</v>
       </c>
       <c r="I83" s="29">
-        <v>7667.1684182542194</v>
+        <v>7921.5691091666549</v>
       </c>
       <c r="J83" s="29">
-        <v>7315.5371245779679</v>
+        <v>7571.618369917268</v>
       </c>
       <c r="K83" s="29">
-        <v>6922.25</v>
+        <v>7004.34</v>
       </c>
       <c r="L83" s="29">
-        <v>6555.6662104469997</v>
+        <v>6854.5730885437642</v>
       </c>
       <c r="M83" s="20">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="84" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="84" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B84" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D84" s="28">
-        <v>7322.5173998828859</v>
+        <v>7257</v>
       </c>
       <c r="E84" s="28">
-        <v>7235.8252554080036</v>
+        <v>7281.5785937608707</v>
       </c>
       <c r="F84" s="28">
-        <v>540.37431961517586</v>
+        <v>497.5536553222949</v>
       </c>
       <c r="G84" s="28">
-        <v>8204.8018404735867</v>
+        <v>8323</v>
       </c>
       <c r="H84" s="28">
-        <v>5900</v>
+        <v>6141.1334618600004</v>
       </c>
       <c r="I84" s="28">
-        <v>7873.9820601273077</v>
+        <v>7928.0737483449448</v>
       </c>
       <c r="J84" s="28">
-        <v>7569.7687328486873</v>
+        <v>7500</v>
       </c>
       <c r="K84" s="28">
-        <v>6856.6356100896955</v>
+        <v>7014.45</v>
       </c>
       <c r="L84" s="28">
-        <v>6584.1617612913651</v>
+        <v>6657.099765955646</v>
       </c>
       <c r="M84" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="85" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="85" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B85" s="21" t="s">
         <v>36</v>
       </c>
@@ -4478,37 +4485,37 @@
         <v>25</v>
       </c>
       <c r="D85" s="29">
-        <v>79120.991314693369</v>
+        <v>79550</v>
       </c>
       <c r="E85" s="29">
-        <v>79224.573811124952</v>
+        <v>79820.874328910199</v>
       </c>
       <c r="F85" s="29">
-        <v>3488.4377876049448</v>
+        <v>3479.057366162489</v>
       </c>
       <c r="G85" s="29">
-        <v>86280</v>
+        <v>92219.933626389844</v>
       </c>
       <c r="H85" s="29">
-        <v>70844</v>
+        <v>74145</v>
       </c>
       <c r="I85" s="29">
-        <v>83288.338600443691</v>
+        <v>83261.928958718461</v>
       </c>
       <c r="J85" s="29">
-        <v>81000</v>
+        <v>80844.615543384891</v>
       </c>
       <c r="K85" s="29">
-        <v>77443.599366499984</v>
+        <v>77789.352089120497</v>
       </c>
       <c r="L85" s="29">
-        <v>75000</v>
+        <v>76310.399999999994</v>
       </c>
       <c r="M85" s="20">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="86" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="86" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B86" s="6" t="s">
         <v>37</v>
       </c>
@@ -4516,37 +4523,37 @@
         <v>25</v>
       </c>
       <c r="D86" s="28">
-        <v>85000</v>
+        <v>84770.076799999995</v>
       </c>
       <c r="E86" s="28">
-        <v>84573.421361730521</v>
+        <v>84512.735764973826</v>
       </c>
       <c r="F86" s="28">
-        <v>5260.5251158121418</v>
+        <v>5165.66582474391</v>
       </c>
       <c r="G86" s="28">
-        <v>94510</v>
+        <v>97083.031782684106</v>
       </c>
       <c r="H86" s="28">
-        <v>69250</v>
+        <v>72350</v>
       </c>
       <c r="I86" s="28">
-        <v>91395.187858085279</v>
+        <v>90007.820606215799</v>
       </c>
       <c r="J86" s="28">
-        <v>87000</v>
+        <v>86561.261359331373</v>
       </c>
       <c r="K86" s="28">
-        <v>82695</v>
+        <v>83021.875</v>
       </c>
       <c r="L86" s="28">
-        <v>78582</v>
+        <v>77300</v>
       </c>
       <c r="M86" s="5">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="87" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="87" spans="2:13" ht="18" x14ac:dyDescent="0.4">
       <c r="B87" s="9"/>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
@@ -4560,7 +4567,7 @@
       <c r="L87" s="10"/>
       <c r="M87" s="10"/>
     </row>
-    <row r="89" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B89" s="14" t="s">
         <v>27</v>
       </c>
@@ -4576,7 +4583,7 @@
       <c r="L89" s="14"/>
       <c r="M89" s="15"/>
     </row>
-    <row r="90" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B90" s="24" t="s">
         <v>1</v>
       </c>
@@ -4614,83 +4621,83 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B91" s="21" t="s">
         <v>36</v>
       </c>
       <c r="C91" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D91" s="29">
-        <v>16000</v>
-      </c>
-      <c r="E91" s="29">
-        <v>15661.112283935619</v>
-      </c>
-      <c r="F91" s="29">
-        <v>2337.594735785749</v>
-      </c>
-      <c r="G91" s="29">
+      <c r="D91" s="44">
+        <v>15900</v>
+      </c>
+      <c r="E91" s="44">
+        <v>15646.10522455944</v>
+      </c>
+      <c r="F91" s="44">
+        <v>2434.530548298173</v>
+      </c>
+      <c r="G91" s="44">
         <v>21056</v>
       </c>
-      <c r="H91" s="29">
+      <c r="H91" s="44">
         <v>9000</v>
       </c>
-      <c r="I91" s="29">
-        <v>17968.029600000002</v>
-      </c>
-      <c r="J91" s="29">
-        <v>16861.58611150815</v>
-      </c>
-      <c r="K91" s="29">
-        <v>14874</v>
-      </c>
-      <c r="L91" s="29">
-        <v>11927</v>
+      <c r="I91" s="44">
+        <v>18626.440425282239</v>
+      </c>
+      <c r="J91" s="44">
+        <v>17011.589536395019</v>
+      </c>
+      <c r="K91" s="44">
+        <v>15000</v>
+      </c>
+      <c r="L91" s="44">
+        <v>11953.6</v>
       </c>
       <c r="M91" s="20">
         <v>39</v>
       </c>
     </row>
-    <row r="92" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B92" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D92" s="28">
-        <v>19950</v>
-      </c>
-      <c r="E92" s="28">
-        <v>18779.39801059278</v>
-      </c>
-      <c r="F92" s="28">
-        <v>3617.8658809494559</v>
-      </c>
-      <c r="G92" s="28">
-        <v>23064</v>
-      </c>
-      <c r="H92" s="28">
+      <c r="D92" s="45">
+        <v>20000</v>
+      </c>
+      <c r="E92" s="45">
+        <v>18904.805407802629</v>
+      </c>
+      <c r="F92" s="45">
+        <v>3648.2621509496271</v>
+      </c>
+      <c r="G92" s="45">
+        <v>23700</v>
+      </c>
+      <c r="H92" s="45">
         <v>5000</v>
       </c>
-      <c r="I92" s="28">
-        <v>22291.824228030058</v>
-      </c>
-      <c r="J92" s="28">
-        <v>20718.75</v>
-      </c>
-      <c r="K92" s="28">
-        <v>17583</v>
-      </c>
-      <c r="L92" s="28">
-        <v>14746.6</v>
+      <c r="I92" s="45">
+        <v>22307.205999999998</v>
+      </c>
+      <c r="J92" s="45">
+        <v>20922.871474548101</v>
+      </c>
+      <c r="K92" s="45">
+        <v>17254.933406915359</v>
+      </c>
+      <c r="L92" s="45">
+        <v>15425</v>
       </c>
       <c r="M92" s="5">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="93" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="93" spans="2:13" ht="18" x14ac:dyDescent="0.4">
       <c r="B93" s="9"/>
       <c r="C93" s="10"/>
       <c r="D93" s="10"/>
@@ -4704,7 +4711,7 @@
       <c r="L93" s="10"/>
       <c r="M93" s="10"/>
     </row>
-    <row r="95" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B95" s="14" t="s">
         <v>29</v>
       </c>
@@ -4720,7 +4727,7 @@
       <c r="L95" s="14"/>
       <c r="M95" s="15"/>
     </row>
-    <row r="96" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B96" s="24" t="s">
         <v>1</v>
       </c>
@@ -4758,7 +4765,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="97" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B97" s="7" t="s">
         <v>38</v>
       </c>
@@ -4766,37 +4773,37 @@
         <v>30</v>
       </c>
       <c r="D97" s="4">
-        <v>7.6</v>
+        <v>7.65</v>
       </c>
       <c r="E97" s="4">
-        <v>7.6175248557677797</v>
+        <v>7.7675812381125748</v>
       </c>
       <c r="F97" s="4">
-        <v>0.44041119118483057</v>
+        <v>0.46621523934897569</v>
       </c>
       <c r="G97" s="4">
-        <v>8.9</v>
+        <v>8.94</v>
       </c>
       <c r="H97" s="4">
         <v>6.5</v>
       </c>
       <c r="I97" s="4">
-        <v>8.1580000000000013</v>
+        <v>8.4</v>
       </c>
       <c r="J97" s="4">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="K97" s="4">
-        <v>7.3989200616030359</v>
+        <v>7.5</v>
       </c>
       <c r="L97" s="4">
-        <v>7.1567793070557864</v>
+        <v>7.4391360492824292</v>
       </c>
       <c r="M97" s="8">
         <v>35</v>
       </c>
     </row>
-    <row r="98" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B98" s="17" t="s">
         <v>43</v>
       </c>
@@ -4804,75 +4811,75 @@
         <v>30</v>
       </c>
       <c r="D98" s="19">
-        <v>7.4597714540951543</v>
+        <v>7.6</v>
       </c>
       <c r="E98" s="19">
-        <v>7.454581643810859</v>
+        <v>7.6207604357961332</v>
       </c>
       <c r="F98" s="19">
-        <v>0.53653238622025157</v>
+        <v>0.45977162928726478</v>
       </c>
       <c r="G98" s="19">
-        <v>8.6</v>
+        <v>8.64</v>
       </c>
       <c r="H98" s="19">
-        <v>6.274548463389519</v>
+        <v>6.4</v>
       </c>
       <c r="I98" s="19">
-        <v>8.1700171544649756</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="J98" s="19">
-        <v>7.7925000000000004</v>
+        <v>7.9361285530051564</v>
       </c>
       <c r="K98" s="19">
-        <v>7.1051548217512774</v>
+        <v>7.3</v>
       </c>
       <c r="L98" s="19">
-        <v>6.86</v>
+        <v>7.2</v>
       </c>
       <c r="M98" s="20">
         <v>34</v>
       </c>
     </row>
-    <row r="99" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B99" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D99" s="4">
-        <v>7.15</v>
+        <v>7.2826194495099692</v>
       </c>
       <c r="E99" s="4">
-        <v>7.159166124393801</v>
+        <v>7.3309184407739929</v>
       </c>
       <c r="F99" s="4">
-        <v>0.6024273319589829</v>
+        <v>0.52069167424193796</v>
       </c>
       <c r="G99" s="4">
         <v>8.6</v>
       </c>
       <c r="H99" s="4">
-        <v>5.9985369511645477</v>
+        <v>6.2</v>
       </c>
       <c r="I99" s="4">
-        <v>7.7223176028971006</v>
+        <v>7.8879999999999999</v>
       </c>
       <c r="J99" s="4">
-        <v>7.5075000000000003</v>
+        <v>7.6750000000000007</v>
       </c>
       <c r="K99" s="4">
-        <v>6.8250000000000002</v>
+        <v>6.9927860518324536</v>
       </c>
       <c r="L99" s="4">
-        <v>6.46311604048433</v>
+        <v>6.8</v>
       </c>
       <c r="M99" s="5">
         <v>34</v>
       </c>
     </row>
-    <row r="100" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B100" s="21" t="s">
         <v>36</v>
       </c>
@@ -4880,37 +4887,37 @@
         <v>31</v>
       </c>
       <c r="D100" s="19">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="E100" s="19">
-        <v>7.2605381405330647</v>
+        <v>7.4627846236821922</v>
       </c>
       <c r="F100" s="19">
-        <v>0.74189228030908738</v>
+        <v>0.58331178698971209</v>
       </c>
       <c r="G100" s="19">
         <v>9</v>
       </c>
       <c r="H100" s="19">
-        <v>5.7167676533114582</v>
+        <v>6</v>
       </c>
       <c r="I100" s="19">
-        <v>7.9565296545939894</v>
+        <v>7.9369790615995601</v>
       </c>
       <c r="J100" s="19">
-        <v>7.7</v>
+        <v>7.75</v>
       </c>
       <c r="K100" s="19">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="L100" s="19">
-        <v>6.330000000000001</v>
+        <v>7</v>
       </c>
       <c r="M100" s="20">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="101" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="101" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B101" s="6" t="s">
         <v>37</v>
       </c>
@@ -4918,37 +4925,37 @@
         <v>44</v>
       </c>
       <c r="D101" s="4">
-        <v>7.0230618385449306</v>
+        <v>7.35</v>
       </c>
       <c r="E101" s="4">
-        <v>7.1267666280723017</v>
+        <v>7.3659148337833944</v>
       </c>
       <c r="F101" s="4">
-        <v>1.087072076713115</v>
+        <v>0.92176436158817854</v>
       </c>
       <c r="G101" s="4">
         <v>10</v>
       </c>
       <c r="H101" s="4">
-        <v>5.0678975151484691</v>
+        <v>5.9</v>
       </c>
       <c r="I101" s="4">
-        <v>8.08</v>
+        <v>8.1665985707465083</v>
       </c>
       <c r="J101" s="4">
-        <v>7.64</v>
+        <v>7.8713480242112146</v>
       </c>
       <c r="K101" s="4">
+        <v>6.7249999999999996</v>
+      </c>
+      <c r="L101" s="4">
         <v>6.5</v>
       </c>
-      <c r="L101" s="4">
-        <v>5.74</v>
-      </c>
       <c r="M101" s="5">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="102" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="102" spans="2:13" ht="18" x14ac:dyDescent="0.4">
       <c r="B102" s="9"/>
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
@@ -4962,7 +4969,7 @@
       <c r="L102" s="9"/>
       <c r="M102" s="9"/>
     </row>
-    <row r="104" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B104" s="14" t="s">
         <v>32</v>
       </c>
@@ -4978,7 +4985,7 @@
       <c r="L104" s="14"/>
       <c r="M104" s="15"/>
     </row>
-    <row r="105" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B105" s="24" t="s">
         <v>1</v>
       </c>
@@ -5016,7 +5023,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B106" s="21" t="s">
         <v>38</v>
       </c>
@@ -5024,37 +5031,37 @@
         <v>33</v>
       </c>
       <c r="D106" s="19">
-        <v>1.290491180436337</v>
+        <v>0.26009201326585729</v>
       </c>
       <c r="E106" s="19">
-        <v>1.2235234860201549</v>
+        <v>0.28569149363916541</v>
       </c>
       <c r="F106" s="19">
-        <v>0.46739766137869038</v>
+        <v>0.473322620216655</v>
       </c>
       <c r="G106" s="19">
-        <v>2.271484024092052</v>
+        <v>1.29</v>
       </c>
       <c r="H106" s="19">
-        <v>0.2</v>
+        <v>-0.84115308514218778</v>
       </c>
       <c r="I106" s="19">
-        <v>1.784309194955721</v>
+        <v>1</v>
       </c>
       <c r="J106" s="19">
-        <v>1.585387299076801</v>
+        <v>0.50041325000000003</v>
       </c>
       <c r="K106" s="19">
-        <v>0.8</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="L106" s="19">
-        <v>0.69599999999999995</v>
+        <v>-0.2</v>
       </c>
       <c r="M106" s="20">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="107" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="107" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B107" s="6" t="s">
         <v>43</v>
       </c>
@@ -5062,75 +5069,75 @@
         <v>33</v>
       </c>
       <c r="D107" s="4">
+        <v>1.04</v>
+      </c>
+      <c r="E107" s="4">
+        <v>1.0627487319688449</v>
+      </c>
+      <c r="F107" s="4">
+        <v>0.6454254473601434</v>
+      </c>
+      <c r="G107" s="4">
+        <v>2.792173544141519</v>
+      </c>
+      <c r="H107" s="4">
+        <v>-0.3</v>
+      </c>
+      <c r="I107" s="4">
+        <v>1.8380000000000001</v>
+      </c>
+      <c r="J107" s="4">
+        <v>1.4796823835457229</v>
+      </c>
+      <c r="K107" s="4">
         <v>0.8</v>
       </c>
-      <c r="E107" s="4">
-        <v>0.77863357224919305</v>
-      </c>
-      <c r="F107" s="4">
-        <v>0.47362986739561952</v>
-      </c>
-      <c r="G107" s="4">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="H107" s="4">
-        <v>-0.28000000000000003</v>
-      </c>
-      <c r="I107" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="J107" s="4">
-        <v>1.002797734563043</v>
-      </c>
-      <c r="K107" s="4">
-        <v>0.5</v>
-      </c>
       <c r="L107" s="4">
-        <v>0.27339109477527251</v>
+        <v>0.27300000000000002</v>
       </c>
       <c r="M107" s="5">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="108" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="108" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B108" s="21" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C108" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D108" s="19">
-        <v>0.70176856717751868</v>
+        <v>0.92005568568728213</v>
       </c>
       <c r="E108" s="19">
-        <v>0.67022639902541703</v>
+        <v>0.89722495230496058</v>
       </c>
       <c r="F108" s="19">
-        <v>0.398438606054551</v>
+        <v>0.48393406637147662</v>
       </c>
       <c r="G108" s="19">
-        <v>1.305306133169726</v>
+        <v>1.777053734930933</v>
       </c>
       <c r="H108" s="19">
-        <v>-0.50915971381411129</v>
+        <v>-0.7</v>
       </c>
       <c r="I108" s="19">
-        <v>1.04</v>
+        <v>1.406783782280008</v>
       </c>
       <c r="J108" s="19">
-        <v>0.91</v>
+        <v>1.2778005692386349</v>
       </c>
       <c r="K108" s="19">
-        <v>0.40643674044333888</v>
+        <v>0.7</v>
       </c>
       <c r="L108" s="19">
-        <v>0.22</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="M108" s="20">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="109" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="109" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B109" s="6" t="s">
         <v>36</v>
       </c>
@@ -5138,37 +5145,37 @@
         <v>34</v>
       </c>
       <c r="D109" s="4">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="E109" s="4">
-        <v>3.2372963012560612</v>
+        <v>2.6950801638259092</v>
       </c>
       <c r="F109" s="4">
-        <v>0.66293886197448693</v>
+        <v>0.80066704232326469</v>
       </c>
       <c r="G109" s="4">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="H109" s="4">
-        <v>1.1100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="I109" s="4">
-        <v>4.0640000000000001</v>
+        <v>3.69</v>
       </c>
       <c r="J109" s="4">
-        <v>3.7</v>
+        <v>3.2524999999999999</v>
       </c>
       <c r="K109" s="4">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="L109" s="4">
-        <v>2.706560739196727</v>
+        <v>1.477721795899285</v>
       </c>
       <c r="M109" s="5">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="110" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="110" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B110" s="21" t="s">
         <v>37</v>
       </c>
@@ -5179,34 +5186,34 @@
         <v>3.1</v>
       </c>
       <c r="E110" s="19">
-        <v>3.1211426659240069</v>
+        <v>3.0715906517504741</v>
       </c>
       <c r="F110" s="19">
-        <v>0.68057136754235914</v>
+        <v>0.75417788846342315</v>
       </c>
       <c r="G110" s="19">
-        <v>4.5</v>
+        <v>4.6553778093723297</v>
       </c>
       <c r="H110" s="19">
-        <v>1.6985474026730121</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I110" s="19">
-        <v>3.8382977658669928</v>
+        <v>3.8564928332416142</v>
       </c>
       <c r="J110" s="19">
-        <v>3.7</v>
+        <v>3.5049999999999999</v>
       </c>
       <c r="K110" s="19">
-        <v>2.6856562299519511</v>
+        <v>2.65</v>
       </c>
       <c r="L110" s="19">
         <v>2</v>
       </c>
       <c r="M110" s="20">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="111" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="111" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B111" s="6" t="s">
         <v>39</v>
       </c>
@@ -5214,37 +5221,37 @@
         <v>34</v>
       </c>
       <c r="D111" s="4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="E111" s="4">
-        <v>3.1257917222901268</v>
+        <v>3.1028544945922261</v>
       </c>
       <c r="F111" s="4">
-        <v>0.7743526756534751</v>
+        <v>0.66179634875555315</v>
       </c>
       <c r="G111" s="4">
         <v>5</v>
       </c>
       <c r="H111" s="4">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="I111" s="4">
-        <v>3.98</v>
+        <v>3.66</v>
       </c>
       <c r="J111" s="4">
-        <v>3.5127268385737831</v>
+        <v>3.4866756333824518</v>
       </c>
       <c r="K111" s="4">
-        <v>2.7988234540929628</v>
+        <v>2.795293816371851</v>
       </c>
       <c r="L111" s="4">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="M111" s="5">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="112" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="112" spans="2:13" ht="18" x14ac:dyDescent="0.4">
       <c r="B112" s="9" t="s">
         <v>51</v>
       </c>
@@ -5274,26 +5281,26 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57923761-BB78-4562-94B9-0D392E6CF52E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A6659E5-89E1-4C5B-8121-B7733FE1BDE9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:M98"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" style="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" style="1" customWidth="1"/>
-    <col min="9" max="12" width="14.42578125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="18.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.81640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.453125" style="1" customWidth="1"/>
+    <col min="6" max="7" width="14.453125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.453125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="14.453125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="18.453125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -5307,7 +5314,7 @@
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
     </row>
-    <row r="3" spans="2:13" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" ht="20.5" x14ac:dyDescent="0.35">
       <c r="B3" s="30"/>
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
@@ -5321,11 +5328,11 @@
       <c r="L3" s="30"/>
       <c r="M3" s="30"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
       <c r="L4" s="12"/>
       <c r="M4" s="13"/>
     </row>
-    <row r="5" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="14" t="s">
         <v>0</v>
       </c>
@@ -5341,7 +5348,7 @@
       <c r="L5" s="14"/>
       <c r="M5" s="15"/>
     </row>
-    <row r="6" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B6" s="16" t="s">
         <v>1</v>
       </c>
@@ -5379,311 +5386,311 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B7" s="2">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="4">
-        <v>3.0701158267483639</v>
+        <v>2.6662500660194182</v>
       </c>
       <c r="E7" s="4">
-        <v>3.0249999999999999</v>
+        <v>2.65</v>
       </c>
       <c r="F7" s="4">
-        <v>0.2123213558184163</v>
+        <v>0.13126120168992619</v>
       </c>
       <c r="G7" s="4">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="H7" s="4">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="I7" s="4">
-        <v>3.32</v>
+        <v>2.81</v>
       </c>
       <c r="J7" s="4">
-        <v>3.1749999999999998</v>
+        <v>2.7524999999999999</v>
       </c>
       <c r="K7" s="4">
-        <v>2.912789566870909</v>
+        <v>2.594375495145631</v>
       </c>
       <c r="L7" s="4">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="M7" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B8" s="31">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C8" s="32" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="33">
-        <v>2.6747149849625291</v>
+        <v>2.3747200205195869</v>
       </c>
       <c r="E8" s="33">
-        <v>2.6749999999999998</v>
+        <v>2.3836001025979372</v>
       </c>
       <c r="F8" s="33">
-        <v>0.19341516474431919</v>
+        <v>0.28598466410201712</v>
       </c>
       <c r="G8" s="33">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="H8" s="33">
+        <v>1.73</v>
+      </c>
+      <c r="I8" s="33">
+        <v>2.62</v>
+      </c>
+      <c r="J8" s="33">
+        <v>2.5375000000000001</v>
+      </c>
+      <c r="K8" s="33">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I8" s="33">
-        <v>2.82</v>
-      </c>
-      <c r="J8" s="33">
-        <v>2.8</v>
-      </c>
-      <c r="K8" s="33">
-        <v>2.5978623872189681</v>
-      </c>
       <c r="L8" s="33">
-        <v>2.48</v>
+        <v>2.153</v>
       </c>
       <c r="M8" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="4">
-        <v>2.5122548589946279</v>
+        <v>2.2629303440086561</v>
       </c>
       <c r="E9" s="4">
-        <v>2.5</v>
+        <v>2.249651720043282</v>
       </c>
       <c r="F9" s="4">
-        <v>0.1222674617534809</v>
+        <v>0.16412816077422199</v>
       </c>
       <c r="G9" s="4">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="H9" s="4">
-        <v>2.2999999999999998</v>
+        <v>2</v>
       </c>
       <c r="I9" s="4">
-        <v>2.7010000000000001</v>
+        <v>2.42</v>
       </c>
       <c r="J9" s="4">
-        <v>2.5150000000000001</v>
+        <v>2.3224999999999998</v>
       </c>
       <c r="K9" s="4">
-        <v>2.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="L9" s="4">
-        <v>2.383293730951654</v>
+        <v>2.09</v>
       </c>
       <c r="M9" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B10" s="31">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C10" s="32" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="33">
-        <v>2.261807248882937</v>
+        <v>2.3748584452880128</v>
       </c>
       <c r="E10" s="33">
-        <v>2.2290362444146892</v>
+        <v>2.3050000000000002</v>
       </c>
       <c r="F10" s="33">
-        <v>0.19543997481865941</v>
+        <v>0.4497483632310465</v>
       </c>
       <c r="G10" s="33">
-        <v>2.5099999999999998</v>
+        <v>3.5</v>
       </c>
       <c r="H10" s="33">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="I10" s="33">
-        <v>2.5009999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J10" s="33">
-        <v>2.4375</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="K10" s="33">
-        <v>2.125</v>
+        <v>2.2289383396600959</v>
       </c>
       <c r="L10" s="33">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="M10" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="4">
-        <v>2.2503550373156398</v>
+        <v>2.0918354473469321</v>
       </c>
       <c r="E11" s="4">
-        <v>2.3317751865781999</v>
+        <v>2.105</v>
       </c>
       <c r="F11" s="4">
-        <v>0.25000896365518732</v>
+        <v>0.35028088530588791</v>
       </c>
       <c r="G11" s="4">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="H11" s="4">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="I11" s="4">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="J11" s="4">
-        <v>2.4849999999999999</v>
+        <v>2.1870886183673308</v>
       </c>
       <c r="K11" s="4">
-        <v>2</v>
+        <v>1.925</v>
       </c>
       <c r="L11" s="4">
-        <v>1.99</v>
+        <v>1.752</v>
       </c>
       <c r="M11" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B12" s="31">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C12" s="32" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="33">
-        <v>1.981237393480539</v>
+        <v>2.074813025139004</v>
       </c>
       <c r="E12" s="33">
-        <v>2.04</v>
+        <v>2.0190651256950201</v>
       </c>
       <c r="F12" s="33">
-        <v>0.25558376474033889</v>
+        <v>0.29914396919777148</v>
       </c>
       <c r="G12" s="33">
-        <v>2.3199999999999998</v>
+        <v>2.57</v>
       </c>
       <c r="H12" s="33">
         <v>1.5</v>
       </c>
       <c r="I12" s="33">
-        <v>2.2120000000000002</v>
+        <v>2.3540000000000001</v>
       </c>
       <c r="J12" s="33">
-        <v>2.178093483701347</v>
+        <v>2.2825000000000002</v>
       </c>
       <c r="K12" s="33">
-        <v>1.825</v>
+        <v>2</v>
       </c>
       <c r="L12" s="33">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="M12" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="4">
-        <v>1.9609879349276049</v>
+        <v>1.978602809014812</v>
       </c>
       <c r="E13" s="4">
-        <v>2</v>
+        <v>1.978014045074064</v>
       </c>
       <c r="F13" s="4">
-        <v>0.26982935971678962</v>
+        <v>0.2275119364476548</v>
       </c>
       <c r="G13" s="4">
-        <v>2.42</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H13" s="4">
         <v>1.5</v>
       </c>
       <c r="I13" s="4">
-        <v>2.2669999999999999</v>
+        <v>2.2189999999999999</v>
       </c>
       <c r="J13" s="4">
-        <v>2.0849698373190129</v>
+        <v>2.1150000000000002</v>
       </c>
       <c r="K13" s="4">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="L13" s="4">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="M13" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B14" s="31" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="33">
-        <v>26.761746881794341</v>
+        <v>26.505980245873481</v>
       </c>
       <c r="E14" s="33">
-        <v>26.1</v>
+        <v>26.934781812296091</v>
       </c>
       <c r="F14" s="33">
-        <v>3.4383631252434701</v>
+        <v>2.09153173781701</v>
       </c>
       <c r="G14" s="33">
-        <v>32.35</v>
+        <v>29.71</v>
       </c>
       <c r="H14" s="33">
-        <v>20.100000000000001</v>
+        <v>22.5</v>
       </c>
       <c r="I14" s="33">
-        <v>30.055</v>
+        <v>28.405000000000001</v>
       </c>
       <c r="J14" s="33">
-        <v>29.081066238502551</v>
+        <v>27.730059708535649</v>
       </c>
       <c r="K14" s="33">
-        <v>25.175000000000001</v>
+        <v>25.1</v>
       </c>
       <c r="L14" s="33">
-        <v>23.91888347753985</v>
+        <v>24.39</v>
       </c>
       <c r="M14" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
         <v>36</v>
       </c>
@@ -5691,37 +5698,37 @@
         <v>16</v>
       </c>
       <c r="D15" s="4">
-        <v>31.794117135222351</v>
+        <v>33.026887228066883</v>
       </c>
       <c r="E15" s="4">
-        <v>31.91023964328302</v>
+        <v>32.805</v>
       </c>
       <c r="F15" s="4">
-        <v>2.589989223533586</v>
+        <v>2.0528596989028278</v>
       </c>
       <c r="G15" s="4">
-        <v>35.6</v>
+        <v>35</v>
       </c>
       <c r="H15" s="4">
-        <v>27.5</v>
+        <v>28.24</v>
       </c>
       <c r="I15" s="4">
-        <v>34.159999999999997</v>
+        <v>34.944985052601929</v>
       </c>
       <c r="J15" s="4">
-        <v>33.555</v>
+        <v>34.770000000000003</v>
       </c>
       <c r="K15" s="4">
-        <v>30.650519049243069</v>
+        <v>32.349999999999987</v>
       </c>
       <c r="L15" s="4">
-        <v>27.95</v>
+        <v>31.803999999999998</v>
       </c>
       <c r="M15" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="14" t="s">
         <v>18</v>
       </c>
@@ -5737,7 +5744,7 @@
       <c r="L18" s="14"/>
       <c r="M18" s="15"/>
     </row>
-    <row r="19" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B19" s="16" t="s">
         <v>1</v>
       </c>
@@ -5775,311 +5782,311 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B20" s="2">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="4">
-        <v>2.959906891118723</v>
+        <v>2.6705516095613651</v>
       </c>
       <c r="E20" s="4">
-        <v>2.872034455593615</v>
+        <v>2.68</v>
       </c>
       <c r="F20" s="4">
-        <v>0.25206429671551078</v>
+        <v>0.16713067498653791</v>
       </c>
       <c r="G20" s="4">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="H20" s="4">
-        <v>2.65</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="I20" s="4">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="J20" s="4">
-        <v>3.2250000000000001</v>
+        <v>2.775850177749565</v>
       </c>
       <c r="K20" s="4">
-        <v>2.7662499999999999</v>
+        <v>2.5180288461538458</v>
       </c>
       <c r="L20" s="4">
-        <v>2.74</v>
+        <v>2.4969999999999999</v>
       </c>
       <c r="M20" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B21" s="31">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C21" s="32" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="33">
-        <v>2.6575000000000002</v>
+        <v>2.5239878922184809</v>
       </c>
       <c r="E21" s="33">
-        <v>2.69</v>
+        <v>2.5149394610924078</v>
       </c>
       <c r="F21" s="33">
-        <v>0.34399006768606938</v>
+        <v>0.16715745908815061</v>
       </c>
       <c r="G21" s="33">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="H21" s="33">
-        <v>2.1800000000000002</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="I21" s="33">
-        <v>3.0209999999999999</v>
+        <v>2.6524999999999999</v>
       </c>
       <c r="J21" s="33">
-        <v>2.8</v>
+        <v>2.5874999999999999</v>
       </c>
       <c r="K21" s="33">
-        <v>2.40625</v>
+        <v>2.41</v>
       </c>
       <c r="L21" s="33">
-        <v>2.2429999999999999</v>
+        <v>2.3675000000000002</v>
       </c>
       <c r="M21" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B22" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="4">
-        <v>2.4849999999999999</v>
+        <v>2.287527374318215</v>
       </c>
       <c r="E22" s="4">
-        <v>2.5</v>
+        <v>2.2227440283177118</v>
       </c>
       <c r="F22" s="4">
-        <v>0.34304194754836881</v>
+        <v>0.194613805426231</v>
       </c>
       <c r="G22" s="4">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="H22" s="4">
-        <v>1.86</v>
+        <v>2.051035686546725</v>
       </c>
       <c r="I22" s="4">
-        <v>2.722</v>
+        <v>2.5819999999999999</v>
       </c>
       <c r="J22" s="4">
-        <v>2.6512500000000001</v>
+        <v>2.4121874999999999</v>
       </c>
       <c r="K22" s="4">
-        <v>2.40625</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="L22" s="4">
-        <v>2.0310000000000001</v>
+        <v>2.068103568654672</v>
       </c>
       <c r="M22" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B23" s="31">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C23" s="32" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="33">
-        <v>2.2523749999999998</v>
+        <v>2.3845295684625412</v>
       </c>
       <c r="E23" s="33">
-        <v>2.202500000000001</v>
+        <v>2.2946779472947392</v>
       </c>
       <c r="F23" s="33">
-        <v>0.35176067562572522</v>
+        <v>0.50068624893740277</v>
       </c>
       <c r="G23" s="33">
-        <v>2.9</v>
+        <v>3.6750000000000012</v>
       </c>
       <c r="H23" s="33">
-        <v>1.75</v>
+        <v>1.8825022900359301</v>
       </c>
       <c r="I23" s="33">
-        <v>2.6120000000000001</v>
+        <v>2.6175000000000002</v>
       </c>
       <c r="J23" s="33">
-        <v>2.4946874999999999</v>
+        <v>2.4674999999999998</v>
       </c>
       <c r="K23" s="33">
-        <v>2.0499999999999998</v>
+        <v>2.196328125</v>
       </c>
       <c r="L23" s="33">
-        <v>1.84</v>
+        <v>1.898250229003593</v>
       </c>
       <c r="M23" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B24" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="4">
-        <v>2.24134375</v>
+        <v>2.0799401111919829</v>
       </c>
       <c r="E24" s="4">
-        <v>2.2492187499999998</v>
+        <v>2</v>
       </c>
       <c r="F24" s="4">
-        <v>0.33494558177670608</v>
+        <v>0.32876736679955021</v>
       </c>
       <c r="G24" s="4">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="H24" s="4">
-        <v>1.72</v>
+        <v>1.787729236919827</v>
       </c>
       <c r="I24" s="4">
-        <v>2.642500000000001</v>
+        <v>2.2829999999999999</v>
       </c>
       <c r="J24" s="4">
-        <v>2.415</v>
+        <v>2.09125390625</v>
       </c>
       <c r="K24" s="4">
-        <v>2.0125000000000002</v>
+        <v>1.925</v>
       </c>
       <c r="L24" s="4">
-        <v>1.8819999999999999</v>
+        <v>1.7987729236919829</v>
       </c>
       <c r="M24" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B25" s="31">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C25" s="32" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="33">
-        <v>2.0261671875</v>
+        <v>1.9091926153562271</v>
       </c>
       <c r="E25" s="33">
-        <v>2.0508359375</v>
+        <v>1.9</v>
       </c>
       <c r="F25" s="33">
-        <v>0.2242245781823349</v>
+        <v>0.1822770353050655</v>
       </c>
       <c r="G25" s="33">
-        <v>2.3199999999999998</v>
+        <v>2.31</v>
       </c>
       <c r="H25" s="33">
         <v>1.7</v>
       </c>
       <c r="I25" s="33">
-        <v>2.3109999999999999</v>
+        <v>2.063778984374999</v>
       </c>
       <c r="J25" s="33">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="K25" s="33">
-        <v>1.8274999999999999</v>
+        <v>1.7625</v>
       </c>
       <c r="L25" s="33">
-        <v>1.79</v>
+        <v>1.7319545538310399</v>
       </c>
       <c r="M25" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B26" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="4">
-        <v>1.9326421093749999</v>
+        <v>1.810879099601421</v>
       </c>
       <c r="E26" s="4">
-        <v>1.98</v>
+        <v>1.7549999999999999</v>
       </c>
       <c r="F26" s="4">
-        <v>0.22436469364146391</v>
+        <v>0.18893178307354619</v>
       </c>
       <c r="G26" s="4">
-        <v>2.42</v>
+        <v>2.21</v>
       </c>
       <c r="H26" s="4">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="I26" s="4">
-        <v>2.074778984375</v>
+        <v>2.003862136718749</v>
       </c>
       <c r="J26" s="4">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K26" s="4">
-        <v>1.7450000000000001</v>
+        <v>1.6644582665816781</v>
       </c>
       <c r="L26" s="4">
-        <v>1.6950000000000001</v>
+        <v>1.645</v>
       </c>
       <c r="M26" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B27" s="31" t="s">
         <v>14</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D27" s="33">
-        <v>27.16702741534662</v>
+        <v>25.927535651284941</v>
       </c>
       <c r="E27" s="33">
-        <v>27.87</v>
+        <v>25.57</v>
       </c>
       <c r="F27" s="33">
-        <v>2.8872798292857071</v>
+        <v>1.810396164820846</v>
       </c>
       <c r="G27" s="33">
-        <v>31.8</v>
+        <v>29.21</v>
       </c>
       <c r="H27" s="33">
-        <v>22.4</v>
+        <v>23.201531525933159</v>
       </c>
       <c r="I27" s="33">
-        <v>29.82</v>
+        <v>27.91905255188172</v>
       </c>
       <c r="J27" s="33">
-        <v>29.002575097161749</v>
+        <v>27.086158280285741</v>
       </c>
       <c r="K27" s="33">
-        <v>25.024999999999999</v>
+        <v>24.675000000000001</v>
       </c>
       <c r="L27" s="33">
-        <v>24.04415662152546</v>
+        <v>24.280153152593311</v>
       </c>
       <c r="M27" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B28" s="2" t="s">
         <v>36</v>
       </c>
@@ -6087,41 +6094,41 @@
         <v>16</v>
       </c>
       <c r="D28" s="4">
-        <v>31.86138461124116</v>
+        <v>32.091426852630221</v>
       </c>
       <c r="E28" s="4">
-        <v>31.435092383353702</v>
+        <v>31.71</v>
       </c>
       <c r="F28" s="4">
-        <v>2.188885307012844</v>
+        <v>1.391162297170363</v>
       </c>
       <c r="G28" s="4">
-        <v>35</v>
+        <v>34.624660950027923</v>
       </c>
       <c r="H28" s="4">
-        <v>27.8</v>
+        <v>30.16960757627438</v>
       </c>
       <c r="I28" s="4">
-        <v>34.909999999999997</v>
+        <v>34.332466095002793</v>
       </c>
       <c r="J28" s="4">
-        <v>33.072500000000012</v>
+        <v>32.325000000000003</v>
       </c>
       <c r="K28" s="4">
-        <v>31.024999999999999</v>
+        <v>31.425000000000001</v>
       </c>
       <c r="L28" s="4">
-        <v>29.828295211133721</v>
+        <v>30.916960757627439</v>
       </c>
       <c r="M28" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B30" s="22"/>
       <c r="C30" s="23"/>
     </row>
-    <row r="31" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="14" t="s">
         <v>35</v>
       </c>
@@ -6137,7 +6144,7 @@
       <c r="L31" s="14"/>
       <c r="M31" s="15"/>
     </row>
-    <row r="32" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B32" s="24" t="s">
         <v>1</v>
       </c>
@@ -6175,273 +6182,273 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B33" s="31">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C33" s="32" t="s">
         <v>19</v>
       </c>
       <c r="D33" s="33">
-        <v>26.780999999999999</v>
+        <v>23.175000000000001</v>
       </c>
       <c r="E33" s="33">
-        <v>26.75</v>
+        <v>23</v>
       </c>
       <c r="F33" s="33">
-        <v>0.91192653212854835</v>
+        <v>0.74879532880784194</v>
       </c>
       <c r="G33" s="33">
-        <v>28.96</v>
+        <v>24.3</v>
       </c>
       <c r="H33" s="33">
-        <v>26</v>
+        <v>22.1</v>
       </c>
       <c r="I33" s="33">
-        <v>27.420999999999999</v>
+        <v>24.03</v>
       </c>
       <c r="J33" s="33">
-        <v>27</v>
+        <v>23.875</v>
       </c>
       <c r="K33" s="33">
-        <v>26.024999999999999</v>
+        <v>22.737500000000001</v>
       </c>
       <c r="L33" s="33">
-        <v>26</v>
+        <v>22.28</v>
       </c>
       <c r="M33" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="4">
-        <v>26.309000000000001</v>
+        <v>23.146000000000001</v>
       </c>
       <c r="E34" s="4">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F34" s="4">
-        <v>1.194510127393001</v>
+        <v>1.0378631894426169</v>
       </c>
       <c r="G34" s="4">
-        <v>28.88</v>
+        <v>25.26</v>
       </c>
       <c r="H34" s="4">
-        <v>25</v>
+        <v>21.9</v>
       </c>
       <c r="I34" s="4">
-        <v>27.277999999999999</v>
+        <v>24.126000000000001</v>
       </c>
       <c r="J34" s="4">
-        <v>27</v>
+        <v>23.824999999999999</v>
       </c>
       <c r="K34" s="4">
-        <v>25.5</v>
+        <v>22.5</v>
       </c>
       <c r="L34" s="4">
-        <v>25.099</v>
+        <v>21.99</v>
       </c>
       <c r="M34" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B35" s="31">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C35" s="32" t="s">
         <v>19</v>
       </c>
       <c r="D35" s="33">
-        <v>25.806999999999999</v>
+        <v>23.291</v>
       </c>
       <c r="E35" s="33">
-        <v>26</v>
+        <v>23.05</v>
       </c>
       <c r="F35" s="33">
-        <v>1.733282371045693</v>
+        <v>1.609944443485896</v>
       </c>
       <c r="G35" s="33">
-        <v>28.8</v>
+        <v>26.21</v>
       </c>
       <c r="H35" s="33">
-        <v>22.97</v>
+        <v>21.1</v>
       </c>
       <c r="I35" s="33">
-        <v>27.18</v>
+        <v>25.120999999999999</v>
       </c>
       <c r="J35" s="33">
-        <v>26.95</v>
+        <v>24.375</v>
       </c>
       <c r="K35" s="33">
-        <v>24.625</v>
+        <v>22</v>
       </c>
       <c r="L35" s="33">
-        <v>23.896999999999998</v>
+        <v>21.91</v>
       </c>
       <c r="M35" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B36" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D36" s="4">
-        <v>25.574999999999999</v>
+        <v>23.58410962262845</v>
       </c>
       <c r="E36" s="4">
-        <v>25.25</v>
+        <v>23.8</v>
       </c>
       <c r="F36" s="4">
-        <v>1.7099528908390691</v>
+        <v>2.4145076230559321</v>
       </c>
       <c r="G36" s="4">
-        <v>28.71</v>
+        <v>27.18</v>
       </c>
       <c r="H36" s="4">
-        <v>23</v>
+        <v>20.5</v>
       </c>
       <c r="I36" s="4">
-        <v>27.440999999999999</v>
+        <v>26.892986603656041</v>
       </c>
       <c r="J36" s="4">
-        <v>26.75</v>
+        <v>24.925000000000001</v>
       </c>
       <c r="K36" s="4">
-        <v>24.56</v>
+        <v>21.25</v>
       </c>
       <c r="L36" s="4">
-        <v>23.9</v>
+        <v>20.95</v>
       </c>
       <c r="M36" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B37" s="31">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C37" s="32" t="s">
         <v>19</v>
       </c>
       <c r="D37" s="33">
-        <v>25.574000000000002</v>
+        <v>23.591107238600891</v>
       </c>
       <c r="E37" s="33">
-        <v>25.055</v>
+        <v>24.05</v>
       </c>
       <c r="F37" s="33">
-        <v>1.822520842740138</v>
+        <v>2.7459206863688861</v>
       </c>
       <c r="G37" s="33">
-        <v>28.63</v>
+        <v>28.14</v>
       </c>
       <c r="H37" s="33">
-        <v>23</v>
+        <v>19.8</v>
       </c>
       <c r="I37" s="33">
-        <v>28.062999999999999</v>
+        <v>26.997965147408038</v>
       </c>
       <c r="J37" s="33">
-        <v>26.75</v>
+        <v>24.875</v>
       </c>
       <c r="K37" s="33">
-        <v>24.25</v>
+        <v>21.25</v>
       </c>
       <c r="L37" s="33">
-        <v>23.9</v>
+        <v>20.43</v>
       </c>
       <c r="M37" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D38" s="4">
-        <v>25.466999999999999</v>
+        <v>23.56323599753253</v>
       </c>
       <c r="E38" s="4">
-        <v>24.94</v>
+        <v>24</v>
       </c>
       <c r="F38" s="4">
-        <v>2.3670800108525651</v>
+        <v>3.0284061943568008</v>
       </c>
       <c r="G38" s="4">
-        <v>29</v>
+        <v>29.12</v>
       </c>
       <c r="H38" s="4">
-        <v>22</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="I38" s="4">
-        <v>28.585999999999999</v>
+        <v>26.863123977792799</v>
       </c>
       <c r="J38" s="4">
-        <v>27.1875</v>
+        <v>24.875</v>
       </c>
       <c r="K38" s="4">
-        <v>24</v>
+        <v>21.25</v>
       </c>
       <c r="L38" s="4">
-        <v>22.9</v>
+        <v>19.940000000000001</v>
       </c>
       <c r="M38" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B39" s="31" t="s">
         <v>14</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D39" s="33">
-        <v>21.708999999999971</v>
+        <v>22.05899999999999</v>
       </c>
       <c r="E39" s="33">
-        <v>21.90499999999987</v>
+        <v>21.92</v>
       </c>
       <c r="F39" s="33">
-        <v>2.2773203063639889</v>
+        <v>3.1369356951578609</v>
       </c>
       <c r="G39" s="33">
-        <v>25</v>
+        <v>27.85</v>
       </c>
       <c r="H39" s="33">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="I39" s="33">
-        <v>24.1</v>
+        <v>25.285</v>
       </c>
       <c r="J39" s="33">
-        <v>23.45</v>
+        <v>23.749999999999972</v>
       </c>
       <c r="K39" s="33">
-        <v>19.545000000000002</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="L39" s="33">
-        <v>18.95</v>
+        <v>17.95</v>
       </c>
       <c r="M39" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B40" s="2" t="s">
         <v>36</v>
       </c>
@@ -6449,41 +6456,41 @@
         <v>20</v>
       </c>
       <c r="D40" s="4">
-        <v>24.34008956449512</v>
+        <v>23.52171579808002</v>
       </c>
       <c r="E40" s="4">
-        <v>24.5</v>
+        <v>23.25</v>
       </c>
       <c r="F40" s="4">
-        <v>2.105210178310351</v>
+        <v>3.5688856224943168</v>
       </c>
       <c r="G40" s="4">
-        <v>28.29</v>
+        <v>31.09</v>
       </c>
       <c r="H40" s="4">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="I40" s="4">
-        <v>26.048999999999999</v>
+        <v>27.073442182720171</v>
       </c>
       <c r="J40" s="4">
-        <v>25.365671733713381</v>
+        <v>24.875</v>
       </c>
       <c r="K40" s="4">
-        <v>23.25</v>
+        <v>20.5</v>
       </c>
       <c r="L40" s="4">
-        <v>21.675000000000001</v>
+        <v>19.95</v>
       </c>
       <c r="M40" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B41" s="22"/>
       <c r="C41" s="23"/>
     </row>
-    <row r="43" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B43" s="14" t="s">
         <v>21</v>
       </c>
@@ -6499,7 +6506,7 @@
       <c r="L43" s="14"/>
       <c r="M43" s="15"/>
     </row>
-    <row r="44" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B44" s="24" t="s">
         <v>1</v>
       </c>
@@ -6537,273 +6544,273 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B45" s="31">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C45" s="32" t="s">
         <v>22</v>
       </c>
       <c r="D45" s="42">
-        <v>1416.8869404913139</v>
+        <v>1402.6729497585691</v>
       </c>
       <c r="E45" s="42">
-        <v>1417.8849951612899</v>
+        <v>1403.2466880876159</v>
       </c>
       <c r="F45" s="42">
-        <v>7.648048134882405</v>
+        <v>16.747296227263089</v>
       </c>
       <c r="G45" s="42">
-        <v>1430</v>
+        <v>1424.136121410455</v>
       </c>
       <c r="H45" s="42">
-        <v>1405</v>
+        <v>1373</v>
       </c>
       <c r="I45" s="42">
-        <v>1424.8676511161291</v>
+        <v>1420.413612141045</v>
       </c>
       <c r="J45" s="42">
-        <v>1420.5025000000001</v>
+        <v>1416.825</v>
       </c>
       <c r="K45" s="42">
-        <v>1411.9200236153811</v>
+        <v>1390.75</v>
       </c>
       <c r="L45" s="42">
-        <v>1407.25</v>
+        <v>1383.8</v>
       </c>
       <c r="M45" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D46" s="36">
-        <v>1437.6218679037549</v>
+        <v>1423.21720466733</v>
       </c>
       <c r="E46" s="36">
-        <v>1438.1849951612901</v>
+        <v>1426.75</v>
       </c>
       <c r="F46" s="36">
-        <v>16.235611191639769</v>
+        <v>23.221571472249419</v>
       </c>
       <c r="G46" s="36">
-        <v>1465</v>
+        <v>1455</v>
       </c>
       <c r="H46" s="36">
-        <v>1411</v>
+        <v>1380</v>
       </c>
       <c r="I46" s="36">
-        <v>1457.0260000000001</v>
+        <v>1446.448346908451</v>
       </c>
       <c r="J46" s="36">
-        <v>1446.379302014527</v>
+        <v>1440.23</v>
       </c>
       <c r="K46" s="36">
-        <v>1426.3928758489001</v>
+        <v>1407.1334708604211</v>
       </c>
       <c r="L46" s="36">
-        <v>1421.35</v>
+        <v>1398</v>
       </c>
       <c r="M46" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B47" s="31">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C47" s="32" t="s">
         <v>22</v>
       </c>
       <c r="D47" s="42">
-        <v>1459.2876847605289</v>
+        <v>1444.3850264557491</v>
       </c>
       <c r="E47" s="42">
-        <v>1465.78499516129</v>
+        <v>1451.314814438701</v>
       </c>
       <c r="F47" s="42">
-        <v>24.537374099442651</v>
+        <v>28.047702660297389</v>
       </c>
       <c r="G47" s="42">
-        <v>1495</v>
+        <v>1475</v>
       </c>
       <c r="H47" s="42">
-        <v>1412</v>
+        <v>1386</v>
       </c>
       <c r="I47" s="42">
-        <v>1486.297</v>
+        <v>1470.086</v>
       </c>
       <c r="J47" s="42">
-        <v>1469.942312255381</v>
+        <v>1465.385476760064</v>
       </c>
       <c r="K47" s="42">
-        <v>1442.6197111170461</v>
+        <v>1430.875</v>
       </c>
       <c r="L47" s="42">
-        <v>1434.95</v>
+        <v>1411.2</v>
       </c>
       <c r="M47" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D48" s="36">
-        <v>1481.3160522422891</v>
+        <v>1476.8222225927991</v>
       </c>
       <c r="E48" s="36">
-        <v>1484.9842149804181</v>
+        <v>1481.4069403563531</v>
       </c>
       <c r="F48" s="36">
-        <v>32.752475142984288</v>
+        <v>34.504834772728607</v>
       </c>
       <c r="G48" s="36">
-        <v>1530</v>
+        <v>1514.22</v>
       </c>
       <c r="H48" s="36">
-        <v>1418</v>
+        <v>1392</v>
       </c>
       <c r="I48" s="36">
-        <v>1517.1120000000001</v>
+        <v>1510.422</v>
       </c>
       <c r="J48" s="36">
-        <v>1499.3423678221429</v>
+        <v>1494.297086303822</v>
       </c>
       <c r="K48" s="36">
-        <v>1460.840786722237</v>
+        <v>1472.75</v>
       </c>
       <c r="L48" s="36">
-        <v>1450.201526856082</v>
+        <v>1450.5</v>
       </c>
       <c r="M48" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B49" s="31">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C49" s="32" t="s">
         <v>22</v>
       </c>
       <c r="D49" s="42">
-        <v>1509.6966297615049</v>
+        <v>1512.4282142601189</v>
       </c>
       <c r="E49" s="42">
-        <v>1511.7478992800261</v>
+        <v>1520.5079861038359</v>
       </c>
       <c r="F49" s="42">
-        <v>41.569195400872132</v>
+        <v>45.620436961664012</v>
       </c>
       <c r="G49" s="42">
-        <v>1561.76</v>
+        <v>1566.74</v>
       </c>
       <c r="H49" s="42">
-        <v>1424</v>
+        <v>1397</v>
       </c>
       <c r="I49" s="42">
-        <v>1555.6759999999999</v>
+        <v>1551.674</v>
       </c>
       <c r="J49" s="42">
-        <v>1538.13867917517</v>
+        <v>1531</v>
       </c>
       <c r="K49" s="42">
-        <v>1495.885414448514</v>
+        <v>1502.8815425983789</v>
       </c>
       <c r="L49" s="42">
-        <v>1463.8855421246431</v>
+        <v>1489.7</v>
       </c>
       <c r="M49" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B50" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D50" s="36">
-        <v>1540.600328297686</v>
+        <v>1546.1912280203319</v>
       </c>
       <c r="E50" s="36">
-        <v>1539.8810209167129</v>
+        <v>1554.7766086269489</v>
       </c>
       <c r="F50" s="36">
-        <v>53.40078837656894</v>
+        <v>55.907881527522861</v>
       </c>
       <c r="G50" s="36">
-        <v>1615.93</v>
+        <v>1612.66</v>
       </c>
       <c r="H50" s="36">
-        <v>1428</v>
+        <v>1404</v>
       </c>
       <c r="I50" s="36">
-        <v>1595.208472623779</v>
+        <v>1583.2660000000001</v>
       </c>
       <c r="J50" s="36">
-        <v>1567.5</v>
+        <v>1575</v>
       </c>
       <c r="K50" s="36">
-        <v>1537.451179683173</v>
+        <v>1536.3992972120641</v>
       </c>
       <c r="L50" s="36">
-        <v>1477.500397545889</v>
+        <v>1516.05</v>
       </c>
       <c r="M50" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B51" s="31" t="s">
         <v>14</v>
       </c>
       <c r="C51" s="32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D51" s="42">
-        <v>1688.3743184397929</v>
+        <v>1696.5515593412181</v>
       </c>
       <c r="E51" s="42">
-        <v>1692.5</v>
+        <v>1704</v>
       </c>
       <c r="F51" s="42">
-        <v>111.84654751848851</v>
+        <v>109.3470888745458</v>
       </c>
       <c r="G51" s="42">
-        <v>1804.82</v>
+        <v>1810.1491352191269</v>
       </c>
       <c r="H51" s="42">
-        <v>1449</v>
+        <v>1436</v>
       </c>
       <c r="I51" s="42">
-        <v>1789.682</v>
+        <v>1791.114913521913</v>
       </c>
       <c r="J51" s="42">
-        <v>1782.906473232131</v>
+        <v>1779.14</v>
       </c>
       <c r="K51" s="42">
-        <v>1654.538014932532</v>
+        <v>1670.350364219229</v>
       </c>
       <c r="L51" s="42">
-        <v>1561.5</v>
+        <v>1607</v>
       </c>
       <c r="M51" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B52" s="2" t="s">
         <v>36</v>
       </c>
@@ -6811,45 +6818,45 @@
         <v>23</v>
       </c>
       <c r="D52" s="36">
-        <v>1632.572228390168</v>
+        <v>1610.780576930583</v>
       </c>
       <c r="E52" s="36">
-        <v>1660</v>
+        <v>1632.6590828750079</v>
       </c>
       <c r="F52" s="36">
-        <v>89.966592818116752</v>
+        <v>79.803434769060772</v>
       </c>
       <c r="G52" s="36">
-        <v>1752.55</v>
+        <v>1681.88</v>
       </c>
       <c r="H52" s="36">
-        <v>1440</v>
+        <v>1416</v>
       </c>
       <c r="I52" s="36">
-        <v>1711.845074373965</v>
+        <v>1675.6880000000001</v>
       </c>
       <c r="J52" s="36">
-        <v>1672.5</v>
+        <v>1666.5093434821861</v>
       </c>
       <c r="K52" s="36">
-        <v>1615.487494760431</v>
+        <v>1582.177672220299</v>
       </c>
       <c r="L52" s="36">
-        <v>1519.11</v>
+        <v>1560</v>
       </c>
       <c r="M52" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B53" s="22"/>
       <c r="C53" s="23"/>
     </row>
-    <row r="54" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B54" s="22"/>
       <c r="C54" s="23"/>
     </row>
-    <row r="55" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B55" s="14" t="s">
         <v>24</v>
       </c>
@@ -6865,7 +6872,7 @@
       <c r="L55" s="14"/>
       <c r="M55" s="15"/>
     </row>
-    <row r="56" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B56" s="24" t="s">
         <v>1</v>
       </c>
@@ -6903,273 +6910,273 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B57" s="38">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C57" s="32" t="s">
         <v>25</v>
       </c>
       <c r="D57" s="39">
-        <v>7362.3736544049507</v>
+        <v>8694.5469412993007</v>
       </c>
       <c r="E57" s="39">
-        <v>7459.1917805892572</v>
+        <v>8791</v>
       </c>
       <c r="F57" s="39">
-        <v>324.14311372368951</v>
+        <v>505.08547458655522</v>
       </c>
       <c r="G57" s="39">
-        <v>7845</v>
+        <v>9400.9726398926268</v>
       </c>
       <c r="H57" s="39">
-        <v>6780.2629675981862</v>
+        <v>7600</v>
       </c>
       <c r="I57" s="39">
-        <v>7570.5</v>
+        <v>9323.6120186438693</v>
       </c>
       <c r="J57" s="39">
-        <v>7521.5925114546062</v>
+        <v>8833.3195302690292</v>
       </c>
       <c r="K57" s="39">
-        <v>7317.5</v>
+        <v>8483.5969180035845</v>
       </c>
       <c r="L57" s="39">
-        <v>6835.1962967598192</v>
+        <v>8339.7999999999993</v>
       </c>
       <c r="M57" s="40">
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B58" s="2">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D58" s="36">
-        <v>7743.7392986506329</v>
+        <v>9056.3634044145092</v>
       </c>
       <c r="E58" s="36">
-        <v>7699.5112431869402</v>
+        <v>9117.6233056483215</v>
       </c>
       <c r="F58" s="36">
-        <v>434.91508077415591</v>
+        <v>616.81790186096282</v>
       </c>
       <c r="G58" s="36">
-        <v>8500</v>
+        <v>9900</v>
       </c>
       <c r="H58" s="36">
-        <v>6874.2</v>
+        <v>7900</v>
       </c>
       <c r="I58" s="36">
-        <v>8212</v>
+        <v>9805.0060245631175</v>
       </c>
       <c r="J58" s="36">
-        <v>7956.25</v>
+        <v>9396.2022208337312</v>
       </c>
       <c r="K58" s="36">
-        <v>7566.9423162384828</v>
+        <v>8627.25</v>
       </c>
       <c r="L58" s="36">
-        <v>7461.942670633025</v>
+        <v>8440</v>
       </c>
       <c r="M58" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B59" s="31">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C59" s="32" t="s">
         <v>25</v>
       </c>
       <c r="D59" s="39">
-        <v>8201.9335995119945</v>
+        <v>8887.6053839424894</v>
       </c>
       <c r="E59" s="39">
-        <v>8244.0987190766355</v>
+        <v>8800.5</v>
       </c>
       <c r="F59" s="39">
-        <v>414.11883977650461</v>
+        <v>612.843384972129</v>
       </c>
       <c r="G59" s="39">
-        <v>8814.8740509557356</v>
+        <v>9871.4532105056478</v>
       </c>
       <c r="H59" s="39">
-        <v>7307.9</v>
+        <v>8100</v>
       </c>
       <c r="I59" s="39">
-        <v>8693.4874050955732</v>
+        <v>9762.1453210505642</v>
       </c>
       <c r="J59" s="39">
-        <v>8295.25</v>
+        <v>9208.239533139058</v>
       </c>
       <c r="K59" s="39">
-        <v>8078.0233795082167</v>
+        <v>8405.2369795167961</v>
       </c>
       <c r="L59" s="39">
-        <v>7840.79</v>
+        <v>8185.5</v>
       </c>
       <c r="M59" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B60" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D60" s="36">
-        <v>8104.1926700078066</v>
+        <v>8819.15008505271</v>
       </c>
       <c r="E60" s="36">
-        <v>8105.8140728156104</v>
+        <v>9135.3040980029418</v>
       </c>
       <c r="F60" s="36">
-        <v>241.85364912898251</v>
+        <v>684.15297963735873</v>
       </c>
       <c r="G60" s="36">
-        <v>8370</v>
+        <v>9684.456232295679</v>
       </c>
       <c r="H60" s="36">
-        <v>7493.3</v>
+        <v>7826</v>
       </c>
       <c r="I60" s="36">
-        <v>8330.1934153065831</v>
+        <v>9563.445623229567</v>
       </c>
       <c r="J60" s="36">
-        <v>8227.1710697463132</v>
+        <v>9210.0773166691488</v>
       </c>
       <c r="K60" s="36">
-        <v>8085</v>
+        <v>8260.25</v>
       </c>
       <c r="L60" s="36">
-        <v>7971.83</v>
+        <v>7892.6</v>
       </c>
       <c r="M60" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B61" s="31">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C61" s="32" t="s">
         <v>25</v>
       </c>
       <c r="D61" s="39">
-        <v>8350.7695703034005</v>
+        <v>8690.5669700840008</v>
       </c>
       <c r="E61" s="39">
-        <v>8448.1466680609919</v>
+        <v>8881.6971326652747</v>
       </c>
       <c r="F61" s="39">
-        <v>359.37206454919959</v>
+        <v>821.72176839900078</v>
       </c>
       <c r="G61" s="39">
-        <v>8821.1574269908306</v>
+        <v>10165.564280137931</v>
       </c>
       <c r="H61" s="39">
-        <v>7865</v>
+        <v>7600</v>
       </c>
       <c r="I61" s="39">
-        <v>8685.1157426990831</v>
+        <v>9566.5564280137933</v>
       </c>
       <c r="J61" s="39">
-        <v>8646.3337049408965</v>
+        <v>9034.0333665286526</v>
       </c>
       <c r="K61" s="39">
-        <v>7995.35</v>
+        <v>8089.75</v>
       </c>
       <c r="L61" s="39">
-        <v>7980.2</v>
+        <v>7622.5</v>
       </c>
       <c r="M61" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B62" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D62" s="36">
-        <v>8233.9606009179442</v>
+        <v>8610.3860180559514</v>
       </c>
       <c r="E62" s="36">
-        <v>8143.485699152774</v>
+        <v>8603.0568597276178</v>
       </c>
       <c r="F62" s="36">
-        <v>512.64802799747679</v>
+        <v>898.13982063678134</v>
       </c>
       <c r="G62" s="36">
-        <v>9137.543488644842</v>
+        <v>10615.8881347724</v>
       </c>
       <c r="H62" s="36">
         <v>7500</v>
       </c>
       <c r="I62" s="36">
-        <v>8792.436358870631</v>
+        <v>9327.9613071759304</v>
       </c>
       <c r="J62" s="36">
-        <v>8582.5</v>
+        <v>8912.5</v>
       </c>
       <c r="K62" s="36">
-        <v>7922.75</v>
+        <v>8107.25</v>
       </c>
       <c r="L62" s="36">
-        <v>7638.6</v>
+        <v>7588.2</v>
       </c>
       <c r="M62" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B63" s="31">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C63" s="32" t="s">
         <v>25</v>
       </c>
       <c r="D63" s="39">
-        <v>8274.9456676732825</v>
+        <v>8520.1081527498227</v>
       </c>
       <c r="E63" s="39">
-        <v>8120.3427817949969</v>
+        <v>8387.4841313309844</v>
       </c>
       <c r="F63" s="39">
-        <v>684.42668375152141</v>
+        <v>934.18541665838211</v>
       </c>
       <c r="G63" s="39">
-        <v>9456.2614126757271</v>
+        <v>10840.359725935061</v>
       </c>
       <c r="H63" s="39">
-        <v>7300</v>
+        <v>7500</v>
       </c>
       <c r="I63" s="39">
-        <v>9048.7848716879671</v>
+        <v>9172.1141576045775</v>
       </c>
       <c r="J63" s="39">
-        <v>8747.5</v>
+        <v>8692</v>
       </c>
       <c r="K63" s="39">
-        <v>7809</v>
+        <v>8038</v>
       </c>
       <c r="L63" s="39">
-        <v>7504.3</v>
+        <v>7650.3</v>
       </c>
       <c r="M63" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B64" s="35" t="s">
         <v>36</v>
       </c>
@@ -7177,45 +7184,45 @@
         <v>25</v>
       </c>
       <c r="D64" s="36">
-        <v>93611.246992911707</v>
+        <v>99944.071568107436</v>
       </c>
       <c r="E64" s="36">
-        <v>92700.959808448999</v>
+        <v>99505</v>
       </c>
       <c r="F64" s="36">
-        <v>3180.6167099813279</v>
+        <v>6098.2658573839817</v>
       </c>
       <c r="G64" s="36">
-        <v>100200.0097815488</v>
+        <v>112857.8562633464</v>
       </c>
       <c r="H64" s="36">
-        <v>89999.9</v>
+        <v>93266</v>
       </c>
       <c r="I64" s="36">
-        <v>98400.000978154887</v>
+        <v>106937.7856263346</v>
       </c>
       <c r="J64" s="36">
-        <v>93719.730398002735</v>
+        <v>101733.46485443199</v>
       </c>
       <c r="K64" s="36">
-        <v>91844.5</v>
+        <v>95242</v>
       </c>
       <c r="L64" s="36">
-        <v>91156.49</v>
+        <v>93614.3</v>
       </c>
       <c r="M64" s="37">
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B65" s="22"/>
       <c r="C65" s="23"/>
     </row>
-    <row r="66" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B66" s="22"/>
       <c r="C66" s="23"/>
     </row>
-    <row r="67" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B67" s="14" t="s">
         <v>26</v>
       </c>
@@ -7231,7 +7238,7 @@
       <c r="L67" s="14"/>
       <c r="M67" s="15"/>
     </row>
-    <row r="68" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B68" s="24" t="s">
         <v>1</v>
       </c>
@@ -7269,273 +7276,273 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B69" s="38">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C69" s="32" t="s">
         <v>25</v>
       </c>
       <c r="D69" s="39">
-        <v>6484.0958437584486</v>
+        <v>6635.1488537975938</v>
       </c>
       <c r="E69" s="39">
-        <v>6481.1976108129784</v>
+        <v>6464.4704671466279</v>
       </c>
       <c r="F69" s="39">
-        <v>548.53116962807849</v>
+        <v>623.34209655294876</v>
       </c>
       <c r="G69" s="39">
-        <v>7273.3638476630513</v>
+        <v>8219</v>
       </c>
       <c r="H69" s="39">
-        <v>5440.22</v>
+        <v>6000</v>
       </c>
       <c r="I69" s="39">
-        <v>7201.9363847663053</v>
+        <v>7137.8542649853061</v>
       </c>
       <c r="J69" s="39">
-        <v>6791.0330341435729</v>
+        <v>6662.2818304198236</v>
       </c>
       <c r="K69" s="39">
-        <v>6154.491544932429</v>
+        <v>6325.8682937731273</v>
       </c>
       <c r="L69" s="39">
-        <v>6018.9940998634011</v>
+        <v>6170.0090561575716</v>
       </c>
       <c r="M69" s="40">
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B70" s="2">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D70" s="36">
-        <v>6804.4500923462501</v>
+        <v>7032.0290728838318</v>
       </c>
       <c r="E70" s="36">
-        <v>6739.6207656258848</v>
+        <v>6902.3662906552854</v>
       </c>
       <c r="F70" s="36">
-        <v>446.56437606819031</v>
+        <v>748.8075933247344</v>
       </c>
       <c r="G70" s="36">
-        <v>7563</v>
+        <v>8928</v>
       </c>
       <c r="H70" s="36">
-        <v>6188.8989512861908</v>
+        <v>6234.9522612827004</v>
       </c>
       <c r="I70" s="36">
-        <v>7366.8</v>
+        <v>7557.2808066364778</v>
       </c>
       <c r="J70" s="36">
-        <v>7066.5733832217593</v>
+        <v>7072.1954324551371</v>
       </c>
       <c r="K70" s="36">
-        <v>6457.0845312751617</v>
+        <v>6700.2356089589539</v>
       </c>
       <c r="L70" s="36">
-        <v>6345.381676020208</v>
+        <v>6383.4952261282697</v>
       </c>
       <c r="M70" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B71" s="31">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C71" s="32" t="s">
         <v>25</v>
       </c>
       <c r="D71" s="39">
-        <v>7014.6057695504496</v>
+        <v>7022.4132019378712</v>
       </c>
       <c r="E71" s="39">
-        <v>6970.8244849605871</v>
+        <v>6860.15489217719</v>
       </c>
       <c r="F71" s="39">
-        <v>598.30018642670257</v>
+        <v>677.74366885151051</v>
       </c>
       <c r="G71" s="39">
-        <v>8003</v>
+        <v>8844</v>
       </c>
       <c r="H71" s="39">
-        <v>6234.9522612827004</v>
+        <v>6500</v>
       </c>
       <c r="I71" s="39">
-        <v>7900.3857086605713</v>
+        <v>7454.3163491573023</v>
       </c>
       <c r="J71" s="39">
-        <v>7301.2933820499211</v>
+        <v>6937.1005050368194</v>
       </c>
       <c r="K71" s="39">
-        <v>6618.8572555818764</v>
+        <v>6669.8487542302228</v>
       </c>
       <c r="L71" s="39">
-        <v>6331.9340398637833</v>
+        <v>6586.3099999999986</v>
       </c>
       <c r="M71" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B72" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D72" s="36">
-        <v>7059.9890981519884</v>
+        <v>7586.9773944270901</v>
       </c>
       <c r="E72" s="36">
-        <v>6930.9614020739009</v>
+        <v>7473.0526735253943</v>
       </c>
       <c r="F72" s="36">
-        <v>473.14816969676309</v>
+        <v>594.40075500832017</v>
       </c>
       <c r="G72" s="36">
-        <v>7957</v>
+        <v>8917</v>
       </c>
       <c r="H72" s="36">
-        <v>6502.32</v>
+        <v>6979.8712142692511</v>
       </c>
       <c r="I72" s="36">
-        <v>7771.1467902553386</v>
+        <v>8218.3658058302426</v>
       </c>
       <c r="J72" s="36">
-        <v>7197.4489522954837</v>
+        <v>7784.4538959487954</v>
       </c>
       <c r="K72" s="36">
-        <v>6857.9855222600636</v>
+        <v>7124.0167748773792</v>
       </c>
       <c r="L72" s="36">
-        <v>6544.6420644590862</v>
+        <v>7087.9871214269251</v>
       </c>
       <c r="M72" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B73" s="31">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C73" s="32" t="s">
         <v>25</v>
       </c>
       <c r="D73" s="39">
-        <v>7460.9073869963568</v>
+        <v>7354.1447641444593</v>
       </c>
       <c r="E73" s="39">
-        <v>7456.6044427470006</v>
+        <v>7199.7369078985303</v>
       </c>
       <c r="F73" s="39">
-        <v>360.08721871178159</v>
+        <v>710.54268110869646</v>
       </c>
       <c r="G73" s="39">
-        <v>8046</v>
+        <v>8770</v>
       </c>
       <c r="H73" s="39">
-        <v>6891.068890282877</v>
+        <v>6440.9771371761644</v>
       </c>
       <c r="I73" s="39">
-        <v>7827.0339626292252</v>
+        <v>8450.813714998254</v>
       </c>
       <c r="J73" s="39">
-        <v>7741.7924999999996</v>
+        <v>7359.7369724296896</v>
       </c>
       <c r="K73" s="39">
-        <v>7184.2945276113414</v>
+        <v>7000.1914011332838</v>
       </c>
       <c r="L73" s="39">
-        <v>7080.4965019640822</v>
+        <v>6789.5280137307154</v>
       </c>
       <c r="M73" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B74" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D74" s="36">
-        <v>7231.8536454316436</v>
+        <v>7681.3766070123747</v>
       </c>
       <c r="E74" s="36">
-        <v>7173.2462177510106</v>
+        <v>7616.6575650945642</v>
       </c>
       <c r="F74" s="36">
-        <v>496.15996146420309</v>
+        <v>615.24745609521904</v>
       </c>
       <c r="G74" s="36">
-        <v>8065.9103591017974</v>
+        <v>8553.938094788864</v>
       </c>
       <c r="H74" s="36">
-        <v>6440.9771371761644</v>
+        <v>6933.3516594765897</v>
       </c>
       <c r="I74" s="36">
-        <v>7945.3910359101792</v>
+        <v>8497.293809478886</v>
       </c>
       <c r="J74" s="36">
-        <v>7396.9411447196344</v>
+        <v>8167.7453544839236</v>
       </c>
       <c r="K74" s="36">
-        <v>6970.6297880489728</v>
+        <v>7195.8413336667336</v>
       </c>
       <c r="L74" s="36">
-        <v>6711.3419733605533</v>
+        <v>6941.0990128178628</v>
       </c>
       <c r="M74" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B75" s="31">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C75" s="32" t="s">
         <v>25</v>
       </c>
       <c r="D75" s="39">
-        <v>7597.8931451005392</v>
+        <v>7576.350872673167</v>
       </c>
       <c r="E75" s="39">
-        <v>7611.1391308748862</v>
+        <v>7565.9354433239732</v>
       </c>
       <c r="F75" s="39">
-        <v>442.40197516235679</v>
+        <v>573.03347441808228</v>
       </c>
       <c r="G75" s="39">
-        <v>8198.7451022090518</v>
+        <v>8323</v>
       </c>
       <c r="H75" s="39">
-        <v>6941.9598298557821</v>
+        <v>6507.2964453080758</v>
       </c>
       <c r="I75" s="39">
-        <v>8179.1745102209052</v>
+        <v>8258.4821130357541</v>
       </c>
       <c r="J75" s="39">
-        <v>7897.1</v>
+        <v>8041.6402508570254</v>
       </c>
       <c r="K75" s="39">
-        <v>7234.7512820716274</v>
+        <v>7272.730368740331</v>
       </c>
       <c r="L75" s="39">
-        <v>7070.6959829855787</v>
+        <v>7000.7036428932142</v>
       </c>
       <c r="M75" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B76" s="35" t="s">
         <v>36</v>
       </c>
@@ -7543,37 +7550,37 @@
         <v>25</v>
       </c>
       <c r="D76" s="36">
-        <v>80302.785725372509</v>
+        <v>80430.743916619744</v>
       </c>
       <c r="E76" s="36">
-        <v>79556.760000000009</v>
+        <v>78400</v>
       </c>
       <c r="F76" s="36">
-        <v>3664.2349507222998</v>
+        <v>5272.1534900626048</v>
       </c>
       <c r="G76" s="36">
-        <v>86280</v>
+        <v>92219.933626389844</v>
       </c>
       <c r="H76" s="36">
-        <v>74348.355211546033</v>
+        <v>74359.316105230988</v>
       </c>
       <c r="I76" s="36">
-        <v>83712.722676453632</v>
+        <v>87245.795513930119</v>
       </c>
       <c r="J76" s="36">
-        <v>83266.253950332772</v>
+        <v>81237.380459129345</v>
       </c>
       <c r="K76" s="36">
-        <v>77881.880350923457</v>
+        <v>77735.980673742219</v>
       </c>
       <c r="L76" s="36">
-        <v>76807.735521154609</v>
+        <v>76824.780494757506</v>
       </c>
       <c r="M76" s="37">
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:13" ht="18" x14ac:dyDescent="0.4">
       <c r="B77" s="9"/>
       <c r="C77" s="10"/>
       <c r="D77" s="10"/>
@@ -7587,7 +7594,7 @@
       <c r="L77" s="10"/>
       <c r="M77" s="10"/>
     </row>
-    <row r="79" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="14" t="s">
         <v>27</v>
       </c>
@@ -7603,7 +7610,7 @@
       <c r="L79" s="14"/>
       <c r="M79" s="15"/>
     </row>
-    <row r="80" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B80" s="24" t="s">
         <v>1</v>
       </c>
@@ -7641,7 +7648,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B81" s="6" t="s">
         <v>36</v>
       </c>
@@ -7649,37 +7656,37 @@
         <v>28</v>
       </c>
       <c r="D81" s="43">
-        <v>16135.826871685729</v>
+        <v>16531.849035752912</v>
       </c>
       <c r="E81" s="43">
-        <v>16374.5</v>
+        <v>15990.5</v>
       </c>
       <c r="F81" s="43">
-        <v>2427.7183821665189</v>
+        <v>2332.9252711705049</v>
       </c>
       <c r="G81" s="43">
         <v>21056</v>
       </c>
       <c r="H81" s="43">
-        <v>11634.15244290778</v>
+        <v>12607.167581384199</v>
       </c>
       <c r="I81" s="43">
-        <v>17861.28206832776</v>
+        <v>18935.599999999999</v>
       </c>
       <c r="J81" s="43">
-        <v>17043.75</v>
+        <v>17700.26409062641</v>
       </c>
       <c r="K81" s="43">
-        <v>14827</v>
+        <v>15363.25</v>
       </c>
       <c r="L81" s="43">
-        <v>14441.83782251762</v>
+        <v>14555.702530413761</v>
       </c>
       <c r="M81" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:13" ht="18" x14ac:dyDescent="0.4">
       <c r="B82" s="9"/>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
@@ -7693,7 +7700,7 @@
       <c r="L82" s="10"/>
       <c r="M82" s="10"/>
     </row>
-    <row r="84" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="14" t="s">
         <v>29</v>
       </c>
@@ -7709,7 +7716,7 @@
       <c r="L84" s="14"/>
       <c r="M84" s="15"/>
     </row>
-    <row r="85" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B85" s="24" t="s">
         <v>1</v>
       </c>
@@ -7747,7 +7754,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B86" s="38" t="s">
         <v>38</v>
       </c>
@@ -7755,37 +7762,37 @@
         <v>30</v>
       </c>
       <c r="D86" s="33">
-        <v>7.5638078870624481</v>
+        <v>7.7713257807101099</v>
       </c>
       <c r="E86" s="33">
+        <v>7.6999999999999993</v>
+      </c>
+      <c r="F86" s="33">
+        <v>0.3768920397311985</v>
+      </c>
+      <c r="G86" s="33">
+        <v>8.6460955860665845</v>
+      </c>
+      <c r="H86" s="33">
+        <v>7.257162221034517</v>
+      </c>
+      <c r="I86" s="33">
+        <v>8.1096095586066586</v>
+      </c>
+      <c r="J86" s="33">
+        <v>7.8450000000000006</v>
+      </c>
+      <c r="K86" s="33">
         <v>7.6</v>
       </c>
-      <c r="F86" s="33">
-        <v>0.33040648036709708</v>
-      </c>
-      <c r="G86" s="33">
-        <v>8.0500000000000007</v>
-      </c>
-      <c r="H86" s="33">
-        <v>7.0240623644232167</v>
-      </c>
-      <c r="I86" s="33">
-        <v>7.8789999999999996</v>
-      </c>
-      <c r="J86" s="33">
-        <v>7.7940127486104087</v>
-      </c>
-      <c r="K86" s="33">
-        <v>7.35</v>
-      </c>
       <c r="L86" s="33">
-        <v>7.1175751970260004</v>
+        <v>7.4757162221034514</v>
       </c>
       <c r="M86" s="40">
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B87" s="6" t="s">
         <v>43</v>
       </c>
@@ -7793,75 +7800,75 @@
         <v>30</v>
       </c>
       <c r="D87" s="4">
-        <v>7.3136219982696771</v>
+        <v>7.527059010217779</v>
       </c>
       <c r="E87" s="4">
-        <v>7.3597714540951547</v>
+        <v>7.5</v>
       </c>
       <c r="F87" s="4">
-        <v>0.55236279879588568</v>
+        <v>0.32704977213802089</v>
       </c>
       <c r="G87" s="4">
         <v>8.08</v>
       </c>
       <c r="H87" s="4">
-        <v>6.274548463389519</v>
+        <v>7.1</v>
       </c>
       <c r="I87" s="4">
-        <v>7.8009999999999993</v>
+        <v>7.9130627908185609</v>
       </c>
       <c r="J87" s="4">
-        <v>7.65</v>
+        <v>7.7525000000000004</v>
       </c>
       <c r="K87" s="4">
-        <v>7.3</v>
+        <v>7.2445569176178752</v>
       </c>
       <c r="L87" s="4">
-        <v>6.470370596344214</v>
+        <v>7.19</v>
       </c>
       <c r="M87" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B88" s="41" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C88" s="32" t="s">
         <v>30</v>
       </c>
       <c r="D88" s="33">
-        <v>6.8647307974561427</v>
+        <v>7.1234364721603809</v>
       </c>
       <c r="E88" s="33">
-        <v>7</v>
+        <v>7.15</v>
       </c>
       <c r="F88" s="33">
-        <v>0.58157836038465016</v>
+        <v>0.31294416868902902</v>
       </c>
       <c r="G88" s="33">
         <v>7.51</v>
       </c>
       <c r="H88" s="33">
-        <v>5.9985369511645477</v>
+        <v>6.6209479589730114</v>
       </c>
       <c r="I88" s="33">
         <v>7.5010000000000003</v>
       </c>
       <c r="J88" s="33">
-        <v>7.3650000000000002</v>
+        <v>7.39</v>
       </c>
       <c r="K88" s="33">
-        <v>6.4604814719474959</v>
+        <v>6.8875625719730946</v>
       </c>
       <c r="L88" s="33">
-        <v>6.0641698498366416</v>
+        <v>6.7820947958973008</v>
       </c>
       <c r="M88" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B89" s="2" t="s">
         <v>36</v>
       </c>
@@ -7869,37 +7876,37 @@
         <v>31</v>
       </c>
       <c r="D89" s="4">
-        <v>7.0989442415886774</v>
+        <v>7.3229546767466021</v>
       </c>
       <c r="E89" s="4">
-        <v>7.3</v>
+        <v>7.2668890043913654</v>
       </c>
       <c r="F89" s="4">
-        <v>0.67558021122334144</v>
+        <v>0.3356857563350964</v>
       </c>
       <c r="G89" s="4">
-        <v>7.7077230281297604</v>
+        <v>7.8357687586832787</v>
       </c>
       <c r="H89" s="4">
-        <v>5.7167676533114582</v>
+        <v>6.7</v>
       </c>
       <c r="I89" s="4">
-        <v>7.6467723028129759</v>
+        <v>7.6595768758683276</v>
       </c>
       <c r="J89" s="4">
-        <v>7.4775</v>
+        <v>7.59</v>
       </c>
       <c r="K89" s="4">
         <v>7.2</v>
       </c>
       <c r="L89" s="4">
-        <v>5.9851333263321456</v>
+        <v>6.97</v>
       </c>
       <c r="M89" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:13" ht="18" x14ac:dyDescent="0.4">
       <c r="B90" s="9"/>
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
@@ -7913,7 +7920,7 @@
       <c r="L90" s="9"/>
       <c r="M90" s="9"/>
     </row>
-    <row r="92" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B92" s="14" t="s">
         <v>32</v>
       </c>
@@ -7929,7 +7936,7 @@
       <c r="L92" s="14"/>
       <c r="M92" s="15"/>
     </row>
-    <row r="93" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B93" s="24" t="s">
         <v>1</v>
       </c>
@@ -7967,7 +7974,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B94" s="38" t="s">
         <v>38</v>
       </c>
@@ -7975,37 +7982,37 @@
         <v>33</v>
       </c>
       <c r="D94" s="33">
-        <v>1.2550491180436341</v>
+        <v>0.32481239870461082</v>
       </c>
       <c r="E94" s="33">
-        <v>1.23</v>
+        <v>0.30406199352305419</v>
       </c>
       <c r="F94" s="33">
-        <v>0.33709289846551571</v>
+        <v>0.35836772021939428</v>
       </c>
       <c r="G94" s="33">
-        <v>1.91</v>
+        <v>1</v>
       </c>
       <c r="H94" s="33">
-        <v>0.8</v>
+        <v>-0.13</v>
       </c>
       <c r="I94" s="33">
-        <v>1.631</v>
+        <v>0.82</v>
       </c>
       <c r="J94" s="33">
-        <v>1.4476227951090841</v>
+        <v>0.4</v>
       </c>
       <c r="K94" s="33">
-        <v>1.01</v>
+        <v>0.11749999999999999</v>
       </c>
       <c r="L94" s="33">
-        <v>0.93499999999999994</v>
+        <v>-8.5000000000000006E-2</v>
       </c>
       <c r="M94" s="40">
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B95" s="6" t="s">
         <v>43</v>
       </c>
@@ -8013,75 +8020,75 @@
         <v>33</v>
       </c>
       <c r="D95" s="4">
-        <v>0.87065999110222592</v>
+        <v>0.95774554315840454</v>
       </c>
       <c r="E95" s="4">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="F95" s="4">
-        <v>0.53936869777869278</v>
+        <v>0.47123553269767421</v>
       </c>
       <c r="G95" s="4">
-        <v>2.2000000000000002</v>
+        <v>1.8</v>
       </c>
       <c r="H95" s="4">
-        <v>0.16659991102225821</v>
+        <v>0.15</v>
       </c>
       <c r="I95" s="4">
-        <v>1.21</v>
+        <v>1.4850000000000001</v>
       </c>
       <c r="J95" s="4">
-        <v>0.96250000000000002</v>
+        <v>1.1225000000000001</v>
       </c>
       <c r="K95" s="4">
-        <v>0.61250000000000004</v>
+        <v>0.80936385789601117</v>
       </c>
       <c r="L95" s="4">
-        <v>0.46665999110222578</v>
+        <v>0.38400000000000001</v>
       </c>
       <c r="M95" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B96" s="41" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C96" s="32" t="s">
         <v>33</v>
       </c>
       <c r="D96" s="33">
-        <v>0.6581134077881361</v>
+        <v>0.89730041345769129</v>
       </c>
       <c r="E96" s="33">
-        <v>0.7</v>
+        <v>0.90650206728845628</v>
       </c>
       <c r="F96" s="33">
-        <v>0.20710426909198801</v>
+        <v>0.27170984261188169</v>
       </c>
       <c r="G96" s="33">
-        <v>0.91</v>
+        <v>1.41</v>
       </c>
       <c r="H96" s="33">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="I96" s="33">
-        <v>0.90100000000000002</v>
+        <v>1.131</v>
       </c>
       <c r="J96" s="33">
-        <v>0.79500000000000004</v>
+        <v>0.98250000000000004</v>
       </c>
       <c r="K96" s="33">
-        <v>0.52528351947034002</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="L96" s="33">
-        <v>0.36499999999999999</v>
+        <v>0.622</v>
       </c>
       <c r="M96" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B97" s="2" t="s">
         <v>36</v>
       </c>
@@ -8089,37 +8096,37 @@
         <v>34</v>
       </c>
       <c r="D97" s="4">
-        <v>3.1902560699018379</v>
+        <v>2.5309488077860349</v>
       </c>
       <c r="E97" s="4">
-        <v>3</v>
+        <v>2.513304840281942</v>
       </c>
       <c r="F97" s="4">
-        <v>0.50447297484337539</v>
+        <v>0.61059626900516895</v>
       </c>
       <c r="G97" s="4">
-        <v>4.0999999999999996</v>
+        <v>3.7</v>
       </c>
       <c r="H97" s="4">
-        <v>2.7328036959836322</v>
+        <v>1.46</v>
       </c>
       <c r="I97" s="4">
-        <v>4.0819999999999999</v>
+        <v>3.07</v>
       </c>
       <c r="J97" s="4">
-        <v>3.2574999999999998</v>
+        <v>2.855</v>
       </c>
       <c r="K97" s="4">
-        <v>2.9</v>
+        <v>2.2107195993241162</v>
       </c>
       <c r="L97" s="4">
-        <v>2.7570616723296348</v>
+        <v>1.946</v>
       </c>
       <c r="M97" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:13" ht="18" x14ac:dyDescent="0.4">
       <c r="B98" s="9" t="s">
         <v>51</v>
       </c>
@@ -8154,9 +8161,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="16384" width="11.453125" style="1"/>
   </cols>
   <sheetData/>
   <sheetProtection algorithmName="SHA-512" hashValue="JI4mgXj1vwTu7GkfF4fWYFkbUu0jpGNsZzzBPX3YfGFuPzcxt+Hjcx6rfoqdT04OcRkZuwwlAbTLaGLAEKR43Q==" saltValue="AakVtiLN9zmEwInSrU9sOA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -8465,16 +8472,16 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB7C2FA5-1A6F-45A0-B729-06C123F95F83}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="6b042263-e944-4dfe-97a8-6e4c84e0ae4b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="b80df5a0-8011-40eb-be96-4c6a59f56b6e"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="b80df5a0-8011-40eb-be96-4c6a59f56b6e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/public/REM/raw/REM.xlsx
+++ b/public/REM/raw/REM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcranet.sharepoint.com/sites/REM/Documentos compartidos/REM/Publicación/Pagina WEB/2026/26 04 Abr/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcranet.sharepoint.com/sites/REM/Documentos compartidos/REM/Publicación/Pagina WEB/2026/26 05 May/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="8_{563D5886-1088-4C76-92B3-92AAC244057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6B43FD0-6DAF-4689-A6AB-67C9C96316FF}"/>
+  <xr:revisionPtr revIDLastSave="121" documentId="8_{563D5886-1088-4C76-92B3-92AAC244057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{553B8805-31A3-4A37-AAB6-8D2F95CFAB19}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8A5F0209-F8EA-4E2B-A469-F799AD0A214D}"/>
   </bookViews>
@@ -184,25 +184,25 @@
     <t>Trim. III-26</t>
   </si>
   <si>
-    <t>Relevamiento de Expectativas de Mercado (REM)  Top 10 - BCRA - Abril 2026</t>
+    <t>Relevamiento de Expectativas de Mercado (REM)  - BCRA - Mayo 2026</t>
   </si>
   <si>
-    <t>var. % i.a.; abr-27</t>
+    <t>var. % i.a.; may-27</t>
   </si>
   <si>
-    <t>var. % i.a.; abr-28</t>
+    <t>var. % i.a.; may-28</t>
   </si>
   <si>
-    <t>TNA; %; abr-27</t>
+    <t>TNA; %; may-27</t>
   </si>
   <si>
-    <t>$/USD; abr-27</t>
+    <t>$/USD; may-27</t>
   </si>
   <si>
-    <t>Fuente: REM - BCRA (abr-26)</t>
+    <t>Fuente: REM - BCRA (may-26)</t>
   </si>
   <si>
-    <t>Relevamiento de Expectativas de Mercado (REM)  - BCRA - Abril 2026</t>
+    <t>Relevamiento de Expectativas de Mercado (REM)  Top 10 - BCRA - Mayo 2026</t>
   </si>
 </sst>
 </file>
@@ -400,7 +400,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -531,6 +531,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1893,7 +1896,7 @@
   <sheetData>
     <row r="2" spans="2:13" ht="20.5" x14ac:dyDescent="0.35">
       <c r="B2" s="11" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -1981,265 +1984,265 @@
     </row>
     <row r="7" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B7" s="17">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="19">
-        <v>2.6</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="E7" s="19">
-        <v>2.635915686224175</v>
+        <v>2.285781786422957</v>
       </c>
       <c r="F7" s="19">
-        <v>0.1933541276142057</v>
+        <v>0.17964644624761211</v>
       </c>
       <c r="G7" s="19">
-        <v>3.2203570721405672</v>
+        <v>3</v>
       </c>
       <c r="H7" s="19">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="I7" s="19">
-        <v>2.86</v>
+        <v>2.494525082167991</v>
       </c>
       <c r="J7" s="19">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="K7" s="19">
-        <v>2.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="L7" s="19">
-        <v>2.452</v>
+        <v>2.1</v>
       </c>
       <c r="M7" s="20">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B8" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="4">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="E8" s="4">
-        <v>2.2867443141716119</v>
+        <v>2.0450934680914599</v>
       </c>
       <c r="F8" s="4">
-        <v>0.39450844352126557</v>
+        <v>0.22524794909787851</v>
       </c>
       <c r="G8" s="4">
-        <v>4.2614964887320861</v>
+        <v>2.6</v>
       </c>
       <c r="H8" s="4">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="I8" s="4">
-        <v>2.532641738593866</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="J8" s="4">
-        <v>2.4</v>
+        <v>2.1924999999999999</v>
       </c>
       <c r="K8" s="4">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="L8" s="4">
-        <v>1.932945170799983</v>
+        <v>1.79</v>
       </c>
       <c r="M8" s="5">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B9" s="17">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="19">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="19">
-        <v>2.0732407212048471</v>
+        <v>1.985883049281437</v>
       </c>
       <c r="F9" s="19">
-        <v>0.31165656475764331</v>
+        <v>0.24108280020744849</v>
       </c>
       <c r="G9" s="19">
-        <v>2.8558870343111442</v>
+        <v>2.5</v>
       </c>
       <c r="H9" s="19">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I9" s="19">
-        <v>2.3719999999999999</v>
+        <v>2.2768713395139319</v>
       </c>
       <c r="J9" s="19">
-        <v>2.220660403931451</v>
+        <v>2.1425000000000001</v>
       </c>
       <c r="K9" s="19">
-        <v>1.97</v>
+        <v>1.8425</v>
       </c>
       <c r="L9" s="19">
-        <v>1.732</v>
+        <v>1.75</v>
       </c>
       <c r="M9" s="20">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="4">
+        <v>1.8</v>
+      </c>
+      <c r="E10" s="4">
+        <v>1.8573360693508489</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.26213937241547541</v>
+      </c>
+      <c r="G10" s="4">
+        <v>2.46</v>
+      </c>
+      <c r="H10" s="4">
+        <v>1</v>
+      </c>
+      <c r="I10" s="4">
+        <v>2.15</v>
+      </c>
+      <c r="J10" s="4">
         <v>2</v>
       </c>
-      <c r="E10" s="4">
-        <v>2.054743329977732</v>
-      </c>
-      <c r="F10" s="4">
-        <v>0.3996493780329925</v>
-      </c>
-      <c r="G10" s="4">
-        <v>3.5</v>
-      </c>
-      <c r="H10" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="I10" s="4">
-        <v>2.452</v>
-      </c>
-      <c r="J10" s="4">
-        <v>2.23</v>
-      </c>
       <c r="K10" s="4">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="L10" s="4">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="M10" s="5">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B11" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="19">
-        <v>1.8</v>
+        <v>1.8854172985115869</v>
       </c>
       <c r="E11" s="19">
-        <v>1.8950276844426019</v>
+        <v>1.8336228542689259</v>
       </c>
       <c r="F11" s="19">
-        <v>0.35886032468214718</v>
+        <v>0.32522298830110818</v>
       </c>
       <c r="G11" s="19">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="H11" s="19">
-        <v>0.70000000000000007</v>
+        <v>0.6</v>
       </c>
       <c r="I11" s="19">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="J11" s="19">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="K11" s="19">
-        <v>1.7</v>
+        <v>1.665461555695821</v>
       </c>
       <c r="L11" s="19">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M11" s="20">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="4">
-        <v>1.87</v>
+        <v>1.7749999999999999</v>
       </c>
       <c r="E12" s="4">
-        <v>1.881652139799723</v>
+        <v>1.7326545942473111</v>
       </c>
       <c r="F12" s="4">
-        <v>0.36698905341149829</v>
+        <v>0.29675539962959019</v>
       </c>
       <c r="G12" s="4">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="H12" s="4">
         <v>0.6</v>
       </c>
       <c r="I12" s="4">
-        <v>2.3220000000000001</v>
+        <v>2.0012070003531912</v>
       </c>
       <c r="J12" s="4">
-        <v>2.0381302513900401</v>
+        <v>1.9</v>
       </c>
       <c r="K12" s="4">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="L12" s="4">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="M12" s="5">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B13" s="17">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="19">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="E13" s="19">
-        <v>1.7747136838776449</v>
+        <v>1.6760885061332751</v>
       </c>
       <c r="F13" s="19">
-        <v>0.34574101990640049</v>
+        <v>0.26707572545525898</v>
       </c>
       <c r="G13" s="19">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H13" s="19">
         <v>0.6</v>
       </c>
       <c r="I13" s="19">
-        <v>2.206</v>
+        <v>1.9359999999999999</v>
       </c>
       <c r="J13" s="19">
-        <v>1.989568231212052</v>
+        <v>1.8</v>
       </c>
       <c r="K13" s="19">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="L13" s="19">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="M13" s="20">
         <v>45</v>
@@ -2253,31 +2256,31 @@
         <v>47</v>
       </c>
       <c r="D14" s="4">
-        <v>24.15</v>
+        <v>23.31743678321612</v>
       </c>
       <c r="E14" s="4">
-        <v>24.11784834817918</v>
+        <v>22.796142688134761</v>
       </c>
       <c r="F14" s="4">
-        <v>4.1853015587247828</v>
+        <v>3.3387418960753048</v>
       </c>
       <c r="G14" s="4">
-        <v>34.556839957471212</v>
+        <v>28.8</v>
       </c>
       <c r="H14" s="4">
-        <v>9.15</v>
+        <v>9.4</v>
       </c>
       <c r="I14" s="4">
-        <v>28.213999999999999</v>
+        <v>25.731000000000002</v>
       </c>
       <c r="J14" s="4">
-        <v>26.524999999999999</v>
+        <v>24.682385686237382</v>
       </c>
       <c r="K14" s="4">
-        <v>22.454999999999998</v>
+        <v>21.517499999999998</v>
       </c>
       <c r="L14" s="4">
-        <v>21.11</v>
+        <v>20.648</v>
       </c>
       <c r="M14" s="5">
         <v>42</v>
@@ -2291,31 +2294,31 @@
         <v>48</v>
       </c>
       <c r="D15" s="19">
-        <v>17.41</v>
+        <v>17.5</v>
       </c>
       <c r="E15" s="19">
-        <v>17.119769979325341</v>
+        <v>17.210252407648429</v>
       </c>
       <c r="F15" s="19">
-        <v>4.1458638126479199</v>
+        <v>4.0811034895200704</v>
       </c>
       <c r="G15" s="19">
-        <v>24</v>
+        <v>24.16299069908365</v>
       </c>
       <c r="H15" s="19">
-        <v>3.1</v>
+        <v>6.1</v>
       </c>
       <c r="I15" s="19">
-        <v>21.04</v>
+        <v>22.3489756849123</v>
       </c>
       <c r="J15" s="19">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="K15" s="19">
-        <v>15.23</v>
+        <v>15</v>
       </c>
       <c r="L15" s="19">
-        <v>12.407999999999999</v>
+        <v>12.512582564000001</v>
       </c>
       <c r="M15" s="20">
         <v>37</v>
@@ -2332,31 +2335,31 @@
         <v>30.5</v>
       </c>
       <c r="E16" s="4">
-        <v>30.873891340780052</v>
+        <v>30.462958270773701</v>
       </c>
       <c r="F16" s="4">
-        <v>3.258278527528184</v>
+        <v>2.1817720385053709</v>
       </c>
       <c r="G16" s="4">
-        <v>40.776691402728588</v>
+        <v>35.4</v>
       </c>
       <c r="H16" s="4">
-        <v>19</v>
+        <v>21.4</v>
       </c>
       <c r="I16" s="4">
-        <v>34.883323368401292</v>
+        <v>32.55746476588584</v>
       </c>
       <c r="J16" s="4">
-        <v>32.493578750716757</v>
+        <v>31.9</v>
       </c>
       <c r="K16" s="4">
-        <v>29.364008464559021</v>
+        <v>29.25</v>
       </c>
       <c r="L16" s="4">
-        <v>28.167999999999999</v>
+        <v>28.705206782484421</v>
       </c>
       <c r="M16" s="5">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -2367,34 +2370,34 @@
         <v>17</v>
       </c>
       <c r="D17" s="19">
-        <v>19.915550103960111</v>
+        <v>19.920000000000002</v>
       </c>
       <c r="E17" s="19">
-        <v>19.793336033059081</v>
+        <v>19.802549403597862</v>
       </c>
       <c r="F17" s="19">
-        <v>4.4722081043372981</v>
+        <v>4.1579769494315082</v>
       </c>
       <c r="G17" s="19">
-        <v>26.9</v>
+        <v>28</v>
       </c>
       <c r="H17" s="19">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="I17" s="19">
-        <v>24.84</v>
+        <v>24.85</v>
       </c>
       <c r="J17" s="19">
-        <v>22.35</v>
+        <v>22.2</v>
       </c>
       <c r="K17" s="19">
-        <v>18.05</v>
+        <v>17.945904117817729</v>
       </c>
       <c r="L17" s="19">
-        <v>15.718</v>
+        <v>15.78</v>
       </c>
       <c r="M17" s="20">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -2405,34 +2408,34 @@
         <v>40</v>
       </c>
       <c r="D18" s="4">
-        <v>13.340712010048231</v>
+        <v>13.933243741899011</v>
       </c>
       <c r="E18" s="4">
-        <v>12.7948750098069</v>
+        <v>13.8722421063352</v>
       </c>
       <c r="F18" s="4">
-        <v>4.0827398420033214</v>
+        <v>4.776649656960462</v>
       </c>
       <c r="G18" s="4">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H18" s="4">
         <v>2.4</v>
       </c>
       <c r="I18" s="4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="J18" s="4">
-        <v>15.035044420583271</v>
+        <v>15.975</v>
       </c>
       <c r="K18" s="4">
-        <v>10.57365283835305</v>
+        <v>11.932499999999999</v>
       </c>
       <c r="L18" s="4">
-        <v>7.751672731833902</v>
+        <v>8.25</v>
       </c>
       <c r="M18" s="5">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -2491,37 +2494,37 @@
     </row>
     <row r="23" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B23" s="17">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="19">
-        <v>2.5721153846153841</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E23" s="19">
-        <v>2.5560386731405531</v>
+        <v>2.186987611982687</v>
       </c>
       <c r="F23" s="19">
-        <v>0.30638569540681349</v>
+        <v>0.1887204567740951</v>
       </c>
       <c r="G23" s="19">
-        <v>3.4716475453420599</v>
+        <v>2.5</v>
       </c>
       <c r="H23" s="19">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="I23" s="19">
-        <v>2.84</v>
+        <v>2.4029316853922098</v>
       </c>
       <c r="J23" s="19">
-        <v>2.8</v>
+        <v>2.31</v>
       </c>
       <c r="K23" s="19">
-        <v>2.3199999999999998</v>
+        <v>2.0068546149244821</v>
       </c>
       <c r="L23" s="19">
-        <v>2.1840000000000002</v>
+        <v>1.9488768904442839</v>
       </c>
       <c r="M23" s="20">
         <v>37</v>
@@ -2529,37 +2532,37 @@
     </row>
     <row r="24" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B24" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="4">
-        <v>2.2999999999999998</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="E24" s="4">
-        <v>2.3243118147546502</v>
+        <v>2.054988686693239</v>
       </c>
       <c r="F24" s="4">
-        <v>0.32088497231341062</v>
+        <v>0.25440500284736861</v>
       </c>
       <c r="G24" s="4">
-        <v>3</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="H24" s="4">
+        <v>1.51</v>
+      </c>
+      <c r="I24" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="J24" s="4">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K24" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="L24" s="4">
         <v>1.7</v>
-      </c>
-      <c r="I24" s="4">
-        <v>2.7240000000000002</v>
-      </c>
-      <c r="J24" s="4">
-        <v>2.5189618916171308</v>
-      </c>
-      <c r="K24" s="4">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="L24" s="4">
-        <v>1.896237932828313</v>
       </c>
       <c r="M24" s="5">
         <v>37</v>
@@ -2567,37 +2570,37 @@
     </row>
     <row r="25" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B25" s="17">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="19">
-        <v>2.15</v>
+        <v>1.9462201480758829</v>
       </c>
       <c r="E25" s="19">
-        <v>2.1327271299301791</v>
+        <v>1.961991474310786</v>
       </c>
       <c r="F25" s="19">
-        <v>0.32395183978377479</v>
+        <v>0.26300444134194872</v>
       </c>
       <c r="G25" s="19">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="H25" s="19">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="I25" s="19">
-        <v>2.6</v>
+        <v>2.2879999999999998</v>
       </c>
       <c r="J25" s="19">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="K25" s="19">
-        <v>1.987760003120312</v>
+        <v>1.88</v>
       </c>
       <c r="L25" s="19">
-        <v>1.7</v>
+        <v>1.6419999999999999</v>
       </c>
       <c r="M25" s="20">
         <v>37</v>
@@ -2605,37 +2608,37 @@
     </row>
     <row r="26" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B26" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="E26" s="4">
+        <v>1.888434240749078</v>
+      </c>
+      <c r="F26" s="4">
+        <v>0.25807196180085251</v>
+      </c>
+      <c r="G26" s="4">
+        <v>2.54</v>
+      </c>
+      <c r="H26" s="4">
+        <v>1.4</v>
+      </c>
+      <c r="I26" s="4">
+        <v>2.27</v>
+      </c>
+      <c r="J26" s="4">
         <v>2</v>
       </c>
-      <c r="E26" s="4">
-        <v>2.0768936912734759</v>
-      </c>
-      <c r="F26" s="4">
-        <v>0.42272587283286489</v>
-      </c>
-      <c r="G26" s="4">
-        <v>3.6750000000000012</v>
-      </c>
-      <c r="H26" s="4">
-        <v>1.28</v>
-      </c>
-      <c r="I26" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="J26" s="4">
-        <v>2.2793558945894778</v>
-      </c>
       <c r="K26" s="4">
-        <v>1.8825022900359301</v>
+        <v>1.71</v>
       </c>
       <c r="L26" s="4">
-        <v>1.7</v>
+        <v>1.631208619680474</v>
       </c>
       <c r="M26" s="5">
         <v>37</v>
@@ -2643,37 +2646,37 @@
     </row>
     <row r="27" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B27" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C27" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="19">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="E27" s="19">
-        <v>1.9564956241261711</v>
+        <v>1.821751013824203</v>
       </c>
       <c r="F27" s="19">
-        <v>0.34389397363868818</v>
+        <v>0.23925530572572001</v>
       </c>
       <c r="G27" s="19">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="H27" s="19">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="I27" s="19">
-        <v>2.3997573654000761</v>
+        <v>2.087405516006728</v>
       </c>
       <c r="J27" s="19">
-        <v>2.1016718750000001</v>
+        <v>1.95</v>
       </c>
       <c r="K27" s="19">
         <v>1.7</v>
       </c>
       <c r="L27" s="19">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="M27" s="20">
         <v>37</v>
@@ -2681,37 +2684,37 @@
     </row>
     <row r="28" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B28" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D28" s="4">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="E28" s="4">
-        <v>1.866648694429669</v>
+        <v>1.752377867350426</v>
       </c>
       <c r="F28" s="4">
-        <v>0.29675319451424642</v>
+        <v>0.23059663001893241</v>
       </c>
       <c r="G28" s="4">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="H28" s="4">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I28" s="4">
-        <v>2.2440000000000002</v>
+        <v>2.004</v>
       </c>
       <c r="J28" s="4">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K28" s="4">
-        <v>1.632420782765087</v>
+        <v>1.615552331574688</v>
       </c>
       <c r="L28" s="4">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="M28" s="5">
         <v>37</v>
@@ -2719,7 +2722,7 @@
     </row>
     <row r="29" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B29" s="17">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>13</v>
@@ -2728,31 +2731,31 @@
         <v>1.71</v>
       </c>
       <c r="E29" s="19">
-        <v>1.7825296567894311</v>
+        <v>1.718483531497051</v>
       </c>
       <c r="F29" s="19">
-        <v>0.28457977612416618</v>
+        <v>0.2382530427895953</v>
       </c>
       <c r="G29" s="19">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="H29" s="19">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I29" s="19">
-        <v>2.1440000000000001</v>
+        <v>2</v>
       </c>
       <c r="J29" s="19">
-        <v>1.9161827716113551</v>
+        <v>1.8613407091195291</v>
       </c>
       <c r="K29" s="19">
-        <v>1.606797367064128</v>
+        <v>1.5974999999999999</v>
       </c>
       <c r="L29" s="19">
-        <v>1.5</v>
+        <v>1.477148570530711</v>
       </c>
       <c r="M29" s="20">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -2763,31 +2766,31 @@
         <v>47</v>
       </c>
       <c r="D30" s="4">
-        <v>24.262037811214771</v>
+        <v>23.264058795931209</v>
       </c>
       <c r="E30" s="4">
-        <v>24.29873134822914</v>
+        <v>22.963397704185429</v>
       </c>
       <c r="F30" s="4">
-        <v>3.544919403683334</v>
+        <v>2.9623276792942002</v>
       </c>
       <c r="G30" s="4">
-        <v>33.1</v>
+        <v>30.9</v>
       </c>
       <c r="H30" s="4">
-        <v>14.7</v>
+        <v>15.7</v>
       </c>
       <c r="I30" s="4">
-        <v>28.471684183960569</v>
+        <v>25.74</v>
       </c>
       <c r="J30" s="4">
-        <v>25.635000000000002</v>
+        <v>24.655000000000001</v>
       </c>
       <c r="K30" s="4">
-        <v>22.727401914941009</v>
+        <v>21.512499999999999</v>
       </c>
       <c r="L30" s="4">
-        <v>20.425000000000001</v>
+        <v>19.457000000000001</v>
       </c>
       <c r="M30" s="5">
         <v>34</v>
@@ -2801,31 +2804,31 @@
         <v>48</v>
       </c>
       <c r="D31" s="19">
-        <v>17.089141716136961</v>
+        <v>17.910842132722731</v>
       </c>
       <c r="E31" s="19">
-        <v>16.829381000364261</v>
+        <v>16.895881186644349</v>
       </c>
       <c r="F31" s="19">
-        <v>4.6611306387057798</v>
+        <v>4.5325415203253003</v>
       </c>
       <c r="G31" s="19">
-        <v>24</v>
+        <v>23.6</v>
       </c>
       <c r="H31" s="19">
-        <v>2.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I31" s="19">
-        <v>20.97</v>
+        <v>21.98</v>
       </c>
       <c r="J31" s="19">
-        <v>19.934455264428021</v>
+        <v>19.649999999999999</v>
       </c>
       <c r="K31" s="19">
-        <v>15.0025</v>
+        <v>14.2</v>
       </c>
       <c r="L31" s="19">
-        <v>9.7459586381162531</v>
+        <v>9.2527298799494151</v>
       </c>
       <c r="M31" s="20">
         <v>32</v>
@@ -2839,34 +2842,34 @@
         <v>16</v>
       </c>
       <c r="D32" s="4">
-        <v>30.274718214025651</v>
+        <v>29.742854205066639</v>
       </c>
       <c r="E32" s="4">
-        <v>30.745577763395492</v>
+        <v>29.730864754698771</v>
       </c>
       <c r="F32" s="4">
-        <v>2.8444369519580608</v>
+        <v>1.928062980188856</v>
       </c>
       <c r="G32" s="4">
-        <v>38.700000000000003</v>
+        <v>34.6</v>
       </c>
       <c r="H32" s="4">
-        <v>26</v>
+        <v>26.4</v>
       </c>
       <c r="I32" s="4">
-        <v>34.429864380011168</v>
+        <v>31.963136003163498</v>
       </c>
       <c r="J32" s="4">
-        <v>32.1</v>
+        <v>30.68135047018913</v>
       </c>
       <c r="K32" s="4">
-        <v>29.05</v>
+        <v>28.581712787023811</v>
       </c>
       <c r="L32" s="4">
-        <v>27.370535381404899</v>
+        <v>27.5</v>
       </c>
       <c r="M32" s="5">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -2877,31 +2880,31 @@
         <v>17</v>
       </c>
       <c r="D33" s="19">
-        <v>19.33084243639756</v>
+        <v>19.460842436397559</v>
       </c>
       <c r="E33" s="19">
-        <v>19.05945285543137</v>
+        <v>19.390588132434591</v>
       </c>
       <c r="F33" s="19">
-        <v>4.5845098097321113</v>
+        <v>4.3987564479017136</v>
       </c>
       <c r="G33" s="19">
-        <v>27.4</v>
+        <v>31</v>
       </c>
       <c r="H33" s="19">
-        <v>3.6</v>
+        <v>8.9</v>
       </c>
       <c r="I33" s="19">
-        <v>23.88468738898807</v>
+        <v>24.133972316289132</v>
       </c>
       <c r="J33" s="19">
-        <v>22.55</v>
+        <v>21.994890336011771</v>
       </c>
       <c r="K33" s="19">
-        <v>17.600000000000001</v>
+        <v>17.5975</v>
       </c>
       <c r="L33" s="19">
-        <v>12.96662072254998</v>
+        <v>12.975369215951529</v>
       </c>
       <c r="M33" s="20">
         <v>36</v>
@@ -2915,34 +2918,34 @@
         <v>40</v>
       </c>
       <c r="D34" s="4">
-        <v>12.864489487</v>
+        <v>13.90648748379801</v>
       </c>
       <c r="E34" s="4">
-        <v>12.64748023646783</v>
+        <v>13.603635463983871</v>
       </c>
       <c r="F34" s="4">
-        <v>4.2732020259204706</v>
+        <v>4.9034633497087734</v>
       </c>
       <c r="G34" s="4">
-        <v>21.9</v>
+        <v>25</v>
       </c>
       <c r="H34" s="4">
         <v>1.8</v>
       </c>
       <c r="I34" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J34" s="4">
-        <v>14.28693255274775</v>
+        <v>15.65</v>
       </c>
       <c r="K34" s="4">
-        <v>10.896984498277339</v>
+        <v>11.3</v>
       </c>
       <c r="L34" s="4">
-        <v>7.5049582472899523</v>
+        <v>7.6293783124454118</v>
       </c>
       <c r="M34" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
@@ -3005,37 +3008,37 @@
     </row>
     <row r="39" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B39" s="7">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="26">
-        <v>23.1</v>
+        <v>22.75</v>
       </c>
       <c r="E39" s="26">
-        <v>23.0812035107664</v>
+        <v>22.644042428977041</v>
       </c>
       <c r="F39" s="26">
-        <v>1.0704068273868279</v>
+        <v>1.0857484117050431</v>
       </c>
       <c r="G39" s="4">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="H39" s="4">
-        <v>21</v>
+        <v>20.41</v>
       </c>
       <c r="I39" s="4">
-        <v>24</v>
+        <v>23.6</v>
       </c>
       <c r="J39" s="4">
-        <v>23.63</v>
+        <v>23</v>
       </c>
       <c r="K39" s="4">
-        <v>22.359375</v>
+        <v>22</v>
       </c>
       <c r="L39" s="4">
-        <v>21.797771628441751</v>
+        <v>21.4</v>
       </c>
       <c r="M39" s="8">
         <v>41</v>
@@ -3043,37 +3046,37 @@
     </row>
     <row r="40" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B40" s="17">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C40" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="27">
-        <v>22.949459806961709</v>
+        <v>22.8</v>
       </c>
       <c r="E40" s="27">
-        <v>22.8105751652487</v>
+        <v>22.86331300534502</v>
       </c>
       <c r="F40" s="27">
-        <v>1.390274547889816</v>
+        <v>1.993401616492493</v>
       </c>
       <c r="G40" s="19">
-        <v>25.9</v>
+        <v>30.336397852763231</v>
       </c>
       <c r="H40" s="19">
-        <v>20</v>
+        <v>19.815636601137939</v>
       </c>
       <c r="I40" s="19">
-        <v>25</v>
+        <v>24.2</v>
       </c>
       <c r="J40" s="19">
-        <v>23.34833320879472</v>
+        <v>23.6</v>
       </c>
       <c r="K40" s="19">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="L40" s="19">
-        <v>20.8</v>
+        <v>20.79</v>
       </c>
       <c r="M40" s="20">
         <v>41</v>
@@ -3081,37 +3084,37 @@
     </row>
     <row r="41" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D41" s="26">
-        <v>22.795572916666671</v>
+        <v>22.7</v>
       </c>
       <c r="E41" s="26">
-        <v>22.88682351686229</v>
+        <v>22.82262020950882</v>
       </c>
       <c r="F41" s="26">
-        <v>2.0106638467265219</v>
+        <v>2.2579219503603118</v>
       </c>
       <c r="G41" s="4">
-        <v>28.515862006449311</v>
+        <v>30.208643875427299</v>
       </c>
       <c r="H41" s="4">
-        <v>19.28</v>
+        <v>18.749676071340001</v>
       </c>
       <c r="I41" s="4">
-        <v>25.4</v>
+        <v>24.7</v>
       </c>
       <c r="J41" s="4">
         <v>24.1</v>
       </c>
       <c r="K41" s="4">
-        <v>21.8</v>
+        <v>21.2</v>
       </c>
       <c r="L41" s="4">
-        <v>20.399999999999999</v>
+        <v>20.5</v>
       </c>
       <c r="M41" s="5">
         <v>41</v>
@@ -3119,37 +3122,37 @@
     </row>
     <row r="42" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B42" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C42" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D42" s="27">
-        <v>22.550833084256119</v>
+        <v>22.8</v>
       </c>
       <c r="E42" s="27">
-        <v>22.89291460207615</v>
+        <v>22.791386201724489</v>
       </c>
       <c r="F42" s="27">
-        <v>2.6464120904879511</v>
+        <v>2.379015892209392</v>
       </c>
       <c r="G42" s="19">
-        <v>28.72311223847257</v>
+        <v>27.5</v>
       </c>
       <c r="H42" s="19">
-        <v>17.5625353699767</v>
+        <v>17.68371554154205</v>
       </c>
       <c r="I42" s="19">
-        <v>26.2</v>
+        <v>25.8</v>
       </c>
       <c r="J42" s="19">
-        <v>24.7</v>
+        <v>24.4</v>
       </c>
       <c r="K42" s="19">
         <v>21</v>
       </c>
       <c r="L42" s="19">
-        <v>19.804124938433201</v>
+        <v>20</v>
       </c>
       <c r="M42" s="20">
         <v>41</v>
@@ -3157,28 +3160,28 @@
     </row>
     <row r="43" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B43" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D43" s="26">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="E43" s="26">
-        <v>22.860155519261131</v>
+        <v>22.54169141134933</v>
       </c>
       <c r="F43" s="26">
-        <v>2.7003013418734358</v>
+        <v>2.7697306467237719</v>
       </c>
       <c r="G43" s="4">
-        <v>28.6</v>
+        <v>29.01</v>
       </c>
       <c r="H43" s="4">
-        <v>16.50372630536042</v>
+        <v>16.617755011744119</v>
       </c>
       <c r="I43" s="4">
-        <v>26.5</v>
+        <v>25.44</v>
       </c>
       <c r="J43" s="4">
         <v>24.5</v>
@@ -3187,7 +3190,7 @@
         <v>21</v>
       </c>
       <c r="L43" s="4">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="M43" s="5">
         <v>41</v>
@@ -3195,7 +3198,7 @@
     </row>
     <row r="44" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B44" s="17">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C44" s="18" t="s">
         <v>19</v>
@@ -3204,28 +3207,28 @@
         <v>22.3</v>
       </c>
       <c r="E44" s="27">
-        <v>22.593670711401959</v>
+        <v>22.188500289152849</v>
       </c>
       <c r="F44" s="27">
-        <v>3.0597223559784812</v>
+        <v>2.7808406071242362</v>
       </c>
       <c r="G44" s="19">
-        <v>29.12</v>
+        <v>27.6</v>
       </c>
       <c r="H44" s="19">
-        <v>15.444917240744131</v>
+        <v>16.084774746845131</v>
       </c>
       <c r="I44" s="19">
-        <v>26.612359975325329</v>
+        <v>25.97</v>
       </c>
       <c r="J44" s="19">
-        <v>24.1</v>
+        <v>23.33</v>
       </c>
       <c r="K44" s="19">
-        <v>20.967461005451391</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="L44" s="19">
-        <v>19.067560763888888</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="M44" s="20">
         <v>41</v>
@@ -3239,34 +3242,34 @@
         <v>49</v>
       </c>
       <c r="D45" s="26">
-        <v>20.7</v>
+        <v>20.29</v>
       </c>
       <c r="E45" s="26">
-        <v>20.171513953840279</v>
+        <v>20.529360093705069</v>
       </c>
       <c r="F45" s="26">
-        <v>3.7540939031233762</v>
+        <v>2.7861710349981008</v>
       </c>
       <c r="G45" s="4">
-        <v>27.85</v>
+        <v>28</v>
       </c>
       <c r="H45" s="4">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="I45" s="4">
-        <v>24</v>
+        <v>23.466000000000001</v>
       </c>
       <c r="J45" s="4">
-        <v>22.074999999999999</v>
+        <v>22.5</v>
       </c>
       <c r="K45" s="4">
-        <v>18.0275</v>
+        <v>19.127154161757659</v>
       </c>
       <c r="L45" s="4">
-        <v>16.35178663625793</v>
+        <v>17.3</v>
       </c>
       <c r="M45" s="5">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -3277,31 +3280,31 @@
         <v>20</v>
       </c>
       <c r="D46" s="27">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="E46" s="27">
-        <v>22.12359937628058</v>
+        <v>22.054607839260509</v>
       </c>
       <c r="F46" s="27">
-        <v>3.4620746879673479</v>
+        <v>2.8187681324373979</v>
       </c>
       <c r="G46" s="19">
-        <v>31.09</v>
+        <v>28.2</v>
       </c>
       <c r="H46" s="19">
-        <v>14.38610817612787</v>
+        <v>15.2</v>
       </c>
       <c r="I46" s="19">
-        <v>26.627157980800192</v>
+        <v>26</v>
       </c>
       <c r="J46" s="19">
-        <v>24</v>
+        <v>23.1</v>
       </c>
       <c r="K46" s="19">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="L46" s="19">
-        <v>19.067560763888888</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="M46" s="20">
         <v>41</v>
@@ -3315,34 +3318,34 @@
         <v>41</v>
       </c>
       <c r="D47" s="26">
-        <v>17.899999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="E47" s="26">
-        <v>17.864777524989648</v>
+        <v>19.18294068968158</v>
       </c>
       <c r="F47" s="26">
-        <v>4.7206460376698187</v>
+        <v>4.3004308521398054</v>
       </c>
       <c r="G47" s="4">
-        <v>27.5</v>
+        <v>28.6</v>
       </c>
       <c r="H47" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I47" s="4">
-        <v>23.82330333109774</v>
+        <v>24.44</v>
       </c>
       <c r="J47" s="4">
-        <v>22</v>
+        <v>22.4</v>
       </c>
       <c r="K47" s="4">
-        <v>14.47</v>
+        <v>16.2</v>
       </c>
       <c r="L47" s="4">
-        <v>12.46</v>
+        <v>14.339220846486249</v>
       </c>
       <c r="M47" s="5">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
@@ -3405,230 +3408,230 @@
     </row>
     <row r="52" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B52" s="7">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D52" s="28">
-        <v>1410</v>
+        <v>1422</v>
       </c>
       <c r="E52" s="28">
-        <v>1416.863500134916</v>
+        <v>1422.557114858188</v>
       </c>
       <c r="F52" s="28">
-        <v>29.519830644725712</v>
+        <v>12.75563630998457</v>
       </c>
       <c r="G52" s="28">
-        <v>1551.1141640000001</v>
+        <v>1455.4860851437541</v>
       </c>
       <c r="H52" s="28">
-        <v>1373</v>
+        <v>1400</v>
       </c>
       <c r="I52" s="28">
-        <v>1437.9442986481049</v>
+        <v>1439.2049999999999</v>
       </c>
       <c r="J52" s="28">
-        <v>1425</v>
+        <v>1429.95</v>
       </c>
       <c r="K52" s="28">
-        <v>1401.72</v>
+        <v>1413.953306943625</v>
       </c>
       <c r="L52" s="28">
-        <v>1389.4</v>
+        <v>1406.4649999999999</v>
       </c>
       <c r="M52" s="5">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B53" s="17">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C53" s="18" t="s">
         <v>22</v>
       </c>
       <c r="D53" s="29">
-        <v>1437</v>
+        <v>1447.239968621363</v>
       </c>
       <c r="E53" s="29">
-        <v>1441.295650977456</v>
+        <v>1448.9632257264959</v>
       </c>
       <c r="F53" s="29">
-        <v>34.3013807971994</v>
+        <v>22.509710297950701</v>
       </c>
       <c r="G53" s="29">
-        <v>1542.582429</v>
+        <v>1518.113150242837</v>
       </c>
       <c r="H53" s="29">
-        <v>1379.33</v>
+        <v>1400</v>
       </c>
       <c r="I53" s="29">
-        <v>1483.342420640874</v>
+        <v>1471.56203592426</v>
       </c>
       <c r="J53" s="29">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="K53" s="29">
-        <v>1422.5338834416859</v>
+        <v>1438.30013117098</v>
       </c>
       <c r="L53" s="29">
-        <v>1400.8</v>
+        <v>1422.83</v>
       </c>
       <c r="M53" s="20">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B54" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D54" s="28">
-        <v>1460</v>
+        <v>1475.902377802618</v>
       </c>
       <c r="E54" s="28">
-        <v>1468.518375575328</v>
+        <v>1483.1522496739251</v>
       </c>
       <c r="F54" s="28">
-        <v>43.259148331608593</v>
+        <v>36.326100544981102</v>
       </c>
       <c r="G54" s="28">
-        <v>1572.5137340000001</v>
+        <v>1589.4763832425319</v>
       </c>
       <c r="H54" s="28">
-        <v>1386</v>
+        <v>1420</v>
       </c>
       <c r="I54" s="28">
-        <v>1528.637283489229</v>
+        <v>1527.91</v>
       </c>
       <c r="J54" s="28">
-        <v>1493.546379994777</v>
+        <v>1496.9947995622281</v>
       </c>
       <c r="K54" s="28">
-        <v>1442</v>
+        <v>1463.7891155680879</v>
       </c>
       <c r="L54" s="28">
-        <v>1418.32</v>
+        <v>1444.6</v>
       </c>
       <c r="M54" s="5">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B55" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C55" s="18" t="s">
         <v>22</v>
       </c>
       <c r="D55" s="29">
-        <v>1500</v>
+        <v>1516.418897928615</v>
       </c>
       <c r="E55" s="29">
-        <v>1507.7131637901621</v>
+        <v>1521.7073994063021</v>
       </c>
       <c r="F55" s="29">
-        <v>53.894629966054502</v>
+        <v>50.305564646569671</v>
       </c>
       <c r="G55" s="29">
-        <v>1627.375896782112</v>
+        <v>1679.9475768687271</v>
       </c>
       <c r="H55" s="29">
-        <v>1392</v>
+        <v>1428</v>
       </c>
       <c r="I55" s="29">
-        <v>1593.6</v>
+        <v>1587.81</v>
       </c>
       <c r="J55" s="29">
-        <v>1534.43</v>
+        <v>1543.4080208720329</v>
       </c>
       <c r="K55" s="29">
-        <v>1475</v>
+        <v>1494.1828901986451</v>
       </c>
       <c r="L55" s="29">
-        <v>1454.6953454503539</v>
+        <v>1466</v>
       </c>
       <c r="M55" s="20">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B56" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D56" s="28">
-        <v>1533</v>
+        <v>1552.90364776349</v>
       </c>
       <c r="E56" s="28">
-        <v>1546.886483291177</v>
+        <v>1562.801289737173</v>
       </c>
       <c r="F56" s="28">
-        <v>60.698836203126447</v>
+        <v>60.630752275269643</v>
       </c>
       <c r="G56" s="28">
-        <v>1708.30283798855</v>
+        <v>1766.3306638135209</v>
       </c>
       <c r="H56" s="28">
-        <v>1397</v>
+        <v>1435</v>
       </c>
       <c r="I56" s="28">
-        <v>1616.18712460698</v>
+        <v>1639.8357552689929</v>
       </c>
       <c r="J56" s="28">
-        <v>1585</v>
+        <v>1589.98242923507</v>
       </c>
       <c r="K56" s="28">
-        <v>1510.41</v>
+        <v>1532.087604614087</v>
       </c>
       <c r="L56" s="28">
-        <v>1492.1137082654991</v>
+        <v>1497.05</v>
       </c>
       <c r="M56" s="5">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B57" s="17">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C57" s="18" t="s">
         <v>22</v>
       </c>
       <c r="D57" s="29">
-        <v>1578.825</v>
+        <v>1596.778465322594</v>
       </c>
       <c r="E57" s="29">
-        <v>1588.762421590513</v>
+        <v>1602.8742837752061</v>
       </c>
       <c r="F57" s="29">
-        <v>70.469362916634893</v>
+        <v>72.983020902140495</v>
       </c>
       <c r="G57" s="29">
-        <v>1796.143955541193</v>
+        <v>1848.053518746955</v>
       </c>
       <c r="H57" s="29">
-        <v>1404</v>
+        <v>1441</v>
       </c>
       <c r="I57" s="29">
-        <v>1683.0440270978149</v>
+        <v>1700.2940000000001</v>
       </c>
       <c r="J57" s="29">
-        <v>1621.23338496</v>
+        <v>1632.54</v>
       </c>
       <c r="K57" s="29">
-        <v>1542</v>
+        <v>1564.6547476439291</v>
       </c>
       <c r="L57" s="29">
-        <v>1518.5015806722779</v>
+        <v>1513.64</v>
       </c>
       <c r="M57" s="20">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -3639,31 +3642,31 @@
         <v>50</v>
       </c>
       <c r="D58" s="28">
-        <v>1789</v>
+        <v>1760</v>
       </c>
       <c r="E58" s="28">
-        <v>1785.924216785096</v>
+        <v>1782.4587625709939</v>
       </c>
       <c r="F58" s="28">
-        <v>124.3433240998848</v>
+        <v>129.61801099286299</v>
       </c>
       <c r="G58" s="28">
-        <v>2044.705388943687</v>
+        <v>2034.3223115228591</v>
       </c>
       <c r="H58" s="28">
-        <v>1436</v>
+        <v>1473</v>
       </c>
       <c r="I58" s="28">
-        <v>1959.11</v>
+        <v>1970.89</v>
       </c>
       <c r="J58" s="28">
-        <v>1866</v>
+        <v>1850</v>
       </c>
       <c r="K58" s="28">
-        <v>1702.2</v>
+        <v>1702</v>
       </c>
       <c r="L58" s="28">
-        <v>1657.361924210194</v>
+        <v>1623.7</v>
       </c>
       <c r="M58" s="5">
         <v>41</v>
@@ -3677,34 +3680,34 @@
         <v>23</v>
       </c>
       <c r="D59" s="29">
-        <v>1676</v>
+        <v>1658.07</v>
       </c>
       <c r="E59" s="29">
-        <v>1683.691910504996</v>
+        <v>1660.1411723744859</v>
       </c>
       <c r="F59" s="29">
-        <v>95.269128238098276</v>
+        <v>91.158382964724623</v>
       </c>
       <c r="G59" s="29">
-        <v>1951.6328885343901</v>
+        <v>1921.133038869473</v>
       </c>
       <c r="H59" s="29">
-        <v>1416</v>
+        <v>1448</v>
       </c>
       <c r="I59" s="29">
-        <v>1809.7254901625181</v>
+        <v>1776.018401457392</v>
       </c>
       <c r="J59" s="29">
-        <v>1748</v>
+        <v>1699.688100018197</v>
       </c>
       <c r="K59" s="29">
-        <v>1615</v>
+        <v>1604</v>
       </c>
       <c r="L59" s="29">
-        <v>1582.3224112747721</v>
+        <v>1556.22</v>
       </c>
       <c r="M59" s="20">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -3715,34 +3718,34 @@
         <v>42</v>
       </c>
       <c r="D60" s="28">
-        <v>2008.89</v>
+        <v>2000</v>
       </c>
       <c r="E60" s="28">
-        <v>2016.822883486371</v>
+        <v>2008.218736989417</v>
       </c>
       <c r="F60" s="28">
-        <v>192.70956690366509</v>
+        <v>186.41477894071389</v>
       </c>
       <c r="G60" s="28">
         <v>2500</v>
       </c>
       <c r="H60" s="28">
-        <v>1516</v>
+        <v>1550</v>
       </c>
       <c r="I60" s="28">
-        <v>2240.4578652887872</v>
+        <v>2206.5120962899268</v>
       </c>
       <c r="J60" s="28">
-        <v>2136.0524999999998</v>
+        <v>2126.9920443450451</v>
       </c>
       <c r="K60" s="28">
-        <v>1886.2904504999999</v>
+        <v>1902.85071813486</v>
       </c>
       <c r="L60" s="28">
-        <v>1803.2289644252969</v>
+        <v>1759.9</v>
       </c>
       <c r="M60" s="5">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
@@ -3809,268 +3812,268 @@
     </row>
     <row r="65" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B65" s="7">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D65" s="28">
-        <v>8343</v>
+        <v>8937.7941348424301</v>
       </c>
       <c r="E65" s="28">
-        <v>8338.5850355264829</v>
+        <v>8980.0446052416519</v>
       </c>
       <c r="F65" s="28">
-        <v>682.58923843594448</v>
+        <v>504.59484648651897</v>
       </c>
       <c r="G65" s="28">
-        <v>10243</v>
+        <v>10125</v>
       </c>
       <c r="H65" s="28">
-        <v>6874.2</v>
+        <v>7754.8046209990562</v>
       </c>
       <c r="I65" s="28">
-        <v>9184.6777501129382</v>
+        <v>9663.0021928415426</v>
       </c>
       <c r="J65" s="28">
-        <v>8750</v>
+        <v>9317.2170455514406</v>
       </c>
       <c r="K65" s="28">
-        <v>8007.5569652688546</v>
+        <v>8691.2606223762923</v>
       </c>
       <c r="L65" s="28">
-        <v>7520</v>
+        <v>8302.0407154269997</v>
       </c>
       <c r="M65" s="8">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B66" s="17">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C66" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D66" s="29">
-        <v>8705</v>
+        <v>8730</v>
       </c>
       <c r="E66" s="29">
-        <v>8763.0558303530743</v>
+        <v>8688.791871122914</v>
       </c>
       <c r="F66" s="29">
-        <v>717.64957571261675</v>
+        <v>514.28961553111003</v>
       </c>
       <c r="G66" s="29">
-        <v>11209</v>
+        <v>9796</v>
       </c>
       <c r="H66" s="29">
         <v>7307.9</v>
       </c>
       <c r="I66" s="29">
-        <v>9467.7067489396613</v>
+        <v>9282.053626346531</v>
       </c>
       <c r="J66" s="29">
-        <v>9130.573107253329</v>
+        <v>9070.6997028747392</v>
       </c>
       <c r="K66" s="29">
-        <v>8346.6770418812448</v>
+        <v>8300</v>
       </c>
       <c r="L66" s="29">
-        <v>7886.013676859091</v>
+        <v>8091.9296361204651</v>
       </c>
       <c r="M66" s="20">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="67" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B67" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D67" s="28">
-        <v>8500</v>
+        <v>8695.9764326895511</v>
       </c>
       <c r="E67" s="28">
-        <v>8551.0219045028589</v>
+        <v>8727.2644687603315</v>
       </c>
       <c r="F67" s="28">
-        <v>634.78317758971355</v>
+        <v>498.33807920677361</v>
       </c>
       <c r="G67" s="28">
-        <v>10532</v>
+        <v>9818</v>
       </c>
       <c r="H67" s="28">
         <v>7493.3</v>
       </c>
       <c r="I67" s="28">
-        <v>9162.3272839501278</v>
+        <v>9228.9030423743261</v>
       </c>
       <c r="J67" s="28">
-        <v>8807.9238644313737</v>
+        <v>9020.4998407587809</v>
       </c>
       <c r="K67" s="28">
-        <v>8100</v>
+        <v>8500</v>
       </c>
       <c r="L67" s="28">
-        <v>7825.5881359890309</v>
+        <v>8215.7335432292093</v>
       </c>
       <c r="M67" s="5">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B68" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C68" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D68" s="29">
-        <v>8501.6007590370264</v>
+        <v>8612.5300344829539</v>
       </c>
       <c r="E68" s="29">
-        <v>8599.9308402448733</v>
+        <v>8674.3125885529844</v>
       </c>
       <c r="F68" s="29">
-        <v>588.75632908820535</v>
+        <v>476.03647873913769</v>
       </c>
       <c r="G68" s="29">
-        <v>10351</v>
+        <v>9953</v>
       </c>
       <c r="H68" s="29">
-        <v>7617.1167626854776</v>
+        <v>7560.3345619176498</v>
       </c>
       <c r="I68" s="29">
-        <v>9205.3745688902127</v>
+        <v>9173.6178549418401</v>
       </c>
       <c r="J68" s="29">
-        <v>8912.499716370834</v>
+        <v>8960</v>
       </c>
       <c r="K68" s="29">
-        <v>8203.6421176626482</v>
+        <v>8412.5</v>
       </c>
       <c r="L68" s="29">
-        <v>7930</v>
+        <v>8116.1</v>
       </c>
       <c r="M68" s="20">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B69" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D69" s="28">
-        <v>8480.8604630527734</v>
+        <v>8435.0921981260126</v>
       </c>
       <c r="E69" s="28">
-        <v>8536.4806165711288</v>
+        <v>8503.8845523759719</v>
       </c>
       <c r="F69" s="28">
-        <v>633.90942043470295</v>
+        <v>484.59694693560101</v>
       </c>
       <c r="G69" s="28">
-        <v>10266</v>
+        <v>9577</v>
       </c>
       <c r="H69" s="28">
-        <v>7500</v>
+        <v>7335.0140597579848</v>
       </c>
       <c r="I69" s="28">
-        <v>9140.0616483893264</v>
+        <v>9145.8640021927094</v>
       </c>
       <c r="J69" s="28">
-        <v>8903.3942653305494</v>
+        <v>8770.2774197305462</v>
       </c>
       <c r="K69" s="28">
-        <v>8121.76130865505</v>
+        <v>8170.75</v>
       </c>
       <c r="L69" s="28">
-        <v>7769.54</v>
+        <v>7989.8</v>
       </c>
       <c r="M69" s="5">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="70" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B70" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C70" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D70" s="29">
-        <v>8184.83</v>
+        <v>8410.3967847878102</v>
       </c>
       <c r="E70" s="29">
-        <v>8369.5679037879563</v>
+        <v>8429.5728913861531</v>
       </c>
       <c r="F70" s="29">
-        <v>701.68082239020259</v>
+        <v>412.15816018529182</v>
       </c>
       <c r="G70" s="29">
-        <v>10615.8881347724</v>
+        <v>9406</v>
       </c>
       <c r="H70" s="29">
-        <v>7200</v>
+        <v>7803</v>
       </c>
       <c r="I70" s="29">
-        <v>9238.4213306380207</v>
+        <v>8912.1330076013619</v>
       </c>
       <c r="J70" s="29">
-        <v>8645</v>
+        <v>8609.9963131288005</v>
       </c>
       <c r="K70" s="29">
-        <v>7889.4213540513992</v>
+        <v>8126.8549759256148</v>
       </c>
       <c r="L70" s="29">
-        <v>7629.2</v>
+        <v>7981.2333885341859</v>
       </c>
       <c r="M70" s="20">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="71" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B71" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D71" s="28">
-        <v>8200</v>
+        <v>8078.6481414428572</v>
       </c>
       <c r="E71" s="28">
-        <v>8312.2424006677411</v>
+        <v>8170.5157479907302</v>
       </c>
       <c r="F71" s="28">
-        <v>663.12458464705003</v>
+        <v>505.16691998431708</v>
       </c>
       <c r="G71" s="28">
-        <v>10840.359725935061</v>
+        <v>9429.3284039023511</v>
       </c>
       <c r="H71" s="28">
         <v>7200</v>
       </c>
       <c r="I71" s="28">
-        <v>8987.4655455267311</v>
+        <v>8810.7729638596084</v>
       </c>
       <c r="J71" s="28">
-        <v>8488</v>
+        <v>8580.3559235344728</v>
       </c>
       <c r="K71" s="28">
-        <v>7984</v>
+        <v>7815.0482840534069</v>
       </c>
       <c r="L71" s="28">
-        <v>7649.3756914236601</v>
+        <v>7598.74</v>
       </c>
       <c r="M71" s="5">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -4081,34 +4084,34 @@
         <v>25</v>
       </c>
       <c r="D72" s="29">
-        <v>96056</v>
+        <v>98547.427458653954</v>
       </c>
       <c r="E72" s="29">
-        <v>97413.901386463316</v>
+        <v>98985.797245783891</v>
       </c>
       <c r="F72" s="29">
-        <v>4670.3925697109789</v>
+        <v>2820.664404126976</v>
       </c>
       <c r="G72" s="29">
-        <v>112857.8562633464</v>
+        <v>106474</v>
       </c>
       <c r="H72" s="29">
-        <v>91630.2</v>
+        <v>93721.9</v>
       </c>
       <c r="I72" s="29">
-        <v>101292.7264604292</v>
+        <v>102376.2000042204</v>
       </c>
       <c r="J72" s="29">
-        <v>99808.78653023293</v>
+        <v>100172.75</v>
       </c>
       <c r="K72" s="29">
-        <v>94491.5</v>
+        <v>97330.975000000006</v>
       </c>
       <c r="L72" s="29">
-        <v>93252.499530829649</v>
+        <v>95701.245703975961</v>
       </c>
       <c r="M72" s="20">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="73" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -4119,34 +4122,34 @@
         <v>25</v>
       </c>
       <c r="D73" s="28">
-        <v>100808.64</v>
+        <v>102306.6979379249</v>
       </c>
       <c r="E73" s="28">
-        <v>101806.2762360107</v>
+        <v>102401.52622875159</v>
       </c>
       <c r="F73" s="28">
-        <v>5901.0000454287347</v>
+        <v>4905.3034555946751</v>
       </c>
       <c r="G73" s="28">
-        <v>117406.1449877891</v>
+        <v>115197</v>
       </c>
       <c r="H73" s="28">
-        <v>89510</v>
+        <v>90160</v>
       </c>
       <c r="I73" s="28">
-        <v>110314.7542154702</v>
+        <v>107249.1129853865</v>
       </c>
       <c r="J73" s="28">
-        <v>104808.764839055</v>
+        <v>105125.0046520645</v>
       </c>
       <c r="K73" s="28">
-        <v>98164.315669467993</v>
+        <v>99984.813199177443</v>
       </c>
       <c r="L73" s="28">
-        <v>95816.603995944315</v>
+        <v>96448.146298848776</v>
       </c>
       <c r="M73" s="5">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="74" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
@@ -4213,268 +4216,268 @@
     </row>
     <row r="78" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B78" s="7">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D78" s="28">
-        <v>6515.3747431719066</v>
+        <v>6787.5</v>
       </c>
       <c r="E78" s="28">
-        <v>6567.4636451322367</v>
+        <v>6801.8800917396666</v>
       </c>
       <c r="F78" s="28">
-        <v>376.06779437197292</v>
+        <v>366.80555441053048</v>
       </c>
       <c r="G78" s="28">
-        <v>8219</v>
+        <v>7899.0041821654322</v>
       </c>
       <c r="H78" s="28">
-        <v>6000</v>
+        <v>6153.5366676800004</v>
       </c>
       <c r="I78" s="28">
-        <v>6918.6957986093184</v>
+        <v>7130.4932564874161</v>
       </c>
       <c r="J78" s="28">
-        <v>6661.95</v>
+        <v>6981.7120813547408</v>
       </c>
       <c r="K78" s="28">
-        <v>6385.02</v>
+        <v>6618.0510212586551</v>
       </c>
       <c r="L78" s="28">
-        <v>6222.1376142820764</v>
+        <v>6312.6</v>
       </c>
       <c r="M78" s="8">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B79" s="17">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C79" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D79" s="29">
-        <v>6895.5233206873454</v>
+        <v>6870.2666475123697</v>
       </c>
       <c r="E79" s="29">
-        <v>6933.6505985854692</v>
+        <v>6864.1693592980864</v>
       </c>
       <c r="F79" s="29">
-        <v>482.10605929090599</v>
+        <v>323.79804022765421</v>
       </c>
       <c r="G79" s="29">
-        <v>8928</v>
+        <v>7944.160146689559</v>
       </c>
       <c r="H79" s="29">
-        <v>6234.9522612827004</v>
+        <v>6203.5366676800004</v>
       </c>
       <c r="I79" s="29">
-        <v>7353.9137682925057</v>
+        <v>7197.2</v>
       </c>
       <c r="J79" s="29">
-        <v>7080.2084767259284</v>
+        <v>7042.835764664771</v>
       </c>
       <c r="K79" s="29">
-        <v>6621</v>
+        <v>6654.0095532853957</v>
       </c>
       <c r="L79" s="29">
-        <v>6507.8254047674427</v>
+        <v>6500</v>
       </c>
       <c r="M79" s="20">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B80" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D80" s="28">
-        <v>6883.5460832410581</v>
+        <v>7287.0197159904601</v>
       </c>
       <c r="E80" s="28">
-        <v>6972.7729387405216</v>
+        <v>7196.338671122413</v>
       </c>
       <c r="F80" s="28">
-        <v>458.98571613302312</v>
+        <v>406.33462273307168</v>
       </c>
       <c r="G80" s="28">
-        <v>8844</v>
+        <v>8140.7397842558248</v>
       </c>
       <c r="H80" s="28">
-        <v>6500</v>
+        <v>6250</v>
       </c>
       <c r="I80" s="28">
-        <v>7429.5693268482764</v>
+        <v>7640.2726231107308</v>
       </c>
       <c r="J80" s="28">
-        <v>7160</v>
+        <v>7418.3850222423498</v>
       </c>
       <c r="K80" s="28">
-        <v>6701</v>
+        <v>7010.3910298164856</v>
       </c>
       <c r="L80" s="28">
-        <v>6518.66</v>
+        <v>6608.4</v>
       </c>
       <c r="M80" s="5">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B81" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C81" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D81" s="29">
-        <v>7191.4350563902026</v>
+        <v>7128.6649350210573</v>
       </c>
       <c r="E81" s="29">
-        <v>7301.9476384200707</v>
+        <v>7122.6303594794954</v>
       </c>
       <c r="F81" s="29">
-        <v>434.35135418764293</v>
+        <v>379.63120045949302</v>
       </c>
       <c r="G81" s="29">
-        <v>8917</v>
+        <v>8415.3485722202822</v>
       </c>
       <c r="H81" s="29">
-        <v>6491.1334618600004</v>
+        <v>6303.5366676800004</v>
       </c>
       <c r="I81" s="29">
-        <v>7704.2986082304196</v>
+        <v>7565.8364461501878</v>
       </c>
       <c r="J81" s="29">
-        <v>7539</v>
+        <v>7321.8453610065208</v>
       </c>
       <c r="K81" s="29">
-        <v>7000</v>
+        <v>6906.2559073758957</v>
       </c>
       <c r="L81" s="29">
-        <v>6912.6</v>
+        <v>6735.3</v>
       </c>
       <c r="M81" s="20">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B82" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D82" s="28">
-        <v>7117.6396046259979</v>
+        <v>7134.4776320438996</v>
       </c>
       <c r="E82" s="28">
-        <v>7174.8733253751698</v>
+        <v>7209.4144895657046</v>
       </c>
       <c r="F82" s="28">
-        <v>482.03768348448642</v>
+        <v>439.86879841131628</v>
       </c>
       <c r="G82" s="28">
-        <v>8770</v>
+        <v>8553.938094788864</v>
       </c>
       <c r="H82" s="28">
-        <v>6341.1334618600004</v>
+        <v>6595.5</v>
       </c>
       <c r="I82" s="28">
-        <v>7619.9537452552449</v>
+        <v>7754.0343837830824</v>
       </c>
       <c r="J82" s="28">
-        <v>7310.4659893623957</v>
+        <v>7408.5592601306744</v>
       </c>
       <c r="K82" s="28">
-        <v>7000</v>
+        <v>6898.8652200132092</v>
       </c>
       <c r="L82" s="28">
-        <v>6598.2</v>
+        <v>6736.0610003040001</v>
       </c>
       <c r="M82" s="5">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="83" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B83" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C83" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D83" s="29">
-        <v>7214.7286574187656</v>
+        <v>7149.484352991085</v>
       </c>
       <c r="E83" s="29">
-        <v>7318.05960639558</v>
+        <v>7198.5738110353059</v>
       </c>
       <c r="F83" s="29">
-        <v>498.07675865054398</v>
+        <v>477.07730727142052</v>
       </c>
       <c r="G83" s="29">
-        <v>8553.938094788864</v>
+        <v>8212.6032111168843</v>
       </c>
       <c r="H83" s="29">
-        <v>6241.1334618600004</v>
+        <v>6200</v>
       </c>
       <c r="I83" s="29">
-        <v>7921.5691091666549</v>
+        <v>7872.3629959310138</v>
       </c>
       <c r="J83" s="29">
-        <v>7571.618369917268</v>
+        <v>7435.3203080036137</v>
       </c>
       <c r="K83" s="29">
-        <v>7004.34</v>
+        <v>6906.7932051064472</v>
       </c>
       <c r="L83" s="29">
-        <v>6854.5730885437642</v>
+        <v>6701.9720195821892</v>
       </c>
       <c r="M83" s="20">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="84" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B84" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D84" s="28">
-        <v>7257</v>
+        <v>6713.8903255796376</v>
       </c>
       <c r="E84" s="28">
-        <v>7281.5785937608707</v>
+        <v>6783.9618342658487</v>
       </c>
       <c r="F84" s="28">
-        <v>497.5536553222949</v>
+        <v>518.72631758468253</v>
       </c>
       <c r="G84" s="28">
-        <v>8323</v>
+        <v>7976.571837667103</v>
       </c>
       <c r="H84" s="28">
-        <v>6141.1334618600004</v>
+        <v>5800</v>
       </c>
       <c r="I84" s="28">
-        <v>7928.0737483449448</v>
+        <v>7368.965982976224</v>
       </c>
       <c r="J84" s="28">
-        <v>7500</v>
+        <v>7196.8563179609637</v>
       </c>
       <c r="K84" s="28">
-        <v>7014.45</v>
+        <v>6384.0393330598527</v>
       </c>
       <c r="L84" s="28">
-        <v>6657.099765955646</v>
+        <v>6247.6117656413526</v>
       </c>
       <c r="M84" s="5">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="85" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -4485,34 +4488,34 @@
         <v>25</v>
       </c>
       <c r="D85" s="29">
-        <v>79550</v>
+        <v>78362.61</v>
       </c>
       <c r="E85" s="29">
-        <v>79820.874328910199</v>
+        <v>78441.592456605329</v>
       </c>
       <c r="F85" s="29">
-        <v>3479.057366162489</v>
+        <v>2437.1183279100328</v>
       </c>
       <c r="G85" s="29">
-        <v>92219.933626389844</v>
+        <v>85759.314598151715</v>
       </c>
       <c r="H85" s="29">
-        <v>74145</v>
+        <v>74367.989567624798</v>
       </c>
       <c r="I85" s="29">
-        <v>83261.928958718461</v>
+        <v>81172</v>
       </c>
       <c r="J85" s="29">
-        <v>80844.615543384891</v>
+        <v>80000</v>
       </c>
       <c r="K85" s="29">
-        <v>77789.352089120497</v>
+        <v>76751</v>
       </c>
       <c r="L85" s="29">
-        <v>76310.399999999994</v>
+        <v>75732.679573528934</v>
       </c>
       <c r="M85" s="20">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="86" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -4523,34 +4526,34 @@
         <v>25</v>
       </c>
       <c r="D86" s="28">
-        <v>84770.076799999995</v>
+        <v>84719</v>
       </c>
       <c r="E86" s="28">
-        <v>84512.735764973826</v>
+        <v>83596.923108813658</v>
       </c>
       <c r="F86" s="28">
-        <v>5165.66582474391</v>
+        <v>4235.3491657957529</v>
       </c>
       <c r="G86" s="28">
-        <v>97083.031782684106</v>
+        <v>94980.71444002421</v>
       </c>
       <c r="H86" s="28">
-        <v>72350</v>
+        <v>71250</v>
       </c>
       <c r="I86" s="28">
-        <v>90007.820606215799</v>
+        <v>87040</v>
       </c>
       <c r="J86" s="28">
-        <v>86561.261359331373</v>
+        <v>86422.738793264987</v>
       </c>
       <c r="K86" s="28">
-        <v>83021.875</v>
+        <v>80622.073250065703</v>
       </c>
       <c r="L86" s="28">
-        <v>77300</v>
+        <v>79093.100000000006</v>
       </c>
       <c r="M86" s="5">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="87" spans="2:13" ht="18" x14ac:dyDescent="0.4">
@@ -4629,34 +4632,34 @@
         <v>28</v>
       </c>
       <c r="D91" s="44">
-        <v>15900</v>
+        <v>16000</v>
       </c>
       <c r="E91" s="44">
-        <v>15646.10522455944</v>
+        <v>15524.56347684777</v>
       </c>
       <c r="F91" s="44">
-        <v>2434.530548298173</v>
+        <v>2066.9298497877039</v>
       </c>
       <c r="G91" s="44">
-        <v>21056</v>
+        <v>19000</v>
       </c>
       <c r="H91" s="44">
         <v>9000</v>
       </c>
       <c r="I91" s="44">
-        <v>18626.440425282239</v>
+        <v>17705.150000000001</v>
       </c>
       <c r="J91" s="44">
-        <v>17011.589536395019</v>
+        <v>16300</v>
       </c>
       <c r="K91" s="44">
-        <v>15000</v>
+        <v>15164</v>
       </c>
       <c r="L91" s="44">
-        <v>11953.6</v>
+        <v>12000</v>
       </c>
       <c r="M91" s="20">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="92" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -4667,34 +4670,34 @@
         <v>28</v>
       </c>
       <c r="D92" s="45">
-        <v>20000</v>
+        <v>19835.5</v>
       </c>
       <c r="E92" s="45">
-        <v>18904.805407802629</v>
+        <v>18798.664286237879</v>
       </c>
       <c r="F92" s="45">
-        <v>3648.2621509496271</v>
+        <v>3511.8851070248588</v>
       </c>
       <c r="G92" s="45">
-        <v>23700</v>
+        <v>24266</v>
       </c>
       <c r="H92" s="45">
         <v>5000</v>
       </c>
       <c r="I92" s="45">
-        <v>22307.205999999998</v>
+        <v>21855.1</v>
       </c>
       <c r="J92" s="45">
-        <v>20922.871474548101</v>
+        <v>20732.538099787249</v>
       </c>
       <c r="K92" s="45">
-        <v>17254.933406915359</v>
+        <v>17976.674170680319</v>
       </c>
       <c r="L92" s="45">
-        <v>15425</v>
+        <v>14979</v>
       </c>
       <c r="M92" s="5">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="93" spans="2:13" ht="18" x14ac:dyDescent="0.4">
@@ -4773,16 +4776,16 @@
         <v>30</v>
       </c>
       <c r="D97" s="4">
-        <v>7.65</v>
+        <v>7.7</v>
       </c>
       <c r="E97" s="4">
-        <v>7.7675812381125748</v>
+        <v>7.7783924509982398</v>
       </c>
       <c r="F97" s="4">
-        <v>0.46621523934897569</v>
+        <v>0.47919870345638288</v>
       </c>
       <c r="G97" s="4">
-        <v>8.94</v>
+        <v>8.9</v>
       </c>
       <c r="H97" s="4">
         <v>6.5</v>
@@ -4791,16 +4794,16 @@
         <v>8.4</v>
       </c>
       <c r="J97" s="4">
-        <v>7.9</v>
+        <v>8.0125000000000011</v>
       </c>
       <c r="K97" s="4">
-        <v>7.5</v>
+        <v>7.5618627395104268</v>
       </c>
       <c r="L97" s="4">
-        <v>7.4391360492824292</v>
+        <v>7.3000135547241616</v>
       </c>
       <c r="M97" s="8">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="98" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -4811,16 +4814,16 @@
         <v>30</v>
       </c>
       <c r="D98" s="19">
-        <v>7.6</v>
+        <v>7.6144157093696974</v>
       </c>
       <c r="E98" s="19">
-        <v>7.6207604357961332</v>
+        <v>7.6408730791881929</v>
       </c>
       <c r="F98" s="19">
-        <v>0.45977162928726478</v>
+        <v>0.47158800807001833</v>
       </c>
       <c r="G98" s="19">
-        <v>8.64</v>
+        <v>8.6</v>
       </c>
       <c r="H98" s="19">
         <v>6.4</v>
@@ -4829,16 +4832,16 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="J98" s="19">
-        <v>7.9361285530051564</v>
+        <v>7.95</v>
       </c>
       <c r="K98" s="19">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="L98" s="19">
-        <v>7.2</v>
+        <v>7.240860712125734</v>
       </c>
       <c r="M98" s="20">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="99" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -4849,13 +4852,13 @@
         <v>30</v>
       </c>
       <c r="D99" s="4">
-        <v>7.2826194495099692</v>
+        <v>7.3</v>
       </c>
       <c r="E99" s="4">
-        <v>7.3309184407739929</v>
+        <v>7.3444337703887896</v>
       </c>
       <c r="F99" s="4">
-        <v>0.52069167424193796</v>
+        <v>0.51182604381202779</v>
       </c>
       <c r="G99" s="4">
         <v>8.6</v>
@@ -4864,19 +4867,19 @@
         <v>6.2</v>
       </c>
       <c r="I99" s="4">
-        <v>7.8879999999999999</v>
+        <v>7.8920000000000003</v>
       </c>
       <c r="J99" s="4">
-        <v>7.6750000000000007</v>
+        <v>7.61</v>
       </c>
       <c r="K99" s="4">
-        <v>6.9927860518324536</v>
+        <v>7.1</v>
       </c>
       <c r="L99" s="4">
-        <v>6.8</v>
+        <v>6.72</v>
       </c>
       <c r="M99" s="5">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="100" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -4890,10 +4893,10 @@
         <v>7.4</v>
       </c>
       <c r="E100" s="19">
-        <v>7.4627846236821922</v>
+        <v>7.5177139255728322</v>
       </c>
       <c r="F100" s="19">
-        <v>0.58331178698971209</v>
+        <v>0.53580956182128403</v>
       </c>
       <c r="G100" s="19">
         <v>9</v>
@@ -4905,13 +4908,13 @@
         <v>7.9369790615995601</v>
       </c>
       <c r="J100" s="19">
-        <v>7.75</v>
+        <v>7.7752933646321072</v>
       </c>
       <c r="K100" s="19">
         <v>7.2</v>
       </c>
       <c r="L100" s="19">
-        <v>7</v>
+        <v>7.0647901803843141</v>
       </c>
       <c r="M100" s="20">
         <v>35</v>
@@ -4925,13 +4928,13 @@
         <v>44</v>
       </c>
       <c r="D101" s="4">
-        <v>7.35</v>
+        <v>7.45</v>
       </c>
       <c r="E101" s="4">
-        <v>7.3659148337833944</v>
+        <v>7.427346807100788</v>
       </c>
       <c r="F101" s="4">
-        <v>0.92176436158817854</v>
+        <v>0.84377627969781244</v>
       </c>
       <c r="G101" s="4">
         <v>10</v>
@@ -4943,13 +4946,13 @@
         <v>8.1665985707465083</v>
       </c>
       <c r="J101" s="4">
-        <v>7.8713480242112146</v>
+        <v>7.875</v>
       </c>
       <c r="K101" s="4">
-        <v>6.7249999999999996</v>
+        <v>6.85</v>
       </c>
       <c r="L101" s="4">
-        <v>6.5</v>
+        <v>6.53</v>
       </c>
       <c r="M101" s="5">
         <v>34</v>
@@ -5031,34 +5034,34 @@
         <v>33</v>
       </c>
       <c r="D106" s="19">
-        <v>0.26009201326585729</v>
+        <v>0.33</v>
       </c>
       <c r="E106" s="19">
-        <v>0.28569149363916541</v>
+        <v>0.35353180863862799</v>
       </c>
       <c r="F106" s="19">
-        <v>0.473322620216655</v>
+        <v>0.1568323317988054</v>
       </c>
       <c r="G106" s="19">
-        <v>1.29</v>
+        <v>0.9</v>
       </c>
       <c r="H106" s="19">
-        <v>-0.84115308514218778</v>
+        <v>3.3411904423816812E-3</v>
       </c>
       <c r="I106" s="19">
-        <v>1</v>
+        <v>0.48699179999999992</v>
       </c>
       <c r="J106" s="19">
-        <v>0.50041325000000003</v>
+        <v>0.35</v>
       </c>
       <c r="K106" s="19">
-        <v>7.4999999999999997E-3</v>
+        <v>0.3</v>
       </c>
       <c r="L106" s="19">
-        <v>-0.2</v>
+        <v>0.27811041591902869</v>
       </c>
       <c r="M106" s="20">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="107" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -5069,34 +5072,34 @@
         <v>33</v>
       </c>
       <c r="D107" s="4">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="E107" s="4">
-        <v>1.0627487319688449</v>
+        <v>1.238947685964475</v>
       </c>
       <c r="F107" s="4">
-        <v>0.6454254473601434</v>
+        <v>0.47070592611055001</v>
       </c>
       <c r="G107" s="4">
-        <v>2.792173544141519</v>
+        <v>2.56</v>
       </c>
       <c r="H107" s="4">
-        <v>-0.3</v>
+        <v>0.35</v>
       </c>
       <c r="I107" s="4">
-        <v>1.8380000000000001</v>
+        <v>1.8080000000000001</v>
       </c>
       <c r="J107" s="4">
-        <v>1.4796823835457229</v>
+        <v>1.58</v>
       </c>
       <c r="K107" s="4">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="L107" s="4">
-        <v>0.27300000000000002</v>
+        <v>0.6</v>
       </c>
       <c r="M107" s="5">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="108" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -5107,34 +5110,34 @@
         <v>33</v>
       </c>
       <c r="D108" s="19">
-        <v>0.92005568568728213</v>
+        <v>0.90300413457693463</v>
       </c>
       <c r="E108" s="19">
-        <v>0.89722495230496058</v>
+        <v>0.88938563675470617</v>
       </c>
       <c r="F108" s="19">
-        <v>0.48393406637147662</v>
+        <v>0.42473001721068793</v>
       </c>
       <c r="G108" s="19">
-        <v>1.777053734930933</v>
+        <v>1.8116320229130569</v>
       </c>
       <c r="H108" s="19">
-        <v>-0.7</v>
+        <v>0.1</v>
       </c>
       <c r="I108" s="19">
-        <v>1.406783782280008</v>
+        <v>1.5026961600044431</v>
       </c>
       <c r="J108" s="19">
-        <v>1.2778005692386349</v>
+        <v>1.0352877878927911</v>
       </c>
       <c r="K108" s="19">
-        <v>0.7</v>
+        <v>0.66148243367194492</v>
       </c>
       <c r="L108" s="19">
-        <v>0.34899999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="M108" s="20">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="109" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -5145,34 +5148,34 @@
         <v>34</v>
       </c>
       <c r="D109" s="4">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="E109" s="4">
-        <v>2.6950801638259092</v>
+        <v>2.894395202523917</v>
       </c>
       <c r="F109" s="4">
-        <v>0.80066704232326469</v>
+        <v>0.54940189466527445</v>
       </c>
       <c r="G109" s="4">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="H109" s="4">
-        <v>0.7</v>
+        <v>1.44</v>
       </c>
       <c r="I109" s="4">
-        <v>3.69</v>
+        <v>3.6</v>
       </c>
       <c r="J109" s="4">
-        <v>3.2524999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="K109" s="4">
-        <v>2.25</v>
+        <v>2.5884106835734602</v>
       </c>
       <c r="L109" s="4">
-        <v>1.477721795899285</v>
+        <v>2.16</v>
       </c>
       <c r="M109" s="5">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="110" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -5186,31 +5189,31 @@
         <v>3.1</v>
       </c>
       <c r="E110" s="19">
-        <v>3.0715906517504741</v>
+        <v>3.0804368731004872</v>
       </c>
       <c r="F110" s="19">
-        <v>0.75417788846342315</v>
+        <v>0.64702325946469508</v>
       </c>
       <c r="G110" s="19">
-        <v>4.6553778093723297</v>
+        <v>4.3</v>
       </c>
       <c r="H110" s="19">
-        <v>1.1000000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="I110" s="19">
-        <v>3.8564928332416142</v>
+        <v>4.01</v>
       </c>
       <c r="J110" s="19">
-        <v>3.5049999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="K110" s="19">
-        <v>2.65</v>
+        <v>2.6749999999999998</v>
       </c>
       <c r="L110" s="19">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="M110" s="20">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="111" spans="2:13" ht="18" x14ac:dyDescent="0.35">
@@ -5221,34 +5224,34 @@
         <v>34</v>
       </c>
       <c r="D111" s="4">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="E111" s="4">
-        <v>3.1028544945922261</v>
+        <v>3.198502000870973</v>
       </c>
       <c r="F111" s="4">
-        <v>0.66179634875555315</v>
+        <v>0.55147904528444192</v>
       </c>
       <c r="G111" s="4">
         <v>5</v>
       </c>
       <c r="H111" s="4">
-        <v>1.6</v>
+        <v>2.1675200533491261</v>
       </c>
       <c r="I111" s="4">
-        <v>3.66</v>
+        <v>3.91</v>
       </c>
       <c r="J111" s="4">
-        <v>3.4866756333824518</v>
+        <v>3.5</v>
       </c>
       <c r="K111" s="4">
-        <v>2.795293816371851</v>
+        <v>3</v>
       </c>
       <c r="L111" s="4">
-        <v>2.42</v>
+        <v>2.5739077412264368</v>
       </c>
       <c r="M111" s="5">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="112" spans="2:13" ht="18" x14ac:dyDescent="0.4">
@@ -5300,7 +5303,7 @@
   <sheetData>
     <row r="2" spans="2:13" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="11" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -5388,37 +5391,37 @@
     </row>
     <row r="7" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B7" s="2">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="4">
-        <v>2.6662500660194182</v>
+        <v>2.3166749617657398</v>
       </c>
       <c r="E7" s="4">
-        <v>2.65</v>
+        <v>2.3250000000000002</v>
       </c>
       <c r="F7" s="4">
-        <v>0.13126120168992619</v>
+        <v>0.12521983662858119</v>
       </c>
       <c r="G7" s="4">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="H7" s="4">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="I7" s="4">
-        <v>2.81</v>
+        <v>2.4550000000000001</v>
       </c>
       <c r="J7" s="4">
-        <v>2.7524999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="K7" s="4">
-        <v>2.594375495145631</v>
+        <v>2.2316874044143491</v>
       </c>
       <c r="L7" s="4">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="M7" s="5">
         <v>10</v>
@@ -5426,37 +5429,37 @@
     </row>
     <row r="8" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B8" s="31">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C8" s="32" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="33">
-        <v>2.3747200205195869</v>
+        <v>2.1639424403015881</v>
       </c>
       <c r="E8" s="33">
-        <v>2.3836001025979372</v>
+        <v>2.1850000000000001</v>
       </c>
       <c r="F8" s="33">
-        <v>0.28598466410201712</v>
+        <v>0.1566716221183185</v>
       </c>
       <c r="G8" s="33">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="H8" s="33">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="I8" s="33">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="J8" s="33">
-        <v>2.5375000000000001</v>
+        <v>2.2149999999999999</v>
       </c>
       <c r="K8" s="33">
-        <v>2.2999999999999998</v>
+        <v>2.1124999999999998</v>
       </c>
       <c r="L8" s="33">
-        <v>2.153</v>
+        <v>2.0694819627142902</v>
       </c>
       <c r="M8" s="34">
         <v>10</v>
@@ -5464,37 +5467,37 @@
     </row>
     <row r="9" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="4">
-        <v>2.2629303440086561</v>
+        <v>2.1432803027806382</v>
       </c>
       <c r="E9" s="4">
-        <v>2.249651720043282</v>
+        <v>2.151401513903191</v>
       </c>
       <c r="F9" s="4">
-        <v>0.16412816077422199</v>
+        <v>0.18612302110791801</v>
       </c>
       <c r="G9" s="4">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="H9" s="4">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="I9" s="4">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J9" s="4">
-        <v>2.3224999999999998</v>
+        <v>2.2374999999999998</v>
       </c>
       <c r="K9" s="4">
-        <v>2.2000000000000002</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="L9" s="4">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="M9" s="5">
         <v>10</v>
@@ -5502,37 +5505,37 @@
     </row>
     <row r="10" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B10" s="31">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C10" s="32" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="33">
-        <v>2.3748584452880128</v>
+        <v>1.9162296469283919</v>
       </c>
       <c r="E10" s="33">
-        <v>2.3050000000000002</v>
+        <v>1.9450000000000001</v>
       </c>
       <c r="F10" s="33">
-        <v>0.4497483632310465</v>
+        <v>0.22412211022352951</v>
       </c>
       <c r="G10" s="33">
-        <v>3.5</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H10" s="33">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="I10" s="33">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="J10" s="33">
-        <v>2.4700000000000002</v>
+        <v>2.0092223519629391</v>
       </c>
       <c r="K10" s="33">
-        <v>2.2289383396600959</v>
+        <v>1.825</v>
       </c>
       <c r="L10" s="33">
-        <v>1.98</v>
+        <v>1.6439999999999999</v>
       </c>
       <c r="M10" s="34">
         <v>10</v>
@@ -5540,37 +5543,37 @@
     </row>
     <row r="11" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="4">
-        <v>2.0918354473469321</v>
+        <v>1.9414724421693259</v>
       </c>
       <c r="E11" s="4">
-        <v>2.105</v>
+        <v>2</v>
       </c>
       <c r="F11" s="4">
-        <v>0.35028088530588791</v>
+        <v>0.28248581175826082</v>
       </c>
       <c r="G11" s="4">
-        <v>2.8</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="H11" s="4">
         <v>1.5</v>
       </c>
       <c r="I11" s="4">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="J11" s="4">
-        <v>2.1870886183673308</v>
+        <v>2.0449999999999999</v>
       </c>
       <c r="K11" s="4">
-        <v>1.925</v>
+        <v>1.7686811054233149</v>
       </c>
       <c r="L11" s="4">
-        <v>1.752</v>
+        <v>1.59</v>
       </c>
       <c r="M11" s="5">
         <v>10</v>
@@ -5578,37 +5581,37 @@
     </row>
     <row r="12" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B12" s="31">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C12" s="32" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="33">
-        <v>2.074813025139004</v>
+        <v>1.8292414000706381</v>
       </c>
       <c r="E12" s="33">
-        <v>2.0190651256950201</v>
+        <v>1.9</v>
       </c>
       <c r="F12" s="33">
-        <v>0.29914396919777148</v>
+        <v>0.2147144959400355</v>
       </c>
       <c r="G12" s="33">
-        <v>2.57</v>
+        <v>2.1</v>
       </c>
       <c r="H12" s="33">
         <v>1.5</v>
       </c>
       <c r="I12" s="33">
-        <v>2.3540000000000001</v>
+        <v>2.012172600635743</v>
       </c>
       <c r="J12" s="33">
-        <v>2.2825000000000002</v>
+        <v>1.9524999999999999</v>
       </c>
       <c r="K12" s="33">
-        <v>2</v>
+        <v>1.675</v>
       </c>
       <c r="L12" s="33">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="M12" s="34">
         <v>10</v>
@@ -5616,37 +5619,37 @@
     </row>
     <row r="13" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="4">
-        <v>1.978602809014812</v>
+        <v>1.754218848942892</v>
       </c>
       <c r="E13" s="4">
-        <v>1.978014045074064</v>
+        <v>1.8</v>
       </c>
       <c r="F13" s="4">
-        <v>0.2275119364476548</v>
+        <v>0.15171541780132899</v>
       </c>
       <c r="G13" s="4">
-        <v>2.2999999999999998</v>
+        <v>1.99</v>
       </c>
       <c r="H13" s="4">
         <v>1.5</v>
       </c>
       <c r="I13" s="4">
-        <v>2.2189999999999999</v>
+        <v>1.873</v>
       </c>
       <c r="J13" s="4">
-        <v>2.1150000000000002</v>
+        <v>1.8</v>
       </c>
       <c r="K13" s="4">
-        <v>1.9</v>
+        <v>1.7280471223572309</v>
       </c>
       <c r="L13" s="4">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="M13" s="5">
         <v>10</v>
@@ -5660,31 +5663,31 @@
         <v>47</v>
       </c>
       <c r="D14" s="33">
-        <v>26.505980245873481</v>
+        <v>23.71390436671474</v>
       </c>
       <c r="E14" s="33">
-        <v>26.934781812296091</v>
+        <v>23.71975046109894</v>
       </c>
       <c r="F14" s="33">
-        <v>2.09153173781701</v>
+        <v>1.4978791200080701</v>
       </c>
       <c r="G14" s="33">
-        <v>29.71</v>
+        <v>25.99</v>
       </c>
       <c r="H14" s="33">
-        <v>22.5</v>
+        <v>21.57</v>
       </c>
       <c r="I14" s="33">
-        <v>28.405000000000001</v>
+        <v>25.198</v>
       </c>
       <c r="J14" s="33">
-        <v>27.730059708535649</v>
+        <v>24.907385686237379</v>
       </c>
       <c r="K14" s="33">
-        <v>25.1</v>
+        <v>22.35</v>
       </c>
       <c r="L14" s="33">
-        <v>24.39</v>
+        <v>21.957000000000001</v>
       </c>
       <c r="M14" s="34">
         <v>10</v>
@@ -5698,31 +5701,31 @@
         <v>16</v>
       </c>
       <c r="D15" s="4">
-        <v>33.026887228066883</v>
+        <v>31.501639848987189</v>
       </c>
       <c r="E15" s="4">
-        <v>32.805</v>
+        <v>31.95</v>
       </c>
       <c r="F15" s="4">
-        <v>2.0528596989028278</v>
+        <v>1.2845886054396241</v>
       </c>
       <c r="G15" s="4">
-        <v>35</v>
+        <v>32.79</v>
       </c>
       <c r="H15" s="4">
-        <v>28.24</v>
+        <v>29</v>
       </c>
       <c r="I15" s="4">
-        <v>34.944985052601929</v>
+        <v>32.595281359429343</v>
       </c>
       <c r="J15" s="4">
-        <v>34.770000000000003</v>
+        <v>32.482500000000002</v>
       </c>
       <c r="K15" s="4">
-        <v>32.349999999999987</v>
+        <v>30.74068813373761</v>
       </c>
       <c r="L15" s="4">
-        <v>31.803999999999998</v>
+        <v>29.81</v>
       </c>
       <c r="M15" s="5">
         <v>10</v>
@@ -5784,37 +5787,37 @@
     </row>
     <row r="20" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B20" s="2">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="4">
-        <v>2.6705516095613651</v>
+        <v>2.2763503270134602</v>
       </c>
       <c r="E20" s="4">
-        <v>2.68</v>
+        <v>2.335</v>
       </c>
       <c r="F20" s="4">
-        <v>0.16713067498653791</v>
+        <v>0.17270671451539571</v>
       </c>
       <c r="G20" s="4">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="H20" s="4">
-        <v>2.4700000000000002</v>
+        <v>2</v>
       </c>
       <c r="I20" s="4">
-        <v>2.82</v>
+        <v>2.41</v>
       </c>
       <c r="J20" s="4">
-        <v>2.775850177749565</v>
+        <v>2.3975</v>
       </c>
       <c r="K20" s="4">
-        <v>2.5180288461538458</v>
+        <v>2.1976274526009481</v>
       </c>
       <c r="L20" s="4">
-        <v>2.4969999999999999</v>
+        <v>2</v>
       </c>
       <c r="M20" s="5">
         <v>10</v>
@@ -5822,37 +5825,37 @@
     </row>
     <row r="21" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B21" s="31">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C21" s="32" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="33">
-        <v>2.5239878922184809</v>
+        <v>2.166947777961441</v>
       </c>
       <c r="E21" s="33">
-        <v>2.5149394610924078</v>
+        <v>2.1572388898072039</v>
       </c>
       <c r="F21" s="33">
-        <v>0.16715745908815061</v>
+        <v>0.17673412434213151</v>
       </c>
       <c r="G21" s="33">
-        <v>2.9</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="H21" s="33">
-        <v>2.2999999999999998</v>
+        <v>1.9</v>
       </c>
       <c r="I21" s="33">
-        <v>2.6524999999999999</v>
+        <v>2.4089999999999998</v>
       </c>
       <c r="J21" s="33">
-        <v>2.5874999999999999</v>
+        <v>2.2037499999999999</v>
       </c>
       <c r="K21" s="33">
-        <v>2.41</v>
+        <v>2.0649999999999999</v>
       </c>
       <c r="L21" s="33">
-        <v>2.3675000000000002</v>
+        <v>1.99</v>
       </c>
       <c r="M21" s="34">
         <v>10</v>
@@ -5860,37 +5863,37 @@
     </row>
     <row r="22" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B22" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="4">
-        <v>2.287527374318215</v>
+        <v>2.1337306112672239</v>
       </c>
       <c r="E22" s="4">
-        <v>2.2227440283177118</v>
+        <v>2.0536530563361231</v>
       </c>
       <c r="F22" s="4">
-        <v>0.194613805426231</v>
+        <v>0.21671771306294679</v>
       </c>
       <c r="G22" s="4">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="H22" s="4">
-        <v>2.051035686546725</v>
+        <v>1.88</v>
       </c>
       <c r="I22" s="4">
-        <v>2.5819999999999999</v>
+        <v>2.4119999999999999</v>
       </c>
       <c r="J22" s="4">
-        <v>2.4121874999999999</v>
+        <v>2.2725</v>
       </c>
       <c r="K22" s="4">
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="L22" s="4">
-        <v>2.068103568654672</v>
+        <v>1.8979999999999999</v>
       </c>
       <c r="M22" s="5">
         <v>10</v>
@@ -5898,37 +5901,37 @@
     </row>
     <row r="23" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B23" s="31">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C23" s="32" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="33">
-        <v>2.3845295684625412</v>
+        <v>1.9795210195771411</v>
       </c>
       <c r="E23" s="33">
-        <v>2.2946779472947392</v>
+        <v>1.980105097885704</v>
       </c>
       <c r="F23" s="33">
-        <v>0.50068624893740277</v>
+        <v>0.18518067870033059</v>
       </c>
       <c r="G23" s="33">
-        <v>3.6750000000000012</v>
+        <v>2.415</v>
       </c>
       <c r="H23" s="33">
-        <v>1.8825022900359301</v>
+        <v>1.7</v>
       </c>
       <c r="I23" s="33">
-        <v>2.6175000000000002</v>
+        <v>2.0775000000000001</v>
       </c>
       <c r="J23" s="33">
-        <v>2.4674999999999998</v>
+        <v>2</v>
       </c>
       <c r="K23" s="33">
-        <v>2.196328125</v>
+        <v>1.93</v>
       </c>
       <c r="L23" s="33">
-        <v>1.898250229003593</v>
+        <v>1.79</v>
       </c>
       <c r="M23" s="34">
         <v>10</v>
@@ -5936,37 +5939,37 @@
     </row>
     <row r="24" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B24" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="4">
-        <v>2.0799401111919829</v>
+        <v>1.8761678666405699</v>
       </c>
       <c r="E24" s="4">
-        <v>2</v>
+        <v>1.9208393332028491</v>
       </c>
       <c r="F24" s="4">
-        <v>0.32876736679955021</v>
+        <v>0.13591558059191691</v>
       </c>
       <c r="G24" s="4">
-        <v>2.94</v>
+        <v>2.06</v>
       </c>
       <c r="H24" s="4">
-        <v>1.787729236919827</v>
+        <v>1.7</v>
       </c>
       <c r="I24" s="4">
-        <v>2.2829999999999999</v>
+        <v>2.0059999999999998</v>
       </c>
       <c r="J24" s="4">
-        <v>2.09125390625</v>
+        <v>1.9875</v>
       </c>
       <c r="K24" s="4">
-        <v>1.925</v>
+        <v>1.7524999999999999</v>
       </c>
       <c r="L24" s="4">
-        <v>1.7987729236919829</v>
+        <v>1.7</v>
       </c>
       <c r="M24" s="5">
         <v>10</v>
@@ -5974,37 +5977,37 @@
     </row>
     <row r="25" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B25" s="31">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C25" s="32" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="33">
-        <v>1.9091926153562271</v>
+        <v>1.8345426866444841</v>
       </c>
       <c r="E25" s="33">
-        <v>1.9</v>
+        <v>1.8525</v>
       </c>
       <c r="F25" s="33">
-        <v>0.1822770353050655</v>
+        <v>0.13815393326838971</v>
       </c>
       <c r="G25" s="33">
-        <v>2.31</v>
+        <v>2.02</v>
       </c>
       <c r="H25" s="33">
+        <v>1.66</v>
+      </c>
+      <c r="I25" s="33">
+        <v>2.0019999999999998</v>
+      </c>
+      <c r="J25" s="33">
+        <v>1.945106716611211</v>
+      </c>
+      <c r="K25" s="33">
         <v>1.7</v>
       </c>
-      <c r="I25" s="33">
-        <v>2.063778984374999</v>
-      </c>
-      <c r="J25" s="33">
-        <v>1.99</v>
-      </c>
-      <c r="K25" s="33">
-        <v>1.7625</v>
-      </c>
       <c r="L25" s="33">
-        <v>1.7319545538310399</v>
+        <v>1.696</v>
       </c>
       <c r="M25" s="34">
         <v>10</v>
@@ -6012,37 +6015,37 @@
     </row>
     <row r="26" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B26" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="4">
-        <v>1.810879099601421</v>
+        <v>1.7955362836478119</v>
       </c>
       <c r="E26" s="4">
-        <v>1.7549999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="F26" s="4">
-        <v>0.18893178307354619</v>
+        <v>0.14876269423172561</v>
       </c>
       <c r="G26" s="4">
-        <v>2.21</v>
+        <v>2.02</v>
       </c>
       <c r="H26" s="4">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="I26" s="4">
-        <v>2.003862136718749</v>
+        <v>2.0019999999999998</v>
       </c>
       <c r="J26" s="4">
-        <v>1.9</v>
+        <v>1.8640221273585871</v>
       </c>
       <c r="K26" s="4">
-        <v>1.6644582665816781</v>
+        <v>1.7024999999999999</v>
       </c>
       <c r="L26" s="4">
-        <v>1.645</v>
+        <v>1.64</v>
       </c>
       <c r="M26" s="5">
         <v>10</v>
@@ -6056,31 +6059,31 @@
         <v>47</v>
       </c>
       <c r="D27" s="33">
-        <v>25.927535651284941</v>
+        <v>24.27345326223276</v>
       </c>
       <c r="E27" s="33">
-        <v>25.57</v>
+        <v>24.51</v>
       </c>
       <c r="F27" s="33">
-        <v>1.810396164820846</v>
+        <v>1.0675748050244691</v>
       </c>
       <c r="G27" s="33">
-        <v>29.21</v>
+        <v>25.8</v>
       </c>
       <c r="H27" s="33">
-        <v>23.201531525933159</v>
+        <v>22.42</v>
       </c>
       <c r="I27" s="33">
-        <v>27.91905255188172</v>
+        <v>25.62</v>
       </c>
       <c r="J27" s="33">
-        <v>27.086158280285741</v>
+        <v>24.827606857227181</v>
       </c>
       <c r="K27" s="33">
-        <v>24.675000000000001</v>
+        <v>23.443505714028479</v>
       </c>
       <c r="L27" s="33">
-        <v>24.280153152593311</v>
+        <v>23.302</v>
       </c>
       <c r="M27" s="34">
         <v>10</v>
@@ -6094,31 +6097,31 @@
         <v>16</v>
       </c>
       <c r="D28" s="4">
-        <v>32.091426852630221</v>
+        <v>30.783551490047369</v>
       </c>
       <c r="E28" s="4">
-        <v>31.71</v>
+        <v>30.789621447073351</v>
       </c>
       <c r="F28" s="4">
-        <v>1.391162297170363</v>
+        <v>0.94062909037821307</v>
       </c>
       <c r="G28" s="4">
-        <v>34.624660950027923</v>
+        <v>32.4</v>
       </c>
       <c r="H28" s="4">
-        <v>30.16960757627438</v>
+        <v>28.9</v>
       </c>
       <c r="I28" s="4">
-        <v>34.332466095002793</v>
+        <v>31.6136448056943</v>
       </c>
       <c r="J28" s="4">
-        <v>32.325000000000003</v>
+        <v>31.31</v>
       </c>
       <c r="K28" s="4">
-        <v>31.425000000000001</v>
+        <v>30.4925</v>
       </c>
       <c r="L28" s="4">
-        <v>30.916960757627439</v>
+        <v>29.89</v>
       </c>
       <c r="M28" s="5">
         <v>10</v>
@@ -6184,37 +6187,37 @@
     </row>
     <row r="33" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B33" s="31">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C33" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="33">
-        <v>23.175000000000001</v>
-      </c>
-      <c r="E33" s="33">
-        <v>23</v>
-      </c>
-      <c r="F33" s="33">
-        <v>0.74879532880784194</v>
+      <c r="D33" s="46">
+        <v>22.24277272727273</v>
+      </c>
+      <c r="E33" s="46">
+        <v>22.40886363636363</v>
+      </c>
+      <c r="F33" s="46">
+        <v>0.90656589868036486</v>
       </c>
       <c r="G33" s="33">
-        <v>24.3</v>
+        <v>23.2</v>
       </c>
       <c r="H33" s="33">
-        <v>22.1</v>
+        <v>20.41</v>
       </c>
       <c r="I33" s="33">
-        <v>24.03</v>
+        <v>23.11</v>
       </c>
       <c r="J33" s="33">
-        <v>23.875</v>
+        <v>22.95</v>
       </c>
       <c r="K33" s="33">
-        <v>22.737500000000001</v>
+        <v>22</v>
       </c>
       <c r="L33" s="33">
-        <v>22.28</v>
+        <v>21.030999999999999</v>
       </c>
       <c r="M33" s="34">
         <v>10</v>
@@ -6222,37 +6225,37 @@
     </row>
     <row r="34" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D34" s="4">
-        <v>23.146000000000001</v>
-      </c>
-      <c r="E34" s="4">
-        <v>23</v>
-      </c>
-      <c r="F34" s="4">
-        <v>1.0378631894426169</v>
+      <c r="D34" s="26">
+        <v>22.402999999999999</v>
+      </c>
+      <c r="E34" s="26">
+        <v>22.19</v>
+      </c>
+      <c r="F34" s="26">
+        <v>1.17900193195582</v>
       </c>
       <c r="G34" s="4">
-        <v>25.26</v>
+        <v>24.2</v>
       </c>
       <c r="H34" s="4">
-        <v>21.9</v>
+        <v>20.5</v>
       </c>
       <c r="I34" s="4">
-        <v>24.126000000000001</v>
+        <v>23.795000000000002</v>
       </c>
       <c r="J34" s="4">
-        <v>23.824999999999999</v>
+        <v>23.324999999999999</v>
       </c>
       <c r="K34" s="4">
-        <v>22.5</v>
+        <v>21.925000000000001</v>
       </c>
       <c r="L34" s="4">
-        <v>21.99</v>
+        <v>20.95</v>
       </c>
       <c r="M34" s="5">
         <v>10</v>
@@ -6260,37 +6263,37 @@
     </row>
     <row r="35" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B35" s="31">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C35" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="D35" s="33">
-        <v>23.291</v>
-      </c>
-      <c r="E35" s="33">
-        <v>23.05</v>
-      </c>
-      <c r="F35" s="33">
-        <v>1.609944443485896</v>
+      <c r="D35" s="46">
+        <v>22.582000000000001</v>
+      </c>
+      <c r="E35" s="46">
+        <v>22.53</v>
+      </c>
+      <c r="F35" s="46">
+        <v>1.8731423390181059</v>
       </c>
       <c r="G35" s="33">
-        <v>26.21</v>
+        <v>25.26</v>
       </c>
       <c r="H35" s="33">
-        <v>21.1</v>
+        <v>19.8</v>
       </c>
       <c r="I35" s="33">
-        <v>25.120999999999999</v>
+        <v>24.756</v>
       </c>
       <c r="J35" s="33">
-        <v>24.375</v>
+        <v>24</v>
       </c>
       <c r="K35" s="33">
-        <v>22</v>
+        <v>21.125</v>
       </c>
       <c r="L35" s="33">
-        <v>21.91</v>
+        <v>20.43</v>
       </c>
       <c r="M35" s="34">
         <v>10</v>
@@ -6298,37 +6301,37 @@
     </row>
     <row r="36" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B36" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D36" s="4">
-        <v>23.58410962262845</v>
-      </c>
-      <c r="E36" s="4">
-        <v>23.8</v>
-      </c>
-      <c r="F36" s="4">
-        <v>2.4145076230559321</v>
+      <c r="D36" s="26">
+        <v>22.491</v>
+      </c>
+      <c r="E36" s="26">
+        <v>22.53</v>
+      </c>
+      <c r="F36" s="26">
+        <v>2.438106961467351</v>
       </c>
       <c r="G36" s="4">
-        <v>27.18</v>
+        <v>27.25</v>
       </c>
       <c r="H36" s="4">
-        <v>20.5</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="I36" s="4">
-        <v>26.892986603656041</v>
+        <v>24.684999999999999</v>
       </c>
       <c r="J36" s="4">
-        <v>24.925000000000001</v>
+        <v>24.05</v>
       </c>
       <c r="K36" s="4">
-        <v>21.25</v>
+        <v>20.350000000000001</v>
       </c>
       <c r="L36" s="4">
-        <v>20.95</v>
+        <v>19.940000000000001</v>
       </c>
       <c r="M36" s="5">
         <v>10</v>
@@ -6336,37 +6339,37 @@
     </row>
     <row r="37" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B37" s="31">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C37" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="D37" s="33">
-        <v>23.591107238600891</v>
-      </c>
-      <c r="E37" s="33">
-        <v>24.05</v>
-      </c>
-      <c r="F37" s="33">
-        <v>2.7459206863688861</v>
+      <c r="D37" s="46">
+        <v>22.477</v>
+      </c>
+      <c r="E37" s="46">
+        <v>22.38</v>
+      </c>
+      <c r="F37" s="46">
+        <v>2.9432108317278258</v>
       </c>
       <c r="G37" s="33">
-        <v>28.14</v>
+        <v>29.01</v>
       </c>
       <c r="H37" s="33">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="I37" s="33">
-        <v>26.997965147408038</v>
+        <v>24.951000000000001</v>
       </c>
       <c r="J37" s="33">
-        <v>24.875</v>
+        <v>23.7</v>
       </c>
       <c r="K37" s="33">
-        <v>21.25</v>
+        <v>20.3</v>
       </c>
       <c r="L37" s="33">
-        <v>20.43</v>
+        <v>19.45</v>
       </c>
       <c r="M37" s="34">
         <v>10</v>
@@ -6374,37 +6377,37 @@
     </row>
     <row r="38" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D38" s="4">
-        <v>23.56323599753253</v>
-      </c>
-      <c r="E38" s="4">
-        <v>24</v>
-      </c>
-      <c r="F38" s="4">
-        <v>3.0284061943568008</v>
+      <c r="D38" s="26">
+        <v>21.890999999999998</v>
+      </c>
+      <c r="E38" s="26">
+        <v>22.28</v>
+      </c>
+      <c r="F38" s="26">
+        <v>2.5506271559929901</v>
       </c>
       <c r="G38" s="4">
-        <v>29.12</v>
+        <v>27.25</v>
       </c>
       <c r="H38" s="4">
-        <v>19.399999999999999</v>
+        <v>19</v>
       </c>
       <c r="I38" s="4">
-        <v>26.863123977792799</v>
+        <v>23.695</v>
       </c>
       <c r="J38" s="4">
-        <v>24.875</v>
+        <v>22.875</v>
       </c>
       <c r="K38" s="4">
-        <v>21.25</v>
+        <v>19.524999999999999</v>
       </c>
       <c r="L38" s="4">
-        <v>19.940000000000001</v>
+        <v>19</v>
       </c>
       <c r="M38" s="5">
         <v>10</v>
@@ -6417,32 +6420,32 @@
       <c r="C39" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="D39" s="33">
-        <v>22.05899999999999</v>
-      </c>
-      <c r="E39" s="33">
-        <v>21.92</v>
-      </c>
-      <c r="F39" s="33">
-        <v>3.1369356951578609</v>
+      <c r="D39" s="46">
+        <v>20.39494623093325</v>
+      </c>
+      <c r="E39" s="46">
+        <v>20.05</v>
+      </c>
+      <c r="F39" s="46">
+        <v>2.1114523531940632</v>
       </c>
       <c r="G39" s="33">
-        <v>27.85</v>
+        <v>23</v>
       </c>
       <c r="H39" s="33">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="I39" s="33">
-        <v>25.285</v>
+        <v>22.999999999999659</v>
       </c>
       <c r="J39" s="33">
-        <v>23.749999999999972</v>
+        <v>22.285</v>
       </c>
       <c r="K39" s="33">
-        <v>20.399999999999999</v>
+        <v>19.857096731999619</v>
       </c>
       <c r="L39" s="33">
-        <v>17.95</v>
+        <v>17.45</v>
       </c>
       <c r="M39" s="34">
         <v>10</v>
@@ -6455,32 +6458,32 @@
       <c r="C40" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D40" s="4">
-        <v>23.52171579808002</v>
-      </c>
-      <c r="E40" s="4">
-        <v>23.25</v>
-      </c>
-      <c r="F40" s="4">
-        <v>3.5688856224943168</v>
+      <c r="D40" s="26">
+        <v>21.687000000000001</v>
+      </c>
+      <c r="E40" s="26">
+        <v>21.88</v>
+      </c>
+      <c r="F40" s="26">
+        <v>2.188099378202208</v>
       </c>
       <c r="G40" s="4">
-        <v>31.09</v>
+        <v>25.11</v>
       </c>
       <c r="H40" s="4">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="I40" s="4">
-        <v>27.073442182720171</v>
+        <v>24.561</v>
       </c>
       <c r="J40" s="4">
-        <v>24.875</v>
+        <v>22.725000000000001</v>
       </c>
       <c r="K40" s="4">
-        <v>20.5</v>
+        <v>20.175000000000001</v>
       </c>
       <c r="L40" s="4">
-        <v>19.95</v>
+        <v>18.95</v>
       </c>
       <c r="M40" s="5">
         <v>10</v>
@@ -6546,37 +6549,37 @@
     </row>
     <row r="45" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B45" s="31">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C45" s="32" t="s">
         <v>22</v>
       </c>
       <c r="D45" s="42">
-        <v>1402.6729497585691</v>
+        <v>1416.7800310405521</v>
       </c>
       <c r="E45" s="42">
-        <v>1403.2466880876159</v>
+        <v>1418.5</v>
       </c>
       <c r="F45" s="42">
-        <v>16.747296227263089</v>
+        <v>8.0887789624817881</v>
       </c>
       <c r="G45" s="42">
-        <v>1424.136121410455</v>
+        <v>1429.8</v>
       </c>
       <c r="H45" s="42">
-        <v>1373</v>
+        <v>1406</v>
       </c>
       <c r="I45" s="42">
-        <v>1420.413612141045</v>
+        <v>1423.923</v>
       </c>
       <c r="J45" s="42">
-        <v>1416.825</v>
+        <v>1422.021863417702</v>
       </c>
       <c r="K45" s="42">
-        <v>1390.75</v>
+        <v>1408.928369386439</v>
       </c>
       <c r="L45" s="42">
-        <v>1383.8</v>
+        <v>1406.837</v>
       </c>
       <c r="M45" s="34">
         <v>10</v>
@@ -6584,37 +6587,37 @@
     </row>
     <row r="46" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D46" s="36">
-        <v>1423.21720466733</v>
+        <v>1436.6614761926639</v>
       </c>
       <c r="E46" s="36">
-        <v>1426.75</v>
+        <v>1439.2177623419609</v>
       </c>
       <c r="F46" s="36">
-        <v>23.221571472249419</v>
+        <v>11.574763535155141</v>
       </c>
       <c r="G46" s="36">
-        <v>1455</v>
+        <v>1449</v>
       </c>
       <c r="H46" s="36">
-        <v>1380</v>
+        <v>1415</v>
       </c>
       <c r="I46" s="36">
-        <v>1446.448346908451</v>
+        <v>1448.82</v>
       </c>
       <c r="J46" s="36">
-        <v>1440.23</v>
+        <v>1445.534952932044</v>
       </c>
       <c r="K46" s="36">
-        <v>1407.1334708604211</v>
+        <v>1431.4</v>
       </c>
       <c r="L46" s="36">
-        <v>1398</v>
+        <v>1420.3993700000001</v>
       </c>
       <c r="M46" s="5">
         <v>10</v>
@@ -6622,37 +6625,37 @@
     </row>
     <row r="47" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B47" s="31">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C47" s="32" t="s">
         <v>22</v>
       </c>
       <c r="D47" s="42">
-        <v>1444.3850264557491</v>
+        <v>1463.431566178082</v>
       </c>
       <c r="E47" s="42">
-        <v>1451.314814438701</v>
+        <v>1466.8146395000001</v>
       </c>
       <c r="F47" s="42">
-        <v>28.047702660297389</v>
+        <v>18.496630948139341</v>
       </c>
       <c r="G47" s="42">
-        <v>1475</v>
+        <v>1492.85</v>
       </c>
       <c r="H47" s="42">
-        <v>1386</v>
+        <v>1423</v>
       </c>
       <c r="I47" s="42">
-        <v>1470.086</v>
+        <v>1476.7850000000001</v>
       </c>
       <c r="J47" s="42">
-        <v>1465.385476760064</v>
+        <v>1471.7117339721281</v>
       </c>
       <c r="K47" s="42">
-        <v>1430.875</v>
+        <v>1460.0250000000001</v>
       </c>
       <c r="L47" s="42">
-        <v>1411.2</v>
+        <v>1444.96</v>
       </c>
       <c r="M47" s="34">
         <v>10</v>
@@ -6660,37 +6663,37 @@
     </row>
     <row r="48" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D48" s="36">
-        <v>1476.8222225927991</v>
+        <v>1498.7363050315871</v>
       </c>
       <c r="E48" s="36">
-        <v>1481.4069403563531</v>
+        <v>1502.976404728867</v>
       </c>
       <c r="F48" s="36">
-        <v>34.504834772728607</v>
+        <v>33.052420507503122</v>
       </c>
       <c r="G48" s="36">
-        <v>1514.22</v>
+        <v>1544.63</v>
       </c>
       <c r="H48" s="36">
-        <v>1392</v>
+        <v>1428</v>
       </c>
       <c r="I48" s="36">
-        <v>1510.422</v>
+        <v>1540.230875139318</v>
       </c>
       <c r="J48" s="36">
-        <v>1494.297086303822</v>
+        <v>1509.3845393424999</v>
       </c>
       <c r="K48" s="36">
-        <v>1472.75</v>
+        <v>1482.7249999999999</v>
       </c>
       <c r="L48" s="36">
-        <v>1450.5</v>
+        <v>1474.08</v>
       </c>
       <c r="M48" s="5">
         <v>10</v>
@@ -6698,37 +6701,37 @@
     </row>
     <row r="49" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B49" s="31">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C49" s="32" t="s">
         <v>22</v>
       </c>
       <c r="D49" s="42">
-        <v>1512.4282142601189</v>
+        <v>1535.567485002593</v>
       </c>
       <c r="E49" s="42">
-        <v>1520.5079861038359</v>
+        <v>1535.236409228173</v>
       </c>
       <c r="F49" s="42">
-        <v>45.620436961664012</v>
+        <v>49.424699458996621</v>
       </c>
       <c r="G49" s="42">
-        <v>1566.74</v>
+        <v>1609.572347904784</v>
       </c>
       <c r="H49" s="42">
-        <v>1397</v>
+        <v>1435</v>
       </c>
       <c r="I49" s="42">
-        <v>1551.674</v>
+        <v>1591.858234790478</v>
       </c>
       <c r="J49" s="42">
-        <v>1531</v>
+        <v>1563.3797627485999</v>
       </c>
       <c r="K49" s="42">
-        <v>1502.8815425983789</v>
+        <v>1514.85</v>
       </c>
       <c r="L49" s="42">
-        <v>1489.7</v>
+        <v>1490.89</v>
       </c>
       <c r="M49" s="34">
         <v>10</v>
@@ -6736,37 +6739,37 @@
     </row>
     <row r="50" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B50" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D50" s="36">
-        <v>1546.1912280203319</v>
+        <v>1566.2809892825619</v>
       </c>
       <c r="E50" s="36">
-        <v>1554.7766086269489</v>
+        <v>1567.327373821965</v>
       </c>
       <c r="F50" s="36">
-        <v>55.907881527522861</v>
+        <v>60.832058840782032</v>
       </c>
       <c r="G50" s="36">
-        <v>1612.66</v>
+        <v>1648.960271006946</v>
       </c>
       <c r="H50" s="36">
-        <v>1404</v>
+        <v>1441</v>
       </c>
       <c r="I50" s="36">
-        <v>1583.2660000000001</v>
+        <v>1631.1040271006941</v>
       </c>
       <c r="J50" s="36">
-        <v>1575</v>
+        <v>1609.281155631058</v>
       </c>
       <c r="K50" s="36">
-        <v>1536.3992972120641</v>
+        <v>1543.5</v>
       </c>
       <c r="L50" s="36">
-        <v>1516.05</v>
+        <v>1506.43</v>
       </c>
       <c r="M50" s="5">
         <v>10</v>
@@ -6780,31 +6783,31 @@
         <v>50</v>
       </c>
       <c r="D51" s="42">
-        <v>1696.5515593412181</v>
+        <v>1712.7887282533079</v>
       </c>
       <c r="E51" s="42">
-        <v>1704</v>
+        <v>1718.5</v>
       </c>
       <c r="F51" s="42">
-        <v>109.3470888745458</v>
+        <v>117.49225919136271</v>
       </c>
       <c r="G51" s="42">
-        <v>1810.1491352191269</v>
+        <v>1850</v>
       </c>
       <c r="H51" s="42">
-        <v>1436</v>
+        <v>1473</v>
       </c>
       <c r="I51" s="42">
-        <v>1791.114913521913</v>
+        <v>1840.0586915089821</v>
       </c>
       <c r="J51" s="42">
-        <v>1779.14</v>
+        <v>1811.0150000000001</v>
       </c>
       <c r="K51" s="42">
-        <v>1670.350364219229</v>
+        <v>1660.0432952141091</v>
       </c>
       <c r="L51" s="42">
-        <v>1607</v>
+        <v>1592.34</v>
       </c>
       <c r="M51" s="34">
         <v>10</v>
@@ -6818,31 +6821,31 @@
         <v>23</v>
       </c>
       <c r="D52" s="36">
-        <v>1610.780576930583</v>
+        <v>1596.369874026793</v>
       </c>
       <c r="E52" s="36">
-        <v>1632.6590828750079</v>
+        <v>1599.5793701339639</v>
       </c>
       <c r="F52" s="36">
-        <v>79.803434769060772</v>
+        <v>71.130380483837826</v>
       </c>
       <c r="G52" s="36">
-        <v>1681.88</v>
+        <v>1688</v>
       </c>
       <c r="H52" s="36">
-        <v>1416</v>
+        <v>1448</v>
       </c>
       <c r="I52" s="36">
-        <v>1675.6880000000001</v>
+        <v>1665.5</v>
       </c>
       <c r="J52" s="36">
-        <v>1666.5093434821861</v>
+        <v>1651.73</v>
       </c>
       <c r="K52" s="36">
-        <v>1582.177672220299</v>
+        <v>1567.75</v>
       </c>
       <c r="L52" s="36">
-        <v>1560</v>
+        <v>1523.51</v>
       </c>
       <c r="M52" s="5">
         <v>10</v>
@@ -6912,37 +6915,37 @@
     </row>
     <row r="57" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B57" s="38">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C57" s="32" t="s">
         <v>25</v>
       </c>
       <c r="D57" s="39">
-        <v>8694.5469412993007</v>
+        <v>9313.67998747602</v>
       </c>
       <c r="E57" s="39">
-        <v>8791</v>
+        <v>9435.0720042625471</v>
       </c>
       <c r="F57" s="39">
-        <v>505.08547458655522</v>
+        <v>557.00096940449623</v>
       </c>
       <c r="G57" s="39">
-        <v>9400.9726398926268</v>
+        <v>10125</v>
       </c>
       <c r="H57" s="39">
-        <v>7600</v>
+        <v>8302.9649802476069</v>
       </c>
       <c r="I57" s="39">
-        <v>9323.6120186438693</v>
+        <v>9860.1407507374206</v>
       </c>
       <c r="J57" s="39">
-        <v>8833.3195302690292</v>
+        <v>9668.5985672622355</v>
       </c>
       <c r="K57" s="39">
-        <v>8483.5969180035845</v>
+        <v>8886.75</v>
       </c>
       <c r="L57" s="39">
-        <v>8339.7999999999993</v>
+        <v>8750.2964980247616</v>
       </c>
       <c r="M57" s="40">
         <v>10</v>
@@ -6950,37 +6953,37 @@
     </row>
     <row r="58" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B58" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D58" s="36">
-        <v>9056.3634044145092</v>
+        <v>8963.9288219552436</v>
       </c>
       <c r="E58" s="36">
-        <v>9117.6233056483215</v>
+        <v>9015.6397392870986</v>
       </c>
       <c r="F58" s="36">
-        <v>616.81790186096282</v>
+        <v>426.27473091349231</v>
       </c>
       <c r="G58" s="36">
-        <v>9900</v>
+        <v>9796</v>
       </c>
       <c r="H58" s="36">
-        <v>7900</v>
+        <v>8327</v>
       </c>
       <c r="I58" s="36">
-        <v>9805.0060245631175</v>
+        <v>9331.2943959798431</v>
       </c>
       <c r="J58" s="36">
-        <v>9396.2022208337312</v>
+        <v>9175.850844796345</v>
       </c>
       <c r="K58" s="36">
-        <v>8627.25</v>
+        <v>8683.8880205276728</v>
       </c>
       <c r="L58" s="36">
-        <v>8440</v>
+        <v>8495.026832511754</v>
       </c>
       <c r="M58" s="5">
         <v>10</v>
@@ -6988,37 +6991,37 @@
     </row>
     <row r="59" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B59" s="31">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C59" s="32" t="s">
         <v>25</v>
       </c>
       <c r="D59" s="39">
-        <v>8887.6053839424894</v>
+        <v>8971.7385727158417</v>
       </c>
       <c r="E59" s="39">
-        <v>8800.5</v>
+        <v>8891.4137740971164</v>
       </c>
       <c r="F59" s="39">
-        <v>612.843384972129</v>
+        <v>537.67280898675642</v>
       </c>
       <c r="G59" s="39">
-        <v>9871.4532105056478</v>
+        <v>9818</v>
       </c>
       <c r="H59" s="39">
-        <v>8100</v>
+        <v>8158</v>
       </c>
       <c r="I59" s="39">
-        <v>9762.1453210505642</v>
+        <v>9733.0510773177793</v>
       </c>
       <c r="J59" s="39">
-        <v>9208.239533139058</v>
+        <v>9282.7364677083297</v>
       </c>
       <c r="K59" s="39">
-        <v>8405.2369795167961</v>
+        <v>8566</v>
       </c>
       <c r="L59" s="39">
-        <v>8185.5</v>
+        <v>8465.7999999999993</v>
       </c>
       <c r="M59" s="34">
         <v>10</v>
@@ -7026,37 +7029,37 @@
     </row>
     <row r="60" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B60" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D60" s="36">
-        <v>8819.15008505271</v>
+        <v>8887.3997398595529</v>
       </c>
       <c r="E60" s="36">
-        <v>9135.3040980029418</v>
+        <v>8899.0788750790634</v>
       </c>
       <c r="F60" s="36">
-        <v>684.15297963735873</v>
+        <v>535.67711851431341</v>
       </c>
       <c r="G60" s="36">
-        <v>9684.456232295679</v>
+        <v>9953</v>
       </c>
       <c r="H60" s="36">
-        <v>7826</v>
+        <v>8123</v>
       </c>
       <c r="I60" s="36">
-        <v>9563.445623229567</v>
+        <v>9459.8720849905549</v>
       </c>
       <c r="J60" s="36">
-        <v>9210.0773166691488</v>
+        <v>9088.0127075152996</v>
       </c>
       <c r="K60" s="36">
-        <v>8260.25</v>
+        <v>8509.25</v>
       </c>
       <c r="L60" s="36">
-        <v>7892.6</v>
+        <v>8372.2999999999993</v>
       </c>
       <c r="M60" s="5">
         <v>10</v>
@@ -7064,37 +7067,37 @@
     </row>
     <row r="61" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B61" s="31">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C61" s="32" t="s">
         <v>25</v>
       </c>
       <c r="D61" s="39">
-        <v>8690.5669700840008</v>
+        <v>8668.3020786640936</v>
       </c>
       <c r="E61" s="39">
-        <v>8881.6971326652747</v>
+        <v>8628.2811940924967</v>
       </c>
       <c r="F61" s="39">
-        <v>821.72176839900078</v>
+        <v>553.19052674271882</v>
       </c>
       <c r="G61" s="39">
-        <v>10165.564280137931</v>
+        <v>9577</v>
       </c>
       <c r="H61" s="39">
-        <v>7600</v>
+        <v>7958</v>
       </c>
       <c r="I61" s="39">
-        <v>9566.5564280137933</v>
+        <v>9344.5892533875121</v>
       </c>
       <c r="J61" s="39">
-        <v>9034.0333665286526</v>
+        <v>9038.822411853791</v>
       </c>
       <c r="K61" s="39">
-        <v>8089.75</v>
+        <v>8240.2323363884134</v>
       </c>
       <c r="L61" s="39">
-        <v>7622.5</v>
+        <v>7995.8</v>
       </c>
       <c r="M61" s="34">
         <v>10</v>
@@ -7102,37 +7105,37 @@
     </row>
     <row r="62" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B62" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D62" s="36">
-        <v>8610.3860180559514</v>
+        <v>8495.4374586647318</v>
       </c>
       <c r="E62" s="36">
-        <v>8603.0568597276178</v>
+        <v>8450.4772068666007</v>
       </c>
       <c r="F62" s="36">
-        <v>898.13982063678134</v>
+        <v>480.25894925396472</v>
       </c>
       <c r="G62" s="36">
-        <v>10615.8881347724</v>
+        <v>9406</v>
       </c>
       <c r="H62" s="36">
-        <v>7500</v>
+        <v>7867</v>
       </c>
       <c r="I62" s="36">
-        <v>9327.9613071759304</v>
+        <v>9030.2801999185376</v>
       </c>
       <c r="J62" s="36">
-        <v>8912.5</v>
+        <v>8790.9682815702217</v>
       </c>
       <c r="K62" s="36">
-        <v>8107.25</v>
+        <v>8157.6488938388593</v>
       </c>
       <c r="L62" s="36">
-        <v>7588.2</v>
+        <v>7986.7</v>
       </c>
       <c r="M62" s="5">
         <v>10</v>
@@ -7140,37 +7143,37 @@
     </row>
     <row r="63" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B63" s="31">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C63" s="32" t="s">
         <v>25</v>
       </c>
       <c r="D63" s="39">
-        <v>8520.1081527498227</v>
+        <v>8219.6177675813233</v>
       </c>
       <c r="E63" s="39">
-        <v>8387.4841313309844</v>
+        <v>8091.4506308811378</v>
       </c>
       <c r="F63" s="39">
-        <v>934.18541665838211</v>
+        <v>615.07485534293187</v>
       </c>
       <c r="G63" s="39">
-        <v>10840.359725935061</v>
+        <v>9180.5453686464207</v>
       </c>
       <c r="H63" s="39">
-        <v>7500</v>
+        <v>7200</v>
       </c>
       <c r="I63" s="39">
-        <v>9172.1141576045775</v>
+        <v>8928.0545368646417</v>
       </c>
       <c r="J63" s="39">
-        <v>8692</v>
+        <v>8696.5</v>
       </c>
       <c r="K63" s="39">
-        <v>8038</v>
+        <v>7815.0482840534069</v>
       </c>
       <c r="L63" s="39">
-        <v>7650.3</v>
+        <v>7713</v>
       </c>
       <c r="M63" s="34">
         <v>10</v>
@@ -7184,31 +7187,31 @@
         <v>25</v>
       </c>
       <c r="D64" s="36">
-        <v>99944.071568107436</v>
+        <v>100578.39202648601</v>
       </c>
       <c r="E64" s="36">
-        <v>99505</v>
+        <v>100625</v>
       </c>
       <c r="F64" s="36">
-        <v>6098.2658573839817</v>
+        <v>3001.0435156550052</v>
       </c>
       <c r="G64" s="36">
-        <v>112857.8562633464</v>
+        <v>106474</v>
       </c>
       <c r="H64" s="36">
-        <v>93266</v>
+        <v>95836</v>
       </c>
       <c r="I64" s="36">
-        <v>106937.7856263346</v>
+        <v>103617.4</v>
       </c>
       <c r="J64" s="36">
-        <v>101733.46485443199</v>
+        <v>101463.4420967887</v>
       </c>
       <c r="K64" s="36">
-        <v>95242</v>
+        <v>99227.5</v>
       </c>
       <c r="L64" s="36">
-        <v>93614.3</v>
+        <v>97025.561472761183</v>
       </c>
       <c r="M64" s="37">
         <v>10</v>
@@ -7278,37 +7281,37 @@
     </row>
     <row r="69" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B69" s="38">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="C69" s="32" t="s">
         <v>25</v>
       </c>
       <c r="D69" s="39">
-        <v>6635.1488537975938</v>
+        <v>6738.9078334678252</v>
       </c>
       <c r="E69" s="39">
-        <v>6464.4704671466279</v>
+        <v>6699.9330532061067</v>
       </c>
       <c r="F69" s="39">
-        <v>623.34209655294876</v>
+        <v>243.90718792723271</v>
       </c>
       <c r="G69" s="39">
-        <v>8219</v>
+        <v>7058.76</v>
       </c>
       <c r="H69" s="39">
-        <v>6000</v>
+        <v>6234.9522612827004</v>
       </c>
       <c r="I69" s="39">
-        <v>7137.8542649853061</v>
+        <v>7050.5432716364094</v>
       </c>
       <c r="J69" s="39">
-        <v>6662.2818304198236</v>
+        <v>6909.3562704549022</v>
       </c>
       <c r="K69" s="39">
-        <v>6325.8682937731273</v>
+        <v>6657.8187750126544</v>
       </c>
       <c r="L69" s="39">
-        <v>6170.0090561575716</v>
+        <v>6579.8789026594304</v>
       </c>
       <c r="M69" s="40">
         <v>10</v>
@@ -7316,37 +7319,37 @@
     </row>
     <row r="70" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B70" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D70" s="36">
-        <v>7032.0290728838318</v>
+        <v>6805.9866167100527</v>
       </c>
       <c r="E70" s="36">
-        <v>6902.3662906552854</v>
+        <v>6811.7996573570472</v>
       </c>
       <c r="F70" s="36">
-        <v>748.8075933247344</v>
+        <v>203.17292409257661</v>
       </c>
       <c r="G70" s="36">
-        <v>8928</v>
+        <v>7172.46</v>
       </c>
       <c r="H70" s="36">
-        <v>6234.9522612827004</v>
+        <v>6521</v>
       </c>
       <c r="I70" s="36">
-        <v>7557.2808066364778</v>
+        <v>7036.1145696502044</v>
       </c>
       <c r="J70" s="36">
-        <v>7072.1954324551371</v>
+        <v>6912.6165653047428</v>
       </c>
       <c r="K70" s="36">
-        <v>6700.2356089589539</v>
+        <v>6654.4567105612141</v>
       </c>
       <c r="L70" s="36">
-        <v>6383.4952261282697</v>
+        <v>6593.7579111668883</v>
       </c>
       <c r="M70" s="5">
         <v>10</v>
@@ -7354,37 +7357,37 @@
     </row>
     <row r="71" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B71" s="31">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C71" s="32" t="s">
         <v>25</v>
       </c>
       <c r="D71" s="39">
-        <v>7022.4132019378712</v>
+        <v>7132.0362927405613</v>
       </c>
       <c r="E71" s="39">
-        <v>6860.15489217719</v>
+        <v>7186.7192195329062</v>
       </c>
       <c r="F71" s="39">
-        <v>677.74366885151051</v>
+        <v>343.58268113280451</v>
       </c>
       <c r="G71" s="39">
-        <v>8844</v>
+        <v>7483.1734120149376</v>
       </c>
       <c r="H71" s="39">
-        <v>6500</v>
+        <v>6250</v>
       </c>
       <c r="I71" s="39">
-        <v>7454.3163491573023</v>
+        <v>7427.6043412014942</v>
       </c>
       <c r="J71" s="39">
-        <v>6937.1005050368194</v>
+        <v>7315.7639721479954</v>
       </c>
       <c r="K71" s="39">
-        <v>6669.8487542302228</v>
+        <v>7104.9059759530273</v>
       </c>
       <c r="L71" s="39">
-        <v>6586.3099999999986</v>
+        <v>6933.9327145554689</v>
       </c>
       <c r="M71" s="34">
         <v>10</v>
@@ -7392,37 +7395,37 @@
     </row>
     <row r="72" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B72" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D72" s="36">
-        <v>7586.9773944270901</v>
+        <v>7004.5356657613547</v>
       </c>
       <c r="E72" s="36">
-        <v>7473.0526735253943</v>
+        <v>7070.7133299023872</v>
       </c>
       <c r="F72" s="36">
-        <v>594.40075500832017</v>
+        <v>242.6875177351111</v>
       </c>
       <c r="G72" s="36">
-        <v>8917</v>
+        <v>7305.77</v>
       </c>
       <c r="H72" s="36">
-        <v>6979.8712142692511</v>
+        <v>6440.9771371761644</v>
       </c>
       <c r="I72" s="36">
-        <v>8218.3658058302426</v>
+        <v>7197.4403148387273</v>
       </c>
       <c r="J72" s="36">
-        <v>7784.4538959487954</v>
+        <v>7142.9380994460898</v>
       </c>
       <c r="K72" s="36">
-        <v>7124.0167748773792</v>
+        <v>6907.3537880883941</v>
       </c>
       <c r="L72" s="36">
-        <v>7087.9871214269251</v>
+        <v>6815.9890908523084</v>
       </c>
       <c r="M72" s="5">
         <v>10</v>
@@ -7430,37 +7433,37 @@
     </row>
     <row r="73" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B73" s="31">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C73" s="32" t="s">
         <v>25</v>
       </c>
       <c r="D73" s="39">
-        <v>7354.1447641444593</v>
+        <v>7131.5168688648582</v>
       </c>
       <c r="E73" s="39">
-        <v>7199.7369078985303</v>
+        <v>7022.3049149278904</v>
       </c>
       <c r="F73" s="39">
-        <v>710.54268110869646</v>
+        <v>421.64242798958639</v>
       </c>
       <c r="G73" s="39">
-        <v>8770</v>
+        <v>7881.3360000000002</v>
       </c>
       <c r="H73" s="39">
-        <v>6440.9771371761644</v>
+        <v>6636.5156895783521</v>
       </c>
       <c r="I73" s="39">
-        <v>8450.813714998254</v>
+        <v>7727.5197080131302</v>
       </c>
       <c r="J73" s="39">
-        <v>7359.7369724296896</v>
+        <v>7363.1630841698116</v>
       </c>
       <c r="K73" s="39">
-        <v>7000.1914011332838</v>
+        <v>6851.3777479264954</v>
       </c>
       <c r="L73" s="39">
-        <v>6789.5280137307154</v>
+        <v>6693.6515689578346</v>
       </c>
       <c r="M73" s="34">
         <v>10</v>
@@ -7468,37 +7471,37 @@
     </row>
     <row r="74" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B74" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D74" s="36">
-        <v>7681.3766070123747</v>
+        <v>7032.0777241648539</v>
       </c>
       <c r="E74" s="36">
-        <v>7616.6575650945642</v>
+        <v>7041.2692366742267</v>
       </c>
       <c r="F74" s="36">
-        <v>615.24745609521904</v>
+        <v>538.42312896514591</v>
       </c>
       <c r="G74" s="36">
-        <v>8553.938094788864</v>
+        <v>7922.2000000000007</v>
       </c>
       <c r="H74" s="36">
-        <v>6933.3516594765897</v>
+        <v>6200</v>
       </c>
       <c r="I74" s="36">
-        <v>8497.293809478886</v>
+        <v>7706.2158316677278</v>
       </c>
       <c r="J74" s="36">
-        <v>8167.7453544839236</v>
+        <v>7334.560702229187</v>
       </c>
       <c r="K74" s="36">
-        <v>7195.8413336667336</v>
+        <v>6621.3201730064493</v>
       </c>
       <c r="L74" s="36">
-        <v>6941.0990128178628</v>
+        <v>6476.5668007772683</v>
       </c>
       <c r="M74" s="5">
         <v>10</v>
@@ -7506,37 +7509,37 @@
     </row>
     <row r="75" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B75" s="31">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C75" s="32" t="s">
         <v>25</v>
       </c>
       <c r="D75" s="39">
-        <v>7576.350872673167</v>
+        <v>6566.0959047611614</v>
       </c>
       <c r="E75" s="39">
-        <v>7565.9354433239732</v>
+        <v>6521.1550000000007</v>
       </c>
       <c r="F75" s="39">
-        <v>573.03347441808228</v>
+        <v>457.2432578383947</v>
       </c>
       <c r="G75" s="39">
-        <v>8323</v>
+        <v>7483</v>
       </c>
       <c r="H75" s="39">
-        <v>6507.2964453080758</v>
+        <v>5839.0150632505774</v>
       </c>
       <c r="I75" s="39">
-        <v>8258.4821130357541</v>
+        <v>6942.1683700058566</v>
       </c>
       <c r="J75" s="39">
-        <v>8041.6402508570254</v>
+        <v>6819.7059201871107</v>
       </c>
       <c r="K75" s="39">
-        <v>7272.730368740331</v>
+        <v>6366.7794315195733</v>
       </c>
       <c r="L75" s="39">
-        <v>7000.7036428932142</v>
+        <v>6100.6351194570652</v>
       </c>
       <c r="M75" s="34">
         <v>10</v>
@@ -7550,31 +7553,31 @@
         <v>25</v>
       </c>
       <c r="D76" s="36">
-        <v>80430.743916619744</v>
+        <v>77392.352659705095</v>
       </c>
       <c r="E76" s="36">
-        <v>78400</v>
+        <v>77815.920062022313</v>
       </c>
       <c r="F76" s="36">
-        <v>5272.1534900626048</v>
+        <v>1537.519693663995</v>
       </c>
       <c r="G76" s="36">
-        <v>92219.933626389844</v>
+        <v>79500</v>
       </c>
       <c r="H76" s="36">
-        <v>74359.316105230988</v>
+        <v>74367.989567624798</v>
       </c>
       <c r="I76" s="36">
-        <v>87245.795513930119</v>
+        <v>78576.455100000006</v>
       </c>
       <c r="J76" s="36">
-        <v>81237.380459129345</v>
+        <v>78364.782703096134</v>
       </c>
       <c r="K76" s="36">
-        <v>77735.980673742219</v>
+        <v>76496.765348597779</v>
       </c>
       <c r="L76" s="36">
-        <v>76824.780494757506</v>
+        <v>75596.210572938522</v>
       </c>
       <c r="M76" s="37">
         <v>10</v>
@@ -7656,31 +7659,31 @@
         <v>28</v>
       </c>
       <c r="D81" s="43">
-        <v>16531.849035752912</v>
+        <v>15722.40612366544</v>
       </c>
       <c r="E81" s="43">
-        <v>15990.5</v>
+        <v>15788.05</v>
       </c>
       <c r="F81" s="43">
-        <v>2332.9252711705049</v>
+        <v>1032.556231234094</v>
       </c>
       <c r="G81" s="43">
-        <v>21056</v>
+        <v>17705.150000000001</v>
       </c>
       <c r="H81" s="43">
-        <v>12607.167581384199</v>
+        <v>13663.936308724091</v>
       </c>
       <c r="I81" s="43">
-        <v>18935.599999999999</v>
+        <v>16440.514999999999</v>
       </c>
       <c r="J81" s="43">
-        <v>17700.26409062641</v>
+        <v>16098.62602800831</v>
       </c>
       <c r="K81" s="43">
-        <v>15363.25</v>
+        <v>15293.75</v>
       </c>
       <c r="L81" s="43">
-        <v>14555.702530413761</v>
+        <v>14866.7298323997</v>
       </c>
       <c r="M81" s="5">
         <v>10</v>
@@ -7762,31 +7765,31 @@
         <v>30</v>
       </c>
       <c r="D86" s="33">
-        <v>7.7713257807101099</v>
+        <v>7.7553257807101108</v>
       </c>
       <c r="E86" s="33">
-        <v>7.6999999999999993</v>
+        <v>7.7</v>
       </c>
       <c r="F86" s="33">
-        <v>0.3768920397311985</v>
+        <v>0.43882326692365248</v>
       </c>
       <c r="G86" s="33">
         <v>8.6460955860665845</v>
       </c>
       <c r="H86" s="33">
-        <v>7.257162221034517</v>
+        <v>7.1</v>
       </c>
       <c r="I86" s="33">
-        <v>8.1096095586066586</v>
+        <v>8.1546095586066585</v>
       </c>
       <c r="J86" s="33">
-        <v>7.8450000000000006</v>
+        <v>7.9875000000000007</v>
       </c>
       <c r="K86" s="33">
         <v>7.6</v>
       </c>
       <c r="L86" s="33">
-        <v>7.4757162221034514</v>
+        <v>7.2414459989310664</v>
       </c>
       <c r="M86" s="40">
         <v>10</v>
@@ -7800,31 +7803,31 @@
         <v>30</v>
       </c>
       <c r="D87" s="4">
-        <v>7.527059010217779</v>
+        <v>7.5300590102177791</v>
       </c>
       <c r="E87" s="4">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="F87" s="4">
-        <v>0.32704977213802089</v>
+        <v>0.42661984645280282</v>
       </c>
       <c r="G87" s="4">
         <v>8.08</v>
       </c>
       <c r="H87" s="4">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="I87" s="4">
-        <v>7.9130627908185609</v>
+        <v>7.9180000000000001</v>
       </c>
       <c r="J87" s="4">
-        <v>7.7525000000000004</v>
+        <v>7.8458856590154671</v>
       </c>
       <c r="K87" s="4">
-        <v>7.2445569176178752</v>
+        <v>7.3250000000000002</v>
       </c>
       <c r="L87" s="4">
-        <v>7.19</v>
+        <v>7.1634683011414504</v>
       </c>
       <c r="M87" s="5">
         <v>10</v>
@@ -7838,31 +7841,31 @@
         <v>30</v>
       </c>
       <c r="D88" s="33">
-        <v>7.1234364721603809</v>
+        <v>7.1184241513166073</v>
       </c>
       <c r="E88" s="33">
-        <v>7.15</v>
+        <v>7.25</v>
       </c>
       <c r="F88" s="33">
-        <v>0.31294416868902902</v>
+        <v>0.35122091812309442</v>
       </c>
       <c r="G88" s="33">
-        <v>7.51</v>
+        <v>7.61</v>
       </c>
       <c r="H88" s="33">
-        <v>6.6209479589730114</v>
+        <v>6.6</v>
       </c>
       <c r="I88" s="33">
-        <v>7.5010000000000003</v>
+        <v>7.4390000000000001</v>
       </c>
       <c r="J88" s="33">
-        <v>7.39</v>
+        <v>7.375</v>
       </c>
       <c r="K88" s="33">
-        <v>6.8875625719730946</v>
+        <v>6.8208541906576983</v>
       </c>
       <c r="L88" s="33">
-        <v>6.7820947958973008</v>
+        <v>6.6637422754817468</v>
       </c>
       <c r="M88" s="34">
         <v>10</v>
@@ -7876,31 +7879,31 @@
         <v>31</v>
       </c>
       <c r="D89" s="4">
-        <v>7.3229546767466021</v>
+        <v>7.373708572599047</v>
       </c>
       <c r="E89" s="4">
-        <v>7.2668890043913654</v>
+        <v>7.3</v>
       </c>
       <c r="F89" s="4">
-        <v>0.3356857563350964</v>
+        <v>0.27113660711044629</v>
       </c>
       <c r="G89" s="4">
         <v>7.8357687586832787</v>
       </c>
       <c r="H89" s="4">
-        <v>6.7</v>
+        <v>7.04131696730719</v>
       </c>
       <c r="I89" s="4">
-        <v>7.6595768758683276</v>
+        <v>7.7315768758683276</v>
       </c>
       <c r="J89" s="4">
-        <v>7.59</v>
+        <v>7.58</v>
       </c>
       <c r="K89" s="4">
         <v>7.2</v>
       </c>
       <c r="L89" s="4">
-        <v>6.97</v>
+        <v>7.0941316967307184</v>
       </c>
       <c r="M89" s="5">
         <v>10</v>
@@ -7982,31 +7985,31 @@
         <v>33</v>
       </c>
       <c r="D94" s="33">
-        <v>0.32481239870461082</v>
+        <v>0.38653772524100077</v>
       </c>
       <c r="E94" s="33">
-        <v>0.30406199352305419</v>
+        <v>0.33</v>
       </c>
       <c r="F94" s="33">
-        <v>0.35836772021939428</v>
+        <v>0.18718357643150851</v>
       </c>
       <c r="G94" s="33">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H94" s="33">
-        <v>-0.13</v>
+        <v>0.23</v>
       </c>
       <c r="I94" s="33">
-        <v>0.82</v>
+        <v>0.48183952716900658</v>
       </c>
       <c r="J94" s="33">
-        <v>0.4</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="K94" s="33">
-        <v>0.11749999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="L94" s="33">
-        <v>-8.5000000000000006E-2</v>
+        <v>0.29299999999999998</v>
       </c>
       <c r="M94" s="40">
         <v>10</v>
@@ -8020,31 +8023,31 @@
         <v>33</v>
       </c>
       <c r="D95" s="4">
-        <v>0.95774554315840454</v>
+        <v>1.2433156069617191</v>
       </c>
       <c r="E95" s="4">
-        <v>0.95</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F95" s="4">
-        <v>0.47123553269767421</v>
+        <v>0.59966368485053956</v>
       </c>
       <c r="G95" s="4">
-        <v>1.8</v>
+        <v>2.56</v>
       </c>
       <c r="H95" s="4">
-        <v>0.15</v>
+        <v>0.41</v>
       </c>
       <c r="I95" s="4">
-        <v>1.4850000000000001</v>
+        <v>1.8759999999999999</v>
       </c>
       <c r="J95" s="4">
-        <v>1.1225000000000001</v>
+        <v>1.4707890174042979</v>
       </c>
       <c r="K95" s="4">
-        <v>0.80936385789601117</v>
+        <v>0.9325</v>
       </c>
       <c r="L95" s="4">
-        <v>0.38400000000000001</v>
+        <v>0.80600000000000005</v>
       </c>
       <c r="M95" s="5">
         <v>10</v>
@@ -8058,31 +8061,31 @@
         <v>33</v>
       </c>
       <c r="D96" s="33">
-        <v>0.89730041345769129</v>
+        <v>0.73530041345769348</v>
       </c>
       <c r="E96" s="33">
-        <v>0.90650206728845628</v>
+        <v>0.86</v>
       </c>
       <c r="F96" s="33">
-        <v>0.27170984261188169</v>
+        <v>0.2357610576533625</v>
       </c>
       <c r="G96" s="33">
-        <v>1.41</v>
+        <v>0.94</v>
       </c>
       <c r="H96" s="33">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="I96" s="33">
-        <v>1.131</v>
+        <v>0.93100000000000005</v>
       </c>
       <c r="J96" s="33">
-        <v>0.98250000000000004</v>
+        <v>0.90825103364423365</v>
       </c>
       <c r="K96" s="33">
-        <v>0.82499999999999996</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L96" s="33">
-        <v>0.622</v>
+        <v>0.435</v>
       </c>
       <c r="M96" s="34">
         <v>10</v>
@@ -8096,31 +8099,31 @@
         <v>34</v>
       </c>
       <c r="D97" s="4">
-        <v>2.5309488077860349</v>
+        <v>2.7805859612668979</v>
       </c>
       <c r="E97" s="4">
-        <v>2.513304840281942</v>
+        <v>2.5934106835734601</v>
       </c>
       <c r="F97" s="4">
-        <v>0.61059626900516895</v>
+        <v>0.52536049175797173</v>
       </c>
       <c r="G97" s="4">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="H97" s="4">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="I97" s="4">
-        <v>3.07</v>
+        <v>3.4449999999999998</v>
       </c>
       <c r="J97" s="4">
-        <v>2.855</v>
+        <v>2.9442786841415458</v>
       </c>
       <c r="K97" s="4">
-        <v>2.2107195993241162</v>
+        <v>2.5024999999999999</v>
       </c>
       <c r="L97" s="4">
-        <v>1.946</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="M97" s="5">
         <v>10</v>
@@ -8174,6 +8177,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b80df5a0-8011-40eb-be96-4c6a59f56b6e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6b042263-e944-4dfe-97a8-6e4c84e0ae4b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -8182,7 +8196,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004E1357DA6D65CA49A875959554824B49" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="e8f8602aebf7bbdcbcb5348c529dc11a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b80df5a0-8011-40eb-be96-4c6a59f56b6e" xmlns:ns3="6b042263-e944-4dfe-97a8-6e4c84e0ae4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a39dbf9ae3c20398b89cd584be7bda98" ns2:_="" ns3:_="">
     <xsd:import namespace="b80df5a0-8011-40eb-be96-4c6a59f56b6e"/>
@@ -8431,18 +8445,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b80df5a0-8011-40eb-be96-4c6a59f56b6e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6b042263-e944-4dfe-97a8-6e4c84e0ae4b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB7C2FA5-1A6F-45A0-B729-06C123F95F83}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="6b042263-e944-4dfe-97a8-6e4c84e0ae4b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="b80df5a0-8011-40eb-be96-4c6a59f56b6e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E4A204-179E-478B-A62E-54900BF00ECD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -8450,7 +8470,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89E97169-F966-43F7-97A7-EB3192694F7A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8467,21 +8487,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB7C2FA5-1A6F-45A0-B729-06C123F95F83}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="6b042263-e944-4dfe-97a8-6e4c84e0ae4b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="b80df5a0-8011-40eb-be96-4c6a59f56b6e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/public/REM/raw/REM.xlsx
+++ b/public/REM/raw/REM.xlsx
@@ -1,25 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcranet.sharepoint.com/sites/REM/Documentos compartidos/REM/Publicación/Pagina WEB/2026/26 05 May/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcranet.sharepoint.com/sites/REM/Documentos compartidos/REM/Publicación/Pagina WEB/2026/26 06 Jun/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="121" documentId="8_{563D5886-1088-4C76-92B3-92AAC244057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{553B8805-31A3-4A37-AAB6-8D2F95CFAB19}"/>
+  <xr:revisionPtr revIDLastSave="170" documentId="8_{563D5886-1088-4C76-92B3-92AAC244057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3626628D-8F7A-4AAC-8648-63E73DAAB3D0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8A5F0209-F8EA-4E2B-A469-F799AD0A214D}"/>
+    <workbookView xWindow="60" yWindow="390" windowWidth="24165" windowHeight="14865" xr2:uid="{8A5F0209-F8EA-4E2B-A469-F799AD0A214D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Cuadros de resultados" sheetId="18" r:id="rId1"/>
-    <sheet name="Resultados TOP 10" sheetId="17" r:id="rId2"/>
+    <sheet name="Cuadros de resultados" sheetId="19" r:id="rId1"/>
+    <sheet name="Resultados TOP 10" sheetId="20" r:id="rId2"/>
     <sheet name="Notas Metodólogicas" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Cuadros de resultados'!$B$2:$M$112</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Resultados TOP 10'!$B$2:$M$98</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Cuadros de resultados'!$2:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Resultados TOP 10'!$2:$4</definedName>
   </definedNames>
@@ -160,9 +159,6 @@
     <t>2027</t>
   </si>
   <si>
-    <t>Trim. I-26</t>
-  </si>
-  <si>
     <t>2028</t>
   </si>
   <si>
@@ -184,36 +180,38 @@
     <t>Trim. III-26</t>
   </si>
   <si>
-    <t>Relevamiento de Expectativas de Mercado (REM)  - BCRA - Mayo 2026</t>
+    <t>Relevamiento de Expectativas de Mercado (REM)  - BCRA - Junio 2026</t>
   </si>
   <si>
-    <t>var. % i.a.; may-27</t>
+    <t>var. % i.a.; jun-27</t>
   </si>
   <si>
-    <t>var. % i.a.; may-28</t>
+    <t>var. % i.a.; jun-28</t>
   </si>
   <si>
-    <t>TNA; %; may-27</t>
+    <t>TNA; %; jun-27</t>
   </si>
   <si>
-    <t>$/USD; may-27</t>
+    <t>$/USD; jun-27</t>
   </si>
   <si>
-    <t>Fuente: REM - BCRA (may-26)</t>
+    <t>Trim. IV-26</t>
   </si>
   <si>
-    <t>Relevamiento de Expectativas de Mercado (REM)  Top 10 - BCRA - Mayo 2026</t>
+    <t>Fuente: REM - BCRA (jun-26)</t>
+  </si>
+  <si>
+    <t>Relevamiento de Expectativas de Mercado (REM)  Top 10 - BCRA - Junio 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -400,7 +398,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -479,61 +477,28 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="2" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1876,27 +1841,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{355761B5-36B1-4B45-8098-A926C2568F38}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED56CF66-85D7-47A2-A74A-AD3F0E36496C}">
+  <sheetPr codeName="Hoja1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:M112"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.54296875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.81640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.453125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.453125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.453125" style="1" customWidth="1"/>
-    <col min="9" max="12" width="14.453125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="18.453125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="14.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="18.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="20.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:13" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B2" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -1910,7 +1875,7 @@
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
     </row>
-    <row r="3" spans="2:13" ht="20.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
@@ -1924,11 +1889,11 @@
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="L4" s="12"/>
       <c r="M4" s="13"/>
     </row>
-    <row r="5" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
         <v>0</v>
       </c>
@@ -1944,7 +1909,7 @@
       <c r="L5" s="14"/>
       <c r="M5" s="15"/>
     </row>
-    <row r="6" spans="2:13" ht="36" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B6" s="16" t="s">
         <v>1</v>
       </c>
@@ -1982,123 +1947,123 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B7" s="17">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="19">
-        <v>2.2999999999999998</v>
+        <v>1.9550000000000001</v>
       </c>
       <c r="E7" s="19">
-        <v>2.285781786422957</v>
+        <v>1.9664205285178511</v>
       </c>
       <c r="F7" s="19">
-        <v>0.17964644624761211</v>
+        <v>0.1161089710294419</v>
       </c>
       <c r="G7" s="19">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="H7" s="19">
+        <v>1.8</v>
+      </c>
+      <c r="I7" s="19">
+        <v>2.1</v>
+      </c>
+      <c r="J7" s="19">
+        <v>2</v>
+      </c>
+      <c r="K7" s="19">
         <v>1.9</v>
       </c>
-      <c r="I7" s="19">
-        <v>2.494525082167991</v>
-      </c>
-      <c r="J7" s="19">
-        <v>2.34</v>
-      </c>
-      <c r="K7" s="19">
-        <v>2.2000000000000002</v>
-      </c>
       <c r="L7" s="19">
-        <v>2.1</v>
+        <v>1.840837887420995</v>
       </c>
       <c r="M7" s="20">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="4">
-        <v>2.1</v>
+        <v>1.9516446347829639</v>
       </c>
       <c r="E8" s="4">
-        <v>2.0450934680914599</v>
+        <v>1.936558955401265</v>
       </c>
       <c r="F8" s="4">
-        <v>0.22524794909787851</v>
+        <v>0.18928608530078569</v>
       </c>
       <c r="G8" s="4">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="H8" s="4">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="I8" s="4">
-        <v>2.2599999999999998</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J8" s="4">
-        <v>2.1924999999999999</v>
+        <v>2.0201713687336871</v>
       </c>
       <c r="K8" s="4">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="L8" s="4">
-        <v>1.79</v>
+        <v>1.786</v>
       </c>
       <c r="M8" s="5">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B9" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="19">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="E9" s="19">
-        <v>1.985883049281437</v>
+        <v>1.802340140820764</v>
       </c>
       <c r="F9" s="19">
-        <v>0.24108280020744849</v>
+        <v>0.2696071807402371</v>
       </c>
       <c r="G9" s="19">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H9" s="19">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I9" s="19">
-        <v>2.2768713395139319</v>
+        <v>2.161110515359042</v>
       </c>
       <c r="J9" s="19">
-        <v>2.1425000000000001</v>
+        <v>1.945857933540875</v>
       </c>
       <c r="K9" s="19">
-        <v>1.8425</v>
+        <v>1.6400050752592601</v>
       </c>
       <c r="L9" s="19">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="M9" s="20">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>13</v>
@@ -2107,224 +2072,224 @@
         <v>1.8</v>
       </c>
       <c r="E10" s="4">
-        <v>1.8573360693508489</v>
+        <v>1.7878046021872069</v>
       </c>
       <c r="F10" s="4">
-        <v>0.26213937241547541</v>
+        <v>0.30804572741485581</v>
       </c>
       <c r="G10" s="4">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="H10" s="4">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I10" s="4">
-        <v>2.15</v>
+        <v>2.1139999999999999</v>
       </c>
       <c r="J10" s="4">
-        <v>2</v>
+        <v>1.9755489354367599</v>
       </c>
       <c r="K10" s="4">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="L10" s="4">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="M10" s="5">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B11" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="19">
-        <v>1.8854172985115869</v>
+        <v>1.7450000000000001</v>
       </c>
       <c r="E11" s="19">
-        <v>1.8336228542689259</v>
+        <v>1.697490920347835</v>
       </c>
       <c r="F11" s="19">
-        <v>0.32522298830110818</v>
+        <v>0.30338151539088509</v>
       </c>
       <c r="G11" s="19">
-        <v>2.52</v>
+        <v>2.23</v>
       </c>
       <c r="H11" s="19">
         <v>0.6</v>
       </c>
       <c r="I11" s="19">
-        <v>2.15</v>
+        <v>1.9951902648797131</v>
       </c>
       <c r="J11" s="19">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K11" s="19">
-        <v>1.665461555695821</v>
+        <v>1.5475000000000001</v>
       </c>
       <c r="L11" s="19">
-        <v>1.55</v>
+        <v>1.390157133155534</v>
       </c>
       <c r="M11" s="20">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B12" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="4">
-        <v>1.7749999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="E12" s="4">
-        <v>1.7326545942473111</v>
+        <v>1.634948641804935</v>
       </c>
       <c r="F12" s="4">
-        <v>0.29675539962959019</v>
+        <v>0.27481747911105769</v>
       </c>
       <c r="G12" s="4">
-        <v>2.23</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H12" s="4">
         <v>0.6</v>
       </c>
       <c r="I12" s="4">
-        <v>2.0012070003531912</v>
+        <v>1.896626177363119</v>
       </c>
       <c r="J12" s="4">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="K12" s="4">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="L12" s="4">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="M12" s="5">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B13" s="17">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="19">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="E13" s="19">
-        <v>1.6760885061332751</v>
+        <v>1.720052678027685</v>
       </c>
       <c r="F13" s="19">
-        <v>0.26707572545525898</v>
+        <v>0.31479137221634268</v>
       </c>
       <c r="G13" s="19">
-        <v>2.2000000000000002</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="H13" s="19">
         <v>0.6</v>
       </c>
       <c r="I13" s="19">
-        <v>1.9359999999999999</v>
+        <v>2.076000000000001</v>
       </c>
       <c r="J13" s="19">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="K13" s="19">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="L13" s="19">
-        <v>1.34</v>
+        <v>1.421</v>
       </c>
       <c r="M13" s="20">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" s="4">
-        <v>23.31743678321612</v>
+        <v>22.3</v>
       </c>
       <c r="E14" s="4">
-        <v>22.796142688134761</v>
+        <v>22.039889923634519</v>
       </c>
       <c r="F14" s="4">
-        <v>3.3387418960753048</v>
+        <v>3.662659117303086</v>
       </c>
       <c r="G14" s="4">
-        <v>28.8</v>
+        <v>28.5</v>
       </c>
       <c r="H14" s="4">
-        <v>9.4</v>
+        <v>9.15</v>
       </c>
       <c r="I14" s="4">
-        <v>25.731000000000002</v>
+        <v>25.8</v>
       </c>
       <c r="J14" s="4">
-        <v>24.682385686237382</v>
+        <v>24</v>
       </c>
       <c r="K14" s="4">
-        <v>21.517499999999998</v>
+        <v>20.98</v>
       </c>
       <c r="L14" s="4">
-        <v>20.648</v>
+        <v>18</v>
       </c>
       <c r="M14" s="5">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B15" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D15" s="19">
-        <v>17.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E15" s="19">
-        <v>17.210252407648429</v>
+        <v>16.942094962712801</v>
       </c>
       <c r="F15" s="19">
-        <v>4.0811034895200704</v>
+        <v>4.0563315999929266</v>
       </c>
       <c r="G15" s="19">
-        <v>24.16299069908365</v>
+        <v>24.34</v>
       </c>
       <c r="H15" s="19">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="I15" s="19">
-        <v>22.3489756849123</v>
+        <v>21.9</v>
       </c>
       <c r="J15" s="19">
-        <v>19.5</v>
+        <v>19.51083680194472</v>
       </c>
       <c r="K15" s="19">
-        <v>15</v>
+        <v>15.226294058910479</v>
       </c>
       <c r="L15" s="19">
-        <v>12.512582564000001</v>
+        <v>13.008992230500001</v>
       </c>
       <c r="M15" s="20">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>36</v>
       </c>
@@ -2332,37 +2297,37 @@
         <v>16</v>
       </c>
       <c r="D16" s="4">
-        <v>30.5</v>
+        <v>30.02</v>
       </c>
       <c r="E16" s="4">
-        <v>30.462958270773701</v>
+        <v>29.897118023566641</v>
       </c>
       <c r="F16" s="4">
-        <v>2.1817720385053709</v>
+        <v>1.9252913817741519</v>
       </c>
       <c r="G16" s="4">
-        <v>35.4</v>
+        <v>33.9</v>
       </c>
       <c r="H16" s="4">
-        <v>21.4</v>
+        <v>22.9</v>
       </c>
       <c r="I16" s="4">
-        <v>32.55746476588584</v>
+        <v>31.889125483192679</v>
       </c>
       <c r="J16" s="4">
-        <v>31.9</v>
+        <v>30.90710907173888</v>
       </c>
       <c r="K16" s="4">
-        <v>29.25</v>
+        <v>29</v>
       </c>
       <c r="L16" s="4">
-        <v>28.705206782484421</v>
+        <v>28.074038221730721</v>
       </c>
       <c r="M16" s="5">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B17" s="21" t="s">
         <v>37</v>
       </c>
@@ -2370,75 +2335,75 @@
         <v>17</v>
       </c>
       <c r="D17" s="19">
-        <v>19.920000000000002</v>
+        <v>20</v>
       </c>
       <c r="E17" s="19">
-        <v>19.802549403597862</v>
+        <v>20.184284829234219</v>
       </c>
       <c r="F17" s="19">
-        <v>4.1579769494315082</v>
+        <v>4.0963186740403508</v>
       </c>
       <c r="G17" s="19">
-        <v>28</v>
+        <v>26.7</v>
       </c>
       <c r="H17" s="19">
         <v>8.4</v>
       </c>
       <c r="I17" s="19">
-        <v>24.85</v>
+        <v>25.72</v>
       </c>
       <c r="J17" s="19">
-        <v>22.2</v>
+        <v>22.7</v>
       </c>
       <c r="K17" s="19">
-        <v>17.945904117817729</v>
+        <v>18.572500000000002</v>
       </c>
       <c r="L17" s="19">
-        <v>15.78</v>
+        <v>16.402000000000001</v>
       </c>
       <c r="M17" s="20">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="D18" s="4">
-        <v>13.933243741899011</v>
+        <v>14.15</v>
       </c>
       <c r="E18" s="4">
-        <v>13.8722421063352</v>
+        <v>13.706728868940489</v>
       </c>
       <c r="F18" s="4">
-        <v>4.776649656960462</v>
+        <v>4.0555276004387926</v>
       </c>
       <c r="G18" s="4">
-        <v>28</v>
+        <v>23.579343539967489</v>
       </c>
       <c r="H18" s="4">
         <v>2.4</v>
       </c>
       <c r="I18" s="4">
-        <v>18.5</v>
+        <v>17.97</v>
       </c>
       <c r="J18" s="4">
-        <v>15.975</v>
+        <v>15.664999999999999</v>
       </c>
       <c r="K18" s="4">
-        <v>11.932499999999999</v>
+        <v>12.070710419534601</v>
       </c>
       <c r="L18" s="4">
-        <v>8.25</v>
+        <v>8.7776885623644318</v>
       </c>
       <c r="M18" s="5">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B21" s="14" t="s">
         <v>18</v>
       </c>
@@ -2454,7 +2419,7 @@
       <c r="L21" s="14"/>
       <c r="M21" s="15"/>
     </row>
-    <row r="22" spans="2:13" ht="36" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B22" s="16" t="s">
         <v>1</v>
       </c>
@@ -2492,349 +2457,349 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B23" s="17">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="19">
-        <v>2.2000000000000002</v>
+        <v>1.903477732686309</v>
       </c>
       <c r="E23" s="19">
-        <v>2.186987611982687</v>
+        <v>1.9472671514439659</v>
       </c>
       <c r="F23" s="19">
-        <v>0.1887204567740951</v>
+        <v>0.23513609022150711</v>
       </c>
       <c r="G23" s="19">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="H23" s="19">
+        <v>1.4690816129342199</v>
+      </c>
+      <c r="I23" s="19">
+        <v>2.226</v>
+      </c>
+      <c r="J23" s="19">
+        <v>2.02811442939521</v>
+      </c>
+      <c r="K23" s="19">
         <v>1.8</v>
       </c>
-      <c r="I23" s="19">
-        <v>2.4029316853922098</v>
-      </c>
-      <c r="J23" s="19">
-        <v>2.31</v>
-      </c>
-      <c r="K23" s="19">
-        <v>2.0068546149244821</v>
-      </c>
       <c r="L23" s="19">
-        <v>1.9488768904442839</v>
+        <v>1.718826509086121</v>
       </c>
       <c r="M23" s="20">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B24" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="4">
-        <v>2.0499999999999998</v>
+        <v>1.9</v>
       </c>
       <c r="E24" s="4">
-        <v>2.054988686693239</v>
+        <v>1.8957187139685989</v>
       </c>
       <c r="F24" s="4">
-        <v>0.25440500284736861</v>
+        <v>0.2363113913001002</v>
       </c>
       <c r="G24" s="4">
-        <v>2.4900000000000002</v>
+        <v>2.6</v>
       </c>
       <c r="H24" s="4">
-        <v>1.51</v>
+        <v>1.5521275018822309</v>
       </c>
       <c r="I24" s="4">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J24" s="4">
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="K24" s="4">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="L24" s="4">
-        <v>1.7</v>
+        <v>1.6080000000000001</v>
       </c>
       <c r="M24" s="5">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B25" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="19">
-        <v>1.9462201480758829</v>
+        <v>1.79</v>
       </c>
       <c r="E25" s="19">
-        <v>1.961991474310786</v>
+        <v>1.831990921046516</v>
       </c>
       <c r="F25" s="19">
-        <v>0.26300444134194872</v>
+        <v>0.30099988147065587</v>
       </c>
       <c r="G25" s="19">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H25" s="19">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="I25" s="19">
-        <v>2.2879999999999998</v>
+        <v>2.3125492378601198</v>
       </c>
       <c r="J25" s="19">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="K25" s="19">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="L25" s="19">
-        <v>1.6419999999999999</v>
+        <v>1.533851268174919</v>
       </c>
       <c r="M25" s="20">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B26" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="4">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="E26" s="4">
-        <v>1.888434240749078</v>
+        <v>1.764020453231395</v>
       </c>
       <c r="F26" s="4">
-        <v>0.25807196180085251</v>
+        <v>0.27311116991048312</v>
       </c>
       <c r="G26" s="4">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="H26" s="4">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="I26" s="4">
-        <v>2.27</v>
+        <v>2.112773248118597</v>
       </c>
       <c r="J26" s="4">
-        <v>2</v>
+        <v>1.895</v>
       </c>
       <c r="K26" s="4">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="L26" s="4">
-        <v>1.631208619680474</v>
+        <v>1.5</v>
       </c>
       <c r="M26" s="5">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B27" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C27" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="19">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="E27" s="19">
-        <v>1.821751013824203</v>
+        <v>1.6862091218637509</v>
       </c>
       <c r="F27" s="19">
-        <v>0.23925530572572001</v>
+        <v>0.24467129630068041</v>
       </c>
       <c r="G27" s="19">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H27" s="19">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I27" s="19">
-        <v>2.087405516006728</v>
+        <v>1.93</v>
       </c>
       <c r="J27" s="19">
-        <v>1.95</v>
+        <v>1.820125</v>
       </c>
       <c r="K27" s="19">
-        <v>1.7</v>
+        <v>1.5249999999999999</v>
       </c>
       <c r="L27" s="19">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="M27" s="20">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B28" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D28" s="4">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="E28" s="4">
-        <v>1.752377867350426</v>
+        <v>1.6308224060474159</v>
       </c>
       <c r="F28" s="4">
-        <v>0.23059663001893241</v>
+        <v>0.2452663861947513</v>
       </c>
       <c r="G28" s="4">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="H28" s="4">
-        <v>1.1000000000000001</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="I28" s="4">
-        <v>2.004</v>
+        <v>1.89968566144053</v>
       </c>
       <c r="J28" s="4">
-        <v>1.9</v>
+        <v>1.797156600306359</v>
       </c>
       <c r="K28" s="4">
-        <v>1.615552331574688</v>
+        <v>1.5</v>
       </c>
       <c r="L28" s="4">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="M28" s="5">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="29" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B29" s="17">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D29" s="19">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="E29" s="19">
-        <v>1.718483531497051</v>
+        <v>1.6875852417773971</v>
       </c>
       <c r="F29" s="19">
-        <v>0.2382530427895953</v>
+        <v>0.27447246158208</v>
       </c>
       <c r="G29" s="19">
-        <v>2.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H29" s="19">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="I29" s="19">
         <v>2</v>
       </c>
       <c r="J29" s="19">
-        <v>1.8613407091195291</v>
+        <v>1.8132946143661139</v>
       </c>
       <c r="K29" s="19">
-        <v>1.5974999999999999</v>
+        <v>1.479076361329672</v>
       </c>
       <c r="L29" s="19">
-        <v>1.477148570530711</v>
+        <v>1.390919741233396</v>
       </c>
       <c r="M29" s="20">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D30" s="4">
-        <v>23.264058795931209</v>
+        <v>21.8</v>
       </c>
       <c r="E30" s="4">
-        <v>22.963397704185429</v>
+        <v>21.878786486212778</v>
       </c>
       <c r="F30" s="4">
-        <v>2.9623276792942002</v>
+        <v>3.3114132753200192</v>
       </c>
       <c r="G30" s="4">
-        <v>30.9</v>
+        <v>28.5</v>
       </c>
       <c r="H30" s="4">
-        <v>15.7</v>
+        <v>13.20549237655384</v>
       </c>
       <c r="I30" s="4">
-        <v>25.74</v>
+        <v>25.78</v>
       </c>
       <c r="J30" s="4">
-        <v>24.655000000000001</v>
+        <v>23.636934539457719</v>
       </c>
       <c r="K30" s="4">
-        <v>21.512499999999999</v>
+        <v>20.74</v>
       </c>
       <c r="L30" s="4">
-        <v>19.457000000000001</v>
+        <v>18.78</v>
       </c>
       <c r="M30" s="5">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B31" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D31" s="19">
-        <v>17.910842132722731</v>
+        <v>16.36</v>
       </c>
       <c r="E31" s="19">
-        <v>16.895881186644349</v>
+        <v>16.35573137512819</v>
       </c>
       <c r="F31" s="19">
-        <v>4.5325415203253003</v>
+        <v>4.5378577126919017</v>
       </c>
       <c r="G31" s="19">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="H31" s="19">
-        <v>5.0999999999999996</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I31" s="19">
-        <v>21.98</v>
+        <v>21.952000000000002</v>
       </c>
       <c r="J31" s="19">
-        <v>19.649999999999999</v>
+        <v>18.68601058009952</v>
       </c>
       <c r="K31" s="19">
-        <v>14.2</v>
+        <v>14.48819041704337</v>
       </c>
       <c r="L31" s="19">
-        <v>9.2527298799494151</v>
+        <v>8.844808370082113</v>
       </c>
       <c r="M31" s="20">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="32" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
         <v>36</v>
       </c>
@@ -2842,37 +2807,37 @@
         <v>16</v>
       </c>
       <c r="D32" s="4">
-        <v>29.742854205066639</v>
+        <v>28.75</v>
       </c>
       <c r="E32" s="4">
-        <v>29.730864754698771</v>
+        <v>28.75636017403901</v>
       </c>
       <c r="F32" s="4">
-        <v>1.928062980188856</v>
+        <v>1.9309470179281389</v>
       </c>
       <c r="G32" s="4">
-        <v>34.6</v>
+        <v>34</v>
       </c>
       <c r="H32" s="4">
-        <v>26.4</v>
+        <v>24.9</v>
       </c>
       <c r="I32" s="4">
-        <v>31.963136003163498</v>
+        <v>30.83952597513721</v>
       </c>
       <c r="J32" s="4">
-        <v>30.68135047018913</v>
+        <v>29.683887744808199</v>
       </c>
       <c r="K32" s="4">
-        <v>28.581712787023811</v>
+        <v>27.802381154589799</v>
       </c>
       <c r="L32" s="4">
-        <v>27.5</v>
+        <v>26.946699668243241</v>
       </c>
       <c r="M32" s="5">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B33" s="21" t="s">
         <v>37</v>
       </c>
@@ -2880,79 +2845,79 @@
         <v>17</v>
       </c>
       <c r="D33" s="19">
-        <v>19.460842436397559</v>
+        <v>19.957775051980061</v>
       </c>
       <c r="E33" s="19">
-        <v>19.390588132434591</v>
+        <v>19.74868672866695</v>
       </c>
       <c r="F33" s="19">
-        <v>4.3987564479017136</v>
+        <v>4.0523777982335396</v>
       </c>
       <c r="G33" s="19">
-        <v>31</v>
+        <v>26.07</v>
       </c>
       <c r="H33" s="19">
         <v>8.9</v>
       </c>
       <c r="I33" s="19">
-        <v>24.133972316289132</v>
+        <v>24.57</v>
       </c>
       <c r="J33" s="19">
-        <v>21.994890336011771</v>
+        <v>22.63</v>
       </c>
       <c r="K33" s="19">
-        <v>17.5975</v>
+        <v>18.237500000000001</v>
       </c>
       <c r="L33" s="19">
-        <v>12.975369215951529</v>
+        <v>14.315516902332149</v>
       </c>
       <c r="M33" s="20">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="D34" s="4">
-        <v>13.90648748379801</v>
+        <v>14</v>
       </c>
       <c r="E34" s="4">
-        <v>13.603635463983871</v>
+        <v>13.41431360717104</v>
       </c>
       <c r="F34" s="4">
-        <v>4.9034633497087734</v>
+        <v>4.3452932966067088</v>
       </c>
       <c r="G34" s="4">
-        <v>25</v>
+        <v>22.656415720267219</v>
       </c>
       <c r="H34" s="4">
         <v>1.8</v>
       </c>
       <c r="I34" s="4">
-        <v>19</v>
+        <v>17.2</v>
       </c>
       <c r="J34" s="4">
-        <v>15.65</v>
+        <v>15.04</v>
       </c>
       <c r="K34" s="4">
-        <v>11.3</v>
+        <v>11.93</v>
       </c>
       <c r="L34" s="4">
-        <v>7.6293783124454118</v>
+        <v>7.940551090791045</v>
       </c>
       <c r="M34" s="5">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B36" s="22"/>
       <c r="C36" s="23"/>
     </row>
-    <row r="37" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B37" s="14" t="s">
         <v>35</v>
       </c>
@@ -2968,7 +2933,7 @@
       <c r="L37" s="14"/>
       <c r="M37" s="15"/>
     </row>
-    <row r="38" spans="2:13" ht="36" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B38" s="24" t="s">
         <v>1</v>
       </c>
@@ -3006,353 +2971,353 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B39" s="7">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D39" s="26">
-        <v>22.75</v>
-      </c>
-      <c r="E39" s="26">
-        <v>22.644042428977041</v>
-      </c>
-      <c r="F39" s="26">
-        <v>1.0857484117050431</v>
-      </c>
-      <c r="G39" s="4">
-        <v>25.6</v>
-      </c>
-      <c r="H39" s="4">
-        <v>20.41</v>
-      </c>
-      <c r="I39" s="4">
-        <v>23.6</v>
-      </c>
-      <c r="J39" s="4">
+      <c r="D39" s="33">
+        <v>22.5</v>
+      </c>
+      <c r="E39" s="33">
+        <v>22.59632694642028</v>
+      </c>
+      <c r="F39" s="33">
+        <v>0.95142550207862098</v>
+      </c>
+      <c r="G39" s="33">
+        <v>25.452888411924771</v>
+      </c>
+      <c r="H39" s="33">
+        <v>20.390191235913321</v>
+      </c>
+      <c r="I39" s="33">
+        <v>24</v>
+      </c>
+      <c r="J39" s="33">
         <v>23</v>
       </c>
-      <c r="K39" s="4">
+      <c r="K39" s="33">
         <v>22</v>
       </c>
-      <c r="L39" s="4">
-        <v>21.4</v>
+      <c r="L39" s="33">
+        <v>21.67</v>
       </c>
       <c r="M39" s="8">
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B40" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C40" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="27">
-        <v>22.8</v>
-      </c>
-      <c r="E40" s="27">
-        <v>22.86331300534502</v>
-      </c>
-      <c r="F40" s="27">
-        <v>1.993401616492493</v>
-      </c>
-      <c r="G40" s="19">
-        <v>30.336397852763231</v>
-      </c>
-      <c r="H40" s="19">
-        <v>19.815636601137939</v>
-      </c>
-      <c r="I40" s="19">
-        <v>24.2</v>
-      </c>
-      <c r="J40" s="19">
-        <v>23.6</v>
-      </c>
-      <c r="K40" s="19">
-        <v>21.9</v>
-      </c>
-      <c r="L40" s="19">
-        <v>20.79</v>
+      <c r="D40" s="32">
+        <v>22.3</v>
+      </c>
+      <c r="E40" s="32">
+        <v>22.566311613960131</v>
+      </c>
+      <c r="F40" s="32">
+        <v>1.7081961310079039</v>
+      </c>
+      <c r="G40" s="32">
+        <v>27.6</v>
+      </c>
+      <c r="H40" s="32">
+        <v>19.03</v>
+      </c>
+      <c r="I40" s="32">
+        <v>24.5</v>
+      </c>
+      <c r="J40" s="32">
+        <v>23.5</v>
+      </c>
+      <c r="K40" s="32">
+        <v>21.52487286176606</v>
+      </c>
+      <c r="L40" s="32">
+        <v>20.9</v>
       </c>
       <c r="M40" s="20">
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B41" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="26">
-        <v>22.7</v>
-      </c>
-      <c r="E41" s="26">
-        <v>22.82262020950882</v>
-      </c>
-      <c r="F41" s="26">
-        <v>2.2579219503603118</v>
-      </c>
-      <c r="G41" s="4">
-        <v>30.208643875427299</v>
-      </c>
-      <c r="H41" s="4">
-        <v>18.749676071340001</v>
-      </c>
-      <c r="I41" s="4">
-        <v>24.7</v>
-      </c>
-      <c r="J41" s="4">
-        <v>24.1</v>
-      </c>
-      <c r="K41" s="4">
-        <v>21.2</v>
-      </c>
-      <c r="L41" s="4">
+      <c r="D41" s="33">
+        <v>22.531764705882338</v>
+      </c>
+      <c r="E41" s="33">
+        <v>22.689597397328509</v>
+      </c>
+      <c r="F41" s="33">
+        <v>2.0295370607586021</v>
+      </c>
+      <c r="G41" s="33">
+        <v>27.600212458493619</v>
+      </c>
+      <c r="H41" s="33">
+        <v>18.206151097038688</v>
+      </c>
+      <c r="I41" s="33">
+        <v>25</v>
+      </c>
+      <c r="J41" s="33">
+        <v>24</v>
+      </c>
+      <c r="K41" s="33">
+        <v>21.5</v>
+      </c>
+      <c r="L41" s="33">
         <v>20.5</v>
       </c>
       <c r="M41" s="5">
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B42" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C42" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D42" s="27">
-        <v>22.8</v>
-      </c>
-      <c r="E42" s="27">
-        <v>22.791386201724489</v>
-      </c>
-      <c r="F42" s="27">
-        <v>2.379015892209392</v>
-      </c>
-      <c r="G42" s="19">
-        <v>27.5</v>
-      </c>
-      <c r="H42" s="19">
-        <v>17.68371554154205</v>
-      </c>
-      <c r="I42" s="19">
-        <v>25.8</v>
-      </c>
-      <c r="J42" s="19">
-        <v>24.4</v>
-      </c>
-      <c r="K42" s="19">
-        <v>21</v>
-      </c>
-      <c r="L42" s="19">
-        <v>20</v>
+      <c r="D42" s="32">
+        <v>22.47</v>
+      </c>
+      <c r="E42" s="32">
+        <v>22.329617077858579</v>
+      </c>
+      <c r="F42" s="32">
+        <v>2.427838877374195</v>
+      </c>
+      <c r="G42" s="32">
+        <v>27.6</v>
+      </c>
+      <c r="H42" s="32">
+        <v>17.114131027601371</v>
+      </c>
+      <c r="I42" s="32">
+        <v>25.007553472267858</v>
+      </c>
+      <c r="J42" s="32">
+        <v>24</v>
+      </c>
+      <c r="K42" s="32">
+        <v>21.15</v>
+      </c>
+      <c r="L42" s="32">
+        <v>19.3</v>
       </c>
       <c r="M42" s="20">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B43" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D43" s="26">
-        <v>22.5</v>
-      </c>
-      <c r="E43" s="26">
-        <v>22.54169141134933</v>
-      </c>
-      <c r="F43" s="26">
-        <v>2.7697306467237719</v>
-      </c>
-      <c r="G43" s="4">
-        <v>29.01</v>
-      </c>
-      <c r="H43" s="4">
-        <v>16.617755011744119</v>
-      </c>
-      <c r="I43" s="4">
-        <v>25.44</v>
-      </c>
-      <c r="J43" s="4">
-        <v>24.5</v>
-      </c>
-      <c r="K43" s="4">
-        <v>21</v>
-      </c>
-      <c r="L43" s="4">
+      <c r="D43" s="33">
+        <v>22.1</v>
+      </c>
+      <c r="E43" s="33">
+        <v>22.016103856159699</v>
+      </c>
+      <c r="F43" s="33">
+        <v>2.7364496860755771</v>
+      </c>
+      <c r="G43" s="33">
+        <v>27.6</v>
+      </c>
+      <c r="H43" s="33">
+        <v>15.5</v>
+      </c>
+      <c r="I43" s="33">
+        <v>25.39</v>
+      </c>
+      <c r="J43" s="33">
+        <v>23</v>
+      </c>
+      <c r="K43" s="33">
+        <v>20.882339343504391</v>
+      </c>
+      <c r="L43" s="33">
         <v>19</v>
       </c>
       <c r="M43" s="5">
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B44" s="17">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C44" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D44" s="27">
-        <v>22.3</v>
-      </c>
-      <c r="E44" s="27">
-        <v>22.188500289152849</v>
-      </c>
-      <c r="F44" s="27">
-        <v>2.7808406071242362</v>
-      </c>
-      <c r="G44" s="19">
-        <v>27.6</v>
-      </c>
-      <c r="H44" s="19">
-        <v>16.084774746845131</v>
-      </c>
-      <c r="I44" s="19">
-        <v>25.97</v>
-      </c>
-      <c r="J44" s="19">
-        <v>23.33</v>
-      </c>
-      <c r="K44" s="19">
-        <v>20.399999999999999</v>
-      </c>
-      <c r="L44" s="19">
-        <v>18.899999999999999</v>
+      <c r="D44" s="32">
+        <v>22</v>
+      </c>
+      <c r="E44" s="32">
+        <v>21.974363861595641</v>
+      </c>
+      <c r="F44" s="32">
+        <v>2.8483699984935691</v>
+      </c>
+      <c r="G44" s="32">
+        <v>28.15</v>
+      </c>
+      <c r="H44" s="32">
+        <v>14.8</v>
+      </c>
+      <c r="I44" s="32">
+        <v>25.207986932140319</v>
+      </c>
+      <c r="J44" s="32">
+        <v>23</v>
+      </c>
+      <c r="K44" s="32">
+        <v>20.302438685005701</v>
+      </c>
+      <c r="L44" s="32">
+        <v>19.100000000000001</v>
       </c>
       <c r="M44" s="20">
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D45" s="26">
-        <v>20.29</v>
-      </c>
-      <c r="E45" s="26">
-        <v>20.529360093705069</v>
-      </c>
-      <c r="F45" s="26">
-        <v>2.7861710349981008</v>
-      </c>
-      <c r="G45" s="4">
-        <v>28</v>
-      </c>
-      <c r="H45" s="4">
-        <v>14</v>
-      </c>
-      <c r="I45" s="4">
-        <v>23.466000000000001</v>
-      </c>
-      <c r="J45" s="4">
-        <v>22.5</v>
-      </c>
-      <c r="K45" s="4">
-        <v>19.127154161757659</v>
-      </c>
-      <c r="L45" s="4">
-        <v>17.3</v>
+        <v>48</v>
+      </c>
+      <c r="D45" s="33">
+        <v>20.75</v>
+      </c>
+      <c r="E45" s="33">
+        <v>21.173643216205701</v>
+      </c>
+      <c r="F45" s="33">
+        <v>3.8228709678238708</v>
+      </c>
+      <c r="G45" s="33">
+        <v>29.20000000000001</v>
+      </c>
+      <c r="H45" s="33">
+        <v>12.4</v>
+      </c>
+      <c r="I45" s="33">
+        <v>25.95000000000001</v>
+      </c>
+      <c r="J45" s="33">
+        <v>23.5625</v>
+      </c>
+      <c r="K45" s="33">
+        <v>18.4725</v>
+      </c>
+      <c r="L45" s="33">
+        <v>16.422154491615458</v>
       </c>
       <c r="M45" s="5">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="46" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B46" s="21" t="s">
         <v>36</v>
       </c>
       <c r="C46" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D46" s="27">
-        <v>22.1</v>
-      </c>
-      <c r="E46" s="27">
-        <v>22.054607839260509</v>
-      </c>
-      <c r="F46" s="27">
-        <v>2.8187681324373979</v>
-      </c>
-      <c r="G46" s="19">
-        <v>28.2</v>
-      </c>
-      <c r="H46" s="19">
-        <v>15.2</v>
-      </c>
-      <c r="I46" s="19">
-        <v>26</v>
-      </c>
-      <c r="J46" s="19">
-        <v>23.1</v>
-      </c>
-      <c r="K46" s="19">
-        <v>20.3</v>
-      </c>
-      <c r="L46" s="19">
+      <c r="D46" s="32">
+        <v>22</v>
+      </c>
+      <c r="E46" s="32">
+        <v>21.974363861595641</v>
+      </c>
+      <c r="F46" s="32">
+        <v>2.8483699984935691</v>
+      </c>
+      <c r="G46" s="32">
+        <v>28.15</v>
+      </c>
+      <c r="H46" s="32">
+        <v>14.8</v>
+      </c>
+      <c r="I46" s="32">
+        <v>25.207986932140319</v>
+      </c>
+      <c r="J46" s="32">
+        <v>23</v>
+      </c>
+      <c r="K46" s="32">
+        <v>20.302438685005701</v>
+      </c>
+      <c r="L46" s="32">
         <v>19.100000000000001</v>
       </c>
       <c r="M46" s="20">
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B47" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D47" s="26">
+        <v>40</v>
+      </c>
+      <c r="D47" s="33">
         <v>18.5</v>
       </c>
-      <c r="E47" s="26">
-        <v>19.18294068968158</v>
-      </c>
-      <c r="F47" s="26">
-        <v>4.3004308521398054</v>
-      </c>
-      <c r="G47" s="4">
+      <c r="E47" s="33">
+        <v>19.23952271483568</v>
+      </c>
+      <c r="F47" s="33">
+        <v>4.4449230351758553</v>
+      </c>
+      <c r="G47" s="33">
         <v>28.6</v>
       </c>
-      <c r="H47" s="4">
-        <v>12</v>
-      </c>
-      <c r="I47" s="4">
-        <v>24.44</v>
-      </c>
-      <c r="J47" s="4">
-        <v>22.4</v>
-      </c>
-      <c r="K47" s="4">
-        <v>16.2</v>
-      </c>
-      <c r="L47" s="4">
-        <v>14.339220846486249</v>
+      <c r="H47" s="33">
+        <v>10.78041462486493</v>
+      </c>
+      <c r="I47" s="33">
+        <v>25</v>
+      </c>
+      <c r="J47" s="33">
+        <v>22.94999999999991</v>
+      </c>
+      <c r="K47" s="33">
+        <v>16.175000000000001</v>
+      </c>
+      <c r="L47" s="33">
+        <v>13.6</v>
       </c>
       <c r="M47" s="5">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="48" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B48" s="22"/>
       <c r="C48" s="23"/>
     </row>
-    <row r="50" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B50" s="14" t="s">
         <v>21</v>
       </c>
@@ -3368,7 +3333,7 @@
       <c r="L50" s="14"/>
       <c r="M50" s="15"/>
     </row>
-    <row r="51" spans="2:13" ht="36" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B51" s="24" t="s">
         <v>1</v>
       </c>
@@ -3406,357 +3371,357 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B52" s="7">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D52" s="28">
-        <v>1422</v>
-      </c>
-      <c r="E52" s="28">
-        <v>1422.557114858188</v>
-      </c>
-      <c r="F52" s="28">
-        <v>12.75563630998457</v>
-      </c>
-      <c r="G52" s="28">
-        <v>1455.4860851437541</v>
-      </c>
-      <c r="H52" s="28">
-        <v>1400</v>
-      </c>
-      <c r="I52" s="28">
-        <v>1439.2049999999999</v>
-      </c>
-      <c r="J52" s="28">
-        <v>1429.95</v>
-      </c>
-      <c r="K52" s="28">
-        <v>1413.953306943625</v>
-      </c>
-      <c r="L52" s="28">
-        <v>1406.4649999999999</v>
+      <c r="D52" s="34">
+        <v>1482</v>
+      </c>
+      <c r="E52" s="34">
+        <v>1483.094729371732</v>
+      </c>
+      <c r="F52" s="34">
+        <v>21.661192365584242</v>
+      </c>
+      <c r="G52" s="34">
+        <v>1527.095508643622</v>
+      </c>
+      <c r="H52" s="34">
+        <v>1437.704736463515</v>
+      </c>
+      <c r="I52" s="34">
+        <v>1506.405274553799</v>
+      </c>
+      <c r="J52" s="34">
+        <v>1499.25</v>
+      </c>
+      <c r="K52" s="34">
+        <v>1473.2934544573361</v>
+      </c>
+      <c r="L52" s="34">
+        <v>1452.450269113885</v>
       </c>
       <c r="M52" s="5">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="53" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B53" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C53" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D53" s="29">
-        <v>1447.239968621363</v>
-      </c>
-      <c r="E53" s="29">
-        <v>1448.9632257264959</v>
-      </c>
-      <c r="F53" s="29">
-        <v>22.509710297950701</v>
-      </c>
-      <c r="G53" s="29">
-        <v>1518.113150242837</v>
-      </c>
-      <c r="H53" s="29">
-        <v>1400</v>
-      </c>
-      <c r="I53" s="29">
-        <v>1471.56203592426</v>
-      </c>
-      <c r="J53" s="29">
-        <v>1460</v>
-      </c>
-      <c r="K53" s="29">
-        <v>1438.30013117098</v>
-      </c>
-      <c r="L53" s="29">
-        <v>1422.83</v>
+      <c r="D53" s="35">
+        <v>1512.776088595379</v>
+      </c>
+      <c r="E53" s="35">
+        <v>1516.0592091939691</v>
+      </c>
+      <c r="F53" s="35">
+        <v>29.85628120137909</v>
+      </c>
+      <c r="G53" s="35">
+        <v>1584.823400588039</v>
+      </c>
+      <c r="H53" s="35">
+        <v>1462</v>
+      </c>
+      <c r="I53" s="35">
+        <v>1552.588</v>
+      </c>
+      <c r="J53" s="35">
+        <v>1533.562112937675</v>
+      </c>
+      <c r="K53" s="35">
+        <v>1499.5138985895869</v>
+      </c>
+      <c r="L53" s="35">
+        <v>1471.8</v>
       </c>
       <c r="M53" s="20">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="54" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="54" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B54" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D54" s="28">
-        <v>1475.902377802618</v>
-      </c>
-      <c r="E54" s="28">
-        <v>1483.1522496739251</v>
-      </c>
-      <c r="F54" s="28">
-        <v>36.326100544981102</v>
-      </c>
-      <c r="G54" s="28">
-        <v>1589.4763832425319</v>
-      </c>
-      <c r="H54" s="28">
-        <v>1420</v>
-      </c>
-      <c r="I54" s="28">
-        <v>1527.91</v>
-      </c>
-      <c r="J54" s="28">
-        <v>1496.9947995622281</v>
-      </c>
-      <c r="K54" s="28">
-        <v>1463.7891155680879</v>
-      </c>
-      <c r="L54" s="28">
-        <v>1444.6</v>
+      <c r="D54" s="34">
+        <v>1548.019695973675</v>
+      </c>
+      <c r="E54" s="34">
+        <v>1551.043416208963</v>
+      </c>
+      <c r="F54" s="34">
+        <v>38.965725029468643</v>
+      </c>
+      <c r="G54" s="34">
+        <v>1641.1237222741911</v>
+      </c>
+      <c r="H54" s="34">
+        <v>1472</v>
+      </c>
+      <c r="I54" s="34">
+        <v>1600.614</v>
+      </c>
+      <c r="J54" s="34">
+        <v>1573.281563267542</v>
+      </c>
+      <c r="K54" s="34">
+        <v>1527.7049999999999</v>
+      </c>
+      <c r="L54" s="34">
+        <v>1497.812092556205</v>
       </c>
       <c r="M54" s="5">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="55" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B55" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C55" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D55" s="29">
-        <v>1516.418897928615</v>
-      </c>
-      <c r="E55" s="29">
-        <v>1521.7073994063021</v>
-      </c>
-      <c r="F55" s="29">
-        <v>50.305564646569671</v>
-      </c>
-      <c r="G55" s="29">
-        <v>1679.9475768687271</v>
-      </c>
-      <c r="H55" s="29">
-        <v>1428</v>
-      </c>
-      <c r="I55" s="29">
-        <v>1587.81</v>
-      </c>
-      <c r="J55" s="29">
-        <v>1543.4080208720329</v>
-      </c>
-      <c r="K55" s="29">
-        <v>1494.1828901986451</v>
-      </c>
-      <c r="L55" s="29">
-        <v>1466</v>
+      <c r="D55" s="35">
+        <v>1588.8549330032929</v>
+      </c>
+      <c r="E55" s="35">
+        <v>1587.5068955214899</v>
+      </c>
+      <c r="F55" s="35">
+        <v>47.040836621505633</v>
+      </c>
+      <c r="G55" s="35">
+        <v>1700.0392641662841</v>
+      </c>
+      <c r="H55" s="35">
+        <v>1490</v>
+      </c>
+      <c r="I55" s="35">
+        <v>1643.509</v>
+      </c>
+      <c r="J55" s="35">
+        <v>1611.2393432655549</v>
+      </c>
+      <c r="K55" s="35">
+        <v>1554.25</v>
+      </c>
+      <c r="L55" s="35">
+        <v>1531.552160520303</v>
       </c>
       <c r="M55" s="20">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="56" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B56" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D56" s="28">
-        <v>1552.90364776349</v>
-      </c>
-      <c r="E56" s="28">
-        <v>1562.801289737173</v>
-      </c>
-      <c r="F56" s="28">
-        <v>60.630752275269643</v>
-      </c>
-      <c r="G56" s="28">
-        <v>1766.3306638135209</v>
-      </c>
-      <c r="H56" s="28">
-        <v>1435</v>
-      </c>
-      <c r="I56" s="28">
-        <v>1639.8357552689929</v>
-      </c>
-      <c r="J56" s="28">
-        <v>1589.98242923507</v>
-      </c>
-      <c r="K56" s="28">
-        <v>1532.087604614087</v>
-      </c>
-      <c r="L56" s="28">
-        <v>1497.05</v>
+      <c r="D56" s="34">
+        <v>1620.5</v>
+      </c>
+      <c r="E56" s="34">
+        <v>1623.304224154007</v>
+      </c>
+      <c r="F56" s="34">
+        <v>58.663304432292414</v>
+      </c>
+      <c r="G56" s="34">
+        <v>1754.9590957633441</v>
+      </c>
+      <c r="H56" s="34">
+        <v>1497</v>
+      </c>
+      <c r="I56" s="34">
+        <v>1689.45733002527</v>
+      </c>
+      <c r="J56" s="34">
+        <v>1663.335</v>
+      </c>
+      <c r="K56" s="34">
+        <v>1578.668217523496</v>
+      </c>
+      <c r="L56" s="34">
+        <v>1560.251580798875</v>
       </c>
       <c r="M56" s="5">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="57" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="57" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B57" s="17">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C57" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D57" s="29">
-        <v>1596.778465322594</v>
-      </c>
-      <c r="E57" s="29">
-        <v>1602.8742837752061</v>
-      </c>
-      <c r="F57" s="29">
-        <v>72.983020902140495</v>
-      </c>
-      <c r="G57" s="29">
-        <v>1848.053518746955</v>
-      </c>
-      <c r="H57" s="29">
-        <v>1441</v>
-      </c>
-      <c r="I57" s="29">
-        <v>1700.2940000000001</v>
-      </c>
-      <c r="J57" s="29">
-        <v>1632.54</v>
-      </c>
-      <c r="K57" s="29">
-        <v>1564.6547476439291</v>
-      </c>
-      <c r="L57" s="29">
-        <v>1513.64</v>
+      <c r="D57" s="35">
+        <v>1672.5</v>
+      </c>
+      <c r="E57" s="35">
+        <v>1665.56479686698</v>
+      </c>
+      <c r="F57" s="35">
+        <v>70.36878388220461</v>
+      </c>
+      <c r="G57" s="35">
+        <v>1814.57</v>
+      </c>
+      <c r="H57" s="35">
+        <v>1503</v>
+      </c>
+      <c r="I57" s="35">
+        <v>1739.17</v>
+      </c>
+      <c r="J57" s="35">
+        <v>1704.8</v>
+      </c>
+      <c r="K57" s="35">
+        <v>1620.95</v>
+      </c>
+      <c r="L57" s="35">
+        <v>1592.0060000000001</v>
       </c>
       <c r="M57" s="20">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="58" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D58" s="28">
-        <v>1760</v>
-      </c>
-      <c r="E58" s="28">
-        <v>1782.4587625709939</v>
-      </c>
-      <c r="F58" s="28">
-        <v>129.61801099286299</v>
-      </c>
-      <c r="G58" s="28">
-        <v>2034.3223115228591</v>
-      </c>
-      <c r="H58" s="28">
-        <v>1473</v>
-      </c>
-      <c r="I58" s="28">
-        <v>1970.89</v>
-      </c>
-      <c r="J58" s="28">
-        <v>1850</v>
-      </c>
-      <c r="K58" s="28">
-        <v>1702</v>
-      </c>
-      <c r="L58" s="28">
-        <v>1623.7</v>
+        <v>49</v>
+      </c>
+      <c r="D58" s="34">
+        <v>1805</v>
+      </c>
+      <c r="E58" s="34">
+        <v>1830.9658213693881</v>
+      </c>
+      <c r="F58" s="34">
+        <v>118.8107865208504</v>
+      </c>
+      <c r="G58" s="34">
+        <v>2036.2756138807511</v>
+      </c>
+      <c r="H58" s="34">
+        <v>1535</v>
+      </c>
+      <c r="I58" s="34">
+        <v>1977</v>
+      </c>
+      <c r="J58" s="34">
+        <v>1931.4238026973781</v>
+      </c>
+      <c r="K58" s="34">
+        <v>1762</v>
+      </c>
+      <c r="L58" s="34">
+        <v>1697.1222435828861</v>
       </c>
       <c r="M58" s="5">
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B59" s="21" t="s">
         <v>36</v>
       </c>
       <c r="C59" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D59" s="29">
-        <v>1658.07</v>
-      </c>
-      <c r="E59" s="29">
-        <v>1660.1411723744859</v>
-      </c>
-      <c r="F59" s="29">
-        <v>91.158382964724623</v>
-      </c>
-      <c r="G59" s="29">
-        <v>1921.133038869473</v>
-      </c>
-      <c r="H59" s="29">
-        <v>1448</v>
-      </c>
-      <c r="I59" s="29">
-        <v>1776.018401457392</v>
-      </c>
-      <c r="J59" s="29">
-        <v>1699.688100018197</v>
-      </c>
-      <c r="K59" s="29">
-        <v>1604</v>
-      </c>
-      <c r="L59" s="29">
-        <v>1556.22</v>
+      <c r="D59" s="35">
+        <v>1672.5</v>
+      </c>
+      <c r="E59" s="35">
+        <v>1665.56479686698</v>
+      </c>
+      <c r="F59" s="35">
+        <v>70.36878388220461</v>
+      </c>
+      <c r="G59" s="35">
+        <v>1814.57</v>
+      </c>
+      <c r="H59" s="35">
+        <v>1503</v>
+      </c>
+      <c r="I59" s="35">
+        <v>1739.17</v>
+      </c>
+      <c r="J59" s="35">
+        <v>1704.8</v>
+      </c>
+      <c r="K59" s="35">
+        <v>1620.95</v>
+      </c>
+      <c r="L59" s="35">
+        <v>1592.0060000000001</v>
       </c>
       <c r="M59" s="20">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="60" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B60" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C60" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="34">
+        <v>2018.2524672873551</v>
+      </c>
+      <c r="E60" s="34">
+        <v>2025.422572003409</v>
+      </c>
+      <c r="F60" s="34">
+        <v>160.41928317066061</v>
+      </c>
+      <c r="G60" s="34">
+        <v>2359.2199999999998</v>
+      </c>
+      <c r="H60" s="34">
+        <v>1609</v>
+      </c>
+      <c r="I60" s="34">
+        <v>2214.6669999999999</v>
+      </c>
+      <c r="J60" s="34">
+        <v>2122.515935914907</v>
+      </c>
+      <c r="K60" s="34">
+        <v>1921</v>
+      </c>
+      <c r="L60" s="34">
+        <v>1832.187674966756</v>
+      </c>
+      <c r="M60" s="5">
         <v>42</v>
       </c>
-      <c r="D60" s="28">
-        <v>2000</v>
-      </c>
-      <c r="E60" s="28">
-        <v>2008.218736989417</v>
-      </c>
-      <c r="F60" s="28">
-        <v>186.41477894071389</v>
-      </c>
-      <c r="G60" s="28">
-        <v>2500</v>
-      </c>
-      <c r="H60" s="28">
-        <v>1550</v>
-      </c>
-      <c r="I60" s="28">
-        <v>2206.5120962899268</v>
-      </c>
-      <c r="J60" s="28">
-        <v>2126.9920443450451</v>
-      </c>
-      <c r="K60" s="28">
-        <v>1902.85071813486</v>
-      </c>
-      <c r="L60" s="28">
-        <v>1759.9</v>
-      </c>
-      <c r="M60" s="5">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="61" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="61" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B61" s="22"/>
       <c r="C61" s="23"/>
     </row>
-    <row r="62" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B62" s="22"/>
       <c r="C62" s="23"/>
     </row>
-    <row r="63" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B63" s="14" t="s">
         <v>24</v>
       </c>
@@ -3772,7 +3737,7 @@
       <c r="L63" s="14"/>
       <c r="M63" s="15"/>
     </row>
-    <row r="64" spans="2:13" ht="36" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B64" s="24" t="s">
         <v>1</v>
       </c>
@@ -3810,273 +3775,273 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B65" s="7">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D65" s="28">
-        <v>8937.7941348424301</v>
+        <v>8965</v>
       </c>
       <c r="E65" s="28">
-        <v>8980.0446052416519</v>
+        <v>8880.8383728003646</v>
       </c>
       <c r="F65" s="28">
-        <v>504.59484648651897</v>
+        <v>440.95615928263999</v>
       </c>
       <c r="G65" s="28">
-        <v>10125</v>
+        <v>9537</v>
       </c>
       <c r="H65" s="28">
-        <v>7754.8046209990562</v>
+        <v>7901.6981850447673</v>
       </c>
       <c r="I65" s="28">
-        <v>9663.0021928415426</v>
+        <v>9350.7558546555574</v>
       </c>
       <c r="J65" s="28">
-        <v>9317.2170455514406</v>
+        <v>9264.451616904571</v>
       </c>
       <c r="K65" s="28">
-        <v>8691.2606223762923</v>
+        <v>8637.7646955909076</v>
       </c>
       <c r="L65" s="28">
-        <v>8302.0407154269997</v>
+        <v>8222.6679562838544</v>
       </c>
       <c r="M65" s="8">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="66" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B66" s="17">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C66" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D66" s="29">
-        <v>8730</v>
+        <v>8757.2930478770559</v>
       </c>
       <c r="E66" s="29">
-        <v>8688.791871122914</v>
+        <v>8817.1015514095488</v>
       </c>
       <c r="F66" s="29">
-        <v>514.28961553111003</v>
+        <v>425.23194289342177</v>
       </c>
       <c r="G66" s="29">
-        <v>9796</v>
+        <v>9607.375445483829</v>
       </c>
       <c r="H66" s="29">
-        <v>7307.9</v>
+        <v>8000</v>
       </c>
       <c r="I66" s="29">
-        <v>9282.053626346531</v>
+        <v>9469</v>
       </c>
       <c r="J66" s="29">
-        <v>9070.6997028747392</v>
+        <v>9140.9458708333186</v>
       </c>
       <c r="K66" s="29">
-        <v>8300</v>
+        <v>8553.8754998076183</v>
       </c>
       <c r="L66" s="29">
-        <v>8091.9296361204651</v>
+        <v>8325.6783425377198</v>
       </c>
       <c r="M66" s="20">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="67" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D67" s="28">
-        <v>8695.9764326895511</v>
+        <v>8693.3134667720005</v>
       </c>
       <c r="E67" s="28">
-        <v>8727.2644687603315</v>
+        <v>8757.4563947870301</v>
       </c>
       <c r="F67" s="28">
-        <v>498.33807920677361</v>
+        <v>388.47089519663979</v>
       </c>
       <c r="G67" s="28">
-        <v>9818</v>
+        <v>9597</v>
       </c>
       <c r="H67" s="28">
-        <v>7493.3</v>
+        <v>8000</v>
       </c>
       <c r="I67" s="28">
-        <v>9228.9030423743261</v>
+        <v>9262.9553055632496</v>
       </c>
       <c r="J67" s="28">
-        <v>9020.4998407587809</v>
+        <v>9060.6139159745726</v>
       </c>
       <c r="K67" s="28">
-        <v>8500</v>
+        <v>8528</v>
       </c>
       <c r="L67" s="28">
-        <v>8215.7335432292093</v>
+        <v>8328.7973129273378</v>
       </c>
       <c r="M67" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="68" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B68" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C68" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D68" s="29">
-        <v>8612.5300344829539</v>
+        <v>8534.5912802010007</v>
       </c>
       <c r="E68" s="29">
-        <v>8674.3125885529844</v>
+        <v>8573.8589547260472</v>
       </c>
       <c r="F68" s="29">
-        <v>476.03647873913769</v>
+        <v>428.64457303111749</v>
       </c>
       <c r="G68" s="29">
-        <v>9953</v>
+        <v>9376</v>
       </c>
       <c r="H68" s="29">
-        <v>7560.3345619176498</v>
+        <v>7859</v>
       </c>
       <c r="I68" s="29">
-        <v>9173.6178549418401</v>
+        <v>9212.5741426171007</v>
       </c>
       <c r="J68" s="29">
-        <v>8960</v>
+        <v>8787.9473102278607</v>
       </c>
       <c r="K68" s="29">
-        <v>8412.5</v>
+        <v>8209</v>
       </c>
       <c r="L68" s="29">
-        <v>8116.1</v>
+        <v>8015.9374467171274</v>
       </c>
       <c r="M68" s="20">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="69" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B69" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D69" s="28">
-        <v>8435.0921981260126</v>
+        <v>8448</v>
       </c>
       <c r="E69" s="28">
-        <v>8503.8845523759719</v>
+        <v>8493.0978562160617</v>
       </c>
       <c r="F69" s="28">
-        <v>484.59694693560101</v>
+        <v>373.19678691121641</v>
       </c>
       <c r="G69" s="28">
-        <v>9577</v>
+        <v>9236.2730954833205</v>
       </c>
       <c r="H69" s="28">
-        <v>7335.0140597579848</v>
+        <v>7764</v>
       </c>
       <c r="I69" s="28">
-        <v>9145.8640021927094</v>
+        <v>9021.120133279026</v>
       </c>
       <c r="J69" s="28">
-        <v>8770.2774197305462</v>
+        <v>8698</v>
       </c>
       <c r="K69" s="28">
-        <v>8170.75</v>
+        <v>8220</v>
       </c>
       <c r="L69" s="28">
-        <v>7989.8</v>
+        <v>8000</v>
       </c>
       <c r="M69" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="70" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B70" s="17">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C70" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D70" s="29">
-        <v>8410.3967847878102</v>
+        <v>8073.028614038255</v>
       </c>
       <c r="E70" s="29">
-        <v>8429.5728913861531</v>
+        <v>8170.7557215339639</v>
       </c>
       <c r="F70" s="29">
-        <v>412.15816018529182</v>
+        <v>474.15207921559141</v>
       </c>
       <c r="G70" s="29">
-        <v>9406</v>
+        <v>9409</v>
       </c>
       <c r="H70" s="29">
-        <v>7803</v>
+        <v>7200</v>
       </c>
       <c r="I70" s="29">
-        <v>8912.1330076013619</v>
+        <v>8720</v>
       </c>
       <c r="J70" s="29">
-        <v>8609.9963131288005</v>
+        <v>8418</v>
       </c>
       <c r="K70" s="29">
-        <v>8126.8549759256148</v>
+        <v>7918</v>
       </c>
       <c r="L70" s="29">
-        <v>7981.2333885341859</v>
+        <v>7686.6735718697964</v>
       </c>
       <c r="M70" s="20">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="71" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B71" s="2">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D71" s="28">
-        <v>8078.6481414428572</v>
+        <v>8086</v>
       </c>
       <c r="E71" s="28">
-        <v>8170.5157479907302</v>
+        <v>8068.1394551233006</v>
       </c>
       <c r="F71" s="28">
-        <v>505.16691998431708</v>
+        <v>335.75819539874141</v>
       </c>
       <c r="G71" s="28">
-        <v>9429.3284039023511</v>
+        <v>8664.987100516626</v>
       </c>
       <c r="H71" s="28">
-        <v>7200</v>
+        <v>7497.72</v>
       </c>
       <c r="I71" s="28">
-        <v>8810.7729638596084</v>
+        <v>8501.2100080315777</v>
       </c>
       <c r="J71" s="28">
-        <v>8580.3559235344728</v>
+        <v>8310</v>
       </c>
       <c r="K71" s="28">
-        <v>7815.0482840534069</v>
+        <v>7820</v>
       </c>
       <c r="L71" s="28">
-        <v>7598.74</v>
+        <v>7631.4390491751137</v>
       </c>
       <c r="M71" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="72" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B72" s="21" t="s">
         <v>36</v>
       </c>
@@ -4084,37 +4049,37 @@
         <v>25</v>
       </c>
       <c r="D72" s="29">
-        <v>98547.427458653954</v>
+        <v>100000</v>
       </c>
       <c r="E72" s="29">
-        <v>98985.797245783891</v>
+        <v>100069.2109906307</v>
       </c>
       <c r="F72" s="29">
-        <v>2820.664404126976</v>
+        <v>2050.5076498295998</v>
       </c>
       <c r="G72" s="29">
-        <v>106474</v>
+        <v>104887</v>
       </c>
       <c r="H72" s="29">
-        <v>93721.9</v>
+        <v>96037.109413863567</v>
       </c>
       <c r="I72" s="29">
-        <v>102376.2000042204</v>
+        <v>102995.71551655031</v>
       </c>
       <c r="J72" s="29">
-        <v>100172.75</v>
+        <v>101130.9879394551</v>
       </c>
       <c r="K72" s="29">
-        <v>97330.975000000006</v>
+        <v>98575.973497176761</v>
       </c>
       <c r="L72" s="29">
-        <v>95701.245703975961</v>
+        <v>97574.815990814124</v>
       </c>
       <c r="M72" s="20">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="73" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B73" s="6" t="s">
         <v>37</v>
       </c>
@@ -4122,45 +4087,45 @@
         <v>25</v>
       </c>
       <c r="D73" s="28">
-        <v>102306.6979379249</v>
+        <v>104770.2894023418</v>
       </c>
       <c r="E73" s="28">
-        <v>102401.52622875159</v>
+        <v>104040.37238559419</v>
       </c>
       <c r="F73" s="28">
-        <v>4905.3034555946751</v>
+        <v>4663.1573469991527</v>
       </c>
       <c r="G73" s="28">
-        <v>115197</v>
+        <v>118021</v>
       </c>
       <c r="H73" s="28">
         <v>90160</v>
       </c>
       <c r="I73" s="28">
-        <v>107249.1129853865</v>
+        <v>108332.3287470568</v>
       </c>
       <c r="J73" s="28">
-        <v>105125.0046520645</v>
+        <v>105965.75</v>
       </c>
       <c r="K73" s="28">
-        <v>99984.813199177443</v>
+        <v>102033.95416274951</v>
       </c>
       <c r="L73" s="28">
-        <v>96448.146298848776</v>
+        <v>101184</v>
       </c>
       <c r="M73" s="5">
         <v>36</v>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B74" s="22"/>
       <c r="C74" s="23"/>
     </row>
-    <row r="75" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B75" s="22"/>
       <c r="C75" s="23"/>
     </row>
-    <row r="76" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B76" s="14" t="s">
         <v>26</v>
       </c>
@@ -4176,7 +4141,7 @@
       <c r="L76" s="14"/>
       <c r="M76" s="15"/>
     </row>
-    <row r="77" spans="2:13" ht="36" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B77" s="24" t="s">
         <v>1</v>
       </c>
@@ -4214,273 +4179,273 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B78" s="7">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D78" s="28">
-        <v>6787.5</v>
+        <v>6587</v>
       </c>
       <c r="E78" s="28">
-        <v>6801.8800917396666</v>
+        <v>6582.7052026004621</v>
       </c>
       <c r="F78" s="28">
-        <v>366.80555441053048</v>
+        <v>360.38605721351638</v>
       </c>
       <c r="G78" s="28">
-        <v>7899.0041821654322</v>
+        <v>7434.7146719178954</v>
       </c>
       <c r="H78" s="28">
-        <v>6153.5366676800004</v>
+        <v>6033</v>
       </c>
       <c r="I78" s="28">
-        <v>7130.4932564874161</v>
+        <v>6982.1223367240236</v>
       </c>
       <c r="J78" s="28">
-        <v>6981.7120813547408</v>
+        <v>6840</v>
       </c>
       <c r="K78" s="28">
-        <v>6618.0510212586551</v>
+        <v>6311.7345990605891</v>
       </c>
       <c r="L78" s="28">
-        <v>6312.6</v>
+        <v>6119.8226054775496</v>
       </c>
       <c r="M78" s="8">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="79" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B79" s="17">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C79" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D79" s="29">
-        <v>6870.2666475123697</v>
+        <v>7046.2659498395751</v>
       </c>
       <c r="E79" s="29">
-        <v>6864.1693592980864</v>
+        <v>6997.248510425834</v>
       </c>
       <c r="F79" s="29">
-        <v>323.79804022765421</v>
+        <v>451.91759935516791</v>
       </c>
       <c r="G79" s="29">
-        <v>7944.160146689559</v>
+        <v>8140.7397842558248</v>
       </c>
       <c r="H79" s="29">
-        <v>6203.5366676800004</v>
+        <v>6132.8437707900002</v>
       </c>
       <c r="I79" s="29">
-        <v>7197.2</v>
+        <v>7441.2179999999998</v>
       </c>
       <c r="J79" s="29">
-        <v>7042.835764664771</v>
+        <v>7238.2236093405272</v>
       </c>
       <c r="K79" s="29">
-        <v>6654.0095532853957</v>
+        <v>6674.1573223177484</v>
       </c>
       <c r="L79" s="29">
-        <v>6500</v>
+        <v>6480.3909011753503</v>
       </c>
       <c r="M79" s="20">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="80" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="80" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B80" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D80" s="28">
-        <v>7287.0197159904601</v>
+        <v>6904</v>
       </c>
       <c r="E80" s="28">
-        <v>7196.338671122413</v>
+        <v>6953.259180423096</v>
       </c>
       <c r="F80" s="28">
-        <v>406.33462273307168</v>
+        <v>441.70629217665658</v>
       </c>
       <c r="G80" s="28">
-        <v>8140.7397842558248</v>
+        <v>8415.3485722202822</v>
       </c>
       <c r="H80" s="28">
-        <v>6250</v>
+        <v>6182.8437707900002</v>
       </c>
       <c r="I80" s="28">
-        <v>7640.2726231107308</v>
+        <v>7518.6379999999999</v>
       </c>
       <c r="J80" s="28">
-        <v>7418.3850222423498</v>
+        <v>7094.6266382464592</v>
       </c>
       <c r="K80" s="28">
-        <v>7010.3910298164856</v>
+        <v>6657</v>
       </c>
       <c r="L80" s="28">
-        <v>6608.4</v>
+        <v>6496.1014953323784</v>
       </c>
       <c r="M80" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="81" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="81" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B81" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C81" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D81" s="29">
-        <v>7128.6649350210573</v>
+        <v>7077.0970267995899</v>
       </c>
       <c r="E81" s="29">
-        <v>7122.6303594794954</v>
+        <v>7062.7837416563443</v>
       </c>
       <c r="F81" s="29">
-        <v>379.63120045949302</v>
+        <v>554.59206254540686</v>
       </c>
       <c r="G81" s="29">
-        <v>8415.3485722202822</v>
+        <v>8553.938094788864</v>
       </c>
       <c r="H81" s="29">
-        <v>6303.5366676800004</v>
+        <v>5801.3762093660598</v>
       </c>
       <c r="I81" s="29">
-        <v>7565.8364461501878</v>
+        <v>7682.716609910618</v>
       </c>
       <c r="J81" s="29">
-        <v>7321.8453610065208</v>
+        <v>7309.6687908009317</v>
       </c>
       <c r="K81" s="29">
-        <v>6906.2559073758957</v>
+        <v>6740</v>
       </c>
       <c r="L81" s="29">
-        <v>6735.3</v>
+        <v>6449.1136674606159</v>
       </c>
       <c r="M81" s="20">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="82" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="82" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B82" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D82" s="28">
-        <v>7134.4776320438996</v>
+        <v>7014.84</v>
       </c>
       <c r="E82" s="28">
-        <v>7209.4144895657046</v>
+        <v>7039.2252289122698</v>
       </c>
       <c r="F82" s="28">
-        <v>439.86879841131628</v>
+        <v>534.80891853094272</v>
       </c>
       <c r="G82" s="28">
-        <v>8553.938094788864</v>
+        <v>8212.6032111168843</v>
       </c>
       <c r="H82" s="28">
-        <v>6595.5</v>
+        <v>5705.8326799021979</v>
       </c>
       <c r="I82" s="28">
-        <v>7754.0343837830824</v>
+        <v>7752.6393709749127</v>
       </c>
       <c r="J82" s="28">
-        <v>7408.5592601306744</v>
+        <v>7302.3271187853315</v>
       </c>
       <c r="K82" s="28">
-        <v>6898.8652200132092</v>
+        <v>6760</v>
       </c>
       <c r="L82" s="28">
-        <v>6736.0610003040001</v>
+        <v>6497.1698372361716</v>
       </c>
       <c r="M82" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="83" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="83" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B83" s="17">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C83" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D83" s="29">
-        <v>7149.484352991085</v>
+        <v>6538.8757896795451</v>
       </c>
       <c r="E83" s="29">
-        <v>7198.5738110353059</v>
+        <v>6585.1344942747064</v>
       </c>
       <c r="F83" s="29">
-        <v>477.07730727142052</v>
+        <v>537.31808315641251</v>
       </c>
       <c r="G83" s="29">
-        <v>8212.6032111168843</v>
+        <v>7976.571837667103</v>
       </c>
       <c r="H83" s="29">
-        <v>6200</v>
+        <v>5358.3417419697053</v>
       </c>
       <c r="I83" s="29">
-        <v>7872.3629959310138</v>
+        <v>7305.7439024337846</v>
       </c>
       <c r="J83" s="29">
-        <v>7435.3203080036137</v>
+        <v>6926.2276415778151</v>
       </c>
       <c r="K83" s="29">
-        <v>6906.7932051064472</v>
+        <v>6235</v>
       </c>
       <c r="L83" s="29">
-        <v>6701.9720195821892</v>
+        <v>5993.5559999999996</v>
       </c>
       <c r="M83" s="20">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="84" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="84" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B84" s="2">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D84" s="28">
-        <v>6713.8903255796376</v>
+        <v>6399</v>
       </c>
       <c r="E84" s="28">
-        <v>6783.9618342658487</v>
+        <v>6441.6363106451336</v>
       </c>
       <c r="F84" s="28">
-        <v>518.72631758468253</v>
+        <v>636.24718393389549</v>
       </c>
       <c r="G84" s="28">
-        <v>7976.571837667103</v>
+        <v>7921.1330656673963</v>
       </c>
       <c r="H84" s="28">
-        <v>5800</v>
+        <v>4918.2185989196932</v>
       </c>
       <c r="I84" s="28">
-        <v>7368.965982976224</v>
+        <v>7201.4924912387369</v>
       </c>
       <c r="J84" s="28">
-        <v>7196.8563179609637</v>
+        <v>6905</v>
       </c>
       <c r="K84" s="28">
-        <v>6384.0393330598527</v>
+        <v>5910.5051336928109</v>
       </c>
       <c r="L84" s="28">
-        <v>6247.6117656413526</v>
+        <v>5777.3828255072976</v>
       </c>
       <c r="M84" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="85" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="85" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B85" s="21" t="s">
         <v>36</v>
       </c>
@@ -4488,37 +4453,37 @@
         <v>25</v>
       </c>
       <c r="D85" s="29">
-        <v>78362.61</v>
+        <v>76400.020523973202</v>
       </c>
       <c r="E85" s="29">
-        <v>78441.592456605329</v>
+        <v>76337.996570649819</v>
       </c>
       <c r="F85" s="29">
-        <v>2437.1183279100328</v>
+        <v>2682.4399466879158</v>
       </c>
       <c r="G85" s="29">
-        <v>85759.314598151715</v>
+        <v>84743.605115298953</v>
       </c>
       <c r="H85" s="29">
-        <v>74367.989567624798</v>
+        <v>68978.521358499303</v>
       </c>
       <c r="I85" s="29">
-        <v>81172</v>
+        <v>78859.20168066943</v>
       </c>
       <c r="J85" s="29">
-        <v>80000</v>
+        <v>77662.409750000006</v>
       </c>
       <c r="K85" s="29">
-        <v>76751</v>
+        <v>74627.186419116348</v>
       </c>
       <c r="L85" s="29">
-        <v>75732.679573528934</v>
+        <v>73785.227401469005</v>
       </c>
       <c r="M85" s="20">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="86" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="86" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B86" s="6" t="s">
         <v>37</v>
       </c>
@@ -4526,13 +4491,13 @@
         <v>25</v>
       </c>
       <c r="D86" s="28">
-        <v>84719</v>
+        <v>82556.42</v>
       </c>
       <c r="E86" s="28">
-        <v>83596.923108813658</v>
+        <v>82330.790384260734</v>
       </c>
       <c r="F86" s="28">
-        <v>4235.3491657957529</v>
+        <v>4441.6093490856383</v>
       </c>
       <c r="G86" s="28">
         <v>94980.71444002421</v>
@@ -4541,22 +4506,22 @@
         <v>71250</v>
       </c>
       <c r="I86" s="28">
-        <v>87040</v>
+        <v>86761.061736059506</v>
       </c>
       <c r="J86" s="28">
-        <v>86422.738793264987</v>
+        <v>84863.112586677657</v>
       </c>
       <c r="K86" s="28">
-        <v>80622.073250065703</v>
+        <v>79850</v>
       </c>
       <c r="L86" s="28">
-        <v>79093.100000000006</v>
+        <v>76606.842554207658</v>
       </c>
       <c r="M86" s="5">
         <v>36</v>
       </c>
     </row>
-    <row r="87" spans="2:13" ht="18" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B87" s="9"/>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
@@ -4570,7 +4535,7 @@
       <c r="L87" s="10"/>
       <c r="M87" s="10"/>
     </row>
-    <row r="89" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B89" s="14" t="s">
         <v>27</v>
       </c>
@@ -4586,7 +4551,7 @@
       <c r="L89" s="14"/>
       <c r="M89" s="15"/>
     </row>
-    <row r="90" spans="2:13" ht="36" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B90" s="24" t="s">
         <v>1</v>
       </c>
@@ -4624,83 +4589,83 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B91" s="21" t="s">
         <v>36</v>
       </c>
       <c r="C91" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D91" s="44">
-        <v>16000</v>
-      </c>
-      <c r="E91" s="44">
-        <v>15524.56347684777</v>
-      </c>
-      <c r="F91" s="44">
-        <v>2066.9298497877039</v>
-      </c>
-      <c r="G91" s="44">
-        <v>19000</v>
-      </c>
-      <c r="H91" s="44">
+      <c r="D91" s="29">
+        <v>15700</v>
+      </c>
+      <c r="E91" s="29">
+        <v>15248.83473917421</v>
+      </c>
+      <c r="F91" s="29">
+        <v>2209.9209280276</v>
+      </c>
+      <c r="G91" s="29">
+        <v>21056</v>
+      </c>
+      <c r="H91" s="29">
         <v>9000</v>
       </c>
-      <c r="I91" s="44">
-        <v>17705.150000000001</v>
-      </c>
-      <c r="J91" s="44">
-        <v>16300</v>
-      </c>
-      <c r="K91" s="44">
-        <v>15164</v>
-      </c>
-      <c r="L91" s="44">
-        <v>12000</v>
+      <c r="I91" s="29">
+        <v>17260.2</v>
+      </c>
+      <c r="J91" s="29">
+        <v>16107.641742069851</v>
+      </c>
+      <c r="K91" s="29">
+        <v>15000</v>
+      </c>
+      <c r="L91" s="29">
+        <v>11948</v>
       </c>
       <c r="M91" s="20">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="92" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="92" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B92" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D92" s="45">
-        <v>19835.5</v>
-      </c>
-      <c r="E92" s="45">
-        <v>18798.664286237879</v>
-      </c>
-      <c r="F92" s="45">
-        <v>3511.8851070248588</v>
-      </c>
-      <c r="G92" s="45">
-        <v>24266</v>
-      </c>
-      <c r="H92" s="45">
+      <c r="D92" s="28">
+        <v>19729</v>
+      </c>
+      <c r="E92" s="28">
+        <v>18554.948196765119</v>
+      </c>
+      <c r="F92" s="28">
+        <v>3312.1495195548619</v>
+      </c>
+      <c r="G92" s="28">
+        <v>22451.67367882196</v>
+      </c>
+      <c r="H92" s="28">
         <v>5000</v>
       </c>
-      <c r="I92" s="45">
-        <v>21855.1</v>
-      </c>
-      <c r="J92" s="45">
-        <v>20732.538099787249</v>
-      </c>
-      <c r="K92" s="45">
-        <v>17976.674170680319</v>
-      </c>
-      <c r="L92" s="45">
-        <v>14979</v>
+      <c r="I92" s="28">
+        <v>21169.594796954789</v>
+      </c>
+      <c r="J92" s="28">
+        <v>20361.424999999999</v>
+      </c>
+      <c r="K92" s="28">
+        <v>17807.069676089519</v>
+      </c>
+      <c r="L92" s="28">
+        <v>15208.5</v>
       </c>
       <c r="M92" s="5">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="93" spans="2:13" ht="18" x14ac:dyDescent="0.4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="93" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B93" s="9"/>
       <c r="C93" s="10"/>
       <c r="D93" s="10"/>
@@ -4714,7 +4679,7 @@
       <c r="L93" s="10"/>
       <c r="M93" s="10"/>
     </row>
-    <row r="95" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B95" s="14" t="s">
         <v>29</v>
       </c>
@@ -4730,7 +4695,7 @@
       <c r="L95" s="14"/>
       <c r="M95" s="15"/>
     </row>
-    <row r="96" spans="2:13" ht="36" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B96" s="24" t="s">
         <v>1</v>
       </c>
@@ -4768,121 +4733,121 @@
         <v>12</v>
       </c>
     </row>
-    <row r="97" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B97" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D97" s="4">
-        <v>7.7</v>
+        <v>7.6834995908704036</v>
       </c>
       <c r="E97" s="4">
-        <v>7.7783924509982398</v>
+        <v>7.657402206971148</v>
       </c>
       <c r="F97" s="4">
-        <v>0.47919870345638288</v>
+        <v>0.2342179642805452</v>
       </c>
       <c r="G97" s="4">
-        <v>8.9</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="H97" s="4">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="I97" s="4">
-        <v>8.4</v>
+        <v>7.9555973741548778</v>
       </c>
       <c r="J97" s="4">
-        <v>8.0125000000000011</v>
+        <v>7.7984735317400302</v>
       </c>
       <c r="K97" s="4">
-        <v>7.5618627395104268</v>
+        <v>7.5</v>
       </c>
       <c r="L97" s="4">
-        <v>7.3000135547241616</v>
+        <v>7.4</v>
       </c>
       <c r="M97" s="8">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="98" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="98" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B98" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C98" s="18" t="s">
         <v>30</v>
       </c>
       <c r="D98" s="19">
-        <v>7.6144157093696974</v>
+        <v>7.3</v>
       </c>
       <c r="E98" s="19">
-        <v>7.6408730791881929</v>
+        <v>7.3043052515190752</v>
       </c>
       <c r="F98" s="19">
-        <v>0.47158800807001833</v>
+        <v>0.5015298063125514</v>
       </c>
       <c r="G98" s="19">
         <v>8.6</v>
       </c>
       <c r="H98" s="19">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="I98" s="19">
-        <v>8.1999999999999993</v>
+        <v>7.79</v>
       </c>
       <c r="J98" s="19">
-        <v>7.95</v>
+        <v>7.6025000000000009</v>
       </c>
       <c r="K98" s="19">
-        <v>7.4</v>
+        <v>6.9749999999999996</v>
       </c>
       <c r="L98" s="19">
-        <v>7.240860712125734</v>
+        <v>6.7549598581975454</v>
       </c>
       <c r="M98" s="20">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="99" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="99" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B99" s="6" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D99" s="4">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="E99" s="4">
-        <v>7.3444337703887896</v>
+        <v>7.5194996235506082</v>
       </c>
       <c r="F99" s="4">
-        <v>0.51182604381202779</v>
+        <v>0.3805533431159987</v>
       </c>
       <c r="G99" s="4">
-        <v>8.6</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="H99" s="4">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="I99" s="4">
         <v>7.8920000000000003</v>
       </c>
       <c r="J99" s="4">
-        <v>7.61</v>
+        <v>7.6998731732282089</v>
       </c>
       <c r="K99" s="4">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="L99" s="4">
-        <v>6.72</v>
+        <v>7.2</v>
       </c>
       <c r="M99" s="5">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="100" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="100" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B100" s="21" t="s">
         <v>36</v>
       </c>
@@ -4890,75 +4855,75 @@
         <v>31</v>
       </c>
       <c r="D100" s="19">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="E100" s="19">
-        <v>7.5177139255728322</v>
+        <v>7.5194996235506082</v>
       </c>
       <c r="F100" s="19">
-        <v>0.53580956182128403</v>
+        <v>0.3805533431159987</v>
       </c>
       <c r="G100" s="19">
-        <v>9</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="H100" s="19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I100" s="19">
-        <v>7.9369790615995601</v>
+        <v>7.8920000000000003</v>
       </c>
       <c r="J100" s="19">
-        <v>7.7752933646321072</v>
+        <v>7.6998731732282089</v>
       </c>
       <c r="K100" s="19">
+        <v>7.3</v>
+      </c>
+      <c r="L100" s="19">
         <v>7.2</v>
-      </c>
-      <c r="L100" s="19">
-        <v>7.0647901803843141</v>
       </c>
       <c r="M100" s="20">
         <v>35</v>
       </c>
     </row>
-    <row r="101" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B101" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D101" s="4">
-        <v>7.45</v>
+        <v>7.4</v>
       </c>
       <c r="E101" s="4">
-        <v>7.427346807100788</v>
+        <v>7.4671161354062674</v>
       </c>
       <c r="F101" s="4">
-        <v>0.84377627969781244</v>
+        <v>0.50336599234653123</v>
       </c>
       <c r="G101" s="4">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="H101" s="4">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="I101" s="4">
-        <v>8.1665985707465083</v>
+        <v>8.1132850532654395</v>
       </c>
       <c r="J101" s="4">
-        <v>7.875</v>
+        <v>7.9</v>
       </c>
       <c r="K101" s="4">
-        <v>6.85</v>
+        <v>7.2</v>
       </c>
       <c r="L101" s="4">
-        <v>6.53</v>
+        <v>6.8</v>
       </c>
       <c r="M101" s="5">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="102" spans="2:13" ht="18" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="102" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B102" s="9"/>
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
@@ -4972,7 +4937,7 @@
       <c r="L102" s="9"/>
       <c r="M102" s="9"/>
     </row>
-    <row r="104" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B104" s="14" t="s">
         <v>32</v>
       </c>
@@ -4988,7 +4953,7 @@
       <c r="L104" s="14"/>
       <c r="M104" s="15"/>
     </row>
-    <row r="105" spans="2:13" ht="36" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B105" s="24" t="s">
         <v>1</v>
       </c>
@@ -5026,121 +4991,121 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B106" s="21" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C106" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D106" s="19">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="E106" s="19">
-        <v>0.35353180863862799</v>
+        <v>0.59905001257264878</v>
       </c>
       <c r="F106" s="19">
-        <v>0.1568323317988054</v>
+        <v>0.44301653237672201</v>
       </c>
       <c r="G106" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="H106" s="19">
+        <v>-0.1</v>
+      </c>
+      <c r="I106" s="19">
+        <v>1.127877560947194</v>
+      </c>
+      <c r="J106" s="19">
         <v>0.9</v>
       </c>
-      <c r="H106" s="19">
-        <v>3.3411904423816812E-3</v>
-      </c>
-      <c r="I106" s="19">
-        <v>0.48699179999999992</v>
-      </c>
-      <c r="J106" s="19">
-        <v>0.35</v>
-      </c>
       <c r="K106" s="19">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L106" s="19">
-        <v>0.27811041591902869</v>
+        <v>0</v>
       </c>
       <c r="M106" s="20">
         <v>37</v>
       </c>
     </row>
-    <row r="107" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B107" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D107" s="4">
-        <v>1.2</v>
+        <v>0.85</v>
       </c>
       <c r="E107" s="4">
-        <v>1.238947685964475</v>
+        <v>0.90515638212672056</v>
       </c>
       <c r="F107" s="4">
-        <v>0.47070592611055001</v>
+        <v>0.46133043886260983</v>
       </c>
       <c r="G107" s="4">
-        <v>2.56</v>
+        <v>1.775788154885261</v>
       </c>
       <c r="H107" s="4">
-        <v>0.35</v>
+        <v>-0.2475404344179033</v>
       </c>
       <c r="I107" s="4">
-        <v>1.8080000000000001</v>
+        <v>1.54</v>
       </c>
       <c r="J107" s="4">
-        <v>1.58</v>
+        <v>1.2377583019893561</v>
       </c>
       <c r="K107" s="4">
-        <v>0.97</v>
+        <v>0.6</v>
       </c>
       <c r="L107" s="4">
-        <v>0.6</v>
+        <v>0.35399999999999998</v>
       </c>
       <c r="M107" s="5">
         <v>37</v>
       </c>
     </row>
-    <row r="108" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B108" s="21" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C108" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D108" s="19">
-        <v>0.90300413457693463</v>
+        <v>0.9</v>
       </c>
       <c r="E108" s="19">
-        <v>0.88938563675470617</v>
+        <v>0.80447436610126755</v>
       </c>
       <c r="F108" s="19">
-        <v>0.42473001721068793</v>
+        <v>0.38537918576876729</v>
       </c>
       <c r="G108" s="19">
-        <v>1.8116320229130569</v>
+        <v>1.507512499999963</v>
       </c>
       <c r="H108" s="19">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="I108" s="19">
-        <v>1.5026961600044431</v>
+        <v>1.2452808900705301</v>
       </c>
       <c r="J108" s="19">
-        <v>1.0352877878927911</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K108" s="19">
-        <v>0.66148243367194492</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L108" s="19">
-        <v>0.3</v>
+        <v>0.29487851523115821</v>
       </c>
       <c r="M108" s="20">
         <v>37</v>
       </c>
     </row>
-    <row r="109" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B109" s="6" t="s">
         <v>36</v>
       </c>
@@ -5148,37 +5113,37 @@
         <v>34</v>
       </c>
       <c r="D109" s="4">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="E109" s="4">
-        <v>2.894395202523917</v>
+        <v>2.9348817483542589</v>
       </c>
       <c r="F109" s="4">
-        <v>0.54940189466527445</v>
+        <v>0.41607582672382798</v>
       </c>
       <c r="G109" s="4">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H109" s="4">
-        <v>1.44</v>
+        <v>1.87</v>
       </c>
       <c r="I109" s="4">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J109" s="4">
-        <v>3.2</v>
+        <v>3.1709652178163461</v>
       </c>
       <c r="K109" s="4">
-        <v>2.5884106835734602</v>
+        <v>2.8</v>
       </c>
       <c r="L109" s="4">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="M109" s="5">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="110" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="110" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B110" s="21" t="s">
         <v>37</v>
       </c>
@@ -5186,75 +5151,75 @@
         <v>34</v>
       </c>
       <c r="D110" s="19">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="E110" s="19">
-        <v>3.0804368731004872</v>
+        <v>2.9265634044282609</v>
       </c>
       <c r="F110" s="19">
-        <v>0.64702325946469508</v>
+        <v>0.54276526538865544</v>
       </c>
       <c r="G110" s="19">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="H110" s="19">
         <v>1.9</v>
       </c>
       <c r="I110" s="19">
-        <v>4.01</v>
+        <v>3.551000000000001</v>
       </c>
       <c r="J110" s="19">
-        <v>3.5</v>
+        <v>3.212810794104509</v>
       </c>
       <c r="K110" s="19">
-        <v>2.6749999999999998</v>
+        <v>2.557909812012555</v>
       </c>
       <c r="L110" s="19">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="M110" s="20">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="111" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="111" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B111" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D111" s="4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="E111" s="4">
-        <v>3.198502000870973</v>
+        <v>3.0999377597044901</v>
       </c>
       <c r="F111" s="4">
-        <v>0.55147904528444192</v>
+        <v>0.64938227513159175</v>
       </c>
       <c r="G111" s="4">
         <v>5</v>
       </c>
       <c r="H111" s="4">
-        <v>2.1675200533491261</v>
+        <v>2</v>
       </c>
       <c r="I111" s="4">
-        <v>3.91</v>
+        <v>3.77</v>
       </c>
       <c r="J111" s="4">
         <v>3.5</v>
       </c>
       <c r="K111" s="4">
-        <v>3</v>
+        <v>2.754418346441839</v>
       </c>
       <c r="L111" s="4">
-        <v>2.5739077412264368</v>
+        <v>2.2396837053027441</v>
       </c>
       <c r="M111" s="5">
         <v>34</v>
       </c>
     </row>
-    <row r="112" spans="2:13" ht="18" x14ac:dyDescent="0.4">
+    <row r="112" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B112" s="9" t="s">
         <v>51</v>
       </c>
@@ -5284,24 +5249,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A6659E5-89E1-4C5B-8121-B7733FE1BDE9}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{130CD0D4-3FB8-4B56-A8AD-D1A48CBBBA0B}">
+  <sheetPr codeName="Hoja3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:M98"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.54296875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.81640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.1796875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.453125" style="1" customWidth="1"/>
-    <col min="6" max="7" width="14.453125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.453125" style="1" customWidth="1"/>
-    <col min="9" max="12" width="14.453125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="18.453125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" style="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="14.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="18.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="11" t="s">
         <v>52</v>
       </c>
@@ -5317,25 +5282,25 @@
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
     </row>
-    <row r="3" spans="2:13" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="L4" s="12"/>
       <c r="M4" s="13"/>
     </row>
-    <row r="5" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
         <v>0</v>
       </c>
@@ -5351,7 +5316,7 @@
       <c r="L5" s="14"/>
       <c r="M5" s="15"/>
     </row>
-    <row r="6" spans="2:13" ht="36" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B6" s="16" t="s">
         <v>1</v>
       </c>
@@ -5389,311 +5354,311 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B7" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="4">
-        <v>2.3166749617657398</v>
+        <v>1.9490078178879839</v>
       </c>
       <c r="E7" s="4">
-        <v>2.3250000000000002</v>
+        <v>1.9400390894399191</v>
       </c>
       <c r="F7" s="4">
-        <v>0.12521983662858119</v>
+        <v>7.1092298929169614E-2</v>
       </c>
       <c r="G7" s="4">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="H7" s="4">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="I7" s="4">
-        <v>2.4550000000000001</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="J7" s="4">
-        <v>2.4</v>
+        <v>1.99</v>
       </c>
       <c r="K7" s="4">
-        <v>2.2316874044143491</v>
+        <v>1.9</v>
       </c>
       <c r="L7" s="4">
-        <v>2.19</v>
+        <v>1.895</v>
       </c>
       <c r="M7" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B8" s="31">
-        <v>46203</v>
-      </c>
-      <c r="C8" s="32" t="s">
+    <row r="8" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="17">
+        <v>46234</v>
+      </c>
+      <c r="C8" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="33">
-        <v>2.1639424403015881</v>
-      </c>
-      <c r="E8" s="33">
-        <v>2.1850000000000001</v>
-      </c>
-      <c r="F8" s="33">
-        <v>0.1566716221183185</v>
-      </c>
-      <c r="G8" s="33">
-        <v>2.4</v>
-      </c>
-      <c r="H8" s="33">
+      <c r="D8" s="19">
+        <v>1.9687975648281439</v>
+      </c>
+      <c r="E8" s="19">
+        <v>1.9750000000000001</v>
+      </c>
+      <c r="F8" s="19">
+        <v>0.17195619139879259</v>
+      </c>
+      <c r="G8" s="19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H8" s="19">
+        <v>1.78</v>
+      </c>
+      <c r="I8" s="19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J8" s="19">
+        <v>2.1184817362110828</v>
+      </c>
+      <c r="K8" s="19">
         <v>1.8</v>
       </c>
-      <c r="I8" s="33">
-        <v>2.31</v>
-      </c>
-      <c r="J8" s="33">
-        <v>2.2149999999999999</v>
-      </c>
-      <c r="K8" s="33">
-        <v>2.1124999999999998</v>
-      </c>
-      <c r="L8" s="33">
-        <v>2.0694819627142902</v>
-      </c>
-      <c r="M8" s="34">
+      <c r="L8" s="19">
+        <v>1.798</v>
+      </c>
+      <c r="M8" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="4">
-        <v>2.1432803027806382</v>
+        <v>1.7683431734163499</v>
       </c>
       <c r="E9" s="4">
-        <v>2.151401513903191</v>
+        <v>1.8</v>
       </c>
       <c r="F9" s="4">
-        <v>0.18612302110791801</v>
+        <v>0.27016217044134699</v>
       </c>
       <c r="G9" s="4">
-        <v>2.4</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H9" s="4">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="I9" s="4">
-        <v>2.4</v>
+        <v>1.997088560747148</v>
       </c>
       <c r="J9" s="4">
-        <v>2.2374999999999998</v>
+        <v>1.8875</v>
       </c>
       <c r="K9" s="4">
-        <v>2.0299999999999998</v>
+        <v>1.5575000000000001</v>
       </c>
       <c r="L9" s="4">
-        <v>1.98</v>
+        <v>1.486</v>
       </c>
       <c r="M9" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B10" s="31">
-        <v>46265</v>
-      </c>
-      <c r="C10" s="32" t="s">
+    <row r="10" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="17">
+        <v>46295</v>
+      </c>
+      <c r="C10" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="33">
-        <v>1.9162296469283919</v>
-      </c>
-      <c r="E10" s="33">
-        <v>1.9450000000000001</v>
-      </c>
-      <c r="F10" s="33">
-        <v>0.22412211022352951</v>
-      </c>
-      <c r="G10" s="33">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="H10" s="33">
+      <c r="D10" s="19">
+        <v>1.800998995955652</v>
+      </c>
+      <c r="E10" s="19">
+        <v>1.854994979778261</v>
+      </c>
+      <c r="F10" s="19">
+        <v>0.22605009554768341</v>
+      </c>
+      <c r="G10" s="19">
+        <v>2.12</v>
+      </c>
+      <c r="H10" s="19">
         <v>1.5</v>
       </c>
-      <c r="I10" s="33">
-        <v>2.12</v>
-      </c>
-      <c r="J10" s="33">
-        <v>2.0092223519629391</v>
-      </c>
-      <c r="K10" s="33">
-        <v>1.825</v>
-      </c>
-      <c r="L10" s="33">
-        <v>1.6439999999999999</v>
-      </c>
-      <c r="M10" s="34">
+      <c r="I10" s="19">
+        <v>2.012</v>
+      </c>
+      <c r="J10" s="19">
+        <v>1.9875</v>
+      </c>
+      <c r="K10" s="19">
+        <v>1.6</v>
+      </c>
+      <c r="L10" s="19">
+        <v>1.5269999999999999</v>
+      </c>
+      <c r="M10" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="4">
-        <v>1.9414724421693259</v>
+        <v>1.6861327619079209</v>
       </c>
       <c r="E11" s="4">
-        <v>2</v>
+        <v>1.7050000000000001</v>
       </c>
       <c r="F11" s="4">
-        <v>0.28248581175826082</v>
+        <v>0.2093683667094963</v>
       </c>
       <c r="G11" s="4">
-        <v>2.4900000000000002</v>
+        <v>1.9413276190792159</v>
       </c>
       <c r="H11" s="4">
+        <v>1.36</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1.904132761907922</v>
+      </c>
+      <c r="J11" s="4">
+        <v>1.8875</v>
+      </c>
+      <c r="K11" s="4">
         <v>1.5</v>
       </c>
-      <c r="I11" s="4">
-        <v>2.13</v>
-      </c>
-      <c r="J11" s="4">
-        <v>2.0449999999999999</v>
-      </c>
-      <c r="K11" s="4">
-        <v>1.7686811054233149</v>
-      </c>
       <c r="L11" s="4">
-        <v>1.59</v>
+        <v>1.486</v>
       </c>
       <c r="M11" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B12" s="31">
-        <v>46326</v>
-      </c>
-      <c r="C12" s="32" t="s">
+    <row r="12" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="17">
+        <v>46356</v>
+      </c>
+      <c r="C12" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="33">
-        <v>1.8292414000706381</v>
-      </c>
-      <c r="E12" s="33">
-        <v>1.9</v>
-      </c>
-      <c r="F12" s="33">
-        <v>0.2147144959400355</v>
-      </c>
-      <c r="G12" s="33">
-        <v>2.1</v>
-      </c>
-      <c r="H12" s="33">
-        <v>1.5</v>
-      </c>
-      <c r="I12" s="33">
-        <v>2.012172600635743</v>
-      </c>
-      <c r="J12" s="33">
-        <v>1.9524999999999999</v>
-      </c>
-      <c r="K12" s="33">
-        <v>1.675</v>
-      </c>
-      <c r="L12" s="33">
-        <v>1.5</v>
-      </c>
-      <c r="M12" s="34">
+      <c r="D12" s="19">
+        <v>1.6248937462650279</v>
+      </c>
+      <c r="E12" s="19">
+        <v>1.6644687313251421</v>
+      </c>
+      <c r="F12" s="19">
+        <v>0.19477276881410549</v>
+      </c>
+      <c r="G12" s="19">
+        <v>1.8</v>
+      </c>
+      <c r="H12" s="19">
+        <v>1.19</v>
+      </c>
+      <c r="I12" s="19">
+        <v>1.8</v>
+      </c>
+      <c r="J12" s="19">
+        <v>1.7875000000000001</v>
+      </c>
+      <c r="K12" s="19">
+        <v>1.52</v>
+      </c>
+      <c r="L12" s="19">
+        <v>1.4690000000000001</v>
+      </c>
+      <c r="M12" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B13" s="2">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="4">
-        <v>1.754218848942892</v>
+        <v>1.782162125705923</v>
       </c>
       <c r="E13" s="4">
-        <v>1.8</v>
+        <v>1.7749999999999999</v>
       </c>
       <c r="F13" s="4">
-        <v>0.15171541780132899</v>
+        <v>0.40257046021018389</v>
       </c>
       <c r="G13" s="4">
-        <v>1.99</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="H13" s="4">
-        <v>1.5</v>
+        <v>1.06</v>
       </c>
       <c r="I13" s="4">
-        <v>1.873</v>
+        <v>2.1349999999999998</v>
       </c>
       <c r="J13" s="4">
-        <v>1.8</v>
+        <v>2.0750000000000002</v>
       </c>
       <c r="K13" s="4">
-        <v>1.7280471223572309</v>
+        <v>1.5404053142648091</v>
       </c>
       <c r="L13" s="4">
-        <v>1.5</v>
+        <v>1.3660000000000001</v>
       </c>
       <c r="M13" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B14" s="31" t="s">
+    <row r="14" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="33">
-        <v>23.71390436671474</v>
-      </c>
-      <c r="E14" s="33">
-        <v>23.71975046109894</v>
-      </c>
-      <c r="F14" s="33">
-        <v>1.4978791200080701</v>
-      </c>
-      <c r="G14" s="33">
-        <v>25.99</v>
-      </c>
-      <c r="H14" s="33">
-        <v>21.57</v>
-      </c>
-      <c r="I14" s="33">
-        <v>25.198</v>
-      </c>
-      <c r="J14" s="33">
-        <v>24.907385686237379</v>
-      </c>
-      <c r="K14" s="33">
-        <v>22.35</v>
-      </c>
-      <c r="L14" s="33">
-        <v>21.957000000000001</v>
-      </c>
-      <c r="M14" s="34">
+      <c r="C14" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="19">
+        <v>22.259142582968028</v>
+      </c>
+      <c r="E14" s="19">
+        <v>22.544601408409751</v>
+      </c>
+      <c r="F14" s="19">
+        <v>2.0360743030345021</v>
+      </c>
+      <c r="G14" s="19">
+        <v>25.02319267747275</v>
+      </c>
+      <c r="H14" s="19">
+        <v>18</v>
+      </c>
+      <c r="I14" s="19">
+        <v>24.462319267747269</v>
+      </c>
+      <c r="J14" s="19">
+        <v>23.374272751541049</v>
+      </c>
+      <c r="K14" s="19">
+        <v>21.285</v>
+      </c>
+      <c r="L14" s="19">
+        <v>20.25</v>
+      </c>
+      <c r="M14" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>36</v>
       </c>
@@ -5701,37 +5666,37 @@
         <v>16</v>
       </c>
       <c r="D15" s="4">
-        <v>31.501639848987189</v>
+        <v>29.974791789561301</v>
       </c>
       <c r="E15" s="4">
-        <v>31.95</v>
+        <v>30.245000000000001</v>
       </c>
       <c r="F15" s="4">
-        <v>1.2845886054396241</v>
+        <v>1.523546164158287</v>
       </c>
       <c r="G15" s="4">
-        <v>32.79</v>
+        <v>32.185246601537877</v>
       </c>
       <c r="H15" s="4">
-        <v>29</v>
+        <v>27.03</v>
       </c>
       <c r="I15" s="4">
-        <v>32.595281359429343</v>
+        <v>31.568524660153791</v>
       </c>
       <c r="J15" s="4">
-        <v>32.482500000000002</v>
+        <v>30.742003470556359</v>
       </c>
       <c r="K15" s="4">
-        <v>30.74068813373761</v>
+        <v>29.234999999999999</v>
       </c>
       <c r="L15" s="4">
-        <v>29.81</v>
+        <v>28.155000000000001</v>
       </c>
       <c r="M15" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="14" t="s">
         <v>18</v>
       </c>
@@ -5747,7 +5712,7 @@
       <c r="L18" s="14"/>
       <c r="M18" s="15"/>
     </row>
-    <row r="19" spans="2:13" ht="36" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B19" s="16" t="s">
         <v>1</v>
       </c>
@@ -5785,311 +5750,311 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B20" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="4">
-        <v>2.2763503270134602</v>
+        <v>1.948064249045719</v>
       </c>
       <c r="E20" s="4">
-        <v>2.335</v>
+        <v>1.906738866343155</v>
       </c>
       <c r="F20" s="4">
-        <v>0.17270671451539571</v>
+        <v>0.16257906350735879</v>
       </c>
       <c r="G20" s="4">
-        <v>2.5</v>
+        <v>2.205000000000001</v>
       </c>
       <c r="H20" s="4">
+        <v>1.68216475777088</v>
+      </c>
+      <c r="I20" s="4">
+        <v>2.2004999999999999</v>
+      </c>
+      <c r="J20" s="4">
         <v>2</v>
       </c>
-      <c r="I20" s="4">
-        <v>2.41</v>
-      </c>
-      <c r="J20" s="4">
-        <v>2.3975</v>
-      </c>
       <c r="K20" s="4">
-        <v>2.1976274526009481</v>
+        <v>1.885</v>
       </c>
       <c r="L20" s="4">
-        <v>2</v>
+        <v>1.788216475777088</v>
       </c>
       <c r="M20" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B21" s="31">
-        <v>46203</v>
-      </c>
-      <c r="C21" s="32" t="s">
+    <row r="21" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="17">
+        <v>46234</v>
+      </c>
+      <c r="C21" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="33">
-        <v>2.166947777961441</v>
-      </c>
-      <c r="E21" s="33">
-        <v>2.1572388898072039</v>
-      </c>
-      <c r="F21" s="33">
-        <v>0.17673412434213151</v>
-      </c>
-      <c r="G21" s="33">
-        <v>2.4900000000000002</v>
-      </c>
-      <c r="H21" s="33">
+      <c r="D21" s="19">
+        <v>1.9783629770519779</v>
+      </c>
+      <c r="E21" s="19">
+        <v>1.9650000000000001</v>
+      </c>
+      <c r="F21" s="19">
+        <v>0.19205183206256071</v>
+      </c>
+      <c r="G21" s="19">
+        <v>2.31</v>
+      </c>
+      <c r="H21" s="19">
+        <v>1.5936297705197799</v>
+      </c>
+      <c r="I21" s="19">
+        <v>2.2109999999999999</v>
+      </c>
+      <c r="J21" s="19">
+        <v>2.0375000000000001</v>
+      </c>
+      <c r="K21" s="19">
         <v>1.9</v>
       </c>
-      <c r="I21" s="33">
-        <v>2.4089999999999998</v>
-      </c>
-      <c r="J21" s="33">
-        <v>2.2037499999999999</v>
-      </c>
-      <c r="K21" s="33">
-        <v>2.0649999999999999</v>
-      </c>
-      <c r="L21" s="33">
-        <v>1.99</v>
-      </c>
-      <c r="M21" s="34">
+      <c r="L21" s="19">
+        <v>1.869362977051978</v>
+      </c>
+      <c r="M21" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B22" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="4">
-        <v>2.1337306112672239</v>
+        <v>1.8578629770519779</v>
       </c>
       <c r="E22" s="4">
-        <v>2.0536530563361231</v>
+        <v>1.82</v>
       </c>
       <c r="F22" s="4">
-        <v>0.21671771306294679</v>
+        <v>0.2164954273272664</v>
       </c>
       <c r="G22" s="4">
-        <v>2.52</v>
+        <v>2.415</v>
       </c>
       <c r="H22" s="4">
-        <v>1.88</v>
+        <v>1.5936297705197799</v>
       </c>
       <c r="I22" s="4">
-        <v>2.4119999999999999</v>
+        <v>1.9515</v>
       </c>
       <c r="J22" s="4">
-        <v>2.2725</v>
+        <v>1.8875</v>
       </c>
       <c r="K22" s="4">
-        <v>2</v>
+        <v>1.7849999999999999</v>
       </c>
       <c r="L22" s="4">
-        <v>1.8979999999999999</v>
+        <v>1.689362977051978</v>
       </c>
       <c r="M22" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B23" s="31">
-        <v>46265</v>
-      </c>
-      <c r="C23" s="32" t="s">
+    <row r="23" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="17">
+        <v>46295</v>
+      </c>
+      <c r="C23" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="33">
-        <v>1.9795210195771411</v>
-      </c>
-      <c r="E23" s="33">
-        <v>1.980105097885704</v>
-      </c>
-      <c r="F23" s="33">
-        <v>0.18518067870033059</v>
-      </c>
-      <c r="G23" s="33">
-        <v>2.415</v>
-      </c>
-      <c r="H23" s="33">
+      <c r="D23" s="19">
+        <v>1.773862977051978</v>
+      </c>
+      <c r="E23" s="19">
+        <v>1.74</v>
+      </c>
+      <c r="F23" s="19">
+        <v>0.15106372162834841</v>
+      </c>
+      <c r="G23" s="19">
+        <v>2</v>
+      </c>
+      <c r="H23" s="19">
+        <v>1.55</v>
+      </c>
+      <c r="I23" s="19">
+        <v>1.9550000000000001</v>
+      </c>
+      <c r="J23" s="19">
+        <v>1.8912500000000001</v>
+      </c>
+      <c r="K23" s="19">
         <v>1.7</v>
       </c>
-      <c r="I23" s="33">
-        <v>2.0775000000000001</v>
-      </c>
-      <c r="J23" s="33">
-        <v>2</v>
-      </c>
-      <c r="K23" s="33">
-        <v>1.93</v>
-      </c>
-      <c r="L23" s="33">
-        <v>1.79</v>
-      </c>
-      <c r="M23" s="34">
+      <c r="L23" s="19">
+        <v>1.589266793467802</v>
+      </c>
+      <c r="M23" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B24" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="4">
-        <v>1.8761678666405699</v>
+        <v>1.7249293765420219</v>
       </c>
       <c r="E24" s="4">
-        <v>1.9208393332028491</v>
+        <v>1.7</v>
       </c>
       <c r="F24" s="4">
-        <v>0.13591558059191691</v>
+        <v>0.1171597255307667</v>
       </c>
       <c r="G24" s="4">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="H24" s="4">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="I24" s="4">
-        <v>2.0059999999999998</v>
+        <v>1.855</v>
       </c>
       <c r="J24" s="4">
-        <v>1.9875</v>
+        <v>1.827687499999999</v>
       </c>
       <c r="K24" s="4">
-        <v>1.7524999999999999</v>
+        <v>1.6417828240651651</v>
       </c>
       <c r="L24" s="4">
-        <v>1.7</v>
+        <v>1.595</v>
       </c>
       <c r="M24" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B25" s="31">
-        <v>46326</v>
-      </c>
-      <c r="C25" s="32" t="s">
+    <row r="25" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B25" s="17">
+        <v>46356</v>
+      </c>
+      <c r="C25" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="33">
-        <v>1.8345426866444841</v>
-      </c>
-      <c r="E25" s="33">
-        <v>1.8525</v>
-      </c>
-      <c r="F25" s="33">
-        <v>0.13815393326838971</v>
-      </c>
-      <c r="G25" s="33">
-        <v>2.02</v>
-      </c>
-      <c r="H25" s="33">
-        <v>1.66</v>
-      </c>
-      <c r="I25" s="33">
-        <v>2.0019999999999998</v>
-      </c>
-      <c r="J25" s="33">
-        <v>1.945106716611211</v>
-      </c>
-      <c r="K25" s="33">
-        <v>1.7</v>
-      </c>
-      <c r="L25" s="33">
-        <v>1.696</v>
-      </c>
-      <c r="M25" s="34">
+      <c r="D25" s="19">
+        <v>1.6655057283268679</v>
+      </c>
+      <c r="E25" s="19">
+        <v>1.7050000000000001</v>
+      </c>
+      <c r="F25" s="19">
+        <v>0.13131017017933519</v>
+      </c>
+      <c r="G25" s="19">
+        <v>1.809962499999999</v>
+      </c>
+      <c r="H25" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="I25" s="19">
+        <v>1.8009962500000001</v>
+      </c>
+      <c r="J25" s="19">
+        <v>1.7875000000000001</v>
+      </c>
+      <c r="K25" s="19">
+        <v>1.523821087451511</v>
+      </c>
+      <c r="L25" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="M25" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B26" s="2">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="4">
-        <v>1.7955362836478119</v>
+        <v>1.8145632882770879</v>
       </c>
       <c r="E26" s="4">
-        <v>1.8</v>
+        <v>1.7649999999999999</v>
       </c>
       <c r="F26" s="4">
-        <v>0.14876269423172561</v>
+        <v>0.1313698066096009</v>
       </c>
       <c r="G26" s="4">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H26" s="4">
-        <v>1.55</v>
+        <v>1.68216475777088</v>
       </c>
       <c r="I26" s="4">
-        <v>2.0019999999999998</v>
+        <v>2</v>
       </c>
       <c r="J26" s="4">
-        <v>1.8640221273585871</v>
+        <v>1.94336703125</v>
       </c>
       <c r="K26" s="4">
-        <v>1.7024999999999999</v>
+        <v>1.7124999999999999</v>
       </c>
       <c r="L26" s="4">
-        <v>1.64</v>
+        <v>1.6982164757770879</v>
       </c>
       <c r="M26" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B27" s="31" t="s">
+    <row r="27" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B27" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" s="33">
-        <v>24.27345326223276</v>
-      </c>
-      <c r="E27" s="33">
-        <v>24.51</v>
-      </c>
-      <c r="F27" s="33">
-        <v>1.0675748050244691</v>
-      </c>
-      <c r="G27" s="33">
-        <v>25.8</v>
-      </c>
-      <c r="H27" s="33">
-        <v>22.42</v>
-      </c>
-      <c r="I27" s="33">
-        <v>25.62</v>
-      </c>
-      <c r="J27" s="33">
-        <v>24.827606857227181</v>
-      </c>
-      <c r="K27" s="33">
-        <v>23.443505714028479</v>
-      </c>
-      <c r="L27" s="33">
-        <v>23.302</v>
-      </c>
-      <c r="M27" s="34">
+      <c r="C27" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="19">
+        <v>22.724355533511709</v>
+      </c>
+      <c r="E27" s="19">
+        <v>22.093718925768979</v>
+      </c>
+      <c r="F27" s="19">
+        <v>1.741925570083982</v>
+      </c>
+      <c r="G27" s="19">
+        <v>26.61</v>
+      </c>
+      <c r="H27" s="19">
+        <v>20.74</v>
+      </c>
+      <c r="I27" s="19">
+        <v>24.260999999999999</v>
+      </c>
+      <c r="J27" s="19">
+        <v>23.57270090459329</v>
+      </c>
+      <c r="K27" s="19">
+        <v>21.822295736030341</v>
+      </c>
+      <c r="L27" s="19">
+        <v>20.974</v>
+      </c>
+      <c r="M27" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
         <v>36</v>
       </c>
@@ -6097,41 +6062,41 @@
         <v>16</v>
       </c>
       <c r="D28" s="4">
-        <v>30.783551490047369</v>
+        <v>29.126677433279959</v>
       </c>
       <c r="E28" s="4">
-        <v>30.789621447073351</v>
+        <v>29.02</v>
       </c>
       <c r="F28" s="4">
-        <v>0.94062909037821307</v>
+        <v>1.072540698728097</v>
       </c>
       <c r="G28" s="4">
-        <v>32.4</v>
+        <v>31.12817292329089</v>
       </c>
       <c r="H28" s="4">
-        <v>28.9</v>
+        <v>27.25237170981303</v>
       </c>
       <c r="I28" s="4">
-        <v>31.6136448056943</v>
+        <v>30.29281729232909</v>
       </c>
       <c r="J28" s="4">
-        <v>31.31</v>
+        <v>29.562172274771779</v>
       </c>
       <c r="K28" s="4">
-        <v>30.4925</v>
+        <v>28.762499999999999</v>
       </c>
       <c r="L28" s="4">
-        <v>29.89</v>
+        <v>27.9972371709813</v>
       </c>
       <c r="M28" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B30" s="22"/>
       <c r="C30" s="23"/>
     </row>
-    <row r="31" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="14" t="s">
         <v>35</v>
       </c>
@@ -6147,7 +6112,7 @@
       <c r="L31" s="14"/>
       <c r="M31" s="15"/>
     </row>
-    <row r="32" spans="2:13" ht="36" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B32" s="24" t="s">
         <v>1</v>
       </c>
@@ -6185,273 +6150,273 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B33" s="31">
-        <v>46203</v>
-      </c>
-      <c r="C33" s="32" t="s">
+    <row r="33" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B33" s="17">
+        <v>46234</v>
+      </c>
+      <c r="C33" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="46">
-        <v>22.24277272727273</v>
-      </c>
-      <c r="E33" s="46">
-        <v>22.40886363636363</v>
-      </c>
-      <c r="F33" s="46">
-        <v>0.90656589868036486</v>
-      </c>
-      <c r="G33" s="33">
-        <v>23.2</v>
-      </c>
-      <c r="H33" s="33">
-        <v>20.41</v>
-      </c>
-      <c r="I33" s="33">
-        <v>23.11</v>
-      </c>
-      <c r="J33" s="33">
-        <v>22.95</v>
-      </c>
-      <c r="K33" s="33">
-        <v>22</v>
-      </c>
-      <c r="L33" s="33">
-        <v>21.030999999999999</v>
-      </c>
-      <c r="M33" s="34">
+      <c r="D33" s="27">
+        <v>22.77200511508952</v>
+      </c>
+      <c r="E33" s="27">
+        <v>22.680025575447569</v>
+      </c>
+      <c r="F33" s="27">
+        <v>0.58112424991507838</v>
+      </c>
+      <c r="G33" s="27">
+        <v>24</v>
+      </c>
+      <c r="H33" s="27">
+        <v>22.06</v>
+      </c>
+      <c r="I33" s="27">
+        <v>23.37</v>
+      </c>
+      <c r="J33" s="27">
+        <v>23</v>
+      </c>
+      <c r="K33" s="27">
+        <v>22.35</v>
+      </c>
+      <c r="L33" s="27">
+        <v>22.186</v>
+      </c>
+      <c r="M33" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B34" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="26">
-        <v>22.402999999999999</v>
+        <v>23.007054739102099</v>
       </c>
       <c r="E34" s="26">
-        <v>22.19</v>
+        <v>22.93</v>
       </c>
       <c r="F34" s="26">
-        <v>1.17900193195582</v>
-      </c>
-      <c r="G34" s="4">
-        <v>24.2</v>
-      </c>
-      <c r="H34" s="4">
-        <v>20.5</v>
-      </c>
-      <c r="I34" s="4">
-        <v>23.795000000000002</v>
-      </c>
-      <c r="J34" s="4">
-        <v>23.324999999999999</v>
-      </c>
-      <c r="K34" s="4">
-        <v>21.925000000000001</v>
-      </c>
-      <c r="L34" s="4">
-        <v>20.95</v>
+        <v>0.78268684599607674</v>
+      </c>
+      <c r="G34" s="26">
+        <v>24.378782685138638</v>
+      </c>
+      <c r="H34" s="26">
+        <v>22</v>
+      </c>
+      <c r="I34" s="26">
+        <v>23.857878268513861</v>
+      </c>
+      <c r="J34" s="26">
+        <v>23.6</v>
+      </c>
+      <c r="K34" s="26">
+        <v>22.35794117647059</v>
+      </c>
+      <c r="L34" s="26">
+        <v>22.18</v>
       </c>
       <c r="M34" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B35" s="31">
-        <v>46265</v>
-      </c>
-      <c r="C35" s="32" t="s">
+    <row r="35" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B35" s="17">
+        <v>46295</v>
+      </c>
+      <c r="C35" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D35" s="46">
-        <v>22.582000000000001</v>
-      </c>
-      <c r="E35" s="46">
-        <v>22.53</v>
-      </c>
-      <c r="F35" s="46">
-        <v>1.8731423390181059</v>
-      </c>
-      <c r="G35" s="33">
-        <v>25.26</v>
-      </c>
-      <c r="H35" s="33">
-        <v>19.8</v>
-      </c>
-      <c r="I35" s="33">
-        <v>24.756</v>
-      </c>
-      <c r="J35" s="33">
-        <v>24</v>
-      </c>
-      <c r="K35" s="33">
-        <v>21.125</v>
-      </c>
-      <c r="L35" s="33">
-        <v>20.43</v>
-      </c>
-      <c r="M35" s="34">
+      <c r="D35" s="27">
+        <v>23.30091813575854</v>
+      </c>
+      <c r="E35" s="27">
+        <v>23.15</v>
+      </c>
+      <c r="F35" s="27">
+        <v>1.3153656147975941</v>
+      </c>
+      <c r="G35" s="27">
+        <v>25.717416651703079</v>
+      </c>
+      <c r="H35" s="27">
+        <v>21.5</v>
+      </c>
+      <c r="I35" s="27">
+        <v>24.67574166517031</v>
+      </c>
+      <c r="J35" s="27">
+        <v>24.225000000000001</v>
+      </c>
+      <c r="K35" s="27">
+        <v>22.28294117647058</v>
+      </c>
+      <c r="L35" s="27">
+        <v>22.04</v>
+      </c>
+      <c r="M35" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B36" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D36" s="26">
-        <v>22.491</v>
+        <v>23.361038173225051</v>
       </c>
       <c r="E36" s="26">
-        <v>22.53</v>
+        <v>22.8</v>
       </c>
       <c r="F36" s="26">
-        <v>2.438106961467351</v>
-      </c>
-      <c r="G36" s="4">
-        <v>27.25</v>
-      </c>
-      <c r="H36" s="4">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="I36" s="4">
-        <v>24.684999999999999</v>
-      </c>
-      <c r="J36" s="4">
-        <v>24.05</v>
-      </c>
-      <c r="K36" s="4">
-        <v>20.350000000000001</v>
-      </c>
-      <c r="L36" s="4">
-        <v>19.940000000000001</v>
+        <v>1.52662048047145</v>
+      </c>
+      <c r="G36" s="26">
+        <v>26.118617026368149</v>
+      </c>
+      <c r="H36" s="26">
+        <v>21.5</v>
+      </c>
+      <c r="I36" s="26">
+        <v>25.61586170263681</v>
+      </c>
+      <c r="J36" s="26">
+        <v>24</v>
+      </c>
+      <c r="K36" s="26">
+        <v>22.28294117647058</v>
+      </c>
+      <c r="L36" s="26">
+        <v>22.04</v>
       </c>
       <c r="M36" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B37" s="31">
-        <v>46326</v>
-      </c>
-      <c r="C37" s="32" t="s">
+    <row r="37" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B37" s="17">
+        <v>46356</v>
+      </c>
+      <c r="C37" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D37" s="46">
-        <v>22.477</v>
-      </c>
-      <c r="E37" s="46">
-        <v>22.38</v>
-      </c>
-      <c r="F37" s="46">
-        <v>2.9432108317278258</v>
-      </c>
-      <c r="G37" s="33">
-        <v>29.01</v>
-      </c>
-      <c r="H37" s="33">
-        <v>19</v>
-      </c>
-      <c r="I37" s="33">
-        <v>24.951000000000001</v>
-      </c>
-      <c r="J37" s="33">
-        <v>23.7</v>
-      </c>
-      <c r="K37" s="33">
-        <v>20.3</v>
-      </c>
-      <c r="L37" s="33">
-        <v>19.45</v>
-      </c>
-      <c r="M37" s="34">
+      <c r="D37" s="27">
+        <v>23.18341785699516</v>
+      </c>
+      <c r="E37" s="27">
+        <v>22.415882352941171</v>
+      </c>
+      <c r="F37" s="27">
+        <v>1.732028967234027</v>
+      </c>
+      <c r="G37" s="27">
+        <v>26.59</v>
+      </c>
+      <c r="H37" s="27">
+        <v>21.5</v>
+      </c>
+      <c r="I37" s="27">
+        <v>26.025172477662281</v>
+      </c>
+      <c r="J37" s="27">
+        <v>23.475000000000001</v>
+      </c>
+      <c r="K37" s="27">
+        <v>22.137499999999999</v>
+      </c>
+      <c r="L37" s="27">
+        <v>22.04</v>
+      </c>
+      <c r="M37" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B38" s="2">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D38" s="26">
-        <v>21.890999999999998</v>
+        <v>23.106975163802272</v>
       </c>
       <c r="E38" s="26">
-        <v>22.28</v>
+        <v>22.31588235294118</v>
       </c>
       <c r="F38" s="26">
-        <v>2.5506271559929901</v>
-      </c>
-      <c r="G38" s="4">
-        <v>27.25</v>
-      </c>
-      <c r="H38" s="4">
-        <v>19</v>
-      </c>
-      <c r="I38" s="4">
-        <v>23.695</v>
-      </c>
-      <c r="J38" s="4">
-        <v>22.875</v>
-      </c>
-      <c r="K38" s="4">
-        <v>19.524999999999999</v>
-      </c>
-      <c r="L38" s="4">
-        <v>19</v>
+        <v>1.7165506021105441</v>
+      </c>
+      <c r="G38" s="26">
+        <v>26.58</v>
+      </c>
+      <c r="H38" s="26">
+        <v>21.5</v>
+      </c>
+      <c r="I38" s="26">
+        <v>25.345188238926291</v>
+      </c>
+      <c r="J38" s="26">
+        <v>24.074999999999999</v>
+      </c>
+      <c r="K38" s="26">
+        <v>22.024999999999999</v>
+      </c>
+      <c r="L38" s="26">
+        <v>21.725000000000001</v>
       </c>
       <c r="M38" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B39" s="31" t="s">
+    <row r="39" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B39" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="D39" s="46">
-        <v>20.39494623093325</v>
-      </c>
-      <c r="E39" s="46">
-        <v>20.05</v>
-      </c>
-      <c r="F39" s="46">
-        <v>2.1114523531940632</v>
-      </c>
-      <c r="G39" s="33">
-        <v>23</v>
-      </c>
-      <c r="H39" s="33">
-        <v>17</v>
-      </c>
-      <c r="I39" s="33">
-        <v>22.999999999999659</v>
-      </c>
-      <c r="J39" s="33">
-        <v>22.285</v>
-      </c>
-      <c r="K39" s="33">
-        <v>19.857096731999619</v>
-      </c>
-      <c r="L39" s="33">
-        <v>17.45</v>
-      </c>
-      <c r="M39" s="34">
+      <c r="C39" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39" s="27">
+        <v>21.41646317151401</v>
+      </c>
+      <c r="E39" s="27">
+        <v>20.5</v>
+      </c>
+      <c r="F39" s="27">
+        <v>3.4204586308639868</v>
+      </c>
+      <c r="G39" s="27">
+        <v>28.69823439014737</v>
+      </c>
+      <c r="H39" s="27">
+        <v>16.240514972051521</v>
+      </c>
+      <c r="I39" s="27">
+        <v>24.23582343901473</v>
+      </c>
+      <c r="J39" s="27">
+        <v>22.95</v>
+      </c>
+      <c r="K39" s="27">
+        <v>20.32147058823529</v>
+      </c>
+      <c r="L39" s="27">
+        <v>17.824051497205151</v>
+      </c>
+      <c r="M39" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
         <v>36</v>
       </c>
@@ -6459,41 +6424,41 @@
         <v>20</v>
       </c>
       <c r="D40" s="26">
-        <v>21.687000000000001</v>
+        <v>23.106975163802272</v>
       </c>
       <c r="E40" s="26">
-        <v>21.88</v>
+        <v>22.31588235294118</v>
       </c>
       <c r="F40" s="26">
-        <v>2.188099378202208</v>
-      </c>
-      <c r="G40" s="4">
-        <v>25.11</v>
-      </c>
-      <c r="H40" s="4">
-        <v>18.5</v>
-      </c>
-      <c r="I40" s="4">
-        <v>24.561</v>
-      </c>
-      <c r="J40" s="4">
-        <v>22.725000000000001</v>
-      </c>
-      <c r="K40" s="4">
-        <v>20.175000000000001</v>
-      </c>
-      <c r="L40" s="4">
-        <v>18.95</v>
+        <v>1.7165506021105441</v>
+      </c>
+      <c r="G40" s="26">
+        <v>26.58</v>
+      </c>
+      <c r="H40" s="26">
+        <v>21.5</v>
+      </c>
+      <c r="I40" s="26">
+        <v>25.345188238926291</v>
+      </c>
+      <c r="J40" s="26">
+        <v>24.074999999999999</v>
+      </c>
+      <c r="K40" s="26">
+        <v>22.024999999999999</v>
+      </c>
+      <c r="L40" s="26">
+        <v>21.725000000000001</v>
       </c>
       <c r="M40" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B41" s="22"/>
       <c r="C41" s="23"/>
     </row>
-    <row r="43" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="14" t="s">
         <v>21</v>
       </c>
@@ -6509,7 +6474,7 @@
       <c r="L43" s="14"/>
       <c r="M43" s="15"/>
     </row>
-    <row r="44" spans="2:13" ht="36" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B44" s="24" t="s">
         <v>1</v>
       </c>
@@ -6547,319 +6512,319 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B45" s="31">
-        <v>46203</v>
-      </c>
-      <c r="C45" s="32" t="s">
+    <row r="45" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B45" s="17">
+        <v>46234</v>
+      </c>
+      <c r="C45" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D45" s="42">
-        <v>1416.7800310405521</v>
-      </c>
-      <c r="E45" s="42">
-        <v>1418.5</v>
-      </c>
-      <c r="F45" s="42">
-        <v>8.0887789624817881</v>
-      </c>
-      <c r="G45" s="42">
-        <v>1429.8</v>
-      </c>
-      <c r="H45" s="42">
-        <v>1406</v>
-      </c>
-      <c r="I45" s="42">
-        <v>1423.923</v>
-      </c>
-      <c r="J45" s="42">
-        <v>1422.021863417702</v>
-      </c>
-      <c r="K45" s="42">
-        <v>1408.928369386439</v>
-      </c>
-      <c r="L45" s="42">
-        <v>1406.837</v>
-      </c>
-      <c r="M45" s="34">
+      <c r="D45" s="32">
+        <v>1470.412317963468</v>
+      </c>
+      <c r="E45" s="32">
+        <v>1471.79563630489</v>
+      </c>
+      <c r="F45" s="32">
+        <v>18.37070183331749</v>
+      </c>
+      <c r="G45" s="32">
+        <v>1498.0971705613861</v>
+      </c>
+      <c r="H45" s="32">
+        <v>1437.704736463515</v>
+      </c>
+      <c r="I45" s="32">
+        <v>1491.709717056139</v>
+      </c>
+      <c r="J45" s="32">
+        <v>1481.1824999999999</v>
+      </c>
+      <c r="K45" s="32">
+        <v>1458</v>
+      </c>
+      <c r="L45" s="32">
+        <v>1451.4704736463509</v>
+      </c>
+      <c r="M45" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B46" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D46" s="36">
-        <v>1436.6614761926639</v>
-      </c>
-      <c r="E46" s="36">
-        <v>1439.2177623419609</v>
-      </c>
-      <c r="F46" s="36">
-        <v>11.574763535155141</v>
-      </c>
-      <c r="G46" s="36">
-        <v>1449</v>
-      </c>
-      <c r="H46" s="36">
-        <v>1415</v>
-      </c>
-      <c r="I46" s="36">
-        <v>1448.82</v>
-      </c>
-      <c r="J46" s="36">
-        <v>1445.534952932044</v>
-      </c>
-      <c r="K46" s="36">
-        <v>1431.4</v>
-      </c>
-      <c r="L46" s="36">
-        <v>1420.3993700000001</v>
+      <c r="D46" s="33">
+        <v>1497.6632158940961</v>
+      </c>
+      <c r="E46" s="33">
+        <v>1499.327797179174</v>
+      </c>
+      <c r="F46" s="33">
+        <v>21.71542137806183</v>
+      </c>
+      <c r="G46" s="33">
+        <v>1532.9523239169</v>
+      </c>
+      <c r="H46" s="33">
+        <v>1469.3342406657121</v>
+      </c>
+      <c r="I46" s="33">
+        <v>1524.6162323916899</v>
+      </c>
+      <c r="J46" s="33">
+        <v>1509.75</v>
+      </c>
+      <c r="K46" s="33">
+        <v>1479.75</v>
+      </c>
+      <c r="L46" s="33">
+        <v>1469.933424066571</v>
       </c>
       <c r="M46" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B47" s="31">
-        <v>46265</v>
-      </c>
-      <c r="C47" s="32" t="s">
+    <row r="47" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B47" s="17">
+        <v>46295</v>
+      </c>
+      <c r="C47" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D47" s="42">
-        <v>1463.431566178082</v>
-      </c>
-      <c r="E47" s="42">
-        <v>1466.8146395000001</v>
-      </c>
-      <c r="F47" s="42">
-        <v>18.496630948139341</v>
-      </c>
-      <c r="G47" s="42">
-        <v>1492.85</v>
-      </c>
-      <c r="H47" s="42">
-        <v>1423</v>
-      </c>
-      <c r="I47" s="42">
-        <v>1476.7850000000001</v>
-      </c>
-      <c r="J47" s="42">
-        <v>1471.7117339721281</v>
-      </c>
-      <c r="K47" s="42">
-        <v>1460.0250000000001</v>
-      </c>
-      <c r="L47" s="42">
-        <v>1444.96</v>
-      </c>
-      <c r="M47" s="34">
+      <c r="D47" s="32">
+        <v>1530.631898003181</v>
+      </c>
+      <c r="E47" s="32">
+        <v>1528.5</v>
+      </c>
+      <c r="F47" s="32">
+        <v>32.491364668734739</v>
+      </c>
+      <c r="G47" s="32">
+        <v>1576.55</v>
+      </c>
+      <c r="H47" s="32">
+        <v>1483.1</v>
+      </c>
+      <c r="I47" s="32">
+        <v>1569.411584434014</v>
+      </c>
+      <c r="J47" s="32">
+        <v>1559.6702198724099</v>
+      </c>
+      <c r="K47" s="32">
+        <v>1503.5176947897689</v>
+      </c>
+      <c r="L47" s="32">
+        <v>1496.51</v>
+      </c>
+      <c r="M47" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B48" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D48" s="36">
-        <v>1498.7363050315871</v>
-      </c>
-      <c r="E48" s="36">
-        <v>1502.976404728867</v>
-      </c>
-      <c r="F48" s="36">
-        <v>33.052420507503122</v>
-      </c>
-      <c r="G48" s="36">
-        <v>1544.63</v>
-      </c>
-      <c r="H48" s="36">
-        <v>1428</v>
-      </c>
-      <c r="I48" s="36">
-        <v>1540.230875139318</v>
-      </c>
-      <c r="J48" s="36">
-        <v>1509.3845393424999</v>
-      </c>
-      <c r="K48" s="36">
-        <v>1482.7249999999999</v>
-      </c>
-      <c r="L48" s="36">
-        <v>1474.08</v>
+      <c r="D48" s="33">
+        <v>1564.2871918463579</v>
+      </c>
+      <c r="E48" s="33">
+        <v>1553.5</v>
+      </c>
+      <c r="F48" s="33">
+        <v>49.471012604648173</v>
+      </c>
+      <c r="G48" s="33">
+        <v>1632.8298553875111</v>
+      </c>
+      <c r="H48" s="33">
+        <v>1490</v>
+      </c>
+      <c r="I48" s="33">
+        <v>1623.757985538751</v>
+      </c>
+      <c r="J48" s="33">
+        <v>1606.153587011765</v>
+      </c>
+      <c r="K48" s="33">
+        <v>1532.6082862717531</v>
+      </c>
+      <c r="L48" s="33">
+        <v>1508.9</v>
       </c>
       <c r="M48" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B49" s="31">
-        <v>46326</v>
-      </c>
-      <c r="C49" s="32" t="s">
+    <row r="49" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B49" s="17">
+        <v>46356</v>
+      </c>
+      <c r="C49" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D49" s="42">
-        <v>1535.567485002593</v>
-      </c>
-      <c r="E49" s="42">
-        <v>1535.236409228173</v>
-      </c>
-      <c r="F49" s="42">
-        <v>49.424699458996621</v>
-      </c>
-      <c r="G49" s="42">
-        <v>1609.572347904784</v>
-      </c>
-      <c r="H49" s="42">
-        <v>1435</v>
-      </c>
-      <c r="I49" s="42">
-        <v>1591.858234790478</v>
-      </c>
-      <c r="J49" s="42">
-        <v>1563.3797627485999</v>
-      </c>
-      <c r="K49" s="42">
-        <v>1514.85</v>
-      </c>
-      <c r="L49" s="42">
-        <v>1490.89</v>
-      </c>
-      <c r="M49" s="34">
+      <c r="D49" s="32">
+        <v>1593.062576279819</v>
+      </c>
+      <c r="E49" s="32">
+        <v>1570</v>
+      </c>
+      <c r="F49" s="32">
+        <v>63.538797752164122</v>
+      </c>
+      <c r="G49" s="32">
+        <v>1685.1811000842349</v>
+      </c>
+      <c r="H49" s="32">
+        <v>1497</v>
+      </c>
+      <c r="I49" s="32">
+        <v>1665.020110008423</v>
+      </c>
+      <c r="J49" s="32">
+        <v>1651.6398483460939</v>
+      </c>
+      <c r="K49" s="32">
+        <v>1560.126317332396</v>
+      </c>
+      <c r="L49" s="32">
+        <v>1524</v>
+      </c>
+      <c r="M49" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B50" s="2">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D50" s="36">
-        <v>1566.2809892825619</v>
-      </c>
-      <c r="E50" s="36">
-        <v>1567.327373821965</v>
-      </c>
-      <c r="F50" s="36">
-        <v>60.832058840782032</v>
-      </c>
-      <c r="G50" s="36">
-        <v>1648.960271006946</v>
-      </c>
-      <c r="H50" s="36">
-        <v>1441</v>
-      </c>
-      <c r="I50" s="36">
-        <v>1631.1040271006941</v>
-      </c>
-      <c r="J50" s="36">
-        <v>1609.281155631058</v>
-      </c>
-      <c r="K50" s="36">
-        <v>1543.5</v>
-      </c>
-      <c r="L50" s="36">
-        <v>1506.43</v>
+      <c r="D50" s="33">
+        <v>1621.38409277294</v>
+      </c>
+      <c r="E50" s="33">
+        <v>1597</v>
+      </c>
+      <c r="F50" s="33">
+        <v>78.355582620653081</v>
+      </c>
+      <c r="G50" s="33">
+        <v>1737</v>
+      </c>
+      <c r="H50" s="33">
+        <v>1503</v>
+      </c>
+      <c r="I50" s="33">
+        <v>1707.57</v>
+      </c>
+      <c r="J50" s="33">
+        <v>1689.4758297826761</v>
+      </c>
+      <c r="K50" s="33">
+        <v>1585.3644021496741</v>
+      </c>
+      <c r="L50" s="33">
+        <v>1524.6</v>
       </c>
       <c r="M50" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B51" s="31" t="s">
+    <row r="51" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B51" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D51" s="42">
-        <v>1712.7887282533079</v>
-      </c>
-      <c r="E51" s="42">
-        <v>1718.5</v>
-      </c>
-      <c r="F51" s="42">
-        <v>117.49225919136271</v>
-      </c>
-      <c r="G51" s="42">
-        <v>1850</v>
-      </c>
-      <c r="H51" s="42">
-        <v>1473</v>
-      </c>
-      <c r="I51" s="42">
-        <v>1840.0586915089821</v>
-      </c>
-      <c r="J51" s="42">
-        <v>1811.0150000000001</v>
-      </c>
-      <c r="K51" s="42">
-        <v>1660.0432952141091</v>
-      </c>
-      <c r="L51" s="42">
-        <v>1592.34</v>
-      </c>
-      <c r="M51" s="34">
+      <c r="C51" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D51" s="32">
+        <v>1765.627124957166</v>
+      </c>
+      <c r="E51" s="32">
+        <v>1767.5</v>
+      </c>
+      <c r="F51" s="32">
+        <v>139.8766384293879</v>
+      </c>
+      <c r="G51" s="32">
+        <v>1970</v>
+      </c>
+      <c r="H51" s="32">
+        <v>1535</v>
+      </c>
+      <c r="I51" s="32">
+        <v>1922.6051053899009</v>
+      </c>
+      <c r="J51" s="32">
+        <v>1881.9525000000001</v>
+      </c>
+      <c r="K51" s="32">
+        <v>1692.530560895721</v>
+      </c>
+      <c r="L51" s="32">
+        <v>1598</v>
+      </c>
+      <c r="M51" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D52" s="36">
-        <v>1596.369874026793</v>
-      </c>
-      <c r="E52" s="36">
-        <v>1599.5793701339639</v>
-      </c>
-      <c r="F52" s="36">
-        <v>71.130380483837826</v>
-      </c>
-      <c r="G52" s="36">
-        <v>1688</v>
-      </c>
-      <c r="H52" s="36">
-        <v>1448</v>
-      </c>
-      <c r="I52" s="36">
-        <v>1665.5</v>
-      </c>
-      <c r="J52" s="36">
-        <v>1651.73</v>
-      </c>
-      <c r="K52" s="36">
-        <v>1567.75</v>
-      </c>
-      <c r="L52" s="36">
-        <v>1523.51</v>
+      <c r="D52" s="33">
+        <v>1621.38409277294</v>
+      </c>
+      <c r="E52" s="33">
+        <v>1597</v>
+      </c>
+      <c r="F52" s="33">
+        <v>78.355582620653081</v>
+      </c>
+      <c r="G52" s="33">
+        <v>1737</v>
+      </c>
+      <c r="H52" s="33">
+        <v>1503</v>
+      </c>
+      <c r="I52" s="33">
+        <v>1707.57</v>
+      </c>
+      <c r="J52" s="33">
+        <v>1689.4758297826761</v>
+      </c>
+      <c r="K52" s="33">
+        <v>1585.3644021496741</v>
+      </c>
+      <c r="L52" s="33">
+        <v>1524.6</v>
       </c>
       <c r="M52" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B53" s="22"/>
       <c r="C53" s="23"/>
     </row>
-    <row r="54" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B54" s="22"/>
       <c r="C54" s="23"/>
     </row>
-    <row r="55" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B55" s="14" t="s">
         <v>24</v>
       </c>
@@ -6875,7 +6840,7 @@
       <c r="L55" s="14"/>
       <c r="M55" s="15"/>
     </row>
-    <row r="56" spans="2:13" ht="36" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B56" s="24" t="s">
         <v>1</v>
       </c>
@@ -6913,319 +6878,319 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B57" s="38">
-        <v>46173</v>
-      </c>
-      <c r="C57" s="32" t="s">
+    <row r="57" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B57" s="17">
+        <v>46203</v>
+      </c>
+      <c r="C57" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D57" s="39">
-        <v>9313.67998747602</v>
-      </c>
-      <c r="E57" s="39">
-        <v>9435.0720042625471</v>
-      </c>
-      <c r="F57" s="39">
-        <v>557.00096940449623</v>
-      </c>
-      <c r="G57" s="39">
-        <v>10125</v>
-      </c>
-      <c r="H57" s="39">
-        <v>8302.9649802476069</v>
-      </c>
-      <c r="I57" s="39">
-        <v>9860.1407507374206</v>
-      </c>
-      <c r="J57" s="39">
-        <v>9668.5985672622355</v>
-      </c>
-      <c r="K57" s="39">
-        <v>8886.75</v>
-      </c>
-      <c r="L57" s="39">
-        <v>8750.2964980247616</v>
-      </c>
-      <c r="M57" s="40">
+      <c r="D57" s="31">
+        <v>9037.4040445464179</v>
+      </c>
+      <c r="E57" s="31">
+        <v>9055.7349498346866</v>
+      </c>
+      <c r="F57" s="31">
+        <v>249.7701614519213</v>
+      </c>
+      <c r="G57" s="31">
+        <v>9447</v>
+      </c>
+      <c r="H57" s="31">
+        <v>8637.7646955909076</v>
+      </c>
+      <c r="I57" s="31">
+        <v>9296.3943959798435</v>
+      </c>
+      <c r="J57" s="31">
+        <v>9178.9501722776622</v>
+      </c>
+      <c r="K57" s="31">
+        <v>8947.5</v>
+      </c>
+      <c r="L57" s="31">
+        <v>8674.4420941922981</v>
+      </c>
+      <c r="M57" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B58" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D58" s="36">
-        <v>8963.9288219552436</v>
-      </c>
-      <c r="E58" s="36">
-        <v>9015.6397392870986</v>
-      </c>
-      <c r="F58" s="36">
-        <v>426.27473091349231</v>
-      </c>
-      <c r="G58" s="36">
-        <v>9796</v>
-      </c>
-      <c r="H58" s="36">
-        <v>8327</v>
-      </c>
-      <c r="I58" s="36">
-        <v>9331.2943959798431</v>
-      </c>
-      <c r="J58" s="36">
-        <v>9175.850844796345</v>
-      </c>
-      <c r="K58" s="36">
-        <v>8683.8880205276728</v>
-      </c>
-      <c r="L58" s="36">
-        <v>8495.026832511754</v>
+      <c r="D58" s="30">
+        <v>8948.9958206388947</v>
+      </c>
+      <c r="E58" s="30">
+        <v>9065.9729354166593</v>
+      </c>
+      <c r="F58" s="30">
+        <v>546.06215451606533</v>
+      </c>
+      <c r="G58" s="30">
+        <v>9607.375445483829</v>
+      </c>
+      <c r="H58" s="30">
+        <v>8000</v>
+      </c>
+      <c r="I58" s="30">
+        <v>9529.4306028315859</v>
+      </c>
+      <c r="J58" s="30">
+        <v>9395.25</v>
+      </c>
+      <c r="K58" s="30">
+        <v>8660.8131256375927</v>
+      </c>
+      <c r="L58" s="30">
+        <v>8211.6043920162956</v>
       </c>
       <c r="M58" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B59" s="31">
-        <v>46234</v>
-      </c>
-      <c r="C59" s="32" t="s">
+    <row r="59" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B59" s="17">
+        <v>46265</v>
+      </c>
+      <c r="C59" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D59" s="39">
-        <v>8971.7385727158417</v>
-      </c>
-      <c r="E59" s="39">
-        <v>8891.4137740971164</v>
-      </c>
-      <c r="F59" s="39">
-        <v>537.67280898675642</v>
-      </c>
-      <c r="G59" s="39">
-        <v>9818</v>
-      </c>
-      <c r="H59" s="39">
-        <v>8158</v>
-      </c>
-      <c r="I59" s="39">
-        <v>9733.0510773177793</v>
-      </c>
-      <c r="J59" s="39">
-        <v>9282.7364677083297</v>
-      </c>
-      <c r="K59" s="39">
-        <v>8566</v>
-      </c>
-      <c r="L59" s="39">
-        <v>8465.7999999999993</v>
-      </c>
-      <c r="M59" s="34">
+      <c r="D59" s="31">
+        <v>8878.634566970708</v>
+      </c>
+      <c r="E59" s="31">
+        <v>9018.5728190144364</v>
+      </c>
+      <c r="F59" s="31">
+        <v>528.12825831798648</v>
+      </c>
+      <c r="G59" s="31">
+        <v>9597</v>
+      </c>
+      <c r="H59" s="31">
+        <v>8000</v>
+      </c>
+      <c r="I59" s="31">
+        <v>9364.2699546427102</v>
+      </c>
+      <c r="J59" s="31">
+        <v>9274.2911979310938</v>
+      </c>
+      <c r="K59" s="31">
+        <v>8447.9768561844048</v>
+      </c>
+      <c r="L59" s="31">
+        <v>8260.5439540865082</v>
+      </c>
+      <c r="M59" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B60" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D60" s="36">
-        <v>8887.3997398595529</v>
-      </c>
-      <c r="E60" s="36">
-        <v>8899.0788750790634</v>
-      </c>
-      <c r="F60" s="36">
-        <v>535.67711851431341</v>
-      </c>
-      <c r="G60" s="36">
-        <v>9953</v>
-      </c>
-      <c r="H60" s="36">
-        <v>8123</v>
-      </c>
-      <c r="I60" s="36">
-        <v>9459.8720849905549</v>
-      </c>
-      <c r="J60" s="36">
-        <v>9088.0127075152996</v>
-      </c>
-      <c r="K60" s="36">
-        <v>8509.25</v>
-      </c>
-      <c r="L60" s="36">
-        <v>8372.2999999999993</v>
+      <c r="D60" s="30">
+        <v>8628.5894663954077</v>
+      </c>
+      <c r="E60" s="30">
+        <v>8704.7811940924967</v>
+      </c>
+      <c r="F60" s="30">
+        <v>497.50320633809793</v>
+      </c>
+      <c r="G60" s="30">
+        <v>9235</v>
+      </c>
+      <c r="H60" s="30">
+        <v>8000</v>
+      </c>
+      <c r="I60" s="30">
+        <v>9183.8957175269061</v>
+      </c>
+      <c r="J60" s="30">
+        <v>9064.5274110537339</v>
+      </c>
+      <c r="K60" s="30">
+        <v>8152.8868894375864</v>
+      </c>
+      <c r="L60" s="30">
+        <v>8023.9061700756911</v>
       </c>
       <c r="M60" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B61" s="31">
-        <v>46295</v>
-      </c>
-      <c r="C61" s="32" t="s">
+    <row r="61" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B61" s="17">
+        <v>46326</v>
+      </c>
+      <c r="C61" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D61" s="39">
-        <v>8668.3020786640936</v>
-      </c>
-      <c r="E61" s="39">
-        <v>8628.2811940924967</v>
-      </c>
-      <c r="F61" s="39">
-        <v>553.19052674271882</v>
-      </c>
-      <c r="G61" s="39">
-        <v>9577</v>
-      </c>
-      <c r="H61" s="39">
-        <v>7958</v>
-      </c>
-      <c r="I61" s="39">
-        <v>9344.5892533875121</v>
-      </c>
-      <c r="J61" s="39">
-        <v>9038.822411853791</v>
-      </c>
-      <c r="K61" s="39">
-        <v>8240.2323363884134</v>
-      </c>
-      <c r="L61" s="39">
-        <v>7995.8</v>
-      </c>
-      <c r="M61" s="34">
+      <c r="D61" s="31">
+        <v>8555.892470159175</v>
+      </c>
+      <c r="E61" s="31">
+        <v>8631.9116434019998</v>
+      </c>
+      <c r="F61" s="31">
+        <v>404.28584223888163</v>
+      </c>
+      <c r="G61" s="31">
+        <v>9070</v>
+      </c>
+      <c r="H61" s="31">
+        <v>7961.6746609917782</v>
+      </c>
+      <c r="I61" s="31">
+        <v>8967.7264592163501</v>
+      </c>
+      <c r="J61" s="31">
+        <v>8867.027401900039</v>
+      </c>
+      <c r="K61" s="31">
+        <v>8219.7386034332994</v>
+      </c>
+      <c r="L61" s="31">
+        <v>7996.1674660991775</v>
+      </c>
+      <c r="M61" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B62" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D62" s="36">
-        <v>8495.4374586647318</v>
-      </c>
-      <c r="E62" s="36">
-        <v>8450.4772068666007</v>
-      </c>
-      <c r="F62" s="36">
-        <v>480.25894925396472</v>
-      </c>
-      <c r="G62" s="36">
-        <v>9406</v>
-      </c>
-      <c r="H62" s="36">
-        <v>7867</v>
-      </c>
-      <c r="I62" s="36">
-        <v>9030.2801999185376</v>
-      </c>
-      <c r="J62" s="36">
-        <v>8790.9682815702217</v>
-      </c>
-      <c r="K62" s="36">
-        <v>8157.6488938388593</v>
-      </c>
-      <c r="L62" s="36">
-        <v>7986.7</v>
+      <c r="D62" s="30">
+        <v>8057.7556913287526</v>
+      </c>
+      <c r="E62" s="30">
+        <v>8001.6353278219658</v>
+      </c>
+      <c r="F62" s="30">
+        <v>471.51993448765108</v>
+      </c>
+      <c r="G62" s="30">
+        <v>8900</v>
+      </c>
+      <c r="H62" s="30">
+        <v>7200</v>
+      </c>
+      <c r="I62" s="30">
+        <v>8482.8050485846379</v>
+      </c>
+      <c r="J62" s="30">
+        <v>8362.2718935118992</v>
+      </c>
+      <c r="K62" s="30">
+        <v>7881.0504862940979</v>
+      </c>
+      <c r="L62" s="30">
+        <v>7562.4131830988454</v>
       </c>
       <c r="M62" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B63" s="31">
-        <v>46356</v>
-      </c>
-      <c r="C63" s="32" t="s">
+    <row r="63" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B63" s="17">
+        <v>46387</v>
+      </c>
+      <c r="C63" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D63" s="39">
-        <v>8219.6177675813233</v>
-      </c>
-      <c r="E63" s="39">
-        <v>8091.4506308811378</v>
-      </c>
-      <c r="F63" s="39">
-        <v>615.07485534293187</v>
-      </c>
-      <c r="G63" s="39">
-        <v>9180.5453686464207</v>
-      </c>
-      <c r="H63" s="39">
-        <v>7200</v>
-      </c>
-      <c r="I63" s="39">
-        <v>8928.0545368646417</v>
-      </c>
-      <c r="J63" s="39">
-        <v>8696.5</v>
-      </c>
-      <c r="K63" s="39">
-        <v>7815.0482840534069</v>
-      </c>
-      <c r="L63" s="39">
-        <v>7713</v>
-      </c>
-      <c r="M63" s="34">
+      <c r="D63" s="31">
+        <v>8108.2064569991589</v>
+      </c>
+      <c r="E63" s="31">
+        <v>8128.6567943578184</v>
+      </c>
+      <c r="F63" s="31">
+        <v>390.59275849159093</v>
+      </c>
+      <c r="G63" s="31">
+        <v>8503.0250200789451</v>
+      </c>
+      <c r="H63" s="31">
+        <v>7498.9721255834384</v>
+      </c>
+      <c r="I63" s="31">
+        <v>8500.3025020078949</v>
+      </c>
+      <c r="J63" s="31">
+        <v>8483.1884589033962</v>
+      </c>
+      <c r="K63" s="31">
+        <v>7851.5</v>
+      </c>
+      <c r="L63" s="31">
+        <v>7557.4972125583436</v>
+      </c>
+      <c r="M63" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B64" s="35" t="s">
+    <row r="64" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B64" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C64" s="36" t="s">
+      <c r="C64" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D64" s="36">
-        <v>100578.39202648601</v>
-      </c>
-      <c r="E64" s="36">
-        <v>100625</v>
-      </c>
-      <c r="F64" s="36">
-        <v>3001.0435156550052</v>
-      </c>
-      <c r="G64" s="36">
-        <v>106474</v>
-      </c>
-      <c r="H64" s="36">
-        <v>95836</v>
-      </c>
-      <c r="I64" s="36">
-        <v>103617.4</v>
-      </c>
-      <c r="J64" s="36">
-        <v>101463.4420967887</v>
-      </c>
-      <c r="K64" s="36">
-        <v>99227.5</v>
-      </c>
-      <c r="L64" s="36">
-        <v>97025.561472761183</v>
-      </c>
-      <c r="M64" s="37">
+      <c r="D64" s="30">
+        <v>100569.289343401</v>
+      </c>
+      <c r="E64" s="30">
+        <v>100787.6637622686</v>
+      </c>
+      <c r="F64" s="30">
+        <v>2490.808745815767</v>
+      </c>
+      <c r="G64" s="30">
+        <v>103598</v>
+      </c>
+      <c r="H64" s="30">
+        <v>96037.109413863567</v>
+      </c>
+      <c r="I64" s="30">
+        <v>103213.6860281532</v>
+      </c>
+      <c r="J64" s="30">
+        <v>102682.18089081479</v>
+      </c>
+      <c r="K64" s="30">
+        <v>98894.25</v>
+      </c>
+      <c r="L64" s="30">
+        <v>97686.918690303399</v>
+      </c>
+      <c r="M64" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B65" s="22"/>
       <c r="C65" s="23"/>
     </row>
-    <row r="66" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B66" s="22"/>
       <c r="C66" s="23"/>
     </row>
-    <row r="67" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="14" t="s">
         <v>26</v>
       </c>
@@ -7241,7 +7206,7 @@
       <c r="L67" s="14"/>
       <c r="M67" s="15"/>
     </row>
-    <row r="68" spans="2:13" ht="36" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B68" s="24" t="s">
         <v>1</v>
       </c>
@@ -7279,311 +7244,311 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B69" s="38">
-        <v>46173</v>
-      </c>
-      <c r="C69" s="32" t="s">
+    <row r="69" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B69" s="17">
+        <v>46203</v>
+      </c>
+      <c r="C69" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D69" s="39">
-        <v>6738.9078334678252</v>
-      </c>
-      <c r="E69" s="39">
-        <v>6699.9330532061067</v>
-      </c>
-      <c r="F69" s="39">
-        <v>243.90718792723271</v>
-      </c>
-      <c r="G69" s="39">
-        <v>7058.76</v>
-      </c>
-      <c r="H69" s="39">
-        <v>6234.9522612827004</v>
-      </c>
-      <c r="I69" s="39">
-        <v>7050.5432716364094</v>
-      </c>
-      <c r="J69" s="39">
-        <v>6909.3562704549022</v>
-      </c>
-      <c r="K69" s="39">
-        <v>6657.8187750126544</v>
-      </c>
-      <c r="L69" s="39">
-        <v>6579.8789026594304</v>
-      </c>
-      <c r="M69" s="40">
+      <c r="D69" s="31">
+        <v>6551.8181821127164</v>
+      </c>
+      <c r="E69" s="31">
+        <v>6489.1450000000004</v>
+      </c>
+      <c r="F69" s="31">
+        <v>351.76824792585899</v>
+      </c>
+      <c r="G69" s="31">
+        <v>7168.72</v>
+      </c>
+      <c r="H69" s="31">
+        <v>6137.4464661806587</v>
+      </c>
+      <c r="I69" s="31">
+        <v>6946.9480533933747</v>
+      </c>
+      <c r="J69" s="31">
+        <v>6809.2825299766973</v>
+      </c>
+      <c r="K69" s="31">
+        <v>6255.7925742447696</v>
+      </c>
+      <c r="L69" s="31">
+        <v>6226.0073125023291</v>
+      </c>
+      <c r="M69" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B70" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D70" s="36">
-        <v>6805.9866167100527</v>
-      </c>
-      <c r="E70" s="36">
-        <v>6811.7996573570472</v>
-      </c>
-      <c r="F70" s="36">
-        <v>203.17292409257661</v>
-      </c>
-      <c r="G70" s="36">
-        <v>7172.46</v>
-      </c>
-      <c r="H70" s="36">
-        <v>6521</v>
-      </c>
-      <c r="I70" s="36">
-        <v>7036.1145696502044</v>
-      </c>
-      <c r="J70" s="36">
-        <v>6912.6165653047428</v>
-      </c>
-      <c r="K70" s="36">
-        <v>6654.4567105612141</v>
-      </c>
-      <c r="L70" s="36">
-        <v>6593.7579111668883</v>
+      <c r="D70" s="30">
+        <v>6882.171759478535</v>
+      </c>
+      <c r="E70" s="30">
+        <v>6850.5823052483074</v>
+      </c>
+      <c r="F70" s="30">
+        <v>372.25516794125002</v>
+      </c>
+      <c r="G70" s="30">
+        <v>7422.03</v>
+      </c>
+      <c r="H70" s="30">
+        <v>6261.5333408658234</v>
+      </c>
+      <c r="I70" s="30">
+        <v>7273.143</v>
+      </c>
+      <c r="J70" s="30">
+        <v>7190.1936602929891</v>
+      </c>
+      <c r="K70" s="30">
+        <v>6681.6486050524136</v>
+      </c>
+      <c r="L70" s="30">
+        <v>6442.297356629806</v>
       </c>
       <c r="M70" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B71" s="31">
-        <v>46234</v>
-      </c>
-      <c r="C71" s="32" t="s">
+    <row r="71" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B71" s="17">
+        <v>46265</v>
+      </c>
+      <c r="C71" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D71" s="39">
-        <v>7132.0362927405613</v>
-      </c>
-      <c r="E71" s="39">
-        <v>7186.7192195329062</v>
-      </c>
-      <c r="F71" s="39">
-        <v>343.58268113280451</v>
-      </c>
-      <c r="G71" s="39">
-        <v>7483.1734120149376</v>
-      </c>
-      <c r="H71" s="39">
-        <v>6250</v>
-      </c>
-      <c r="I71" s="39">
-        <v>7427.6043412014942</v>
-      </c>
-      <c r="J71" s="39">
-        <v>7315.7639721479954</v>
-      </c>
-      <c r="K71" s="39">
-        <v>7104.9059759530273</v>
-      </c>
-      <c r="L71" s="39">
-        <v>6933.9327145554689</v>
-      </c>
-      <c r="M71" s="34">
+      <c r="D71" s="31">
+        <v>6756.3980884336752</v>
+      </c>
+      <c r="E71" s="31">
+        <v>6690.3573271466921</v>
+      </c>
+      <c r="F71" s="31">
+        <v>343.66178635895761</v>
+      </c>
+      <c r="G71" s="31">
+        <v>7290.49</v>
+      </c>
+      <c r="H71" s="31">
+        <v>6220.6495191451713</v>
+      </c>
+      <c r="I71" s="31">
+        <v>7195.9123148387271</v>
+      </c>
+      <c r="J71" s="31">
+        <v>7031.6349786848441</v>
+      </c>
+      <c r="K71" s="31">
+        <v>6529.3869883749794</v>
+      </c>
+      <c r="L71" s="31">
+        <v>6463.2933164123688</v>
+      </c>
+      <c r="M71" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B72" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D72" s="36">
-        <v>7004.5356657613547</v>
-      </c>
-      <c r="E72" s="36">
-        <v>7070.7133299023872</v>
-      </c>
-      <c r="F72" s="36">
-        <v>242.6875177351111</v>
-      </c>
-      <c r="G72" s="36">
-        <v>7305.77</v>
-      </c>
-      <c r="H72" s="36">
-        <v>6440.9771371761644</v>
-      </c>
-      <c r="I72" s="36">
-        <v>7197.4403148387273</v>
-      </c>
-      <c r="J72" s="36">
-        <v>7142.9380994460898</v>
-      </c>
-      <c r="K72" s="36">
-        <v>6907.3537880883941</v>
-      </c>
-      <c r="L72" s="36">
-        <v>6815.9890908523084</v>
+      <c r="D72" s="30">
+        <v>6770.6086930994688</v>
+      </c>
+      <c r="E72" s="30">
+        <v>6760.8154513102872</v>
+      </c>
+      <c r="F72" s="30">
+        <v>503.39627472129928</v>
+      </c>
+      <c r="G72" s="30">
+        <v>7613.9</v>
+      </c>
+      <c r="H72" s="30">
+        <v>5801.3762093660598</v>
+      </c>
+      <c r="I72" s="30">
+        <v>7249.2323858308173</v>
+      </c>
+      <c r="J72" s="30">
+        <v>7078.8302828272499</v>
+      </c>
+      <c r="K72" s="30">
+        <v>6503.2849049840679</v>
+      </c>
+      <c r="L72" s="30">
+        <v>6331.1408304273464</v>
       </c>
       <c r="M72" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B73" s="31">
-        <v>46295</v>
-      </c>
-      <c r="C73" s="32" t="s">
+    <row r="73" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B73" s="17">
+        <v>46326</v>
+      </c>
+      <c r="C73" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D73" s="39">
-        <v>7131.5168688648582</v>
-      </c>
-      <c r="E73" s="39">
-        <v>7022.3049149278904</v>
-      </c>
-      <c r="F73" s="39">
-        <v>421.64242798958639</v>
-      </c>
-      <c r="G73" s="39">
-        <v>7881.3360000000002</v>
-      </c>
-      <c r="H73" s="39">
-        <v>6636.5156895783521</v>
-      </c>
-      <c r="I73" s="39">
-        <v>7727.5197080131302</v>
-      </c>
-      <c r="J73" s="39">
-        <v>7363.1630841698116</v>
-      </c>
-      <c r="K73" s="39">
-        <v>6851.3777479264954</v>
-      </c>
-      <c r="L73" s="39">
-        <v>6693.6515689578346</v>
-      </c>
-      <c r="M73" s="34">
+      <c r="D73" s="31">
+        <v>6705.5583381064152</v>
+      </c>
+      <c r="E73" s="31">
+        <v>6896.6950267337197</v>
+      </c>
+      <c r="F73" s="31">
+        <v>418.38881804621059</v>
+      </c>
+      <c r="G73" s="31">
+        <v>7074.3991128733842</v>
+      </c>
+      <c r="H73" s="31">
+        <v>5705.8326799021979</v>
+      </c>
+      <c r="I73" s="31">
+        <v>7020.7959112873386</v>
+      </c>
+      <c r="J73" s="31">
+        <v>6973.9108831492676</v>
+      </c>
+      <c r="K73" s="31">
+        <v>6562.9535043375736</v>
+      </c>
+      <c r="L73" s="31">
+        <v>6331.8343100308912</v>
+      </c>
+      <c r="M73" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B74" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D74" s="36">
-        <v>7032.0777241648539</v>
-      </c>
-      <c r="E74" s="36">
-        <v>7041.2692366742267</v>
-      </c>
-      <c r="F74" s="36">
-        <v>538.42312896514591</v>
-      </c>
-      <c r="G74" s="36">
-        <v>7922.2000000000007</v>
-      </c>
-      <c r="H74" s="36">
-        <v>6200</v>
-      </c>
-      <c r="I74" s="36">
-        <v>7706.2158316677278</v>
-      </c>
-      <c r="J74" s="36">
-        <v>7334.560702229187</v>
-      </c>
-      <c r="K74" s="36">
-        <v>6621.3201730064493</v>
-      </c>
-      <c r="L74" s="36">
-        <v>6476.5668007772683</v>
+      <c r="D74" s="30">
+        <v>6313.4239196228173</v>
+      </c>
+      <c r="E74" s="30">
+        <v>6451.688958400021</v>
+      </c>
+      <c r="F74" s="30">
+        <v>507.1676552722721</v>
+      </c>
+      <c r="G74" s="30">
+        <v>6926.2276415778151</v>
+      </c>
+      <c r="H74" s="30">
+        <v>5358.3417419697053</v>
+      </c>
+      <c r="I74" s="30">
+        <v>6787.6933879985309</v>
+      </c>
+      <c r="J74" s="30">
+        <v>6715.0088200013961</v>
+      </c>
+      <c r="K74" s="30">
+        <v>5987.9174999999996</v>
+      </c>
+      <c r="L74" s="30">
+        <v>5754.018672647092</v>
       </c>
       <c r="M74" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B75" s="31">
-        <v>46356</v>
-      </c>
-      <c r="C75" s="32" t="s">
+    <row r="75" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B75" s="17">
+        <v>46387</v>
+      </c>
+      <c r="C75" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D75" s="39">
-        <v>6566.0959047611614</v>
-      </c>
-      <c r="E75" s="39">
-        <v>6521.1550000000007</v>
-      </c>
-      <c r="F75" s="39">
-        <v>457.2432578383947</v>
-      </c>
-      <c r="G75" s="39">
-        <v>7483</v>
-      </c>
-      <c r="H75" s="39">
-        <v>5839.0150632505774</v>
-      </c>
-      <c r="I75" s="39">
-        <v>6942.1683700058566</v>
-      </c>
-      <c r="J75" s="39">
-        <v>6819.7059201871107</v>
-      </c>
-      <c r="K75" s="39">
-        <v>6366.7794315195733</v>
-      </c>
-      <c r="L75" s="39">
-        <v>6100.6351194570652</v>
-      </c>
-      <c r="M75" s="34">
+      <c r="D75" s="31">
+        <v>6222.1524661352332</v>
+      </c>
+      <c r="E75" s="31">
+        <v>6142.93</v>
+      </c>
+      <c r="F75" s="31">
+        <v>668.84422712974708</v>
+      </c>
+      <c r="G75" s="31">
+        <v>7203.7312280968417</v>
+      </c>
+      <c r="H75" s="31">
+        <v>4918.2185989196932</v>
+      </c>
+      <c r="I75" s="31">
+        <v>7195.2788341943651</v>
+      </c>
+      <c r="J75" s="31">
+        <v>6469.7419528555311</v>
+      </c>
+      <c r="K75" s="31">
+        <v>5954.2888502696078</v>
+      </c>
+      <c r="L75" s="31">
+        <v>5700.0960981529161</v>
+      </c>
+      <c r="M75" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B76" s="35" t="s">
+    <row r="76" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B76" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C76" s="36" t="s">
+      <c r="C76" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D76" s="36">
-        <v>77392.352659705095</v>
-      </c>
-      <c r="E76" s="36">
-        <v>77815.920062022313</v>
-      </c>
-      <c r="F76" s="36">
-        <v>1537.519693663995</v>
-      </c>
-      <c r="G76" s="36">
-        <v>79500</v>
-      </c>
-      <c r="H76" s="36">
-        <v>74367.989567624798</v>
-      </c>
-      <c r="I76" s="36">
-        <v>78576.455100000006</v>
-      </c>
-      <c r="J76" s="36">
-        <v>78364.782703096134</v>
-      </c>
-      <c r="K76" s="36">
-        <v>76496.765348597779</v>
-      </c>
-      <c r="L76" s="36">
-        <v>75596.210572938522</v>
-      </c>
-      <c r="M76" s="37">
+      <c r="D76" s="30">
+        <v>74777.444275749294</v>
+      </c>
+      <c r="E76" s="30">
+        <v>74898.406994736724</v>
+      </c>
+      <c r="F76" s="30">
+        <v>2396.411596796037</v>
+      </c>
+      <c r="G76" s="30">
+        <v>77315.149999999994</v>
+      </c>
+      <c r="H76" s="30">
+        <v>68978.521358499303</v>
+      </c>
+      <c r="I76" s="30">
+        <v>77135.471243715365</v>
+      </c>
+      <c r="J76" s="30">
+        <v>76349.320785959804</v>
+      </c>
+      <c r="K76" s="30">
+        <v>74125</v>
+      </c>
+      <c r="L76" s="30">
+        <v>73322.576617550934</v>
+      </c>
+      <c r="M76" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="18" x14ac:dyDescent="0.4">
+    <row r="77" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B77" s="9"/>
       <c r="C77" s="10"/>
       <c r="D77" s="10"/>
@@ -7597,7 +7562,7 @@
       <c r="L77" s="10"/>
       <c r="M77" s="10"/>
     </row>
-    <row r="79" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="14" t="s">
         <v>27</v>
       </c>
@@ -7613,7 +7578,7 @@
       <c r="L79" s="14"/>
       <c r="M79" s="15"/>
     </row>
-    <row r="80" spans="2:13" ht="36" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B80" s="24" t="s">
         <v>1</v>
       </c>
@@ -7651,45 +7616,45 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B81" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="43">
-        <v>15722.40612366544</v>
-      </c>
-      <c r="E81" s="43">
-        <v>15788.05</v>
-      </c>
-      <c r="F81" s="43">
-        <v>1032.556231234094</v>
-      </c>
-      <c r="G81" s="43">
-        <v>17705.150000000001</v>
-      </c>
-      <c r="H81" s="43">
-        <v>13663.936308724091</v>
-      </c>
-      <c r="I81" s="43">
-        <v>16440.514999999999</v>
-      </c>
-      <c r="J81" s="43">
-        <v>16098.62602800831</v>
-      </c>
-      <c r="K81" s="43">
-        <v>15293.75</v>
-      </c>
-      <c r="L81" s="43">
-        <v>14866.7298323997</v>
+      <c r="D81" s="30">
+        <v>15836.79840434871</v>
+      </c>
+      <c r="E81" s="30">
+        <v>15741.5</v>
+      </c>
+      <c r="F81" s="30">
+        <v>2387.8197008217089</v>
+      </c>
+      <c r="G81" s="30">
+        <v>21056</v>
+      </c>
+      <c r="H81" s="30">
+        <v>12696.110347427109</v>
+      </c>
+      <c r="I81" s="30">
+        <v>18131.080999999998</v>
+      </c>
+      <c r="J81" s="30">
+        <v>16101.462613104781</v>
+      </c>
+      <c r="K81" s="30">
+        <v>15166.957449599129</v>
+      </c>
+      <c r="L81" s="30">
+        <v>12780.21228595202</v>
       </c>
       <c r="M81" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="2:13" ht="18" x14ac:dyDescent="0.4">
+    <row r="82" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B82" s="9"/>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
@@ -7703,7 +7668,7 @@
       <c r="L82" s="10"/>
       <c r="M82" s="10"/>
     </row>
-    <row r="84" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="14" t="s">
         <v>29</v>
       </c>
@@ -7719,7 +7684,7 @@
       <c r="L84" s="14"/>
       <c r="M84" s="15"/>
     </row>
-    <row r="85" spans="2:13" ht="36" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B85" s="24" t="s">
         <v>1</v>
       </c>
@@ -7757,159 +7722,159 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B86" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="C86" s="32" t="s">
+    <row r="86" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B86" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C86" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D86" s="33">
-        <v>7.7553257807101108</v>
-      </c>
-      <c r="E86" s="33">
+      <c r="D86" s="19">
+        <v>7.641</v>
+      </c>
+      <c r="E86" s="19">
         <v>7.7</v>
       </c>
-      <c r="F86" s="33">
-        <v>0.43882326692365248</v>
-      </c>
-      <c r="G86" s="33">
-        <v>8.6460955860665845</v>
-      </c>
-      <c r="H86" s="33">
-        <v>7.1</v>
-      </c>
-      <c r="I86" s="33">
-        <v>8.1546095586066585</v>
-      </c>
-      <c r="J86" s="33">
-        <v>7.9875000000000007</v>
-      </c>
-      <c r="K86" s="33">
-        <v>7.6</v>
-      </c>
-      <c r="L86" s="33">
-        <v>7.2414459989310664</v>
-      </c>
-      <c r="M86" s="40">
+      <c r="F86" s="19">
+        <v>0.25414125556032369</v>
+      </c>
+      <c r="G86" s="19">
+        <v>8.1</v>
+      </c>
+      <c r="H86" s="19">
+        <v>7.2</v>
+      </c>
+      <c r="I86" s="19">
+        <v>7.92</v>
+      </c>
+      <c r="J86" s="19">
+        <v>7.7</v>
+      </c>
+      <c r="K86" s="19">
+        <v>7.5025000000000004</v>
+      </c>
+      <c r="L86" s="19">
+        <v>7.3800000000000008</v>
+      </c>
+      <c r="M86" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B87" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D87" s="4">
-        <v>7.5300590102177791</v>
+        <v>7.3040000000000003</v>
       </c>
       <c r="E87" s="4">
-        <v>7.6</v>
+        <v>7.45</v>
       </c>
       <c r="F87" s="4">
-        <v>0.42661984645280282</v>
+        <v>0.6288296006603592</v>
       </c>
       <c r="G87" s="4">
-        <v>8.08</v>
+        <v>8.4</v>
       </c>
       <c r="H87" s="4">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="I87" s="4">
-        <v>7.9180000000000001</v>
+        <v>7.77</v>
       </c>
       <c r="J87" s="4">
-        <v>7.8458856590154671</v>
+        <v>7.6775000000000002</v>
       </c>
       <c r="K87" s="4">
-        <v>7.3250000000000002</v>
+        <v>6.875</v>
       </c>
       <c r="L87" s="4">
-        <v>7.1634683011414504</v>
+        <v>6.5070000000000006</v>
       </c>
       <c r="M87" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B88" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="C88" s="32" t="s">
+    <row r="88" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B88" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C88" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D88" s="33">
-        <v>7.1184241513166073</v>
-      </c>
-      <c r="E88" s="33">
-        <v>7.25</v>
-      </c>
-      <c r="F88" s="33">
-        <v>0.35122091812309442</v>
-      </c>
-      <c r="G88" s="33">
-        <v>7.61</v>
-      </c>
-      <c r="H88" s="33">
-        <v>6.6</v>
-      </c>
-      <c r="I88" s="33">
-        <v>7.4390000000000001</v>
-      </c>
-      <c r="J88" s="33">
-        <v>7.375</v>
-      </c>
-      <c r="K88" s="33">
-        <v>6.8208541906576983</v>
-      </c>
-      <c r="L88" s="33">
-        <v>6.6637422754817468</v>
-      </c>
-      <c r="M88" s="34">
+      <c r="D88" s="19">
+        <v>7.4520000000000008</v>
+      </c>
+      <c r="E88" s="19">
+        <v>7.35</v>
+      </c>
+      <c r="F88" s="19">
+        <v>0.28584378017838108</v>
+      </c>
+      <c r="G88" s="19">
+        <v>8</v>
+      </c>
+      <c r="H88" s="19">
+        <v>7</v>
+      </c>
+      <c r="I88" s="19">
+        <v>7.7479999999999993</v>
+      </c>
+      <c r="J88" s="19">
+        <v>7.65</v>
+      </c>
+      <c r="K88" s="19">
+        <v>7.3</v>
+      </c>
+      <c r="L88" s="19">
+        <v>7.27</v>
+      </c>
+      <c r="M88" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B89" s="2" t="s">
+    <row r="89" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B89" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>31</v>
       </c>
       <c r="D89" s="4">
-        <v>7.373708572599047</v>
+        <v>7.4520000000000008</v>
       </c>
       <c r="E89" s="4">
+        <v>7.35</v>
+      </c>
+      <c r="F89" s="4">
+        <v>0.28584378017838108</v>
+      </c>
+      <c r="G89" s="4">
+        <v>8</v>
+      </c>
+      <c r="H89" s="4">
+        <v>7</v>
+      </c>
+      <c r="I89" s="4">
+        <v>7.7479999999999993</v>
+      </c>
+      <c r="J89" s="4">
+        <v>7.65</v>
+      </c>
+      <c r="K89" s="4">
         <v>7.3</v>
       </c>
-      <c r="F89" s="4">
-        <v>0.27113660711044629</v>
-      </c>
-      <c r="G89" s="4">
-        <v>7.8357687586832787</v>
-      </c>
-      <c r="H89" s="4">
-        <v>7.04131696730719</v>
-      </c>
-      <c r="I89" s="4">
-        <v>7.7315768758683276</v>
-      </c>
-      <c r="J89" s="4">
-        <v>7.58</v>
-      </c>
-      <c r="K89" s="4">
-        <v>7.2</v>
-      </c>
       <c r="L89" s="4">
-        <v>7.0941316967307184</v>
+        <v>7.27</v>
       </c>
       <c r="M89" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="2:13" ht="18" x14ac:dyDescent="0.4">
+    <row r="90" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B90" s="9"/>
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
@@ -7923,7 +7888,7 @@
       <c r="L90" s="9"/>
       <c r="M90" s="9"/>
     </row>
-    <row r="92" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="14" t="s">
         <v>32</v>
       </c>
@@ -7939,7 +7904,7 @@
       <c r="L92" s="14"/>
       <c r="M92" s="15"/>
     </row>
-    <row r="93" spans="2:13" ht="36" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B93" s="24" t="s">
         <v>1</v>
       </c>
@@ -7977,159 +7942,159 @@
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B94" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="C94" s="32" t="s">
+    <row r="94" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B94" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C94" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D94" s="33">
-        <v>0.38653772524100077</v>
-      </c>
-      <c r="E94" s="33">
-        <v>0.33</v>
-      </c>
-      <c r="F94" s="33">
-        <v>0.18718357643150851</v>
-      </c>
-      <c r="G94" s="33">
-        <v>0.9</v>
-      </c>
-      <c r="H94" s="33">
-        <v>0.23</v>
-      </c>
-      <c r="I94" s="33">
-        <v>0.48183952716900658</v>
-      </c>
-      <c r="J94" s="33">
-        <v>0.34499999999999997</v>
-      </c>
-      <c r="K94" s="33">
-        <v>0.33</v>
-      </c>
-      <c r="L94" s="33">
-        <v>0.29299999999999998</v>
-      </c>
-      <c r="M94" s="40">
+      <c r="D94" s="19">
+        <v>0.83973187627716295</v>
+      </c>
+      <c r="E94" s="19">
+        <v>0.8</v>
+      </c>
+      <c r="F94" s="19">
+        <v>0.4680720957344785</v>
+      </c>
+      <c r="G94" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="H94" s="19">
+        <v>-0.1</v>
+      </c>
+      <c r="I94" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="J94" s="19">
+        <v>1</v>
+      </c>
+      <c r="K94" s="19">
+        <v>0.64620921285602484</v>
+      </c>
+      <c r="L94" s="19">
+        <v>0.45800000000000002</v>
+      </c>
+      <c r="M94" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B95" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D95" s="4">
-        <v>1.2433156069617191</v>
+        <v>0.78507830018468128</v>
       </c>
       <c r="E95" s="4">
-        <v>1.1000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="F95" s="4">
-        <v>0.59966368485053956</v>
+        <v>0.18708942312473201</v>
       </c>
       <c r="G95" s="4">
-        <v>2.56</v>
+        <v>1.06</v>
       </c>
       <c r="H95" s="4">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="I95" s="4">
-        <v>1.8759999999999999</v>
+        <v>1.0400009805428909</v>
       </c>
       <c r="J95" s="4">
-        <v>1.4707890174042979</v>
+        <v>0.88975310093270099</v>
       </c>
       <c r="K95" s="4">
-        <v>0.9325</v>
+        <v>0.625</v>
       </c>
       <c r="L95" s="4">
-        <v>0.80600000000000005</v>
+        <v>0.59</v>
       </c>
       <c r="M95" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B96" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="C96" s="32" t="s">
+    <row r="96" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B96" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C96" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D96" s="33">
-        <v>0.73530041345769348</v>
-      </c>
-      <c r="E96" s="33">
-        <v>0.86</v>
-      </c>
-      <c r="F96" s="33">
-        <v>0.2357610576533625</v>
-      </c>
-      <c r="G96" s="33">
-        <v>0.94</v>
-      </c>
-      <c r="H96" s="33">
-        <v>0.3</v>
-      </c>
-      <c r="I96" s="33">
-        <v>0.93100000000000005</v>
-      </c>
-      <c r="J96" s="33">
-        <v>0.90825103364423365</v>
-      </c>
-      <c r="K96" s="33">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="L96" s="33">
-        <v>0.435</v>
-      </c>
-      <c r="M96" s="34">
+      <c r="D96" s="19">
+        <v>0.76371566150731707</v>
+      </c>
+      <c r="E96" s="19">
+        <v>0.7</v>
+      </c>
+      <c r="F96" s="19">
+        <v>0.31633449629329369</v>
+      </c>
+      <c r="G96" s="19">
+        <v>1.204504732979861</v>
+      </c>
+      <c r="H96" s="19">
+        <v>0.28265188209330988</v>
+      </c>
+      <c r="I96" s="19">
+        <v>1.2004504732979859</v>
+      </c>
+      <c r="J96" s="19">
+        <v>1.0249999999999999</v>
+      </c>
+      <c r="K96" s="19">
+        <v>0.5625</v>
+      </c>
+      <c r="L96" s="19">
+        <v>0.478265188209331</v>
+      </c>
+      <c r="M96" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B97" s="2" t="s">
+    <row r="97" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B97" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D97" s="4">
-        <v>2.7805859612668979</v>
+        <v>3.0180813867745471</v>
       </c>
       <c r="E97" s="4">
-        <v>2.5934106835734601</v>
+        <v>3</v>
       </c>
       <c r="F97" s="4">
-        <v>0.52536049175797173</v>
+        <v>0.26602346951008471</v>
       </c>
       <c r="G97" s="4">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="H97" s="4">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I97" s="4">
-        <v>3.4449999999999998</v>
+        <v>3.32</v>
       </c>
       <c r="J97" s="4">
-        <v>2.9442786841415458</v>
+        <v>3.0750000000000002</v>
       </c>
       <c r="K97" s="4">
-        <v>2.5024999999999999</v>
+        <v>2.9899475030957912</v>
       </c>
       <c r="L97" s="4">
-        <v>2.4500000000000002</v>
+        <v>2.77</v>
       </c>
       <c r="M97" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="2:13" ht="18" x14ac:dyDescent="0.4">
+    <row r="98" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B98" s="9" t="s">
         <v>51</v>
       </c>
@@ -8153,7 +8118,7 @@
     <oddFooter>&amp;C&amp;"Roboto,Normal"Página &amp;P</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="42" min="1" max="12" man="1"/>
+    <brk id="42" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -8164,9 +8129,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.453125" style="1"/>
+    <col min="1" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData/>
   <sheetProtection algorithmName="SHA-512" hashValue="JI4mgXj1vwTu7GkfF4fWYFkbUu0jpGNsZzzBPX3YfGFuPzcxt+Hjcx6rfoqdT04OcRkZuwwlAbTLaGLAEKR43Q==" saltValue="AakVtiLN9zmEwInSrU9sOA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -8448,16 +8413,16 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB7C2FA5-1A6F-45A0-B729-06C123F95F83}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="6b042263-e944-4dfe-97a8-6e4c84e0ae4b"/>
+    <ds:schemaRef ds:uri="b80df5a0-8011-40eb-be96-4c6a59f56b6e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="b80df5a0-8011-40eb-be96-4c6a59f56b6e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="6b042263-e944-4dfe-97a8-6e4c84e0ae4b"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/public/REM/raw/REM.xlsx
+++ b/public/REM/raw/REM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcranet.sharepoint.com/sites/REM/Documentos compartidos/REM/Publicación/Pagina WEB/2026/26 06 Jun/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcranet.sharepoint.com/sites/REM/Documentos compartidos/REM/Publicación/Pagina WEB/2026/26 07 Jul/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="170" documentId="8_{563D5886-1088-4C76-92B3-92AAC244057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3626628D-8F7A-4AAC-8648-63E73DAAB3D0}"/>
+  <xr:revisionPtr revIDLastSave="214" documentId="8_{563D5886-1088-4C76-92B3-92AAC244057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDDF0718-43C5-4625-ABD3-DE8DF8ABE2F2}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="390" windowWidth="24165" windowHeight="14865" xr2:uid="{8A5F0209-F8EA-4E2B-A469-F799AD0A214D}"/>
+    <workbookView xWindow="690" yWindow="1485" windowWidth="12840" windowHeight="13950" xr2:uid="{8A5F0209-F8EA-4E2B-A469-F799AD0A214D}"/>
   </bookViews>
   <sheets>
     <sheet name="Cuadros de resultados" sheetId="19" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="53">
   <si>
     <t>Precios minoristas (IPC nivel general-Nacional; INDEC)</t>
   </si>
@@ -180,38 +180,39 @@
     <t>Trim. III-26</t>
   </si>
   <si>
-    <t>Relevamiento de Expectativas de Mercado (REM)  - BCRA - Junio 2026</t>
-  </si>
-  <si>
-    <t>var. % i.a.; jun-27</t>
-  </si>
-  <si>
-    <t>var. % i.a.; jun-28</t>
-  </si>
-  <si>
-    <t>TNA; %; jun-27</t>
-  </si>
-  <si>
-    <t>$/USD; jun-27</t>
-  </si>
-  <si>
     <t>Trim. IV-26</t>
   </si>
   <si>
-    <t>Fuente: REM - BCRA (jun-26)</t>
+    <t>Relevamiento de Expectativas de Mercado (REM)  - BCRA - Julio 2026</t>
   </si>
   <si>
-    <t>Relevamiento de Expectativas de Mercado (REM)  Top 10 - BCRA - Junio 2026</t>
+    <t>var. % i.a.; jul-27</t>
+  </si>
+  <si>
+    <t>var. % i.a.; jul-28</t>
+  </si>
+  <si>
+    <t>TNA; %; jul-27</t>
+  </si>
+  <si>
+    <t>$/USD; jul-27</t>
+  </si>
+  <si>
+    <t>Fuente: REM - BCRA (jul-26)</t>
+  </si>
+  <si>
+    <t>Relevamiento de Expectativas de Mercado (REM)  Top 10 - BCRA - Julio 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -398,7 +399,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -489,16 +490,19 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="2" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1845,7 +1849,7 @@
   <sheetPr codeName="Hoja1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:M112"/>
+  <dimension ref="B2:AL112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.5703125" style="1" customWidth="1"/>
@@ -1857,11 +1861,21 @@
     <col min="8" max="8" width="18.42578125" style="1" customWidth="1"/>
     <col min="9" max="12" width="14.42578125" style="1" customWidth="1"/>
     <col min="13" max="13" width="18.42578125" style="1" customWidth="1"/>
+    <col min="15" max="25" width="17.28515625" customWidth="1"/>
+    <col min="27" max="27" width="24.5703125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="30.85546875" style="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" customWidth="1"/>
+    <col min="30" max="30" width="16.42578125" style="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" customWidth="1"/>
+    <col min="32" max="32" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="18.42578125" style="1" customWidth="1"/>
+    <col min="34" max="37" width="14.42578125" style="1" customWidth="1"/>
+    <col min="38" max="38" width="18.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:38" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B2" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -1874,8 +1888,20 @@
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
-    </row>
-    <row r="3" spans="2:13" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
+      <c r="AE2" s="11"/>
+      <c r="AF2" s="11"/>
+      <c r="AG2" s="11"/>
+      <c r="AH2" s="11"/>
+      <c r="AI2" s="11"/>
+      <c r="AJ2" s="11"/>
+      <c r="AK2" s="11"/>
+      <c r="AL2" s="11"/>
+    </row>
+    <row r="3" spans="2:38" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
@@ -1888,12 +1914,26 @@
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="AA3" s="11"/>
+      <c r="AB3" s="11"/>
+      <c r="AC3" s="11"/>
+      <c r="AD3" s="11"/>
+      <c r="AE3" s="11"/>
+      <c r="AF3" s="11"/>
+      <c r="AG3" s="11"/>
+      <c r="AH3" s="11"/>
+      <c r="AI3" s="11"/>
+      <c r="AJ3" s="11"/>
+      <c r="AK3" s="11"/>
+      <c r="AL3" s="11"/>
+    </row>
+    <row r="4" spans="2:38" x14ac:dyDescent="0.25">
       <c r="L4" s="12"/>
       <c r="M4" s="13"/>
-    </row>
-    <row r="5" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AK4" s="12"/>
+      <c r="AL4" s="13"/>
+    </row>
+    <row r="5" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
         <v>0</v>
       </c>
@@ -1908,8 +1948,20 @@
       <c r="K5" s="14"/>
       <c r="L5" s="14"/>
       <c r="M5" s="15"/>
-    </row>
-    <row r="6" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="14"/>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="14"/>
+      <c r="AF5" s="14"/>
+      <c r="AG5" s="14"/>
+      <c r="AH5" s="14"/>
+      <c r="AI5" s="14"/>
+      <c r="AJ5" s="14"/>
+      <c r="AK5" s="14"/>
+      <c r="AL5" s="15"/>
+    </row>
+    <row r="6" spans="2:38" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B6" s="16" t="s">
         <v>1</v>
       </c>
@@ -1946,28 +1998,40 @@
       <c r="M6" s="16" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA6" s="16"/>
+      <c r="AB6" s="16"/>
+      <c r="AC6" s="16"/>
+      <c r="AD6" s="16"/>
+      <c r="AE6" s="16"/>
+      <c r="AF6" s="16"/>
+      <c r="AG6" s="16"/>
+      <c r="AH6" s="16"/>
+      <c r="AI6" s="16"/>
+      <c r="AJ6" s="16"/>
+      <c r="AK6" s="16"/>
+      <c r="AL6" s="16"/>
+    </row>
+    <row r="7" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B7" s="17">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="19">
-        <v>1.9550000000000001</v>
+        <v>1.95</v>
       </c>
       <c r="E7" s="19">
-        <v>1.9664205285178511</v>
+        <v>1.933473834898124</v>
       </c>
       <c r="F7" s="19">
-        <v>0.1161089710294419</v>
+        <v>0.12056181263309521</v>
       </c>
       <c r="G7" s="19">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="H7" s="19">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="I7" s="19">
         <v>2.1</v>
@@ -1976,56 +2040,80 @@
         <v>2</v>
       </c>
       <c r="K7" s="19">
-        <v>1.9</v>
+        <v>1.8986566050117171</v>
       </c>
       <c r="L7" s="19">
-        <v>1.840837887420995</v>
+        <v>1.8</v>
       </c>
       <c r="M7" s="20">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="AA7" s="17"/>
+      <c r="AB7" s="18"/>
+      <c r="AC7" s="19"/>
+      <c r="AD7" s="19"/>
+      <c r="AE7" s="19"/>
+      <c r="AF7" s="19"/>
+      <c r="AG7" s="19"/>
+      <c r="AH7" s="19"/>
+      <c r="AI7" s="19"/>
+      <c r="AJ7" s="19"/>
+      <c r="AK7" s="19"/>
+      <c r="AL7" s="20"/>
+    </row>
+    <row r="8" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="4">
-        <v>1.9516446347829639</v>
+        <v>1.8</v>
       </c>
       <c r="E8" s="4">
-        <v>1.936558955401265</v>
+        <v>1.764970064037616</v>
       </c>
       <c r="F8" s="4">
-        <v>0.18928608530078569</v>
+        <v>0.1825673854004142</v>
       </c>
       <c r="G8" s="4">
-        <v>2.34</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H8" s="4">
-        <v>1.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I8" s="4">
-        <v>2.2000000000000002</v>
+        <v>1.9288888605224139</v>
       </c>
       <c r="J8" s="4">
-        <v>2.0201713687336871</v>
+        <v>1.85</v>
       </c>
       <c r="K8" s="4">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="L8" s="4">
-        <v>1.786</v>
+        <v>1.6</v>
       </c>
       <c r="M8" s="5">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="AA8" s="2"/>
+      <c r="AB8" s="3"/>
+      <c r="AC8" s="4"/>
+      <c r="AD8" s="4"/>
+      <c r="AE8" s="4"/>
+      <c r="AF8" s="4"/>
+      <c r="AG8" s="4"/>
+      <c r="AH8" s="4"/>
+      <c r="AI8" s="4"/>
+      <c r="AJ8" s="4"/>
+      <c r="AK8" s="4"/>
+      <c r="AL8" s="5"/>
+    </row>
+    <row r="9" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B9" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>13</v>
@@ -2034,60 +2122,72 @@
         <v>1.8</v>
       </c>
       <c r="E9" s="19">
-        <v>1.802340140820764</v>
+        <v>1.752248579067857</v>
       </c>
       <c r="F9" s="19">
-        <v>0.2696071807402371</v>
+        <v>0.2392173124436853</v>
       </c>
       <c r="G9" s="19">
-        <v>2.46</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="H9" s="19">
-        <v>1.1000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="I9" s="19">
-        <v>2.161110515359042</v>
+        <v>2</v>
       </c>
       <c r="J9" s="19">
-        <v>1.945857933540875</v>
+        <v>1.9</v>
       </c>
       <c r="K9" s="19">
-        <v>1.6400050752592601</v>
+        <v>1.65</v>
       </c>
       <c r="L9" s="19">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="M9" s="20">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="AA9" s="17"/>
+      <c r="AB9" s="18"/>
+      <c r="AC9" s="19"/>
+      <c r="AD9" s="19"/>
+      <c r="AE9" s="19"/>
+      <c r="AF9" s="19"/>
+      <c r="AG9" s="19"/>
+      <c r="AH9" s="19"/>
+      <c r="AI9" s="19"/>
+      <c r="AJ9" s="19"/>
+      <c r="AK9" s="19"/>
+      <c r="AL9" s="20"/>
+    </row>
+    <row r="10" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="4">
-        <v>1.8</v>
+        <v>1.655047763820076</v>
       </c>
       <c r="E10" s="4">
-        <v>1.7878046021872069</v>
+        <v>1.670086538000408</v>
       </c>
       <c r="F10" s="4">
-        <v>0.30804572741485581</v>
+        <v>0.25858579750844118</v>
       </c>
       <c r="G10" s="4">
-        <v>2.52</v>
+        <v>2.037874061555534</v>
       </c>
       <c r="H10" s="4">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="I10" s="4">
-        <v>2.1139999999999999</v>
+        <v>1.9229965922972601</v>
       </c>
       <c r="J10" s="4">
-        <v>1.9755489354367599</v>
+        <v>1.88</v>
       </c>
       <c r="K10" s="4">
         <v>1.6</v>
@@ -2096,200 +2196,272 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="5">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="3"/>
+      <c r="AC10" s="4"/>
+      <c r="AD10" s="4"/>
+      <c r="AE10" s="4"/>
+      <c r="AF10" s="4"/>
+      <c r="AG10" s="4"/>
+      <c r="AH10" s="4"/>
+      <c r="AI10" s="4"/>
+      <c r="AJ10" s="4"/>
+      <c r="AK10" s="4"/>
+      <c r="AL10" s="5"/>
+    </row>
+    <row r="11" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B11" s="17">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="19">
-        <v>1.7450000000000001</v>
+        <v>1.633373609332045</v>
       </c>
       <c r="E11" s="19">
-        <v>1.697490920347835</v>
+        <v>1.6227503638802989</v>
       </c>
       <c r="F11" s="19">
-        <v>0.30338151539088509</v>
+        <v>0.2465148605450535</v>
       </c>
       <c r="G11" s="19">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="H11" s="19">
         <v>0.6</v>
       </c>
       <c r="I11" s="19">
-        <v>1.9951902648797131</v>
+        <v>1.8879999999999999</v>
       </c>
       <c r="J11" s="19">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="K11" s="19">
-        <v>1.5475000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="L11" s="19">
-        <v>1.390157133155534</v>
+        <v>1.4</v>
       </c>
       <c r="M11" s="20">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="18"/>
+      <c r="AC11" s="19"/>
+      <c r="AD11" s="19"/>
+      <c r="AE11" s="19"/>
+      <c r="AF11" s="19"/>
+      <c r="AG11" s="19"/>
+      <c r="AH11" s="19"/>
+      <c r="AI11" s="19"/>
+      <c r="AJ11" s="19"/>
+      <c r="AK11" s="19"/>
+      <c r="AL11" s="20"/>
+    </row>
+    <row r="12" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B12" s="2">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="4">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="E12" s="4">
-        <v>1.634948641804935</v>
+        <v>1.712493045747693</v>
       </c>
       <c r="F12" s="4">
-        <v>0.27481747911105769</v>
+        <v>0.26545533695012991</v>
       </c>
       <c r="G12" s="4">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
       <c r="H12" s="4">
         <v>0.6</v>
       </c>
       <c r="I12" s="4">
-        <v>1.896626177363119</v>
+        <v>2</v>
       </c>
       <c r="J12" s="4">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="K12" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="L12" s="4">
         <v>1.5</v>
       </c>
-      <c r="L12" s="4">
-        <v>1.3</v>
-      </c>
       <c r="M12" s="5">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="AA12" s="2"/>
+      <c r="AB12" s="3"/>
+      <c r="AC12" s="4"/>
+      <c r="AD12" s="4"/>
+      <c r="AE12" s="4"/>
+      <c r="AF12" s="4"/>
+      <c r="AG12" s="4"/>
+      <c r="AH12" s="4"/>
+      <c r="AI12" s="4"/>
+      <c r="AJ12" s="4"/>
+      <c r="AK12" s="4"/>
+      <c r="AL12" s="5"/>
+    </row>
+    <row r="13" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B13" s="17">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="19">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="E13" s="19">
-        <v>1.720052678027685</v>
+        <v>1.626027117751248</v>
       </c>
       <c r="F13" s="19">
-        <v>0.31479137221634268</v>
+        <v>0.33192967756681369</v>
       </c>
       <c r="G13" s="19">
-        <v>2.4500000000000002</v>
+        <v>2.5</v>
       </c>
       <c r="H13" s="19">
         <v>0.6</v>
       </c>
       <c r="I13" s="19">
-        <v>2.076000000000001</v>
+        <v>1.9159999999999999</v>
       </c>
       <c r="J13" s="19">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="K13" s="19">
         <v>1.5</v>
       </c>
       <c r="L13" s="19">
-        <v>1.421</v>
+        <v>1.2426076570096241</v>
       </c>
       <c r="M13" s="20">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="18"/>
+      <c r="AC13" s="19"/>
+      <c r="AD13" s="19"/>
+      <c r="AE13" s="19"/>
+      <c r="AF13" s="19"/>
+      <c r="AG13" s="19"/>
+      <c r="AH13" s="19"/>
+      <c r="AI13" s="19"/>
+      <c r="AJ13" s="19"/>
+      <c r="AK13" s="19"/>
+      <c r="AL13" s="20"/>
+    </row>
+    <row r="14" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="4">
-        <v>22.3</v>
+        <v>21.8</v>
       </c>
       <c r="E14" s="4">
-        <v>22.039889923634519</v>
+        <v>21.180990767499178</v>
       </c>
       <c r="F14" s="4">
-        <v>3.662659117303086</v>
+        <v>3.4759614618547729</v>
       </c>
       <c r="G14" s="4">
-        <v>28.5</v>
+        <v>26.2</v>
       </c>
       <c r="H14" s="4">
-        <v>9.15</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="I14" s="4">
-        <v>25.8</v>
+        <v>24.5</v>
       </c>
       <c r="J14" s="4">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="K14" s="4">
-        <v>20.98</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="L14" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M14" s="5">
         <v>41</v>
       </c>
-    </row>
-    <row r="15" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA14" s="2"/>
+      <c r="AB14" s="3"/>
+      <c r="AC14" s="4"/>
+      <c r="AD14" s="4"/>
+      <c r="AE14" s="4"/>
+      <c r="AF14" s="4"/>
+      <c r="AG14" s="4"/>
+      <c r="AH14" s="4"/>
+      <c r="AI14" s="4"/>
+      <c r="AJ14" s="4"/>
+      <c r="AK14" s="4"/>
+      <c r="AL14" s="5"/>
+    </row>
+    <row r="15" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B15" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" s="19">
-        <v>16.899999999999999</v>
+        <v>16.630484330289651</v>
       </c>
       <c r="E15" s="19">
-        <v>16.942094962712801</v>
+        <v>16.600625041112181</v>
       </c>
       <c r="F15" s="19">
-        <v>4.0563315999929266</v>
+        <v>4.0314695666029747</v>
       </c>
       <c r="G15" s="19">
-        <v>24.34</v>
+        <v>22.8</v>
       </c>
       <c r="H15" s="19">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="I15" s="19">
-        <v>21.9</v>
+        <v>21.525748390149399</v>
       </c>
       <c r="J15" s="19">
-        <v>19.51083680194472</v>
+        <v>19.226594370956239</v>
       </c>
       <c r="K15" s="19">
-        <v>15.226294058910479</v>
+        <v>15.03202164819572</v>
       </c>
       <c r="L15" s="19">
-        <v>13.008992230500001</v>
+        <v>12.099021892811351</v>
       </c>
       <c r="M15" s="20">
         <v>36</v>
       </c>
-    </row>
-    <row r="16" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA15" s="17"/>
+      <c r="AB15" s="18"/>
+      <c r="AC15" s="19"/>
+      <c r="AD15" s="19"/>
+      <c r="AE15" s="19"/>
+      <c r="AF15" s="19"/>
+      <c r="AG15" s="19"/>
+      <c r="AH15" s="19"/>
+      <c r="AI15" s="19"/>
+      <c r="AJ15" s="19"/>
+      <c r="AK15" s="19"/>
+      <c r="AL15" s="20"/>
+    </row>
+    <row r="16" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>36</v>
       </c>
@@ -2297,37 +2469,49 @@
         <v>16</v>
       </c>
       <c r="D16" s="4">
-        <v>30.02</v>
+        <v>29.79</v>
       </c>
       <c r="E16" s="4">
-        <v>29.897118023566641</v>
+        <v>29.616954427741248</v>
       </c>
       <c r="F16" s="4">
-        <v>1.9252913817741519</v>
+        <v>1.461595598020436</v>
       </c>
       <c r="G16" s="4">
-        <v>33.9</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="H16" s="4">
-        <v>22.9</v>
+        <v>23.17</v>
       </c>
       <c r="I16" s="4">
-        <v>31.889125483192679</v>
+        <v>30.96</v>
       </c>
       <c r="J16" s="4">
-        <v>30.90710907173888</v>
+        <v>30.4</v>
       </c>
       <c r="K16" s="4">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="L16" s="4">
-        <v>28.074038221730721</v>
+        <v>28.327999999999999</v>
       </c>
       <c r="M16" s="5">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="AA16" s="2"/>
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="4"/>
+      <c r="AD16" s="4"/>
+      <c r="AE16" s="4"/>
+      <c r="AF16" s="4"/>
+      <c r="AG16" s="4"/>
+      <c r="AH16" s="4"/>
+      <c r="AI16" s="4"/>
+      <c r="AJ16" s="4"/>
+      <c r="AK16" s="4"/>
+      <c r="AL16" s="5"/>
+    </row>
+    <row r="17" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B17" s="21" t="s">
         <v>37</v>
       </c>
@@ -2338,34 +2522,46 @@
         <v>20</v>
       </c>
       <c r="E17" s="19">
-        <v>20.184284829234219</v>
+        <v>20.009353973013759</v>
       </c>
       <c r="F17" s="19">
-        <v>4.0963186740403508</v>
+        <v>3.9992963057440369</v>
       </c>
       <c r="G17" s="19">
-        <v>26.7</v>
+        <v>27</v>
       </c>
       <c r="H17" s="19">
         <v>8.4</v>
       </c>
       <c r="I17" s="19">
-        <v>25.72</v>
+        <v>25</v>
       </c>
       <c r="J17" s="19">
-        <v>22.7</v>
+        <v>22.45</v>
       </c>
       <c r="K17" s="19">
-        <v>18.572500000000002</v>
+        <v>18.645</v>
       </c>
       <c r="L17" s="19">
-        <v>16.402000000000001</v>
+        <v>16.228449351366731</v>
       </c>
       <c r="M17" s="20">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="AA17" s="21"/>
+      <c r="AB17" s="18"/>
+      <c r="AC17" s="19"/>
+      <c r="AD17" s="19"/>
+      <c r="AE17" s="19"/>
+      <c r="AF17" s="19"/>
+      <c r="AG17" s="19"/>
+      <c r="AH17" s="19"/>
+      <c r="AI17" s="19"/>
+      <c r="AJ17" s="19"/>
+      <c r="AK17" s="19"/>
+      <c r="AL17" s="20"/>
+    </row>
+    <row r="18" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
         <v>38</v>
       </c>
@@ -2373,37 +2569,49 @@
         <v>39</v>
       </c>
       <c r="D18" s="4">
-        <v>14.15</v>
+        <v>14.129585438581721</v>
       </c>
       <c r="E18" s="4">
-        <v>13.706728868940489</v>
+        <v>13.587795923714291</v>
       </c>
       <c r="F18" s="4">
-        <v>4.0555276004387926</v>
+        <v>4.1218821019266727</v>
       </c>
       <c r="G18" s="4">
-        <v>23.579343539967489</v>
+        <v>23.25761781839218</v>
       </c>
       <c r="H18" s="4">
         <v>2.4</v>
       </c>
       <c r="I18" s="4">
-        <v>17.97</v>
+        <v>18</v>
       </c>
       <c r="J18" s="4">
-        <v>15.664999999999999</v>
+        <v>15.34473120912932</v>
       </c>
       <c r="K18" s="4">
-        <v>12.070710419534601</v>
+        <v>12.03</v>
       </c>
       <c r="L18" s="4">
-        <v>8.7776885623644318</v>
+        <v>7.9351282624947812</v>
       </c>
       <c r="M18" s="5">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="AA18" s="6"/>
+      <c r="AB18" s="3"/>
+      <c r="AC18" s="4"/>
+      <c r="AD18" s="4"/>
+      <c r="AE18" s="4"/>
+      <c r="AF18" s="4"/>
+      <c r="AG18" s="4"/>
+      <c r="AH18" s="4"/>
+      <c r="AI18" s="4"/>
+      <c r="AJ18" s="4"/>
+      <c r="AK18" s="4"/>
+      <c r="AL18" s="5"/>
+    </row>
+    <row r="21" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B21" s="14" t="s">
         <v>18</v>
       </c>
@@ -2418,8 +2626,20 @@
       <c r="K21" s="14"/>
       <c r="L21" s="14"/>
       <c r="M21" s="15"/>
-    </row>
-    <row r="22" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="AA21" s="14"/>
+      <c r="AB21" s="14"/>
+      <c r="AC21" s="14"/>
+      <c r="AD21" s="14"/>
+      <c r="AE21" s="14"/>
+      <c r="AF21" s="14"/>
+      <c r="AG21" s="14"/>
+      <c r="AH21" s="14"/>
+      <c r="AI21" s="14"/>
+      <c r="AJ21" s="14"/>
+      <c r="AK21" s="14"/>
+      <c r="AL21" s="15"/>
+    </row>
+    <row r="22" spans="2:38" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B22" s="16" t="s">
         <v>1</v>
       </c>
@@ -2456,350 +2676,470 @@
       <c r="M22" s="16" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="23" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA22" s="16"/>
+      <c r="AB22" s="16"/>
+      <c r="AC22" s="16"/>
+      <c r="AD22" s="16"/>
+      <c r="AE22" s="16"/>
+      <c r="AF22" s="16"/>
+      <c r="AG22" s="16"/>
+      <c r="AH22" s="16"/>
+      <c r="AI22" s="16"/>
+      <c r="AJ22" s="16"/>
+      <c r="AK22" s="16"/>
+      <c r="AL22" s="16"/>
+    </row>
+    <row r="23" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B23" s="17">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="19">
-        <v>1.903477732686309</v>
+        <v>1.8</v>
       </c>
       <c r="E23" s="19">
-        <v>1.9472671514439659</v>
+        <v>1.785486950066997</v>
       </c>
       <c r="F23" s="19">
-        <v>0.23513609022150711</v>
+        <v>0.1864529594445816</v>
       </c>
       <c r="G23" s="19">
-        <v>2.7</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="H23" s="19">
-        <v>1.4690816129342199</v>
+        <v>1.4702434016336421</v>
       </c>
       <c r="I23" s="19">
-        <v>2.226</v>
+        <v>2.0205861261459641</v>
       </c>
       <c r="J23" s="19">
-        <v>2.02811442939521</v>
+        <v>1.9</v>
       </c>
       <c r="K23" s="19">
-        <v>1.8</v>
+        <v>1.645</v>
       </c>
       <c r="L23" s="19">
-        <v>1.718826509086121</v>
+        <v>1.543436185502151</v>
       </c>
       <c r="M23" s="20">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="AA23" s="17"/>
+      <c r="AB23" s="18"/>
+      <c r="AC23" s="19"/>
+      <c r="AD23" s="19"/>
+      <c r="AE23" s="19"/>
+      <c r="AF23" s="19"/>
+      <c r="AG23" s="19"/>
+      <c r="AH23" s="19"/>
+      <c r="AI23" s="19"/>
+      <c r="AJ23" s="19"/>
+      <c r="AK23" s="19"/>
+      <c r="AL23" s="20"/>
+    </row>
+    <row r="24" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B24" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="4">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="E24" s="4">
-        <v>1.8957187139685989</v>
+        <v>1.7067747432585221</v>
       </c>
       <c r="F24" s="4">
-        <v>0.2363113913001002</v>
+        <v>0.2178059457958709</v>
       </c>
       <c r="G24" s="4">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="H24" s="4">
-        <v>1.5521275018822309</v>
+        <v>1.2</v>
       </c>
       <c r="I24" s="4">
-        <v>2.2000000000000002</v>
+        <v>1.98</v>
       </c>
       <c r="J24" s="4">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K24" s="4">
-        <v>1.7</v>
+        <v>1.5740316522551969</v>
       </c>
       <c r="L24" s="4">
-        <v>1.6080000000000001</v>
+        <v>1.5023142839063599</v>
       </c>
       <c r="M24" s="5">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="AA24" s="2"/>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="4"/>
+      <c r="AD24" s="4"/>
+      <c r="AE24" s="4"/>
+      <c r="AF24" s="4"/>
+      <c r="AG24" s="4"/>
+      <c r="AH24" s="4"/>
+      <c r="AI24" s="4"/>
+      <c r="AJ24" s="4"/>
+      <c r="AK24" s="4"/>
+      <c r="AL24" s="5"/>
+    </row>
+    <row r="25" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B25" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="19">
-        <v>1.79</v>
+        <v>1.67699493076314</v>
       </c>
       <c r="E25" s="19">
-        <v>1.831990921046516</v>
+        <v>1.6776263088831129</v>
       </c>
       <c r="F25" s="19">
-        <v>0.30099988147065587</v>
+        <v>0.24605749906018201</v>
       </c>
       <c r="G25" s="19">
-        <v>2.54</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H25" s="19">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="I25" s="19">
-        <v>2.3125492378601198</v>
+        <v>1.95</v>
       </c>
       <c r="J25" s="19">
-        <v>1.9</v>
+        <v>1.8302044796835339</v>
       </c>
       <c r="K25" s="19">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="L25" s="19">
-        <v>1.533851268174919</v>
+        <v>1.409</v>
       </c>
       <c r="M25" s="20">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="AA25" s="17"/>
+      <c r="AB25" s="18"/>
+      <c r="AC25" s="19"/>
+      <c r="AD25" s="19"/>
+      <c r="AE25" s="19"/>
+      <c r="AF25" s="19"/>
+      <c r="AG25" s="19"/>
+      <c r="AH25" s="19"/>
+      <c r="AI25" s="19"/>
+      <c r="AJ25" s="19"/>
+      <c r="AK25" s="19"/>
+      <c r="AL25" s="20"/>
+    </row>
+    <row r="26" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B26" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="4">
-        <v>1.78</v>
+        <v>1.630491543516168</v>
       </c>
       <c r="E26" s="4">
-        <v>1.764020453231395</v>
+        <v>1.6130515351915991</v>
       </c>
       <c r="F26" s="4">
-        <v>0.27311116991048312</v>
+        <v>0.2364910588883041</v>
       </c>
       <c r="G26" s="4">
-        <v>2.36</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H26" s="4">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I26" s="4">
-        <v>2.112773248118597</v>
+        <v>1.89</v>
       </c>
       <c r="J26" s="4">
-        <v>1.895</v>
+        <v>1.774262298947926</v>
       </c>
       <c r="K26" s="4">
-        <v>1.6</v>
+        <v>1.4597770612984591</v>
       </c>
       <c r="L26" s="4">
-        <v>1.5</v>
+        <v>1.3049999999999999</v>
       </c>
       <c r="M26" s="5">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="AA26" s="2"/>
+      <c r="AB26" s="3"/>
+      <c r="AC26" s="4"/>
+      <c r="AD26" s="4"/>
+      <c r="AE26" s="4"/>
+      <c r="AF26" s="4"/>
+      <c r="AG26" s="4"/>
+      <c r="AH26" s="4"/>
+      <c r="AI26" s="4"/>
+      <c r="AJ26" s="4"/>
+      <c r="AK26" s="4"/>
+      <c r="AL26" s="5"/>
+    </row>
+    <row r="27" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B27" s="17">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C27" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="19">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="E27" s="19">
-        <v>1.6862091218637509</v>
+        <v>1.5879010595808729</v>
       </c>
       <c r="F27" s="19">
-        <v>0.24467129630068041</v>
+        <v>0.24426048261540181</v>
       </c>
       <c r="G27" s="19">
         <v>2.2000000000000002</v>
       </c>
       <c r="H27" s="19">
-        <v>1.1000000000000001</v>
+        <v>1.1393514175688011</v>
       </c>
       <c r="I27" s="19">
-        <v>1.93</v>
+        <v>1.85498125</v>
       </c>
       <c r="J27" s="19">
-        <v>1.820125</v>
+        <v>1.7247221361084399</v>
       </c>
       <c r="K27" s="19">
-        <v>1.5249999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="L27" s="19">
-        <v>1.4</v>
+        <v>1.2849999999999999</v>
       </c>
       <c r="M27" s="20">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="AA27" s="17"/>
+      <c r="AB27" s="18"/>
+      <c r="AC27" s="19"/>
+      <c r="AD27" s="19"/>
+      <c r="AE27" s="19"/>
+      <c r="AF27" s="19"/>
+      <c r="AG27" s="19"/>
+      <c r="AH27" s="19"/>
+      <c r="AI27" s="19"/>
+      <c r="AJ27" s="19"/>
+      <c r="AK27" s="19"/>
+      <c r="AL27" s="20"/>
+    </row>
+    <row r="28" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B28" s="2">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D28" s="4">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="E28" s="4">
-        <v>1.6308224060474159</v>
+        <v>1.6649492261873251</v>
       </c>
       <c r="F28" s="4">
-        <v>0.2452663861947513</v>
+        <v>0.2556392926219378</v>
       </c>
       <c r="G28" s="4">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H28" s="4">
-        <v>1.1299999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="I28" s="4">
-        <v>1.89968566144053</v>
+        <v>2</v>
       </c>
       <c r="J28" s="4">
-        <v>1.797156600306359</v>
+        <v>1.805901493227845</v>
       </c>
       <c r="K28" s="4">
-        <v>1.5</v>
+        <v>1.4775</v>
       </c>
       <c r="L28" s="4">
-        <v>1.3</v>
+        <v>1.383031305275306</v>
       </c>
       <c r="M28" s="5">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="AA28" s="2"/>
+      <c r="AB28" s="3"/>
+      <c r="AC28" s="4"/>
+      <c r="AD28" s="4"/>
+      <c r="AE28" s="4"/>
+      <c r="AF28" s="4"/>
+      <c r="AG28" s="4"/>
+      <c r="AH28" s="4"/>
+      <c r="AI28" s="4"/>
+      <c r="AJ28" s="4"/>
+      <c r="AK28" s="4"/>
+      <c r="AL28" s="5"/>
+    </row>
+    <row r="29" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B29" s="17">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D29" s="19">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="E29" s="19">
-        <v>1.6875852417773971</v>
+        <v>1.5904222381028641</v>
       </c>
       <c r="F29" s="19">
-        <v>0.27447246158208</v>
+        <v>0.2906592807395359</v>
       </c>
       <c r="G29" s="19">
         <v>2.2000000000000002</v>
       </c>
       <c r="H29" s="19">
-        <v>1.03</v>
+        <v>0.9482479817222389</v>
       </c>
       <c r="I29" s="19">
-        <v>2</v>
+        <v>1.9850000000000001</v>
       </c>
       <c r="J29" s="19">
-        <v>1.8132946143661139</v>
+        <v>1.7</v>
       </c>
       <c r="K29" s="19">
-        <v>1.479076361329672</v>
+        <v>1.4137500000000001</v>
       </c>
       <c r="L29" s="19">
-        <v>1.390919741233396</v>
+        <v>1.231887360362572</v>
       </c>
       <c r="M29" s="20">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="AA29" s="17"/>
+      <c r="AB29" s="18"/>
+      <c r="AC29" s="19"/>
+      <c r="AD29" s="19"/>
+      <c r="AE29" s="19"/>
+      <c r="AF29" s="19"/>
+      <c r="AG29" s="19"/>
+      <c r="AH29" s="19"/>
+      <c r="AI29" s="19"/>
+      <c r="AJ29" s="19"/>
+      <c r="AK29" s="19"/>
+      <c r="AL29" s="20"/>
+    </row>
+    <row r="30" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D30" s="4">
-        <v>21.8</v>
+        <v>20.907295710087649</v>
       </c>
       <c r="E30" s="4">
-        <v>21.878786486212778</v>
+        <v>20.546536655762679</v>
       </c>
       <c r="F30" s="4">
-        <v>3.3114132753200192</v>
+        <v>3.3204255065378909</v>
       </c>
       <c r="G30" s="4">
-        <v>28.5</v>
+        <v>27.6</v>
       </c>
       <c r="H30" s="4">
-        <v>13.20549237655384</v>
+        <v>11.83009467033758</v>
       </c>
       <c r="I30" s="4">
-        <v>25.78</v>
+        <v>23.86</v>
       </c>
       <c r="J30" s="4">
-        <v>23.636934539457719</v>
+        <v>23.02678496332376</v>
       </c>
       <c r="K30" s="4">
-        <v>20.74</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="L30" s="4">
-        <v>18.78</v>
+        <v>16.8771131737088</v>
       </c>
       <c r="M30" s="5">
         <v>33</v>
       </c>
-    </row>
-    <row r="31" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA30" s="2"/>
+      <c r="AB30" s="3"/>
+      <c r="AC30" s="4"/>
+      <c r="AD30" s="4"/>
+      <c r="AE30" s="4"/>
+      <c r="AF30" s="4"/>
+      <c r="AG30" s="4"/>
+      <c r="AH30" s="4"/>
+      <c r="AI30" s="4"/>
+      <c r="AJ30" s="4"/>
+      <c r="AK30" s="4"/>
+      <c r="AL30" s="5"/>
+    </row>
+    <row r="31" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B31" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D31" s="19">
-        <v>16.36</v>
+        <v>16.34</v>
       </c>
       <c r="E31" s="19">
-        <v>16.35573137512819</v>
+        <v>16.169021842050832</v>
       </c>
       <c r="F31" s="19">
-        <v>4.5378577126919017</v>
+        <v>4.6459220795595417</v>
       </c>
       <c r="G31" s="19">
         <v>23.7</v>
       </c>
       <c r="H31" s="19">
-        <v>4.5999999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I31" s="19">
-        <v>21.952000000000002</v>
+        <v>22</v>
       </c>
       <c r="J31" s="19">
-        <v>18.68601058009952</v>
+        <v>19.959696927407592</v>
       </c>
       <c r="K31" s="19">
-        <v>14.48819041704337</v>
+        <v>13.95509590181944</v>
       </c>
       <c r="L31" s="19">
-        <v>8.844808370082113</v>
+        <v>9.1849508286797388</v>
       </c>
       <c r="M31" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="AA31" s="17"/>
+      <c r="AB31" s="18"/>
+      <c r="AC31" s="19"/>
+      <c r="AD31" s="19"/>
+      <c r="AE31" s="19"/>
+      <c r="AF31" s="19"/>
+      <c r="AG31" s="19"/>
+      <c r="AH31" s="19"/>
+      <c r="AI31" s="19"/>
+      <c r="AJ31" s="19"/>
+      <c r="AK31" s="19"/>
+      <c r="AL31" s="20"/>
+    </row>
+    <row r="32" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
         <v>36</v>
       </c>
@@ -2807,37 +3147,49 @@
         <v>16</v>
       </c>
       <c r="D32" s="4">
-        <v>28.75</v>
+        <v>27.516255022985199</v>
       </c>
       <c r="E32" s="4">
-        <v>28.75636017403901</v>
+        <v>27.7366359344215</v>
       </c>
       <c r="F32" s="4">
-        <v>1.9309470179281389</v>
+        <v>1.677441103007199</v>
       </c>
       <c r="G32" s="4">
-        <v>34</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="H32" s="4">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="I32" s="4">
-        <v>30.83952597513721</v>
+        <v>29.22567485924213</v>
       </c>
       <c r="J32" s="4">
-        <v>29.683887744808199</v>
+        <v>28.819719942103401</v>
       </c>
       <c r="K32" s="4">
-        <v>27.802381154589799</v>
+        <v>26.78499963755613</v>
       </c>
       <c r="L32" s="4">
-        <v>26.946699668243241</v>
+        <v>25.89</v>
       </c>
       <c r="M32" s="5">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="AA32" s="2"/>
+      <c r="AB32" s="3"/>
+      <c r="AC32" s="4"/>
+      <c r="AD32" s="4"/>
+      <c r="AE32" s="4"/>
+      <c r="AF32" s="4"/>
+      <c r="AG32" s="4"/>
+      <c r="AH32" s="4"/>
+      <c r="AI32" s="4"/>
+      <c r="AJ32" s="4"/>
+      <c r="AK32" s="4"/>
+      <c r="AL32" s="5"/>
+    </row>
+    <row r="33" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B33" s="21" t="s">
         <v>37</v>
       </c>
@@ -2845,37 +3197,49 @@
         <v>17</v>
       </c>
       <c r="D33" s="19">
-        <v>19.957775051980061</v>
+        <v>19.719393854815181</v>
       </c>
       <c r="E33" s="19">
-        <v>19.74868672866695</v>
+        <v>19.353625836756901</v>
       </c>
       <c r="F33" s="19">
-        <v>4.0523777982335396</v>
+        <v>3.928542018898975</v>
       </c>
       <c r="G33" s="19">
-        <v>26.07</v>
+        <v>25</v>
       </c>
       <c r="H33" s="19">
         <v>8.9</v>
       </c>
       <c r="I33" s="19">
-        <v>24.57</v>
+        <v>24.577513220304819</v>
       </c>
       <c r="J33" s="19">
-        <v>22.63</v>
+        <v>21.79217244187727</v>
       </c>
       <c r="K33" s="19">
-        <v>18.237500000000001</v>
+        <v>17.75</v>
       </c>
       <c r="L33" s="19">
-        <v>14.315516902332149</v>
+        <v>14.3767578157209</v>
       </c>
       <c r="M33" s="20">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="AA33" s="21"/>
+      <c r="AB33" s="18"/>
+      <c r="AC33" s="19"/>
+      <c r="AD33" s="19"/>
+      <c r="AE33" s="19"/>
+      <c r="AF33" s="19"/>
+      <c r="AG33" s="19"/>
+      <c r="AH33" s="19"/>
+      <c r="AI33" s="19"/>
+      <c r="AJ33" s="19"/>
+      <c r="AK33" s="19"/>
+      <c r="AL33" s="20"/>
+    </row>
+    <row r="34" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="s">
         <v>38</v>
       </c>
@@ -2883,41 +3247,55 @@
         <v>39</v>
       </c>
       <c r="D34" s="4">
-        <v>14</v>
+        <v>13.55</v>
       </c>
       <c r="E34" s="4">
-        <v>13.41431360717104</v>
+        <v>13.10074803637859</v>
       </c>
       <c r="F34" s="4">
-        <v>4.3452932966067088</v>
+        <v>4.4370162501625687</v>
       </c>
       <c r="G34" s="4">
-        <v>22.656415720267219</v>
+        <v>22.08940474568584</v>
       </c>
       <c r="H34" s="4">
         <v>1.8</v>
       </c>
       <c r="I34" s="4">
-        <v>17.2</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="J34" s="4">
-        <v>15.04</v>
+        <v>15.302096813694</v>
       </c>
       <c r="K34" s="4">
-        <v>11.93</v>
+        <v>11.18965259023531</v>
       </c>
       <c r="L34" s="4">
-        <v>7.940551090791045</v>
+        <v>7.5502458255406797</v>
       </c>
       <c r="M34" s="5">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="36" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="AA34" s="6"/>
+      <c r="AB34" s="3"/>
+      <c r="AC34" s="4"/>
+      <c r="AD34" s="4"/>
+      <c r="AE34" s="4"/>
+      <c r="AF34" s="4"/>
+      <c r="AG34" s="4"/>
+      <c r="AH34" s="4"/>
+      <c r="AI34" s="4"/>
+      <c r="AJ34" s="4"/>
+      <c r="AK34" s="4"/>
+      <c r="AL34" s="5"/>
+    </row>
+    <row r="36" spans="2:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B36" s="22"/>
       <c r="C36" s="23"/>
-    </row>
-    <row r="37" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA36" s="22"/>
+      <c r="AB36" s="23"/>
+    </row>
+    <row r="37" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B37" s="14" t="s">
         <v>35</v>
       </c>
@@ -2932,8 +3310,20 @@
       <c r="K37" s="14"/>
       <c r="L37" s="14"/>
       <c r="M37" s="15"/>
-    </row>
-    <row r="38" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="AA37" s="14"/>
+      <c r="AB37" s="14"/>
+      <c r="AC37" s="14"/>
+      <c r="AD37" s="14"/>
+      <c r="AE37" s="14"/>
+      <c r="AF37" s="14"/>
+      <c r="AG37" s="14"/>
+      <c r="AH37" s="14"/>
+      <c r="AI37" s="14"/>
+      <c r="AJ37" s="14"/>
+      <c r="AK37" s="14"/>
+      <c r="AL37" s="15"/>
+    </row>
+    <row r="38" spans="2:38" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B38" s="24" t="s">
         <v>1</v>
       </c>
@@ -2970,354 +3360,476 @@
       <c r="M38" s="25" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA38" s="24"/>
+      <c r="AB38" s="24"/>
+      <c r="AC38" s="24"/>
+      <c r="AD38" s="24"/>
+      <c r="AE38" s="24"/>
+      <c r="AF38" s="24"/>
+      <c r="AG38" s="24"/>
+      <c r="AH38" s="24"/>
+      <c r="AI38" s="24"/>
+      <c r="AJ38" s="24"/>
+      <c r="AK38" s="24"/>
+      <c r="AL38" s="25"/>
+    </row>
+    <row r="39" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B39" s="7">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D39" s="33">
-        <v>22.5</v>
-      </c>
-      <c r="E39" s="33">
-        <v>22.59632694642028</v>
-      </c>
-      <c r="F39" s="33">
-        <v>0.95142550207862098</v>
-      </c>
-      <c r="G39" s="33">
-        <v>25.452888411924771</v>
-      </c>
-      <c r="H39" s="33">
-        <v>20.390191235913321</v>
-      </c>
-      <c r="I39" s="33">
+      <c r="D39" s="26">
+        <v>22.4</v>
+      </c>
+      <c r="E39" s="26">
+        <v>22.50043893856251</v>
+      </c>
+      <c r="F39" s="26">
+        <v>1.140351207459817</v>
+      </c>
+      <c r="G39" s="4">
+        <v>25.313953364862879</v>
+      </c>
+      <c r="H39" s="4">
+        <v>19.33106073773558</v>
+      </c>
+      <c r="I39" s="4">
         <v>24</v>
       </c>
-      <c r="J39" s="33">
+      <c r="J39" s="4">
         <v>23</v>
       </c>
-      <c r="K39" s="33">
+      <c r="K39" s="4">
         <v>22</v>
       </c>
-      <c r="L39" s="33">
-        <v>21.67</v>
+      <c r="L39" s="4">
+        <v>21.37806981031099</v>
       </c>
       <c r="M39" s="8">
         <v>41</v>
       </c>
-    </row>
-    <row r="40" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA39" s="7"/>
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="26"/>
+      <c r="AD39" s="26"/>
+      <c r="AE39" s="26"/>
+      <c r="AF39" s="4"/>
+      <c r="AG39" s="4"/>
+      <c r="AH39" s="4"/>
+      <c r="AI39" s="4"/>
+      <c r="AJ39" s="4"/>
+      <c r="AK39" s="4"/>
+      <c r="AL39" s="8"/>
+    </row>
+    <row r="40" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B40" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C40" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="32">
-        <v>22.3</v>
-      </c>
-      <c r="E40" s="32">
-        <v>22.566311613960131</v>
-      </c>
-      <c r="F40" s="32">
-        <v>1.7081961310079039</v>
-      </c>
-      <c r="G40" s="32">
-        <v>27.6</v>
-      </c>
-      <c r="H40" s="32">
-        <v>19.03</v>
-      </c>
-      <c r="I40" s="32">
-        <v>24.5</v>
-      </c>
-      <c r="J40" s="32">
-        <v>23.5</v>
-      </c>
-      <c r="K40" s="32">
-        <v>21.52487286176606</v>
-      </c>
-      <c r="L40" s="32">
-        <v>20.9</v>
+      <c r="D40" s="27">
+        <v>22.72212634574791</v>
+      </c>
+      <c r="E40" s="27">
+        <v>22.597270068484288</v>
+      </c>
+      <c r="F40" s="27">
+        <v>1.3124115447960509</v>
+      </c>
+      <c r="G40" s="19">
+        <v>25.824582987707529</v>
+      </c>
+      <c r="H40" s="19">
+        <v>20.2</v>
+      </c>
+      <c r="I40" s="19">
+        <v>24.406568013994221</v>
+      </c>
+      <c r="J40" s="19">
+        <v>23.03</v>
+      </c>
+      <c r="K40" s="19">
+        <v>21.8</v>
+      </c>
+      <c r="L40" s="19">
+        <v>21</v>
       </c>
       <c r="M40" s="20">
         <v>41</v>
       </c>
-    </row>
-    <row r="41" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA40" s="17"/>
+      <c r="AB40" s="18"/>
+      <c r="AC40" s="27"/>
+      <c r="AD40" s="27"/>
+      <c r="AE40" s="27"/>
+      <c r="AF40" s="19"/>
+      <c r="AG40" s="19"/>
+      <c r="AH40" s="19"/>
+      <c r="AI40" s="19"/>
+      <c r="AJ40" s="19"/>
+      <c r="AK40" s="19"/>
+      <c r="AL40" s="20"/>
+    </row>
+    <row r="41" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B41" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="33">
-        <v>22.531764705882338</v>
-      </c>
-      <c r="E41" s="33">
-        <v>22.689597397328509</v>
-      </c>
-      <c r="F41" s="33">
-        <v>2.0295370607586021</v>
-      </c>
-      <c r="G41" s="33">
-        <v>27.600212458493619</v>
-      </c>
-      <c r="H41" s="33">
-        <v>18.206151097038688</v>
-      </c>
-      <c r="I41" s="33">
-        <v>25</v>
-      </c>
-      <c r="J41" s="33">
-        <v>24</v>
-      </c>
-      <c r="K41" s="33">
-        <v>21.5</v>
-      </c>
-      <c r="L41" s="33">
-        <v>20.5</v>
+      <c r="D41" s="26">
+        <v>22.3</v>
+      </c>
+      <c r="E41" s="26">
+        <v>22.310166639344551</v>
+      </c>
+      <c r="F41" s="26">
+        <v>1.996901960449055</v>
+      </c>
+      <c r="G41" s="4">
+        <v>28.982258372729358</v>
+      </c>
+      <c r="H41" s="4">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="I41" s="4">
+        <v>24.2</v>
+      </c>
+      <c r="J41" s="4">
+        <v>23.09</v>
+      </c>
+      <c r="K41" s="4">
+        <v>21.15</v>
+      </c>
+      <c r="L41" s="4">
+        <v>20</v>
       </c>
       <c r="M41" s="5">
         <v>41</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA41" s="2"/>
+      <c r="AB41" s="3"/>
+      <c r="AC41" s="26"/>
+      <c r="AD41" s="26"/>
+      <c r="AE41" s="26"/>
+      <c r="AF41" s="4"/>
+      <c r="AG41" s="4"/>
+      <c r="AH41" s="4"/>
+      <c r="AI41" s="4"/>
+      <c r="AJ41" s="4"/>
+      <c r="AK41" s="4"/>
+      <c r="AL41" s="5"/>
+    </row>
+    <row r="42" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B42" s="17">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C42" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D42" s="32">
-        <v>22.47</v>
-      </c>
-      <c r="E42" s="32">
-        <v>22.329617077858579</v>
-      </c>
-      <c r="F42" s="32">
-        <v>2.427838877374195</v>
-      </c>
-      <c r="G42" s="32">
-        <v>27.6</v>
-      </c>
-      <c r="H42" s="32">
-        <v>17.114131027601371</v>
-      </c>
-      <c r="I42" s="32">
-        <v>25.007553472267858</v>
-      </c>
-      <c r="J42" s="32">
-        <v>24</v>
-      </c>
-      <c r="K42" s="32">
-        <v>21.15</v>
-      </c>
-      <c r="L42" s="32">
-        <v>19.3</v>
+      <c r="D42" s="27">
+        <v>22.1</v>
+      </c>
+      <c r="E42" s="27">
+        <v>22.08205183331366</v>
+      </c>
+      <c r="F42" s="27">
+        <v>2.0003160554149071</v>
+      </c>
+      <c r="G42" s="19">
+        <v>25.65</v>
+      </c>
+      <c r="H42" s="19">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="I42" s="19">
+        <v>24.583085208000231</v>
+      </c>
+      <c r="J42" s="19">
+        <v>23</v>
+      </c>
+      <c r="K42" s="19">
+        <v>21</v>
+      </c>
+      <c r="L42" s="19">
+        <v>19.5</v>
       </c>
       <c r="M42" s="20">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA42" s="17"/>
+      <c r="AB42" s="18"/>
+      <c r="AC42" s="27"/>
+      <c r="AD42" s="27"/>
+      <c r="AE42" s="27"/>
+      <c r="AF42" s="19"/>
+      <c r="AG42" s="19"/>
+      <c r="AH42" s="19"/>
+      <c r="AI42" s="19"/>
+      <c r="AJ42" s="19"/>
+      <c r="AK42" s="19"/>
+      <c r="AL42" s="20"/>
+    </row>
+    <row r="43" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B43" s="2">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D43" s="33">
-        <v>22.1</v>
-      </c>
-      <c r="E43" s="33">
-        <v>22.016103856159699</v>
-      </c>
-      <c r="F43" s="33">
-        <v>2.7364496860755771</v>
-      </c>
-      <c r="G43" s="33">
-        <v>27.6</v>
-      </c>
-      <c r="H43" s="33">
-        <v>15.5</v>
-      </c>
-      <c r="I43" s="33">
-        <v>25.39</v>
-      </c>
-      <c r="J43" s="33">
+      <c r="D43" s="26">
+        <v>22.2</v>
+      </c>
+      <c r="E43" s="26">
+        <v>22.075724229351191</v>
+      </c>
+      <c r="F43" s="26">
+        <v>2.2140497892619568</v>
+      </c>
+      <c r="G43" s="4">
+        <v>25.8</v>
+      </c>
+      <c r="H43" s="4">
+        <v>14.7</v>
+      </c>
+      <c r="I43" s="4">
+        <v>25</v>
+      </c>
+      <c r="J43" s="4">
         <v>23</v>
       </c>
-      <c r="K43" s="33">
-        <v>20.882339343504391</v>
-      </c>
-      <c r="L43" s="33">
-        <v>19</v>
+      <c r="K43" s="4">
+        <v>20.8</v>
+      </c>
+      <c r="L43" s="4">
+        <v>19.5</v>
       </c>
       <c r="M43" s="5">
         <v>41</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA43" s="2"/>
+      <c r="AB43" s="3"/>
+      <c r="AC43" s="26"/>
+      <c r="AD43" s="26"/>
+      <c r="AE43" s="26"/>
+      <c r="AF43" s="4"/>
+      <c r="AG43" s="4"/>
+      <c r="AH43" s="4"/>
+      <c r="AI43" s="4"/>
+      <c r="AJ43" s="4"/>
+      <c r="AK43" s="4"/>
+      <c r="AL43" s="5"/>
+    </row>
+    <row r="44" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B44" s="17">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C44" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D44" s="32">
-        <v>22</v>
-      </c>
-      <c r="E44" s="32">
-        <v>21.974363861595641</v>
-      </c>
-      <c r="F44" s="32">
-        <v>2.8483699984935691</v>
-      </c>
-      <c r="G44" s="32">
-        <v>28.15</v>
-      </c>
-      <c r="H44" s="32">
-        <v>14.8</v>
-      </c>
-      <c r="I44" s="32">
-        <v>25.207986932140319</v>
-      </c>
-      <c r="J44" s="32">
-        <v>23</v>
-      </c>
-      <c r="K44" s="32">
-        <v>20.302438685005701</v>
-      </c>
-      <c r="L44" s="32">
-        <v>19.100000000000001</v>
+      <c r="D44" s="27">
+        <v>22.1</v>
+      </c>
+      <c r="E44" s="27">
+        <v>21.814435765720191</v>
+      </c>
+      <c r="F44" s="27">
+        <v>2.2906628962858981</v>
+      </c>
+      <c r="G44" s="19">
+        <v>26.454814361485109</v>
+      </c>
+      <c r="H44" s="19">
+        <v>14</v>
+      </c>
+      <c r="I44" s="19">
+        <v>24.64249667675406</v>
+      </c>
+      <c r="J44" s="19">
+        <v>22.824999999999999</v>
+      </c>
+      <c r="K44" s="19">
+        <v>20.675000000000001</v>
+      </c>
+      <c r="L44" s="19">
+        <v>19</v>
       </c>
       <c r="M44" s="20">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="AA44" s="17"/>
+      <c r="AB44" s="18"/>
+      <c r="AC44" s="27"/>
+      <c r="AD44" s="27"/>
+      <c r="AE44" s="27"/>
+      <c r="AF44" s="19"/>
+      <c r="AG44" s="19"/>
+      <c r="AH44" s="19"/>
+      <c r="AI44" s="19"/>
+      <c r="AJ44" s="19"/>
+      <c r="AK44" s="19"/>
+      <c r="AL44" s="20"/>
+    </row>
+    <row r="45" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D45" s="33">
-        <v>20.75</v>
-      </c>
-      <c r="E45" s="33">
-        <v>21.173643216205701</v>
-      </c>
-      <c r="F45" s="33">
-        <v>3.8228709678238708</v>
-      </c>
-      <c r="G45" s="33">
-        <v>29.20000000000001</v>
-      </c>
-      <c r="H45" s="33">
+        <v>49</v>
+      </c>
+      <c r="D45" s="26">
+        <v>22</v>
+      </c>
+      <c r="E45" s="26">
+        <v>22.452416652320512</v>
+      </c>
+      <c r="F45" s="26">
+        <v>4.6516404345387876</v>
+      </c>
+      <c r="G45" s="4">
+        <v>34.7606076740121</v>
+      </c>
+      <c r="H45" s="4">
         <v>12.4</v>
       </c>
-      <c r="I45" s="33">
-        <v>25.95000000000001</v>
-      </c>
-      <c r="J45" s="33">
-        <v>23.5625</v>
-      </c>
-      <c r="K45" s="33">
-        <v>18.4725</v>
-      </c>
-      <c r="L45" s="33">
-        <v>16.422154491615458</v>
+      <c r="I45" s="4">
+        <v>27.37623301038046</v>
+      </c>
+      <c r="J45" s="4">
+        <v>25.09071738844878</v>
+      </c>
+      <c r="K45" s="4">
+        <v>19.767499999999998</v>
+      </c>
+      <c r="L45" s="4">
+        <v>17.225000000000001</v>
       </c>
       <c r="M45" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="46" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="AA45" s="2"/>
+      <c r="AB45" s="3"/>
+      <c r="AC45" s="26"/>
+      <c r="AD45" s="26"/>
+      <c r="AE45" s="26"/>
+      <c r="AF45" s="4"/>
+      <c r="AG45" s="4"/>
+      <c r="AH45" s="4"/>
+      <c r="AI45" s="4"/>
+      <c r="AJ45" s="4"/>
+      <c r="AK45" s="4"/>
+      <c r="AL45" s="5"/>
+    </row>
+    <row r="46" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B46" s="21" t="s">
         <v>36</v>
       </c>
       <c r="C46" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D46" s="32">
-        <v>22</v>
-      </c>
-      <c r="E46" s="32">
-        <v>21.974363861595641</v>
-      </c>
-      <c r="F46" s="32">
-        <v>2.8483699984935691</v>
-      </c>
-      <c r="G46" s="32">
-        <v>28.15</v>
-      </c>
-      <c r="H46" s="32">
-        <v>14.8</v>
-      </c>
-      <c r="I46" s="32">
-        <v>25.207986932140319</v>
-      </c>
-      <c r="J46" s="32">
+      <c r="D46" s="27">
+        <v>22.2</v>
+      </c>
+      <c r="E46" s="27">
+        <v>22.075724229351191</v>
+      </c>
+      <c r="F46" s="27">
+        <v>2.2140497892619568</v>
+      </c>
+      <c r="G46" s="19">
+        <v>25.8</v>
+      </c>
+      <c r="H46" s="19">
+        <v>14.7</v>
+      </c>
+      <c r="I46" s="19">
+        <v>25</v>
+      </c>
+      <c r="J46" s="19">
         <v>23</v>
       </c>
-      <c r="K46" s="32">
-        <v>20.302438685005701</v>
-      </c>
-      <c r="L46" s="32">
-        <v>19.100000000000001</v>
+      <c r="K46" s="19">
+        <v>20.8</v>
+      </c>
+      <c r="L46" s="19">
+        <v>19.5</v>
       </c>
       <c r="M46" s="20">
         <v>41</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA46" s="21"/>
+      <c r="AB46" s="18"/>
+      <c r="AC46" s="27"/>
+      <c r="AD46" s="27"/>
+      <c r="AE46" s="27"/>
+      <c r="AF46" s="19"/>
+      <c r="AG46" s="19"/>
+      <c r="AH46" s="19"/>
+      <c r="AI46" s="19"/>
+      <c r="AJ46" s="19"/>
+      <c r="AK46" s="19"/>
+      <c r="AL46" s="20"/>
+    </row>
+    <row r="47" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B47" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="33">
-        <v>18.5</v>
-      </c>
-      <c r="E47" s="33">
-        <v>19.23952271483568</v>
-      </c>
-      <c r="F47" s="33">
-        <v>4.4449230351758553</v>
-      </c>
-      <c r="G47" s="33">
-        <v>28.6</v>
-      </c>
-      <c r="H47" s="33">
-        <v>10.78041462486493</v>
-      </c>
-      <c r="I47" s="33">
+      <c r="D47" s="26">
+        <v>19.05586373591925</v>
+      </c>
+      <c r="E47" s="26">
+        <v>19.7521109075665</v>
+      </c>
+      <c r="F47" s="26">
+        <v>4.0272850378977694</v>
+      </c>
+      <c r="G47" s="4">
+        <v>28.5</v>
+      </c>
+      <c r="H47" s="4">
+        <v>12</v>
+      </c>
+      <c r="I47" s="4">
         <v>25</v>
       </c>
-      <c r="J47" s="33">
+      <c r="J47" s="4">
         <v>22.94999999999991</v>
       </c>
-      <c r="K47" s="33">
-        <v>16.175000000000001</v>
-      </c>
-      <c r="L47" s="33">
-        <v>13.6</v>
+      <c r="K47" s="4">
+        <v>17.244676623889461</v>
+      </c>
+      <c r="L47" s="4">
+        <v>15.35</v>
       </c>
       <c r="M47" s="5">
         <v>38</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AA47" s="6"/>
+      <c r="AB47" s="3"/>
+      <c r="AC47" s="26"/>
+      <c r="AD47" s="26"/>
+      <c r="AE47" s="26"/>
+      <c r="AF47" s="4"/>
+      <c r="AG47" s="4"/>
+      <c r="AH47" s="4"/>
+      <c r="AI47" s="4"/>
+      <c r="AJ47" s="4"/>
+      <c r="AK47" s="4"/>
+      <c r="AL47" s="5"/>
+    </row>
+    <row r="48" spans="2:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B48" s="22"/>
       <c r="C48" s="23"/>
-    </row>
-    <row r="50" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA48" s="22"/>
+      <c r="AB48" s="23"/>
+    </row>
+    <row r="50" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B50" s="14" t="s">
         <v>21</v>
       </c>
@@ -3332,8 +3844,20 @@
       <c r="K50" s="14"/>
       <c r="L50" s="14"/>
       <c r="M50" s="15"/>
-    </row>
-    <row r="51" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="AA50" s="14"/>
+      <c r="AB50" s="14"/>
+      <c r="AC50" s="14"/>
+      <c r="AD50" s="14"/>
+      <c r="AE50" s="14"/>
+      <c r="AF50" s="14"/>
+      <c r="AG50" s="14"/>
+      <c r="AH50" s="14"/>
+      <c r="AI50" s="14"/>
+      <c r="AJ50" s="14"/>
+      <c r="AK50" s="14"/>
+      <c r="AL50" s="15"/>
+    </row>
+    <row r="51" spans="2:38" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B51" s="24" t="s">
         <v>1</v>
       </c>
@@ -3370,358 +3894,482 @@
       <c r="M51" s="25" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="52" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA51" s="24"/>
+      <c r="AB51" s="24"/>
+      <c r="AC51" s="24"/>
+      <c r="AD51" s="24"/>
+      <c r="AE51" s="24"/>
+      <c r="AF51" s="24"/>
+      <c r="AG51" s="24"/>
+      <c r="AH51" s="24"/>
+      <c r="AI51" s="24"/>
+      <c r="AJ51" s="24"/>
+      <c r="AK51" s="24"/>
+      <c r="AL51" s="25"/>
+    </row>
+    <row r="52" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B52" s="7">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D52" s="34">
-        <v>1482</v>
-      </c>
-      <c r="E52" s="34">
-        <v>1483.094729371732</v>
-      </c>
-      <c r="F52" s="34">
-        <v>21.661192365584242</v>
-      </c>
-      <c r="G52" s="34">
-        <v>1527.095508643622</v>
-      </c>
-      <c r="H52" s="34">
-        <v>1437.704736463515</v>
-      </c>
-      <c r="I52" s="34">
-        <v>1506.405274553799</v>
-      </c>
-      <c r="J52" s="34">
-        <v>1499.25</v>
-      </c>
-      <c r="K52" s="34">
-        <v>1473.2934544573361</v>
-      </c>
-      <c r="L52" s="34">
-        <v>1452.450269113885</v>
+      <c r="D52" s="28">
+        <v>1512.381372401137</v>
+      </c>
+      <c r="E52" s="28">
+        <v>1514.0013983571509</v>
+      </c>
+      <c r="F52" s="28">
+        <v>14.571792776314179</v>
+      </c>
+      <c r="G52" s="28">
+        <v>1552.8294134397479</v>
+      </c>
+      <c r="H52" s="28">
+        <v>1465</v>
+      </c>
+      <c r="I52" s="28">
+        <v>1530.160389000461</v>
+      </c>
+      <c r="J52" s="28">
+        <v>1523.7</v>
+      </c>
+      <c r="K52" s="28">
+        <v>1506</v>
+      </c>
+      <c r="L52" s="28">
+        <v>1499.797239503589</v>
       </c>
       <c r="M52" s="5">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="53" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="AA52" s="7"/>
+      <c r="AB52" s="3"/>
+      <c r="AC52" s="28"/>
+      <c r="AD52" s="28"/>
+      <c r="AE52" s="28"/>
+      <c r="AF52" s="28"/>
+      <c r="AG52" s="28"/>
+      <c r="AH52" s="28"/>
+      <c r="AI52" s="28"/>
+      <c r="AJ52" s="28"/>
+      <c r="AK52" s="28"/>
+      <c r="AL52" s="5"/>
+    </row>
+    <row r="53" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B53" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C53" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D53" s="35">
-        <v>1512.776088595379</v>
-      </c>
-      <c r="E53" s="35">
-        <v>1516.0592091939691</v>
-      </c>
-      <c r="F53" s="35">
-        <v>29.85628120137909</v>
-      </c>
-      <c r="G53" s="35">
-        <v>1584.823400588039</v>
-      </c>
-      <c r="H53" s="35">
-        <v>1462</v>
-      </c>
-      <c r="I53" s="35">
-        <v>1552.588</v>
-      </c>
-      <c r="J53" s="35">
-        <v>1533.562112937675</v>
-      </c>
-      <c r="K53" s="35">
-        <v>1499.5138985895869</v>
-      </c>
-      <c r="L53" s="35">
-        <v>1471.8</v>
+      <c r="D53" s="29">
+        <v>1546.240057783051</v>
+      </c>
+      <c r="E53" s="29">
+        <v>1546.5355382437299</v>
+      </c>
+      <c r="F53" s="29">
+        <v>22.249760865873419</v>
+      </c>
+      <c r="G53" s="29">
+        <v>1594</v>
+      </c>
+      <c r="H53" s="29">
+        <v>1495</v>
+      </c>
+      <c r="I53" s="29">
+        <v>1574.978768235824</v>
+      </c>
+      <c r="J53" s="29">
+        <v>1561.191691478524</v>
+      </c>
+      <c r="K53" s="29">
+        <v>1533.8860814976749</v>
+      </c>
+      <c r="L53" s="29">
+        <v>1517.81047009605</v>
       </c>
       <c r="M53" s="20">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="54" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="AA53" s="17"/>
+      <c r="AB53" s="18"/>
+      <c r="AC53" s="29"/>
+      <c r="AD53" s="29"/>
+      <c r="AE53" s="29"/>
+      <c r="AF53" s="29"/>
+      <c r="AG53" s="29"/>
+      <c r="AH53" s="29"/>
+      <c r="AI53" s="29"/>
+      <c r="AJ53" s="29"/>
+      <c r="AK53" s="29"/>
+      <c r="AL53" s="20"/>
+    </row>
+    <row r="54" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B54" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D54" s="34">
-        <v>1548.019695973675</v>
-      </c>
-      <c r="E54" s="34">
-        <v>1551.043416208963</v>
-      </c>
-      <c r="F54" s="34">
-        <v>38.965725029468643</v>
-      </c>
-      <c r="G54" s="34">
-        <v>1641.1237222741911</v>
-      </c>
-      <c r="H54" s="34">
-        <v>1472</v>
-      </c>
-      <c r="I54" s="34">
-        <v>1600.614</v>
-      </c>
-      <c r="J54" s="34">
-        <v>1573.281563267542</v>
-      </c>
-      <c r="K54" s="34">
-        <v>1527.7049999999999</v>
-      </c>
-      <c r="L54" s="34">
-        <v>1497.812092556205</v>
+      <c r="D54" s="28">
+        <v>1577.273109422091</v>
+      </c>
+      <c r="E54" s="28">
+        <v>1583.206958130661</v>
+      </c>
+      <c r="F54" s="28">
+        <v>33.058705620999547</v>
+      </c>
+      <c r="G54" s="28">
+        <v>1644</v>
+      </c>
+      <c r="H54" s="28">
+        <v>1514</v>
+      </c>
+      <c r="I54" s="28">
+        <v>1634.5110335885811</v>
+      </c>
+      <c r="J54" s="28">
+        <v>1608.6</v>
+      </c>
+      <c r="K54" s="28">
+        <v>1560</v>
+      </c>
+      <c r="L54" s="28">
+        <v>1545.4</v>
       </c>
       <c r="M54" s="5">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="55" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="AA54" s="2"/>
+      <c r="AB54" s="3"/>
+      <c r="AC54" s="28"/>
+      <c r="AD54" s="28"/>
+      <c r="AE54" s="28"/>
+      <c r="AF54" s="28"/>
+      <c r="AG54" s="28"/>
+      <c r="AH54" s="28"/>
+      <c r="AI54" s="28"/>
+      <c r="AJ54" s="28"/>
+      <c r="AK54" s="28"/>
+      <c r="AL54" s="5"/>
+    </row>
+    <row r="55" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B55" s="17">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C55" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D55" s="35">
-        <v>1588.8549330032929</v>
-      </c>
-      <c r="E55" s="35">
-        <v>1587.5068955214899</v>
-      </c>
-      <c r="F55" s="35">
-        <v>47.040836621505633</v>
-      </c>
-      <c r="G55" s="35">
-        <v>1700.0392641662841</v>
-      </c>
-      <c r="H55" s="35">
-        <v>1490</v>
-      </c>
-      <c r="I55" s="35">
-        <v>1643.509</v>
-      </c>
-      <c r="J55" s="35">
-        <v>1611.2393432655549</v>
-      </c>
-      <c r="K55" s="35">
-        <v>1554.25</v>
-      </c>
-      <c r="L55" s="35">
-        <v>1531.552160520303</v>
+      <c r="D55" s="29">
+        <v>1618.1042185054771</v>
+      </c>
+      <c r="E55" s="29">
+        <v>1619.5767169773169</v>
+      </c>
+      <c r="F55" s="29">
+        <v>44.76401768957323</v>
+      </c>
+      <c r="G55" s="29">
+        <v>1706.42</v>
+      </c>
+      <c r="H55" s="29">
+        <v>1520</v>
+      </c>
+      <c r="I55" s="29">
+        <v>1686.202784033499</v>
+      </c>
+      <c r="J55" s="29">
+        <v>1644.8966200286891</v>
+      </c>
+      <c r="K55" s="29">
+        <v>1587.072511158972</v>
+      </c>
+      <c r="L55" s="29">
+        <v>1565.9</v>
       </c>
       <c r="M55" s="20">
         <v>44</v>
       </c>
-    </row>
-    <row r="56" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA55" s="17"/>
+      <c r="AB55" s="18"/>
+      <c r="AC55" s="29"/>
+      <c r="AD55" s="29"/>
+      <c r="AE55" s="29"/>
+      <c r="AF55" s="29"/>
+      <c r="AG55" s="29"/>
+      <c r="AH55" s="29"/>
+      <c r="AI55" s="29"/>
+      <c r="AJ55" s="29"/>
+      <c r="AK55" s="29"/>
+      <c r="AL55" s="20"/>
+    </row>
+    <row r="56" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B56" s="2">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D56" s="34">
-        <v>1620.5</v>
-      </c>
-      <c r="E56" s="34">
-        <v>1623.304224154007</v>
-      </c>
-      <c r="F56" s="34">
-        <v>58.663304432292414</v>
-      </c>
-      <c r="G56" s="34">
-        <v>1754.9590957633441</v>
-      </c>
-      <c r="H56" s="34">
-        <v>1497</v>
-      </c>
-      <c r="I56" s="34">
-        <v>1689.45733002527</v>
-      </c>
-      <c r="J56" s="34">
-        <v>1663.335</v>
-      </c>
-      <c r="K56" s="34">
-        <v>1578.668217523496</v>
-      </c>
-      <c r="L56" s="34">
-        <v>1560.251580798875</v>
+      <c r="D56" s="28">
+        <v>1651.7928018417031</v>
+      </c>
+      <c r="E56" s="28">
+        <v>1655.0218066534601</v>
+      </c>
+      <c r="F56" s="28">
+        <v>55.226953642813243</v>
+      </c>
+      <c r="G56" s="28">
+        <v>1774.68</v>
+      </c>
+      <c r="H56" s="28">
+        <v>1527</v>
+      </c>
+      <c r="I56" s="28">
+        <v>1733.9929228078299</v>
+      </c>
+      <c r="J56" s="28">
+        <v>1680</v>
+      </c>
+      <c r="K56" s="28">
+        <v>1611</v>
+      </c>
+      <c r="L56" s="28">
+        <v>1592</v>
       </c>
       <c r="M56" s="5">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="57" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="AA56" s="2"/>
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="28"/>
+      <c r="AD56" s="28"/>
+      <c r="AE56" s="28"/>
+      <c r="AF56" s="28"/>
+      <c r="AG56" s="28"/>
+      <c r="AH56" s="28"/>
+      <c r="AI56" s="28"/>
+      <c r="AJ56" s="28"/>
+      <c r="AK56" s="28"/>
+      <c r="AL56" s="5"/>
+    </row>
+    <row r="57" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B57" s="17">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C57" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D57" s="35">
-        <v>1672.5</v>
-      </c>
-      <c r="E57" s="35">
-        <v>1665.56479686698</v>
-      </c>
-      <c r="F57" s="35">
-        <v>70.36878388220461</v>
-      </c>
-      <c r="G57" s="35">
-        <v>1814.57</v>
-      </c>
-      <c r="H57" s="35">
-        <v>1503</v>
-      </c>
-      <c r="I57" s="35">
-        <v>1739.17</v>
-      </c>
-      <c r="J57" s="35">
-        <v>1704.8</v>
-      </c>
-      <c r="K57" s="35">
-        <v>1620.95</v>
-      </c>
-      <c r="L57" s="35">
-        <v>1592.0060000000001</v>
+      <c r="D57" s="29">
+        <v>1688.1933162856869</v>
+      </c>
+      <c r="E57" s="29">
+        <v>1684.443365446062</v>
+      </c>
+      <c r="F57" s="29">
+        <v>62.755911127529629</v>
+      </c>
+      <c r="G57" s="29">
+        <v>1810.17</v>
+      </c>
+      <c r="H57" s="29">
+        <v>1532</v>
+      </c>
+      <c r="I57" s="29">
+        <v>1767.2142622732449</v>
+      </c>
+      <c r="J57" s="29">
+        <v>1710.382012342661</v>
+      </c>
+      <c r="K57" s="29">
+        <v>1638.0546840037659</v>
+      </c>
+      <c r="L57" s="29">
+        <v>1613.6</v>
       </c>
       <c r="M57" s="20">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="58" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="AA57" s="17"/>
+      <c r="AB57" s="18"/>
+      <c r="AC57" s="29"/>
+      <c r="AD57" s="29"/>
+      <c r="AE57" s="29"/>
+      <c r="AF57" s="29"/>
+      <c r="AG57" s="29"/>
+      <c r="AH57" s="29"/>
+      <c r="AI57" s="29"/>
+      <c r="AJ57" s="29"/>
+      <c r="AK57" s="29"/>
+      <c r="AL57" s="20"/>
+    </row>
+    <row r="58" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D58" s="34">
-        <v>1805</v>
-      </c>
-      <c r="E58" s="34">
-        <v>1830.9658213693881</v>
-      </c>
-      <c r="F58" s="34">
-        <v>118.8107865208504</v>
-      </c>
-      <c r="G58" s="34">
-        <v>2036.2756138807511</v>
-      </c>
-      <c r="H58" s="34">
-        <v>1535</v>
-      </c>
-      <c r="I58" s="34">
-        <v>1977</v>
-      </c>
-      <c r="J58" s="34">
-        <v>1931.4238026973781</v>
-      </c>
-      <c r="K58" s="34">
-        <v>1762</v>
-      </c>
-      <c r="L58" s="34">
-        <v>1697.1222435828861</v>
+        <v>50</v>
+      </c>
+      <c r="D58" s="28">
+        <v>1859</v>
+      </c>
+      <c r="E58" s="28">
+        <v>1853.3564608448521</v>
+      </c>
+      <c r="F58" s="28">
+        <v>110.1052088001979</v>
+      </c>
+      <c r="G58" s="28">
+        <v>2122.06</v>
+      </c>
+      <c r="H58" s="28">
+        <v>1575</v>
+      </c>
+      <c r="I58" s="28">
+        <v>1966.476616006388</v>
+      </c>
+      <c r="J58" s="28">
+        <v>1923.1053973415401</v>
+      </c>
+      <c r="K58" s="28">
+        <v>1786</v>
+      </c>
+      <c r="L58" s="28">
+        <v>1729.4108688576321</v>
       </c>
       <c r="M58" s="5">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="59" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AA58" s="2"/>
+      <c r="AB58" s="3"/>
+      <c r="AC58" s="28"/>
+      <c r="AD58" s="28"/>
+      <c r="AE58" s="28"/>
+      <c r="AF58" s="28"/>
+      <c r="AG58" s="28"/>
+      <c r="AH58" s="28"/>
+      <c r="AI58" s="28"/>
+      <c r="AJ58" s="28"/>
+      <c r="AK58" s="28"/>
+      <c r="AL58" s="5"/>
+    </row>
+    <row r="59" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B59" s="21" t="s">
         <v>36</v>
       </c>
       <c r="C59" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D59" s="35">
-        <v>1672.5</v>
-      </c>
-      <c r="E59" s="35">
-        <v>1665.56479686698</v>
-      </c>
-      <c r="F59" s="35">
-        <v>70.36878388220461</v>
-      </c>
-      <c r="G59" s="35">
-        <v>1814.57</v>
-      </c>
-      <c r="H59" s="35">
-        <v>1503</v>
-      </c>
-      <c r="I59" s="35">
-        <v>1739.17</v>
-      </c>
-      <c r="J59" s="35">
-        <v>1704.8</v>
-      </c>
-      <c r="K59" s="35">
-        <v>1620.95</v>
-      </c>
-      <c r="L59" s="35">
-        <v>1592.0060000000001</v>
+      <c r="D59" s="29">
+        <v>1651.7928018417031</v>
+      </c>
+      <c r="E59" s="29">
+        <v>1655.0217070148931</v>
+      </c>
+      <c r="F59" s="29">
+        <v>55.226865793337637</v>
+      </c>
+      <c r="G59" s="29">
+        <v>1774.68</v>
+      </c>
+      <c r="H59" s="29">
+        <v>1527</v>
+      </c>
+      <c r="I59" s="29">
+        <v>1733.9929228078299</v>
+      </c>
+      <c r="J59" s="29">
+        <v>1680</v>
+      </c>
+      <c r="K59" s="29">
+        <v>1611</v>
+      </c>
+      <c r="L59" s="29">
+        <v>1592</v>
       </c>
       <c r="M59" s="20">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="60" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="AA59" s="21"/>
+      <c r="AB59" s="18"/>
+      <c r="AC59" s="29"/>
+      <c r="AD59" s="29"/>
+      <c r="AE59" s="29"/>
+      <c r="AF59" s="29"/>
+      <c r="AG59" s="29"/>
+      <c r="AH59" s="29"/>
+      <c r="AI59" s="29"/>
+      <c r="AJ59" s="29"/>
+      <c r="AK59" s="29"/>
+      <c r="AL59" s="20"/>
+    </row>
+    <row r="60" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B60" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="34">
-        <v>2018.2524672873551</v>
-      </c>
-      <c r="E60" s="34">
-        <v>2025.422572003409</v>
-      </c>
-      <c r="F60" s="34">
-        <v>160.41928317066061</v>
-      </c>
-      <c r="G60" s="34">
-        <v>2359.2199999999998</v>
-      </c>
-      <c r="H60" s="34">
-        <v>1609</v>
-      </c>
-      <c r="I60" s="34">
-        <v>2214.6669999999999</v>
-      </c>
-      <c r="J60" s="34">
-        <v>2122.515935914907</v>
-      </c>
-      <c r="K60" s="34">
-        <v>1921</v>
-      </c>
-      <c r="L60" s="34">
-        <v>1832.187674966756</v>
+      <c r="D60" s="28">
+        <v>2018.25</v>
+      </c>
+      <c r="E60" s="28">
+        <v>2015.3488190279261</v>
+      </c>
+      <c r="F60" s="28">
+        <v>147.85171216893571</v>
+      </c>
+      <c r="G60" s="28">
+        <v>2357</v>
+      </c>
+      <c r="H60" s="28">
+        <v>1634</v>
+      </c>
+      <c r="I60" s="28">
+        <v>2198.84</v>
+      </c>
+      <c r="J60" s="28">
+        <v>2100</v>
+      </c>
+      <c r="K60" s="28">
+        <v>1931.401455023502</v>
+      </c>
+      <c r="L60" s="28">
+        <v>1810.9788287891099</v>
       </c>
       <c r="M60" s="5">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="61" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="AA60" s="6"/>
+      <c r="AB60" s="3"/>
+      <c r="AC60" s="28"/>
+      <c r="AD60" s="28"/>
+      <c r="AE60" s="28"/>
+      <c r="AF60" s="28"/>
+      <c r="AG60" s="28"/>
+      <c r="AH60" s="28"/>
+      <c r="AI60" s="28"/>
+      <c r="AJ60" s="28"/>
+      <c r="AK60" s="28"/>
+      <c r="AL60" s="5"/>
+    </row>
+    <row r="61" spans="2:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B61" s="22"/>
       <c r="C61" s="23"/>
-    </row>
-    <row r="62" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AA61" s="22"/>
+      <c r="AB61" s="23"/>
+    </row>
+    <row r="62" spans="2:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B62" s="22"/>
       <c r="C62" s="23"/>
-    </row>
-    <row r="63" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA62" s="22"/>
+      <c r="AB62" s="23"/>
+    </row>
+    <row r="63" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B63" s="14" t="s">
         <v>24</v>
       </c>
@@ -3736,8 +4384,20 @@
       <c r="K63" s="14"/>
       <c r="L63" s="14"/>
       <c r="M63" s="15"/>
-    </row>
-    <row r="64" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="AA63" s="14"/>
+      <c r="AB63" s="14"/>
+      <c r="AC63" s="14"/>
+      <c r="AD63" s="14"/>
+      <c r="AE63" s="14"/>
+      <c r="AF63" s="14"/>
+      <c r="AG63" s="14"/>
+      <c r="AH63" s="14"/>
+      <c r="AI63" s="14"/>
+      <c r="AJ63" s="14"/>
+      <c r="AK63" s="14"/>
+      <c r="AL63" s="15"/>
+    </row>
+    <row r="64" spans="2:38" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B64" s="24" t="s">
         <v>1</v>
       </c>
@@ -3774,274 +4434,370 @@
       <c r="M64" s="25" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA64" s="24"/>
+      <c r="AB64" s="24"/>
+      <c r="AC64" s="24"/>
+      <c r="AD64" s="24"/>
+      <c r="AE64" s="24"/>
+      <c r="AF64" s="24"/>
+      <c r="AG64" s="24"/>
+      <c r="AH64" s="24"/>
+      <c r="AI64" s="24"/>
+      <c r="AJ64" s="24"/>
+      <c r="AK64" s="24"/>
+      <c r="AL64" s="25"/>
+    </row>
+    <row r="65" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B65" s="7">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D65" s="28">
-        <v>8965</v>
+        <v>8900</v>
       </c>
       <c r="E65" s="28">
-        <v>8880.8383728003646</v>
+        <v>8875.9362242947518</v>
       </c>
       <c r="F65" s="28">
-        <v>440.95615928263999</v>
+        <v>338.55332476494539</v>
       </c>
       <c r="G65" s="28">
-        <v>9537</v>
+        <v>9678.0851647567706</v>
       </c>
       <c r="H65" s="28">
-        <v>7901.6981850447673</v>
+        <v>8261.5257744472037</v>
       </c>
       <c r="I65" s="28">
-        <v>9350.7558546555574</v>
+        <v>9328</v>
       </c>
       <c r="J65" s="28">
-        <v>9264.451616904571</v>
+        <v>9023</v>
       </c>
       <c r="K65" s="28">
-        <v>8637.7646955909076</v>
+        <v>8656.1377913832293</v>
       </c>
       <c r="L65" s="28">
-        <v>8222.6679562838544</v>
+        <v>8450.204290000218</v>
       </c>
       <c r="M65" s="8">
         <v>37</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA65" s="7"/>
+      <c r="AB65" s="3"/>
+      <c r="AC65" s="28"/>
+      <c r="AD65" s="28"/>
+      <c r="AE65" s="28"/>
+      <c r="AF65" s="28"/>
+      <c r="AG65" s="28"/>
+      <c r="AH65" s="28"/>
+      <c r="AI65" s="28"/>
+      <c r="AJ65" s="28"/>
+      <c r="AK65" s="28"/>
+      <c r="AL65" s="8"/>
+    </row>
+    <row r="66" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B66" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C66" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D66" s="29">
-        <v>8757.2930478770559</v>
+        <v>8785.1471619888889</v>
       </c>
       <c r="E66" s="29">
-        <v>8817.1015514095488</v>
+        <v>8801.9047354729901</v>
       </c>
       <c r="F66" s="29">
-        <v>425.23194289342177</v>
+        <v>431.66639318607912</v>
       </c>
       <c r="G66" s="29">
-        <v>9607.375445483829</v>
+        <v>10165.564280137931</v>
       </c>
       <c r="H66" s="29">
         <v>8000</v>
       </c>
       <c r="I66" s="29">
-        <v>9469</v>
+        <v>9290.4438765941013</v>
       </c>
       <c r="J66" s="29">
-        <v>9140.9458708333186</v>
+        <v>9097.1456380288746</v>
       </c>
       <c r="K66" s="29">
-        <v>8553.8754998076183</v>
+        <v>8533</v>
       </c>
       <c r="L66" s="29">
-        <v>8325.6783425377198</v>
+        <v>8280.8799999999992</v>
       </c>
       <c r="M66" s="20">
         <v>37</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA66" s="17"/>
+      <c r="AB66" s="18"/>
+      <c r="AC66" s="29"/>
+      <c r="AD66" s="29"/>
+      <c r="AE66" s="29"/>
+      <c r="AF66" s="29"/>
+      <c r="AG66" s="29"/>
+      <c r="AH66" s="29"/>
+      <c r="AI66" s="29"/>
+      <c r="AJ66" s="29"/>
+      <c r="AK66" s="29"/>
+      <c r="AL66" s="20"/>
+    </row>
+    <row r="67" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D67" s="28">
-        <v>8693.3134667720005</v>
+        <v>8580</v>
       </c>
       <c r="E67" s="28">
-        <v>8757.4563947870301</v>
+        <v>8663.0256283639919</v>
       </c>
       <c r="F67" s="28">
-        <v>388.47089519663979</v>
+        <v>483.2642572915392</v>
       </c>
       <c r="G67" s="28">
-        <v>9597</v>
+        <v>10615.8881347724</v>
       </c>
       <c r="H67" s="28">
         <v>8000</v>
       </c>
       <c r="I67" s="28">
-        <v>9262.9553055632496</v>
+        <v>9168.4288843558224</v>
       </c>
       <c r="J67" s="28">
-        <v>9060.6139159745726</v>
+        <v>8832.2144566698935</v>
       </c>
       <c r="K67" s="28">
-        <v>8528</v>
+        <v>8325</v>
       </c>
       <c r="L67" s="28">
-        <v>8328.7973129273378</v>
+        <v>8188.24</v>
       </c>
       <c r="M67" s="5">
         <v>37</v>
       </c>
-    </row>
-    <row r="68" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA67" s="2"/>
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="28"/>
+      <c r="AD67" s="28"/>
+      <c r="AE67" s="28"/>
+      <c r="AF67" s="28"/>
+      <c r="AG67" s="28"/>
+      <c r="AH67" s="28"/>
+      <c r="AI67" s="28"/>
+      <c r="AJ67" s="28"/>
+      <c r="AK67" s="28"/>
+      <c r="AL67" s="5"/>
+    </row>
+    <row r="68" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B68" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C68" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D68" s="29">
-        <v>8534.5912802010007</v>
+        <v>8498.3378442743015</v>
       </c>
       <c r="E68" s="29">
-        <v>8573.8589547260472</v>
+        <v>8570.3175150722909</v>
       </c>
       <c r="F68" s="29">
-        <v>428.64457303111749</v>
+        <v>521.15346441489226</v>
       </c>
       <c r="G68" s="29">
-        <v>9376</v>
+        <v>10829.486808082331</v>
       </c>
       <c r="H68" s="29">
-        <v>7859</v>
+        <v>7828</v>
       </c>
       <c r="I68" s="29">
-        <v>9212.5741426171007</v>
+        <v>9010.2646363466756</v>
       </c>
       <c r="J68" s="29">
-        <v>8787.9473102278607</v>
+        <v>8760</v>
       </c>
       <c r="K68" s="29">
-        <v>8209</v>
+        <v>8238</v>
       </c>
       <c r="L68" s="29">
-        <v>8015.9374467171274</v>
+        <v>8056.6</v>
       </c>
       <c r="M68" s="20">
         <v>37</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA68" s="17"/>
+      <c r="AB68" s="18"/>
+      <c r="AC68" s="29"/>
+      <c r="AD68" s="29"/>
+      <c r="AE68" s="29"/>
+      <c r="AF68" s="29"/>
+      <c r="AG68" s="29"/>
+      <c r="AH68" s="29"/>
+      <c r="AI68" s="29"/>
+      <c r="AJ68" s="29"/>
+      <c r="AK68" s="29"/>
+      <c r="AL68" s="20"/>
+    </row>
+    <row r="69" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B69" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D69" s="28">
-        <v>8448</v>
+        <v>8165.7695664374223</v>
       </c>
       <c r="E69" s="28">
-        <v>8493.0978562160617</v>
+        <v>8260.5017212912844</v>
       </c>
       <c r="F69" s="28">
-        <v>373.19678691121641</v>
+        <v>559.63348603213808</v>
       </c>
       <c r="G69" s="28">
-        <v>9236.2730954833205</v>
+        <v>10754.40831195166</v>
       </c>
       <c r="H69" s="28">
-        <v>7764</v>
+        <v>7629.7620461218703</v>
       </c>
       <c r="I69" s="28">
-        <v>9021.120133279026</v>
+        <v>8780</v>
       </c>
       <c r="J69" s="28">
-        <v>8698</v>
+        <v>8411.3797338921613</v>
       </c>
       <c r="K69" s="28">
-        <v>8220</v>
+        <v>7970</v>
       </c>
       <c r="L69" s="28">
-        <v>8000</v>
+        <v>7763.410636303206</v>
       </c>
       <c r="M69" s="5">
         <v>37</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA69" s="2"/>
+      <c r="AB69" s="3"/>
+      <c r="AC69" s="28"/>
+      <c r="AD69" s="28"/>
+      <c r="AE69" s="28"/>
+      <c r="AF69" s="28"/>
+      <c r="AG69" s="28"/>
+      <c r="AH69" s="28"/>
+      <c r="AI69" s="28"/>
+      <c r="AJ69" s="28"/>
+      <c r="AK69" s="28"/>
+      <c r="AL69" s="5"/>
+    </row>
+    <row r="70" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B70" s="17">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C70" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D70" s="29">
-        <v>8073.028614038255</v>
+        <v>8058.2851629484776</v>
       </c>
       <c r="E70" s="29">
-        <v>8170.7557215339639</v>
+        <v>8154.7465167735909</v>
       </c>
       <c r="F70" s="29">
-        <v>474.15207921559141</v>
+        <v>540.58747744758182</v>
       </c>
       <c r="G70" s="29">
-        <v>9409</v>
+        <v>10431.305485114641</v>
       </c>
       <c r="H70" s="29">
-        <v>7200</v>
+        <v>7563</v>
       </c>
       <c r="I70" s="29">
-        <v>8720</v>
+        <v>8673.6232695737508</v>
       </c>
       <c r="J70" s="29">
-        <v>8418</v>
+        <v>8380</v>
       </c>
       <c r="K70" s="29">
-        <v>7918</v>
+        <v>7820</v>
       </c>
       <c r="L70" s="29">
-        <v>7686.6735718697964</v>
+        <v>7625.4173585751068</v>
       </c>
       <c r="M70" s="20">
         <v>37</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA70" s="17"/>
+      <c r="AB70" s="18"/>
+      <c r="AC70" s="29"/>
+      <c r="AD70" s="29"/>
+      <c r="AE70" s="29"/>
+      <c r="AF70" s="29"/>
+      <c r="AG70" s="29"/>
+      <c r="AH70" s="29"/>
+      <c r="AI70" s="29"/>
+      <c r="AJ70" s="29"/>
+      <c r="AK70" s="29"/>
+      <c r="AL70" s="20"/>
+    </row>
+    <row r="71" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B71" s="2">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D71" s="28">
-        <v>8086</v>
+        <v>7520.7358315058009</v>
       </c>
       <c r="E71" s="28">
-        <v>8068.1394551233006</v>
+        <v>7531.3552162137712</v>
       </c>
       <c r="F71" s="28">
-        <v>335.75819539874141</v>
+        <v>384.97596930346782</v>
       </c>
       <c r="G71" s="28">
-        <v>8664.987100516626</v>
+        <v>8410</v>
       </c>
       <c r="H71" s="28">
-        <v>7497.72</v>
+        <v>6728.8</v>
       </c>
       <c r="I71" s="28">
-        <v>8501.2100080315777</v>
+        <v>7986.8</v>
       </c>
       <c r="J71" s="28">
-        <v>8310</v>
+        <v>7773.0534868192099</v>
       </c>
       <c r="K71" s="28">
-        <v>7820</v>
+        <v>7318.7860049768506</v>
       </c>
       <c r="L71" s="28">
-        <v>7631.4390491751137</v>
+        <v>7014.6535533726783</v>
       </c>
       <c r="M71" s="5">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="72" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="AA71" s="2"/>
+      <c r="AB71" s="3"/>
+      <c r="AC71" s="28"/>
+      <c r="AD71" s="28"/>
+      <c r="AE71" s="28"/>
+      <c r="AF71" s="28"/>
+      <c r="AG71" s="28"/>
+      <c r="AH71" s="28"/>
+      <c r="AI71" s="28"/>
+      <c r="AJ71" s="28"/>
+      <c r="AK71" s="28"/>
+      <c r="AL71" s="5"/>
+    </row>
+    <row r="72" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B72" s="21" t="s">
         <v>36</v>
       </c>
@@ -4049,37 +4805,49 @@
         <v>25</v>
       </c>
       <c r="D72" s="29">
-        <v>100000</v>
+        <v>100207.38084529219</v>
       </c>
       <c r="E72" s="29">
-        <v>100069.2109906307</v>
+        <v>100679.7296427807</v>
       </c>
       <c r="F72" s="29">
-        <v>2050.5076498295998</v>
+        <v>2448.1933922907861</v>
       </c>
       <c r="G72" s="29">
-        <v>104887</v>
+        <v>111928.73818481569</v>
       </c>
       <c r="H72" s="29">
-        <v>96037.109413863567</v>
+        <v>96958</v>
       </c>
       <c r="I72" s="29">
-        <v>102995.71551655031</v>
+        <v>103077.8784387601</v>
       </c>
       <c r="J72" s="29">
-        <v>101130.9879394551</v>
+        <v>101381.4433785436</v>
       </c>
       <c r="K72" s="29">
-        <v>98575.973497176761</v>
+        <v>99402.950391798062</v>
       </c>
       <c r="L72" s="29">
-        <v>97574.815990814124</v>
+        <v>98299.932000000001</v>
       </c>
       <c r="M72" s="20">
         <v>40</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA72" s="21"/>
+      <c r="AB72" s="18"/>
+      <c r="AC72" s="29"/>
+      <c r="AD72" s="29"/>
+      <c r="AE72" s="29"/>
+      <c r="AF72" s="29"/>
+      <c r="AG72" s="29"/>
+      <c r="AH72" s="29"/>
+      <c r="AI72" s="29"/>
+      <c r="AJ72" s="29"/>
+      <c r="AK72" s="29"/>
+      <c r="AL72" s="20"/>
+    </row>
+    <row r="73" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B73" s="6" t="s">
         <v>37</v>
       </c>
@@ -4087,45 +4855,61 @@
         <v>25</v>
       </c>
       <c r="D73" s="28">
-        <v>104770.2894023418</v>
+        <v>104447.68290056199</v>
       </c>
       <c r="E73" s="28">
-        <v>104040.37238559419</v>
+        <v>104745.2910050075</v>
       </c>
       <c r="F73" s="28">
-        <v>4663.1573469991527</v>
+        <v>3671.124364693625</v>
       </c>
       <c r="G73" s="28">
-        <v>118021</v>
+        <v>116235.87468463169</v>
       </c>
       <c r="H73" s="28">
-        <v>90160</v>
+        <v>92437.488358738512</v>
       </c>
       <c r="I73" s="28">
-        <v>108332.3287470568</v>
+        <v>108761.9217075646</v>
       </c>
       <c r="J73" s="28">
-        <v>105965.75</v>
+        <v>105791.2106455692</v>
       </c>
       <c r="K73" s="28">
-        <v>102033.95416274951</v>
+        <v>103095.277</v>
       </c>
       <c r="L73" s="28">
-        <v>101184</v>
+        <v>101953.9033254989</v>
       </c>
       <c r="M73" s="5">
         <v>36</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AA73" s="6"/>
+      <c r="AB73" s="3"/>
+      <c r="AC73" s="28"/>
+      <c r="AD73" s="28"/>
+      <c r="AE73" s="28"/>
+      <c r="AF73" s="28"/>
+      <c r="AG73" s="28"/>
+      <c r="AH73" s="28"/>
+      <c r="AI73" s="28"/>
+      <c r="AJ73" s="28"/>
+      <c r="AK73" s="28"/>
+      <c r="AL73" s="5"/>
+    </row>
+    <row r="74" spans="2:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B74" s="22"/>
       <c r="C74" s="23"/>
-    </row>
-    <row r="75" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AA74" s="22"/>
+      <c r="AB74" s="23"/>
+    </row>
+    <row r="75" spans="2:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B75" s="22"/>
       <c r="C75" s="23"/>
-    </row>
-    <row r="76" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA75" s="22"/>
+      <c r="AB75" s="23"/>
+    </row>
+    <row r="76" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B76" s="14" t="s">
         <v>26</v>
       </c>
@@ -4140,8 +4924,20 @@
       <c r="K76" s="14"/>
       <c r="L76" s="14"/>
       <c r="M76" s="15"/>
-    </row>
-    <row r="77" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="AA76" s="14"/>
+      <c r="AB76" s="14"/>
+      <c r="AC76" s="14"/>
+      <c r="AD76" s="14"/>
+      <c r="AE76" s="14"/>
+      <c r="AF76" s="14"/>
+      <c r="AG76" s="14"/>
+      <c r="AH76" s="14"/>
+      <c r="AI76" s="14"/>
+      <c r="AJ76" s="14"/>
+      <c r="AK76" s="14"/>
+      <c r="AL76" s="15"/>
+    </row>
+    <row r="77" spans="2:38" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B77" s="24" t="s">
         <v>1</v>
       </c>
@@ -4178,274 +4974,370 @@
       <c r="M77" s="25" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="78" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA77" s="24"/>
+      <c r="AB77" s="24"/>
+      <c r="AC77" s="24"/>
+      <c r="AD77" s="24"/>
+      <c r="AE77" s="24"/>
+      <c r="AF77" s="24"/>
+      <c r="AG77" s="24"/>
+      <c r="AH77" s="24"/>
+      <c r="AI77" s="24"/>
+      <c r="AJ77" s="24"/>
+      <c r="AK77" s="24"/>
+      <c r="AL77" s="25"/>
+    </row>
+    <row r="78" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B78" s="7">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D78" s="28">
-        <v>6587</v>
+        <v>7033.2951998234794</v>
       </c>
       <c r="E78" s="28">
-        <v>6582.7052026004621</v>
+        <v>7072.0430161598706</v>
       </c>
       <c r="F78" s="28">
-        <v>360.38605721351638</v>
+        <v>243.53278542790201</v>
       </c>
       <c r="G78" s="28">
-        <v>7434.7146719178954</v>
+        <v>7805.3</v>
       </c>
       <c r="H78" s="28">
-        <v>6033</v>
+        <v>6500</v>
       </c>
       <c r="I78" s="28">
-        <v>6982.1223367240236</v>
+        <v>7359.8307194826884</v>
       </c>
       <c r="J78" s="28">
-        <v>6840</v>
+        <v>7210.5235102967217</v>
       </c>
       <c r="K78" s="28">
-        <v>6311.7345990605891</v>
+        <v>6908.9703736302054</v>
       </c>
       <c r="L78" s="28">
-        <v>6119.8226054775496</v>
+        <v>6814.8334183792067</v>
       </c>
       <c r="M78" s="8">
         <v>37</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA78" s="7"/>
+      <c r="AB78" s="3"/>
+      <c r="AC78" s="28"/>
+      <c r="AD78" s="28"/>
+      <c r="AE78" s="28"/>
+      <c r="AF78" s="28"/>
+      <c r="AG78" s="28"/>
+      <c r="AH78" s="28"/>
+      <c r="AI78" s="28"/>
+      <c r="AJ78" s="28"/>
+      <c r="AK78" s="28"/>
+      <c r="AL78" s="8"/>
+    </row>
+    <row r="79" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B79" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C79" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D79" s="29">
-        <v>7046.2659498395751</v>
+        <v>7001.3020479708739</v>
       </c>
       <c r="E79" s="29">
-        <v>6997.248510425834</v>
+        <v>6966.4668325842922</v>
       </c>
       <c r="F79" s="29">
-        <v>451.91759935516791</v>
+        <v>284.76624518555798</v>
       </c>
       <c r="G79" s="29">
-        <v>8140.7397842558248</v>
+        <v>7577.8215142893287</v>
       </c>
       <c r="H79" s="29">
-        <v>6132.8437707900002</v>
+        <v>6241</v>
       </c>
       <c r="I79" s="29">
-        <v>7441.2179999999998</v>
+        <v>7285.6480000000001</v>
       </c>
       <c r="J79" s="29">
-        <v>7238.2236093405272</v>
+        <v>7138.5050792755246</v>
       </c>
       <c r="K79" s="29">
-        <v>6674.1573223177484</v>
+        <v>6750</v>
       </c>
       <c r="L79" s="29">
-        <v>6480.3909011753503</v>
+        <v>6600</v>
       </c>
       <c r="M79" s="20">
         <v>37</v>
       </c>
-    </row>
-    <row r="80" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA79" s="17"/>
+      <c r="AB79" s="18"/>
+      <c r="AC79" s="29"/>
+      <c r="AD79" s="29"/>
+      <c r="AE79" s="29"/>
+      <c r="AF79" s="29"/>
+      <c r="AG79" s="29"/>
+      <c r="AH79" s="29"/>
+      <c r="AI79" s="29"/>
+      <c r="AJ79" s="29"/>
+      <c r="AK79" s="29"/>
+      <c r="AL79" s="20"/>
+    </row>
+    <row r="80" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B80" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D80" s="28">
-        <v>6904</v>
+        <v>7031.2834464039724</v>
       </c>
       <c r="E80" s="28">
-        <v>6953.259180423096</v>
+        <v>7068.4344864384357</v>
       </c>
       <c r="F80" s="28">
-        <v>441.70629217665658</v>
+        <v>344.48170518806791</v>
       </c>
       <c r="G80" s="28">
-        <v>8415.3485722202822</v>
+        <v>7881.4822741985608</v>
       </c>
       <c r="H80" s="28">
-        <v>6182.8437707900002</v>
+        <v>6485.4398714765784</v>
       </c>
       <c r="I80" s="28">
-        <v>7518.6379999999999</v>
+        <v>7535.6360842415224</v>
       </c>
       <c r="J80" s="28">
-        <v>7094.6266382464592</v>
+        <v>7263</v>
       </c>
       <c r="K80" s="28">
-        <v>6657</v>
+        <v>6863.2801174340739</v>
       </c>
       <c r="L80" s="28">
-        <v>6496.1014953323784</v>
+        <v>6700</v>
       </c>
       <c r="M80" s="5">
         <v>37</v>
       </c>
-    </row>
-    <row r="81" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA80" s="2"/>
+      <c r="AB80" s="3"/>
+      <c r="AC80" s="28"/>
+      <c r="AD80" s="28"/>
+      <c r="AE80" s="28"/>
+      <c r="AF80" s="28"/>
+      <c r="AG80" s="28"/>
+      <c r="AH80" s="28"/>
+      <c r="AI80" s="28"/>
+      <c r="AJ80" s="28"/>
+      <c r="AK80" s="28"/>
+      <c r="AL80" s="5"/>
+    </row>
+    <row r="81" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B81" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C81" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D81" s="29">
-        <v>7077.0970267995899</v>
+        <v>7012.8821908806567</v>
       </c>
       <c r="E81" s="29">
-        <v>7062.7837416563443</v>
+        <v>7023.3147998800478</v>
       </c>
       <c r="F81" s="29">
-        <v>554.59206254540686</v>
+        <v>377.82142687826661</v>
       </c>
       <c r="G81" s="29">
-        <v>8553.938094788864</v>
+        <v>7922.1678652521614</v>
       </c>
       <c r="H81" s="29">
-        <v>5801.3762093660598</v>
+        <v>6032.7398046560238</v>
       </c>
       <c r="I81" s="29">
-        <v>7682.716609910618</v>
+        <v>7534.515281200247</v>
       </c>
       <c r="J81" s="29">
-        <v>7309.6687908009317</v>
+        <v>7167</v>
       </c>
       <c r="K81" s="29">
-        <v>6740</v>
+        <v>6782</v>
       </c>
       <c r="L81" s="29">
-        <v>6449.1136674606159</v>
+        <v>6619.7086786653699</v>
       </c>
       <c r="M81" s="20">
         <v>37</v>
       </c>
-    </row>
-    <row r="82" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA81" s="17"/>
+      <c r="AB81" s="18"/>
+      <c r="AC81" s="29"/>
+      <c r="AD81" s="29"/>
+      <c r="AE81" s="29"/>
+      <c r="AF81" s="29"/>
+      <c r="AG81" s="29"/>
+      <c r="AH81" s="29"/>
+      <c r="AI81" s="29"/>
+      <c r="AJ81" s="29"/>
+      <c r="AK81" s="29"/>
+      <c r="AL81" s="20"/>
+    </row>
+    <row r="82" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B82" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D82" s="28">
-        <v>7014.84</v>
+        <v>6490</v>
       </c>
       <c r="E82" s="28">
-        <v>7039.2252289122698</v>
+        <v>6490.6744930159512</v>
       </c>
       <c r="F82" s="28">
-        <v>534.80891853094272</v>
+        <v>448.29536651714511</v>
       </c>
       <c r="G82" s="28">
-        <v>8212.6032111168843</v>
+        <v>7300</v>
       </c>
       <c r="H82" s="28">
-        <v>5705.8326799021979</v>
+        <v>5598</v>
       </c>
       <c r="I82" s="28">
-        <v>7752.6393709749127</v>
+        <v>7024.739216165447</v>
       </c>
       <c r="J82" s="28">
-        <v>7302.3271187853315</v>
+        <v>6877.9534473778631</v>
       </c>
       <c r="K82" s="28">
-        <v>6760</v>
+        <v>6102.3878989944169</v>
       </c>
       <c r="L82" s="28">
-        <v>6497.1698372361716</v>
+        <v>5978.0992541318064</v>
       </c>
       <c r="M82" s="5">
         <v>37</v>
       </c>
-    </row>
-    <row r="83" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA82" s="2"/>
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="28"/>
+      <c r="AD82" s="28"/>
+      <c r="AE82" s="28"/>
+      <c r="AF82" s="28"/>
+      <c r="AG82" s="28"/>
+      <c r="AH82" s="28"/>
+      <c r="AI82" s="28"/>
+      <c r="AJ82" s="28"/>
+      <c r="AK82" s="28"/>
+      <c r="AL82" s="5"/>
+    </row>
+    <row r="83" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B83" s="17">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C83" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D83" s="29">
-        <v>6538.8757896795451</v>
+        <v>6200</v>
       </c>
       <c r="E83" s="29">
-        <v>6585.1344942747064</v>
+        <v>6351.5857067710613</v>
       </c>
       <c r="F83" s="29">
-        <v>537.31808315641251</v>
+        <v>525.49812692546493</v>
       </c>
       <c r="G83" s="29">
-        <v>7976.571837667103</v>
+        <v>7537.8182296339728</v>
       </c>
       <c r="H83" s="29">
-        <v>5358.3417419697053</v>
+        <v>5498.1455859689804</v>
       </c>
       <c r="I83" s="29">
-        <v>7305.7439024337846</v>
+        <v>7047.1790225396117</v>
       </c>
       <c r="J83" s="29">
-        <v>6926.2276415778151</v>
+        <v>6800</v>
       </c>
       <c r="K83" s="29">
-        <v>6235</v>
+        <v>5913.68</v>
       </c>
       <c r="L83" s="29">
-        <v>5993.5559999999996</v>
+        <v>5754.8716545095131</v>
       </c>
       <c r="M83" s="20">
         <v>37</v>
       </c>
-    </row>
-    <row r="84" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA83" s="17"/>
+      <c r="AB83" s="18"/>
+      <c r="AC83" s="29"/>
+      <c r="AD83" s="29"/>
+      <c r="AE83" s="29"/>
+      <c r="AF83" s="29"/>
+      <c r="AG83" s="29"/>
+      <c r="AH83" s="29"/>
+      <c r="AI83" s="29"/>
+      <c r="AJ83" s="29"/>
+      <c r="AK83" s="29"/>
+      <c r="AL83" s="20"/>
+    </row>
+    <row r="84" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B84" s="2">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D84" s="28">
-        <v>6399</v>
+        <v>6088.3095745162354</v>
       </c>
       <c r="E84" s="28">
-        <v>6441.6363106451336</v>
+        <v>6108.2938771766421</v>
       </c>
       <c r="F84" s="28">
-        <v>636.24718393389549</v>
+        <v>555.93846288976488</v>
       </c>
       <c r="G84" s="28">
-        <v>7921.1330656673963</v>
+        <v>7105.6103548315104</v>
       </c>
       <c r="H84" s="28">
-        <v>4918.2185989196932</v>
+        <v>5000</v>
       </c>
       <c r="I84" s="28">
-        <v>7201.4924912387369</v>
+        <v>6886.4761480270708</v>
       </c>
       <c r="J84" s="28">
-        <v>6905</v>
+        <v>6500</v>
       </c>
       <c r="K84" s="28">
-        <v>5910.5051336928109</v>
+        <v>5745.7247400592933</v>
       </c>
       <c r="L84" s="28">
-        <v>5777.3828255072976</v>
+        <v>5427.1811893476697</v>
       </c>
       <c r="M84" s="5">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="85" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="AA84" s="2"/>
+      <c r="AB84" s="3"/>
+      <c r="AC84" s="28"/>
+      <c r="AD84" s="28"/>
+      <c r="AE84" s="28"/>
+      <c r="AF84" s="28"/>
+      <c r="AG84" s="28"/>
+      <c r="AH84" s="28"/>
+      <c r="AI84" s="28"/>
+      <c r="AJ84" s="28"/>
+      <c r="AK84" s="28"/>
+      <c r="AL84" s="5"/>
+    </row>
+    <row r="85" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B85" s="21" t="s">
         <v>36</v>
       </c>
@@ -4453,37 +5345,49 @@
         <v>25</v>
       </c>
       <c r="D85" s="29">
-        <v>76400.020523973202</v>
+        <v>76773.020427460811</v>
       </c>
       <c r="E85" s="29">
-        <v>76337.996570649819</v>
+        <v>76544.543174221923</v>
       </c>
       <c r="F85" s="29">
-        <v>2682.4399466879158</v>
+        <v>1586.9348757586049</v>
       </c>
       <c r="G85" s="29">
-        <v>84743.605115298953</v>
+        <v>80376</v>
       </c>
       <c r="H85" s="29">
-        <v>68978.521358499303</v>
+        <v>73837.831692513268</v>
       </c>
       <c r="I85" s="29">
-        <v>78859.20168066943</v>
+        <v>78191.21854772963</v>
       </c>
       <c r="J85" s="29">
-        <v>77662.409750000006</v>
+        <v>77490.7112708895</v>
       </c>
       <c r="K85" s="29">
-        <v>74627.186419116348</v>
+        <v>75178.661705379112</v>
       </c>
       <c r="L85" s="29">
-        <v>73785.227401469005</v>
+        <v>74315.118910948193</v>
       </c>
       <c r="M85" s="20">
         <v>40</v>
       </c>
-    </row>
-    <row r="86" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA85" s="21"/>
+      <c r="AB85" s="18"/>
+      <c r="AC85" s="29"/>
+      <c r="AD85" s="29"/>
+      <c r="AE85" s="29"/>
+      <c r="AF85" s="29"/>
+      <c r="AG85" s="29"/>
+      <c r="AH85" s="29"/>
+      <c r="AI85" s="29"/>
+      <c r="AJ85" s="29"/>
+      <c r="AK85" s="29"/>
+      <c r="AL85" s="20"/>
+    </row>
+    <row r="86" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B86" s="6" t="s">
         <v>37</v>
       </c>
@@ -4491,37 +5395,49 @@
         <v>25</v>
       </c>
       <c r="D86" s="28">
-        <v>82556.42</v>
+        <v>83025.895000000004</v>
       </c>
       <c r="E86" s="28">
-        <v>82330.790384260734</v>
+        <v>82702.05152977386</v>
       </c>
       <c r="F86" s="28">
-        <v>4441.6093490856383</v>
+        <v>3138.8560718211988</v>
       </c>
       <c r="G86" s="28">
-        <v>94980.71444002421</v>
+        <v>90000</v>
       </c>
       <c r="H86" s="28">
-        <v>71250</v>
+        <v>75262.710316640572</v>
       </c>
       <c r="I86" s="28">
-        <v>86761.061736059506</v>
+        <v>86434</v>
       </c>
       <c r="J86" s="28">
-        <v>84863.112586677657</v>
+        <v>84592.889023072203</v>
       </c>
       <c r="K86" s="28">
-        <v>79850</v>
+        <v>80880.96684620966</v>
       </c>
       <c r="L86" s="28">
-        <v>76606.842554207658</v>
+        <v>78956.317198216188</v>
       </c>
       <c r="M86" s="5">
         <v>36</v>
       </c>
-    </row>
-    <row r="87" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="AA86" s="6"/>
+      <c r="AB86" s="3"/>
+      <c r="AC86" s="28"/>
+      <c r="AD86" s="28"/>
+      <c r="AE86" s="28"/>
+      <c r="AF86" s="28"/>
+      <c r="AG86" s="28"/>
+      <c r="AH86" s="28"/>
+      <c r="AI86" s="28"/>
+      <c r="AJ86" s="28"/>
+      <c r="AK86" s="28"/>
+      <c r="AL86" s="5"/>
+    </row>
+    <row r="87" spans="2:38" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B87" s="9"/>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
@@ -4534,8 +5450,20 @@
       <c r="K87" s="10"/>
       <c r="L87" s="10"/>
       <c r="M87" s="10"/>
-    </row>
-    <row r="89" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA87" s="9"/>
+      <c r="AB87" s="10"/>
+      <c r="AC87" s="10"/>
+      <c r="AD87" s="10"/>
+      <c r="AE87" s="10"/>
+      <c r="AF87" s="10"/>
+      <c r="AG87" s="10"/>
+      <c r="AH87" s="10"/>
+      <c r="AI87" s="10"/>
+      <c r="AJ87" s="10"/>
+      <c r="AK87" s="10"/>
+      <c r="AL87" s="10"/>
+    </row>
+    <row r="89" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B89" s="14" t="s">
         <v>27</v>
       </c>
@@ -4550,8 +5478,20 @@
       <c r="K89" s="14"/>
       <c r="L89" s="14"/>
       <c r="M89" s="15"/>
-    </row>
-    <row r="90" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="AA89" s="14"/>
+      <c r="AB89" s="14"/>
+      <c r="AC89" s="14"/>
+      <c r="AD89" s="14"/>
+      <c r="AE89" s="14"/>
+      <c r="AF89" s="14"/>
+      <c r="AG89" s="14"/>
+      <c r="AH89" s="14"/>
+      <c r="AI89" s="14"/>
+      <c r="AJ89" s="14"/>
+      <c r="AK89" s="14"/>
+      <c r="AL89" s="15"/>
+    </row>
+    <row r="90" spans="2:38" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B90" s="24" t="s">
         <v>1</v>
       </c>
@@ -4588,84 +5528,120 @@
       <c r="M90" s="25" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="91" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA90" s="24"/>
+      <c r="AB90" s="24"/>
+      <c r="AC90" s="24"/>
+      <c r="AD90" s="24"/>
+      <c r="AE90" s="24"/>
+      <c r="AF90" s="24"/>
+      <c r="AG90" s="24"/>
+      <c r="AH90" s="24"/>
+      <c r="AI90" s="24"/>
+      <c r="AJ90" s="24"/>
+      <c r="AK90" s="24"/>
+      <c r="AL90" s="25"/>
+    </row>
+    <row r="91" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B91" s="21" t="s">
         <v>36</v>
       </c>
       <c r="C91" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D91" s="29">
-        <v>15700</v>
-      </c>
-      <c r="E91" s="29">
-        <v>15248.83473917421</v>
-      </c>
-      <c r="F91" s="29">
-        <v>2209.9209280276</v>
-      </c>
-      <c r="G91" s="29">
+      <c r="D91" s="32">
+        <v>15554.3</v>
+      </c>
+      <c r="E91" s="32">
+        <v>15261.625501435939</v>
+      </c>
+      <c r="F91" s="32">
+        <v>2106.9482637727001</v>
+      </c>
+      <c r="G91" s="32">
         <v>21056</v>
       </c>
-      <c r="H91" s="29">
+      <c r="H91" s="32">
         <v>9000</v>
       </c>
-      <c r="I91" s="29">
-        <v>17260.2</v>
-      </c>
-      <c r="J91" s="29">
-        <v>16107.641742069851</v>
-      </c>
-      <c r="K91" s="29">
-        <v>15000</v>
-      </c>
-      <c r="L91" s="29">
-        <v>11948</v>
+      <c r="I91" s="32">
+        <v>17721.657999999999</v>
+      </c>
+      <c r="J91" s="32">
+        <v>15966.25</v>
+      </c>
+      <c r="K91" s="32">
+        <v>14425</v>
+      </c>
+      <c r="L91" s="32">
+        <v>12710.601251209309</v>
       </c>
       <c r="M91" s="20">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="92" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="AA91" s="21"/>
+      <c r="AB91" s="18"/>
+      <c r="AC91" s="32"/>
+      <c r="AD91" s="32"/>
+      <c r="AE91" s="32"/>
+      <c r="AF91" s="32"/>
+      <c r="AG91" s="32"/>
+      <c r="AH91" s="32"/>
+      <c r="AI91" s="32"/>
+      <c r="AJ91" s="32"/>
+      <c r="AK91" s="32"/>
+      <c r="AL91" s="20"/>
+    </row>
+    <row r="92" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B92" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D92" s="28">
-        <v>19729</v>
-      </c>
-      <c r="E92" s="28">
-        <v>18554.948196765119</v>
-      </c>
-      <c r="F92" s="28">
-        <v>3312.1495195548619</v>
-      </c>
-      <c r="G92" s="28">
-        <v>22451.67367882196</v>
-      </c>
-      <c r="H92" s="28">
+      <c r="D92" s="33">
+        <v>19307</v>
+      </c>
+      <c r="E92" s="33">
+        <v>18536.880757174531</v>
+      </c>
+      <c r="F92" s="33">
+        <v>3147.7105999325199</v>
+      </c>
+      <c r="G92" s="33">
+        <v>22542.95823806425</v>
+      </c>
+      <c r="H92" s="33">
         <v>5000</v>
       </c>
-      <c r="I92" s="28">
-        <v>21169.594796954789</v>
-      </c>
-      <c r="J92" s="28">
-        <v>20361.424999999999</v>
-      </c>
-      <c r="K92" s="28">
-        <v>17807.069676089519</v>
-      </c>
-      <c r="L92" s="28">
-        <v>15208.5</v>
+      <c r="I92" s="33">
+        <v>21160.290289536679</v>
+      </c>
+      <c r="J92" s="33">
+        <v>20356.410952458729</v>
+      </c>
+      <c r="K92" s="33">
+        <v>17662.716754113571</v>
+      </c>
+      <c r="L92" s="33">
+        <v>15400</v>
       </c>
       <c r="M92" s="5">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="93" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="AA92" s="6"/>
+      <c r="AB92" s="3"/>
+      <c r="AC92" s="33"/>
+      <c r="AD92" s="33"/>
+      <c r="AE92" s="33"/>
+      <c r="AF92" s="33"/>
+      <c r="AG92" s="33"/>
+      <c r="AH92" s="33"/>
+      <c r="AI92" s="33"/>
+      <c r="AJ92" s="33"/>
+      <c r="AK92" s="33"/>
+      <c r="AL92" s="5"/>
+    </row>
+    <row r="93" spans="2:38" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B93" s="9"/>
       <c r="C93" s="10"/>
       <c r="D93" s="10"/>
@@ -4678,8 +5654,20 @@
       <c r="K93" s="10"/>
       <c r="L93" s="10"/>
       <c r="M93" s="10"/>
-    </row>
-    <row r="95" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA93" s="9"/>
+      <c r="AB93" s="10"/>
+      <c r="AC93" s="10"/>
+      <c r="AD93" s="10"/>
+      <c r="AE93" s="10"/>
+      <c r="AF93" s="10"/>
+      <c r="AG93" s="10"/>
+      <c r="AH93" s="10"/>
+      <c r="AI93" s="10"/>
+      <c r="AJ93" s="10"/>
+      <c r="AK93" s="10"/>
+      <c r="AL93" s="10"/>
+    </row>
+    <row r="95" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B95" s="14" t="s">
         <v>29</v>
       </c>
@@ -4694,8 +5682,20 @@
       <c r="K95" s="14"/>
       <c r="L95" s="14"/>
       <c r="M95" s="15"/>
-    </row>
-    <row r="96" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="AA95" s="14"/>
+      <c r="AB95" s="14"/>
+      <c r="AC95" s="14"/>
+      <c r="AD95" s="14"/>
+      <c r="AE95" s="14"/>
+      <c r="AF95" s="14"/>
+      <c r="AG95" s="14"/>
+      <c r="AH95" s="14"/>
+      <c r="AI95" s="14"/>
+      <c r="AJ95" s="14"/>
+      <c r="AK95" s="14"/>
+      <c r="AL95" s="15"/>
+    </row>
+    <row r="96" spans="2:38" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B96" s="24" t="s">
         <v>1</v>
       </c>
@@ -4732,8 +5732,20 @@
       <c r="M96" s="25" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="97" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA96" s="24"/>
+      <c r="AB96" s="24"/>
+      <c r="AC96" s="24"/>
+      <c r="AD96" s="24"/>
+      <c r="AE96" s="24"/>
+      <c r="AF96" s="24"/>
+      <c r="AG96" s="24"/>
+      <c r="AH96" s="24"/>
+      <c r="AI96" s="24"/>
+      <c r="AJ96" s="24"/>
+      <c r="AK96" s="24"/>
+      <c r="AL96" s="25"/>
+    </row>
+    <row r="97" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B97" s="7" t="s">
         <v>42</v>
       </c>
@@ -4741,37 +5753,49 @@
         <v>30</v>
       </c>
       <c r="D97" s="4">
-        <v>7.6834995908704036</v>
+        <v>7.7</v>
       </c>
       <c r="E97" s="4">
-        <v>7.657402206971148</v>
+        <v>7.6931282041086746</v>
       </c>
       <c r="F97" s="4">
-        <v>0.2342179642805452</v>
+        <v>0.26097067207673619</v>
       </c>
       <c r="G97" s="4">
-        <v>8.1999999999999993</v>
+        <v>8.2286757743888757</v>
       </c>
       <c r="H97" s="4">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="I97" s="4">
-        <v>7.9555973741548778</v>
+        <v>8.066966897073252</v>
       </c>
       <c r="J97" s="4">
-        <v>7.7984735317400302</v>
+        <v>7.83</v>
       </c>
       <c r="K97" s="4">
-        <v>7.5</v>
+        <v>7.5068461061614924</v>
       </c>
       <c r="L97" s="4">
         <v>7.4</v>
       </c>
       <c r="M97" s="8">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="98" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="AA97" s="7"/>
+      <c r="AB97" s="3"/>
+      <c r="AC97" s="4"/>
+      <c r="AD97" s="4"/>
+      <c r="AE97" s="4"/>
+      <c r="AF97" s="4"/>
+      <c r="AG97" s="4"/>
+      <c r="AH97" s="4"/>
+      <c r="AI97" s="4"/>
+      <c r="AJ97" s="4"/>
+      <c r="AK97" s="4"/>
+      <c r="AL97" s="8"/>
+    </row>
+    <row r="98" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B98" s="17" t="s">
         <v>44</v>
       </c>
@@ -4779,39 +5803,51 @@
         <v>30</v>
       </c>
       <c r="D98" s="19">
-        <v>7.3</v>
+        <v>7.2618775758281311</v>
       </c>
       <c r="E98" s="19">
-        <v>7.3043052515190752</v>
+        <v>7.2629977374112569</v>
       </c>
       <c r="F98" s="19">
-        <v>0.5015298063125514</v>
+        <v>0.49619959081075188</v>
       </c>
       <c r="G98" s="19">
         <v>8.6</v>
       </c>
       <c r="H98" s="19">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="I98" s="19">
-        <v>7.79</v>
+        <v>7.7489999999999997</v>
       </c>
       <c r="J98" s="19">
-        <v>7.6025000000000009</v>
+        <v>7.5749999999999993</v>
       </c>
       <c r="K98" s="19">
-        <v>6.9749999999999996</v>
+        <v>6.9250000000000007</v>
       </c>
       <c r="L98" s="19">
-        <v>6.7549598581975454</v>
+        <v>6.6116457709346621</v>
       </c>
       <c r="M98" s="20">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="99" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="AA98" s="17"/>
+      <c r="AB98" s="18"/>
+      <c r="AC98" s="19"/>
+      <c r="AD98" s="19"/>
+      <c r="AE98" s="19"/>
+      <c r="AF98" s="19"/>
+      <c r="AG98" s="19"/>
+      <c r="AH98" s="19"/>
+      <c r="AI98" s="19"/>
+      <c r="AJ98" s="19"/>
+      <c r="AK98" s="19"/>
+      <c r="AL98" s="20"/>
+    </row>
+    <row r="99" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B99" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>30</v>
@@ -4820,10 +5856,10 @@
         <v>7.5</v>
       </c>
       <c r="E99" s="4">
-        <v>7.5194996235506082</v>
+        <v>7.5557198905846796</v>
       </c>
       <c r="F99" s="4">
-        <v>0.3805533431159987</v>
+        <v>0.37399958307768139</v>
       </c>
       <c r="G99" s="4">
         <v>8.6999999999999993</v>
@@ -4832,22 +5868,34 @@
         <v>7</v>
       </c>
       <c r="I99" s="4">
-        <v>7.8920000000000003</v>
+        <v>8</v>
       </c>
       <c r="J99" s="4">
-        <v>7.6998731732282089</v>
+        <v>7.6998097598423136</v>
       </c>
       <c r="K99" s="4">
-        <v>7.3</v>
+        <v>7.3100441038012036</v>
       </c>
       <c r="L99" s="4">
         <v>7.2</v>
       </c>
       <c r="M99" s="5">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="100" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="AA99" s="6"/>
+      <c r="AB99" s="3"/>
+      <c r="AC99" s="4"/>
+      <c r="AD99" s="4"/>
+      <c r="AE99" s="4"/>
+      <c r="AF99" s="4"/>
+      <c r="AG99" s="4"/>
+      <c r="AH99" s="4"/>
+      <c r="AI99" s="4"/>
+      <c r="AJ99" s="4"/>
+      <c r="AK99" s="4"/>
+      <c r="AL99" s="5"/>
+    </row>
+    <row r="100" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B100" s="21" t="s">
         <v>36</v>
       </c>
@@ -4858,10 +5906,10 @@
         <v>7.5</v>
       </c>
       <c r="E100" s="19">
-        <v>7.5194996235506082</v>
+        <v>7.5557198905846796</v>
       </c>
       <c r="F100" s="19">
-        <v>0.3805533431159987</v>
+        <v>0.37399958307768139</v>
       </c>
       <c r="G100" s="19">
         <v>8.6999999999999993</v>
@@ -4870,22 +5918,34 @@
         <v>7</v>
       </c>
       <c r="I100" s="19">
-        <v>7.8920000000000003</v>
+        <v>8</v>
       </c>
       <c r="J100" s="19">
-        <v>7.6998731732282089</v>
+        <v>7.6998097598423136</v>
       </c>
       <c r="K100" s="19">
-        <v>7.3</v>
+        <v>7.3100441038012036</v>
       </c>
       <c r="L100" s="19">
         <v>7.2</v>
       </c>
       <c r="M100" s="20">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="101" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="AA100" s="21"/>
+      <c r="AB100" s="18"/>
+      <c r="AC100" s="19"/>
+      <c r="AD100" s="19"/>
+      <c r="AE100" s="19"/>
+      <c r="AF100" s="19"/>
+      <c r="AG100" s="19"/>
+      <c r="AH100" s="19"/>
+      <c r="AI100" s="19"/>
+      <c r="AJ100" s="19"/>
+      <c r="AK100" s="19"/>
+      <c r="AL100" s="20"/>
+    </row>
+    <row r="101" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B101" s="6" t="s">
         <v>37</v>
       </c>
@@ -4893,13 +5953,13 @@
         <v>43</v>
       </c>
       <c r="D101" s="4">
-        <v>7.4</v>
+        <v>7.4671161354062674</v>
       </c>
       <c r="E101" s="4">
-        <v>7.4671161354062674</v>
+        <v>7.514391658035918</v>
       </c>
       <c r="F101" s="4">
-        <v>0.50336599234653123</v>
+        <v>0.48972191098902362</v>
       </c>
       <c r="G101" s="4">
         <v>8.5</v>
@@ -4908,22 +5968,34 @@
         <v>6.4</v>
       </c>
       <c r="I101" s="4">
-        <v>8.1132850532654395</v>
+        <v>8.16</v>
       </c>
       <c r="J101" s="4">
-        <v>7.9</v>
+        <v>7.8563429956464184</v>
       </c>
       <c r="K101" s="4">
-        <v>7.2</v>
+        <v>7.2000000000000011</v>
       </c>
       <c r="L101" s="4">
-        <v>6.8</v>
+        <v>7.04</v>
       </c>
       <c r="M101" s="5">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="102" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="AA101" s="6"/>
+      <c r="AB101" s="3"/>
+      <c r="AC101" s="4"/>
+      <c r="AD101" s="4"/>
+      <c r="AE101" s="4"/>
+      <c r="AF101" s="4"/>
+      <c r="AG101" s="4"/>
+      <c r="AH101" s="4"/>
+      <c r="AI101" s="4"/>
+      <c r="AJ101" s="4"/>
+      <c r="AK101" s="4"/>
+      <c r="AL101" s="5"/>
+    </row>
+    <row r="102" spans="2:38" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B102" s="9"/>
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
@@ -4936,8 +6008,20 @@
       <c r="K102" s="9"/>
       <c r="L102" s="9"/>
       <c r="M102" s="9"/>
-    </row>
-    <row r="104" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA102" s="9"/>
+      <c r="AB102" s="9"/>
+      <c r="AC102" s="9"/>
+      <c r="AD102" s="9"/>
+      <c r="AE102" s="9"/>
+      <c r="AF102" s="9"/>
+      <c r="AG102" s="9"/>
+      <c r="AH102" s="9"/>
+      <c r="AI102" s="9"/>
+      <c r="AJ102" s="9"/>
+      <c r="AK102" s="9"/>
+      <c r="AL102" s="9"/>
+    </row>
+    <row r="104" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B104" s="14" t="s">
         <v>32</v>
       </c>
@@ -4952,8 +6036,20 @@
       <c r="K104" s="14"/>
       <c r="L104" s="14"/>
       <c r="M104" s="15"/>
-    </row>
-    <row r="105" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="AA104" s="14"/>
+      <c r="AB104" s="14"/>
+      <c r="AC104" s="14"/>
+      <c r="AD104" s="14"/>
+      <c r="AE104" s="14"/>
+      <c r="AF104" s="14"/>
+      <c r="AG104" s="14"/>
+      <c r="AH104" s="14"/>
+      <c r="AI104" s="14"/>
+      <c r="AJ104" s="14"/>
+      <c r="AK104" s="14"/>
+      <c r="AL104" s="15"/>
+    </row>
+    <row r="105" spans="2:38" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B105" s="24" t="s">
         <v>1</v>
       </c>
@@ -4990,8 +6086,20 @@
       <c r="M105" s="25" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="106" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="AA105" s="24"/>
+      <c r="AB105" s="24"/>
+      <c r="AC105" s="24"/>
+      <c r="AD105" s="24"/>
+      <c r="AE105" s="24"/>
+      <c r="AF105" s="24"/>
+      <c r="AG105" s="24"/>
+      <c r="AH105" s="24"/>
+      <c r="AI105" s="24"/>
+      <c r="AJ105" s="24"/>
+      <c r="AK105" s="24"/>
+      <c r="AL105" s="25"/>
+    </row>
+    <row r="106" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B106" s="21" t="s">
         <v>42</v>
       </c>
@@ -4999,37 +6107,49 @@
         <v>33</v>
       </c>
       <c r="D106" s="19">
-        <v>0.6</v>
+        <v>-0.36482277121374629</v>
       </c>
       <c r="E106" s="19">
-        <v>0.59905001257264878</v>
+        <v>-0.16485186429756171</v>
       </c>
       <c r="F106" s="19">
-        <v>0.44301653237672201</v>
+        <v>0.6446639540341722</v>
       </c>
       <c r="G106" s="19">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="H106" s="19">
-        <v>-0.1</v>
+        <v>-1.2</v>
       </c>
       <c r="I106" s="19">
-        <v>1.127877560947194</v>
+        <v>0.78149180291177556</v>
       </c>
       <c r="J106" s="19">
-        <v>0.9</v>
+        <v>0.375</v>
       </c>
       <c r="K106" s="19">
-        <v>0.2</v>
+        <v>-0.67913528710848503</v>
       </c>
       <c r="L106" s="19">
-        <v>0</v>
+        <v>-0.81246464867356938</v>
       </c>
       <c r="M106" s="20">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="107" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="AA106" s="21"/>
+      <c r="AB106" s="18"/>
+      <c r="AC106" s="19"/>
+      <c r="AD106" s="19"/>
+      <c r="AE106" s="19"/>
+      <c r="AF106" s="19"/>
+      <c r="AG106" s="19"/>
+      <c r="AH106" s="19"/>
+      <c r="AI106" s="19"/>
+      <c r="AJ106" s="19"/>
+      <c r="AK106" s="19"/>
+      <c r="AL106" s="20"/>
+    </row>
+    <row r="107" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B107" s="6" t="s">
         <v>44</v>
       </c>
@@ -5037,75 +6157,99 @@
         <v>33</v>
       </c>
       <c r="D107" s="4">
-        <v>0.85</v>
+        <v>0.99029807479322729</v>
       </c>
       <c r="E107" s="4">
-        <v>0.90515638212672056</v>
+        <v>0.99558242362588045</v>
       </c>
       <c r="F107" s="4">
-        <v>0.46133043886260983</v>
+        <v>0.58899383197798394</v>
       </c>
       <c r="G107" s="4">
-        <v>1.775788154885261</v>
+        <v>2.4298719384043821</v>
       </c>
       <c r="H107" s="4">
-        <v>-0.2475404344179033</v>
+        <v>-0.41780837525143832</v>
       </c>
       <c r="I107" s="4">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="J107" s="4">
-        <v>1.2377583019893561</v>
+        <v>1.3461916558747979</v>
       </c>
       <c r="K107" s="4">
-        <v>0.6</v>
+        <v>0.70716759170165955</v>
       </c>
       <c r="L107" s="4">
-        <v>0.35399999999999998</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="M107" s="5">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="108" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="AA107" s="6"/>
+      <c r="AB107" s="3"/>
+      <c r="AC107" s="4"/>
+      <c r="AD107" s="4"/>
+      <c r="AE107" s="4"/>
+      <c r="AF107" s="4"/>
+      <c r="AG107" s="4"/>
+      <c r="AH107" s="4"/>
+      <c r="AI107" s="4"/>
+      <c r="AJ107" s="4"/>
+      <c r="AK107" s="4"/>
+      <c r="AL107" s="5"/>
+    </row>
+    <row r="108" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B108" s="21" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C108" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D108" s="19">
-        <v>0.9</v>
+        <v>0.95649339143928302</v>
       </c>
       <c r="E108" s="19">
-        <v>0.80447436610126755</v>
+        <v>1.083483637838178</v>
       </c>
       <c r="F108" s="19">
-        <v>0.38537918576876729</v>
+        <v>0.56159124498069291</v>
       </c>
       <c r="G108" s="19">
-        <v>1.507512499999963</v>
+        <v>2.38418147629387</v>
       </c>
       <c r="H108" s="19">
         <v>-0.1</v>
       </c>
       <c r="I108" s="19">
-        <v>1.2452808900705301</v>
+        <v>1.8513543569747239</v>
       </c>
       <c r="J108" s="19">
-        <v>1.1000000000000001</v>
+        <v>1.363932439748119</v>
       </c>
       <c r="K108" s="19">
-        <v>0.55000000000000004</v>
+        <v>0.8</v>
       </c>
       <c r="L108" s="19">
-        <v>0.29487851523115821</v>
+        <v>0.37234335976756833</v>
       </c>
       <c r="M108" s="20">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="109" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="AA108" s="21"/>
+      <c r="AB108" s="18"/>
+      <c r="AC108" s="19"/>
+      <c r="AD108" s="19"/>
+      <c r="AE108" s="19"/>
+      <c r="AF108" s="19"/>
+      <c r="AG108" s="19"/>
+      <c r="AH108" s="19"/>
+      <c r="AI108" s="19"/>
+      <c r="AJ108" s="19"/>
+      <c r="AK108" s="19"/>
+      <c r="AL108" s="20"/>
+    </row>
+    <row r="109" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B109" s="6" t="s">
         <v>36</v>
       </c>
@@ -5113,37 +6257,49 @@
         <v>34</v>
       </c>
       <c r="D109" s="4">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="E109" s="4">
-        <v>2.9348817483542589</v>
+        <v>2.514935008320895</v>
       </c>
       <c r="F109" s="4">
-        <v>0.41607582672382798</v>
+        <v>0.60005513319056747</v>
       </c>
       <c r="G109" s="4">
         <v>3.8</v>
       </c>
       <c r="H109" s="4">
-        <v>1.87</v>
+        <v>0.93</v>
       </c>
       <c r="I109" s="4">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="J109" s="4">
-        <v>3.1709652178163461</v>
+        <v>2.8810229838139039</v>
       </c>
       <c r="K109" s="4">
-        <v>2.8</v>
+        <v>2.1475</v>
       </c>
       <c r="L109" s="4">
-        <v>2.4</v>
+        <v>1.8130119756029099</v>
       </c>
       <c r="M109" s="5">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="110" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="AA109" s="6"/>
+      <c r="AB109" s="3"/>
+      <c r="AC109" s="4"/>
+      <c r="AD109" s="4"/>
+      <c r="AE109" s="4"/>
+      <c r="AF109" s="4"/>
+      <c r="AG109" s="4"/>
+      <c r="AH109" s="4"/>
+      <c r="AI109" s="4"/>
+      <c r="AJ109" s="4"/>
+      <c r="AK109" s="4"/>
+      <c r="AL109" s="5"/>
+    </row>
+    <row r="110" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B110" s="21" t="s">
         <v>37</v>
       </c>
@@ -5151,37 +6307,49 @@
         <v>34</v>
       </c>
       <c r="D110" s="19">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="E110" s="19">
-        <v>2.9265634044282609</v>
+        <v>2.9323098688389959</v>
       </c>
       <c r="F110" s="19">
-        <v>0.54276526538865544</v>
+        <v>0.58464546547681007</v>
       </c>
       <c r="G110" s="19">
-        <v>4</v>
+        <v>4.5037547763228298</v>
       </c>
       <c r="H110" s="19">
         <v>1.9</v>
       </c>
       <c r="I110" s="19">
-        <v>3.551000000000001</v>
+        <v>3.92</v>
       </c>
       <c r="J110" s="19">
-        <v>3.212810794104509</v>
+        <v>3.1</v>
       </c>
       <c r="K110" s="19">
-        <v>2.557909812012555</v>
+        <v>2.5688768917180398</v>
       </c>
       <c r="L110" s="19">
-        <v>2</v>
+        <v>2.2509193625893871</v>
       </c>
       <c r="M110" s="20">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="111" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AA110" s="21"/>
+      <c r="AB110" s="18"/>
+      <c r="AC110" s="19"/>
+      <c r="AD110" s="19"/>
+      <c r="AE110" s="19"/>
+      <c r="AF110" s="19"/>
+      <c r="AG110" s="19"/>
+      <c r="AH110" s="19"/>
+      <c r="AI110" s="19"/>
+      <c r="AJ110" s="19"/>
+      <c r="AK110" s="19"/>
+      <c r="AL110" s="20"/>
+    </row>
+    <row r="111" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B111" s="6" t="s">
         <v>38</v>
       </c>
@@ -5192,10 +6360,10 @@
         <v>3</v>
       </c>
       <c r="E111" s="4">
-        <v>3.0999377597044901</v>
+        <v>3.0139051176356668</v>
       </c>
       <c r="F111" s="4">
-        <v>0.64938227513159175</v>
+        <v>0.6177350891627198</v>
       </c>
       <c r="G111" s="4">
         <v>5</v>
@@ -5204,22 +6372,34 @@
         <v>2</v>
       </c>
       <c r="I111" s="4">
-        <v>3.77</v>
+        <v>3.698608495568926</v>
       </c>
       <c r="J111" s="4">
-        <v>3.5</v>
+        <v>3.2872526117354122</v>
       </c>
       <c r="K111" s="4">
-        <v>2.754418346441839</v>
+        <v>2.7245603446666529</v>
       </c>
       <c r="L111" s="4">
-        <v>2.2396837053027441</v>
+        <v>2.26285990933181</v>
       </c>
       <c r="M111" s="5">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="112" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="AA111" s="6"/>
+      <c r="AB111" s="3"/>
+      <c r="AC111" s="4"/>
+      <c r="AD111" s="4"/>
+      <c r="AE111" s="4"/>
+      <c r="AF111" s="4"/>
+      <c r="AG111" s="4"/>
+      <c r="AH111" s="4"/>
+      <c r="AI111" s="4"/>
+      <c r="AJ111" s="4"/>
+      <c r="AK111" s="4"/>
+      <c r="AL111" s="5"/>
+    </row>
+    <row r="112" spans="2:38" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B112" s="9" t="s">
         <v>51</v>
       </c>
@@ -5234,6 +6414,18 @@
       <c r="K112" s="10"/>
       <c r="L112" s="10"/>
       <c r="M112" s="10"/>
+      <c r="AA112" s="9"/>
+      <c r="AB112" s="10"/>
+      <c r="AC112" s="10"/>
+      <c r="AD112" s="10"/>
+      <c r="AE112" s="10"/>
+      <c r="AF112" s="10"/>
+      <c r="AG112" s="10"/>
+      <c r="AH112" s="10"/>
+      <c r="AI112" s="10"/>
+      <c r="AJ112" s="10"/>
+      <c r="AK112" s="10"/>
+      <c r="AL112" s="10"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -5253,7 +6445,7 @@
   <sheetPr codeName="Hoja3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:M98"/>
+  <dimension ref="B2:M99"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.5703125" style="1" customWidth="1"/>
@@ -5283,18 +6475,18 @@
       <c r="M2" s="11"/>
     </row>
     <row r="3" spans="2:13" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="L4" s="12"/>
@@ -5356,37 +6548,37 @@
     </row>
     <row r="7" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B7" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="4">
-        <v>1.9490078178879839</v>
+        <v>1.909055504108458</v>
       </c>
       <c r="E7" s="4">
-        <v>1.9400390894399191</v>
+        <v>1.945277520542293</v>
       </c>
       <c r="F7" s="4">
-        <v>7.1092298929169614E-2</v>
+        <v>8.0501683771755456E-2</v>
       </c>
       <c r="G7" s="4">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="4">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="I7" s="4">
-        <v>2.0099999999999998</v>
+        <v>2</v>
       </c>
       <c r="J7" s="4">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="K7" s="4">
-        <v>1.9</v>
+        <v>1.825</v>
       </c>
       <c r="L7" s="4">
-        <v>1.895</v>
+        <v>1.8</v>
       </c>
       <c r="M7" s="5">
         <v>10</v>
@@ -5394,37 +6586,37 @@
     </row>
     <row r="8" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B8" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="19">
-        <v>1.9687975648281439</v>
+        <v>1.7452222151306029</v>
       </c>
       <c r="E8" s="19">
-        <v>1.9750000000000001</v>
+        <v>1.75</v>
       </c>
       <c r="F8" s="19">
-        <v>0.17195619139879259</v>
+        <v>0.1306342451664084</v>
       </c>
       <c r="G8" s="19">
-        <v>2.2000000000000002</v>
+        <v>1.9122221513060349</v>
       </c>
       <c r="H8" s="19">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="I8" s="19">
-        <v>2.2000000000000002</v>
+        <v>1.9012222151306031</v>
       </c>
       <c r="J8" s="19">
-        <v>2.1184817362110828</v>
+        <v>1.8374999999999999</v>
       </c>
       <c r="K8" s="19">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="L8" s="19">
-        <v>1.798</v>
+        <v>1.617</v>
       </c>
       <c r="M8" s="20">
         <v>10</v>
@@ -5432,37 +6624,37 @@
     </row>
     <row r="9" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="4">
-        <v>1.7683431734163499</v>
+        <v>1.758725300233237</v>
       </c>
       <c r="E9" s="4">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="F9" s="4">
-        <v>0.27016217044134699</v>
+        <v>0.17078971412376481</v>
       </c>
       <c r="G9" s="4">
-        <v>2.2999999999999998</v>
+        <v>2.04</v>
       </c>
       <c r="H9" s="4">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="I9" s="4">
-        <v>1.997088560747148</v>
+        <v>1.9590000000000001</v>
       </c>
       <c r="J9" s="4">
-        <v>1.8875</v>
+        <v>1.872939751749277</v>
       </c>
       <c r="K9" s="4">
-        <v>1.5575000000000001</v>
+        <v>1.625</v>
       </c>
       <c r="L9" s="4">
-        <v>1.486</v>
+        <v>1.59</v>
       </c>
       <c r="M9" s="5">
         <v>10</v>
@@ -5470,37 +6662,37 @@
     </row>
     <row r="10" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B10" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="19">
-        <v>1.800998995955652</v>
+        <v>1.6778327653828771</v>
       </c>
       <c r="E10" s="19">
-        <v>1.854994979778261</v>
+        <v>1.65</v>
       </c>
       <c r="F10" s="19">
-        <v>0.22605009554768341</v>
+        <v>0.1668286571685047</v>
       </c>
       <c r="G10" s="19">
-        <v>2.12</v>
+        <v>1.9383276538287659</v>
       </c>
       <c r="H10" s="19">
         <v>1.5</v>
       </c>
       <c r="I10" s="19">
-        <v>2.012</v>
+        <v>1.894832765382876</v>
       </c>
       <c r="J10" s="19">
-        <v>1.9875</v>
+        <v>1.8125</v>
       </c>
       <c r="K10" s="19">
-        <v>1.6</v>
+        <v>1.5249999999999999</v>
       </c>
       <c r="L10" s="19">
-        <v>1.5269999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="M10" s="20">
         <v>10</v>
@@ -5508,37 +6700,37 @@
     </row>
     <row r="11" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="4">
-        <v>1.6861327619079209</v>
+        <v>1.64582308738359</v>
       </c>
       <c r="E11" s="4">
-        <v>1.7050000000000001</v>
+        <v>1.605</v>
       </c>
       <c r="F11" s="4">
-        <v>0.2093683667094963</v>
+        <v>0.14335100806957751</v>
       </c>
       <c r="G11" s="4">
-        <v>1.9413276190792159</v>
+        <v>1.9</v>
       </c>
       <c r="H11" s="4">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="I11" s="4">
-        <v>1.904132761907922</v>
+        <v>1.81</v>
       </c>
       <c r="J11" s="4">
-        <v>1.8875</v>
+        <v>1.744557718458974</v>
       </c>
       <c r="K11" s="4">
-        <v>1.5</v>
+        <v>1.5249999999999999</v>
       </c>
       <c r="L11" s="4">
-        <v>1.486</v>
+        <v>1.4970000000000001</v>
       </c>
       <c r="M11" s="5">
         <v>10</v>
@@ -5546,37 +6738,37 @@
     </row>
     <row r="12" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B12" s="17">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="19">
-        <v>1.6248937462650279</v>
+        <v>1.77514548325473</v>
       </c>
       <c r="E12" s="19">
-        <v>1.6644687313251421</v>
+        <v>1.7749999999999999</v>
       </c>
       <c r="F12" s="19">
-        <v>0.19477276881410549</v>
+        <v>0.2095808763005311</v>
       </c>
       <c r="G12" s="19">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="H12" s="19">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="I12" s="19">
-        <v>1.8</v>
+        <v>2.0459999999999998</v>
       </c>
       <c r="J12" s="19">
-        <v>1.7875000000000001</v>
+        <v>1.8975</v>
       </c>
       <c r="K12" s="19">
-        <v>1.52</v>
+        <v>1.6153637081368259</v>
       </c>
       <c r="L12" s="19">
-        <v>1.4690000000000001</v>
+        <v>1.5089999999999999</v>
       </c>
       <c r="M12" s="20">
         <v>10</v>
@@ -5584,37 +6776,37 @@
     </row>
     <row r="13" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B13" s="2">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="4">
-        <v>1.782162125705923</v>
+        <v>1.7110060298667411</v>
       </c>
       <c r="E13" s="4">
-        <v>1.7749999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="F13" s="4">
-        <v>0.40257046021018389</v>
+        <v>0.2472736505907841</v>
       </c>
       <c r="G13" s="4">
-        <v>2.4500000000000002</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H13" s="4">
-        <v>1.06</v>
+        <v>1.5</v>
       </c>
       <c r="I13" s="4">
-        <v>2.1349999999999998</v>
+        <v>1.931</v>
       </c>
       <c r="J13" s="4">
-        <v>2.0750000000000002</v>
+        <v>1.762545224000557</v>
       </c>
       <c r="K13" s="4">
-        <v>1.5404053142648091</v>
+        <v>1.5075000000000001</v>
       </c>
       <c r="L13" s="4">
-        <v>1.3660000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="M13" s="5">
         <v>10</v>
@@ -5625,34 +6817,34 @@
         <v>14</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="19">
-        <v>22.259142582968028</v>
+        <v>21.385899376768201</v>
       </c>
       <c r="E14" s="19">
-        <v>22.544601408409751</v>
+        <v>21.649675394879651</v>
       </c>
       <c r="F14" s="19">
-        <v>2.0360743030345021</v>
+        <v>2.298236641761513</v>
       </c>
       <c r="G14" s="19">
-        <v>25.02319267747275</v>
+        <v>24.531727757926909</v>
       </c>
       <c r="H14" s="19">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I14" s="19">
-        <v>24.462319267747269</v>
+        <v>23.963172775792689</v>
       </c>
       <c r="J14" s="19">
-        <v>23.374272751541049</v>
+        <v>22.77033242073524</v>
       </c>
       <c r="K14" s="19">
-        <v>21.285</v>
+        <v>20.102499999999999</v>
       </c>
       <c r="L14" s="19">
-        <v>20.25</v>
+        <v>18.981853385845071</v>
       </c>
       <c r="M14" s="20">
         <v>10</v>
@@ -5666,37 +6858,37 @@
         <v>16</v>
       </c>
       <c r="D15" s="4">
-        <v>29.974791789561301</v>
+        <v>29.65260639977593</v>
       </c>
       <c r="E15" s="4">
-        <v>30.245000000000001</v>
+        <v>29.918046643009671</v>
       </c>
       <c r="F15" s="4">
-        <v>1.523546164158287</v>
+        <v>0.78550301418302748</v>
       </c>
       <c r="G15" s="4">
-        <v>32.185246601537877</v>
+        <v>30.4021147952839</v>
       </c>
       <c r="H15" s="4">
-        <v>27.03</v>
+        <v>28.28</v>
       </c>
       <c r="I15" s="4">
-        <v>31.568524660153791</v>
+        <v>30.400211479528391</v>
       </c>
       <c r="J15" s="4">
-        <v>30.742003470556359</v>
+        <v>30.2679278742511</v>
       </c>
       <c r="K15" s="4">
-        <v>29.234999999999999</v>
+        <v>29.080988021030311</v>
       </c>
       <c r="L15" s="4">
-        <v>28.155000000000001</v>
+        <v>28.568000000000001</v>
       </c>
       <c r="M15" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B18" s="14" t="s">
         <v>18</v>
       </c>
@@ -5752,37 +6944,37 @@
     </row>
     <row r="20" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B20" s="2">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="4">
-        <v>1.948064249045719</v>
+        <v>1.772517225229193</v>
       </c>
       <c r="E20" s="4">
-        <v>1.906738866343155</v>
+        <v>1.77</v>
       </c>
       <c r="F20" s="4">
-        <v>0.16257906350735879</v>
+        <v>0.13919340900790511</v>
       </c>
       <c r="G20" s="4">
-        <v>2.205000000000001</v>
+        <v>2.0011722522919269</v>
       </c>
       <c r="H20" s="4">
-        <v>1.68216475777088</v>
+        <v>1.5840000000000001</v>
       </c>
       <c r="I20" s="4">
-        <v>2.2004999999999999</v>
+        <v>1.9101172252291929</v>
       </c>
       <c r="J20" s="4">
-        <v>2</v>
+        <v>1.885</v>
       </c>
       <c r="K20" s="4">
-        <v>1.885</v>
+        <v>1.67</v>
       </c>
       <c r="L20" s="4">
-        <v>1.788216475777088</v>
+        <v>1.5984</v>
       </c>
       <c r="M20" s="5">
         <v>10</v>
@@ -5790,37 +6982,37 @@
     </row>
     <row r="21" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B21" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="19">
-        <v>1.9783629770519779</v>
+        <v>1.7086995002705141</v>
       </c>
       <c r="E21" s="19">
-        <v>1.9650000000000001</v>
+        <v>1.67</v>
       </c>
       <c r="F21" s="19">
-        <v>0.19205183206256071</v>
+        <v>0.18043677832976041</v>
       </c>
       <c r="G21" s="19">
-        <v>2.31</v>
+        <v>2.0309950027051382</v>
       </c>
       <c r="H21" s="19">
-        <v>1.5936297705197799</v>
+        <v>1.496</v>
       </c>
       <c r="I21" s="19">
-        <v>2.2109999999999999</v>
+        <v>1.913099500270514</v>
       </c>
       <c r="J21" s="19">
-        <v>2.0375000000000001</v>
+        <v>1.83</v>
       </c>
       <c r="K21" s="19">
-        <v>1.9</v>
+        <v>1.575</v>
       </c>
       <c r="L21" s="19">
-        <v>1.869362977051978</v>
+        <v>1.5176000000000001</v>
       </c>
       <c r="M21" s="20">
         <v>10</v>
@@ -5828,37 +7020,37 @@
     </row>
     <row r="22" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B22" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="4">
-        <v>1.8578629770519779</v>
+        <v>1.648094619600178</v>
       </c>
       <c r="E22" s="4">
-        <v>1.82</v>
+        <v>1.575</v>
       </c>
       <c r="F22" s="4">
-        <v>0.2164954273272664</v>
+        <v>0.2191106421493477</v>
       </c>
       <c r="G22" s="4">
-        <v>2.415</v>
+        <v>2.1279461960017838</v>
       </c>
       <c r="H22" s="4">
-        <v>1.5936297705197799</v>
+        <v>1.4079999999999999</v>
       </c>
       <c r="I22" s="4">
-        <v>1.9515</v>
+        <v>1.8912946196001781</v>
       </c>
       <c r="J22" s="4">
-        <v>1.8875</v>
+        <v>1.73</v>
       </c>
       <c r="K22" s="4">
-        <v>1.7849999999999999</v>
+        <v>1.5125</v>
       </c>
       <c r="L22" s="4">
-        <v>1.689362977051978</v>
+        <v>1.4368000000000001</v>
       </c>
       <c r="M22" s="5">
         <v>10</v>
@@ -5866,37 +7058,37 @@
     </row>
     <row r="23" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B23" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="19">
-        <v>1.773862977051978</v>
+        <v>1.5827427322734899</v>
       </c>
       <c r="E23" s="19">
-        <v>1.74</v>
+        <v>1.56</v>
       </c>
       <c r="F23" s="19">
-        <v>0.15106372162834841</v>
+        <v>0.1984315062297278</v>
       </c>
       <c r="G23" s="19">
-        <v>2</v>
+        <v>1.902177322734899</v>
       </c>
       <c r="H23" s="19">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="I23" s="19">
-        <v>1.9550000000000001</v>
+        <v>1.8419427322734889</v>
       </c>
       <c r="J23" s="19">
-        <v>1.8912500000000001</v>
+        <v>1.6850000000000001</v>
       </c>
       <c r="K23" s="19">
-        <v>1.7</v>
+        <v>1.5075000000000001</v>
       </c>
       <c r="L23" s="19">
-        <v>1.589266793467802</v>
+        <v>1.3160000000000001</v>
       </c>
       <c r="M23" s="20">
         <v>10</v>
@@ -5904,37 +7096,37 @@
     </row>
     <row r="24" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B24" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="4">
-        <v>1.7249293765420219</v>
+        <v>1.5958064637613349</v>
       </c>
       <c r="E24" s="4">
-        <v>1.7</v>
+        <v>1.5649999999999999</v>
       </c>
       <c r="F24" s="4">
-        <v>0.1171597255307667</v>
+        <v>0.16914962371173339</v>
       </c>
       <c r="G24" s="4">
-        <v>1.9</v>
+        <v>1.809962499999999</v>
       </c>
       <c r="H24" s="4">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="I24" s="4">
-        <v>1.855</v>
+        <v>1.8009962500000001</v>
       </c>
       <c r="J24" s="4">
-        <v>1.827687499999999</v>
+        <v>1.7500766032100079</v>
       </c>
       <c r="K24" s="4">
-        <v>1.6417828240651651</v>
+        <v>1.5</v>
       </c>
       <c r="L24" s="4">
-        <v>1.595</v>
+        <v>1.4690000000000001</v>
       </c>
       <c r="M24" s="5">
         <v>10</v>
@@ -5942,37 +7134,37 @@
     </row>
     <row r="25" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B25" s="17">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="19">
-        <v>1.6655057283268679</v>
+        <v>1.6813816026735111</v>
       </c>
       <c r="E25" s="19">
-        <v>1.7050000000000001</v>
+        <v>1.7450000000000001</v>
       </c>
       <c r="F25" s="19">
-        <v>0.13131017017933519</v>
+        <v>0.18160658539069191</v>
       </c>
       <c r="G25" s="19">
-        <v>1.809962499999999</v>
+        <v>2</v>
       </c>
       <c r="H25" s="19">
-        <v>1.5</v>
+        <v>1.380147901735107</v>
       </c>
       <c r="I25" s="19">
-        <v>1.8009962500000001</v>
+        <v>1.81568</v>
       </c>
       <c r="J25" s="19">
-        <v>1.7875000000000001</v>
+        <v>1.7788510937499999</v>
       </c>
       <c r="K25" s="19">
-        <v>1.523821087451511</v>
+        <v>1.5375000000000001</v>
       </c>
       <c r="L25" s="19">
-        <v>1.5</v>
+        <v>1.488014790173511</v>
       </c>
       <c r="M25" s="20">
         <v>10</v>
@@ -5980,37 +7172,37 @@
     </row>
     <row r="26" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B26" s="2">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="4">
-        <v>1.8145632882770879</v>
+        <v>1.6572435483882899</v>
       </c>
       <c r="E26" s="4">
-        <v>1.7649999999999999</v>
+        <v>1.63</v>
       </c>
       <c r="F26" s="4">
-        <v>0.1313698066096009</v>
+        <v>0.24347367675150389</v>
       </c>
       <c r="G26" s="4">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H26" s="4">
-        <v>1.68216475777088</v>
+        <v>1.32</v>
       </c>
       <c r="I26" s="4">
-        <v>2</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="J26" s="4">
-        <v>1.94336703125</v>
+        <v>1.745457824095725</v>
       </c>
       <c r="K26" s="4">
-        <v>1.7124999999999999</v>
+        <v>1.4970000000000001</v>
       </c>
       <c r="L26" s="4">
-        <v>1.6982164757770879</v>
+        <v>1.4415</v>
       </c>
       <c r="M26" s="5">
         <v>10</v>
@@ -6021,34 +7213,34 @@
         <v>14</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D27" s="19">
-        <v>22.724355533511709</v>
+        <v>20.910635077753721</v>
       </c>
       <c r="E27" s="19">
-        <v>22.093718925768979</v>
+        <v>20.952028159920399</v>
       </c>
       <c r="F27" s="19">
-        <v>1.741925570083982</v>
+        <v>2.3305978834516381</v>
       </c>
       <c r="G27" s="19">
-        <v>26.61</v>
+        <v>23.7</v>
       </c>
       <c r="H27" s="19">
-        <v>20.74</v>
+        <v>16.846391467136002</v>
       </c>
       <c r="I27" s="19">
-        <v>24.260999999999999</v>
+        <v>23.52</v>
       </c>
       <c r="J27" s="19">
-        <v>23.57270090459329</v>
+        <v>22.900980703311951</v>
       </c>
       <c r="K27" s="19">
-        <v>21.822295736030341</v>
+        <v>19.423887525990029</v>
       </c>
       <c r="L27" s="19">
-        <v>20.974</v>
+        <v>18.2716391467136</v>
       </c>
       <c r="M27" s="20">
         <v>10</v>
@@ -6062,31 +7254,31 @@
         <v>16</v>
       </c>
       <c r="D28" s="4">
-        <v>29.126677433279959</v>
+        <v>27.565289279378199</v>
       </c>
       <c r="E28" s="4">
-        <v>29.02</v>
+        <v>27.45</v>
       </c>
       <c r="F28" s="4">
-        <v>1.072540698728097</v>
+        <v>1.034267004112092</v>
       </c>
       <c r="G28" s="4">
-        <v>31.12817292329089</v>
+        <v>29.151349718484251</v>
       </c>
       <c r="H28" s="4">
-        <v>27.25237170981303</v>
+        <v>25.918174815210332</v>
       </c>
       <c r="I28" s="4">
-        <v>30.29281729232909</v>
+        <v>28.902669966772951</v>
       </c>
       <c r="J28" s="4">
-        <v>29.562172274771779</v>
+        <v>28.282499999999999</v>
       </c>
       <c r="K28" s="4">
-        <v>28.762499999999999</v>
+        <v>26.812498912668399</v>
       </c>
       <c r="L28" s="4">
-        <v>27.9972371709813</v>
+        <v>26.6293152254731</v>
       </c>
       <c r="M28" s="5">
         <v>10</v>
@@ -6096,7 +7288,7 @@
       <c r="B30" s="22"/>
       <c r="C30" s="23"/>
     </row>
-    <row r="31" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B31" s="14" t="s">
         <v>35</v>
       </c>
@@ -6152,37 +7344,37 @@
     </row>
     <row r="33" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B33" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C33" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D33" s="27">
-        <v>22.77200511508952</v>
+        <v>22.740509609184048</v>
       </c>
       <c r="E33" s="27">
-        <v>22.680025575447569</v>
+        <v>22.55</v>
       </c>
       <c r="F33" s="27">
-        <v>0.58112424991507838</v>
+        <v>1.176748686323507</v>
       </c>
       <c r="G33" s="27">
-        <v>24</v>
+        <v>25.313953364862879</v>
       </c>
       <c r="H33" s="27">
-        <v>22.06</v>
+        <v>21.37806981031099</v>
       </c>
       <c r="I33" s="27">
-        <v>23.37</v>
+        <v>24.131395336486289</v>
       </c>
       <c r="J33" s="27">
-        <v>23</v>
+        <v>22.95</v>
       </c>
       <c r="K33" s="27">
-        <v>22.35</v>
+        <v>22.074999999999999</v>
       </c>
       <c r="L33" s="27">
-        <v>22.186</v>
+        <v>21.499572606031101</v>
       </c>
       <c r="M33" s="20">
         <v>10</v>
@@ -6190,37 +7382,37 @@
     </row>
     <row r="34" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B34" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="26">
-        <v>23.007054739102099</v>
+        <v>22.60695162160934</v>
       </c>
       <c r="E34" s="26">
-        <v>22.93</v>
+        <v>22.8</v>
       </c>
       <c r="F34" s="26">
-        <v>0.78268684599607674</v>
+        <v>1.3716928934609549</v>
       </c>
       <c r="G34" s="26">
-        <v>24.378782685138638</v>
+        <v>25.824582987707529</v>
       </c>
       <c r="H34" s="26">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I34" s="26">
-        <v>23.857878268513861</v>
+        <v>23.282458298770749</v>
       </c>
       <c r="J34" s="26">
-        <v>23.6</v>
+        <v>22.95</v>
       </c>
       <c r="K34" s="26">
-        <v>22.35794117647059</v>
+        <v>21.719520233789378</v>
       </c>
       <c r="L34" s="26">
-        <v>22.18</v>
+        <v>21.077015625000001</v>
       </c>
       <c r="M34" s="5">
         <v>10</v>
@@ -6228,37 +7420,37 @@
     </row>
     <row r="35" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B35" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C35" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D35" s="27">
-        <v>23.30091813575854</v>
+        <v>22.710917944833739</v>
       </c>
       <c r="E35" s="27">
-        <v>23.15</v>
+        <v>22.6</v>
       </c>
       <c r="F35" s="27">
-        <v>1.3153656147975941</v>
+        <v>2.56122134919026</v>
       </c>
       <c r="G35" s="27">
-        <v>25.717416651703079</v>
+        <v>28.982258372729358</v>
       </c>
       <c r="H35" s="27">
-        <v>21.5</v>
+        <v>19.067560763888888</v>
       </c>
       <c r="I35" s="27">
-        <v>24.67574166517031</v>
+        <v>24.101650117820189</v>
       </c>
       <c r="J35" s="27">
-        <v>24.225000000000001</v>
+        <v>22.8</v>
       </c>
       <c r="K35" s="27">
-        <v>22.28294117647058</v>
+        <v>22.05</v>
       </c>
       <c r="L35" s="27">
-        <v>22.04</v>
+        <v>20.356756076388891</v>
       </c>
       <c r="M35" s="20">
         <v>10</v>
@@ -6266,75 +7458,75 @@
     </row>
     <row r="36" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B36" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D36" s="26">
-        <v>23.361038173225051</v>
+        <v>22.50009865759942</v>
       </c>
       <c r="E36" s="26">
+        <v>22.5</v>
+      </c>
+      <c r="F36" s="26">
+        <v>2.0561746097930329</v>
+      </c>
+      <c r="G36" s="26">
+        <v>25.641698340266782</v>
+      </c>
+      <c r="H36" s="26">
+        <v>19.067560763888888</v>
+      </c>
+      <c r="I36" s="26">
+        <v>25.596724558681341</v>
+      </c>
+      <c r="J36" s="26">
         <v>22.8</v>
       </c>
-      <c r="F36" s="26">
-        <v>1.52662048047145</v>
-      </c>
-      <c r="G36" s="26">
-        <v>26.118617026368149</v>
-      </c>
-      <c r="H36" s="26">
-        <v>21.5</v>
-      </c>
-      <c r="I36" s="26">
-        <v>25.61586170263681</v>
-      </c>
-      <c r="J36" s="26">
-        <v>24</v>
-      </c>
       <c r="K36" s="26">
-        <v>22.28294117647058</v>
+        <v>22.024999999999999</v>
       </c>
       <c r="L36" s="26">
-        <v>22.04</v>
+        <v>19.906756076388891</v>
       </c>
       <c r="M36" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="17">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C37" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D37" s="27">
-        <v>23.18341785699516</v>
+        <v>22.485342559190109</v>
       </c>
       <c r="E37" s="27">
-        <v>22.415882352941171</v>
+        <v>22.8</v>
       </c>
       <c r="F37" s="27">
-        <v>1.732028967234027</v>
+        <v>2.2117017442021289</v>
       </c>
       <c r="G37" s="27">
-        <v>26.59</v>
+        <v>25.710320936233391</v>
       </c>
       <c r="H37" s="27">
-        <v>21.5</v>
+        <v>19.067560763888888</v>
       </c>
       <c r="I37" s="27">
-        <v>26.025172477662281</v>
+        <v>25.589021596224299</v>
       </c>
       <c r="J37" s="27">
-        <v>23.475000000000001</v>
+        <v>23.225000000000001</v>
       </c>
       <c r="K37" s="27">
-        <v>22.137499999999999</v>
+        <v>21.274999999999999</v>
       </c>
       <c r="L37" s="27">
-        <v>22.04</v>
+        <v>19.456756076388888</v>
       </c>
       <c r="M37" s="20">
         <v>10</v>
@@ -6342,37 +7534,37 @@
     </row>
     <row r="38" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B38" s="2">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D38" s="26">
-        <v>23.106975163802272</v>
+        <v>21.907803558118712</v>
       </c>
       <c r="E38" s="26">
-        <v>22.31588235294118</v>
+        <v>22.05</v>
       </c>
       <c r="F38" s="26">
-        <v>1.7165506021105441</v>
+        <v>2.5355116408557921</v>
       </c>
       <c r="G38" s="26">
-        <v>26.58</v>
+        <v>26.454814361485109</v>
       </c>
       <c r="H38" s="26">
-        <v>21.5</v>
+        <v>18.59087174479167</v>
       </c>
       <c r="I38" s="26">
-        <v>25.345188238926291</v>
+        <v>25.122406913612199</v>
       </c>
       <c r="J38" s="26">
-        <v>24.074999999999999</v>
+        <v>22.785799319727889</v>
       </c>
       <c r="K38" s="26">
-        <v>22.024999999999999</v>
+        <v>19.853697638593101</v>
       </c>
       <c r="L38" s="26">
-        <v>21.725000000000001</v>
+        <v>18.959087174479169</v>
       </c>
       <c r="M38" s="5">
         <v>10</v>
@@ -6383,34 +7575,34 @@
         <v>14</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D39" s="27">
-        <v>21.41646317151401</v>
+        <v>23.184366885045531</v>
       </c>
       <c r="E39" s="27">
-        <v>20.5</v>
+        <v>22.203499999999998</v>
       </c>
       <c r="F39" s="27">
-        <v>3.4204586308639868</v>
+        <v>4.7667192445907984</v>
       </c>
       <c r="G39" s="27">
-        <v>28.69823439014737</v>
+        <v>34.7606076740121</v>
       </c>
       <c r="H39" s="27">
-        <v>16.240514972051521</v>
+        <v>19</v>
       </c>
       <c r="I39" s="27">
-        <v>24.23582343901473</v>
+        <v>27.8895158262001</v>
       </c>
       <c r="J39" s="27">
-        <v>22.95</v>
+        <v>23.75</v>
       </c>
       <c r="K39" s="27">
-        <v>20.32147058823529</v>
+        <v>20.07</v>
       </c>
       <c r="L39" s="27">
-        <v>17.824051497205151</v>
+        <v>19.170999999999999</v>
       </c>
       <c r="M39" s="20">
         <v>10</v>
@@ -6424,31 +7616,31 @@
         <v>20</v>
       </c>
       <c r="D40" s="26">
-        <v>23.106975163802272</v>
+        <v>22.485342559190109</v>
       </c>
       <c r="E40" s="26">
-        <v>22.31588235294118</v>
+        <v>22.8</v>
       </c>
       <c r="F40" s="26">
-        <v>1.7165506021105441</v>
+        <v>2.2117017442021289</v>
       </c>
       <c r="G40" s="26">
-        <v>26.58</v>
+        <v>25.710320936233391</v>
       </c>
       <c r="H40" s="26">
-        <v>21.5</v>
+        <v>19.067560763888888</v>
       </c>
       <c r="I40" s="26">
-        <v>25.345188238926291</v>
+        <v>25.589021596224299</v>
       </c>
       <c r="J40" s="26">
-        <v>24.074999999999999</v>
+        <v>23.225000000000001</v>
       </c>
       <c r="K40" s="26">
-        <v>22.024999999999999</v>
+        <v>21.274999999999999</v>
       </c>
       <c r="L40" s="26">
-        <v>21.725000000000001</v>
+        <v>19.456756076388888</v>
       </c>
       <c r="M40" s="5">
         <v>10</v>
@@ -6458,7 +7650,7 @@
       <c r="B41" s="22"/>
       <c r="C41" s="23"/>
     </row>
-    <row r="43" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B43" s="14" t="s">
         <v>21</v>
       </c>
@@ -6514,37 +7706,37 @@
     </row>
     <row r="45" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B45" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C45" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D45" s="32">
-        <v>1470.412317963468</v>
-      </c>
-      <c r="E45" s="32">
-        <v>1471.79563630489</v>
-      </c>
-      <c r="F45" s="32">
-        <v>18.37070183331749</v>
-      </c>
-      <c r="G45" s="32">
-        <v>1498.0971705613861</v>
-      </c>
-      <c r="H45" s="32">
-        <v>1437.704736463515</v>
-      </c>
-      <c r="I45" s="32">
-        <v>1491.709717056139</v>
-      </c>
-      <c r="J45" s="32">
-        <v>1481.1824999999999</v>
-      </c>
-      <c r="K45" s="32">
-        <v>1458</v>
-      </c>
-      <c r="L45" s="32">
-        <v>1451.4704736463509</v>
+      <c r="D45" s="31">
+        <v>1507.8801390950621</v>
+      </c>
+      <c r="E45" s="31">
+        <v>1507.36687052142</v>
+      </c>
+      <c r="F45" s="19">
+        <v>9.5000102384142533</v>
+      </c>
+      <c r="G45" s="31">
+        <v>1523.7</v>
+      </c>
+      <c r="H45" s="31">
+        <v>1493.941658614204</v>
+      </c>
+      <c r="I45" s="31">
+        <v>1523.209087069652</v>
+      </c>
+      <c r="J45" s="31">
+        <v>1509.3</v>
+      </c>
+      <c r="K45" s="31">
+        <v>1502.467862526267</v>
+      </c>
+      <c r="L45" s="31">
+        <v>1498.49416586142</v>
       </c>
       <c r="M45" s="20">
         <v>10</v>
@@ -6552,37 +7744,37 @@
     </row>
     <row r="46" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B46" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D46" s="33">
-        <v>1497.6632158940961</v>
-      </c>
-      <c r="E46" s="33">
-        <v>1499.327797179174</v>
-      </c>
-      <c r="F46" s="33">
-        <v>21.71542137806183</v>
-      </c>
-      <c r="G46" s="33">
-        <v>1532.9523239169</v>
-      </c>
-      <c r="H46" s="33">
-        <v>1469.3342406657121</v>
-      </c>
-      <c r="I46" s="33">
-        <v>1524.6162323916899</v>
-      </c>
-      <c r="J46" s="33">
-        <v>1509.75</v>
-      </c>
-      <c r="K46" s="33">
-        <v>1479.75</v>
-      </c>
-      <c r="L46" s="33">
-        <v>1469.933424066571</v>
+      <c r="D46" s="30">
+        <v>1532.5083628305849</v>
+      </c>
+      <c r="E46" s="30">
+        <v>1531.47056810348</v>
+      </c>
+      <c r="F46" s="4">
+        <v>18.51374871200689</v>
+      </c>
+      <c r="G46" s="30">
+        <v>1561.8</v>
+      </c>
+      <c r="H46" s="30">
+        <v>1506</v>
+      </c>
+      <c r="I46" s="30">
+        <v>1561.252522330672</v>
+      </c>
+      <c r="J46" s="30">
+        <v>1539.2500128452141</v>
+      </c>
+      <c r="K46" s="30">
+        <v>1519.5130876200631</v>
+      </c>
+      <c r="L46" s="30">
+        <v>1513.2</v>
       </c>
       <c r="M46" s="5">
         <v>10</v>
@@ -6590,37 +7782,37 @@
     </row>
     <row r="47" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B47" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C47" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D47" s="32">
-        <v>1530.631898003181</v>
-      </c>
-      <c r="E47" s="32">
-        <v>1528.5</v>
-      </c>
-      <c r="F47" s="32">
-        <v>32.491364668734739</v>
-      </c>
-      <c r="G47" s="32">
-        <v>1576.55</v>
-      </c>
-      <c r="H47" s="32">
-        <v>1483.1</v>
-      </c>
-      <c r="I47" s="32">
-        <v>1569.411584434014</v>
-      </c>
-      <c r="J47" s="32">
-        <v>1559.6702198724099</v>
-      </c>
-      <c r="K47" s="32">
-        <v>1503.5176947897689</v>
-      </c>
-      <c r="L47" s="32">
-        <v>1496.51</v>
+      <c r="D47" s="31">
+        <v>1558.7468676493861</v>
+      </c>
+      <c r="E47" s="31">
+        <v>1556.133567761239</v>
+      </c>
+      <c r="F47" s="19">
+        <v>30.758774211637281</v>
+      </c>
+      <c r="G47" s="31">
+        <v>1608.6</v>
+      </c>
+      <c r="H47" s="31">
+        <v>1514</v>
+      </c>
+      <c r="I47" s="31">
+        <v>1603.7691476731229</v>
+      </c>
+      <c r="J47" s="31">
+        <v>1572.9548320665681</v>
+      </c>
+      <c r="K47" s="31">
+        <v>1541.5720339343641</v>
+      </c>
+      <c r="L47" s="31">
+        <v>1523</v>
       </c>
       <c r="M47" s="20">
         <v>10</v>
@@ -6628,37 +7820,37 @@
     </row>
     <row r="48" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B48" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D48" s="33">
-        <v>1564.2871918463579</v>
-      </c>
-      <c r="E48" s="33">
-        <v>1553.5</v>
-      </c>
-      <c r="F48" s="33">
-        <v>49.471012604648173</v>
-      </c>
-      <c r="G48" s="33">
-        <v>1632.8298553875111</v>
-      </c>
-      <c r="H48" s="33">
-        <v>1490</v>
-      </c>
-      <c r="I48" s="33">
-        <v>1623.757985538751</v>
-      </c>
-      <c r="J48" s="33">
-        <v>1606.153587011765</v>
-      </c>
-      <c r="K48" s="33">
-        <v>1532.6082862717531</v>
-      </c>
-      <c r="L48" s="33">
-        <v>1508.9</v>
+      <c r="D48" s="30">
+        <v>1582.821659286893</v>
+      </c>
+      <c r="E48" s="30">
+        <v>1580.3393048454191</v>
+      </c>
+      <c r="F48" s="4">
+        <v>40.309619738875689</v>
+      </c>
+      <c r="G48" s="30">
+        <v>1642.783809353323</v>
+      </c>
+      <c r="H48" s="30">
+        <v>1520</v>
+      </c>
+      <c r="I48" s="30">
+        <v>1640.9983809353321</v>
+      </c>
+      <c r="J48" s="30">
+        <v>1606.0787659251939</v>
+      </c>
+      <c r="K48" s="30">
+        <v>1563.636864443379</v>
+      </c>
+      <c r="L48" s="30">
+        <v>1535.3</v>
       </c>
       <c r="M48" s="5">
         <v>10</v>
@@ -6666,37 +7858,37 @@
     </row>
     <row r="49" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B49" s="17">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C49" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D49" s="32">
-        <v>1593.062576279819</v>
-      </c>
-      <c r="E49" s="32">
-        <v>1570</v>
-      </c>
-      <c r="F49" s="32">
-        <v>63.538797752164122</v>
-      </c>
-      <c r="G49" s="32">
-        <v>1685.1811000842349</v>
-      </c>
-      <c r="H49" s="32">
-        <v>1497</v>
-      </c>
-      <c r="I49" s="32">
-        <v>1665.020110008423</v>
-      </c>
-      <c r="J49" s="32">
-        <v>1651.6398483460939</v>
-      </c>
-      <c r="K49" s="32">
-        <v>1560.126317332396</v>
-      </c>
-      <c r="L49" s="32">
-        <v>1524</v>
+      <c r="D49" s="31">
+        <v>1605.3736448478039</v>
+      </c>
+      <c r="E49" s="31">
+        <v>1596.5</v>
+      </c>
+      <c r="F49" s="19">
+        <v>48.51780132257413</v>
+      </c>
+      <c r="G49" s="31">
+        <v>1673.6</v>
+      </c>
+      <c r="H49" s="31">
+        <v>1527</v>
+      </c>
+      <c r="I49" s="31">
+        <v>1672.2085514334069</v>
+      </c>
+      <c r="J49" s="31">
+        <v>1640.924247088029</v>
+      </c>
+      <c r="K49" s="31">
+        <v>1586.71141741003</v>
+      </c>
+      <c r="L49" s="31">
+        <v>1548.6</v>
       </c>
       <c r="M49" s="20">
         <v>10</v>
@@ -6704,37 +7896,37 @@
     </row>
     <row r="50" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B50" s="2">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D50" s="33">
-        <v>1621.38409277294</v>
-      </c>
-      <c r="E50" s="33">
-        <v>1597</v>
-      </c>
-      <c r="F50" s="33">
-        <v>78.355582620653081</v>
-      </c>
-      <c r="G50" s="33">
-        <v>1737</v>
-      </c>
-      <c r="H50" s="33">
-        <v>1503</v>
-      </c>
-      <c r="I50" s="33">
-        <v>1707.57</v>
-      </c>
-      <c r="J50" s="33">
-        <v>1689.4758297826761</v>
-      </c>
-      <c r="K50" s="33">
-        <v>1585.3644021496741</v>
-      </c>
-      <c r="L50" s="33">
-        <v>1524.6</v>
+      <c r="D50" s="30">
+        <v>1627.1768483710771</v>
+      </c>
+      <c r="E50" s="30">
+        <v>1622.6</v>
+      </c>
+      <c r="F50" s="4">
+        <v>55.316864450457317</v>
+      </c>
+      <c r="G50" s="30">
+        <v>1703.2</v>
+      </c>
+      <c r="H50" s="30">
+        <v>1532</v>
+      </c>
+      <c r="I50" s="30">
+        <v>1689.931494621102</v>
+      </c>
+      <c r="J50" s="30">
+        <v>1674.7719149730781</v>
+      </c>
+      <c r="K50" s="30">
+        <v>1608.657680108123</v>
+      </c>
+      <c r="L50" s="30">
+        <v>1559</v>
       </c>
       <c r="M50" s="5">
         <v>10</v>
@@ -6745,34 +7937,34 @@
         <v>14</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D51" s="32">
-        <v>1765.627124957166</v>
-      </c>
-      <c r="E51" s="32">
-        <v>1767.5</v>
-      </c>
-      <c r="F51" s="32">
-        <v>139.8766384293879</v>
-      </c>
-      <c r="G51" s="32">
-        <v>1970</v>
-      </c>
-      <c r="H51" s="32">
-        <v>1535</v>
-      </c>
-      <c r="I51" s="32">
-        <v>1922.6051053899009</v>
-      </c>
-      <c r="J51" s="32">
-        <v>1881.9525000000001</v>
-      </c>
-      <c r="K51" s="32">
-        <v>1692.530560895721</v>
-      </c>
-      <c r="L51" s="32">
-        <v>1598</v>
+        <v>50</v>
+      </c>
+      <c r="D51" s="31">
+        <v>1770.7747062220949</v>
+      </c>
+      <c r="E51" s="31">
+        <v>1766.2776468190859</v>
+      </c>
+      <c r="F51" s="19">
+        <v>114.2284604342176</v>
+      </c>
+      <c r="G51" s="31">
+        <v>1925.137424294614</v>
+      </c>
+      <c r="H51" s="31">
+        <v>1575</v>
+      </c>
+      <c r="I51" s="31">
+        <v>1902.513742429461</v>
+      </c>
+      <c r="J51" s="31">
+        <v>1863.75</v>
+      </c>
+      <c r="K51" s="31">
+        <v>1706.01358607204</v>
+      </c>
+      <c r="L51" s="31">
+        <v>1637.1</v>
       </c>
       <c r="M51" s="20">
         <v>10</v>
@@ -6785,32 +7977,32 @@
       <c r="C52" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D52" s="33">
-        <v>1621.38409277294</v>
-      </c>
-      <c r="E52" s="33">
-        <v>1597</v>
-      </c>
-      <c r="F52" s="33">
-        <v>78.355582620653081</v>
-      </c>
-      <c r="G52" s="33">
-        <v>1737</v>
-      </c>
-      <c r="H52" s="33">
-        <v>1503</v>
-      </c>
-      <c r="I52" s="33">
-        <v>1707.57</v>
-      </c>
-      <c r="J52" s="33">
-        <v>1689.4758297826761</v>
-      </c>
-      <c r="K52" s="33">
-        <v>1585.3644021496741</v>
-      </c>
-      <c r="L52" s="33">
-        <v>1524.6</v>
+      <c r="D52" s="30">
+        <v>1605.3736448478039</v>
+      </c>
+      <c r="E52" s="30">
+        <v>1596.5</v>
+      </c>
+      <c r="F52" s="4">
+        <v>48.51780132257413</v>
+      </c>
+      <c r="G52" s="30">
+        <v>1673.6</v>
+      </c>
+      <c r="H52" s="30">
+        <v>1527</v>
+      </c>
+      <c r="I52" s="30">
+        <v>1672.2085514334069</v>
+      </c>
+      <c r="J52" s="30">
+        <v>1640.924247088029</v>
+      </c>
+      <c r="K52" s="30">
+        <v>1586.71141741003</v>
+      </c>
+      <c r="L52" s="30">
+        <v>1548.6</v>
       </c>
       <c r="M52" s="5">
         <v>10</v>
@@ -6880,37 +8072,37 @@
     </row>
     <row r="57" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B57" s="17">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C57" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D57" s="31">
-        <v>9037.4040445464179</v>
+        <v>9114.3404774388182</v>
       </c>
       <c r="E57" s="31">
-        <v>9055.7349498346866</v>
-      </c>
-      <c r="F57" s="31">
-        <v>249.7701614519213</v>
+        <v>9081.9729354166593</v>
+      </c>
+      <c r="F57" s="35">
+        <v>423.99503912923672</v>
       </c>
       <c r="G57" s="31">
-        <v>9447</v>
+        <v>9678.0851647567706</v>
       </c>
       <c r="H57" s="31">
-        <v>8637.7646955909076</v>
+        <v>8500</v>
       </c>
       <c r="I57" s="31">
-        <v>9296.3943959798435</v>
+        <v>9543.6607470745421</v>
       </c>
       <c r="J57" s="31">
-        <v>9178.9501722776622</v>
+        <v>9505.5775485693357</v>
       </c>
       <c r="K57" s="31">
-        <v>8947.5</v>
+        <v>8789.0186439034987</v>
       </c>
       <c r="L57" s="31">
-        <v>8674.4420941922981</v>
+        <v>8570.0239579836179</v>
       </c>
       <c r="M57" s="20">
         <v>10</v>
@@ -6918,37 +8110,37 @@
     </row>
     <row r="58" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B58" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D58" s="30">
-        <v>8948.9958206388947</v>
+        <v>9109.7315467613553</v>
       </c>
       <c r="E58" s="30">
-        <v>9065.9729354166593</v>
-      </c>
-      <c r="F58" s="30">
-        <v>546.06215451606533</v>
+        <v>9189.7669509685002</v>
+      </c>
+      <c r="F58" s="36">
+        <v>501.93836023526228</v>
       </c>
       <c r="G58" s="30">
-        <v>9607.375445483829</v>
+        <v>10165.564280137931</v>
       </c>
       <c r="H58" s="30">
-        <v>8000</v>
+        <v>8500</v>
       </c>
       <c r="I58" s="30">
-        <v>9529.4306028315859</v>
+        <v>9473.2331295672157</v>
       </c>
       <c r="J58" s="30">
-        <v>9395.25</v>
+        <v>9303.5</v>
       </c>
       <c r="K58" s="30">
-        <v>8660.8131256375927</v>
+        <v>8717.4762353394162</v>
       </c>
       <c r="L58" s="30">
-        <v>8211.6043920162956</v>
+        <v>8519.8044082094584</v>
       </c>
       <c r="M58" s="5">
         <v>10</v>
@@ -6956,37 +8148,37 @@
     </row>
     <row r="59" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B59" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C59" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D59" s="31">
-        <v>8878.634566970708</v>
+        <v>8919.9310512758166</v>
       </c>
       <c r="E59" s="31">
-        <v>9018.5728190144364</v>
-      </c>
-      <c r="F59" s="31">
-        <v>528.12825831798648</v>
+        <v>8720.2811940924967</v>
+      </c>
+      <c r="F59" s="35">
+        <v>729.06295504720492</v>
       </c>
       <c r="G59" s="31">
-        <v>9597</v>
+        <v>10615.8881347724</v>
       </c>
       <c r="H59" s="31">
-        <v>8000</v>
+        <v>8206</v>
       </c>
       <c r="I59" s="31">
-        <v>9364.2699546427102</v>
+        <v>9566.5888134772395</v>
       </c>
       <c r="J59" s="31">
-        <v>9274.2911979310938</v>
+        <v>9174.1388891008828</v>
       </c>
       <c r="K59" s="31">
-        <v>8447.9768561844048</v>
+        <v>8427.039500883242</v>
       </c>
       <c r="L59" s="31">
-        <v>8260.5439540865082</v>
+        <v>8240.2180240514335</v>
       </c>
       <c r="M59" s="20">
         <v>10</v>
@@ -6994,37 +8186,37 @@
     </row>
     <row r="60" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B60" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D60" s="30">
-        <v>8628.5894663954077</v>
+        <v>8806.1279840867537</v>
       </c>
       <c r="E60" s="30">
-        <v>8704.7811940924967</v>
-      </c>
-      <c r="F60" s="30">
-        <v>497.50320633809793</v>
+        <v>8596.5</v>
+      </c>
+      <c r="F60" s="36">
+        <v>829.37134977170081</v>
       </c>
       <c r="G60" s="30">
-        <v>9235</v>
+        <v>10829.486808082331</v>
       </c>
       <c r="H60" s="30">
-        <v>8000</v>
+        <v>7965.7426762584164</v>
       </c>
       <c r="I60" s="30">
-        <v>9183.8957175269061</v>
+        <v>9497.9486808082329</v>
       </c>
       <c r="J60" s="30">
-        <v>9064.5274110537339</v>
+        <v>8954.4658310675241</v>
       </c>
       <c r="K60" s="30">
-        <v>8152.8868894375864</v>
+        <v>8377.2071660198308</v>
       </c>
       <c r="L60" s="30">
-        <v>8023.9061700756911</v>
+        <v>8022.6742676258418</v>
       </c>
       <c r="M60" s="5">
         <v>10</v>
@@ -7032,37 +8224,37 @@
     </row>
     <row r="61" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B61" s="17">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C61" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D61" s="31">
-        <v>8555.892470159175</v>
+        <v>8286.0651784577567</v>
       </c>
       <c r="E61" s="31">
-        <v>8631.9116434019998</v>
-      </c>
-      <c r="F61" s="31">
-        <v>404.28584223888163</v>
+        <v>7999.5</v>
+      </c>
+      <c r="F61" s="35">
+        <v>917.28745091576616</v>
       </c>
       <c r="G61" s="31">
-        <v>9070</v>
+        <v>10754.40831195166</v>
       </c>
       <c r="H61" s="31">
-        <v>7961.6746609917782</v>
+        <v>7629.7620461218703</v>
       </c>
       <c r="I61" s="31">
-        <v>8967.7264592163501</v>
+        <v>8668.2458797798026</v>
       </c>
       <c r="J61" s="31">
-        <v>8867.027401900039</v>
+        <v>8391.4150847903547</v>
       </c>
       <c r="K61" s="31">
-        <v>8219.7386034332994</v>
+        <v>7755.1429471978017</v>
       </c>
       <c r="L61" s="31">
-        <v>7996.1674660991775</v>
+        <v>7663.276204612187</v>
       </c>
       <c r="M61" s="20">
         <v>10</v>
@@ -7070,37 +8262,37 @@
     </row>
     <row r="62" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B62" s="2">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D62" s="30">
-        <v>8057.7556913287526</v>
+        <v>8306.5389876654008</v>
       </c>
       <c r="E62" s="30">
-        <v>8001.6353278219658</v>
-      </c>
-      <c r="F62" s="30">
-        <v>471.51993448765108</v>
+        <v>8045.2406139619088</v>
+      </c>
+      <c r="F62" s="36">
+        <v>868.3848842026058</v>
       </c>
       <c r="G62" s="30">
-        <v>8900</v>
+        <v>10431.305485114641</v>
       </c>
       <c r="H62" s="30">
-        <v>7200</v>
+        <v>7563</v>
       </c>
       <c r="I62" s="30">
-        <v>8482.8050485846379</v>
+        <v>9139.5305485114641</v>
       </c>
       <c r="J62" s="30">
-        <v>8362.2718935118992</v>
+        <v>8453.0532673307825</v>
       </c>
       <c r="K62" s="30">
-        <v>7881.0504862940979</v>
+        <v>7729.5903435107393</v>
       </c>
       <c r="L62" s="30">
-        <v>7562.4131830988454</v>
+        <v>7588.2</v>
       </c>
       <c r="M62" s="5">
         <v>10</v>
@@ -7108,37 +8300,37 @@
     </row>
     <row r="63" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B63" s="17">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C63" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D63" s="31">
-        <v>8108.2064569991589</v>
+        <v>7586.4408507856469</v>
       </c>
       <c r="E63" s="31">
-        <v>8128.6567943578184</v>
-      </c>
-      <c r="F63" s="31">
-        <v>390.59275849159093</v>
+        <v>7518.194786058355</v>
+      </c>
+      <c r="F63" s="35">
+        <v>308.45947322842039</v>
       </c>
       <c r="G63" s="31">
-        <v>8503.0250200789451</v>
+        <v>8000</v>
       </c>
       <c r="H63" s="31">
-        <v>7498.9721255834384</v>
+        <v>7169.0639113038887</v>
       </c>
       <c r="I63" s="31">
-        <v>8500.3025020078949</v>
+        <v>7935.3379749778187</v>
       </c>
       <c r="J63" s="31">
-        <v>8483.1884589033962</v>
+        <v>7898.0114490970454</v>
       </c>
       <c r="K63" s="31">
-        <v>7851.5</v>
+        <v>7335.2730569455662</v>
       </c>
       <c r="L63" s="31">
-        <v>7557.4972125583436</v>
+        <v>7275.8311942243654</v>
       </c>
       <c r="M63" s="20">
         <v>10</v>
@@ -7152,31 +8344,31 @@
         <v>25</v>
       </c>
       <c r="D64" s="30">
-        <v>100569.289343401</v>
+        <v>101992.97942967351</v>
       </c>
       <c r="E64" s="30">
-        <v>100787.6637622686</v>
-      </c>
-      <c r="F64" s="30">
-        <v>2490.808745815767</v>
+        <v>100815.76885752979</v>
+      </c>
+      <c r="F64" s="36">
+        <v>4081.1492971389662</v>
       </c>
       <c r="G64" s="30">
-        <v>103598</v>
+        <v>111928.73818481569</v>
       </c>
       <c r="H64" s="30">
-        <v>96037.109413863567</v>
+        <v>98305</v>
       </c>
       <c r="I64" s="30">
-        <v>103213.6860281532</v>
+        <v>105197.8738184816</v>
       </c>
       <c r="J64" s="30">
-        <v>102682.18089081479</v>
+        <v>103234.59117889369</v>
       </c>
       <c r="K64" s="30">
-        <v>98894.25</v>
+        <v>99415.144878052757</v>
       </c>
       <c r="L64" s="30">
-        <v>97686.918690303399</v>
+        <v>98419.740005340602</v>
       </c>
       <c r="M64" s="5">
         <v>10</v>
@@ -7246,75 +8438,75 @@
     </row>
     <row r="69" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B69" s="17">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C69" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D69" s="31">
-        <v>6551.8181821127164</v>
+        <v>7052.268444832861</v>
       </c>
       <c r="E69" s="31">
-        <v>6489.1450000000004</v>
-      </c>
-      <c r="F69" s="31">
-        <v>351.76824792585899</v>
+        <v>7086.5586521113273</v>
+      </c>
+      <c r="F69" s="35">
+        <v>147.26660529503931</v>
       </c>
       <c r="G69" s="31">
-        <v>7168.72</v>
+        <v>7240</v>
       </c>
       <c r="H69" s="31">
-        <v>6137.4464661806587</v>
+        <v>6824.7223639653439</v>
       </c>
       <c r="I69" s="31">
-        <v>6946.9480533933747</v>
+        <v>7213.4711592670492</v>
       </c>
       <c r="J69" s="31">
-        <v>6809.2825299766973</v>
+        <v>7161.3010275704482</v>
       </c>
       <c r="K69" s="31">
-        <v>6255.7925742447696</v>
+        <v>6939.4098767351643</v>
       </c>
       <c r="L69" s="31">
-        <v>6226.0073125023291</v>
+        <v>6851.0722363965342</v>
       </c>
       <c r="M69" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D70" s="30">
-        <v>6882.171759478535</v>
+        <v>6861.260135845022</v>
       </c>
       <c r="E70" s="30">
-        <v>6850.5823052483074</v>
-      </c>
-      <c r="F70" s="30">
-        <v>372.25516794125002</v>
+        <v>6947.2735061230705</v>
+      </c>
+      <c r="F70" s="36">
+        <v>254.07638626587669</v>
       </c>
       <c r="G70" s="30">
-        <v>7422.03</v>
+        <v>7185.4036831541416</v>
       </c>
       <c r="H70" s="30">
-        <v>6261.5333408658234</v>
+        <v>6463</v>
       </c>
       <c r="I70" s="30">
-        <v>7273.143</v>
+        <v>7154.4403683154142</v>
       </c>
       <c r="J70" s="30">
-        <v>7190.1936602929891</v>
+        <v>7000.0520201582476</v>
       </c>
       <c r="K70" s="30">
-        <v>6681.6486050524136</v>
+        <v>6708.094705020806</v>
       </c>
       <c r="L70" s="30">
-        <v>6442.297356629806</v>
+        <v>6487.5283644978517</v>
       </c>
       <c r="M70" s="5">
         <v>10</v>
@@ -7322,37 +8514,37 @@
     </row>
     <row r="71" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B71" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C71" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D71" s="31">
-        <v>6756.3980884336752</v>
+        <v>6966.3664834211204</v>
       </c>
       <c r="E71" s="31">
-        <v>6690.3573271466921</v>
-      </c>
-      <c r="F71" s="31">
-        <v>343.66178635895761</v>
+        <v>6951</v>
+      </c>
+      <c r="F71" s="35">
+        <v>275.01669387206942</v>
       </c>
       <c r="G71" s="31">
-        <v>7290.49</v>
+        <v>7456.0388043566936</v>
       </c>
       <c r="H71" s="31">
-        <v>6220.6495191451713</v>
+        <v>6485.4398714765784</v>
       </c>
       <c r="I71" s="31">
-        <v>7195.9123148387271</v>
+        <v>7233.4462662664873</v>
       </c>
       <c r="J71" s="31">
-        <v>7031.6349786848441</v>
+        <v>7151.0708616009924</v>
       </c>
       <c r="K71" s="31">
-        <v>6529.3869883749794</v>
+        <v>6802.0432063239496</v>
       </c>
       <c r="L71" s="31">
-        <v>6463.2933164123688</v>
+        <v>6718.3941240442236</v>
       </c>
       <c r="M71" s="20">
         <v>10</v>
@@ -7360,37 +8552,37 @@
     </row>
     <row r="72" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B72" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D72" s="30">
-        <v>6770.6086930994688</v>
+        <v>6876.9245646630707</v>
       </c>
       <c r="E72" s="30">
-        <v>6760.8154513102872</v>
-      </c>
-      <c r="F72" s="30">
-        <v>503.39627472129928</v>
+        <v>6970.4853059699653</v>
+      </c>
+      <c r="F72" s="36">
+        <v>282.02666303803232</v>
       </c>
       <c r="G72" s="30">
-        <v>7613.9</v>
+        <v>7167</v>
       </c>
       <c r="H72" s="30">
-        <v>5801.3762093660598</v>
+        <v>6378.6304191872841</v>
       </c>
       <c r="I72" s="30">
-        <v>7249.2323858308173</v>
+        <v>7151.7</v>
       </c>
       <c r="J72" s="30">
-        <v>7078.8302828272499</v>
+        <v>7055.2577263323165</v>
       </c>
       <c r="K72" s="30">
-        <v>6503.2849049840679</v>
+        <v>6800.1262268568407</v>
       </c>
       <c r="L72" s="30">
-        <v>6331.1408304273464</v>
+        <v>6399.1140839594</v>
       </c>
       <c r="M72" s="5">
         <v>10</v>
@@ -7398,37 +8590,37 @@
     </row>
     <row r="73" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B73" s="17">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C73" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D73" s="31">
-        <v>6705.5583381064152</v>
+        <v>6314.4925052379449</v>
       </c>
       <c r="E73" s="31">
-        <v>6896.6950267337197</v>
-      </c>
-      <c r="F73" s="31">
-        <v>418.38881804621059</v>
+        <v>6189.6950963704776</v>
+      </c>
+      <c r="F73" s="35">
+        <v>513.29359349301615</v>
       </c>
       <c r="G73" s="31">
-        <v>7074.3991128733842</v>
+        <v>7017.5111313089974</v>
       </c>
       <c r="H73" s="31">
-        <v>5705.8326799021979</v>
+        <v>5598</v>
       </c>
       <c r="I73" s="31">
-        <v>7020.7959112873386</v>
+        <v>6921.6511131308998</v>
       </c>
       <c r="J73" s="31">
-        <v>6973.9108831492676</v>
+        <v>6811.6956058691312</v>
       </c>
       <c r="K73" s="31">
-        <v>6562.9535043375736</v>
+        <v>5967.5413558882519</v>
       </c>
       <c r="L73" s="31">
-        <v>6331.8343100308912</v>
+        <v>5777.9844984501206</v>
       </c>
       <c r="M73" s="20">
         <v>10</v>
@@ -7436,75 +8628,75 @@
     </row>
     <row r="74" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B74" s="2">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D74" s="30">
-        <v>6313.4239196228173</v>
+        <v>6192.4733722954152</v>
       </c>
       <c r="E74" s="30">
-        <v>6451.688958400021</v>
-      </c>
-      <c r="F74" s="30">
-        <v>507.1676552722721</v>
+        <v>6090.3126635479784</v>
+      </c>
+      <c r="F74" s="36">
+        <v>548.51790196534876</v>
       </c>
       <c r="G74" s="30">
-        <v>6926.2276415778151</v>
+        <v>7166.8561912724499</v>
       </c>
       <c r="H74" s="30">
-        <v>5358.3417419697053</v>
+        <v>5498.1455859689804</v>
       </c>
       <c r="I74" s="30">
-        <v>6787.6933879985309</v>
+        <v>6869.8391428213017</v>
       </c>
       <c r="J74" s="30">
-        <v>6715.0088200013961</v>
+        <v>6520.5946453971292</v>
       </c>
       <c r="K74" s="30">
-        <v>5987.9174999999996</v>
+        <v>5817.8548153073252</v>
       </c>
       <c r="L74" s="30">
-        <v>5754.018672647092</v>
+        <v>5550.2145585968983</v>
       </c>
       <c r="M74" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="17">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C75" s="18" t="s">
         <v>25</v>
       </c>
       <c r="D75" s="31">
-        <v>6222.1524661352332</v>
+        <v>6045.903290695107</v>
       </c>
       <c r="E75" s="31">
-        <v>6142.93</v>
-      </c>
-      <c r="F75" s="31">
-        <v>668.84422712974708</v>
+        <v>6056.6895694166778</v>
+      </c>
+      <c r="F75" s="35">
+        <v>567.59685298450904</v>
       </c>
       <c r="G75" s="31">
-        <v>7203.7312280968417</v>
+        <v>6867.6903700676767</v>
       </c>
       <c r="H75" s="31">
-        <v>4918.2185989196932</v>
+        <v>5208.71</v>
       </c>
       <c r="I75" s="31">
-        <v>7195.2788341943651</v>
+        <v>6696.7248829728542</v>
       </c>
       <c r="J75" s="31">
-        <v>6469.7419528555311</v>
+        <v>6453.0397606723736</v>
       </c>
       <c r="K75" s="31">
-        <v>5954.2888502696078</v>
+        <v>5685.3280894338468</v>
       </c>
       <c r="L75" s="31">
-        <v>5700.0960981529161</v>
+        <v>5247.9063665377889</v>
       </c>
       <c r="M75" s="20">
         <v>10</v>
@@ -7518,31 +8710,31 @@
         <v>25</v>
       </c>
       <c r="D76" s="30">
-        <v>74777.444275749294</v>
+        <v>75795.630999170651</v>
       </c>
       <c r="E76" s="30">
-        <v>74898.406994736724</v>
-      </c>
-      <c r="F76" s="30">
-        <v>2396.411596796037</v>
+        <v>76212.02726919188</v>
+      </c>
+      <c r="F76" s="36">
+        <v>1333.31111337934</v>
       </c>
       <c r="G76" s="30">
-        <v>77315.149999999994</v>
+        <v>77300</v>
       </c>
       <c r="H76" s="30">
-        <v>68978.521358499303</v>
+        <v>73837.831692513268</v>
       </c>
       <c r="I76" s="30">
-        <v>77135.471243715365</v>
+        <v>77133.956243715365</v>
       </c>
       <c r="J76" s="30">
-        <v>76349.320785959804</v>
+        <v>76786.187836806421</v>
       </c>
       <c r="K76" s="30">
-        <v>74125</v>
+        <v>74625.5</v>
       </c>
       <c r="L76" s="30">
-        <v>73322.576617550934</v>
+        <v>73910.771540835049</v>
       </c>
       <c r="M76" s="5">
         <v>10</v>
@@ -7562,7 +8754,7 @@
       <c r="L77" s="10"/>
       <c r="M77" s="10"/>
     </row>
-    <row r="79" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B79" s="14" t="s">
         <v>27</v>
       </c>
@@ -7617,498 +8809,536 @@
       </c>
     </row>
     <row r="81" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B81" s="6" t="s">
+      <c r="B81" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C81" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="30">
-        <v>15836.79840434871</v>
-      </c>
-      <c r="E81" s="30">
-        <v>15741.5</v>
-      </c>
-      <c r="F81" s="30">
-        <v>2387.8197008217089</v>
-      </c>
-      <c r="G81" s="30">
+      <c r="D81" s="32">
+        <v>15128.113060884471</v>
+      </c>
+      <c r="E81" s="32">
+        <v>14561.5</v>
+      </c>
+      <c r="F81" s="32">
+        <v>2717.8591949458</v>
+      </c>
+      <c r="G81" s="32">
         <v>21056</v>
       </c>
-      <c r="H81" s="30">
-        <v>12696.110347427109</v>
-      </c>
-      <c r="I81" s="30">
-        <v>18131.080999999998</v>
-      </c>
-      <c r="J81" s="30">
-        <v>16101.462613104781</v>
-      </c>
-      <c r="K81" s="30">
-        <v>15166.957449599129</v>
-      </c>
-      <c r="L81" s="30">
-        <v>12780.21228595202</v>
-      </c>
-      <c r="M81" s="5">
+      <c r="H81" s="32">
+        <v>11470</v>
+      </c>
+      <c r="I81" s="32">
+        <v>18060.421999999999</v>
+      </c>
+      <c r="J81" s="32">
+        <v>15845.3127745528</v>
+      </c>
+      <c r="K81" s="32">
+        <v>13786.63247273963</v>
+      </c>
+      <c r="L81" s="32">
+        <v>12657.601251209309</v>
+      </c>
+      <c r="M81" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B82" s="9"/>
-      <c r="C82" s="10"/>
-      <c r="D82" s="10"/>
-      <c r="E82" s="10"/>
-      <c r="F82" s="10"/>
-      <c r="G82" s="10"/>
-      <c r="H82" s="10"/>
-      <c r="I82" s="10"/>
-      <c r="J82" s="10"/>
-      <c r="K82" s="10"/>
-      <c r="L82" s="10"/>
-      <c r="M82" s="10"/>
-    </row>
-    <row r="84" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="14" t="s">
+    <row r="82" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D82" s="33">
+        <v>19429.486883779191</v>
+      </c>
+      <c r="E82" s="33">
+        <v>19575.5</v>
+      </c>
+      <c r="F82" s="33">
+        <v>2690.2428523222588</v>
+      </c>
+      <c r="G82" s="33">
+        <v>22542.95823806425</v>
+      </c>
+      <c r="H82" s="33">
+        <v>14500</v>
+      </c>
+      <c r="I82" s="33">
+        <v>22324.80882380643</v>
+      </c>
+      <c r="J82" s="33">
+        <v>21761.075000000001</v>
+      </c>
+      <c r="K82" s="33">
+        <v>18176.75</v>
+      </c>
+      <c r="L82" s="33">
+        <v>15894.136539754951</v>
+      </c>
+      <c r="M82" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B83" s="9"/>
+      <c r="C83" s="10"/>
+      <c r="D83" s="10"/>
+      <c r="E83" s="10"/>
+      <c r="F83" s="10"/>
+      <c r="G83" s="10"/>
+      <c r="H83" s="10"/>
+      <c r="I83" s="10"/>
+      <c r="J83" s="10"/>
+      <c r="K83" s="10"/>
+      <c r="L83" s="10"/>
+      <c r="M83" s="10"/>
+    </row>
+    <row r="85" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B85" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C84" s="14"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="14"/>
-      <c r="I84" s="14"/>
-      <c r="J84" s="14"/>
-      <c r="K84" s="14"/>
-      <c r="L84" s="14"/>
-      <c r="M84" s="15"/>
-    </row>
-    <row r="85" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B85" s="24" t="s">
+      <c r="C85" s="14"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="14"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="14"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="14"/>
+      <c r="K85" s="14"/>
+      <c r="L85" s="14"/>
+      <c r="M85" s="15"/>
+    </row>
+    <row r="86" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B86" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C85" s="24" t="s">
+      <c r="C86" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D85" s="16" t="s">
+      <c r="D86" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E85" s="16" t="s">
+      <c r="E86" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F85" s="24" t="s">
+      <c r="F86" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G85" s="24" t="s">
+      <c r="G86" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H85" s="24" t="s">
+      <c r="H86" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I85" s="24" t="s">
+      <c r="I86" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J85" s="24" t="s">
+      <c r="J86" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K85" s="24" t="s">
+      <c r="K86" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="L85" s="24" t="s">
+      <c r="L86" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="M85" s="25" t="s">
+      <c r="M86" s="25" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B86" s="17" t="s">
+    <row r="87" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B87" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C86" s="18" t="s">
+      <c r="C87" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D86" s="19">
-        <v>7.641</v>
-      </c>
-      <c r="E86" s="19">
+      <c r="D87" s="19">
+        <v>7.6763692212322976</v>
+      </c>
+      <c r="E87" s="19">
         <v>7.7</v>
       </c>
-      <c r="F86" s="19">
-        <v>0.25414125556032369</v>
-      </c>
-      <c r="G86" s="19">
+      <c r="F87" s="19">
+        <v>0.2337202636337872</v>
+      </c>
+      <c r="G87" s="19">
         <v>8.1</v>
       </c>
-      <c r="H86" s="19">
-        <v>7.2</v>
-      </c>
-      <c r="I86" s="19">
+      <c r="H87" s="19">
+        <v>7.3</v>
+      </c>
+      <c r="I87" s="19">
         <v>7.92</v>
       </c>
-      <c r="J86" s="19">
-        <v>7.7</v>
-      </c>
-      <c r="K86" s="19">
-        <v>7.5025000000000004</v>
-      </c>
-      <c r="L86" s="19">
-        <v>7.3800000000000008</v>
-      </c>
-      <c r="M86" s="20">
+      <c r="J87" s="19">
+        <v>7.7750000000000004</v>
+      </c>
+      <c r="K87" s="19">
+        <v>7.5477691592422387</v>
+      </c>
+      <c r="L87" s="19">
+        <v>7.3900000000000006</v>
+      </c>
+      <c r="M87" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="6" t="s">
+    <row r="88" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B88" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C88" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D87" s="4">
-        <v>7.3040000000000003</v>
-      </c>
-      <c r="E87" s="4">
-        <v>7.45</v>
-      </c>
-      <c r="F87" s="4">
-        <v>0.6288296006603592</v>
-      </c>
-      <c r="G87" s="4">
+      <c r="D88" s="4">
+        <v>7.3335048500175244</v>
+      </c>
+      <c r="E88" s="4">
+        <v>7.4</v>
+      </c>
+      <c r="F88" s="4">
+        <v>0.62052165127716929</v>
+      </c>
+      <c r="G88" s="4">
         <v>8.4</v>
       </c>
-      <c r="H87" s="4">
-        <v>6.3</v>
-      </c>
-      <c r="I87" s="4">
-        <v>7.77</v>
-      </c>
-      <c r="J87" s="4">
+      <c r="H88" s="4">
+        <v>6.4</v>
+      </c>
+      <c r="I88" s="4">
+        <v>7.95</v>
+      </c>
+      <c r="J88" s="4">
         <v>7.6775000000000002</v>
       </c>
-      <c r="K87" s="4">
-        <v>6.875</v>
-      </c>
-      <c r="L87" s="4">
-        <v>6.5070000000000006</v>
-      </c>
-      <c r="M87" s="5">
+      <c r="K88" s="4">
+        <v>6.95</v>
+      </c>
+      <c r="L88" s="4">
+        <v>6.5125436501577019</v>
+      </c>
+      <c r="M88" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B88" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C88" s="18" t="s">
+    <row r="89" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B89" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C89" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D88" s="19">
-        <v>7.4520000000000008</v>
-      </c>
-      <c r="E88" s="19">
-        <v>7.35</v>
-      </c>
-      <c r="F88" s="19">
-        <v>0.28584378017838108</v>
-      </c>
-      <c r="G88" s="19">
+      <c r="D89" s="19">
+        <v>7.673339213840161</v>
+      </c>
+      <c r="E89" s="19">
+        <v>7.6</v>
+      </c>
+      <c r="F89" s="19">
+        <v>0.47524936886544977</v>
+      </c>
+      <c r="G89" s="19">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="H89" s="19">
+        <v>7</v>
+      </c>
+      <c r="I89" s="19">
+        <v>8.07</v>
+      </c>
+      <c r="J89" s="19">
+        <v>7.93</v>
+      </c>
+      <c r="K89" s="19">
+        <v>7.4</v>
+      </c>
+      <c r="L89" s="19">
+        <v>7.2820529245614436</v>
+      </c>
+      <c r="M89" s="20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B90" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D90" s="4">
+        <v>7.673339213840161</v>
+      </c>
+      <c r="E90" s="4">
+        <v>7.6</v>
+      </c>
+      <c r="F90" s="4">
+        <v>0.47524936886544977</v>
+      </c>
+      <c r="G90" s="4">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="H90" s="4">
+        <v>7</v>
+      </c>
+      <c r="I90" s="4">
+        <v>8.07</v>
+      </c>
+      <c r="J90" s="4">
+        <v>7.93</v>
+      </c>
+      <c r="K90" s="4">
+        <v>7.4</v>
+      </c>
+      <c r="L90" s="4">
+        <v>7.2820529245614436</v>
+      </c>
+      <c r="M90" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B91" s="9"/>
+      <c r="C91" s="9"/>
+      <c r="D91" s="9"/>
+      <c r="E91" s="9"/>
+      <c r="F91" s="9"/>
+      <c r="G91" s="9"/>
+      <c r="H91" s="9"/>
+      <c r="I91" s="9"/>
+      <c r="J91" s="9"/>
+      <c r="K91" s="9"/>
+      <c r="L91" s="9"/>
+      <c r="M91" s="9"/>
+    </row>
+    <row r="93" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B93" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C93" s="14"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+      <c r="H93" s="14"/>
+      <c r="I93" s="14"/>
+      <c r="J93" s="14"/>
+      <c r="K93" s="14"/>
+      <c r="L93" s="14"/>
+      <c r="M93" s="15"/>
+    </row>
+    <row r="94" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B94" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C94" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D94" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H94" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="I94" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="H88" s="19">
-        <v>7</v>
-      </c>
-      <c r="I88" s="19">
-        <v>7.7479999999999993</v>
-      </c>
-      <c r="J88" s="19">
-        <v>7.65</v>
-      </c>
-      <c r="K88" s="19">
-        <v>7.3</v>
-      </c>
-      <c r="L88" s="19">
-        <v>7.27</v>
-      </c>
-      <c r="M88" s="20">
+      <c r="J94" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="K94" s="24" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="89" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B89" s="6" t="s">
+      <c r="L94" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="M94" s="25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B95" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C95" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D95" s="19">
+        <v>-6.3147298146425432E-2</v>
+      </c>
+      <c r="E95" s="19">
+        <v>-0.39751634995482388</v>
+      </c>
+      <c r="F95" s="19">
+        <v>0.60988853256141229</v>
+      </c>
+      <c r="G95" s="19">
+        <v>0.8</v>
+      </c>
+      <c r="H95" s="19">
+        <v>-0.71</v>
+      </c>
+      <c r="I95" s="19">
+        <v>0.77620374660085412</v>
+      </c>
+      <c r="J95" s="19">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="K95" s="19">
+        <v>-0.5</v>
+      </c>
+      <c r="L95" s="19">
+        <v>-0.61099999999999999</v>
+      </c>
+      <c r="M95" s="20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B96" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D96" s="4">
+        <v>1.1190725117402669</v>
+      </c>
+      <c r="E96" s="4">
+        <v>1.068889433634939</v>
+      </c>
+      <c r="F96" s="4">
+        <v>0.33329694681539151</v>
+      </c>
+      <c r="G96" s="4">
+        <v>1.7</v>
+      </c>
+      <c r="H96" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="I96" s="4">
+        <v>1.52</v>
+      </c>
+      <c r="J96" s="4">
+        <v>1.3922096875995911</v>
+      </c>
+      <c r="K96" s="4">
+        <v>0.8125</v>
+      </c>
+      <c r="L96" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="M96" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B97" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C97" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D97" s="19">
+        <v>1.036111500893466</v>
+      </c>
+      <c r="E97" s="19">
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="F97" s="19">
+        <v>0.47354602969504173</v>
+      </c>
+      <c r="G97" s="19">
+        <v>2</v>
+      </c>
+      <c r="H97" s="19">
+        <v>0.28265188209330988</v>
+      </c>
+      <c r="I97" s="19">
+        <v>1.4330000000000001</v>
+      </c>
+      <c r="J97" s="19">
+        <v>1.284615781710337</v>
+      </c>
+      <c r="K97" s="19">
+        <v>0.77750000000000008</v>
+      </c>
+      <c r="L97" s="19">
+        <v>0.658265188209331</v>
+      </c>
+      <c r="M97" s="20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B98" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C89" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D89" s="4">
-        <v>7.4520000000000008</v>
-      </c>
-      <c r="E89" s="4">
-        <v>7.35</v>
-      </c>
-      <c r="F89" s="4">
-        <v>0.28584378017838108</v>
-      </c>
-      <c r="G89" s="4">
-        <v>8</v>
-      </c>
-      <c r="H89" s="4">
-        <v>7</v>
-      </c>
-      <c r="I89" s="4">
-        <v>7.7479999999999993</v>
-      </c>
-      <c r="J89" s="4">
-        <v>7.65</v>
-      </c>
-      <c r="K89" s="4">
-        <v>7.3</v>
-      </c>
-      <c r="L89" s="4">
-        <v>7.27</v>
-      </c>
-      <c r="M89" s="5">
+      <c r="C98" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D98" s="4">
+        <v>2.6367890567517511</v>
+      </c>
+      <c r="E98" s="4">
+        <v>2.7</v>
+      </c>
+      <c r="F98" s="4">
+        <v>0.34026924224694738</v>
+      </c>
+      <c r="G98" s="4">
+        <v>3</v>
+      </c>
+      <c r="H98" s="4">
+        <v>2.1</v>
+      </c>
+      <c r="I98" s="4">
+        <v>3</v>
+      </c>
+      <c r="J98" s="4">
+        <v>2.9421160542391349</v>
+      </c>
+      <c r="K98" s="4">
+        <v>2.4613018713989989</v>
+      </c>
+      <c r="L98" s="4">
+        <v>2.1269999999999998</v>
+      </c>
+      <c r="M98" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9"/>
-      <c r="F90" s="9"/>
-      <c r="G90" s="9"/>
-      <c r="H90" s="9"/>
-      <c r="I90" s="9"/>
-      <c r="J90" s="9"/>
-      <c r="K90" s="9"/>
-      <c r="L90" s="9"/>
-      <c r="M90" s="9"/>
-    </row>
-    <row r="92" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C92" s="14"/>
-      <c r="D92" s="14"/>
-      <c r="E92" s="14"/>
-      <c r="F92" s="14"/>
-      <c r="G92" s="14"/>
-      <c r="H92" s="14"/>
-      <c r="I92" s="14"/>
-      <c r="J92" s="14"/>
-      <c r="K92" s="14"/>
-      <c r="L92" s="14"/>
-      <c r="M92" s="15"/>
-    </row>
-    <row r="93" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B93" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C93" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D93" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="E93" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="F93" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="G93" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H93" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="I93" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="J93" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="K93" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L93" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="M93" s="25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="94" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B94" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C94" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D94" s="19">
-        <v>0.83973187627716295</v>
-      </c>
-      <c r="E94" s="19">
-        <v>0.8</v>
-      </c>
-      <c r="F94" s="19">
-        <v>0.4680720957344785</v>
-      </c>
-      <c r="G94" s="19">
-        <v>1.5</v>
-      </c>
-      <c r="H94" s="19">
-        <v>-0.1</v>
-      </c>
-      <c r="I94" s="19">
-        <v>1.5</v>
-      </c>
-      <c r="J94" s="19">
-        <v>1</v>
-      </c>
-      <c r="K94" s="19">
-        <v>0.64620921285602484</v>
-      </c>
-      <c r="L94" s="19">
-        <v>0.45800000000000002</v>
-      </c>
-      <c r="M94" s="20">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="95" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B95" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D95" s="4">
-        <v>0.78507830018468128</v>
-      </c>
-      <c r="E95" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="F95" s="4">
-        <v>0.18708942312473201</v>
-      </c>
-      <c r="G95" s="4">
-        <v>1.06</v>
-      </c>
-      <c r="H95" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="I95" s="4">
-        <v>1.0400009805428909</v>
-      </c>
-      <c r="J95" s="4">
-        <v>0.88975310093270099</v>
-      </c>
-      <c r="K95" s="4">
-        <v>0.625</v>
-      </c>
-      <c r="L95" s="4">
-        <v>0.59</v>
-      </c>
-      <c r="M95" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="96" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B96" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C96" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D96" s="19">
-        <v>0.76371566150731707</v>
-      </c>
-      <c r="E96" s="19">
-        <v>0.7</v>
-      </c>
-      <c r="F96" s="19">
-        <v>0.31633449629329369</v>
-      </c>
-      <c r="G96" s="19">
-        <v>1.204504732979861</v>
-      </c>
-      <c r="H96" s="19">
-        <v>0.28265188209330988</v>
-      </c>
-      <c r="I96" s="19">
-        <v>1.2004504732979859</v>
-      </c>
-      <c r="J96" s="19">
-        <v>1.0249999999999999</v>
-      </c>
-      <c r="K96" s="19">
-        <v>0.5625</v>
-      </c>
-      <c r="L96" s="19">
-        <v>0.478265188209331</v>
-      </c>
-      <c r="M96" s="20">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="97" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B97" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D97" s="4">
-        <v>3.0180813867745471</v>
-      </c>
-      <c r="E97" s="4">
-        <v>3</v>
-      </c>
-      <c r="F97" s="4">
-        <v>0.26602346951008471</v>
-      </c>
-      <c r="G97" s="4">
-        <v>3.5</v>
-      </c>
-      <c r="H97" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="I97" s="4">
-        <v>3.32</v>
-      </c>
-      <c r="J97" s="4">
-        <v>3.0750000000000002</v>
-      </c>
-      <c r="K97" s="4">
-        <v>2.9899475030957912</v>
-      </c>
-      <c r="L97" s="4">
-        <v>2.77</v>
-      </c>
-      <c r="M97" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B98" s="9" t="s">
+    <row r="99" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B99" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C98" s="10"/>
-      <c r="D98" s="10"/>
-      <c r="E98" s="10"/>
-      <c r="F98" s="10"/>
-      <c r="G98" s="10"/>
-      <c r="H98" s="10"/>
-      <c r="I98" s="10"/>
-      <c r="J98" s="10"/>
-      <c r="K98" s="10"/>
-      <c r="L98" s="10"/>
-      <c r="M98" s="10"/>
+      <c r="C99" s="10"/>
+      <c r="D99" s="10"/>
+      <c r="E99" s="10"/>
+      <c r="F99" s="10"/>
+      <c r="G99" s="10"/>
+      <c r="H99" s="10"/>
+      <c r="I99" s="10"/>
+      <c r="J99" s="10"/>
+      <c r="K99" s="10"/>
+      <c r="L99" s="10"/>
+      <c r="M99" s="10"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -8118,7 +9348,7 @@
     <oddFooter>&amp;C&amp;"Roboto,Normal"Página &amp;P</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="42" max="16383" man="1"/>
+    <brk id="36" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -8142,17 +9372,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b80df5a0-8011-40eb-be96-4c6a59f56b6e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6b042263-e944-4dfe-97a8-6e4c84e0ae4b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -8161,7 +9380,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004E1357DA6D65CA49A875959554824B49" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="e8f8602aebf7bbdcbcb5348c529dc11a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b80df5a0-8011-40eb-be96-4c6a59f56b6e" xmlns:ns3="6b042263-e944-4dfe-97a8-6e4c84e0ae4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a39dbf9ae3c20398b89cd584be7bda98" ns2:_="" ns3:_="">
     <xsd:import namespace="b80df5a0-8011-40eb-be96-4c6a59f56b6e"/>
@@ -8410,24 +9629,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB7C2FA5-1A6F-45A0-B729-06C123F95F83}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="b80df5a0-8011-40eb-be96-4c6a59f56b6e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="6b042263-e944-4dfe-97a8-6e4c84e0ae4b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b80df5a0-8011-40eb-be96-4c6a59f56b6e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6b042263-e944-4dfe-97a8-6e4c84e0ae4b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E4A204-179E-478B-A62E-54900BF00ECD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -8435,7 +9648,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89E97169-F966-43F7-97A7-EB3192694F7A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8452,4 +9665,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB7C2FA5-1A6F-45A0-B729-06C123F95F83}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="b80df5a0-8011-40eb-be96-4c6a59f56b6e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="6b042263-e944-4dfe-97a8-6e4c84e0ae4b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/public/REM/raw/REM.xlsx
+++ b/public/REM/raw/REM.xlsx
@@ -5,20 +5,21 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcranet.sharepoint.com/sites/REM/Documentos compartidos/REM/Publicación/Pagina WEB/2026/26 07 Jul/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcranet.sharepoint.com/sites/REM/Documentos compartidos/REM/Publicación/Pagina WEB/2026/26 08 Ago/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="214" documentId="8_{563D5886-1088-4C76-92B3-92AAC244057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDDF0718-43C5-4625-ABD3-DE8DF8ABE2F2}"/>
+  <xr:revisionPtr revIDLastSave="254" documentId="8_{563D5886-1088-4C76-92B3-92AAC244057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2F7E15A-BAE0-44D7-8BF7-D02F6147171C}"/>
   <bookViews>
-    <workbookView xWindow="690" yWindow="1485" windowWidth="12840" windowHeight="13950" xr2:uid="{8A5F0209-F8EA-4E2B-A469-F799AD0A214D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8A5F0209-F8EA-4E2B-A469-F799AD0A214D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Cuadros de resultados" sheetId="19" r:id="rId1"/>
-    <sheet name="Resultados TOP 10" sheetId="20" r:id="rId2"/>
+    <sheet name="Cuadros de resultados" sheetId="24" r:id="rId1"/>
+    <sheet name="Resultados TOP 10" sheetId="23" r:id="rId2"/>
     <sheet name="Notas Metodólogicas" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Cuadros de resultados'!$B$2:$M$112</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Resultados TOP 10'!$B$2:$M$96</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Cuadros de resultados'!$2:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Resultados TOP 10'!$2:$4</definedName>
   </definedNames>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="53">
   <si>
     <t>Precios minoristas (IPC nivel general-Nacional; INDEC)</t>
   </si>
@@ -183,25 +184,25 @@
     <t>Trim. IV-26</t>
   </si>
   <si>
-    <t>Relevamiento de Expectativas de Mercado (REM)  - BCRA - Julio 2026</t>
+    <t>Relevamiento de Expectativas de Mercado (REM)  - BCRA - Agosto 2026</t>
   </si>
   <si>
-    <t>var. % i.a.; jul-27</t>
+    <t>var. % i.a.; ago-27</t>
   </si>
   <si>
-    <t>var. % i.a.; jul-28</t>
+    <t>var. % i.a.; ago-28</t>
   </si>
   <si>
-    <t>TNA; %; jul-27</t>
+    <t>TNA; %; ago-27</t>
   </si>
   <si>
-    <t>$/USD; jul-27</t>
+    <t>$/USD; ago-27</t>
   </si>
   <si>
-    <t>Fuente: REM - BCRA (jul-26)</t>
+    <t>Fuente: REM - BCRA (ago-26)</t>
   </si>
   <si>
-    <t>Relevamiento de Expectativas de Mercado (REM)  Top 10 - BCRA - Julio 2026</t>
+    <t>Relevamiento de Expectativas de Mercado (REM)  Top 10 - BCRA - Agosto 2026</t>
   </si>
 </sst>
 </file>
@@ -399,7 +400,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -478,19 +479,10 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="2" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -503,6 +495,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1845,35 +1849,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED56CF66-85D7-47A2-A74A-AD3F0E36496C}">
-  <sheetPr codeName="Hoja1">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268F1693-CC27-4920-9CC8-01BF818C71A5}">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:AL112"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:M112"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" style="1" customWidth="1"/>
-    <col min="9" max="12" width="14.42578125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="18.42578125" style="1" customWidth="1"/>
-    <col min="15" max="25" width="17.28515625" customWidth="1"/>
-    <col min="27" max="27" width="24.5703125" style="1" customWidth="1"/>
-    <col min="28" max="28" width="30.85546875" style="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" customWidth="1"/>
-    <col min="30" max="30" width="16.42578125" style="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" customWidth="1"/>
-    <col min="32" max="32" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="18.42578125" style="1" customWidth="1"/>
-    <col min="34" max="37" width="14.42578125" style="1" customWidth="1"/>
-    <col min="38" max="38" width="18.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.81640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.453125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.453125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="14.453125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="18.453125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:38" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="20.5" x14ac:dyDescent="0.35">
       <c r="B2" s="11" t="s">
         <v>46</v>
       </c>
@@ -1888,20 +1882,8 @@
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
-      <c r="AA2" s="11"/>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="11"/>
-      <c r="AD2" s="11"/>
-      <c r="AE2" s="11"/>
-      <c r="AF2" s="11"/>
-      <c r="AG2" s="11"/>
-      <c r="AH2" s="11"/>
-      <c r="AI2" s="11"/>
-      <c r="AJ2" s="11"/>
-      <c r="AK2" s="11"/>
-      <c r="AL2" s="11"/>
-    </row>
-    <row r="3" spans="2:38" ht="20.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="2:13" ht="20.5" x14ac:dyDescent="0.35">
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
@@ -1914,26 +1896,12 @@
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
-      <c r="AA3" s="11"/>
-      <c r="AB3" s="11"/>
-      <c r="AC3" s="11"/>
-      <c r="AD3" s="11"/>
-      <c r="AE3" s="11"/>
-      <c r="AF3" s="11"/>
-      <c r="AG3" s="11"/>
-      <c r="AH3" s="11"/>
-      <c r="AI3" s="11"/>
-      <c r="AJ3" s="11"/>
-      <c r="AK3" s="11"/>
-      <c r="AL3" s="11"/>
-    </row>
-    <row r="4" spans="2:38" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
       <c r="L4" s="12"/>
       <c r="M4" s="13"/>
-      <c r="AK4" s="12"/>
-      <c r="AL4" s="13"/>
-    </row>
-    <row r="5" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B5" s="14" t="s">
         <v>0</v>
       </c>
@@ -1948,20 +1916,8 @@
       <c r="K5" s="14"/>
       <c r="L5" s="14"/>
       <c r="M5" s="15"/>
-      <c r="AA5" s="14"/>
-      <c r="AB5" s="14"/>
-      <c r="AC5" s="14"/>
-      <c r="AD5" s="14"/>
-      <c r="AE5" s="14"/>
-      <c r="AF5" s="14"/>
-      <c r="AG5" s="14"/>
-      <c r="AH5" s="14"/>
-      <c r="AI5" s="14"/>
-      <c r="AJ5" s="14"/>
-      <c r="AK5" s="14"/>
-      <c r="AL5" s="15"/>
-    </row>
-    <row r="6" spans="2:38" ht="37.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B6" s="16" t="s">
         <v>1</v>
       </c>
@@ -1998,72 +1954,48 @@
       <c r="M6" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="AA6" s="16"/>
-      <c r="AB6" s="16"/>
-      <c r="AC6" s="16"/>
-      <c r="AD6" s="16"/>
-      <c r="AE6" s="16"/>
-      <c r="AF6" s="16"/>
-      <c r="AG6" s="16"/>
-      <c r="AH6" s="16"/>
-      <c r="AI6" s="16"/>
-      <c r="AJ6" s="16"/>
-      <c r="AK6" s="16"/>
-      <c r="AL6" s="16"/>
-    </row>
-    <row r="7" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B7" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="19">
-        <v>1.95</v>
+        <v>1.7172107378641499</v>
       </c>
       <c r="E7" s="19">
-        <v>1.933473834898124</v>
+        <v>1.7503297228448369</v>
       </c>
       <c r="F7" s="19">
-        <v>0.12056181263309521</v>
+        <v>0.1343814159492035</v>
       </c>
       <c r="G7" s="19">
-        <v>2.17</v>
+        <v>2.046154238657016</v>
       </c>
       <c r="H7" s="19">
+        <v>1.4</v>
+      </c>
+      <c r="I7" s="19">
+        <v>1.964</v>
+      </c>
+      <c r="J7" s="19">
+        <v>1.8</v>
+      </c>
+      <c r="K7" s="19">
+        <v>1.6968569200648651</v>
+      </c>
+      <c r="L7" s="19">
         <v>1.6</v>
       </c>
-      <c r="I7" s="19">
-        <v>2.1</v>
-      </c>
-      <c r="J7" s="19">
-        <v>2</v>
-      </c>
-      <c r="K7" s="19">
-        <v>1.8986566050117171</v>
-      </c>
-      <c r="L7" s="19">
-        <v>1.8</v>
-      </c>
       <c r="M7" s="20">
-        <v>45</v>
-      </c>
-      <c r="AA7" s="17"/>
-      <c r="AB7" s="18"/>
-      <c r="AC7" s="19"/>
-      <c r="AD7" s="19"/>
-      <c r="AE7" s="19"/>
-      <c r="AF7" s="19"/>
-      <c r="AG7" s="19"/>
-      <c r="AH7" s="19"/>
-      <c r="AI7" s="19"/>
-      <c r="AJ7" s="19"/>
-      <c r="AK7" s="19"/>
-      <c r="AL7" s="20"/>
-    </row>
-    <row r="8" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B8" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>13</v>
@@ -2072,22 +2004,22 @@
         <v>1.8</v>
       </c>
       <c r="E8" s="4">
-        <v>1.764970064037616</v>
+        <v>1.772386592387269</v>
       </c>
       <c r="F8" s="4">
-        <v>0.1825673854004142</v>
+        <v>0.1969499617942998</v>
       </c>
       <c r="G8" s="4">
         <v>2.2000000000000002</v>
       </c>
       <c r="H8" s="4">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="I8" s="4">
-        <v>1.9288888605224139</v>
+        <v>1.97653503583947</v>
       </c>
       <c r="J8" s="4">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="K8" s="4">
         <v>1.7</v>
@@ -2096,272 +2028,200 @@
         <v>1.6</v>
       </c>
       <c r="M8" s="5">
-        <v>45</v>
-      </c>
-      <c r="AA8" s="2"/>
-      <c r="AB8" s="3"/>
-      <c r="AC8" s="4"/>
-      <c r="AD8" s="4"/>
-      <c r="AE8" s="4"/>
-      <c r="AF8" s="4"/>
-      <c r="AG8" s="4"/>
-      <c r="AH8" s="4"/>
-      <c r="AI8" s="4"/>
-      <c r="AJ8" s="4"/>
-      <c r="AK8" s="4"/>
-      <c r="AL8" s="5"/>
-    </row>
-    <row r="9" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B9" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="19">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="E9" s="19">
-        <v>1.752248579067857</v>
+        <v>1.6768341439475789</v>
       </c>
       <c r="F9" s="19">
-        <v>0.2392173124436853</v>
+        <v>0.23091680301767381</v>
       </c>
       <c r="G9" s="19">
-        <v>2.2599999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="H9" s="19">
         <v>0.8</v>
       </c>
       <c r="I9" s="19">
-        <v>2</v>
+        <v>1.9159821990736721</v>
       </c>
       <c r="J9" s="19">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="K9" s="19">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="L9" s="19">
-        <v>1.54</v>
+        <v>1.488</v>
       </c>
       <c r="M9" s="20">
-        <v>45</v>
-      </c>
-      <c r="AA9" s="17"/>
-      <c r="AB9" s="18"/>
-      <c r="AC9" s="19"/>
-      <c r="AD9" s="19"/>
-      <c r="AE9" s="19"/>
-      <c r="AF9" s="19"/>
-      <c r="AG9" s="19"/>
-      <c r="AH9" s="19"/>
-      <c r="AI9" s="19"/>
-      <c r="AJ9" s="19"/>
-      <c r="AK9" s="19"/>
-      <c r="AL9" s="20"/>
-    </row>
-    <row r="10" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="4">
-        <v>1.655047763820076</v>
+        <v>1.6</v>
       </c>
       <c r="E10" s="4">
-        <v>1.670086538000408</v>
+        <v>1.6231408313512761</v>
       </c>
       <c r="F10" s="4">
-        <v>0.25858579750844118</v>
+        <v>0.2228708007595139</v>
       </c>
       <c r="G10" s="4">
-        <v>2.037874061555534</v>
+        <v>2</v>
       </c>
       <c r="H10" s="4">
         <v>0.6</v>
       </c>
       <c r="I10" s="4">
-        <v>1.9229965922972601</v>
+        <v>1.84</v>
       </c>
       <c r="J10" s="4">
-        <v>1.88</v>
+        <v>1.707971717071683</v>
       </c>
       <c r="K10" s="4">
-        <v>1.6</v>
+        <v>1.573233929153228</v>
       </c>
       <c r="L10" s="4">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="M10" s="5">
-        <v>45</v>
-      </c>
-      <c r="AA10" s="2"/>
-      <c r="AB10" s="3"/>
-      <c r="AC10" s="4"/>
-      <c r="AD10" s="4"/>
-      <c r="AE10" s="4"/>
-      <c r="AF10" s="4"/>
-      <c r="AG10" s="4"/>
-      <c r="AH10" s="4"/>
-      <c r="AI10" s="4"/>
-      <c r="AJ10" s="4"/>
-      <c r="AK10" s="4"/>
-      <c r="AL10" s="5"/>
-    </row>
-    <row r="11" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B11" s="17">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="19">
-        <v>1.633373609332045</v>
+        <v>1.776387951127933</v>
       </c>
       <c r="E11" s="19">
-        <v>1.6227503638802989</v>
+        <v>1.7226779106883769</v>
       </c>
       <c r="F11" s="19">
-        <v>0.2465148605450535</v>
+        <v>0.22952386822584001</v>
       </c>
       <c r="G11" s="19">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H11" s="19">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="I11" s="19">
-        <v>1.8879999999999999</v>
+        <v>2</v>
       </c>
       <c r="J11" s="19">
-        <v>1.8</v>
+        <v>1.8808039926447691</v>
       </c>
       <c r="K11" s="19">
+        <v>1.6</v>
+      </c>
+      <c r="L11" s="19">
         <v>1.5</v>
       </c>
-      <c r="L11" s="19">
-        <v>1.4</v>
-      </c>
       <c r="M11" s="20">
-        <v>45</v>
-      </c>
-      <c r="AA11" s="17"/>
-      <c r="AB11" s="18"/>
-      <c r="AC11" s="19"/>
-      <c r="AD11" s="19"/>
-      <c r="AE11" s="19"/>
-      <c r="AF11" s="19"/>
-      <c r="AG11" s="19"/>
-      <c r="AH11" s="19"/>
-      <c r="AI11" s="19"/>
-      <c r="AJ11" s="19"/>
-      <c r="AK11" s="19"/>
-      <c r="AL11" s="20"/>
-    </row>
-    <row r="12" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="4">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="E12" s="4">
-        <v>1.712493045747693</v>
+        <v>1.6291210738236721</v>
       </c>
       <c r="F12" s="4">
-        <v>0.26545533695012991</v>
+        <v>0.30564616932402022</v>
       </c>
       <c r="G12" s="4">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="H12" s="4">
         <v>0.6</v>
       </c>
       <c r="I12" s="4">
-        <v>2</v>
+        <v>1.925</v>
       </c>
       <c r="J12" s="4">
-        <v>1.89</v>
+        <v>1.860975410193471</v>
       </c>
       <c r="K12" s="4">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="L12" s="4">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="M12" s="5">
-        <v>45</v>
-      </c>
-      <c r="AA12" s="2"/>
-      <c r="AB12" s="3"/>
-      <c r="AC12" s="4"/>
-      <c r="AD12" s="4"/>
-      <c r="AE12" s="4"/>
-      <c r="AF12" s="4"/>
-      <c r="AG12" s="4"/>
-      <c r="AH12" s="4"/>
-      <c r="AI12" s="4"/>
-      <c r="AJ12" s="4"/>
-      <c r="AK12" s="4"/>
-      <c r="AL12" s="5"/>
-    </row>
-    <row r="13" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B13" s="17">
-        <v>46418</v>
+        <v>46446</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="19">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="E13" s="19">
-        <v>1.626027117751248</v>
+        <v>1.5567650372180519</v>
       </c>
       <c r="F13" s="19">
-        <v>0.33192967756681369</v>
+        <v>0.28341010967998409</v>
       </c>
       <c r="G13" s="19">
-        <v>2.5</v>
+        <v>2.2508010136898582</v>
       </c>
       <c r="H13" s="19">
         <v>0.6</v>
       </c>
       <c r="I13" s="19">
-        <v>1.9159999999999999</v>
+        <v>1.895</v>
       </c>
       <c r="J13" s="19">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="K13" s="19">
-        <v>1.5</v>
+        <v>1.4069461347615511</v>
       </c>
       <c r="L13" s="19">
-        <v>1.2426076570096241</v>
+        <v>1.26</v>
       </c>
       <c r="M13" s="20">
-        <v>43</v>
-      </c>
-      <c r="AA13" s="17"/>
-      <c r="AB13" s="18"/>
-      <c r="AC13" s="19"/>
-      <c r="AD13" s="19"/>
-      <c r="AE13" s="19"/>
-      <c r="AF13" s="19"/>
-      <c r="AG13" s="19"/>
-      <c r="AH13" s="19"/>
-      <c r="AI13" s="19"/>
-      <c r="AJ13" s="19"/>
-      <c r="AK13" s="19"/>
-      <c r="AL13" s="20"/>
-    </row>
-    <row r="14" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
@@ -2369,49 +2229,37 @@
         <v>47</v>
       </c>
       <c r="D14" s="4">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="E14" s="4">
-        <v>21.180990767499178</v>
+        <v>20.944192026847979</v>
       </c>
       <c r="F14" s="4">
-        <v>3.4759614618547729</v>
+        <v>3.253592823940513</v>
       </c>
       <c r="G14" s="4">
         <v>26.2</v>
       </c>
       <c r="H14" s="4">
-        <v>8.1999999999999993</v>
+        <v>8.9</v>
       </c>
       <c r="I14" s="4">
-        <v>24.5</v>
+        <v>24.26984661810534</v>
       </c>
       <c r="J14" s="4">
-        <v>23.5</v>
+        <v>23.28</v>
       </c>
       <c r="K14" s="4">
-        <v>20.100000000000001</v>
+        <v>19.7</v>
       </c>
       <c r="L14" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M14" s="5">
-        <v>41</v>
-      </c>
-      <c r="AA14" s="2"/>
-      <c r="AB14" s="3"/>
-      <c r="AC14" s="4"/>
-      <c r="AD14" s="4"/>
-      <c r="AE14" s="4"/>
-      <c r="AF14" s="4"/>
-      <c r="AG14" s="4"/>
-      <c r="AH14" s="4"/>
-      <c r="AI14" s="4"/>
-      <c r="AJ14" s="4"/>
-      <c r="AK14" s="4"/>
-      <c r="AL14" s="5"/>
-    </row>
-    <row r="15" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B15" s="17" t="s">
         <v>15</v>
       </c>
@@ -2419,49 +2267,37 @@
         <v>48</v>
       </c>
       <c r="D15" s="19">
-        <v>16.630484330289651</v>
+        <v>17.222945217496989</v>
       </c>
       <c r="E15" s="19">
-        <v>16.600625041112181</v>
+        <v>16.799521307178651</v>
       </c>
       <c r="F15" s="19">
-        <v>4.0314695666029747</v>
+        <v>3.7480808060907971</v>
       </c>
       <c r="G15" s="19">
-        <v>22.8</v>
+        <v>23.3</v>
       </c>
       <c r="H15" s="19">
-        <v>5</v>
+        <v>7.44</v>
       </c>
       <c r="I15" s="19">
-        <v>21.525748390149399</v>
+        <v>20.922999999999998</v>
       </c>
       <c r="J15" s="19">
-        <v>19.226594370956239</v>
+        <v>18.936435221563901</v>
       </c>
       <c r="K15" s="19">
-        <v>15.03202164819572</v>
+        <v>14.975</v>
       </c>
       <c r="L15" s="19">
-        <v>12.099021892811351</v>
+        <v>11.936</v>
       </c>
       <c r="M15" s="20">
-        <v>36</v>
-      </c>
-      <c r="AA15" s="17"/>
-      <c r="AB15" s="18"/>
-      <c r="AC15" s="19"/>
-      <c r="AD15" s="19"/>
-      <c r="AE15" s="19"/>
-      <c r="AF15" s="19"/>
-      <c r="AG15" s="19"/>
-      <c r="AH15" s="19"/>
-      <c r="AI15" s="19"/>
-      <c r="AJ15" s="19"/>
-      <c r="AK15" s="19"/>
-      <c r="AL15" s="20"/>
-    </row>
-    <row r="16" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B16" s="2" t="s">
         <v>36</v>
       </c>
@@ -2469,49 +2305,37 @@
         <v>16</v>
       </c>
       <c r="D16" s="4">
-        <v>29.79</v>
+        <v>30</v>
       </c>
       <c r="E16" s="4">
-        <v>29.616954427741248</v>
+        <v>29.889435313482132</v>
       </c>
       <c r="F16" s="4">
-        <v>1.461595598020436</v>
+        <v>1.1312407990053881</v>
       </c>
       <c r="G16" s="4">
-        <v>32.299999999999997</v>
+        <v>32.1</v>
       </c>
       <c r="H16" s="4">
-        <v>23.17</v>
+        <v>25.1</v>
       </c>
       <c r="I16" s="4">
-        <v>30.96</v>
+        <v>31.002798955511309</v>
       </c>
       <c r="J16" s="4">
-        <v>30.4</v>
+        <v>30.506481679936091</v>
       </c>
       <c r="K16" s="4">
-        <v>29.2</v>
+        <v>29.54151002442303</v>
       </c>
       <c r="L16" s="4">
-        <v>28.327999999999999</v>
+        <v>29.12</v>
       </c>
       <c r="M16" s="5">
-        <v>45</v>
-      </c>
-      <c r="AA16" s="2"/>
-      <c r="AB16" s="3"/>
-      <c r="AC16" s="4"/>
-      <c r="AD16" s="4"/>
-      <c r="AE16" s="4"/>
-      <c r="AF16" s="4"/>
-      <c r="AG16" s="4"/>
-      <c r="AH16" s="4"/>
-      <c r="AI16" s="4"/>
-      <c r="AJ16" s="4"/>
-      <c r="AK16" s="4"/>
-      <c r="AL16" s="5"/>
-    </row>
-    <row r="17" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B17" s="21" t="s">
         <v>37</v>
       </c>
@@ -2519,49 +2343,37 @@
         <v>17</v>
       </c>
       <c r="D17" s="19">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="E17" s="19">
-        <v>20.009353973013759</v>
+        <v>20.582885031556319</v>
       </c>
       <c r="F17" s="19">
-        <v>3.9992963057440369</v>
+        <v>3.9431509869058079</v>
       </c>
       <c r="G17" s="19">
-        <v>27</v>
+        <v>27.03</v>
       </c>
       <c r="H17" s="19">
-        <v>8.4</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="I17" s="19">
         <v>25</v>
       </c>
       <c r="J17" s="19">
-        <v>22.45</v>
+        <v>23.3</v>
       </c>
       <c r="K17" s="19">
-        <v>18.645</v>
+        <v>19.32599593654167</v>
       </c>
       <c r="L17" s="19">
-        <v>16.228449351366731</v>
+        <v>16.544295094869909</v>
       </c>
       <c r="M17" s="20">
-        <v>43</v>
-      </c>
-      <c r="AA17" s="21"/>
-      <c r="AB17" s="18"/>
-      <c r="AC17" s="19"/>
-      <c r="AD17" s="19"/>
-      <c r="AE17" s="19"/>
-      <c r="AF17" s="19"/>
-      <c r="AG17" s="19"/>
-      <c r="AH17" s="19"/>
-      <c r="AI17" s="19"/>
-      <c r="AJ17" s="19"/>
-      <c r="AK17" s="19"/>
-      <c r="AL17" s="20"/>
-    </row>
-    <row r="18" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B18" s="6" t="s">
         <v>38</v>
       </c>
@@ -2569,49 +2381,37 @@
         <v>39</v>
       </c>
       <c r="D18" s="4">
-        <v>14.129585438581721</v>
+        <v>14.11479271929085</v>
       </c>
       <c r="E18" s="4">
-        <v>13.587795923714291</v>
+        <v>14.21113365744848</v>
       </c>
       <c r="F18" s="4">
-        <v>4.1218821019266727</v>
+        <v>3.7879532400201721</v>
       </c>
       <c r="G18" s="4">
-        <v>23.25761781839218</v>
+        <v>23.194453831240651</v>
       </c>
       <c r="H18" s="4">
-        <v>2.4</v>
+        <v>6.17</v>
       </c>
       <c r="I18" s="4">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="J18" s="4">
-        <v>15.34473120912932</v>
+        <v>16.925000000000001</v>
       </c>
       <c r="K18" s="4">
-        <v>12.03</v>
+        <v>12.53758767943234</v>
       </c>
       <c r="L18" s="4">
-        <v>7.9351282624947812</v>
+        <v>8.9645933843245729</v>
       </c>
       <c r="M18" s="5">
-        <v>35</v>
-      </c>
-      <c r="AA18" s="6"/>
-      <c r="AB18" s="3"/>
-      <c r="AC18" s="4"/>
-      <c r="AD18" s="4"/>
-      <c r="AE18" s="4"/>
-      <c r="AF18" s="4"/>
-      <c r="AG18" s="4"/>
-      <c r="AH18" s="4"/>
-      <c r="AI18" s="4"/>
-      <c r="AJ18" s="4"/>
-      <c r="AK18" s="4"/>
-      <c r="AL18" s="5"/>
-    </row>
-    <row r="21" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B21" s="14" t="s">
         <v>18</v>
       </c>
@@ -2626,20 +2426,8 @@
       <c r="K21" s="14"/>
       <c r="L21" s="14"/>
       <c r="M21" s="15"/>
-      <c r="AA21" s="14"/>
-      <c r="AB21" s="14"/>
-      <c r="AC21" s="14"/>
-      <c r="AD21" s="14"/>
-      <c r="AE21" s="14"/>
-      <c r="AF21" s="14"/>
-      <c r="AG21" s="14"/>
-      <c r="AH21" s="14"/>
-      <c r="AI21" s="14"/>
-      <c r="AJ21" s="14"/>
-      <c r="AK21" s="14"/>
-      <c r="AL21" s="15"/>
-    </row>
-    <row r="22" spans="2:38" ht="37.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B22" s="16" t="s">
         <v>1</v>
       </c>
@@ -2676,72 +2464,48 @@
       <c r="M22" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="AA22" s="16"/>
-      <c r="AB22" s="16"/>
-      <c r="AC22" s="16"/>
-      <c r="AD22" s="16"/>
-      <c r="AE22" s="16"/>
-      <c r="AF22" s="16"/>
-      <c r="AG22" s="16"/>
-      <c r="AH22" s="16"/>
-      <c r="AI22" s="16"/>
-      <c r="AJ22" s="16"/>
-      <c r="AK22" s="16"/>
-      <c r="AL22" s="16"/>
-    </row>
-    <row r="23" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B23" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="19">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="E23" s="19">
-        <v>1.785486950066997</v>
+        <v>1.677542677767357</v>
       </c>
       <c r="F23" s="19">
-        <v>0.1864529594445816</v>
+        <v>0.1817673080353619</v>
       </c>
       <c r="G23" s="19">
-        <v>2.1800000000000002</v>
+        <v>2.1</v>
       </c>
       <c r="H23" s="19">
-        <v>1.4702434016336421</v>
+        <v>1.27</v>
       </c>
       <c r="I23" s="19">
-        <v>2.0205861261459641</v>
+        <v>1.9179999999999999</v>
       </c>
       <c r="J23" s="19">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="K23" s="19">
-        <v>1.645</v>
+        <v>1.569538013529681</v>
       </c>
       <c r="L23" s="19">
-        <v>1.543436185502151</v>
+        <v>1.469934770744372</v>
       </c>
       <c r="M23" s="20">
-        <v>36</v>
-      </c>
-      <c r="AA23" s="17"/>
-      <c r="AB23" s="18"/>
-      <c r="AC23" s="19"/>
-      <c r="AD23" s="19"/>
-      <c r="AE23" s="19"/>
-      <c r="AF23" s="19"/>
-      <c r="AG23" s="19"/>
-      <c r="AH23" s="19"/>
-      <c r="AI23" s="19"/>
-      <c r="AJ23" s="19"/>
-      <c r="AK23" s="19"/>
-      <c r="AL23" s="20"/>
-    </row>
-    <row r="24" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B24" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>13</v>
@@ -2750,110 +2514,86 @@
         <v>1.7</v>
       </c>
       <c r="E24" s="4">
-        <v>1.7067747432585221</v>
+        <v>1.6921122661925661</v>
       </c>
       <c r="F24" s="4">
-        <v>0.2178059457958709</v>
+        <v>0.21721053762150419</v>
       </c>
       <c r="G24" s="4">
-        <v>2.38</v>
+        <v>2.152153475229968</v>
       </c>
       <c r="H24" s="4">
-        <v>1.2</v>
+        <v>1.1972478378336799</v>
       </c>
       <c r="I24" s="4">
-        <v>1.98</v>
+        <v>1.9834607386093119</v>
       </c>
       <c r="J24" s="4">
         <v>1.8</v>
       </c>
       <c r="K24" s="4">
-        <v>1.5740316522551969</v>
+        <v>1.53</v>
       </c>
       <c r="L24" s="4">
-        <v>1.5023142839063599</v>
+        <v>1.4359999999999999</v>
       </c>
       <c r="M24" s="5">
-        <v>36</v>
-      </c>
-      <c r="AA24" s="2"/>
-      <c r="AB24" s="3"/>
-      <c r="AC24" s="4"/>
-      <c r="AD24" s="4"/>
-      <c r="AE24" s="4"/>
-      <c r="AF24" s="4"/>
-      <c r="AG24" s="4"/>
-      <c r="AH24" s="4"/>
-      <c r="AI24" s="4"/>
-      <c r="AJ24" s="4"/>
-      <c r="AK24" s="4"/>
-      <c r="AL24" s="5"/>
-    </row>
-    <row r="25" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B25" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="19">
-        <v>1.67699493076314</v>
+        <v>1.6</v>
       </c>
       <c r="E25" s="19">
-        <v>1.6776263088831129</v>
+        <v>1.6060329641593509</v>
       </c>
       <c r="F25" s="19">
-        <v>0.24605749906018201</v>
+        <v>0.23735667557973389</v>
       </c>
       <c r="G25" s="19">
         <v>2.2000000000000002</v>
       </c>
       <c r="H25" s="19">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I25" s="19">
-        <v>1.95</v>
+        <v>1.875413953574937</v>
       </c>
       <c r="J25" s="19">
-        <v>1.8302044796835339</v>
+        <v>1.7732930991399229</v>
       </c>
       <c r="K25" s="19">
         <v>1.5</v>
       </c>
       <c r="L25" s="19">
-        <v>1.409</v>
+        <v>1.282</v>
       </c>
       <c r="M25" s="20">
-        <v>36</v>
-      </c>
-      <c r="AA25" s="17"/>
-      <c r="AB25" s="18"/>
-      <c r="AC25" s="19"/>
-      <c r="AD25" s="19"/>
-      <c r="AE25" s="19"/>
-      <c r="AF25" s="19"/>
-      <c r="AG25" s="19"/>
-      <c r="AH25" s="19"/>
-      <c r="AI25" s="19"/>
-      <c r="AJ25" s="19"/>
-      <c r="AK25" s="19"/>
-      <c r="AL25" s="20"/>
-    </row>
-    <row r="26" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B26" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="4">
-        <v>1.630491543516168</v>
+        <v>1.6</v>
       </c>
       <c r="E26" s="4">
-        <v>1.6130515351915991</v>
+        <v>1.571298429043124</v>
       </c>
       <c r="F26" s="4">
-        <v>0.2364910588883041</v>
+        <v>0.22508894150328379</v>
       </c>
       <c r="G26" s="4">
         <v>2.2000000000000002</v>
@@ -2862,184 +2602,136 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="I26" s="4">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="J26" s="4">
-        <v>1.774262298947926</v>
+        <v>1.6992584671560169</v>
       </c>
       <c r="K26" s="4">
-        <v>1.4597770612984591</v>
+        <v>1.4333128757059399</v>
       </c>
       <c r="L26" s="4">
-        <v>1.3049999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="M26" s="5">
-        <v>36</v>
-      </c>
-      <c r="AA26" s="2"/>
-      <c r="AB26" s="3"/>
-      <c r="AC26" s="4"/>
-      <c r="AD26" s="4"/>
-      <c r="AE26" s="4"/>
-      <c r="AF26" s="4"/>
-      <c r="AG26" s="4"/>
-      <c r="AH26" s="4"/>
-      <c r="AI26" s="4"/>
-      <c r="AJ26" s="4"/>
-      <c r="AK26" s="4"/>
-      <c r="AL26" s="5"/>
-    </row>
-    <row r="27" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B27" s="17">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C27" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="19">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="E27" s="19">
-        <v>1.5879010595808729</v>
+        <v>1.6814373237351961</v>
       </c>
       <c r="F27" s="19">
-        <v>0.24426048261540181</v>
+        <v>0.29210245502151999</v>
       </c>
       <c r="G27" s="19">
-        <v>2.2000000000000002</v>
+        <v>2.5</v>
       </c>
       <c r="H27" s="19">
-        <v>1.1393514175688011</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I27" s="19">
-        <v>1.85498125</v>
+        <v>2.0122010898706821</v>
       </c>
       <c r="J27" s="19">
-        <v>1.7247221361084399</v>
+        <v>1.81</v>
       </c>
       <c r="K27" s="19">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="L27" s="19">
-        <v>1.2849999999999999</v>
+        <v>1.3504182337542181</v>
       </c>
       <c r="M27" s="20">
-        <v>36</v>
-      </c>
-      <c r="AA27" s="17"/>
-      <c r="AB27" s="18"/>
-      <c r="AC27" s="19"/>
-      <c r="AD27" s="19"/>
-      <c r="AE27" s="19"/>
-      <c r="AF27" s="19"/>
-      <c r="AG27" s="19"/>
-      <c r="AH27" s="19"/>
-      <c r="AI27" s="19"/>
-      <c r="AJ27" s="19"/>
-      <c r="AK27" s="19"/>
-      <c r="AL27" s="20"/>
-    </row>
-    <row r="28" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B28" s="2">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D28" s="4">
-        <v>1.7</v>
+        <v>1.605</v>
       </c>
       <c r="E28" s="4">
-        <v>1.6649492261873251</v>
+        <v>1.612258592998203</v>
       </c>
       <c r="F28" s="4">
-        <v>0.2556392926219378</v>
+        <v>0.32459472649054633</v>
       </c>
       <c r="G28" s="4">
-        <v>2.2000000000000002</v>
+        <v>2.5</v>
       </c>
       <c r="H28" s="4">
-        <v>1.2</v>
+        <v>0.94727963924805503</v>
       </c>
       <c r="I28" s="4">
         <v>2</v>
       </c>
       <c r="J28" s="4">
-        <v>1.805901493227845</v>
+        <v>1.77</v>
       </c>
       <c r="K28" s="4">
-        <v>1.4775</v>
+        <v>1.4</v>
       </c>
       <c r="L28" s="4">
-        <v>1.383031305275306</v>
+        <v>1.2268083022567511</v>
       </c>
       <c r="M28" s="5">
         <v>36</v>
       </c>
-      <c r="AA28" s="2"/>
-      <c r="AB28" s="3"/>
-      <c r="AC28" s="4"/>
-      <c r="AD28" s="4"/>
-      <c r="AE28" s="4"/>
-      <c r="AF28" s="4"/>
-      <c r="AG28" s="4"/>
-      <c r="AH28" s="4"/>
-      <c r="AI28" s="4"/>
-      <c r="AJ28" s="4"/>
-      <c r="AK28" s="4"/>
-      <c r="AL28" s="5"/>
-    </row>
-    <row r="29" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B29" s="17">
-        <v>46418</v>
+        <v>46446</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D29" s="19">
-        <v>1.61</v>
+        <v>1.5149999999999999</v>
       </c>
       <c r="E29" s="19">
-        <v>1.5904222381028641</v>
+        <v>1.5475538158579281</v>
       </c>
       <c r="F29" s="19">
-        <v>0.2906592807395359</v>
+        <v>0.32389254734168199</v>
       </c>
       <c r="G29" s="19">
-        <v>2.2000000000000002</v>
+        <v>2.7</v>
       </c>
       <c r="H29" s="19">
-        <v>0.9482479817222389</v>
+        <v>0.87755392583488401</v>
       </c>
       <c r="I29" s="19">
-        <v>1.9850000000000001</v>
+        <v>1.7953940290915791</v>
       </c>
       <c r="J29" s="19">
         <v>1.7</v>
       </c>
       <c r="K29" s="19">
-        <v>1.4137500000000001</v>
+        <v>1.4</v>
       </c>
       <c r="L29" s="19">
-        <v>1.231887360362572</v>
+        <v>1.24</v>
       </c>
       <c r="M29" s="20">
-        <v>34</v>
-      </c>
-      <c r="AA29" s="17"/>
-      <c r="AB29" s="18"/>
-      <c r="AC29" s="19"/>
-      <c r="AD29" s="19"/>
-      <c r="AE29" s="19"/>
-      <c r="AF29" s="19"/>
-      <c r="AG29" s="19"/>
-      <c r="AH29" s="19"/>
-      <c r="AI29" s="19"/>
-      <c r="AJ29" s="19"/>
-      <c r="AK29" s="19"/>
-      <c r="AL29" s="20"/>
-    </row>
-    <row r="30" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B30" s="2" t="s">
         <v>14</v>
       </c>
@@ -3047,49 +2739,37 @@
         <v>47</v>
       </c>
       <c r="D30" s="4">
-        <v>20.907295710087649</v>
+        <v>20.893367651879679</v>
       </c>
       <c r="E30" s="4">
-        <v>20.546536655762679</v>
+        <v>20.352041318274729</v>
       </c>
       <c r="F30" s="4">
-        <v>3.3204255065378909</v>
+        <v>3.19807072235422</v>
       </c>
       <c r="G30" s="4">
-        <v>27.6</v>
+        <v>25.5</v>
       </c>
       <c r="H30" s="4">
-        <v>11.83009467033758</v>
+        <v>11.0155224221455</v>
       </c>
       <c r="I30" s="4">
-        <v>23.86</v>
+        <v>23.783406727078361</v>
       </c>
       <c r="J30" s="4">
-        <v>23.02678496332376</v>
+        <v>22.925000000000001</v>
       </c>
       <c r="K30" s="4">
-        <v>18.600000000000001</v>
+        <v>18.63341390631226</v>
       </c>
       <c r="L30" s="4">
-        <v>16.8771131737088</v>
+        <v>16.761683378195521</v>
       </c>
       <c r="M30" s="5">
-        <v>33</v>
-      </c>
-      <c r="AA30" s="2"/>
-      <c r="AB30" s="3"/>
-      <c r="AC30" s="4"/>
-      <c r="AD30" s="4"/>
-      <c r="AE30" s="4"/>
-      <c r="AF30" s="4"/>
-      <c r="AG30" s="4"/>
-      <c r="AH30" s="4"/>
-      <c r="AI30" s="4"/>
-      <c r="AJ30" s="4"/>
-      <c r="AK30" s="4"/>
-      <c r="AL30" s="5"/>
-    </row>
-    <row r="31" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B31" s="17" t="s">
         <v>15</v>
       </c>
@@ -3097,49 +2777,37 @@
         <v>48</v>
       </c>
       <c r="D31" s="19">
-        <v>16.34</v>
+        <v>16.631906540915921</v>
       </c>
       <c r="E31" s="19">
-        <v>16.169021842050832</v>
+        <v>15.94903970289228</v>
       </c>
       <c r="F31" s="19">
-        <v>4.6459220795595417</v>
+        <v>4.3261607204043777</v>
       </c>
       <c r="G31" s="19">
-        <v>23.7</v>
+        <v>23.264481314242701</v>
       </c>
       <c r="H31" s="19">
-        <v>4.0999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="I31" s="19">
-        <v>22</v>
+        <v>20.361999999999998</v>
       </c>
       <c r="J31" s="19">
-        <v>19.959696927407592</v>
+        <v>18.215765529965481</v>
       </c>
       <c r="K31" s="19">
-        <v>13.95509590181944</v>
+        <v>14.205698303527759</v>
       </c>
       <c r="L31" s="19">
-        <v>9.1849508286797388</v>
+        <v>9.2679950441645076</v>
       </c>
       <c r="M31" s="20">
-        <v>31</v>
-      </c>
-      <c r="AA31" s="17"/>
-      <c r="AB31" s="18"/>
-      <c r="AC31" s="19"/>
-      <c r="AD31" s="19"/>
-      <c r="AE31" s="19"/>
-      <c r="AF31" s="19"/>
-      <c r="AG31" s="19"/>
-      <c r="AH31" s="19"/>
-      <c r="AI31" s="19"/>
-      <c r="AJ31" s="19"/>
-      <c r="AK31" s="19"/>
-      <c r="AL31" s="20"/>
-    </row>
-    <row r="32" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B32" s="2" t="s">
         <v>36</v>
       </c>
@@ -3147,49 +2815,37 @@
         <v>16</v>
       </c>
       <c r="D32" s="4">
-        <v>27.516255022985199</v>
+        <v>27.719152626643801</v>
       </c>
       <c r="E32" s="4">
-        <v>27.7366359344215</v>
+        <v>27.651365470138241</v>
       </c>
       <c r="F32" s="4">
-        <v>1.677441103007199</v>
+        <v>1.2599158648151161</v>
       </c>
       <c r="G32" s="4">
-        <v>32.700000000000003</v>
+        <v>30.7</v>
       </c>
       <c r="H32" s="4">
-        <v>24.6</v>
+        <v>24.9</v>
       </c>
       <c r="I32" s="4">
-        <v>29.22567485924213</v>
+        <v>28.988</v>
       </c>
       <c r="J32" s="4">
-        <v>28.819719942103401</v>
+        <v>28.28771059380259</v>
       </c>
       <c r="K32" s="4">
-        <v>26.78499963755613</v>
+        <v>26.7</v>
       </c>
       <c r="L32" s="4">
-        <v>25.89</v>
+        <v>26.353243514486969</v>
       </c>
       <c r="M32" s="5">
-        <v>36</v>
-      </c>
-      <c r="AA32" s="2"/>
-      <c r="AB32" s="3"/>
-      <c r="AC32" s="4"/>
-      <c r="AD32" s="4"/>
-      <c r="AE32" s="4"/>
-      <c r="AF32" s="4"/>
-      <c r="AG32" s="4"/>
-      <c r="AH32" s="4"/>
-      <c r="AI32" s="4"/>
-      <c r="AJ32" s="4"/>
-      <c r="AK32" s="4"/>
-      <c r="AL32" s="5"/>
-    </row>
-    <row r="33" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B33" s="21" t="s">
         <v>37</v>
       </c>
@@ -3197,49 +2853,37 @@
         <v>17</v>
       </c>
       <c r="D33" s="19">
-        <v>19.719393854815181</v>
+        <v>20.85</v>
       </c>
       <c r="E33" s="19">
-        <v>19.353625836756901</v>
+        <v>19.93580388378896</v>
       </c>
       <c r="F33" s="19">
-        <v>3.928542018898975</v>
+        <v>3.91709479955616</v>
       </c>
       <c r="G33" s="19">
-        <v>25</v>
+        <v>28.2</v>
       </c>
       <c r="H33" s="19">
-        <v>8.9</v>
+        <v>9.9242448183973995</v>
       </c>
       <c r="I33" s="19">
-        <v>24.577513220304819</v>
+        <v>23.872277002366101</v>
       </c>
       <c r="J33" s="19">
-        <v>21.79217244187727</v>
+        <v>22.374074571967331</v>
       </c>
       <c r="K33" s="19">
-        <v>17.75</v>
+        <v>17.625</v>
       </c>
       <c r="L33" s="19">
-        <v>14.3767578157209</v>
+        <v>14.3253692159515</v>
       </c>
       <c r="M33" s="20">
-        <v>35</v>
-      </c>
-      <c r="AA33" s="21"/>
-      <c r="AB33" s="18"/>
-      <c r="AC33" s="19"/>
-      <c r="AD33" s="19"/>
-      <c r="AE33" s="19"/>
-      <c r="AF33" s="19"/>
-      <c r="AG33" s="19"/>
-      <c r="AH33" s="19"/>
-      <c r="AI33" s="19"/>
-      <c r="AJ33" s="19"/>
-      <c r="AK33" s="19"/>
-      <c r="AL33" s="20"/>
-    </row>
-    <row r="34" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B34" s="6" t="s">
         <v>38</v>
       </c>
@@ -3247,55 +2891,41 @@
         <v>39</v>
       </c>
       <c r="D34" s="4">
-        <v>13.55</v>
+        <v>13.774358043764259</v>
       </c>
       <c r="E34" s="4">
-        <v>13.10074803637859</v>
+        <v>13.51346609422334</v>
       </c>
       <c r="F34" s="4">
-        <v>4.4370162501625687</v>
+        <v>4.1946574975005788</v>
       </c>
       <c r="G34" s="4">
-        <v>22.08940474568584</v>
+        <v>21.9378891640687</v>
       </c>
       <c r="H34" s="4">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="I34" s="4">
-        <v>17.100000000000001</v>
+        <v>18.02</v>
       </c>
       <c r="J34" s="4">
-        <v>15.302096813694</v>
+        <v>16.239999999999998</v>
       </c>
       <c r="K34" s="4">
-        <v>11.18965259023531</v>
+        <v>11.76874427336541</v>
       </c>
       <c r="L34" s="4">
-        <v>7.5502458255406797</v>
+        <v>7.5760540946851229</v>
       </c>
       <c r="M34" s="5">
         <v>30</v>
       </c>
-      <c r="AA34" s="6"/>
-      <c r="AB34" s="3"/>
-      <c r="AC34" s="4"/>
-      <c r="AD34" s="4"/>
-      <c r="AE34" s="4"/>
-      <c r="AF34" s="4"/>
-      <c r="AG34" s="4"/>
-      <c r="AH34" s="4"/>
-      <c r="AI34" s="4"/>
-      <c r="AJ34" s="4"/>
-      <c r="AK34" s="4"/>
-      <c r="AL34" s="5"/>
-    </row>
-    <row r="36" spans="2:38" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B36" s="22"/>
       <c r="C36" s="23"/>
-      <c r="AA36" s="22"/>
-      <c r="AB36" s="23"/>
-    </row>
-    <row r="37" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B37" s="14" t="s">
         <v>35</v>
       </c>
@@ -3310,20 +2940,8 @@
       <c r="K37" s="14"/>
       <c r="L37" s="14"/>
       <c r="M37" s="15"/>
-      <c r="AA37" s="14"/>
-      <c r="AB37" s="14"/>
-      <c r="AC37" s="14"/>
-      <c r="AD37" s="14"/>
-      <c r="AE37" s="14"/>
-      <c r="AF37" s="14"/>
-      <c r="AG37" s="14"/>
-      <c r="AH37" s="14"/>
-      <c r="AI37" s="14"/>
-      <c r="AJ37" s="14"/>
-      <c r="AK37" s="14"/>
-      <c r="AL37" s="15"/>
-    </row>
-    <row r="38" spans="2:38" ht="37.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B38" s="24" t="s">
         <v>1</v>
       </c>
@@ -3360,320 +2978,236 @@
       <c r="M38" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="AA38" s="24"/>
-      <c r="AB38" s="24"/>
-      <c r="AC38" s="24"/>
-      <c r="AD38" s="24"/>
-      <c r="AE38" s="24"/>
-      <c r="AF38" s="24"/>
-      <c r="AG38" s="24"/>
-      <c r="AH38" s="24"/>
-      <c r="AI38" s="24"/>
-      <c r="AJ38" s="24"/>
-      <c r="AK38" s="24"/>
-      <c r="AL38" s="25"/>
-    </row>
-    <row r="39" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B39" s="7">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="26">
-        <v>22.4</v>
+        <v>24.11</v>
       </c>
       <c r="E39" s="26">
-        <v>22.50043893856251</v>
+        <v>24.110844862200739</v>
       </c>
       <c r="F39" s="26">
-        <v>1.140351207459817</v>
+        <v>1.4866459383803849</v>
       </c>
       <c r="G39" s="4">
-        <v>25.313953364862879</v>
+        <v>28.2</v>
       </c>
       <c r="H39" s="4">
-        <v>19.33106073773558</v>
+        <v>20.2</v>
       </c>
       <c r="I39" s="4">
-        <v>24</v>
+        <v>25.27</v>
       </c>
       <c r="J39" s="4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K39" s="4">
-        <v>22</v>
+        <v>23.397917341007471</v>
       </c>
       <c r="L39" s="4">
-        <v>21.37806981031099</v>
+        <v>22.396405287703889</v>
       </c>
       <c r="M39" s="8">
-        <v>41</v>
-      </c>
-      <c r="AA39" s="7"/>
-      <c r="AB39" s="3"/>
-      <c r="AC39" s="26"/>
-      <c r="AD39" s="26"/>
-      <c r="AE39" s="26"/>
-      <c r="AF39" s="4"/>
-      <c r="AG39" s="4"/>
-      <c r="AH39" s="4"/>
-      <c r="AI39" s="4"/>
-      <c r="AJ39" s="4"/>
-      <c r="AK39" s="4"/>
-      <c r="AL39" s="8"/>
-    </row>
-    <row r="40" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B40" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C40" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="27">
-        <v>22.72212634574791</v>
+        <v>23.802261055634808</v>
       </c>
       <c r="E40" s="27">
-        <v>22.597270068484288</v>
+        <v>23.787110278037179</v>
       </c>
       <c r="F40" s="27">
-        <v>1.3124115447960509</v>
+        <v>1.813342472585123</v>
       </c>
       <c r="G40" s="19">
-        <v>25.824582987707529</v>
+        <v>28.7</v>
       </c>
       <c r="H40" s="19">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="I40" s="19">
-        <v>24.406568013994221</v>
+        <v>25.54</v>
       </c>
       <c r="J40" s="19">
-        <v>23.03</v>
+        <v>25</v>
       </c>
       <c r="K40" s="19">
-        <v>21.8</v>
+        <v>22.712499999999999</v>
       </c>
       <c r="L40" s="19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M40" s="20">
-        <v>41</v>
-      </c>
-      <c r="AA40" s="17"/>
-      <c r="AB40" s="18"/>
-      <c r="AC40" s="27"/>
-      <c r="AD40" s="27"/>
-      <c r="AE40" s="27"/>
-      <c r="AF40" s="19"/>
-      <c r="AG40" s="19"/>
-      <c r="AH40" s="19"/>
-      <c r="AI40" s="19"/>
-      <c r="AJ40" s="19"/>
-      <c r="AK40" s="19"/>
-      <c r="AL40" s="20"/>
-    </row>
-    <row r="41" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D41" s="26">
-        <v>22.3</v>
+        <v>23.26127318667481</v>
       </c>
       <c r="E41" s="26">
-        <v>22.310166639344551</v>
+        <v>23.38537370139279</v>
       </c>
       <c r="F41" s="26">
-        <v>1.996901960449055</v>
+        <v>2.088678185567721</v>
       </c>
       <c r="G41" s="4">
-        <v>28.982258372729358</v>
+        <v>28.4</v>
       </c>
       <c r="H41" s="4">
-        <v>17.399999999999999</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="I41" s="4">
-        <v>24.2</v>
+        <v>25.67</v>
       </c>
       <c r="J41" s="4">
-        <v>23.09</v>
+        <v>24.730031235507109</v>
       </c>
       <c r="K41" s="4">
-        <v>21.15</v>
+        <v>22</v>
       </c>
       <c r="L41" s="4">
-        <v>20</v>
+        <v>21.731423161717029</v>
       </c>
       <c r="M41" s="5">
-        <v>41</v>
-      </c>
-      <c r="AA41" s="2"/>
-      <c r="AB41" s="3"/>
-      <c r="AC41" s="26"/>
-      <c r="AD41" s="26"/>
-      <c r="AE41" s="26"/>
-      <c r="AF41" s="4"/>
-      <c r="AG41" s="4"/>
-      <c r="AH41" s="4"/>
-      <c r="AI41" s="4"/>
-      <c r="AJ41" s="4"/>
-      <c r="AK41" s="4"/>
-      <c r="AL41" s="5"/>
-    </row>
-    <row r="42" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B42" s="17">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C42" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D42" s="27">
-        <v>22.1</v>
+        <v>23.45</v>
       </c>
       <c r="E42" s="27">
-        <v>22.08205183331366</v>
+        <v>23.364629627014061</v>
       </c>
       <c r="F42" s="27">
-        <v>2.0003160554149071</v>
+        <v>2.072857826326914</v>
       </c>
       <c r="G42" s="19">
-        <v>25.65</v>
+        <v>27.5</v>
       </c>
       <c r="H42" s="19">
-        <v>16.399999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="I42" s="19">
-        <v>24.583085208000231</v>
+        <v>25.8</v>
       </c>
       <c r="J42" s="19">
-        <v>23</v>
+        <v>24.51948563027009</v>
       </c>
       <c r="K42" s="19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L42" s="19">
-        <v>19.5</v>
+        <v>21.36</v>
       </c>
       <c r="M42" s="20">
-        <v>41</v>
-      </c>
-      <c r="AA42" s="17"/>
-      <c r="AB42" s="18"/>
-      <c r="AC42" s="27"/>
-      <c r="AD42" s="27"/>
-      <c r="AE42" s="27"/>
-      <c r="AF42" s="19"/>
-      <c r="AG42" s="19"/>
-      <c r="AH42" s="19"/>
-      <c r="AI42" s="19"/>
-      <c r="AJ42" s="19"/>
-      <c r="AK42" s="19"/>
-      <c r="AL42" s="20"/>
-    </row>
-    <row r="43" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B43" s="2">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D43" s="26">
-        <v>22.2</v>
+        <v>23</v>
       </c>
       <c r="E43" s="26">
-        <v>22.075724229351191</v>
+        <v>22.95690179797937</v>
       </c>
       <c r="F43" s="26">
-        <v>2.2140497892619568</v>
+        <v>2.2796676211887572</v>
       </c>
       <c r="G43" s="4">
-        <v>25.8</v>
+        <v>27</v>
       </c>
       <c r="H43" s="4">
-        <v>14.7</v>
+        <v>14</v>
       </c>
       <c r="I43" s="4">
-        <v>25</v>
+        <v>25.514547808607919</v>
       </c>
       <c r="J43" s="4">
-        <v>23</v>
+        <v>24.46752629187603</v>
       </c>
       <c r="K43" s="4">
-        <v>20.8</v>
+        <v>21.900000000000009</v>
       </c>
       <c r="L43" s="4">
-        <v>19.5</v>
+        <v>20.968</v>
       </c>
       <c r="M43" s="5">
-        <v>41</v>
-      </c>
-      <c r="AA43" s="2"/>
-      <c r="AB43" s="3"/>
-      <c r="AC43" s="26"/>
-      <c r="AD43" s="26"/>
-      <c r="AE43" s="26"/>
-      <c r="AF43" s="4"/>
-      <c r="AG43" s="4"/>
-      <c r="AH43" s="4"/>
-      <c r="AI43" s="4"/>
-      <c r="AJ43" s="4"/>
-      <c r="AK43" s="4"/>
-      <c r="AL43" s="5"/>
-    </row>
-    <row r="44" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B44" s="17">
-        <v>46418</v>
+        <v>46446</v>
       </c>
       <c r="C44" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D44" s="27">
-        <v>22.1</v>
+        <v>22.9</v>
       </c>
       <c r="E44" s="27">
-        <v>21.814435765720191</v>
+        <v>22.651225749959231</v>
       </c>
       <c r="F44" s="27">
-        <v>2.2906628962858981</v>
+        <v>2.2384626654908448</v>
       </c>
       <c r="G44" s="19">
-        <v>26.454814361485109</v>
+        <v>27</v>
       </c>
       <c r="H44" s="19">
         <v>14</v>
       </c>
       <c r="I44" s="19">
-        <v>24.64249667675406</v>
+        <v>25.24</v>
       </c>
       <c r="J44" s="19">
-        <v>22.824999999999999</v>
+        <v>23.858381502890179</v>
       </c>
       <c r="K44" s="19">
-        <v>20.675000000000001</v>
+        <v>21.715000000000011</v>
       </c>
       <c r="L44" s="19">
-        <v>19</v>
+        <v>20.574000000000002</v>
       </c>
       <c r="M44" s="20">
-        <v>40</v>
-      </c>
-      <c r="AA44" s="17"/>
-      <c r="AB44" s="18"/>
-      <c r="AC44" s="27"/>
-      <c r="AD44" s="27"/>
-      <c r="AE44" s="27"/>
-      <c r="AF44" s="19"/>
-      <c r="AG44" s="19"/>
-      <c r="AH44" s="19"/>
-      <c r="AI44" s="19"/>
-      <c r="AJ44" s="19"/>
-      <c r="AK44" s="19"/>
-      <c r="AL44" s="20"/>
-    </row>
-    <row r="45" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B45" s="2" t="s">
         <v>14</v>
       </c>
@@ -3681,49 +3215,37 @@
         <v>49</v>
       </c>
       <c r="D45" s="26">
+        <v>24.708954739981841</v>
+      </c>
+      <c r="E45" s="26">
+        <v>25.565938831558409</v>
+      </c>
+      <c r="F45" s="26">
+        <v>6.0210834238103441</v>
+      </c>
+      <c r="G45" s="4">
+        <v>41.681393548720443</v>
+      </c>
+      <c r="H45" s="4">
+        <v>15.3</v>
+      </c>
+      <c r="I45" s="4">
+        <v>32.555000000000007</v>
+      </c>
+      <c r="J45" s="4">
+        <v>27.812604645556881</v>
+      </c>
+      <c r="K45" s="4">
         <v>22</v>
       </c>
-      <c r="E45" s="26">
-        <v>22.452416652320512</v>
-      </c>
-      <c r="F45" s="26">
-        <v>4.6516404345387876</v>
-      </c>
-      <c r="G45" s="4">
-        <v>34.7606076740121</v>
-      </c>
-      <c r="H45" s="4">
-        <v>12.4</v>
-      </c>
-      <c r="I45" s="4">
-        <v>27.37623301038046</v>
-      </c>
-      <c r="J45" s="4">
-        <v>25.09071738844878</v>
-      </c>
-      <c r="K45" s="4">
-        <v>19.767499999999998</v>
-      </c>
       <c r="L45" s="4">
-        <v>17.225000000000001</v>
+        <v>18.71509129213479</v>
       </c>
       <c r="M45" s="5">
-        <v>36</v>
-      </c>
-      <c r="AA45" s="2"/>
-      <c r="AB45" s="3"/>
-      <c r="AC45" s="26"/>
-      <c r="AD45" s="26"/>
-      <c r="AE45" s="26"/>
-      <c r="AF45" s="4"/>
-      <c r="AG45" s="4"/>
-      <c r="AH45" s="4"/>
-      <c r="AI45" s="4"/>
-      <c r="AJ45" s="4"/>
-      <c r="AK45" s="4"/>
-      <c r="AL45" s="5"/>
-    </row>
-    <row r="46" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B46" s="21" t="s">
         <v>36</v>
       </c>
@@ -3731,49 +3253,37 @@
         <v>20</v>
       </c>
       <c r="D46" s="27">
-        <v>22.2</v>
+        <v>23.45</v>
       </c>
       <c r="E46" s="27">
-        <v>22.075724229351191</v>
+        <v>23.364629627014061</v>
       </c>
       <c r="F46" s="27">
-        <v>2.2140497892619568</v>
+        <v>2.072857826326914</v>
       </c>
       <c r="G46" s="19">
+        <v>27.5</v>
+      </c>
+      <c r="H46" s="19">
+        <v>16.7</v>
+      </c>
+      <c r="I46" s="19">
         <v>25.8</v>
       </c>
-      <c r="H46" s="19">
-        <v>14.7</v>
-      </c>
-      <c r="I46" s="19">
-        <v>25</v>
-      </c>
       <c r="J46" s="19">
-        <v>23</v>
+        <v>24.51948563027009</v>
       </c>
       <c r="K46" s="19">
-        <v>20.8</v>
+        <v>22</v>
       </c>
       <c r="L46" s="19">
-        <v>19.5</v>
+        <v>21.36</v>
       </c>
       <c r="M46" s="20">
-        <v>41</v>
-      </c>
-      <c r="AA46" s="21"/>
-      <c r="AB46" s="18"/>
-      <c r="AC46" s="27"/>
-      <c r="AD46" s="27"/>
-      <c r="AE46" s="27"/>
-      <c r="AF46" s="19"/>
-      <c r="AG46" s="19"/>
-      <c r="AH46" s="19"/>
-      <c r="AI46" s="19"/>
-      <c r="AJ46" s="19"/>
-      <c r="AK46" s="19"/>
-      <c r="AL46" s="20"/>
-    </row>
-    <row r="47" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B47" s="6" t="s">
         <v>37</v>
       </c>
@@ -3781,55 +3291,41 @@
         <v>40</v>
       </c>
       <c r="D47" s="26">
-        <v>19.05586373591925</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="E47" s="26">
-        <v>19.7521109075665</v>
+        <v>20.885447039389351</v>
       </c>
       <c r="F47" s="26">
-        <v>4.0272850378977694</v>
+        <v>4.386135563278005</v>
       </c>
       <c r="G47" s="4">
-        <v>28.5</v>
+        <v>33</v>
       </c>
       <c r="H47" s="4">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="I47" s="4">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="J47" s="4">
-        <v>22.94999999999991</v>
+        <v>23.175000000000001</v>
       </c>
       <c r="K47" s="4">
-        <v>17.244676623889461</v>
+        <v>18</v>
       </c>
       <c r="L47" s="4">
-        <v>15.35</v>
+        <v>16.690000000000001</v>
       </c>
       <c r="M47" s="5">
-        <v>38</v>
-      </c>
-      <c r="AA47" s="6"/>
-      <c r="AB47" s="3"/>
-      <c r="AC47" s="26"/>
-      <c r="AD47" s="26"/>
-      <c r="AE47" s="26"/>
-      <c r="AF47" s="4"/>
-      <c r="AG47" s="4"/>
-      <c r="AH47" s="4"/>
-      <c r="AI47" s="4"/>
-      <c r="AJ47" s="4"/>
-      <c r="AK47" s="4"/>
-      <c r="AL47" s="5"/>
-    </row>
-    <row r="48" spans="2:38" ht="15.75" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B48" s="22"/>
       <c r="C48" s="23"/>
-      <c r="AA48" s="22"/>
-      <c r="AB48" s="23"/>
-    </row>
-    <row r="50" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B50" s="14" t="s">
         <v>21</v>
       </c>
@@ -3844,20 +3340,8 @@
       <c r="K50" s="14"/>
       <c r="L50" s="14"/>
       <c r="M50" s="15"/>
-      <c r="AA50" s="14"/>
-      <c r="AB50" s="14"/>
-      <c r="AC50" s="14"/>
-      <c r="AD50" s="14"/>
-      <c r="AE50" s="14"/>
-      <c r="AF50" s="14"/>
-      <c r="AG50" s="14"/>
-      <c r="AH50" s="14"/>
-      <c r="AI50" s="14"/>
-      <c r="AJ50" s="14"/>
-      <c r="AK50" s="14"/>
-      <c r="AL50" s="15"/>
-    </row>
-    <row r="51" spans="2:38" ht="37.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B51" s="24" t="s">
         <v>1</v>
       </c>
@@ -3894,482 +3378,358 @@
       <c r="M51" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="AA51" s="24"/>
-      <c r="AB51" s="24"/>
-      <c r="AC51" s="24"/>
-      <c r="AD51" s="24"/>
-      <c r="AE51" s="24"/>
-      <c r="AF51" s="24"/>
-      <c r="AG51" s="24"/>
-      <c r="AH51" s="24"/>
-      <c r="AI51" s="24"/>
-      <c r="AJ51" s="24"/>
-      <c r="AK51" s="24"/>
-      <c r="AL51" s="25"/>
-    </row>
-    <row r="52" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B52" s="7">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D52" s="28">
-        <v>1512.381372401137</v>
-      </c>
-      <c r="E52" s="28">
-        <v>1514.0013983571509</v>
-      </c>
-      <c r="F52" s="28">
-        <v>14.571792776314179</v>
-      </c>
-      <c r="G52" s="28">
-        <v>1552.8294134397479</v>
-      </c>
-      <c r="H52" s="28">
-        <v>1465</v>
-      </c>
-      <c r="I52" s="28">
-        <v>1530.160389000461</v>
-      </c>
-      <c r="J52" s="28">
-        <v>1523.7</v>
-      </c>
-      <c r="K52" s="28">
-        <v>1506</v>
-      </c>
-      <c r="L52" s="28">
-        <v>1499.797239503589</v>
+      <c r="D52" s="34">
+        <v>1530.397708358</v>
+      </c>
+      <c r="E52" s="34">
+        <v>1532.1136508273721</v>
+      </c>
+      <c r="F52" s="34">
+        <v>17.1937403629192</v>
+      </c>
+      <c r="G52" s="34">
+        <v>1603.770007557921</v>
+      </c>
+      <c r="H52" s="34">
+        <v>1500</v>
+      </c>
+      <c r="I52" s="34">
+        <v>1546.7908160147131</v>
+      </c>
+      <c r="J52" s="34">
+        <v>1540.16</v>
+      </c>
+      <c r="K52" s="34">
+        <v>1521.4793549317001</v>
+      </c>
+      <c r="L52" s="34">
+        <v>1514.192</v>
       </c>
       <c r="M52" s="5">
-        <v>45</v>
-      </c>
-      <c r="AA52" s="7"/>
-      <c r="AB52" s="3"/>
-      <c r="AC52" s="28"/>
-      <c r="AD52" s="28"/>
-      <c r="AE52" s="28"/>
-      <c r="AF52" s="28"/>
-      <c r="AG52" s="28"/>
-      <c r="AH52" s="28"/>
-      <c r="AI52" s="28"/>
-      <c r="AJ52" s="28"/>
-      <c r="AK52" s="28"/>
-      <c r="AL52" s="5"/>
-    </row>
-    <row r="53" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B53" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C53" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D53" s="29">
-        <v>1546.240057783051</v>
-      </c>
-      <c r="E53" s="29">
-        <v>1546.5355382437299</v>
-      </c>
-      <c r="F53" s="29">
-        <v>22.249760865873419</v>
-      </c>
-      <c r="G53" s="29">
-        <v>1594</v>
-      </c>
-      <c r="H53" s="29">
-        <v>1495</v>
-      </c>
-      <c r="I53" s="29">
-        <v>1574.978768235824</v>
-      </c>
-      <c r="J53" s="29">
-        <v>1561.191691478524</v>
-      </c>
-      <c r="K53" s="29">
-        <v>1533.8860814976749</v>
-      </c>
-      <c r="L53" s="29">
-        <v>1517.81047009605</v>
+      <c r="D53" s="35">
+        <v>1565</v>
+      </c>
+      <c r="E53" s="35">
+        <v>1567.942835278571</v>
+      </c>
+      <c r="F53" s="35">
+        <v>27.56557208334721</v>
+      </c>
+      <c r="G53" s="35">
+        <v>1680.3063467217471</v>
+      </c>
+      <c r="H53" s="35">
+        <v>1517</v>
+      </c>
+      <c r="I53" s="35">
+        <v>1594.35</v>
+      </c>
+      <c r="J53" s="35">
+        <v>1581.415291532634</v>
+      </c>
+      <c r="K53" s="35">
+        <v>1550.6864029322101</v>
+      </c>
+      <c r="L53" s="35">
+        <v>1539.3077400381781</v>
       </c>
       <c r="M53" s="20">
-        <v>45</v>
-      </c>
-      <c r="AA53" s="17"/>
-      <c r="AB53" s="18"/>
-      <c r="AC53" s="29"/>
-      <c r="AD53" s="29"/>
-      <c r="AE53" s="29"/>
-      <c r="AF53" s="29"/>
-      <c r="AG53" s="29"/>
-      <c r="AH53" s="29"/>
-      <c r="AI53" s="29"/>
-      <c r="AJ53" s="29"/>
-      <c r="AK53" s="29"/>
-      <c r="AL53" s="20"/>
-    </row>
-    <row r="54" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B54" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D54" s="28">
-        <v>1577.273109422091</v>
-      </c>
-      <c r="E54" s="28">
-        <v>1583.206958130661</v>
-      </c>
-      <c r="F54" s="28">
-        <v>33.058705620999547</v>
-      </c>
-      <c r="G54" s="28">
-        <v>1644</v>
-      </c>
-      <c r="H54" s="28">
-        <v>1514</v>
-      </c>
-      <c r="I54" s="28">
-        <v>1634.5110335885811</v>
-      </c>
-      <c r="J54" s="28">
-        <v>1608.6</v>
-      </c>
-      <c r="K54" s="28">
-        <v>1560</v>
-      </c>
-      <c r="L54" s="28">
-        <v>1545.4</v>
+      <c r="D54" s="34">
+        <v>1600</v>
+      </c>
+      <c r="E54" s="34">
+        <v>1603.534267165305</v>
+      </c>
+      <c r="F54" s="34">
+        <v>38.068314583914358</v>
+      </c>
+      <c r="G54" s="34">
+        <v>1741.5446154094791</v>
+      </c>
+      <c r="H54" s="34">
+        <v>1524</v>
+      </c>
+      <c r="I54" s="34">
+        <v>1645.6009454952009</v>
+      </c>
+      <c r="J54" s="34">
+        <v>1621.92897187173</v>
+      </c>
+      <c r="K54" s="34">
+        <v>1579.135</v>
+      </c>
+      <c r="L54" s="34">
+        <v>1562.9085852563801</v>
       </c>
       <c r="M54" s="5">
-        <v>45</v>
-      </c>
-      <c r="AA54" s="2"/>
-      <c r="AB54" s="3"/>
-      <c r="AC54" s="28"/>
-      <c r="AD54" s="28"/>
-      <c r="AE54" s="28"/>
-      <c r="AF54" s="28"/>
-      <c r="AG54" s="28"/>
-      <c r="AH54" s="28"/>
-      <c r="AI54" s="28"/>
-      <c r="AJ54" s="28"/>
-      <c r="AK54" s="28"/>
-      <c r="AL54" s="5"/>
-    </row>
-    <row r="55" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B55" s="17">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C55" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D55" s="29">
-        <v>1618.1042185054771</v>
-      </c>
-      <c r="E55" s="29">
-        <v>1619.5767169773169</v>
-      </c>
-      <c r="F55" s="29">
-        <v>44.76401768957323</v>
-      </c>
-      <c r="G55" s="29">
-        <v>1706.42</v>
-      </c>
-      <c r="H55" s="29">
-        <v>1520</v>
-      </c>
-      <c r="I55" s="29">
-        <v>1686.202784033499</v>
-      </c>
-      <c r="J55" s="29">
-        <v>1644.8966200286891</v>
-      </c>
-      <c r="K55" s="29">
-        <v>1587.072511158972</v>
-      </c>
-      <c r="L55" s="29">
-        <v>1565.9</v>
+      <c r="D55" s="35">
+        <v>1629.580206637178</v>
+      </c>
+      <c r="E55" s="35">
+        <v>1638.909027607541</v>
+      </c>
+      <c r="F55" s="35">
+        <v>47.545335709114823</v>
+      </c>
+      <c r="G55" s="35">
+        <v>1729.91</v>
+      </c>
+      <c r="H55" s="35">
+        <v>1532</v>
+      </c>
+      <c r="I55" s="35">
+        <v>1704.704297480436</v>
+      </c>
+      <c r="J55" s="35">
+        <v>1672.0450000000001</v>
+      </c>
+      <c r="K55" s="35">
+        <v>1604.65</v>
+      </c>
+      <c r="L55" s="35">
+        <v>1591.3542386719159</v>
       </c>
       <c r="M55" s="20">
-        <v>44</v>
-      </c>
-      <c r="AA55" s="17"/>
-      <c r="AB55" s="18"/>
-      <c r="AC55" s="29"/>
-      <c r="AD55" s="29"/>
-      <c r="AE55" s="29"/>
-      <c r="AF55" s="29"/>
-      <c r="AG55" s="29"/>
-      <c r="AH55" s="29"/>
-      <c r="AI55" s="29"/>
-      <c r="AJ55" s="29"/>
-      <c r="AK55" s="29"/>
-      <c r="AL55" s="20"/>
-    </row>
-    <row r="56" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B56" s="2">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D56" s="28">
-        <v>1651.7928018417031</v>
-      </c>
-      <c r="E56" s="28">
-        <v>1655.0218066534601</v>
-      </c>
-      <c r="F56" s="28">
-        <v>55.226953642813243</v>
-      </c>
-      <c r="G56" s="28">
-        <v>1774.68</v>
-      </c>
-      <c r="H56" s="28">
-        <v>1527</v>
-      </c>
-      <c r="I56" s="28">
-        <v>1733.9929228078299</v>
-      </c>
-      <c r="J56" s="28">
-        <v>1680</v>
-      </c>
-      <c r="K56" s="28">
-        <v>1611</v>
-      </c>
-      <c r="L56" s="28">
-        <v>1592</v>
+      <c r="D56" s="34">
+        <v>1661.0881979865269</v>
+      </c>
+      <c r="E56" s="34">
+        <v>1668.626929491528</v>
+      </c>
+      <c r="F56" s="34">
+        <v>55.53012500516283</v>
+      </c>
+      <c r="G56" s="34">
+        <v>1765.7072911920659</v>
+      </c>
+      <c r="H56" s="34">
+        <v>1537</v>
+      </c>
+      <c r="I56" s="34">
+        <v>1746.742</v>
+      </c>
+      <c r="J56" s="34">
+        <v>1715.11</v>
+      </c>
+      <c r="K56" s="34">
+        <v>1630.8</v>
+      </c>
+      <c r="L56" s="34">
+        <v>1614.0519400000001</v>
       </c>
       <c r="M56" s="5">
         <v>45</v>
       </c>
-      <c r="AA56" s="2"/>
-      <c r="AB56" s="3"/>
-      <c r="AC56" s="28"/>
-      <c r="AD56" s="28"/>
-      <c r="AE56" s="28"/>
-      <c r="AF56" s="28"/>
-      <c r="AG56" s="28"/>
-      <c r="AH56" s="28"/>
-      <c r="AI56" s="28"/>
-      <c r="AJ56" s="28"/>
-      <c r="AK56" s="28"/>
-      <c r="AL56" s="5"/>
-    </row>
-    <row r="57" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B57" s="17">
-        <v>46418</v>
+        <v>46446</v>
       </c>
       <c r="C57" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D57" s="29">
-        <v>1688.1933162856869</v>
-      </c>
-      <c r="E57" s="29">
-        <v>1684.443365446062</v>
-      </c>
-      <c r="F57" s="29">
-        <v>62.755911127529629</v>
-      </c>
-      <c r="G57" s="29">
-        <v>1810.17</v>
-      </c>
-      <c r="H57" s="29">
-        <v>1532</v>
-      </c>
-      <c r="I57" s="29">
-        <v>1767.2142622732449</v>
-      </c>
-      <c r="J57" s="29">
-        <v>1710.382012342661</v>
-      </c>
-      <c r="K57" s="29">
-        <v>1638.0546840037659</v>
-      </c>
-      <c r="L57" s="29">
-        <v>1613.6</v>
+      <c r="D57" s="35">
+        <v>1695</v>
+      </c>
+      <c r="E57" s="35">
+        <v>1696.6010905299031</v>
+      </c>
+      <c r="F57" s="35">
+        <v>62.582317660140212</v>
+      </c>
+      <c r="G57" s="35">
+        <v>1816.5676895261049</v>
+      </c>
+      <c r="H57" s="35">
+        <v>1543</v>
+      </c>
+      <c r="I57" s="35">
+        <v>1782.944</v>
+      </c>
+      <c r="J57" s="35">
+        <v>1750.8583003148269</v>
+      </c>
+      <c r="K57" s="35">
+        <v>1657</v>
+      </c>
+      <c r="L57" s="35">
+        <v>1638.27278</v>
       </c>
       <c r="M57" s="20">
-        <v>43</v>
-      </c>
-      <c r="AA57" s="17"/>
-      <c r="AB57" s="18"/>
-      <c r="AC57" s="29"/>
-      <c r="AD57" s="29"/>
-      <c r="AE57" s="29"/>
-      <c r="AF57" s="29"/>
-      <c r="AG57" s="29"/>
-      <c r="AH57" s="29"/>
-      <c r="AI57" s="29"/>
-      <c r="AJ57" s="29"/>
-      <c r="AK57" s="29"/>
-      <c r="AL57" s="20"/>
-    </row>
-    <row r="58" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D58" s="28">
-        <v>1859</v>
-      </c>
-      <c r="E58" s="28">
-        <v>1853.3564608448521</v>
-      </c>
-      <c r="F58" s="28">
-        <v>110.1052088001979</v>
-      </c>
-      <c r="G58" s="28">
-        <v>2122.06</v>
-      </c>
-      <c r="H58" s="28">
-        <v>1575</v>
-      </c>
-      <c r="I58" s="28">
-        <v>1966.476616006388</v>
-      </c>
-      <c r="J58" s="28">
-        <v>1923.1053973415401</v>
-      </c>
-      <c r="K58" s="28">
-        <v>1786</v>
-      </c>
-      <c r="L58" s="28">
-        <v>1729.4108688576321</v>
+      <c r="D58" s="34">
+        <v>1844</v>
+      </c>
+      <c r="E58" s="34">
+        <v>1878.3639933735931</v>
+      </c>
+      <c r="F58" s="34">
+        <v>133.56626773120081</v>
+      </c>
+      <c r="G58" s="34">
+        <v>2142.3000000000002</v>
+      </c>
+      <c r="H58" s="34">
+        <v>1604</v>
+      </c>
+      <c r="I58" s="34">
+        <v>2069</v>
+      </c>
+      <c r="J58" s="34">
+        <v>1967.254908830042</v>
+      </c>
+      <c r="K58" s="34">
+        <v>1794</v>
+      </c>
+      <c r="L58" s="34">
+        <v>1721.0220999999999</v>
       </c>
       <c r="M58" s="5">
-        <v>39</v>
-      </c>
-      <c r="AA58" s="2"/>
-      <c r="AB58" s="3"/>
-      <c r="AC58" s="28"/>
-      <c r="AD58" s="28"/>
-      <c r="AE58" s="28"/>
-      <c r="AF58" s="28"/>
-      <c r="AG58" s="28"/>
-      <c r="AH58" s="28"/>
-      <c r="AI58" s="28"/>
-      <c r="AJ58" s="28"/>
-      <c r="AK58" s="28"/>
-      <c r="AL58" s="5"/>
-    </row>
-    <row r="59" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B59" s="21" t="s">
         <v>36</v>
       </c>
       <c r="C59" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D59" s="29">
-        <v>1651.7928018417031</v>
-      </c>
-      <c r="E59" s="29">
-        <v>1655.0217070148931</v>
-      </c>
-      <c r="F59" s="29">
-        <v>55.226865793337637</v>
-      </c>
-      <c r="G59" s="29">
-        <v>1774.68</v>
-      </c>
-      <c r="H59" s="29">
-        <v>1527</v>
-      </c>
-      <c r="I59" s="29">
-        <v>1733.9929228078299</v>
-      </c>
-      <c r="J59" s="29">
-        <v>1680</v>
-      </c>
-      <c r="K59" s="29">
-        <v>1611</v>
-      </c>
-      <c r="L59" s="29">
-        <v>1592</v>
+      <c r="D59" s="35">
+        <v>1629.580206637178</v>
+      </c>
+      <c r="E59" s="35">
+        <v>1638.909027607541</v>
+      </c>
+      <c r="F59" s="35">
+        <v>47.545335709114823</v>
+      </c>
+      <c r="G59" s="35">
+        <v>1729.91</v>
+      </c>
+      <c r="H59" s="35">
+        <v>1532</v>
+      </c>
+      <c r="I59" s="35">
+        <v>1704.704297480436</v>
+      </c>
+      <c r="J59" s="35">
+        <v>1672.0450000000001</v>
+      </c>
+      <c r="K59" s="35">
+        <v>1604.65</v>
+      </c>
+      <c r="L59" s="35">
+        <v>1591.3542386719159</v>
       </c>
       <c r="M59" s="20">
-        <v>45</v>
-      </c>
-      <c r="AA59" s="21"/>
-      <c r="AB59" s="18"/>
-      <c r="AC59" s="29"/>
-      <c r="AD59" s="29"/>
-      <c r="AE59" s="29"/>
-      <c r="AF59" s="29"/>
-      <c r="AG59" s="29"/>
-      <c r="AH59" s="29"/>
-      <c r="AI59" s="29"/>
-      <c r="AJ59" s="29"/>
-      <c r="AK59" s="29"/>
-      <c r="AL59" s="20"/>
-    </row>
-    <row r="60" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B60" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="28">
-        <v>2018.25</v>
-      </c>
-      <c r="E60" s="28">
-        <v>2015.3488190279261</v>
-      </c>
-      <c r="F60" s="28">
-        <v>147.85171216893571</v>
-      </c>
-      <c r="G60" s="28">
-        <v>2357</v>
-      </c>
-      <c r="H60" s="28">
-        <v>1634</v>
-      </c>
-      <c r="I60" s="28">
-        <v>2198.84</v>
-      </c>
-      <c r="J60" s="28">
+      <c r="D60" s="34">
+        <v>2015.7025366818041</v>
+      </c>
+      <c r="E60" s="34">
+        <v>2016.731098939299</v>
+      </c>
+      <c r="F60" s="34">
+        <v>156.79152636028149</v>
+      </c>
+      <c r="G60" s="34">
+        <v>2356.4299999999998</v>
+      </c>
+      <c r="H60" s="34">
+        <v>1652</v>
+      </c>
+      <c r="I60" s="34">
+        <v>2244.294531816055</v>
+      </c>
+      <c r="J60" s="34">
         <v>2100</v>
       </c>
-      <c r="K60" s="28">
-        <v>1931.401455023502</v>
-      </c>
-      <c r="L60" s="28">
-        <v>1810.9788287891099</v>
+      <c r="K60" s="34">
+        <v>1919.8617008816591</v>
+      </c>
+      <c r="L60" s="34">
+        <v>1821.4</v>
       </c>
       <c r="M60" s="5">
-        <v>43</v>
-      </c>
-      <c r="AA60" s="6"/>
-      <c r="AB60" s="3"/>
-      <c r="AC60" s="28"/>
-      <c r="AD60" s="28"/>
-      <c r="AE60" s="28"/>
-      <c r="AF60" s="28"/>
-      <c r="AG60" s="28"/>
-      <c r="AH60" s="28"/>
-      <c r="AI60" s="28"/>
-      <c r="AJ60" s="28"/>
-      <c r="AK60" s="28"/>
-      <c r="AL60" s="5"/>
-    </row>
-    <row r="61" spans="2:38" ht="15.75" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B61" s="22"/>
       <c r="C61" s="23"/>
-      <c r="AA61" s="22"/>
-      <c r="AB61" s="23"/>
-    </row>
-    <row r="62" spans="2:38" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B62" s="22"/>
       <c r="C62" s="23"/>
-      <c r="AA62" s="22"/>
-      <c r="AB62" s="23"/>
-    </row>
-    <row r="63" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B63" s="14" t="s">
         <v>24</v>
       </c>
@@ -4384,20 +3744,8 @@
       <c r="K63" s="14"/>
       <c r="L63" s="14"/>
       <c r="M63" s="15"/>
-      <c r="AA63" s="14"/>
-      <c r="AB63" s="14"/>
-      <c r="AC63" s="14"/>
-      <c r="AD63" s="14"/>
-      <c r="AE63" s="14"/>
-      <c r="AF63" s="14"/>
-      <c r="AG63" s="14"/>
-      <c r="AH63" s="14"/>
-      <c r="AI63" s="14"/>
-      <c r="AJ63" s="14"/>
-      <c r="AK63" s="14"/>
-      <c r="AL63" s="15"/>
-    </row>
-    <row r="64" spans="2:38" ht="37.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B64" s="24" t="s">
         <v>1</v>
       </c>
@@ -4434,482 +3782,358 @@
       <c r="M64" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="AA64" s="24"/>
-      <c r="AB64" s="24"/>
-      <c r="AC64" s="24"/>
-      <c r="AD64" s="24"/>
-      <c r="AE64" s="24"/>
-      <c r="AF64" s="24"/>
-      <c r="AG64" s="24"/>
-      <c r="AH64" s="24"/>
-      <c r="AI64" s="24"/>
-      <c r="AJ64" s="24"/>
-      <c r="AK64" s="24"/>
-      <c r="AL64" s="25"/>
-    </row>
-    <row r="65" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B65" s="7">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D65" s="28">
-        <v>8900</v>
-      </c>
-      <c r="E65" s="28">
-        <v>8875.9362242947518</v>
-      </c>
-      <c r="F65" s="28">
-        <v>338.55332476494539</v>
-      </c>
-      <c r="G65" s="28">
-        <v>9678.0851647567706</v>
-      </c>
-      <c r="H65" s="28">
-        <v>8261.5257744472037</v>
-      </c>
-      <c r="I65" s="28">
-        <v>9328</v>
-      </c>
-      <c r="J65" s="28">
-        <v>9023</v>
-      </c>
-      <c r="K65" s="28">
-        <v>8656.1377913832293</v>
-      </c>
-      <c r="L65" s="28">
-        <v>8450.204290000218</v>
+      <c r="D65" s="34">
+        <v>8778.3951114141073</v>
+      </c>
+      <c r="E65" s="34">
+        <v>8799.1939386031336</v>
+      </c>
+      <c r="F65" s="34">
+        <v>334.84761855530132</v>
+      </c>
+      <c r="G65" s="34">
+        <v>9672</v>
+      </c>
+      <c r="H65" s="34">
+        <v>8000</v>
+      </c>
+      <c r="I65" s="34">
+        <v>9163.4885922229914</v>
+      </c>
+      <c r="J65" s="34">
+        <v>8896.1630038541934</v>
+      </c>
+      <c r="K65" s="34">
+        <v>8693.0783666930001</v>
+      </c>
+      <c r="L65" s="34">
+        <v>8471.4208767468608</v>
       </c>
       <c r="M65" s="8">
-        <v>37</v>
-      </c>
-      <c r="AA65" s="7"/>
-      <c r="AB65" s="3"/>
-      <c r="AC65" s="28"/>
-      <c r="AD65" s="28"/>
-      <c r="AE65" s="28"/>
-      <c r="AF65" s="28"/>
-      <c r="AG65" s="28"/>
-      <c r="AH65" s="28"/>
-      <c r="AI65" s="28"/>
-      <c r="AJ65" s="28"/>
-      <c r="AK65" s="28"/>
-      <c r="AL65" s="8"/>
-    </row>
-    <row r="66" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B66" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C66" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D66" s="29">
-        <v>8785.1471619888889</v>
-      </c>
-      <c r="E66" s="29">
-        <v>8801.9047354729901</v>
-      </c>
-      <c r="F66" s="29">
-        <v>431.66639318607912</v>
-      </c>
-      <c r="G66" s="29">
-        <v>10165.564280137931</v>
-      </c>
-      <c r="H66" s="29">
-        <v>8000</v>
-      </c>
-      <c r="I66" s="29">
-        <v>9290.4438765941013</v>
-      </c>
-      <c r="J66" s="29">
-        <v>9097.1456380288746</v>
-      </c>
-      <c r="K66" s="29">
-        <v>8533</v>
-      </c>
-      <c r="L66" s="29">
-        <v>8280.8799999999992</v>
+      <c r="D66" s="35">
+        <v>8700</v>
+      </c>
+      <c r="E66" s="35">
+        <v>8672.5453582648133</v>
+      </c>
+      <c r="F66" s="35">
+        <v>304.04471561824681</v>
+      </c>
+      <c r="G66" s="35">
+        <v>9310</v>
+      </c>
+      <c r="H66" s="35">
+        <v>8125</v>
+      </c>
+      <c r="I66" s="35">
+        <v>9037.9561713134717</v>
+      </c>
+      <c r="J66" s="35">
+        <v>8880.0897335236878</v>
+      </c>
+      <c r="K66" s="35">
+        <v>8498.9335001966301</v>
+      </c>
+      <c r="L66" s="35">
+        <v>8302.1316597373498</v>
       </c>
       <c r="M66" s="20">
-        <v>37</v>
-      </c>
-      <c r="AA66" s="17"/>
-      <c r="AB66" s="18"/>
-      <c r="AC66" s="29"/>
-      <c r="AD66" s="29"/>
-      <c r="AE66" s="29"/>
-      <c r="AF66" s="29"/>
-      <c r="AG66" s="29"/>
-      <c r="AH66" s="29"/>
-      <c r="AI66" s="29"/>
-      <c r="AJ66" s="29"/>
-      <c r="AK66" s="29"/>
-      <c r="AL66" s="20"/>
-    </row>
-    <row r="67" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B67" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D67" s="28">
-        <v>8580</v>
-      </c>
-      <c r="E67" s="28">
-        <v>8663.0256283639919</v>
-      </c>
-      <c r="F67" s="28">
-        <v>483.2642572915392</v>
-      </c>
-      <c r="G67" s="28">
-        <v>10615.8881347724</v>
-      </c>
-      <c r="H67" s="28">
-        <v>8000</v>
-      </c>
-      <c r="I67" s="28">
-        <v>9168.4288843558224</v>
-      </c>
-      <c r="J67" s="28">
-        <v>8832.2144566698935</v>
-      </c>
-      <c r="K67" s="28">
-        <v>8325</v>
-      </c>
-      <c r="L67" s="28">
-        <v>8188.24</v>
+      <c r="D67" s="34">
+        <v>8550.1749999999993</v>
+      </c>
+      <c r="E67" s="34">
+        <v>8574.0472163064278</v>
+      </c>
+      <c r="F67" s="34">
+        <v>285.52513648472791</v>
+      </c>
+      <c r="G67" s="34">
+        <v>9160</v>
+      </c>
+      <c r="H67" s="34">
+        <v>8034.1336058320276</v>
+      </c>
+      <c r="I67" s="34">
+        <v>8970.8405478535933</v>
+      </c>
+      <c r="J67" s="34">
+        <v>8756.5811683453503</v>
+      </c>
+      <c r="K67" s="34">
+        <v>8373.2938074597932</v>
+      </c>
+      <c r="L67" s="34">
+        <v>8252.5728523414564</v>
       </c>
       <c r="M67" s="5">
-        <v>37</v>
-      </c>
-      <c r="AA67" s="2"/>
-      <c r="AB67" s="3"/>
-      <c r="AC67" s="28"/>
-      <c r="AD67" s="28"/>
-      <c r="AE67" s="28"/>
-      <c r="AF67" s="28"/>
-      <c r="AG67" s="28"/>
-      <c r="AH67" s="28"/>
-      <c r="AI67" s="28"/>
-      <c r="AJ67" s="28"/>
-      <c r="AK67" s="28"/>
-      <c r="AL67" s="5"/>
-    </row>
-    <row r="68" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B68" s="17">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C68" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D68" s="29">
-        <v>8498.3378442743015</v>
-      </c>
-      <c r="E68" s="29">
-        <v>8570.3175150722909</v>
-      </c>
-      <c r="F68" s="29">
-        <v>521.15346441489226</v>
-      </c>
-      <c r="G68" s="29">
-        <v>10829.486808082331</v>
-      </c>
-      <c r="H68" s="29">
-        <v>7828</v>
-      </c>
-      <c r="I68" s="29">
-        <v>9010.2646363466756</v>
-      </c>
-      <c r="J68" s="29">
-        <v>8760</v>
-      </c>
-      <c r="K68" s="29">
-        <v>8238</v>
-      </c>
-      <c r="L68" s="29">
-        <v>8056.6</v>
+      <c r="D68" s="35">
+        <v>8194.9451265075295</v>
+      </c>
+      <c r="E68" s="35">
+        <v>8319.5969970779661</v>
+      </c>
+      <c r="F68" s="35">
+        <v>361.55130199440981</v>
+      </c>
+      <c r="G68" s="35">
+        <v>9063</v>
+      </c>
+      <c r="H68" s="35">
+        <v>7745.7071426302018</v>
+      </c>
+      <c r="I68" s="35">
+        <v>8816</v>
+      </c>
+      <c r="J68" s="35">
+        <v>8654.9660520965608</v>
+      </c>
+      <c r="K68" s="35">
+        <v>8042.3404823165574</v>
+      </c>
+      <c r="L68" s="35">
+        <v>7973.7449999999999</v>
       </c>
       <c r="M68" s="20">
-        <v>37</v>
-      </c>
-      <c r="AA68" s="17"/>
-      <c r="AB68" s="18"/>
-      <c r="AC68" s="29"/>
-      <c r="AD68" s="29"/>
-      <c r="AE68" s="29"/>
-      <c r="AF68" s="29"/>
-      <c r="AG68" s="29"/>
-      <c r="AH68" s="29"/>
-      <c r="AI68" s="29"/>
-      <c r="AJ68" s="29"/>
-      <c r="AK68" s="29"/>
-      <c r="AL68" s="20"/>
-    </row>
-    <row r="69" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B69" s="2">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D69" s="28">
-        <v>8165.7695664374223</v>
-      </c>
-      <c r="E69" s="28">
-        <v>8260.5017212912844</v>
-      </c>
-      <c r="F69" s="28">
-        <v>559.63348603213808</v>
-      </c>
-      <c r="G69" s="28">
-        <v>10754.40831195166</v>
-      </c>
-      <c r="H69" s="28">
-        <v>7629.7620461218703</v>
-      </c>
-      <c r="I69" s="28">
-        <v>8780</v>
-      </c>
-      <c r="J69" s="28">
-        <v>8411.3797338921613</v>
-      </c>
-      <c r="K69" s="28">
-        <v>7970</v>
-      </c>
-      <c r="L69" s="28">
-        <v>7763.410636303206</v>
+      <c r="D69" s="34">
+        <v>8119</v>
+      </c>
+      <c r="E69" s="34">
+        <v>8168.656290238504</v>
+      </c>
+      <c r="F69" s="34">
+        <v>342.50782220308122</v>
+      </c>
+      <c r="G69" s="34">
+        <v>8930.2833274626992</v>
+      </c>
+      <c r="H69" s="34">
+        <v>7599</v>
+      </c>
+      <c r="I69" s="34">
+        <v>8632.4</v>
+      </c>
+      <c r="J69" s="34">
+        <v>8339.2823588460906</v>
+      </c>
+      <c r="K69" s="34">
+        <v>7955.9750000000004</v>
+      </c>
+      <c r="L69" s="34">
+        <v>7719.9180240362602</v>
       </c>
       <c r="M69" s="5">
-        <v>37</v>
-      </c>
-      <c r="AA69" s="2"/>
-      <c r="AB69" s="3"/>
-      <c r="AC69" s="28"/>
-      <c r="AD69" s="28"/>
-      <c r="AE69" s="28"/>
-      <c r="AF69" s="28"/>
-      <c r="AG69" s="28"/>
-      <c r="AH69" s="28"/>
-      <c r="AI69" s="28"/>
-      <c r="AJ69" s="28"/>
-      <c r="AK69" s="28"/>
-      <c r="AL69" s="5"/>
-    </row>
-    <row r="70" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B70" s="17">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C70" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D70" s="29">
-        <v>8058.2851629484776</v>
-      </c>
-      <c r="E70" s="29">
-        <v>8154.7465167735909</v>
-      </c>
-      <c r="F70" s="29">
-        <v>540.58747744758182</v>
-      </c>
-      <c r="G70" s="29">
-        <v>10431.305485114641</v>
-      </c>
-      <c r="H70" s="29">
-        <v>7563</v>
-      </c>
-      <c r="I70" s="29">
-        <v>8673.6232695737508</v>
-      </c>
-      <c r="J70" s="29">
-        <v>8380</v>
-      </c>
-      <c r="K70" s="29">
-        <v>7820</v>
-      </c>
-      <c r="L70" s="29">
-        <v>7625.4173585751068</v>
+      <c r="D70" s="35">
+        <v>7500</v>
+      </c>
+      <c r="E70" s="35">
+        <v>7623.8791727223088</v>
+      </c>
+      <c r="F70" s="35">
+        <v>389.61311317094118</v>
+      </c>
+      <c r="G70" s="35">
+        <v>8610</v>
+      </c>
+      <c r="H70" s="35">
+        <v>7092</v>
+      </c>
+      <c r="I70" s="35">
+        <v>8167.7601792586129</v>
+      </c>
+      <c r="J70" s="35">
+        <v>7813</v>
+      </c>
+      <c r="K70" s="35">
+        <v>7368.5443350182923</v>
+      </c>
+      <c r="L70" s="35">
+        <v>7205.4702526333231</v>
       </c>
       <c r="M70" s="20">
         <v>37</v>
       </c>
-      <c r="AA70" s="17"/>
-      <c r="AB70" s="18"/>
-      <c r="AC70" s="29"/>
-      <c r="AD70" s="29"/>
-      <c r="AE70" s="29"/>
-      <c r="AF70" s="29"/>
-      <c r="AG70" s="29"/>
-      <c r="AH70" s="29"/>
-      <c r="AI70" s="29"/>
-      <c r="AJ70" s="29"/>
-      <c r="AK70" s="29"/>
-      <c r="AL70" s="20"/>
-    </row>
-    <row r="71" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B71" s="2">
-        <v>46418</v>
+        <v>46446</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D71" s="28">
-        <v>7520.7358315058009</v>
-      </c>
-      <c r="E71" s="28">
-        <v>7531.3552162137712</v>
-      </c>
-      <c r="F71" s="28">
-        <v>384.97596930346782</v>
-      </c>
-      <c r="G71" s="28">
-        <v>8410</v>
-      </c>
-      <c r="H71" s="28">
-        <v>6728.8</v>
-      </c>
-      <c r="I71" s="28">
-        <v>7986.8</v>
-      </c>
-      <c r="J71" s="28">
-        <v>7773.0534868192099</v>
-      </c>
-      <c r="K71" s="28">
-        <v>7318.7860049768506</v>
-      </c>
-      <c r="L71" s="28">
-        <v>7014.6535533726783</v>
+      <c r="D71" s="34">
+        <v>7262.92</v>
+      </c>
+      <c r="E71" s="34">
+        <v>7251.0594494848556</v>
+      </c>
+      <c r="F71" s="34">
+        <v>605.34289625022961</v>
+      </c>
+      <c r="G71" s="34">
+        <v>8300</v>
+      </c>
+      <c r="H71" s="34">
+        <v>6081</v>
+      </c>
+      <c r="I71" s="34">
+        <v>8162</v>
+      </c>
+      <c r="J71" s="34">
+        <v>7560.0226040209654</v>
+      </c>
+      <c r="K71" s="34">
+        <v>6823.1035115965842</v>
+      </c>
+      <c r="L71" s="34">
+        <v>6385.6238148919056</v>
       </c>
       <c r="M71" s="5">
-        <v>35</v>
-      </c>
-      <c r="AA71" s="2"/>
-      <c r="AB71" s="3"/>
-      <c r="AC71" s="28"/>
-      <c r="AD71" s="28"/>
-      <c r="AE71" s="28"/>
-      <c r="AF71" s="28"/>
-      <c r="AG71" s="28"/>
-      <c r="AH71" s="28"/>
-      <c r="AI71" s="28"/>
-      <c r="AJ71" s="28"/>
-      <c r="AK71" s="28"/>
-      <c r="AL71" s="5"/>
-    </row>
-    <row r="72" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B72" s="21" t="s">
         <v>36</v>
       </c>
       <c r="C72" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D72" s="29">
-        <v>100207.38084529219</v>
-      </c>
-      <c r="E72" s="29">
-        <v>100679.7296427807</v>
-      </c>
-      <c r="F72" s="29">
-        <v>2448.1933922907861</v>
-      </c>
-      <c r="G72" s="29">
-        <v>111928.73818481569</v>
-      </c>
-      <c r="H72" s="29">
-        <v>96958</v>
-      </c>
-      <c r="I72" s="29">
-        <v>103077.8784387601</v>
-      </c>
-      <c r="J72" s="29">
-        <v>101381.4433785436</v>
-      </c>
-      <c r="K72" s="29">
-        <v>99402.950391798062</v>
-      </c>
-      <c r="L72" s="29">
-        <v>98299.932000000001</v>
+      <c r="D72" s="35">
+        <v>100895</v>
+      </c>
+      <c r="E72" s="35">
+        <v>100827.8481998714</v>
+      </c>
+      <c r="F72" s="35">
+        <v>1134.4280944663619</v>
+      </c>
+      <c r="G72" s="35">
+        <v>103240</v>
+      </c>
+      <c r="H72" s="35">
+        <v>98355</v>
+      </c>
+      <c r="I72" s="35">
+        <v>102443.722324923</v>
+      </c>
+      <c r="J72" s="35">
+        <v>101341.9245047248</v>
+      </c>
+      <c r="K72" s="35">
+        <v>100092.4120300034</v>
+      </c>
+      <c r="L72" s="35">
+        <v>99699.514499147917</v>
       </c>
       <c r="M72" s="20">
-        <v>40</v>
-      </c>
-      <c r="AA72" s="21"/>
-      <c r="AB72" s="18"/>
-      <c r="AC72" s="29"/>
-      <c r="AD72" s="29"/>
-      <c r="AE72" s="29"/>
-      <c r="AF72" s="29"/>
-      <c r="AG72" s="29"/>
-      <c r="AH72" s="29"/>
-      <c r="AI72" s="29"/>
-      <c r="AJ72" s="29"/>
-      <c r="AK72" s="29"/>
-      <c r="AL72" s="20"/>
-    </row>
-    <row r="73" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B73" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D73" s="28">
-        <v>104447.68290056199</v>
-      </c>
-      <c r="E73" s="28">
-        <v>104745.2910050075</v>
-      </c>
-      <c r="F73" s="28">
-        <v>3671.124364693625</v>
-      </c>
-      <c r="G73" s="28">
-        <v>116235.87468463169</v>
-      </c>
-      <c r="H73" s="28">
-        <v>92437.488358738512</v>
-      </c>
-      <c r="I73" s="28">
-        <v>108761.9217075646</v>
-      </c>
-      <c r="J73" s="28">
-        <v>105791.2106455692</v>
-      </c>
-      <c r="K73" s="28">
-        <v>103095.277</v>
-      </c>
-      <c r="L73" s="28">
-        <v>101953.9033254989</v>
+      <c r="D73" s="34">
+        <v>104810.1958823974</v>
+      </c>
+      <c r="E73" s="34">
+        <v>105283.46721621</v>
+      </c>
+      <c r="F73" s="34">
+        <v>3672.2284983260502</v>
+      </c>
+      <c r="G73" s="34">
+        <v>114070</v>
+      </c>
+      <c r="H73" s="34">
+        <v>96210</v>
+      </c>
+      <c r="I73" s="34">
+        <v>110018.1222231695</v>
+      </c>
+      <c r="J73" s="34">
+        <v>107469.5</v>
+      </c>
+      <c r="K73" s="34">
+        <v>103392.6298065407</v>
+      </c>
+      <c r="L73" s="34">
+        <v>101793.3646556985</v>
       </c>
       <c r="M73" s="5">
-        <v>36</v>
-      </c>
-      <c r="AA73" s="6"/>
-      <c r="AB73" s="3"/>
-      <c r="AC73" s="28"/>
-      <c r="AD73" s="28"/>
-      <c r="AE73" s="28"/>
-      <c r="AF73" s="28"/>
-      <c r="AG73" s="28"/>
-      <c r="AH73" s="28"/>
-      <c r="AI73" s="28"/>
-      <c r="AJ73" s="28"/>
-      <c r="AK73" s="28"/>
-      <c r="AL73" s="5"/>
-    </row>
-    <row r="74" spans="2:38" ht="15.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B74" s="22"/>
       <c r="C74" s="23"/>
-      <c r="AA74" s="22"/>
-      <c r="AB74" s="23"/>
-    </row>
-    <row r="75" spans="2:38" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B75" s="22"/>
       <c r="C75" s="23"/>
-      <c r="AA75" s="22"/>
-      <c r="AB75" s="23"/>
-    </row>
-    <row r="76" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B76" s="14" t="s">
         <v>26</v>
       </c>
@@ -4924,20 +4148,8 @@
       <c r="K76" s="14"/>
       <c r="L76" s="14"/>
       <c r="M76" s="15"/>
-      <c r="AA76" s="14"/>
-      <c r="AB76" s="14"/>
-      <c r="AC76" s="14"/>
-      <c r="AD76" s="14"/>
-      <c r="AE76" s="14"/>
-      <c r="AF76" s="14"/>
-      <c r="AG76" s="14"/>
-      <c r="AH76" s="14"/>
-      <c r="AI76" s="14"/>
-      <c r="AJ76" s="14"/>
-      <c r="AK76" s="14"/>
-      <c r="AL76" s="15"/>
-    </row>
-    <row r="77" spans="2:38" ht="37.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B77" s="24" t="s">
         <v>1</v>
       </c>
@@ -4974,470 +4186,350 @@
       <c r="M77" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="AA77" s="24"/>
-      <c r="AB77" s="24"/>
-      <c r="AC77" s="24"/>
-      <c r="AD77" s="24"/>
-      <c r="AE77" s="24"/>
-      <c r="AF77" s="24"/>
-      <c r="AG77" s="24"/>
-      <c r="AH77" s="24"/>
-      <c r="AI77" s="24"/>
-      <c r="AJ77" s="24"/>
-      <c r="AK77" s="24"/>
-      <c r="AL77" s="25"/>
-    </row>
-    <row r="78" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B78" s="7">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D78" s="28">
-        <v>7033.2951998234794</v>
-      </c>
-      <c r="E78" s="28">
-        <v>7072.0430161598706</v>
-      </c>
-      <c r="F78" s="28">
-        <v>243.53278542790201</v>
-      </c>
-      <c r="G78" s="28">
-        <v>7805.3</v>
-      </c>
-      <c r="H78" s="28">
-        <v>6500</v>
-      </c>
-      <c r="I78" s="28">
-        <v>7359.8307194826884</v>
-      </c>
-      <c r="J78" s="28">
-        <v>7210.5235102967217</v>
-      </c>
-      <c r="K78" s="28">
-        <v>6908.9703736302054</v>
-      </c>
-      <c r="L78" s="28">
-        <v>6814.8334183792067</v>
+      <c r="D78" s="34">
+        <v>6851.6238776415994</v>
+      </c>
+      <c r="E78" s="34">
+        <v>6847.0542287467306</v>
+      </c>
+      <c r="F78" s="34">
+        <v>285.42872953909301</v>
+      </c>
+      <c r="G78" s="34">
+        <v>7469</v>
+      </c>
+      <c r="H78" s="34">
+        <v>6121.375040554246</v>
+      </c>
+      <c r="I78" s="34">
+        <v>7181.5808525031916</v>
+      </c>
+      <c r="J78" s="34">
+        <v>6989.3151278238929</v>
+      </c>
+      <c r="K78" s="34">
+        <v>6703.75</v>
+      </c>
+      <c r="L78" s="34">
+        <v>6485.9776168316648</v>
       </c>
       <c r="M78" s="8">
-        <v>37</v>
-      </c>
-      <c r="AA78" s="7"/>
-      <c r="AB78" s="3"/>
-      <c r="AC78" s="28"/>
-      <c r="AD78" s="28"/>
-      <c r="AE78" s="28"/>
-      <c r="AF78" s="28"/>
-      <c r="AG78" s="28"/>
-      <c r="AH78" s="28"/>
-      <c r="AI78" s="28"/>
-      <c r="AJ78" s="28"/>
-      <c r="AK78" s="28"/>
-      <c r="AL78" s="8"/>
-    </row>
-    <row r="79" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B79" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C79" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D79" s="29">
-        <v>7001.3020479708739</v>
-      </c>
-      <c r="E79" s="29">
-        <v>6966.4668325842922</v>
-      </c>
-      <c r="F79" s="29">
-        <v>284.76624518555798</v>
-      </c>
-      <c r="G79" s="29">
-        <v>7577.8215142893287</v>
-      </c>
-      <c r="H79" s="29">
-        <v>6241</v>
-      </c>
-      <c r="I79" s="29">
-        <v>7285.6480000000001</v>
-      </c>
-      <c r="J79" s="29">
-        <v>7138.5050792755246</v>
-      </c>
-      <c r="K79" s="29">
-        <v>6750</v>
-      </c>
-      <c r="L79" s="29">
-        <v>6600</v>
+      <c r="D79" s="35">
+        <v>6909.4209351934569</v>
+      </c>
+      <c r="E79" s="35">
+        <v>6947.6489024790953</v>
+      </c>
+      <c r="F79" s="35">
+        <v>373.67192680168262</v>
+      </c>
+      <c r="G79" s="35">
+        <v>7881.4822741985608</v>
+      </c>
+      <c r="H79" s="35">
+        <v>6202.4724848340184</v>
+      </c>
+      <c r="I79" s="35">
+        <v>7413.4070000000002</v>
+      </c>
+      <c r="J79" s="35">
+        <v>7142.5099635903789</v>
+      </c>
+      <c r="K79" s="35">
+        <v>6700</v>
+      </c>
+      <c r="L79" s="35">
+        <v>6537.8979461337876</v>
       </c>
       <c r="M79" s="20">
-        <v>37</v>
-      </c>
-      <c r="AA79" s="17"/>
-      <c r="AB79" s="18"/>
-      <c r="AC79" s="29"/>
-      <c r="AD79" s="29"/>
-      <c r="AE79" s="29"/>
-      <c r="AF79" s="29"/>
-      <c r="AG79" s="29"/>
-      <c r="AH79" s="29"/>
-      <c r="AI79" s="29"/>
-      <c r="AJ79" s="29"/>
-      <c r="AK79" s="29"/>
-      <c r="AL79" s="20"/>
-    </row>
-    <row r="80" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="80" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B80" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D80" s="28">
-        <v>7031.2834464039724</v>
-      </c>
-      <c r="E80" s="28">
-        <v>7068.4344864384357</v>
-      </c>
-      <c r="F80" s="28">
-        <v>344.48170518806791</v>
-      </c>
-      <c r="G80" s="28">
-        <v>7881.4822741985608</v>
-      </c>
-      <c r="H80" s="28">
-        <v>6485.4398714765784</v>
-      </c>
-      <c r="I80" s="28">
-        <v>7535.6360842415224</v>
-      </c>
-      <c r="J80" s="28">
-        <v>7263</v>
-      </c>
-      <c r="K80" s="28">
-        <v>6863.2801174340739</v>
-      </c>
-      <c r="L80" s="28">
-        <v>6700</v>
+      <c r="D80" s="34">
+        <v>7003.5</v>
+      </c>
+      <c r="E80" s="34">
+        <v>6900.0140682152587</v>
+      </c>
+      <c r="F80" s="34">
+        <v>411.93421828559377</v>
+      </c>
+      <c r="G80" s="34">
+        <v>7922.1678652521614</v>
+      </c>
+      <c r="H80" s="34">
+        <v>6032.3250031080106</v>
+      </c>
+      <c r="I80" s="34">
+        <v>7319.6289831497334</v>
+      </c>
+      <c r="J80" s="34">
+        <v>7138.55</v>
+      </c>
+      <c r="K80" s="34">
+        <v>6623.6497740464074</v>
+      </c>
+      <c r="L80" s="34">
+        <v>6366.2868415098465</v>
       </c>
       <c r="M80" s="5">
-        <v>37</v>
-      </c>
-      <c r="AA80" s="2"/>
-      <c r="AB80" s="3"/>
-      <c r="AC80" s="28"/>
-      <c r="AD80" s="28"/>
-      <c r="AE80" s="28"/>
-      <c r="AF80" s="28"/>
-      <c r="AG80" s="28"/>
-      <c r="AH80" s="28"/>
-      <c r="AI80" s="28"/>
-      <c r="AJ80" s="28"/>
-      <c r="AK80" s="28"/>
-      <c r="AL80" s="5"/>
-    </row>
-    <row r="81" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="81" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B81" s="17">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C81" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D81" s="29">
-        <v>7012.8821908806567</v>
-      </c>
-      <c r="E81" s="29">
-        <v>7023.3147998800478</v>
-      </c>
-      <c r="F81" s="29">
-        <v>377.82142687826661</v>
-      </c>
-      <c r="G81" s="29">
-        <v>7922.1678652521614</v>
-      </c>
-      <c r="H81" s="29">
-        <v>6032.7398046560238</v>
-      </c>
-      <c r="I81" s="29">
-        <v>7534.515281200247</v>
-      </c>
-      <c r="J81" s="29">
-        <v>7167</v>
-      </c>
-      <c r="K81" s="29">
-        <v>6782</v>
-      </c>
-      <c r="L81" s="29">
-        <v>6619.7086786653699</v>
+      <c r="D81" s="35">
+        <v>6383.2647591774148</v>
+      </c>
+      <c r="E81" s="35">
+        <v>6479.6968900817883</v>
+      </c>
+      <c r="F81" s="35">
+        <v>505.80874462731231</v>
+      </c>
+      <c r="G81" s="35">
+        <v>7937</v>
+      </c>
+      <c r="H81" s="35">
+        <v>5598</v>
+      </c>
+      <c r="I81" s="35">
+        <v>7180.3509703377631</v>
+      </c>
+      <c r="J81" s="35">
+        <v>6711.917989236219</v>
+      </c>
+      <c r="K81" s="35">
+        <v>6206.3419884151563</v>
+      </c>
+      <c r="L81" s="35">
+        <v>5799.3948328167071</v>
       </c>
       <c r="M81" s="20">
-        <v>37</v>
-      </c>
-      <c r="AA81" s="17"/>
-      <c r="AB81" s="18"/>
-      <c r="AC81" s="29"/>
-      <c r="AD81" s="29"/>
-      <c r="AE81" s="29"/>
-      <c r="AF81" s="29"/>
-      <c r="AG81" s="29"/>
-      <c r="AH81" s="29"/>
-      <c r="AI81" s="29"/>
-      <c r="AJ81" s="29"/>
-      <c r="AK81" s="29"/>
-      <c r="AL81" s="20"/>
-    </row>
-    <row r="82" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="82" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B82" s="2">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D82" s="28">
-        <v>6490</v>
-      </c>
-      <c r="E82" s="28">
-        <v>6490.6744930159512</v>
-      </c>
-      <c r="F82" s="28">
-        <v>448.29536651714511</v>
-      </c>
-      <c r="G82" s="28">
-        <v>7300</v>
-      </c>
-      <c r="H82" s="28">
-        <v>5598</v>
-      </c>
-      <c r="I82" s="28">
-        <v>7024.739216165447</v>
-      </c>
-      <c r="J82" s="28">
-        <v>6877.9534473778631</v>
-      </c>
-      <c r="K82" s="28">
-        <v>6102.3878989944169</v>
-      </c>
-      <c r="L82" s="28">
-        <v>5978.0992541318064</v>
+      <c r="D82" s="34">
+        <v>6221.3309749812915</v>
+      </c>
+      <c r="E82" s="34">
+        <v>6333.1920265412564</v>
+      </c>
+      <c r="F82" s="34">
+        <v>535.49878544135788</v>
+      </c>
+      <c r="G82" s="34">
+        <v>7464.054851280026</v>
+      </c>
+      <c r="H82" s="34">
+        <v>5292.9976039808453</v>
+      </c>
+      <c r="I82" s="34">
+        <v>7032.2098530555368</v>
+      </c>
+      <c r="J82" s="34">
+        <v>6688.2873594430639</v>
+      </c>
+      <c r="K82" s="34">
+        <v>5893.6496964159351</v>
+      </c>
+      <c r="L82" s="34">
+        <v>5708.4</v>
       </c>
       <c r="M82" s="5">
-        <v>37</v>
-      </c>
-      <c r="AA82" s="2"/>
-      <c r="AB82" s="3"/>
-      <c r="AC82" s="28"/>
-      <c r="AD82" s="28"/>
-      <c r="AE82" s="28"/>
-      <c r="AF82" s="28"/>
-      <c r="AG82" s="28"/>
-      <c r="AH82" s="28"/>
-      <c r="AI82" s="28"/>
-      <c r="AJ82" s="28"/>
-      <c r="AK82" s="28"/>
-      <c r="AL82" s="5"/>
-    </row>
-    <row r="83" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="83" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B83" s="17">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C83" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D83" s="29">
-        <v>6200</v>
-      </c>
-      <c r="E83" s="29">
-        <v>6351.5857067710613</v>
-      </c>
-      <c r="F83" s="29">
-        <v>525.49812692546493</v>
-      </c>
-      <c r="G83" s="29">
-        <v>7537.8182296339728</v>
-      </c>
-      <c r="H83" s="29">
-        <v>5498.1455859689804</v>
-      </c>
-      <c r="I83" s="29">
-        <v>7047.1790225396117</v>
-      </c>
-      <c r="J83" s="29">
-        <v>6800</v>
-      </c>
-      <c r="K83" s="29">
-        <v>5913.68</v>
-      </c>
-      <c r="L83" s="29">
-        <v>5754.8716545095131</v>
+      <c r="D83" s="35">
+        <v>6143</v>
+      </c>
+      <c r="E83" s="35">
+        <v>6106.0652465276644</v>
+      </c>
+      <c r="F83" s="35">
+        <v>572.66821097932041</v>
+      </c>
+      <c r="G83" s="35">
+        <v>7422</v>
+      </c>
+      <c r="H83" s="35">
+        <v>5000</v>
+      </c>
+      <c r="I83" s="35">
+        <v>6795.2</v>
+      </c>
+      <c r="J83" s="35">
+        <v>6440</v>
+      </c>
+      <c r="K83" s="35">
+        <v>5651.7367532053613</v>
+      </c>
+      <c r="L83" s="35">
+        <v>5382.9023919200881</v>
       </c>
       <c r="M83" s="20">
         <v>37</v>
       </c>
-      <c r="AA83" s="17"/>
-      <c r="AB83" s="18"/>
-      <c r="AC83" s="29"/>
-      <c r="AD83" s="29"/>
-      <c r="AE83" s="29"/>
-      <c r="AF83" s="29"/>
-      <c r="AG83" s="29"/>
-      <c r="AH83" s="29"/>
-      <c r="AI83" s="29"/>
-      <c r="AJ83" s="29"/>
-      <c r="AK83" s="29"/>
-      <c r="AL83" s="20"/>
-    </row>
-    <row r="84" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B84" s="2">
-        <v>46418</v>
+        <v>46446</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D84" s="28">
-        <v>6088.3095745162354</v>
-      </c>
-      <c r="E84" s="28">
-        <v>6108.2938771766421</v>
-      </c>
-      <c r="F84" s="28">
-        <v>555.93846288976488</v>
-      </c>
-      <c r="G84" s="28">
-        <v>7105.6103548315104</v>
-      </c>
-      <c r="H84" s="28">
-        <v>5000</v>
-      </c>
-      <c r="I84" s="28">
-        <v>6886.4761480270708</v>
-      </c>
-      <c r="J84" s="28">
-        <v>6500</v>
-      </c>
-      <c r="K84" s="28">
-        <v>5745.7247400592933</v>
-      </c>
-      <c r="L84" s="28">
-        <v>5427.1811893476697</v>
+      <c r="D84" s="34">
+        <v>5909.1695728265477</v>
+      </c>
+      <c r="E84" s="34">
+        <v>6005.1260938642317</v>
+      </c>
+      <c r="F84" s="34">
+        <v>583.42423023267963</v>
+      </c>
+      <c r="G84" s="34">
+        <v>7422</v>
+      </c>
+      <c r="H84" s="34">
+        <v>5100</v>
+      </c>
+      <c r="I84" s="34">
+        <v>6683.6325934915421</v>
+      </c>
+      <c r="J84" s="34">
+        <v>6323.76</v>
+      </c>
+      <c r="K84" s="34">
+        <v>5511</v>
+      </c>
+      <c r="L84" s="34">
+        <v>5336.5319364542383</v>
       </c>
       <c r="M84" s="5">
-        <v>35</v>
-      </c>
-      <c r="AA84" s="2"/>
-      <c r="AB84" s="3"/>
-      <c r="AC84" s="28"/>
-      <c r="AD84" s="28"/>
-      <c r="AE84" s="28"/>
-      <c r="AF84" s="28"/>
-      <c r="AG84" s="28"/>
-      <c r="AH84" s="28"/>
-      <c r="AI84" s="28"/>
-      <c r="AJ84" s="28"/>
-      <c r="AK84" s="28"/>
-      <c r="AL84" s="5"/>
-    </row>
-    <row r="85" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="85" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B85" s="21" t="s">
         <v>36</v>
       </c>
       <c r="C85" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D85" s="29">
-        <v>76773.020427460811</v>
-      </c>
-      <c r="E85" s="29">
-        <v>76544.543174221923</v>
-      </c>
-      <c r="F85" s="29">
-        <v>1586.9348757586049</v>
-      </c>
-      <c r="G85" s="29">
+      <c r="D85" s="35">
+        <v>75861</v>
+      </c>
+      <c r="E85" s="35">
+        <v>75916.170734400745</v>
+      </c>
+      <c r="F85" s="35">
+        <v>1666.909259268348</v>
+      </c>
+      <c r="G85" s="35">
         <v>80376</v>
       </c>
-      <c r="H85" s="29">
-        <v>73837.831692513268</v>
-      </c>
-      <c r="I85" s="29">
-        <v>78191.21854772963</v>
-      </c>
-      <c r="J85" s="29">
-        <v>77490.7112708895</v>
-      </c>
-      <c r="K85" s="29">
-        <v>75178.661705379112</v>
-      </c>
-      <c r="L85" s="29">
-        <v>74315.118910948193</v>
+      <c r="H85" s="35">
+        <v>72424.05963568583</v>
+      </c>
+      <c r="I85" s="35">
+        <v>78011.090218837504</v>
+      </c>
+      <c r="J85" s="35">
+        <v>77005</v>
+      </c>
+      <c r="K85" s="35">
+        <v>74847.557824799005</v>
+      </c>
+      <c r="L85" s="35">
+        <v>73898.940653202881</v>
       </c>
       <c r="M85" s="20">
-        <v>40</v>
-      </c>
-      <c r="AA85" s="21"/>
-      <c r="AB85" s="18"/>
-      <c r="AC85" s="29"/>
-      <c r="AD85" s="29"/>
-      <c r="AE85" s="29"/>
-      <c r="AF85" s="29"/>
-      <c r="AG85" s="29"/>
-      <c r="AH85" s="29"/>
-      <c r="AI85" s="29"/>
-      <c r="AJ85" s="29"/>
-      <c r="AK85" s="29"/>
-      <c r="AL85" s="20"/>
-    </row>
-    <row r="86" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="86" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B86" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D86" s="28">
-        <v>83025.895000000004</v>
-      </c>
-      <c r="E86" s="28">
-        <v>82702.05152977386</v>
-      </c>
-      <c r="F86" s="28">
-        <v>3138.8560718211988</v>
-      </c>
-      <c r="G86" s="28">
-        <v>90000</v>
-      </c>
-      <c r="H86" s="28">
-        <v>75262.710316640572</v>
-      </c>
-      <c r="I86" s="28">
-        <v>86434</v>
-      </c>
-      <c r="J86" s="28">
-        <v>84592.889023072203</v>
-      </c>
-      <c r="K86" s="28">
-        <v>80880.96684620966</v>
-      </c>
-      <c r="L86" s="28">
-        <v>78956.317198216188</v>
+      <c r="D86" s="34">
+        <v>82885.675000000003</v>
+      </c>
+      <c r="E86" s="34">
+        <v>82342.341538128167</v>
+      </c>
+      <c r="F86" s="34">
+        <v>3866.117937100998</v>
+      </c>
+      <c r="G86" s="34">
+        <v>93307</v>
+      </c>
+      <c r="H86" s="34">
+        <v>75262.710316640601</v>
+      </c>
+      <c r="I86" s="34">
+        <v>86591.086430483309</v>
+      </c>
+      <c r="J86" s="34">
+        <v>84395.684686176246</v>
+      </c>
+      <c r="K86" s="34">
+        <v>79503.5</v>
+      </c>
+      <c r="L86" s="34">
+        <v>77837.347000424881</v>
       </c>
       <c r="M86" s="5">
-        <v>36</v>
-      </c>
-      <c r="AA86" s="6"/>
-      <c r="AB86" s="3"/>
-      <c r="AC86" s="28"/>
-      <c r="AD86" s="28"/>
-      <c r="AE86" s="28"/>
-      <c r="AF86" s="28"/>
-      <c r="AG86" s="28"/>
-      <c r="AH86" s="28"/>
-      <c r="AI86" s="28"/>
-      <c r="AJ86" s="28"/>
-      <c r="AK86" s="28"/>
-      <c r="AL86" s="5"/>
-    </row>
-    <row r="87" spans="2:38" ht="18.75" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="87" spans="2:13" ht="18" x14ac:dyDescent="0.4">
       <c r="B87" s="9"/>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
@@ -5450,20 +4542,8 @@
       <c r="K87" s="10"/>
       <c r="L87" s="10"/>
       <c r="M87" s="10"/>
-      <c r="AA87" s="9"/>
-      <c r="AB87" s="10"/>
-      <c r="AC87" s="10"/>
-      <c r="AD87" s="10"/>
-      <c r="AE87" s="10"/>
-      <c r="AF87" s="10"/>
-      <c r="AG87" s="10"/>
-      <c r="AH87" s="10"/>
-      <c r="AI87" s="10"/>
-      <c r="AJ87" s="10"/>
-      <c r="AK87" s="10"/>
-      <c r="AL87" s="10"/>
-    </row>
-    <row r="89" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B89" s="14" t="s">
         <v>27</v>
       </c>
@@ -5478,20 +4558,8 @@
       <c r="K89" s="14"/>
       <c r="L89" s="14"/>
       <c r="M89" s="15"/>
-      <c r="AA89" s="14"/>
-      <c r="AB89" s="14"/>
-      <c r="AC89" s="14"/>
-      <c r="AD89" s="14"/>
-      <c r="AE89" s="14"/>
-      <c r="AF89" s="14"/>
-      <c r="AG89" s="14"/>
-      <c r="AH89" s="14"/>
-      <c r="AI89" s="14"/>
-      <c r="AJ89" s="14"/>
-      <c r="AK89" s="14"/>
-      <c r="AL89" s="15"/>
-    </row>
-    <row r="90" spans="2:38" ht="37.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B90" s="24" t="s">
         <v>1</v>
       </c>
@@ -5528,120 +4596,84 @@
       <c r="M90" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="AA90" s="24"/>
-      <c r="AB90" s="24"/>
-      <c r="AC90" s="24"/>
-      <c r="AD90" s="24"/>
-      <c r="AE90" s="24"/>
-      <c r="AF90" s="24"/>
-      <c r="AG90" s="24"/>
-      <c r="AH90" s="24"/>
-      <c r="AI90" s="24"/>
-      <c r="AJ90" s="24"/>
-      <c r="AK90" s="24"/>
-      <c r="AL90" s="25"/>
-    </row>
-    <row r="91" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B91" s="21" t="s">
         <v>36</v>
       </c>
       <c r="C91" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D91" s="32">
-        <v>15554.3</v>
-      </c>
-      <c r="E91" s="32">
-        <v>15261.625501435939</v>
-      </c>
-      <c r="F91" s="32">
-        <v>2106.9482637727001</v>
-      </c>
-      <c r="G91" s="32">
+      <c r="D91" s="36">
+        <v>15400</v>
+      </c>
+      <c r="E91" s="36">
+        <v>15110.155283384211</v>
+      </c>
+      <c r="F91" s="36">
+        <v>2122.8515436266839</v>
+      </c>
+      <c r="G91" s="36">
         <v>21056</v>
       </c>
-      <c r="H91" s="32">
+      <c r="H91" s="36">
         <v>9000</v>
       </c>
-      <c r="I91" s="32">
-        <v>17721.657999999999</v>
-      </c>
-      <c r="J91" s="32">
-        <v>15966.25</v>
-      </c>
-      <c r="K91" s="32">
-        <v>14425</v>
-      </c>
-      <c r="L91" s="32">
-        <v>12710.601251209309</v>
+      <c r="I91" s="36">
+        <v>17481.810000000001</v>
+      </c>
+      <c r="J91" s="36">
+        <v>16000</v>
+      </c>
+      <c r="K91" s="36">
+        <v>14200</v>
+      </c>
+      <c r="L91" s="36">
+        <v>12550.9822856219</v>
       </c>
       <c r="M91" s="20">
-        <v>40</v>
-      </c>
-      <c r="AA91" s="21"/>
-      <c r="AB91" s="18"/>
-      <c r="AC91" s="32"/>
-      <c r="AD91" s="32"/>
-      <c r="AE91" s="32"/>
-      <c r="AF91" s="32"/>
-      <c r="AG91" s="32"/>
-      <c r="AH91" s="32"/>
-      <c r="AI91" s="32"/>
-      <c r="AJ91" s="32"/>
-      <c r="AK91" s="32"/>
-      <c r="AL91" s="20"/>
-    </row>
-    <row r="92" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="92" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B92" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D92" s="33">
-        <v>19307</v>
-      </c>
-      <c r="E92" s="33">
-        <v>18536.880757174531</v>
-      </c>
-      <c r="F92" s="33">
-        <v>3147.7105999325199</v>
-      </c>
-      <c r="G92" s="33">
-        <v>22542.95823806425</v>
-      </c>
-      <c r="H92" s="33">
+      <c r="D92" s="37">
+        <v>18468.90633894872</v>
+      </c>
+      <c r="E92" s="37">
+        <v>18241.138597365571</v>
+      </c>
+      <c r="F92" s="37">
+        <v>3016.0170022436291</v>
+      </c>
+      <c r="G92" s="37">
+        <v>22200</v>
+      </c>
+      <c r="H92" s="37">
         <v>5000</v>
       </c>
-      <c r="I92" s="33">
-        <v>21160.290289536679</v>
-      </c>
-      <c r="J92" s="33">
-        <v>20356.410952458729</v>
-      </c>
-      <c r="K92" s="33">
-        <v>17662.716754113571</v>
-      </c>
-      <c r="L92" s="33">
-        <v>15400</v>
+      <c r="I92" s="37">
+        <v>21092</v>
+      </c>
+      <c r="J92" s="37">
+        <v>19872.27891352486</v>
+      </c>
+      <c r="K92" s="37">
+        <v>17119.720278999561</v>
+      </c>
+      <c r="L92" s="37">
+        <v>15500</v>
       </c>
       <c r="M92" s="5">
-        <v>35</v>
-      </c>
-      <c r="AA92" s="6"/>
-      <c r="AB92" s="3"/>
-      <c r="AC92" s="33"/>
-      <c r="AD92" s="33"/>
-      <c r="AE92" s="33"/>
-      <c r="AF92" s="33"/>
-      <c r="AG92" s="33"/>
-      <c r="AH92" s="33"/>
-      <c r="AI92" s="33"/>
-      <c r="AJ92" s="33"/>
-      <c r="AK92" s="33"/>
-      <c r="AL92" s="5"/>
-    </row>
-    <row r="93" spans="2:38" ht="18.75" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="93" spans="2:13" ht="18" x14ac:dyDescent="0.4">
       <c r="B93" s="9"/>
       <c r="C93" s="10"/>
       <c r="D93" s="10"/>
@@ -5654,20 +4686,8 @@
       <c r="K93" s="10"/>
       <c r="L93" s="10"/>
       <c r="M93" s="10"/>
-      <c r="AA93" s="9"/>
-      <c r="AB93" s="10"/>
-      <c r="AC93" s="10"/>
-      <c r="AD93" s="10"/>
-      <c r="AE93" s="10"/>
-      <c r="AF93" s="10"/>
-      <c r="AG93" s="10"/>
-      <c r="AH93" s="10"/>
-      <c r="AI93" s="10"/>
-      <c r="AJ93" s="10"/>
-      <c r="AK93" s="10"/>
-      <c r="AL93" s="10"/>
-    </row>
-    <row r="95" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B95" s="14" t="s">
         <v>29</v>
       </c>
@@ -5682,20 +4702,8 @@
       <c r="K95" s="14"/>
       <c r="L95" s="14"/>
       <c r="M95" s="15"/>
-      <c r="AA95" s="14"/>
-      <c r="AB95" s="14"/>
-      <c r="AC95" s="14"/>
-      <c r="AD95" s="14"/>
-      <c r="AE95" s="14"/>
-      <c r="AF95" s="14"/>
-      <c r="AG95" s="14"/>
-      <c r="AH95" s="14"/>
-      <c r="AI95" s="14"/>
-      <c r="AJ95" s="14"/>
-      <c r="AK95" s="14"/>
-      <c r="AL95" s="15"/>
-    </row>
-    <row r="96" spans="2:38" ht="37.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B96" s="24" t="s">
         <v>1</v>
       </c>
@@ -5732,20 +4740,8 @@
       <c r="M96" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="AA96" s="24"/>
-      <c r="AB96" s="24"/>
-      <c r="AC96" s="24"/>
-      <c r="AD96" s="24"/>
-      <c r="AE96" s="24"/>
-      <c r="AF96" s="24"/>
-      <c r="AG96" s="24"/>
-      <c r="AH96" s="24"/>
-      <c r="AI96" s="24"/>
-      <c r="AJ96" s="24"/>
-      <c r="AK96" s="24"/>
-      <c r="AL96" s="25"/>
-    </row>
-    <row r="97" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B97" s="7" t="s">
         <v>42</v>
       </c>
@@ -5756,46 +4752,34 @@
         <v>7.7</v>
       </c>
       <c r="E97" s="4">
-        <v>7.6931282041086746</v>
+        <v>7.701499446225883</v>
       </c>
       <c r="F97" s="4">
-        <v>0.26097067207673619</v>
+        <v>0.22528575748352189</v>
       </c>
       <c r="G97" s="4">
-        <v>8.2286757743888757</v>
+        <v>8.23</v>
       </c>
       <c r="H97" s="4">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="I97" s="4">
-        <v>8.066966897073252</v>
+        <v>8.0176644864634472</v>
       </c>
       <c r="J97" s="4">
-        <v>7.83</v>
+        <v>7.8</v>
       </c>
       <c r="K97" s="4">
-        <v>7.5068461061614924</v>
+        <v>7.5075000000000003</v>
       </c>
       <c r="L97" s="4">
-        <v>7.4</v>
+        <v>7.4144226214473887</v>
       </c>
       <c r="M97" s="8">
-        <v>35</v>
-      </c>
-      <c r="AA97" s="7"/>
-      <c r="AB97" s="3"/>
-      <c r="AC97" s="4"/>
-      <c r="AD97" s="4"/>
-      <c r="AE97" s="4"/>
-      <c r="AF97" s="4"/>
-      <c r="AG97" s="4"/>
-      <c r="AH97" s="4"/>
-      <c r="AI97" s="4"/>
-      <c r="AJ97" s="4"/>
-      <c r="AK97" s="4"/>
-      <c r="AL97" s="8"/>
-    </row>
-    <row r="98" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="98" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B98" s="17" t="s">
         <v>44</v>
       </c>
@@ -5803,49 +4787,37 @@
         <v>30</v>
       </c>
       <c r="D98" s="19">
-        <v>7.2618775758281311</v>
+        <v>7.3</v>
       </c>
       <c r="E98" s="19">
-        <v>7.2629977374112569</v>
+        <v>7.3222080492577239</v>
       </c>
       <c r="F98" s="19">
-        <v>0.49619959081075188</v>
+        <v>0.47776707946957658</v>
       </c>
       <c r="G98" s="19">
         <v>8.6</v>
       </c>
       <c r="H98" s="19">
-        <v>6.4</v>
+        <v>6.53</v>
       </c>
       <c r="I98" s="19">
-        <v>7.7489999999999997</v>
+        <v>7.8680000000000003</v>
       </c>
       <c r="J98" s="19">
-        <v>7.5749999999999993</v>
+        <v>7.6</v>
       </c>
       <c r="K98" s="19">
-        <v>6.9250000000000007</v>
+        <v>6.95</v>
       </c>
       <c r="L98" s="19">
-        <v>6.6116457709346621</v>
+        <v>6.781086896752555</v>
       </c>
       <c r="M98" s="20">
-        <v>34</v>
-      </c>
-      <c r="AA98" s="17"/>
-      <c r="AB98" s="18"/>
-      <c r="AC98" s="19"/>
-      <c r="AD98" s="19"/>
-      <c r="AE98" s="19"/>
-      <c r="AF98" s="19"/>
-      <c r="AG98" s="19"/>
-      <c r="AH98" s="19"/>
-      <c r="AI98" s="19"/>
-      <c r="AJ98" s="19"/>
-      <c r="AK98" s="19"/>
-      <c r="AL98" s="20"/>
-    </row>
-    <row r="99" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="99" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B99" s="6" t="s">
         <v>45</v>
       </c>
@@ -5856,46 +4828,34 @@
         <v>7.5</v>
       </c>
       <c r="E99" s="4">
-        <v>7.5557198905846796</v>
+        <v>7.5685020130157712</v>
       </c>
       <c r="F99" s="4">
-        <v>0.37399958307768139</v>
+        <v>0.38518189869358482</v>
       </c>
       <c r="G99" s="4">
         <v>8.6999999999999993</v>
       </c>
       <c r="H99" s="4">
-        <v>7</v>
+        <v>6.8000000000000007</v>
       </c>
       <c r="I99" s="4">
         <v>8</v>
       </c>
       <c r="J99" s="4">
-        <v>7.6998097598423136</v>
+        <v>7.72</v>
       </c>
       <c r="K99" s="4">
-        <v>7.3100441038012036</v>
+        <v>7.31</v>
       </c>
       <c r="L99" s="4">
         <v>7.2</v>
       </c>
       <c r="M99" s="5">
-        <v>36</v>
-      </c>
-      <c r="AA99" s="6"/>
-      <c r="AB99" s="3"/>
-      <c r="AC99" s="4"/>
-      <c r="AD99" s="4"/>
-      <c r="AE99" s="4"/>
-      <c r="AF99" s="4"/>
-      <c r="AG99" s="4"/>
-      <c r="AH99" s="4"/>
-      <c r="AI99" s="4"/>
-      <c r="AJ99" s="4"/>
-      <c r="AK99" s="4"/>
-      <c r="AL99" s="5"/>
-    </row>
-    <row r="100" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="100" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B100" s="21" t="s">
         <v>36</v>
       </c>
@@ -5906,46 +4866,34 @@
         <v>7.5</v>
       </c>
       <c r="E100" s="19">
-        <v>7.5557198905846796</v>
+        <v>7.5685020130157712</v>
       </c>
       <c r="F100" s="19">
-        <v>0.37399958307768139</v>
+        <v>0.38518189869358482</v>
       </c>
       <c r="G100" s="19">
         <v>8.6999999999999993</v>
       </c>
       <c r="H100" s="19">
-        <v>7</v>
+        <v>6.8000000000000007</v>
       </c>
       <c r="I100" s="19">
         <v>8</v>
       </c>
       <c r="J100" s="19">
-        <v>7.6998097598423136</v>
+        <v>7.72</v>
       </c>
       <c r="K100" s="19">
-        <v>7.3100441038012036</v>
+        <v>7.31</v>
       </c>
       <c r="L100" s="19">
         <v>7.2</v>
       </c>
       <c r="M100" s="20">
-        <v>36</v>
-      </c>
-      <c r="AA100" s="21"/>
-      <c r="AB100" s="18"/>
-      <c r="AC100" s="19"/>
-      <c r="AD100" s="19"/>
-      <c r="AE100" s="19"/>
-      <c r="AF100" s="19"/>
-      <c r="AG100" s="19"/>
-      <c r="AH100" s="19"/>
-      <c r="AI100" s="19"/>
-      <c r="AJ100" s="19"/>
-      <c r="AK100" s="19"/>
-      <c r="AL100" s="20"/>
-    </row>
-    <row r="101" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="101" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B101" s="6" t="s">
         <v>37</v>
       </c>
@@ -5953,49 +4901,37 @@
         <v>43</v>
       </c>
       <c r="D101" s="4">
-        <v>7.4671161354062674</v>
+        <v>7.5</v>
       </c>
       <c r="E101" s="4">
-        <v>7.514391658035918</v>
+        <v>7.5564051107672512</v>
       </c>
       <c r="F101" s="4">
-        <v>0.48972191098902362</v>
+        <v>0.58015819169782312</v>
       </c>
       <c r="G101" s="4">
         <v>8.5</v>
       </c>
       <c r="H101" s="4">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="I101" s="4">
-        <v>8.16</v>
+        <v>8.3600000000000012</v>
       </c>
       <c r="J101" s="4">
-        <v>7.8563429956464184</v>
+        <v>8</v>
       </c>
       <c r="K101" s="4">
-        <v>7.2000000000000011</v>
+        <v>7.2</v>
       </c>
       <c r="L101" s="4">
-        <v>7.04</v>
+        <v>7</v>
       </c>
       <c r="M101" s="5">
         <v>35</v>
       </c>
-      <c r="AA101" s="6"/>
-      <c r="AB101" s="3"/>
-      <c r="AC101" s="4"/>
-      <c r="AD101" s="4"/>
-      <c r="AE101" s="4"/>
-      <c r="AF101" s="4"/>
-      <c r="AG101" s="4"/>
-      <c r="AH101" s="4"/>
-      <c r="AI101" s="4"/>
-      <c r="AJ101" s="4"/>
-      <c r="AK101" s="4"/>
-      <c r="AL101" s="5"/>
-    </row>
-    <row r="102" spans="2:38" ht="18.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="2:13" ht="18" x14ac:dyDescent="0.4">
       <c r="B102" s="9"/>
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
@@ -6008,20 +4944,8 @@
       <c r="K102" s="9"/>
       <c r="L102" s="9"/>
       <c r="M102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="9"/>
-      <c r="AE102" s="9"/>
-      <c r="AF102" s="9"/>
-      <c r="AG102" s="9"/>
-      <c r="AH102" s="9"/>
-      <c r="AI102" s="9"/>
-      <c r="AJ102" s="9"/>
-      <c r="AK102" s="9"/>
-      <c r="AL102" s="9"/>
-    </row>
-    <row r="104" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B104" s="14" t="s">
         <v>32</v>
       </c>
@@ -6036,20 +4960,8 @@
       <c r="K104" s="14"/>
       <c r="L104" s="14"/>
       <c r="M104" s="15"/>
-      <c r="AA104" s="14"/>
-      <c r="AB104" s="14"/>
-      <c r="AC104" s="14"/>
-      <c r="AD104" s="14"/>
-      <c r="AE104" s="14"/>
-      <c r="AF104" s="14"/>
-      <c r="AG104" s="14"/>
-      <c r="AH104" s="14"/>
-      <c r="AI104" s="14"/>
-      <c r="AJ104" s="14"/>
-      <c r="AK104" s="14"/>
-      <c r="AL104" s="15"/>
-    </row>
-    <row r="105" spans="2:38" ht="37.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B105" s="24" t="s">
         <v>1</v>
       </c>
@@ -6086,20 +4998,8 @@
       <c r="M105" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="AA105" s="24"/>
-      <c r="AB105" s="24"/>
-      <c r="AC105" s="24"/>
-      <c r="AD105" s="24"/>
-      <c r="AE105" s="24"/>
-      <c r="AF105" s="24"/>
-      <c r="AG105" s="24"/>
-      <c r="AH105" s="24"/>
-      <c r="AI105" s="24"/>
-      <c r="AJ105" s="24"/>
-      <c r="AK105" s="24"/>
-      <c r="AL105" s="25"/>
-    </row>
-    <row r="106" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B106" s="21" t="s">
         <v>42</v>
       </c>
@@ -6107,49 +5007,37 @@
         <v>33</v>
       </c>
       <c r="D106" s="19">
-        <v>-0.36482277121374629</v>
+        <v>-0.9</v>
       </c>
       <c r="E106" s="19">
-        <v>-0.16485186429756171</v>
+        <v>-0.76799467324208748</v>
       </c>
       <c r="F106" s="19">
-        <v>0.6446639540341722</v>
+        <v>0.2346433118568825</v>
       </c>
       <c r="G106" s="19">
-        <v>1.3</v>
+        <v>-0.13524694967358419</v>
       </c>
       <c r="H106" s="19">
-        <v>-1.2</v>
+        <v>-0.99105533016186076</v>
       </c>
       <c r="I106" s="19">
-        <v>0.78149180291177556</v>
+        <v>-0.4</v>
       </c>
       <c r="J106" s="19">
-        <v>0.375</v>
+        <v>-0.58499999999999996</v>
       </c>
       <c r="K106" s="19">
-        <v>-0.67913528710848503</v>
+        <v>-0.93</v>
       </c>
       <c r="L106" s="19">
-        <v>-0.81246464867356938</v>
+        <v>-0.9308567507125165</v>
       </c>
       <c r="M106" s="20">
-        <v>38</v>
-      </c>
-      <c r="AA106" s="21"/>
-      <c r="AB106" s="18"/>
-      <c r="AC106" s="19"/>
-      <c r="AD106" s="19"/>
-      <c r="AE106" s="19"/>
-      <c r="AF106" s="19"/>
-      <c r="AG106" s="19"/>
-      <c r="AH106" s="19"/>
-      <c r="AI106" s="19"/>
-      <c r="AJ106" s="19"/>
-      <c r="AK106" s="19"/>
-      <c r="AL106" s="20"/>
-    </row>
-    <row r="107" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="107" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B107" s="6" t="s">
         <v>44</v>
       </c>
@@ -6157,49 +5045,37 @@
         <v>33</v>
       </c>
       <c r="D107" s="4">
-        <v>0.99029807479322729</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E107" s="4">
-        <v>0.99558242362588045</v>
+        <v>1.081820380971269</v>
       </c>
       <c r="F107" s="4">
-        <v>0.58899383197798394</v>
+        <v>0.40890717883975009</v>
       </c>
       <c r="G107" s="4">
-        <v>2.4298719384043821</v>
+        <v>2</v>
       </c>
       <c r="H107" s="4">
-        <v>-0.41780837525143832</v>
+        <v>0</v>
       </c>
       <c r="I107" s="4">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="J107" s="4">
-        <v>1.3461916558747979</v>
+        <v>1.30322524247636</v>
       </c>
       <c r="K107" s="4">
-        <v>0.70716759170165955</v>
+        <v>0.75835351859631717</v>
       </c>
       <c r="L107" s="4">
-        <v>0.26500000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="M107" s="5">
-        <v>38</v>
-      </c>
-      <c r="AA107" s="6"/>
-      <c r="AB107" s="3"/>
-      <c r="AC107" s="4"/>
-      <c r="AD107" s="4"/>
-      <c r="AE107" s="4"/>
-      <c r="AF107" s="4"/>
-      <c r="AG107" s="4"/>
-      <c r="AH107" s="4"/>
-      <c r="AI107" s="4"/>
-      <c r="AJ107" s="4"/>
-      <c r="AK107" s="4"/>
-      <c r="AL107" s="5"/>
-    </row>
-    <row r="108" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="108" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B108" s="21" t="s">
         <v>45</v>
       </c>
@@ -6207,49 +5083,37 @@
         <v>33</v>
       </c>
       <c r="D108" s="19">
-        <v>0.95649339143928302</v>
+        <v>1.3</v>
       </c>
       <c r="E108" s="19">
-        <v>1.083483637838178</v>
+        <v>1.27095769483229</v>
       </c>
       <c r="F108" s="19">
-        <v>0.56159124498069291</v>
+        <v>0.60336504329056084</v>
       </c>
       <c r="G108" s="19">
-        <v>2.38418147629387</v>
+        <v>2.5175166669416442</v>
       </c>
       <c r="H108" s="19">
-        <v>-0.1</v>
+        <v>5.5301646023986351E-2</v>
       </c>
       <c r="I108" s="19">
-        <v>1.8513543569747239</v>
+        <v>2.028003366555533</v>
       </c>
       <c r="J108" s="19">
-        <v>1.363932439748119</v>
+        <v>1.631585356498279</v>
       </c>
       <c r="K108" s="19">
-        <v>0.8</v>
+        <v>0.90500000000000003</v>
       </c>
       <c r="L108" s="19">
-        <v>0.37234335976756833</v>
+        <v>0.38951211389773183</v>
       </c>
       <c r="M108" s="20">
-        <v>38</v>
-      </c>
-      <c r="AA108" s="21"/>
-      <c r="AB108" s="18"/>
-      <c r="AC108" s="19"/>
-      <c r="AD108" s="19"/>
-      <c r="AE108" s="19"/>
-      <c r="AF108" s="19"/>
-      <c r="AG108" s="19"/>
-      <c r="AH108" s="19"/>
-      <c r="AI108" s="19"/>
-      <c r="AJ108" s="19"/>
-      <c r="AK108" s="19"/>
-      <c r="AL108" s="20"/>
-    </row>
-    <row r="109" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="109" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B109" s="6" t="s">
         <v>36</v>
       </c>
@@ -6257,49 +5121,37 @@
         <v>34</v>
       </c>
       <c r="D109" s="4">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="E109" s="4">
-        <v>2.514935008320895</v>
+        <v>2.1412564619463721</v>
       </c>
       <c r="F109" s="4">
-        <v>0.60005513319056747</v>
+        <v>0.43968173434670438</v>
       </c>
       <c r="G109" s="4">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="H109" s="4">
-        <v>0.93</v>
+        <v>1.37</v>
       </c>
       <c r="I109" s="4">
-        <v>3</v>
+        <v>2.7834687699638292</v>
       </c>
       <c r="J109" s="4">
-        <v>2.8810229838139039</v>
+        <v>2.346512924194943</v>
       </c>
       <c r="K109" s="4">
-        <v>2.1475</v>
+        <v>1.9</v>
       </c>
       <c r="L109" s="4">
-        <v>1.8130119756029099</v>
+        <v>1.5620000000000001</v>
       </c>
       <c r="M109" s="5">
-        <v>42</v>
-      </c>
-      <c r="AA109" s="6"/>
-      <c r="AB109" s="3"/>
-      <c r="AC109" s="4"/>
-      <c r="AD109" s="4"/>
-      <c r="AE109" s="4"/>
-      <c r="AF109" s="4"/>
-      <c r="AG109" s="4"/>
-      <c r="AH109" s="4"/>
-      <c r="AI109" s="4"/>
-      <c r="AJ109" s="4"/>
-      <c r="AK109" s="4"/>
-      <c r="AL109" s="5"/>
-    </row>
-    <row r="110" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="110" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B110" s="21" t="s">
         <v>37</v>
       </c>
@@ -6307,49 +5159,37 @@
         <v>34</v>
       </c>
       <c r="D110" s="19">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="E110" s="19">
-        <v>2.9323098688389959</v>
+        <v>2.7419813229171499</v>
       </c>
       <c r="F110" s="19">
-        <v>0.58464546547681007</v>
+        <v>0.54537485609929581</v>
       </c>
       <c r="G110" s="19">
-        <v>4.5037547763228298</v>
+        <v>4</v>
       </c>
       <c r="H110" s="19">
-        <v>1.9</v>
+        <v>0.94</v>
       </c>
       <c r="I110" s="19">
-        <v>3.92</v>
+        <v>3.37</v>
       </c>
       <c r="J110" s="19">
-        <v>3.1</v>
+        <v>3.0044876002870091</v>
       </c>
       <c r="K110" s="19">
-        <v>2.5688768917180398</v>
+        <v>2.5</v>
       </c>
       <c r="L110" s="19">
-        <v>2.2509193625893871</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="M110" s="20">
-        <v>39</v>
-      </c>
-      <c r="AA110" s="21"/>
-      <c r="AB110" s="18"/>
-      <c r="AC110" s="19"/>
-      <c r="AD110" s="19"/>
-      <c r="AE110" s="19"/>
-      <c r="AF110" s="19"/>
-      <c r="AG110" s="19"/>
-      <c r="AH110" s="19"/>
-      <c r="AI110" s="19"/>
-      <c r="AJ110" s="19"/>
-      <c r="AK110" s="19"/>
-      <c r="AL110" s="20"/>
-    </row>
-    <row r="111" spans="2:38" ht="18.75" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="111" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B111" s="6" t="s">
         <v>38</v>
       </c>
@@ -6360,10 +5200,10 @@
         <v>3</v>
       </c>
       <c r="E111" s="4">
-        <v>3.0139051176356668</v>
+        <v>3.0005932541257039</v>
       </c>
       <c r="F111" s="4">
-        <v>0.6177350891627198</v>
+        <v>0.60641118778913572</v>
       </c>
       <c r="G111" s="4">
         <v>5</v>
@@ -6372,34 +5212,22 @@
         <v>2</v>
       </c>
       <c r="I111" s="4">
-        <v>3.698608495568926</v>
+        <v>3.7</v>
       </c>
       <c r="J111" s="4">
-        <v>3.2872526117354122</v>
+        <v>3.2853323328990971</v>
       </c>
       <c r="K111" s="4">
-        <v>2.7245603446666529</v>
+        <v>2.5455452631462561</v>
       </c>
       <c r="L111" s="4">
-        <v>2.26285990933181</v>
+        <v>2.35</v>
       </c>
       <c r="M111" s="5">
-        <v>35</v>
-      </c>
-      <c r="AA111" s="6"/>
-      <c r="AB111" s="3"/>
-      <c r="AC111" s="4"/>
-      <c r="AD111" s="4"/>
-      <c r="AE111" s="4"/>
-      <c r="AF111" s="4"/>
-      <c r="AG111" s="4"/>
-      <c r="AH111" s="4"/>
-      <c r="AI111" s="4"/>
-      <c r="AJ111" s="4"/>
-      <c r="AK111" s="4"/>
-      <c r="AL111" s="5"/>
-    </row>
-    <row r="112" spans="2:38" ht="18.75" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="112" spans="2:13" ht="18" x14ac:dyDescent="0.4">
       <c r="B112" s="9" t="s">
         <v>51</v>
       </c>
@@ -6414,18 +5242,6 @@
       <c r="K112" s="10"/>
       <c r="L112" s="10"/>
       <c r="M112" s="10"/>
-      <c r="AA112" s="9"/>
-      <c r="AB112" s="10"/>
-      <c r="AC112" s="10"/>
-      <c r="AD112" s="10"/>
-      <c r="AE112" s="10"/>
-      <c r="AF112" s="10"/>
-      <c r="AG112" s="10"/>
-      <c r="AH112" s="10"/>
-      <c r="AI112" s="10"/>
-      <c r="AJ112" s="10"/>
-      <c r="AK112" s="10"/>
-      <c r="AL112" s="10"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -6441,24 +5257,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{130CD0D4-3FB8-4B56-A8AD-D1A48CBBBA0B}">
-  <sheetPr codeName="Hoja3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41D6261-19CD-43AD-85D2-2EC42C1283D9}">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:M99"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:M97"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" style="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" style="1" customWidth="1"/>
-    <col min="9" max="12" width="14.42578125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="18.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.81640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.453125" style="1" customWidth="1"/>
+    <col min="6" max="7" width="14.453125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.453125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="14.453125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="18.453125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="11" t="s">
         <v>52</v>
       </c>
@@ -6474,25 +5290,25 @@
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
     </row>
-    <row r="3" spans="2:13" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" ht="20.5" x14ac:dyDescent="0.35">
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
       <c r="L4" s="12"/>
       <c r="M4" s="13"/>
     </row>
-    <row r="5" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="14" t="s">
         <v>0</v>
       </c>
@@ -6508,7 +5324,7 @@
       <c r="L5" s="14"/>
       <c r="M5" s="15"/>
     </row>
-    <row r="6" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B6" s="16" t="s">
         <v>1</v>
       </c>
@@ -6546,273 +5362,273 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B7" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="4">
-        <v>1.909055504108458</v>
+        <v>1.7164373066764551</v>
       </c>
       <c r="E7" s="4">
-        <v>1.945277520542293</v>
+        <v>1.7</v>
       </c>
       <c r="F7" s="4">
-        <v>8.0501683771755456E-2</v>
+        <v>0.11471833131256701</v>
       </c>
       <c r="G7" s="4">
         <v>2</v>
       </c>
       <c r="H7" s="4">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="I7" s="4">
-        <v>2</v>
+        <v>1.7929999999999999</v>
       </c>
       <c r="J7" s="4">
-        <v>1.95</v>
+        <v>1.7375</v>
       </c>
       <c r="K7" s="4">
-        <v>1.825</v>
+        <v>1.6625000000000001</v>
       </c>
       <c r="L7" s="4">
-        <v>1.8</v>
+        <v>1.6029357600880949</v>
       </c>
       <c r="M7" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B8" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="19">
-        <v>1.7452222151306029</v>
+        <v>1.830672300066599</v>
       </c>
       <c r="E8" s="19">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="F8" s="19">
-        <v>0.1306342451664084</v>
+        <v>0.11657733467014519</v>
       </c>
       <c r="G8" s="19">
-        <v>1.9122221513060349</v>
+        <v>2</v>
       </c>
       <c r="H8" s="19">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="I8" s="19">
-        <v>1.9012222151306031</v>
+        <v>1.964811758058252</v>
       </c>
       <c r="J8" s="19">
-        <v>1.8374999999999999</v>
+        <v>1.9143657854509499</v>
       </c>
       <c r="K8" s="19">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="L8" s="19">
-        <v>1.617</v>
+        <v>1.726</v>
       </c>
       <c r="M8" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="4">
-        <v>1.758725300233237</v>
+        <v>1.757933255150455</v>
       </c>
       <c r="E9" s="4">
-        <v>1.75</v>
+        <v>1.7549999999999999</v>
       </c>
       <c r="F9" s="4">
-        <v>0.17078971412376481</v>
+        <v>0.1213501273859801</v>
       </c>
       <c r="G9" s="4">
-        <v>2.04</v>
+        <v>1.914492656979345</v>
       </c>
       <c r="H9" s="4">
         <v>1.5</v>
       </c>
       <c r="I9" s="4">
-        <v>1.9590000000000001</v>
+        <v>1.901449265697934</v>
       </c>
       <c r="J9" s="4">
-        <v>1.872939751749277</v>
+        <v>1.8337099736313021</v>
       </c>
       <c r="K9" s="4">
-        <v>1.625</v>
+        <v>1.7</v>
       </c>
       <c r="L9" s="4">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="M9" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B10" s="17">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="19">
-        <v>1.6778327653828771</v>
+        <v>1.6665636935768131</v>
       </c>
       <c r="E10" s="19">
-        <v>1.65</v>
+        <v>1.694846750812379</v>
       </c>
       <c r="F10" s="19">
-        <v>0.1668286571685047</v>
+        <v>9.5557167955330841E-2</v>
       </c>
       <c r="G10" s="19">
-        <v>1.9383276538287659</v>
+        <v>1.8</v>
       </c>
       <c r="H10" s="19">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="I10" s="19">
-        <v>1.894832765382876</v>
+        <v>1.7909999999999999</v>
       </c>
       <c r="J10" s="19">
-        <v>1.8125</v>
+        <v>1.711957575607524</v>
       </c>
       <c r="K10" s="19">
-        <v>1.5249999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="L10" s="19">
-        <v>1.5</v>
+        <v>1.5469999999999999</v>
       </c>
       <c r="M10" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="4">
-        <v>1.64582308738359</v>
+        <v>1.7649228010986191</v>
       </c>
       <c r="E11" s="4">
-        <v>1.605</v>
+        <v>1.712241005208667</v>
       </c>
       <c r="F11" s="4">
-        <v>0.14335100806957751</v>
+        <v>0.19797072458150961</v>
       </c>
       <c r="G11" s="4">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="H11" s="4">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="I11" s="4">
-        <v>1.81</v>
+        <v>2.004</v>
       </c>
       <c r="J11" s="4">
-        <v>1.744557718458974</v>
+        <v>1.9650000000000001</v>
       </c>
       <c r="K11" s="4">
-        <v>1.5249999999999999</v>
+        <v>1.59605950042664</v>
       </c>
       <c r="L11" s="4">
-        <v>1.4970000000000001</v>
+        <v>1.577</v>
       </c>
       <c r="M11" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B12" s="17">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="19">
-        <v>1.77514548325473</v>
+        <v>1.613139902696112</v>
       </c>
       <c r="E12" s="19">
-        <v>1.7749999999999999</v>
+        <v>1.58</v>
       </c>
       <c r="F12" s="19">
-        <v>0.2095808763005311</v>
+        <v>0.18961789959594749</v>
       </c>
       <c r="G12" s="19">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="H12" s="19">
-        <v>1.5</v>
+        <v>1.253616604513502</v>
       </c>
       <c r="I12" s="19">
-        <v>2.0459999999999998</v>
+        <v>1.8129999999999999</v>
       </c>
       <c r="J12" s="19">
-        <v>1.8975</v>
+        <v>1.735836816835715</v>
       </c>
       <c r="K12" s="19">
-        <v>1.6153637081368259</v>
+        <v>1.5149999999999999</v>
       </c>
       <c r="L12" s="19">
-        <v>1.5089999999999999</v>
+        <v>1.47536166045135</v>
       </c>
       <c r="M12" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
-        <v>46418</v>
+        <v>46446</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="4">
-        <v>1.7110060298667411</v>
+        <v>1.6202540552736111</v>
       </c>
       <c r="E13" s="4">
-        <v>1.7</v>
+        <v>1.575</v>
       </c>
       <c r="F13" s="4">
-        <v>0.2472736505907841</v>
+        <v>0.17142491621940931</v>
       </c>
       <c r="G13" s="4">
-        <v>2.2999999999999998</v>
+        <v>2</v>
       </c>
       <c r="H13" s="4">
-        <v>1.5</v>
+        <v>1.4277845390462001</v>
       </c>
       <c r="I13" s="4">
-        <v>1.931</v>
+        <v>1.82</v>
       </c>
       <c r="J13" s="4">
-        <v>1.762545224000557</v>
+        <v>1.676189003422478</v>
       </c>
       <c r="K13" s="4">
-        <v>1.5075000000000001</v>
+        <v>1.5049999999999999</v>
       </c>
       <c r="L13" s="4">
-        <v>1.5</v>
+        <v>1.4927784539046201</v>
       </c>
       <c r="M13" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B14" s="17" t="s">
         <v>14</v>
       </c>
@@ -6820,37 +5636,37 @@
         <v>47</v>
       </c>
       <c r="D14" s="19">
-        <v>21.385899376768201</v>
+        <v>21.29481854983155</v>
       </c>
       <c r="E14" s="19">
-        <v>21.649675394879651</v>
+        <v>20.8</v>
       </c>
       <c r="F14" s="19">
-        <v>2.298236641761513</v>
+        <v>2.0352105885544489</v>
       </c>
       <c r="G14" s="19">
-        <v>24.531727757926909</v>
+        <v>24.28730827263168</v>
       </c>
       <c r="H14" s="19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I14" s="19">
-        <v>23.963172775792689</v>
+        <v>23.695730827263169</v>
       </c>
       <c r="J14" s="19">
-        <v>22.77033242073524</v>
+        <v>23.010939245098569</v>
       </c>
       <c r="K14" s="19">
-        <v>20.102499999999999</v>
+        <v>19.89</v>
       </c>
       <c r="L14" s="19">
-        <v>18.981853385845071</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="M14" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
         <v>36</v>
       </c>
@@ -6858,37 +5674,37 @@
         <v>16</v>
       </c>
       <c r="D15" s="4">
-        <v>29.65260639977593</v>
+        <v>30.161089757872752</v>
       </c>
       <c r="E15" s="4">
-        <v>29.918046643009671</v>
+        <v>30.174773745908919</v>
       </c>
       <c r="F15" s="4">
-        <v>0.78550301418302748</v>
+        <v>0.4155314169513753</v>
       </c>
       <c r="G15" s="4">
-        <v>30.4021147952839</v>
+        <v>30.7</v>
       </c>
       <c r="H15" s="4">
-        <v>28.28</v>
+        <v>29.57</v>
       </c>
       <c r="I15" s="4">
-        <v>30.400211479528391</v>
+        <v>30.7</v>
       </c>
       <c r="J15" s="4">
-        <v>30.2679278742511</v>
+        <v>30.464722519904139</v>
       </c>
       <c r="K15" s="4">
-        <v>29.080988021030311</v>
+        <v>29.893790045278131</v>
       </c>
       <c r="L15" s="4">
-        <v>28.568000000000001</v>
+        <v>29.597000000000001</v>
       </c>
       <c r="M15" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="14" t="s">
         <v>18</v>
       </c>
@@ -6904,7 +5720,7 @@
       <c r="L18" s="14"/>
       <c r="M18" s="15"/>
     </row>
-    <row r="19" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B19" s="16" t="s">
         <v>1</v>
       </c>
@@ -6942,273 +5758,273 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B20" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="4">
-        <v>1.772517225229193</v>
+        <v>1.636722382258438</v>
       </c>
       <c r="E20" s="4">
-        <v>1.77</v>
+        <v>1.655</v>
       </c>
       <c r="F20" s="4">
-        <v>0.13919340900790511</v>
+        <v>0.19194272788124389</v>
       </c>
       <c r="G20" s="4">
-        <v>2.0011722522919269</v>
+        <v>2</v>
       </c>
       <c r="H20" s="4">
-        <v>1.5840000000000001</v>
+        <v>1.27</v>
       </c>
       <c r="I20" s="4">
-        <v>1.9101172252291929</v>
+        <v>1.758454775215921</v>
       </c>
       <c r="J20" s="4">
-        <v>1.885</v>
+        <v>1.716720897478893</v>
       </c>
       <c r="K20" s="4">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="L20" s="4">
-        <v>1.5984</v>
+        <v>1.416981588135346</v>
       </c>
       <c r="M20" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B21" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="19">
-        <v>1.7086995002705141</v>
+        <v>1.694410408027718</v>
       </c>
       <c r="E21" s="19">
-        <v>1.67</v>
+        <v>1.7364751257208091</v>
       </c>
       <c r="F21" s="19">
-        <v>0.18043677832976041</v>
+        <v>0.2475553407787543</v>
       </c>
       <c r="G21" s="19">
-        <v>2.0309950027051382</v>
+        <v>2.152153475229968</v>
       </c>
       <c r="H21" s="19">
-        <v>1.496</v>
+        <v>1.349000353605591</v>
       </c>
       <c r="I21" s="19">
-        <v>1.913099500270514</v>
+        <v>1.9252153475229969</v>
       </c>
       <c r="J21" s="19">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="K21" s="19">
-        <v>1.575</v>
+        <v>1.5249999999999999</v>
       </c>
       <c r="L21" s="19">
-        <v>1.5176000000000001</v>
+        <v>1.367900035360559</v>
       </c>
       <c r="M21" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B22" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="4">
-        <v>1.648094619600178</v>
+        <v>1.5665720527955389</v>
       </c>
       <c r="E22" s="4">
-        <v>1.575</v>
+        <v>1.5851636827812881</v>
       </c>
       <c r="F22" s="4">
-        <v>0.2191106421493477</v>
+        <v>0.20546797248821089</v>
       </c>
       <c r="G22" s="4">
-        <v>2.1279461960017838</v>
+        <v>1.8</v>
       </c>
       <c r="H22" s="4">
-        <v>1.4079999999999999</v>
+        <v>1.264687831505241</v>
       </c>
       <c r="I22" s="4">
-        <v>1.8912946196001781</v>
+        <v>1.8</v>
       </c>
       <c r="J22" s="4">
-        <v>1.73</v>
+        <v>1.7551763327218941</v>
       </c>
       <c r="K22" s="4">
-        <v>1.5125</v>
+        <v>1.425</v>
       </c>
       <c r="L22" s="4">
-        <v>1.4368000000000001</v>
+        <v>1.269468783150524</v>
       </c>
       <c r="M22" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B23" s="17">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="19">
-        <v>1.5827427322734899</v>
+        <v>1.60213214509181</v>
       </c>
       <c r="E23" s="19">
-        <v>1.56</v>
+        <v>1.5851636827812881</v>
       </c>
       <c r="F23" s="19">
-        <v>0.1984315062297278</v>
+        <v>0.20499207339975881</v>
       </c>
       <c r="G23" s="19">
-        <v>1.902177322734899</v>
+        <v>1.9</v>
       </c>
       <c r="H23" s="19">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="I23" s="19">
-        <v>1.8419427322734889</v>
+        <v>1.81</v>
       </c>
       <c r="J23" s="19">
-        <v>1.6850000000000001</v>
+        <v>1.779260907237189</v>
       </c>
       <c r="K23" s="19">
-        <v>1.5075000000000001</v>
+        <v>1.449984656779455</v>
       </c>
       <c r="L23" s="19">
-        <v>1.3160000000000001</v>
+        <v>1.387</v>
       </c>
       <c r="M23" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B24" s="2">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="4">
-        <v>1.5958064637613349</v>
+        <v>1.6675506091879111</v>
       </c>
       <c r="E24" s="4">
-        <v>1.5649999999999999</v>
+        <v>1.709987725423564</v>
       </c>
       <c r="F24" s="4">
-        <v>0.16914962371173339</v>
+        <v>0.21855205974870209</v>
       </c>
       <c r="G24" s="4">
-        <v>1.809962499999999</v>
+        <v>2.1</v>
       </c>
       <c r="H24" s="4">
-        <v>1.28</v>
+        <v>1.384030389590363</v>
       </c>
       <c r="I24" s="4">
-        <v>1.8009962500000001</v>
+        <v>1.83</v>
       </c>
       <c r="J24" s="4">
-        <v>1.7500766032100079</v>
+        <v>1.766850188581214</v>
       </c>
       <c r="K24" s="4">
-        <v>1.5</v>
+        <v>1.4875</v>
       </c>
       <c r="L24" s="4">
-        <v>1.4690000000000001</v>
+        <v>1.3984030389590369</v>
       </c>
       <c r="M24" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B25" s="17">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="19">
-        <v>1.6813816026735111</v>
+        <v>1.598080268138947</v>
       </c>
       <c r="E25" s="19">
-        <v>1.7450000000000001</v>
+        <v>1.660491543516168</v>
       </c>
       <c r="F25" s="19">
-        <v>0.18160658539069191</v>
+        <v>0.22044952644086829</v>
       </c>
       <c r="G25" s="19">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H25" s="19">
-        <v>1.380147901735107</v>
+        <v>1.289981588135346</v>
       </c>
       <c r="I25" s="19">
-        <v>1.81568</v>
+        <v>1.855</v>
       </c>
       <c r="J25" s="19">
-        <v>1.7788510937499999</v>
+        <v>1.7305932515554461</v>
       </c>
       <c r="K25" s="19">
-        <v>1.5375000000000001</v>
+        <v>1.4175</v>
       </c>
       <c r="L25" s="19">
-        <v>1.488014790173511</v>
+        <v>1.2989981588135351</v>
       </c>
       <c r="M25" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B26" s="2">
-        <v>46418</v>
+        <v>46446</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="4">
-        <v>1.6572435483882899</v>
+        <v>1.522358284025418</v>
       </c>
       <c r="E26" s="4">
-        <v>1.63</v>
+        <v>1.527228132516711</v>
       </c>
       <c r="F26" s="4">
-        <v>0.24347367675150389</v>
+        <v>0.17696003643867811</v>
       </c>
       <c r="G26" s="4">
-        <v>2.1</v>
+        <v>1.7258273749999999</v>
       </c>
       <c r="H26" s="4">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="I26" s="4">
-        <v>2.0099999999999998</v>
+        <v>1.7025827375</v>
       </c>
       <c r="J26" s="4">
-        <v>1.745457824095725</v>
+        <v>1.6965626105017471</v>
       </c>
       <c r="K26" s="4">
-        <v>1.4970000000000001</v>
+        <v>1.355</v>
       </c>
       <c r="L26" s="4">
-        <v>1.4415</v>
+        <v>1.315343882392396</v>
       </c>
       <c r="M26" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B27" s="17" t="s">
         <v>14</v>
       </c>
@@ -7216,37 +6032,37 @@
         <v>47</v>
       </c>
       <c r="D27" s="19">
-        <v>20.910635077753721</v>
+        <v>20.18290562753868</v>
       </c>
       <c r="E27" s="19">
-        <v>20.952028159920399</v>
+        <v>20.119032478910508</v>
       </c>
       <c r="F27" s="19">
-        <v>2.3305978834516381</v>
+        <v>1.836432214585328</v>
       </c>
       <c r="G27" s="19">
-        <v>23.7</v>
+        <v>23.63</v>
       </c>
       <c r="H27" s="19">
-        <v>16.846391467136002</v>
+        <v>17.8</v>
       </c>
       <c r="I27" s="19">
-        <v>23.52</v>
+        <v>22.265912687592269</v>
       </c>
       <c r="J27" s="19">
-        <v>22.900980703311951</v>
+        <v>21.008873544364299</v>
       </c>
       <c r="K27" s="19">
-        <v>19.423887525990029</v>
+        <v>19.022741718936778</v>
       </c>
       <c r="L27" s="19">
-        <v>18.2716391467136</v>
+        <v>17.89</v>
       </c>
       <c r="M27" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B28" s="2" t="s">
         <v>36</v>
       </c>
@@ -7254,41 +6070,41 @@
         <v>16</v>
       </c>
       <c r="D28" s="4">
-        <v>27.565289279378199</v>
+        <v>27.579747156607581</v>
       </c>
       <c r="E28" s="4">
-        <v>27.45</v>
+        <v>27.82800912302206</v>
       </c>
       <c r="F28" s="4">
-        <v>1.034267004112092</v>
+        <v>1.107977817050362</v>
       </c>
       <c r="G28" s="4">
-        <v>29.151349718484251</v>
+        <v>28.9</v>
       </c>
       <c r="H28" s="4">
-        <v>25.918174815210332</v>
+        <v>25.63</v>
       </c>
       <c r="I28" s="4">
-        <v>28.902669966772951</v>
+        <v>28.855</v>
       </c>
       <c r="J28" s="4">
-        <v>28.282499999999999</v>
+        <v>28.281473530667689</v>
       </c>
       <c r="K28" s="4">
-        <v>26.812498912668399</v>
+        <v>26.700903699061509</v>
       </c>
       <c r="L28" s="4">
-        <v>26.6293152254731</v>
+        <v>26.27179790759568</v>
       </c>
       <c r="M28" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B30" s="22"/>
       <c r="C30" s="23"/>
     </row>
-    <row r="31" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="14" t="s">
         <v>35</v>
       </c>
@@ -7304,7 +6120,7 @@
       <c r="L31" s="14"/>
       <c r="M31" s="15"/>
     </row>
-    <row r="32" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B32" s="24" t="s">
         <v>1</v>
       </c>
@@ -7342,235 +6158,235 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B33" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C33" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D33" s="27">
-        <v>22.740509609184048</v>
+        <v>24.12438150289017</v>
       </c>
       <c r="E33" s="27">
-        <v>22.55</v>
+        <v>24.15</v>
       </c>
       <c r="F33" s="27">
-        <v>1.176748686323507</v>
+        <v>0.64225773199030145</v>
       </c>
       <c r="G33" s="27">
-        <v>25.313953364862879</v>
+        <v>25.333815028901721</v>
       </c>
       <c r="H33" s="27">
-        <v>21.37806981031099</v>
+        <v>23</v>
       </c>
       <c r="I33" s="27">
-        <v>24.131395336486289</v>
+        <v>24.67338150289017</v>
       </c>
       <c r="J33" s="27">
-        <v>22.95</v>
+        <v>24.45</v>
       </c>
       <c r="K33" s="27">
-        <v>22.074999999999999</v>
+        <v>23.827500000000001</v>
       </c>
       <c r="L33" s="27">
-        <v>21.499572606031101</v>
+        <v>23.45</v>
       </c>
       <c r="M33" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="26">
-        <v>22.60695162160934</v>
+        <v>23.751815502728789</v>
       </c>
       <c r="E34" s="26">
-        <v>22.8</v>
+        <v>23.55</v>
       </c>
       <c r="F34" s="26">
-        <v>1.3716928934609549</v>
+        <v>1.384012247829469</v>
       </c>
       <c r="G34" s="26">
-        <v>25.824582987707529</v>
+        <v>26.3</v>
       </c>
       <c r="H34" s="26">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I34" s="26">
-        <v>23.282458298770749</v>
+        <v>25.430433526011551</v>
       </c>
       <c r="J34" s="26">
-        <v>22.95</v>
+        <v>24.436084999596542</v>
       </c>
       <c r="K34" s="26">
-        <v>21.719520233789378</v>
+        <v>22.885000000000002</v>
       </c>
       <c r="L34" s="26">
-        <v>21.077015625000001</v>
+        <v>22</v>
       </c>
       <c r="M34" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B35" s="17">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C35" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D35" s="27">
-        <v>22.710917944833739</v>
+        <v>23.43698963273421</v>
       </c>
       <c r="E35" s="27">
-        <v>22.6</v>
+        <v>23.361554274323421</v>
       </c>
       <c r="F35" s="27">
-        <v>2.56122134919026</v>
+        <v>1.347221263298866</v>
       </c>
       <c r="G35" s="27">
-        <v>28.982258372729358</v>
+        <v>26.3</v>
       </c>
       <c r="H35" s="27">
-        <v>19.067560763888888</v>
+        <v>22</v>
       </c>
       <c r="I35" s="27">
-        <v>24.101650117820189</v>
+        <v>24.668109000825758</v>
       </c>
       <c r="J35" s="27">
-        <v>22.8</v>
+        <v>23.975000000000001</v>
       </c>
       <c r="K35" s="27">
-        <v>22.05</v>
+        <v>22.364999999999998</v>
       </c>
       <c r="L35" s="27">
-        <v>20.356756076388891</v>
+        <v>22</v>
       </c>
       <c r="M35" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B36" s="2">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D36" s="26">
-        <v>22.50009865759942</v>
+        <v>23.175470552686068</v>
       </c>
       <c r="E36" s="26">
-        <v>22.5</v>
+        <v>23.608381502890179</v>
       </c>
       <c r="F36" s="26">
-        <v>2.0561746097930329</v>
+        <v>1.180364946281407</v>
       </c>
       <c r="G36" s="26">
-        <v>25.641698340266782</v>
+        <v>24.577942521080359</v>
       </c>
       <c r="H36" s="26">
-        <v>19.067560763888888</v>
+        <v>21.5</v>
       </c>
       <c r="I36" s="26">
-        <v>25.596724558681341</v>
+        <v>24.327794252108038</v>
       </c>
       <c r="J36" s="26">
-        <v>22.8</v>
+        <v>24.074999999999999</v>
       </c>
       <c r="K36" s="26">
-        <v>22.024999999999999</v>
+        <v>22.14</v>
       </c>
       <c r="L36" s="26">
-        <v>19.906756076388891</v>
+        <v>21.5</v>
       </c>
       <c r="M36" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B37" s="17">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C37" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D37" s="27">
-        <v>22.485342559190109</v>
+        <v>22.708674197660521</v>
       </c>
       <c r="E37" s="27">
-        <v>22.8</v>
+        <v>23.19498948541246</v>
       </c>
       <c r="F37" s="27">
-        <v>2.2117017442021289</v>
+        <v>1.300390192801379</v>
       </c>
       <c r="G37" s="27">
-        <v>25.710320936233391</v>
+        <v>24.4</v>
       </c>
       <c r="H37" s="27">
-        <v>19.067560763888888</v>
+        <v>20.96</v>
       </c>
       <c r="I37" s="27">
-        <v>25.589021596224299</v>
+        <v>23.86</v>
       </c>
       <c r="J37" s="27">
-        <v>23.225000000000001</v>
+        <v>23.662572254335259</v>
       </c>
       <c r="K37" s="27">
-        <v>21.274999999999999</v>
+        <v>21.33</v>
       </c>
       <c r="L37" s="27">
-        <v>19.456756076388888</v>
+        <v>20.995999999999999</v>
       </c>
       <c r="M37" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
-        <v>46418</v>
+        <v>46446</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D38" s="26">
-        <v>21.907803558118712</v>
+        <v>22.485383014082629</v>
       </c>
       <c r="E38" s="26">
-        <v>22.05</v>
+        <v>22.725000000000001</v>
       </c>
       <c r="F38" s="26">
-        <v>2.5355116408557921</v>
+        <v>1.422008641111046</v>
       </c>
       <c r="G38" s="26">
-        <v>26.454814361485109</v>
+        <v>24.6</v>
       </c>
       <c r="H38" s="26">
-        <v>18.59087174479167</v>
+        <v>20.5</v>
       </c>
       <c r="I38" s="26">
-        <v>25.122406913612199</v>
+        <v>23.805086705202321</v>
       </c>
       <c r="J38" s="26">
-        <v>22.785799319727889</v>
+        <v>23.57176678376149</v>
       </c>
       <c r="K38" s="26">
-        <v>19.853697638593101</v>
+        <v>21.157499999999999</v>
       </c>
       <c r="L38" s="26">
-        <v>18.959087174479169</v>
+        <v>20.832999999999998</v>
       </c>
       <c r="M38" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B39" s="17" t="s">
         <v>14</v>
       </c>
@@ -7578,37 +6394,37 @@
         <v>49</v>
       </c>
       <c r="D39" s="27">
-        <v>23.184366885045531</v>
+        <v>29.08713935487204</v>
       </c>
       <c r="E39" s="27">
-        <v>22.203499999999998</v>
+        <v>26.335000000000001</v>
       </c>
       <c r="F39" s="27">
-        <v>4.7667192445907984</v>
+        <v>7.2441555727960836</v>
       </c>
       <c r="G39" s="27">
-        <v>34.7606076740121</v>
+        <v>41.681393548720443</v>
       </c>
       <c r="H39" s="27">
-        <v>19</v>
+        <v>20.37</v>
       </c>
       <c r="I39" s="27">
-        <v>27.8895158262001</v>
+        <v>40.168139354872046</v>
       </c>
       <c r="J39" s="27">
-        <v>23.75</v>
+        <v>32.337500000000013</v>
       </c>
       <c r="K39" s="27">
-        <v>20.07</v>
+        <v>24.024999999999999</v>
       </c>
       <c r="L39" s="27">
-        <v>19.170999999999999</v>
+        <v>22.736999999999998</v>
       </c>
       <c r="M39" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B40" s="2" t="s">
         <v>36</v>
       </c>
@@ -7616,41 +6432,41 @@
         <v>20</v>
       </c>
       <c r="D40" s="26">
-        <v>22.485342559190109</v>
+        <v>23.175470552686068</v>
       </c>
       <c r="E40" s="26">
-        <v>22.8</v>
+        <v>23.608381502890179</v>
       </c>
       <c r="F40" s="26">
-        <v>2.2117017442021289</v>
+        <v>1.180364946281407</v>
       </c>
       <c r="G40" s="26">
-        <v>25.710320936233391</v>
+        <v>24.577942521080359</v>
       </c>
       <c r="H40" s="26">
-        <v>19.067560763888888</v>
+        <v>21.5</v>
       </c>
       <c r="I40" s="26">
-        <v>25.589021596224299</v>
+        <v>24.327794252108038</v>
       </c>
       <c r="J40" s="26">
-        <v>23.225000000000001</v>
+        <v>24.074999999999999</v>
       </c>
       <c r="K40" s="26">
-        <v>21.274999999999999</v>
+        <v>22.14</v>
       </c>
       <c r="L40" s="26">
-        <v>19.456756076388888</v>
+        <v>21.5</v>
       </c>
       <c r="M40" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B41" s="22"/>
       <c r="C41" s="23"/>
     </row>
-    <row r="43" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B43" s="14" t="s">
         <v>21</v>
       </c>
@@ -7666,7 +6482,7 @@
       <c r="L43" s="14"/>
       <c r="M43" s="15"/>
     </row>
-    <row r="44" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B44" s="24" t="s">
         <v>1</v>
       </c>
@@ -7704,319 +6520,319 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B45" s="17">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C45" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D45" s="31">
-        <v>1507.8801390950621</v>
-      </c>
-      <c r="E45" s="31">
-        <v>1507.36687052142</v>
+      <c r="D45" s="29">
+        <v>1533.372358428699</v>
+      </c>
+      <c r="E45" s="29">
+        <v>1528.73</v>
       </c>
       <c r="F45" s="19">
-        <v>9.5000102384142533</v>
-      </c>
-      <c r="G45" s="31">
-        <v>1523.7</v>
-      </c>
-      <c r="H45" s="31">
-        <v>1493.941658614204</v>
-      </c>
-      <c r="I45" s="31">
-        <v>1523.209087069652</v>
-      </c>
-      <c r="J45" s="31">
-        <v>1509.3</v>
-      </c>
-      <c r="K45" s="31">
-        <v>1502.467862526267</v>
-      </c>
-      <c r="L45" s="31">
-        <v>1498.49416586142</v>
+        <v>27.212334933756729</v>
+      </c>
+      <c r="G45" s="29">
+        <v>1603.770007557921</v>
+      </c>
+      <c r="H45" s="29">
+        <v>1509</v>
+      </c>
+      <c r="I45" s="29">
+        <v>1547.277000755792</v>
+      </c>
+      <c r="J45" s="29">
+        <v>1537.7199561625</v>
+      </c>
+      <c r="K45" s="29">
+        <v>1517.118438019769</v>
+      </c>
+      <c r="L45" s="29">
+        <v>1509.9</v>
       </c>
       <c r="M45" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D46" s="30">
-        <v>1532.5083628305849</v>
-      </c>
-      <c r="E46" s="30">
-        <v>1531.47056810348</v>
+      <c r="D46" s="28">
+        <v>1569.9989773729169</v>
+      </c>
+      <c r="E46" s="28">
+        <v>1563.0795000000001</v>
       </c>
       <c r="F46" s="4">
-        <v>18.51374871200689</v>
-      </c>
-      <c r="G46" s="30">
-        <v>1561.8</v>
-      </c>
-      <c r="H46" s="30">
-        <v>1506</v>
-      </c>
-      <c r="I46" s="30">
-        <v>1561.252522330672</v>
-      </c>
-      <c r="J46" s="30">
-        <v>1539.2500128452141</v>
-      </c>
-      <c r="K46" s="30">
-        <v>1519.5130876200631</v>
-      </c>
-      <c r="L46" s="30">
-        <v>1513.2</v>
+        <v>43.53852067322736</v>
+      </c>
+      <c r="G46" s="28">
+        <v>1680.3063467217471</v>
+      </c>
+      <c r="H46" s="28">
+        <v>1517</v>
+      </c>
+      <c r="I46" s="28">
+        <v>1597.230634672175</v>
+      </c>
+      <c r="J46" s="28">
+        <v>1576.4629052857499</v>
+      </c>
+      <c r="K46" s="28">
+        <v>1548.343201466105</v>
+      </c>
+      <c r="L46" s="28">
+        <v>1542.2</v>
       </c>
       <c r="M46" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B47" s="17">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C47" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D47" s="31">
-        <v>1558.7468676493861</v>
-      </c>
-      <c r="E47" s="31">
-        <v>1556.133567761239</v>
+      <c r="D47" s="29">
+        <v>1604.684721973359</v>
+      </c>
+      <c r="E47" s="29">
+        <v>1594.3410899999999</v>
       </c>
       <c r="F47" s="19">
-        <v>30.758774211637281</v>
-      </c>
-      <c r="G47" s="31">
-        <v>1608.6</v>
-      </c>
-      <c r="H47" s="31">
-        <v>1514</v>
-      </c>
-      <c r="I47" s="31">
-        <v>1603.7691476731229</v>
-      </c>
-      <c r="J47" s="31">
-        <v>1572.9548320665681</v>
-      </c>
-      <c r="K47" s="31">
-        <v>1541.5720339343641</v>
-      </c>
-      <c r="L47" s="31">
-        <v>1523</v>
+        <v>56.088175335099073</v>
+      </c>
+      <c r="G47" s="29">
+        <v>1741.5446154094791</v>
+      </c>
+      <c r="H47" s="29">
+        <v>1524</v>
+      </c>
+      <c r="I47" s="29">
+        <v>1643.854461540948</v>
+      </c>
+      <c r="J47" s="29">
+        <v>1613.5294133914649</v>
+      </c>
+      <c r="K47" s="29">
+        <v>1582.25</v>
+      </c>
+      <c r="L47" s="29">
+        <v>1569.1464936824259</v>
       </c>
       <c r="M47" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D48" s="30">
-        <v>1582.821659286893</v>
-      </c>
-      <c r="E48" s="30">
-        <v>1580.3393048454191</v>
+      <c r="D48" s="28">
+        <v>1626.48626494837</v>
+      </c>
+      <c r="E48" s="28">
+        <v>1626.2159118</v>
       </c>
       <c r="F48" s="4">
-        <v>40.309619738875689</v>
-      </c>
-      <c r="G48" s="30">
-        <v>1642.783809353323</v>
-      </c>
-      <c r="H48" s="30">
-        <v>1520</v>
-      </c>
-      <c r="I48" s="30">
-        <v>1640.9983809353321</v>
-      </c>
-      <c r="J48" s="30">
-        <v>1606.0787659251939</v>
-      </c>
-      <c r="K48" s="30">
-        <v>1563.636864443379</v>
-      </c>
-      <c r="L48" s="30">
-        <v>1535.3</v>
+        <v>51.248961370693792</v>
+      </c>
+      <c r="G48" s="28">
+        <v>1723</v>
+      </c>
+      <c r="H48" s="28">
+        <v>1532</v>
+      </c>
+      <c r="I48" s="28">
+        <v>1684.3</v>
+      </c>
+      <c r="J48" s="28">
+        <v>1642.750051659295</v>
+      </c>
+      <c r="K48" s="28">
+        <v>1601.17765481163</v>
+      </c>
+      <c r="L48" s="28">
+        <v>1591.4</v>
       </c>
       <c r="M48" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B49" s="17">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C49" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D49" s="31">
-        <v>1605.3736448478039</v>
-      </c>
-      <c r="E49" s="31">
-        <v>1596.5</v>
+      <c r="D49" s="29">
+        <v>1652.0138487291549</v>
+      </c>
+      <c r="E49" s="29">
+        <v>1658.2940989932631</v>
       </c>
       <c r="F49" s="19">
-        <v>48.51780132257413</v>
-      </c>
-      <c r="G49" s="31">
-        <v>1673.6</v>
-      </c>
-      <c r="H49" s="31">
-        <v>1527</v>
-      </c>
-      <c r="I49" s="31">
-        <v>1672.2085514334069</v>
-      </c>
-      <c r="J49" s="31">
-        <v>1640.924247088029</v>
-      </c>
-      <c r="K49" s="31">
-        <v>1586.71141741003</v>
-      </c>
-      <c r="L49" s="31">
-        <v>1548.6</v>
+        <v>58.345028253218651</v>
+      </c>
+      <c r="G49" s="29">
+        <v>1756</v>
+      </c>
+      <c r="H49" s="29">
+        <v>1537</v>
+      </c>
+      <c r="I49" s="29">
+        <v>1717.3</v>
+      </c>
+      <c r="J49" s="29">
+        <v>1664.705508077353</v>
+      </c>
+      <c r="K49" s="29">
+        <v>1623.684069633804</v>
+      </c>
+      <c r="L49" s="29">
+        <v>1612.6</v>
       </c>
       <c r="M49" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B50" s="2">
-        <v>46418</v>
+        <v>46446</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D50" s="30">
-        <v>1627.1768483710771</v>
-      </c>
-      <c r="E50" s="30">
-        <v>1622.6</v>
+      <c r="D50" s="28">
+        <v>1676.987964890887</v>
+      </c>
+      <c r="E50" s="28">
+        <v>1679.43</v>
       </c>
       <c r="F50" s="4">
-        <v>55.316864450457317</v>
-      </c>
-      <c r="G50" s="30">
-        <v>1703.2</v>
-      </c>
-      <c r="H50" s="30">
-        <v>1532</v>
-      </c>
-      <c r="I50" s="30">
-        <v>1689.931494621102</v>
-      </c>
-      <c r="J50" s="30">
-        <v>1674.7719149730781</v>
-      </c>
-      <c r="K50" s="30">
-        <v>1608.657680108123</v>
-      </c>
-      <c r="L50" s="30">
-        <v>1559</v>
+        <v>65.210258652930619</v>
+      </c>
+      <c r="G50" s="28">
+        <v>1789</v>
+      </c>
+      <c r="H50" s="28">
+        <v>1543</v>
+      </c>
+      <c r="I50" s="28">
+        <v>1744</v>
+      </c>
+      <c r="J50" s="28">
+        <v>1702.316514132046</v>
+      </c>
+      <c r="K50" s="28">
+        <v>1648.153137617132</v>
+      </c>
+      <c r="L50" s="28">
+        <v>1633</v>
       </c>
       <c r="M50" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B51" s="17" t="s">
         <v>14</v>
       </c>
       <c r="C51" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="D51" s="31">
-        <v>1770.7747062220949</v>
-      </c>
-      <c r="E51" s="31">
-        <v>1766.2776468190859</v>
+      <c r="D51" s="29">
+        <v>1844.742131350431</v>
+      </c>
+      <c r="E51" s="29">
+        <v>1855.3499559982481</v>
       </c>
       <c r="F51" s="19">
-        <v>114.2284604342176</v>
-      </c>
-      <c r="G51" s="31">
-        <v>1925.137424294614</v>
-      </c>
-      <c r="H51" s="31">
-        <v>1575</v>
-      </c>
-      <c r="I51" s="31">
-        <v>1902.513742429461</v>
-      </c>
-      <c r="J51" s="31">
-        <v>1863.75</v>
-      </c>
-      <c r="K51" s="31">
-        <v>1706.01358607204</v>
-      </c>
-      <c r="L51" s="31">
-        <v>1637.1</v>
+        <v>120.54638682612079</v>
+      </c>
+      <c r="G51" s="29">
+        <v>2000</v>
+      </c>
+      <c r="H51" s="29">
+        <v>1604</v>
+      </c>
+      <c r="I51" s="29">
+        <v>1970.251548187591</v>
+      </c>
+      <c r="J51" s="29">
+        <v>1934.25</v>
+      </c>
+      <c r="K51" s="29">
+        <v>1779.236427641202</v>
+      </c>
+      <c r="L51" s="29">
+        <v>1735.4</v>
       </c>
       <c r="M51" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B52" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D52" s="30">
-        <v>1605.3736448478039</v>
-      </c>
-      <c r="E52" s="30">
-        <v>1596.5</v>
+      <c r="D52" s="28">
+        <v>1626.48626494837</v>
+      </c>
+      <c r="E52" s="28">
+        <v>1626.2159118</v>
       </c>
       <c r="F52" s="4">
-        <v>48.51780132257413</v>
-      </c>
-      <c r="G52" s="30">
-        <v>1673.6</v>
-      </c>
-      <c r="H52" s="30">
-        <v>1527</v>
-      </c>
-      <c r="I52" s="30">
-        <v>1672.2085514334069</v>
-      </c>
-      <c r="J52" s="30">
-        <v>1640.924247088029</v>
-      </c>
-      <c r="K52" s="30">
-        <v>1586.71141741003</v>
-      </c>
-      <c r="L52" s="30">
-        <v>1548.6</v>
+        <v>51.248961370693792</v>
+      </c>
+      <c r="G52" s="28">
+        <v>1723</v>
+      </c>
+      <c r="H52" s="28">
+        <v>1532</v>
+      </c>
+      <c r="I52" s="28">
+        <v>1684.3</v>
+      </c>
+      <c r="J52" s="28">
+        <v>1642.750051659295</v>
+      </c>
+      <c r="K52" s="28">
+        <v>1601.17765481163</v>
+      </c>
+      <c r="L52" s="28">
+        <v>1591.4</v>
       </c>
       <c r="M52" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B53" s="22"/>
       <c r="C53" s="23"/>
     </row>
-    <row r="54" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B54" s="22"/>
       <c r="C54" s="23"/>
     </row>
-    <row r="55" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B55" s="14" t="s">
         <v>24</v>
       </c>
@@ -8032,7 +6848,7 @@
       <c r="L55" s="14"/>
       <c r="M55" s="15"/>
     </row>
-    <row r="56" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B56" s="24" t="s">
         <v>1</v>
       </c>
@@ -8070,319 +6886,319 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B57" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C57" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D57" s="31">
-        <v>9114.3404774388182</v>
-      </c>
-      <c r="E57" s="31">
-        <v>9081.9729354166593</v>
-      </c>
-      <c r="F57" s="35">
-        <v>423.99503912923672</v>
-      </c>
-      <c r="G57" s="31">
-        <v>9678.0851647567706</v>
-      </c>
-      <c r="H57" s="31">
-        <v>8500</v>
-      </c>
-      <c r="I57" s="31">
-        <v>9543.6607470745421</v>
-      </c>
-      <c r="J57" s="31">
-        <v>9505.5775485693357</v>
-      </c>
-      <c r="K57" s="31">
-        <v>8789.0186439034987</v>
-      </c>
-      <c r="L57" s="31">
-        <v>8570.0239579836179</v>
+      <c r="D57" s="29">
+        <v>8942.4938493097943</v>
+      </c>
+      <c r="E57" s="29">
+        <v>8848.6267821955935</v>
+      </c>
+      <c r="F57" s="32">
+        <v>386.40878477922411</v>
+      </c>
+      <c r="G57" s="29">
+        <v>9517.3467062741001</v>
+      </c>
+      <c r="H57" s="29">
+        <v>8404.7362558228688</v>
+      </c>
+      <c r="I57" s="29">
+        <v>9456.7346706274093</v>
+      </c>
+      <c r="J57" s="29">
+        <v>9238.9736979310965</v>
+      </c>
+      <c r="K57" s="29">
+        <v>8730.8627770262374</v>
+      </c>
+      <c r="L57" s="29">
+        <v>8490.4736255822863</v>
       </c>
       <c r="M57" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B58" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D58" s="30">
-        <v>9109.7315467613553</v>
-      </c>
-      <c r="E58" s="30">
-        <v>9189.7669509685002</v>
-      </c>
-      <c r="F58" s="36">
-        <v>501.93836023526228</v>
-      </c>
-      <c r="G58" s="30">
-        <v>10165.564280137931</v>
-      </c>
-      <c r="H58" s="30">
+      <c r="D58" s="28">
+        <v>8743.0596537842739</v>
+      </c>
+      <c r="E58" s="28">
+        <v>8823.349687134878</v>
+      </c>
+      <c r="F58" s="33">
+        <v>304.3766391603798</v>
+      </c>
+      <c r="G58" s="28">
+        <v>9178.2174639187906</v>
+      </c>
+      <c r="H58" s="28">
+        <v>8334.9718004515689</v>
+      </c>
+      <c r="I58" s="28">
+        <v>9028.5386513218018</v>
+      </c>
+      <c r="J58" s="28">
+        <v>8957.0605188236259</v>
+      </c>
+      <c r="K58" s="28">
         <v>8500</v>
       </c>
-      <c r="I58" s="30">
-        <v>9473.2331295672157</v>
-      </c>
-      <c r="J58" s="30">
-        <v>9303.5</v>
-      </c>
-      <c r="K58" s="30">
-        <v>8717.4762353394162</v>
-      </c>
-      <c r="L58" s="30">
-        <v>8519.8044082094584</v>
+      <c r="L58" s="28">
+        <v>8346.1447618092443</v>
       </c>
       <c r="M58" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B59" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C59" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D59" s="31">
-        <v>8919.9310512758166</v>
-      </c>
-      <c r="E59" s="31">
-        <v>8720.2811940924967</v>
-      </c>
-      <c r="F59" s="35">
-        <v>729.06295504720492</v>
-      </c>
-      <c r="G59" s="31">
-        <v>10615.8881347724</v>
-      </c>
-      <c r="H59" s="31">
-        <v>8206</v>
-      </c>
-      <c r="I59" s="31">
-        <v>9566.5888134772395</v>
-      </c>
-      <c r="J59" s="31">
-        <v>9174.1388891008828</v>
-      </c>
-      <c r="K59" s="31">
-        <v>8427.039500883242</v>
-      </c>
-      <c r="L59" s="31">
-        <v>8240.2180240514335</v>
+      <c r="D59" s="29">
+        <v>8607.0722186560834</v>
+      </c>
+      <c r="E59" s="29">
+        <v>8663.239230799325</v>
+      </c>
+      <c r="F59" s="32">
+        <v>272.25760933408452</v>
+      </c>
+      <c r="G59" s="29">
+        <v>8956.3627324626104</v>
+      </c>
+      <c r="H59" s="29">
+        <v>8034.1336058320276</v>
+      </c>
+      <c r="I59" s="29">
+        <v>8859.7362732462607</v>
+      </c>
+      <c r="J59" s="29">
+        <v>8781.486309698932</v>
+      </c>
+      <c r="K59" s="29">
+        <v>8492.5</v>
+      </c>
+      <c r="L59" s="29">
+        <v>8331.8375022689943</v>
       </c>
       <c r="M59" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B60" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D60" s="30">
-        <v>8806.1279840867537</v>
-      </c>
-      <c r="E60" s="30">
-        <v>8596.5</v>
-      </c>
-      <c r="F60" s="36">
-        <v>829.37134977170081</v>
-      </c>
-      <c r="G60" s="30">
-        <v>10829.486808082331</v>
-      </c>
-      <c r="H60" s="30">
-        <v>7965.7426762584164</v>
-      </c>
-      <c r="I60" s="30">
-        <v>9497.9486808082329</v>
-      </c>
-      <c r="J60" s="30">
-        <v>8954.4658310675241</v>
-      </c>
-      <c r="K60" s="30">
-        <v>8377.2071660198308</v>
-      </c>
-      <c r="L60" s="30">
-        <v>8022.6742676258418</v>
+      <c r="D60" s="28">
+        <v>8182.4127646038269</v>
+      </c>
+      <c r="E60" s="28">
+        <v>8130.5</v>
+      </c>
+      <c r="F60" s="33">
+        <v>295.47803288173759</v>
+      </c>
+      <c r="G60" s="28">
+        <v>8771.3672105363639</v>
+      </c>
+      <c r="H60" s="28">
+        <v>7745.7071426302018</v>
+      </c>
+      <c r="I60" s="28">
+        <v>8469.9417696382734</v>
+      </c>
+      <c r="J60" s="28">
+        <v>8359.9341585768634</v>
+      </c>
+      <c r="K60" s="28">
+        <v>7981.5125000000007</v>
+      </c>
+      <c r="L60" s="28">
+        <v>7938.1033231528763</v>
       </c>
       <c r="M60" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B61" s="17">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C61" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D61" s="31">
-        <v>8286.0651784577567</v>
-      </c>
-      <c r="E61" s="31">
-        <v>7999.5</v>
-      </c>
-      <c r="F61" s="35">
-        <v>917.28745091576616</v>
-      </c>
-      <c r="G61" s="31">
-        <v>10754.40831195166</v>
-      </c>
-      <c r="H61" s="31">
-        <v>7629.7620461218703</v>
-      </c>
-      <c r="I61" s="31">
-        <v>8668.2458797798026</v>
-      </c>
-      <c r="J61" s="31">
-        <v>8391.4150847903547</v>
-      </c>
-      <c r="K61" s="31">
-        <v>7755.1429471978017</v>
-      </c>
-      <c r="L61" s="31">
-        <v>7663.276204612187</v>
+      <c r="D61" s="29">
+        <v>8109.4845577799397</v>
+      </c>
+      <c r="E61" s="29">
+        <v>8122.5587618701502</v>
+      </c>
+      <c r="F61" s="32">
+        <v>268.79150055607818</v>
+      </c>
+      <c r="G61" s="29">
+        <v>8502.2620200189995</v>
+      </c>
+      <c r="H61" s="29">
+        <v>7717.9235251819018</v>
+      </c>
+      <c r="I61" s="29">
+        <v>8363.4136806543502</v>
+      </c>
+      <c r="J61" s="29">
+        <v>8309.8996919714064</v>
+      </c>
+      <c r="K61" s="29">
+        <v>7955.9750000000004</v>
+      </c>
+      <c r="L61" s="29">
+        <v>7726.0923525181906</v>
       </c>
       <c r="M61" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B62" s="2">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D62" s="30">
-        <v>8306.5389876654008</v>
-      </c>
-      <c r="E62" s="30">
-        <v>8045.2406139619088</v>
-      </c>
-      <c r="F62" s="36">
-        <v>868.3848842026058</v>
-      </c>
-      <c r="G62" s="30">
-        <v>10431.305485114641</v>
-      </c>
-      <c r="H62" s="30">
-        <v>7563</v>
-      </c>
-      <c r="I62" s="30">
-        <v>9139.5305485114641</v>
-      </c>
-      <c r="J62" s="30">
-        <v>8453.0532673307825</v>
-      </c>
-      <c r="K62" s="30">
-        <v>7729.5903435107393</v>
-      </c>
-      <c r="L62" s="30">
-        <v>7588.2</v>
+      <c r="D62" s="28">
+        <v>7547.1756792723372</v>
+      </c>
+      <c r="E62" s="28">
+        <v>7446.7288479909612</v>
+      </c>
+      <c r="F62" s="33">
+        <v>311.60725454471662</v>
+      </c>
+      <c r="G62" s="28">
+        <v>8146.2669654310212</v>
+      </c>
+      <c r="H62" s="28">
+        <v>7253.54</v>
+      </c>
+      <c r="I62" s="28">
+        <v>8099.7881141503212</v>
+      </c>
+      <c r="J62" s="28">
+        <v>7499.5</v>
+      </c>
+      <c r="K62" s="28">
+        <v>7364.9702679510974</v>
+      </c>
+      <c r="L62" s="28">
+        <v>7332.2539999999999</v>
       </c>
       <c r="M62" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B63" s="17">
-        <v>46418</v>
+        <v>46446</v>
       </c>
       <c r="C63" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D63" s="31">
-        <v>7586.4408507856469</v>
-      </c>
-      <c r="E63" s="31">
-        <v>7518.194786058355</v>
-      </c>
-      <c r="F63" s="35">
-        <v>308.45947322842039</v>
-      </c>
-      <c r="G63" s="31">
-        <v>8000</v>
-      </c>
-      <c r="H63" s="31">
-        <v>7169.0639113038887</v>
-      </c>
-      <c r="I63" s="31">
-        <v>7935.3379749778187</v>
-      </c>
-      <c r="J63" s="31">
-        <v>7898.0114490970454</v>
-      </c>
-      <c r="K63" s="31">
-        <v>7335.2730569455662</v>
-      </c>
-      <c r="L63" s="31">
-        <v>7275.8311942243654</v>
+      <c r="D63" s="29">
+        <v>7470.9709195484702</v>
+      </c>
+      <c r="E63" s="29">
+        <v>7315.0475998612947</v>
+      </c>
+      <c r="F63" s="32">
+        <v>431.13918324003072</v>
+      </c>
+      <c r="G63" s="29">
+        <v>8222.9728441687239</v>
+      </c>
+      <c r="H63" s="29">
+        <v>6892.0223797461958</v>
+      </c>
+      <c r="I63" s="29">
+        <v>8185.7861654968674</v>
+      </c>
+      <c r="J63" s="29">
+        <v>7590</v>
+      </c>
+      <c r="K63" s="29">
+        <v>7223.5544813291772</v>
+      </c>
+      <c r="L63" s="29">
+        <v>7161.10223797462</v>
       </c>
       <c r="M63" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B64" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D64" s="30">
-        <v>101992.97942967351</v>
-      </c>
-      <c r="E64" s="30">
-        <v>100815.76885752979</v>
-      </c>
-      <c r="F64" s="36">
-        <v>4081.1492971389662</v>
-      </c>
-      <c r="G64" s="30">
-        <v>111928.73818481569</v>
-      </c>
-      <c r="H64" s="30">
-        <v>98305</v>
-      </c>
-      <c r="I64" s="30">
-        <v>105197.8738184816</v>
-      </c>
-      <c r="J64" s="30">
-        <v>103234.59117889369</v>
-      </c>
-      <c r="K64" s="30">
-        <v>99415.144878052757</v>
-      </c>
-      <c r="L64" s="30">
-        <v>98419.740005340602</v>
+      <c r="D64" s="28">
+        <v>100931.6041624865</v>
+      </c>
+      <c r="E64" s="28">
+        <v>101013.0587463344</v>
+      </c>
+      <c r="F64" s="33">
+        <v>1044.1485853044319</v>
+      </c>
+      <c r="G64" s="28">
+        <v>102443.722324923</v>
+      </c>
+      <c r="H64" s="28">
+        <v>99139.383071893215</v>
+      </c>
+      <c r="I64" s="28">
+        <v>102311.2151856815</v>
+      </c>
+      <c r="J64" s="28">
+        <v>101442.5</v>
+      </c>
+      <c r="K64" s="28">
+        <v>100266.9175</v>
+      </c>
+      <c r="L64" s="28">
+        <v>99741.729215842322</v>
       </c>
       <c r="M64" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B65" s="22"/>
       <c r="C65" s="23"/>
     </row>
-    <row r="66" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B66" s="22"/>
       <c r="C66" s="23"/>
     </row>
-    <row r="67" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B67" s="14" t="s">
         <v>26</v>
       </c>
@@ -8398,7 +7214,7 @@
       <c r="L67" s="14"/>
       <c r="M67" s="15"/>
     </row>
-    <row r="68" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B68" s="24" t="s">
         <v>1</v>
       </c>
@@ -8436,311 +7252,311 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B69" s="17">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C69" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D69" s="31">
-        <v>7052.268444832861</v>
-      </c>
-      <c r="E69" s="31">
-        <v>7086.5586521113273</v>
-      </c>
-      <c r="F69" s="35">
-        <v>147.26660529503931</v>
-      </c>
-      <c r="G69" s="31">
-        <v>7240</v>
-      </c>
-      <c r="H69" s="31">
-        <v>6824.7223639653439</v>
-      </c>
-      <c r="I69" s="31">
-        <v>7213.4711592670492</v>
-      </c>
-      <c r="J69" s="31">
-        <v>7161.3010275704482</v>
-      </c>
-      <c r="K69" s="31">
-        <v>6939.4098767351643</v>
-      </c>
-      <c r="L69" s="31">
-        <v>6851.0722363965342</v>
+      <c r="D69" s="29">
+        <v>6671.5038868856154</v>
+      </c>
+      <c r="E69" s="29">
+        <v>6682.9828563561423</v>
+      </c>
+      <c r="F69" s="32">
+        <v>215.5970424333623</v>
+      </c>
+      <c r="G69" s="29">
+        <v>6993.739525065801</v>
+      </c>
+      <c r="H69" s="29">
+        <v>6300.5714213348392</v>
+      </c>
+      <c r="I69" s="29">
+        <v>6909.3739525065803</v>
+      </c>
+      <c r="J69" s="29">
+        <v>6834.8771178530678</v>
+      </c>
+      <c r="K69" s="29">
+        <v>6517.6903037482134</v>
+      </c>
+      <c r="L69" s="29">
+        <v>6446.7571421334842</v>
       </c>
       <c r="M69" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B70" s="2">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D70" s="30">
-        <v>6861.260135845022</v>
-      </c>
-      <c r="E70" s="30">
-        <v>6947.2735061230705</v>
-      </c>
-      <c r="F70" s="36">
-        <v>254.07638626587669</v>
-      </c>
-      <c r="G70" s="30">
-        <v>7185.4036831541416</v>
-      </c>
-      <c r="H70" s="30">
-        <v>6463</v>
-      </c>
-      <c r="I70" s="30">
-        <v>7154.4403683154142</v>
-      </c>
-      <c r="J70" s="30">
-        <v>7000.0520201582476</v>
-      </c>
-      <c r="K70" s="30">
-        <v>6708.094705020806</v>
-      </c>
-      <c r="L70" s="30">
-        <v>6487.5283644978517</v>
+      <c r="D70" s="28">
+        <v>6688.6172333803597</v>
+      </c>
+      <c r="E70" s="28">
+        <v>6702.3227758513294</v>
+      </c>
+      <c r="F70" s="33">
+        <v>250.69963525724719</v>
+      </c>
+      <c r="G70" s="28">
+        <v>7191</v>
+      </c>
+      <c r="H70" s="28">
+        <v>6243.453754314799</v>
+      </c>
+      <c r="I70" s="28">
+        <v>6929.0999999999995</v>
+      </c>
+      <c r="J70" s="28">
+        <v>6766.4731769654272</v>
+      </c>
+      <c r="K70" s="28">
+        <v>6548.1374302196709</v>
+      </c>
+      <c r="L70" s="28">
+        <v>6501.5231473255362</v>
       </c>
       <c r="M70" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B71" s="17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C71" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D71" s="31">
-        <v>6966.3664834211204</v>
-      </c>
-      <c r="E71" s="31">
-        <v>6951</v>
-      </c>
-      <c r="F71" s="35">
-        <v>275.01669387206942</v>
-      </c>
-      <c r="G71" s="31">
-        <v>7456.0388043566936</v>
-      </c>
-      <c r="H71" s="31">
-        <v>6485.4398714765784</v>
-      </c>
-      <c r="I71" s="31">
-        <v>7233.4462662664873</v>
-      </c>
-      <c r="J71" s="31">
-        <v>7151.0708616009924</v>
-      </c>
-      <c r="K71" s="31">
-        <v>6802.0432063239496</v>
-      </c>
-      <c r="L71" s="31">
-        <v>6718.3941240442236</v>
+      <c r="D71" s="29">
+        <v>6629.7585425440166</v>
+      </c>
+      <c r="E71" s="29">
+        <v>6626.1894916938054</v>
+      </c>
+      <c r="F71" s="32">
+        <v>324.4099747121719</v>
+      </c>
+      <c r="G71" s="29">
+        <v>7150</v>
+      </c>
+      <c r="H71" s="29">
+        <v>6140.6295991137322</v>
+      </c>
+      <c r="I71" s="29">
+        <v>7015</v>
+      </c>
+      <c r="J71" s="29">
+        <v>6810.0230558463973</v>
+      </c>
+      <c r="K71" s="29">
+        <v>6440.3161782442403</v>
+      </c>
+      <c r="L71" s="29">
+        <v>6194.0629599113736</v>
       </c>
       <c r="M71" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B72" s="2">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D72" s="30">
-        <v>6876.9245646630707</v>
-      </c>
-      <c r="E72" s="30">
-        <v>6970.4853059699653</v>
-      </c>
-      <c r="F72" s="36">
-        <v>282.02666303803232</v>
-      </c>
-      <c r="G72" s="30">
-        <v>7167</v>
-      </c>
-      <c r="H72" s="30">
-        <v>6378.6304191872841</v>
-      </c>
-      <c r="I72" s="30">
-        <v>7151.7</v>
-      </c>
-      <c r="J72" s="30">
-        <v>7055.2577263323165</v>
-      </c>
-      <c r="K72" s="30">
-        <v>6800.1262268568407</v>
-      </c>
-      <c r="L72" s="30">
-        <v>6399.1140839594</v>
+      <c r="D72" s="28">
+        <v>6315.6534103547901</v>
+      </c>
+      <c r="E72" s="28">
+        <v>6270.3595706881752</v>
+      </c>
+      <c r="F72" s="33">
+        <v>710.8994268979352</v>
+      </c>
+      <c r="G72" s="28">
+        <v>7937</v>
+      </c>
+      <c r="H72" s="28">
+        <v>5598</v>
+      </c>
+      <c r="I72" s="28">
+        <v>6838.0015870834623</v>
+      </c>
+      <c r="J72" s="28">
+        <v>6599.3704904618307</v>
+      </c>
+      <c r="K72" s="28">
+        <v>5774.4900132659113</v>
+      </c>
+      <c r="L72" s="28">
+        <v>5602.3204316558295</v>
       </c>
       <c r="M72" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B73" s="17">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C73" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D73" s="31">
-        <v>6314.4925052379449</v>
-      </c>
-      <c r="E73" s="31">
-        <v>6189.6950963704776</v>
-      </c>
-      <c r="F73" s="35">
-        <v>513.29359349301615</v>
-      </c>
-      <c r="G73" s="31">
-        <v>7017.5111313089974</v>
-      </c>
-      <c r="H73" s="31">
-        <v>5598</v>
-      </c>
-      <c r="I73" s="31">
-        <v>6921.6511131308998</v>
-      </c>
-      <c r="J73" s="31">
-        <v>6811.6956058691312</v>
-      </c>
-      <c r="K73" s="31">
-        <v>5967.5413558882519</v>
-      </c>
-      <c r="L73" s="31">
-        <v>5777.9844984501206</v>
+      <c r="D73" s="29">
+        <v>6199.1064604519197</v>
+      </c>
+      <c r="E73" s="29">
+        <v>6196.5227742250117</v>
+      </c>
+      <c r="F73" s="32">
+        <v>635.86701779565044</v>
+      </c>
+      <c r="G73" s="29">
+        <v>7375</v>
+      </c>
+      <c r="H73" s="29">
+        <v>5292.9976039808453</v>
+      </c>
+      <c r="I73" s="29">
+        <v>6754</v>
+      </c>
+      <c r="J73" s="29">
+        <v>6617.4557720532921</v>
+      </c>
+      <c r="K73" s="29">
+        <v>5705.8246290902061</v>
+      </c>
+      <c r="L73" s="29">
+        <v>5529.6997603980844</v>
       </c>
       <c r="M73" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B74" s="2">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D74" s="30">
-        <v>6192.4733722954152</v>
-      </c>
-      <c r="E74" s="30">
-        <v>6090.3126635479784</v>
-      </c>
-      <c r="F74" s="36">
-        <v>548.51790196534876</v>
-      </c>
-      <c r="G74" s="30">
-        <v>7166.8561912724499</v>
-      </c>
-      <c r="H74" s="30">
-        <v>5498.1455859689804</v>
-      </c>
-      <c r="I74" s="30">
-        <v>6869.8391428213017</v>
-      </c>
-      <c r="J74" s="30">
-        <v>6520.5946453971292</v>
-      </c>
-      <c r="K74" s="30">
-        <v>5817.8548153073252</v>
-      </c>
-      <c r="L74" s="30">
-        <v>5550.2145585968983</v>
+      <c r="D74" s="28">
+        <v>5901.1231913239981</v>
+      </c>
+      <c r="E74" s="28">
+        <v>5800.4130261193113</v>
+      </c>
+      <c r="F74" s="33">
+        <v>625.31235832441371</v>
+      </c>
+      <c r="G74" s="28">
+        <v>6899</v>
+      </c>
+      <c r="H74" s="28">
+        <v>5208.71</v>
+      </c>
+      <c r="I74" s="28">
+        <v>6676.0834806162993</v>
+      </c>
+      <c r="J74" s="28">
+        <v>6421.7021777408336</v>
+      </c>
+      <c r="K74" s="28">
+        <v>5369.7876633000369</v>
+      </c>
+      <c r="L74" s="28">
+        <v>5247.906366537788</v>
       </c>
       <c r="M74" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B75" s="17">
-        <v>46418</v>
+        <v>46446</v>
       </c>
       <c r="C75" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D75" s="31">
-        <v>6045.903290695107</v>
-      </c>
-      <c r="E75" s="31">
-        <v>6056.6895694166778</v>
-      </c>
-      <c r="F75" s="35">
-        <v>567.59685298450904</v>
-      </c>
-      <c r="G75" s="31">
-        <v>6867.6903700676767</v>
-      </c>
-      <c r="H75" s="31">
-        <v>5208.71</v>
-      </c>
-      <c r="I75" s="31">
-        <v>6696.7248829728542</v>
-      </c>
-      <c r="J75" s="31">
-        <v>6453.0397606723736</v>
-      </c>
-      <c r="K75" s="31">
-        <v>5685.3280894338468</v>
-      </c>
-      <c r="L75" s="31">
-        <v>5247.9063665377889</v>
+      <c r="D75" s="29">
+        <v>5755.3487329506252</v>
+      </c>
+      <c r="E75" s="29">
+        <v>5494.01</v>
+      </c>
+      <c r="F75" s="32">
+        <v>614.7605783858221</v>
+      </c>
+      <c r="G75" s="29">
+        <v>6921</v>
+      </c>
+      <c r="H75" s="29">
+        <v>5147.5967615262862</v>
+      </c>
+      <c r="I75" s="29">
+        <v>6689.2439972800003</v>
+      </c>
+      <c r="J75" s="29">
+        <v>6041.0117926507028</v>
+      </c>
+      <c r="K75" s="29">
+        <v>5339.8696169076748</v>
+      </c>
+      <c r="L75" s="29">
+        <v>5295.4203521757809</v>
       </c>
       <c r="M75" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B76" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D76" s="30">
-        <v>75795.630999170651</v>
-      </c>
-      <c r="E76" s="30">
-        <v>76212.02726919188</v>
-      </c>
-      <c r="F76" s="36">
-        <v>1333.31111337934</v>
-      </c>
-      <c r="G76" s="30">
-        <v>77300</v>
-      </c>
-      <c r="H76" s="30">
-        <v>73837.831692513268</v>
-      </c>
-      <c r="I76" s="30">
-        <v>77133.956243715365</v>
-      </c>
-      <c r="J76" s="30">
-        <v>76786.187836806421</v>
-      </c>
-      <c r="K76" s="30">
-        <v>74625.5</v>
-      </c>
-      <c r="L76" s="30">
-        <v>73910.771540835049</v>
+      <c r="D76" s="28">
+        <v>74782.22564722992</v>
+      </c>
+      <c r="E76" s="28">
+        <v>74958.932291829173</v>
+      </c>
+      <c r="F76" s="33">
+        <v>1497.8625879036599</v>
+      </c>
+      <c r="G76" s="28">
+        <v>77315</v>
+      </c>
+      <c r="H76" s="28">
+        <v>72424.05963568583</v>
+      </c>
+      <c r="I76" s="28">
+        <v>76119.8</v>
+      </c>
+      <c r="J76" s="28">
+        <v>75733.770719805296</v>
+      </c>
+      <c r="K76" s="28">
+        <v>73718.98823628595</v>
+      </c>
+      <c r="L76" s="28">
+        <v>72942.405963568584</v>
       </c>
       <c r="M76" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:13" ht="18" x14ac:dyDescent="0.4">
       <c r="B77" s="9"/>
       <c r="C77" s="10"/>
       <c r="D77" s="10"/>
@@ -8754,7 +7570,7 @@
       <c r="L77" s="10"/>
       <c r="M77" s="10"/>
     </row>
-    <row r="79" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="14" t="s">
         <v>27</v>
       </c>
@@ -8770,7 +7586,7 @@
       <c r="L79" s="14"/>
       <c r="M79" s="15"/>
     </row>
-    <row r="80" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:13" ht="36" x14ac:dyDescent="0.35">
       <c r="B80" s="24" t="s">
         <v>1</v>
       </c>
@@ -8808,537 +7624,513 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B81" s="21" t="s">
+    <row r="81" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B81" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C81" s="18" t="s">
+      <c r="C81" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="32">
-        <v>15128.113060884471</v>
-      </c>
-      <c r="E81" s="32">
-        <v>14561.5</v>
-      </c>
-      <c r="F81" s="32">
-        <v>2717.8591949458</v>
-      </c>
-      <c r="G81" s="32">
+      <c r="D81" s="30">
+        <v>14663.682899428761</v>
+      </c>
+      <c r="E81" s="30">
+        <v>13802.5</v>
+      </c>
+      <c r="F81" s="30">
+        <v>2757.9934065013272</v>
+      </c>
+      <c r="G81" s="30">
         <v>21056</v>
       </c>
-      <c r="H81" s="32">
-        <v>11470</v>
-      </c>
-      <c r="I81" s="32">
-        <v>18060.421999999999</v>
-      </c>
-      <c r="J81" s="32">
-        <v>15845.3127745528</v>
-      </c>
-      <c r="K81" s="32">
-        <v>13786.63247273963</v>
-      </c>
-      <c r="L81" s="32">
-        <v>12657.601251209309</v>
-      </c>
-      <c r="M81" s="20">
+      <c r="H81" s="30">
+        <v>11809.8</v>
+      </c>
+      <c r="I81" s="30">
+        <v>17839.228999999999</v>
+      </c>
+      <c r="J81" s="30">
+        <v>15037.5</v>
+      </c>
+      <c r="K81" s="30">
+        <v>12854.42753149925</v>
+      </c>
+      <c r="L81" s="30">
+        <v>12476.864057059711</v>
+      </c>
+      <c r="M81" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D82" s="33">
-        <v>19429.486883779191</v>
-      </c>
-      <c r="E82" s="33">
-        <v>19575.5</v>
-      </c>
-      <c r="F82" s="33">
-        <v>2690.2428523222588</v>
-      </c>
-      <c r="G82" s="33">
-        <v>22542.95823806425</v>
-      </c>
-      <c r="H82" s="33">
-        <v>14500</v>
-      </c>
-      <c r="I82" s="33">
-        <v>22324.80882380643</v>
-      </c>
-      <c r="J82" s="33">
-        <v>21761.075000000001</v>
-      </c>
-      <c r="K82" s="33">
-        <v>18176.75</v>
-      </c>
-      <c r="L82" s="33">
-        <v>15894.136539754951</v>
-      </c>
-      <c r="M82" s="5">
+    <row r="82" spans="2:13" ht="18" x14ac:dyDescent="0.4">
+      <c r="B82" s="9"/>
+      <c r="C82" s="10"/>
+      <c r="D82" s="10"/>
+      <c r="E82" s="10"/>
+      <c r="F82" s="10"/>
+      <c r="G82" s="10"/>
+      <c r="H82" s="10"/>
+      <c r="I82" s="10"/>
+      <c r="J82" s="10"/>
+      <c r="K82" s="10"/>
+      <c r="L82" s="10"/>
+      <c r="M82" s="10"/>
+    </row>
+    <row r="83" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B83" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C83" s="14"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="14"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="14"/>
+      <c r="H83" s="14"/>
+      <c r="I83" s="14"/>
+      <c r="J83" s="14"/>
+      <c r="K83" s="14"/>
+      <c r="L83" s="14"/>
+      <c r="M83" s="15"/>
+    </row>
+    <row r="84" spans="2:13" ht="36" x14ac:dyDescent="0.35">
+      <c r="B84" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D84" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E84" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F84" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="G84" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H84" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="I84" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="J84" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="K84" s="24" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="83" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B83" s="9"/>
-      <c r="C83" s="10"/>
-      <c r="D83" s="10"/>
-      <c r="E83" s="10"/>
-      <c r="F83" s="10"/>
-      <c r="G83" s="10"/>
-      <c r="H83" s="10"/>
-      <c r="I83" s="10"/>
-      <c r="J83" s="10"/>
-      <c r="K83" s="10"/>
-      <c r="L83" s="10"/>
-      <c r="M83" s="10"/>
-    </row>
-    <row r="85" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B85" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C85" s="14"/>
-      <c r="D85" s="14"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
-      <c r="H85" s="14"/>
-      <c r="I85" s="14"/>
-      <c r="J85" s="14"/>
-      <c r="K85" s="14"/>
-      <c r="L85" s="14"/>
-      <c r="M85" s="15"/>
-    </row>
-    <row r="86" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B86" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C86" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D86" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="E86" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="F86" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="G86" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H86" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="I86" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="J86" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="K86" s="24" t="s">
+      <c r="L84" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="M84" s="25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B85" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C85" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D85" s="19">
+        <v>7.641</v>
+      </c>
+      <c r="E85" s="19">
+        <v>7.7</v>
+      </c>
+      <c r="F85" s="19">
+        <v>0.15680490355144441</v>
+      </c>
+      <c r="G85" s="19">
+        <v>7.9</v>
+      </c>
+      <c r="H85" s="19">
+        <v>7.4</v>
+      </c>
+      <c r="I85" s="19">
+        <v>7.81</v>
+      </c>
+      <c r="J85" s="19">
+        <v>7.7</v>
+      </c>
+      <c r="K85" s="19">
+        <v>7.5025000000000004</v>
+      </c>
+      <c r="L85" s="19">
+        <v>7.49</v>
+      </c>
+      <c r="M85" s="20">
         <v>10</v>
       </c>
-      <c r="L86" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="M86" s="25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="87" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B86" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D86" s="4">
+        <v>7.2840000000000007</v>
+      </c>
+      <c r="E86" s="4">
+        <v>7.4</v>
+      </c>
+      <c r="F86" s="4">
+        <v>0.43670992152177579</v>
+      </c>
+      <c r="G86" s="4">
+        <v>7.9</v>
+      </c>
+      <c r="H86" s="4">
+        <v>6.53</v>
+      </c>
+      <c r="I86" s="4">
+        <v>7.72</v>
+      </c>
+      <c r="J86" s="4">
+        <v>7.5824999999999996</v>
+      </c>
+      <c r="K86" s="4">
+        <v>6.95</v>
+      </c>
+      <c r="L86" s="4">
+        <v>6.7729999999999997</v>
+      </c>
+      <c r="M86" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B87" s="17" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C87" s="18" t="s">
         <v>30</v>
       </c>
       <c r="D87" s="19">
-        <v>7.6763692212322976</v>
+        <v>7.5730000000000004</v>
       </c>
       <c r="E87" s="19">
-        <v>7.7</v>
+        <v>7.55</v>
       </c>
       <c r="F87" s="19">
-        <v>0.2337202636337872</v>
+        <v>0.30572500352077481</v>
       </c>
       <c r="G87" s="19">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="H87" s="19">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="I87" s="19">
-        <v>7.92</v>
+        <v>8</v>
       </c>
       <c r="J87" s="19">
-        <v>7.7750000000000004</v>
+        <v>7.7149999999999999</v>
       </c>
       <c r="K87" s="19">
-        <v>7.5477691592422387</v>
+        <v>7.4250000000000007</v>
       </c>
       <c r="L87" s="19">
-        <v>7.3900000000000006</v>
+        <v>7.2789999999999999</v>
       </c>
       <c r="M87" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B88" s="6" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D88" s="4">
-        <v>7.3335048500175244</v>
+        <v>7.5730000000000004</v>
       </c>
       <c r="E88" s="4">
-        <v>7.4</v>
+        <v>7.55</v>
       </c>
       <c r="F88" s="4">
-        <v>0.62052165127716929</v>
+        <v>0.30572500352077481</v>
       </c>
       <c r="G88" s="4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="H88" s="4">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="I88" s="4">
-        <v>7.95</v>
+        <v>8</v>
       </c>
       <c r="J88" s="4">
-        <v>7.6775000000000002</v>
+        <v>7.7149999999999999</v>
       </c>
       <c r="K88" s="4">
-        <v>6.95</v>
+        <v>7.4250000000000007</v>
       </c>
       <c r="L88" s="4">
-        <v>6.5125436501577019</v>
+        <v>7.2789999999999999</v>
       </c>
       <c r="M88" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B89" s="17" t="s">
+    <row r="89" spans="2:13" ht="18" x14ac:dyDescent="0.4">
+      <c r="B89" s="9"/>
+      <c r="C89" s="9"/>
+      <c r="D89" s="9"/>
+      <c r="E89" s="9"/>
+      <c r="F89" s="9"/>
+      <c r="G89" s="9"/>
+      <c r="H89" s="9"/>
+      <c r="I89" s="9"/>
+      <c r="J89" s="9"/>
+      <c r="K89" s="9"/>
+      <c r="L89" s="9"/>
+      <c r="M89" s="9"/>
+    </row>
+    <row r="90" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B90" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C90" s="14"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="14"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="14"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="14"/>
+      <c r="J90" s="14"/>
+      <c r="K90" s="14"/>
+      <c r="L90" s="14"/>
+      <c r="M90" s="15"/>
+    </row>
+    <row r="91" spans="2:13" ht="36" x14ac:dyDescent="0.35">
+      <c r="B91" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C91" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D91" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H91" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="I91" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="K91" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="L91" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="M91" s="25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B92" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C92" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D92" s="19">
+        <v>-0.75782350207401761</v>
+      </c>
+      <c r="E92" s="19">
+        <v>-0.9</v>
+      </c>
+      <c r="F92" s="19">
+        <v>0.2324735923236271</v>
+      </c>
+      <c r="G92" s="19">
+        <v>-0.4</v>
+      </c>
+      <c r="H92" s="19">
+        <v>-0.99105533016186076</v>
+      </c>
+      <c r="I92" s="19">
+        <v>-0.44246172152048291</v>
+      </c>
+      <c r="J92" s="19">
+        <v>-0.53749999999999998</v>
+      </c>
+      <c r="K92" s="19">
+        <v>-0.93</v>
+      </c>
+      <c r="L92" s="19">
+        <v>-0.93610553301618615</v>
+      </c>
+      <c r="M92" s="20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B93" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D93" s="4">
+        <v>1.302975177778994</v>
+      </c>
+      <c r="E93" s="4">
+        <v>1.345</v>
+      </c>
+      <c r="F93" s="4">
+        <v>0.39197091065255252</v>
+      </c>
+      <c r="G93" s="4">
+        <v>2</v>
+      </c>
+      <c r="H93" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I93" s="4">
+        <v>1.674758482473713</v>
+      </c>
+      <c r="J93" s="4">
+        <v>1.48278281042701</v>
+      </c>
+      <c r="K93" s="4">
+        <v>1.1025</v>
+      </c>
+      <c r="L93" s="4">
+        <v>0.86999999999999988</v>
+      </c>
+      <c r="M93" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B94" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C89" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D89" s="19">
-        <v>7.673339213840161</v>
-      </c>
-      <c r="E89" s="19">
-        <v>7.6</v>
-      </c>
-      <c r="F89" s="19">
-        <v>0.47524936886544977</v>
-      </c>
-      <c r="G89" s="19">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="H89" s="19">
-        <v>7</v>
-      </c>
-      <c r="I89" s="19">
-        <v>8.07</v>
-      </c>
-      <c r="J89" s="19">
-        <v>7.93</v>
-      </c>
-      <c r="K89" s="19">
-        <v>7.4</v>
-      </c>
-      <c r="L89" s="19">
-        <v>7.2820529245614436</v>
-      </c>
-      <c r="M89" s="20">
+      <c r="C94" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D94" s="19">
+        <v>1.342080914602394</v>
+      </c>
+      <c r="E94" s="19">
+        <v>1.4850000000000001</v>
+      </c>
+      <c r="F94" s="19">
+        <v>0.5733523534838384</v>
+      </c>
+      <c r="G94" s="19">
+        <v>2</v>
+      </c>
+      <c r="H94" s="19">
+        <v>5.5301646023986351E-2</v>
+      </c>
+      <c r="I94" s="19">
+        <v>2</v>
+      </c>
+      <c r="J94" s="19">
+        <v>1.605</v>
+      </c>
+      <c r="K94" s="19">
+        <v>1.1138768749999901</v>
+      </c>
+      <c r="L94" s="19">
+        <v>0.81553016460239869</v>
+      </c>
+      <c r="M94" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B90" s="6" t="s">
+    <row r="95" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B95" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C90" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D90" s="4">
-        <v>7.673339213840161</v>
-      </c>
-      <c r="E90" s="4">
-        <v>7.6</v>
-      </c>
-      <c r="F90" s="4">
-        <v>0.47524936886544977</v>
-      </c>
-      <c r="G90" s="4">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="H90" s="4">
-        <v>7</v>
-      </c>
-      <c r="I90" s="4">
-        <v>8.07</v>
-      </c>
-      <c r="J90" s="4">
-        <v>7.93</v>
-      </c>
-      <c r="K90" s="4">
-        <v>7.4</v>
-      </c>
-      <c r="L90" s="4">
-        <v>7.2820529245614436</v>
-      </c>
-      <c r="M90" s="5">
+      <c r="C95" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D95" s="4">
+        <v>2.2084089636107729</v>
+      </c>
+      <c r="E95" s="4">
+        <v>2.1452942973514921</v>
+      </c>
+      <c r="F95" s="4">
+        <v>0.30610789089472301</v>
+      </c>
+      <c r="G95" s="4">
+        <v>3</v>
+      </c>
+      <c r="H95" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="I95" s="4">
+        <v>2.37</v>
+      </c>
+      <c r="J95" s="4">
+        <v>2.2708752603511861</v>
+      </c>
+      <c r="K95" s="4">
+        <v>2.0474999999999999</v>
+      </c>
+      <c r="L95" s="4">
+        <v>1.972</v>
+      </c>
+      <c r="M95" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="91" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B91" s="9"/>
-      <c r="C91" s="9"/>
-      <c r="D91" s="9"/>
-      <c r="E91" s="9"/>
-      <c r="F91" s="9"/>
-      <c r="G91" s="9"/>
-      <c r="H91" s="9"/>
-      <c r="I91" s="9"/>
-      <c r="J91" s="9"/>
-      <c r="K91" s="9"/>
-      <c r="L91" s="9"/>
-      <c r="M91" s="9"/>
-    </row>
-    <row r="93" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B93" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C93" s="14"/>
-      <c r="D93" s="14"/>
-      <c r="E93" s="14"/>
-      <c r="F93" s="14"/>
-      <c r="G93" s="14"/>
-      <c r="H93" s="14"/>
-      <c r="I93" s="14"/>
-      <c r="J93" s="14"/>
-      <c r="K93" s="14"/>
-      <c r="L93" s="14"/>
-      <c r="M93" s="15"/>
-    </row>
-    <row r="94" spans="2:13" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B94" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C94" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D94" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="E94" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="F94" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="G94" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H94" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="I94" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="J94" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="K94" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L94" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="M94" s="25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="95" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B95" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C95" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D95" s="19">
-        <v>-6.3147298146425432E-2</v>
-      </c>
-      <c r="E95" s="19">
-        <v>-0.39751634995482388</v>
-      </c>
-      <c r="F95" s="19">
-        <v>0.60988853256141229</v>
-      </c>
-      <c r="G95" s="19">
-        <v>0.8</v>
-      </c>
-      <c r="H95" s="19">
-        <v>-0.71</v>
-      </c>
-      <c r="I95" s="19">
-        <v>0.77620374660085412</v>
-      </c>
-      <c r="J95" s="19">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="K95" s="19">
-        <v>-0.5</v>
-      </c>
-      <c r="L95" s="19">
-        <v>-0.61099999999999999</v>
-      </c>
-      <c r="M95" s="20">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="96" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B96" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D96" s="4">
-        <v>1.1190725117402669</v>
-      </c>
-      <c r="E96" s="4">
-        <v>1.068889433634939</v>
-      </c>
-      <c r="F96" s="4">
-        <v>0.33329694681539151</v>
-      </c>
-      <c r="G96" s="4">
-        <v>1.7</v>
-      </c>
-      <c r="H96" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="I96" s="4">
-        <v>1.52</v>
-      </c>
-      <c r="J96" s="4">
-        <v>1.3922096875995911</v>
-      </c>
-      <c r="K96" s="4">
-        <v>0.8125</v>
-      </c>
-      <c r="L96" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="M96" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="97" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B97" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C97" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D97" s="19">
-        <v>1.036111500893466</v>
-      </c>
-      <c r="E97" s="19">
-        <v>0.95000000000000007</v>
-      </c>
-      <c r="F97" s="19">
-        <v>0.47354602969504173</v>
-      </c>
-      <c r="G97" s="19">
-        <v>2</v>
-      </c>
-      <c r="H97" s="19">
-        <v>0.28265188209330988</v>
-      </c>
-      <c r="I97" s="19">
-        <v>1.4330000000000001</v>
-      </c>
-      <c r="J97" s="19">
-        <v>1.284615781710337</v>
-      </c>
-      <c r="K97" s="19">
-        <v>0.77750000000000008</v>
-      </c>
-      <c r="L97" s="19">
-        <v>0.658265188209331</v>
-      </c>
-      <c r="M97" s="20">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98" spans="2:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B98" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D98" s="4">
-        <v>2.6367890567517511</v>
-      </c>
-      <c r="E98" s="4">
-        <v>2.7</v>
-      </c>
-      <c r="F98" s="4">
-        <v>0.34026924224694738</v>
-      </c>
-      <c r="G98" s="4">
-        <v>3</v>
-      </c>
-      <c r="H98" s="4">
-        <v>2.1</v>
-      </c>
-      <c r="I98" s="4">
-        <v>3</v>
-      </c>
-      <c r="J98" s="4">
-        <v>2.9421160542391349</v>
-      </c>
-      <c r="K98" s="4">
-        <v>2.4613018713989989</v>
-      </c>
-      <c r="L98" s="4">
-        <v>2.1269999999999998</v>
-      </c>
-      <c r="M98" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="99" spans="2:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B99" s="9" t="s">
+    <row r="96" spans="2:13" ht="18" x14ac:dyDescent="0.4">
+      <c r="B96" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C99" s="10"/>
-      <c r="D99" s="10"/>
-      <c r="E99" s="10"/>
-      <c r="F99" s="10"/>
-      <c r="G99" s="10"/>
-      <c r="H99" s="10"/>
-      <c r="I99" s="10"/>
-      <c r="J99" s="10"/>
-      <c r="K99" s="10"/>
-      <c r="L99" s="10"/>
-      <c r="M99" s="10"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="10"/>
+      <c r="E96" s="10"/>
+      <c r="F96" s="10"/>
+      <c r="G96" s="10"/>
+      <c r="H96" s="10"/>
+      <c r="I96" s="10"/>
+      <c r="J96" s="10"/>
+      <c r="K96" s="10"/>
+      <c r="L96" s="10"/>
+      <c r="M96" s="10"/>
+    </row>
+    <row r="97" spans="2:13" ht="18" x14ac:dyDescent="0.4">
+      <c r="B97" s="9"/>
+      <c r="C97" s="10"/>
+      <c r="D97" s="10"/>
+      <c r="E97" s="10"/>
+      <c r="F97" s="10"/>
+      <c r="G97" s="10"/>
+      <c r="H97" s="10"/>
+      <c r="I97" s="10"/>
+      <c r="J97" s="10"/>
+      <c r="K97" s="10"/>
+      <c r="L97" s="10"/>
+      <c r="M97" s="10"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -9348,7 +8140,7 @@
     <oddFooter>&amp;C&amp;"Roboto,Normal"Página &amp;P</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="36" max="16383" man="1"/>
+    <brk id="42" min="1" max="12" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -9359,9 +8151,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="16384" width="11.453125" style="1"/>
   </cols>
   <sheetData/>
   <sheetProtection algorithmName="SHA-512" hashValue="JI4mgXj1vwTu7GkfF4fWYFkbUu0jpGNsZzzBPX3YfGFuPzcxt+Hjcx6rfoqdT04OcRkZuwwlAbTLaGLAEKR43Q==" saltValue="AakVtiLN9zmEwInSrU9sOA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -9372,15 +8164,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004E1357DA6D65CA49A875959554824B49" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="e8f8602aebf7bbdcbcb5348c529dc11a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b80df5a0-8011-40eb-be96-4c6a59f56b6e" xmlns:ns3="6b042263-e944-4dfe-97a8-6e4c84e0ae4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a39dbf9ae3c20398b89cd584be7bda98" ns2:_="" ns3:_="">
     <xsd:import namespace="b80df5a0-8011-40eb-be96-4c6a59f56b6e"/>
@@ -9629,7 +8412,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="b80df5a0-8011-40eb-be96-4c6a59f56b6e">
@@ -9640,15 +8423,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E4A204-179E-478B-A62E-54900BF00ECD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89E97169-F966-43F7-97A7-EB3192694F7A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9667,19 +8451,27 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB7C2FA5-1A6F-45A0-B729-06C123F95F83}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6b042263-e944-4dfe-97a8-6e4c84e0ae4b"/>
     <ds:schemaRef ds:uri="b80df5a0-8011-40eb-be96-4c6a59f56b6e"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="6b042263-e944-4dfe-97a8-6e4c84e0ae4b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E4A204-179E-478B-A62E-54900BF00ECD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>